--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -47982,6 +47982,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2071">
+      <c r="A2071" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2071" t="n">
+        <v>2920</v>
+      </c>
+      <c r="C2071" t="n">
+        <v>8.92000007629395</v>
+      </c>
+      <c r="D2071" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="E2071" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="F2071" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="G2071" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -47990,7 +47990,7 @@
         <v>2920</v>
       </c>
       <c r="C2071" t="n">
-        <v>8.92000007629395</v>
+        <v>9.02000045776367</v>
       </c>
       <c r="D2071" t="n">
         <v>8.89999961853027</v>
@@ -48002,6 +48002,29 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G2071" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2072" t="n">
+        <v>660</v>
+      </c>
+      <c r="C2072" t="n">
+        <v>9.07999992370605</v>
+      </c>
+      <c r="D2072" t="n">
+        <v>8.97999954223633</v>
+      </c>
+      <c r="E2072" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2072" t="n">
+        <v>9.03999996185303</v>
+      </c>
+      <c r="G2072" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -48028,6 +48028,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2073">
+      <c r="A2073" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2073" t="n">
+        <v>4693</v>
+      </c>
+      <c r="C2073" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="D2073" t="n">
+        <v>8.84000015258789</v>
+      </c>
+      <c r="E2073" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="F2073" t="n">
+        <v>8.92000007629395</v>
+      </c>
+      <c r="G2073" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -48051,6 +48051,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2074">
+      <c r="A2074" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2074" t="n">
+        <v>2978</v>
+      </c>
+      <c r="C2074" t="n">
+        <v>8.9399995803833</v>
+      </c>
+      <c r="D2074" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="E2074" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="F2074" t="n">
+        <v>9.0600004196167</v>
+      </c>
+      <c r="G2074" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -47892,22 +47892,22 @@
     </row>
     <row r="2067">
       <c r="A2067" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2067" t="n">
-        <v>1222</v>
+        <v>401</v>
       </c>
       <c r="C2067" t="n">
-        <v>8.97999954223633</v>
+        <v>9.07999992370605</v>
       </c>
       <c r="D2067" t="n">
-        <v>8.89999961853027</v>
+        <v>8.9399995803833</v>
       </c>
       <c r="E2067" t="n">
-        <v>8.9399995803833</v>
+        <v>9.03999996185303</v>
       </c>
       <c r="F2067" t="n">
-        <v>8.97999954223633</v>
+        <v>9.07999992370605</v>
       </c>
       <c r="G2067" t="s">
         <v>7</v>
@@ -47915,22 +47915,22 @@
     </row>
     <row r="2068">
       <c r="A2068" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2068" t="n">
-        <v>2691</v>
+        <v>1222</v>
       </c>
       <c r="C2068" t="n">
-        <v>9.22000026702881</v>
+        <v>8.97999954223633</v>
       </c>
       <c r="D2068" t="n">
-        <v>8.9399995803833</v>
+        <v>8.89999961853027</v>
       </c>
       <c r="E2068" t="n">
         <v>8.9399995803833</v>
       </c>
       <c r="F2068" t="n">
-        <v>9.18000030517578</v>
+        <v>8.97999954223633</v>
       </c>
       <c r="G2068" t="s">
         <v>7</v>
@@ -47938,22 +47938,22 @@
     </row>
     <row r="2069">
       <c r="A2069" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2069" t="n">
-        <v>2069</v>
+        <v>2691</v>
       </c>
       <c r="C2069" t="n">
-        <v>9.07999992370605</v>
+        <v>9.22000026702881</v>
       </c>
       <c r="D2069" t="n">
-        <v>8.96000003814697</v>
+        <v>8.9399995803833</v>
       </c>
       <c r="E2069" t="n">
-        <v>9.0600004196167</v>
+        <v>8.9399995803833</v>
       </c>
       <c r="F2069" t="n">
-        <v>8.96000003814697</v>
+        <v>9.18000030517578</v>
       </c>
       <c r="G2069" t="s">
         <v>7</v>
@@ -47961,22 +47961,22 @@
     </row>
     <row r="2070">
       <c r="A2070" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2070" t="n">
-        <v>151</v>
+        <v>2069</v>
       </c>
       <c r="C2070" t="n">
-        <v>9.10000038146973</v>
+        <v>9.07999992370605</v>
       </c>
       <c r="D2070" t="n">
         <v>8.96000003814697</v>
       </c>
       <c r="E2070" t="n">
-        <v>9.10000038146973</v>
+        <v>9.0600004196167</v>
       </c>
       <c r="F2070" t="n">
-        <v>9.07999992370605</v>
+        <v>8.96000003814697</v>
       </c>
       <c r="G2070" t="s">
         <v>7</v>
@@ -47984,22 +47984,22 @@
     </row>
     <row r="2071">
       <c r="A2071" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2071" t="n">
-        <v>2920</v>
+        <v>151</v>
       </c>
       <c r="C2071" t="n">
-        <v>9.02000045776367</v>
+        <v>9.10000038146973</v>
       </c>
       <c r="D2071" t="n">
-        <v>8.89999961853027</v>
+        <v>8.96000003814697</v>
       </c>
       <c r="E2071" t="n">
-        <v>8.89999961853027</v>
+        <v>9.10000038146973</v>
       </c>
       <c r="F2071" t="n">
-        <v>9.02000045776367</v>
+        <v>9.07999992370605</v>
       </c>
       <c r="G2071" t="s">
         <v>7</v>
@@ -48007,22 +48007,22 @@
     </row>
     <row r="2072">
       <c r="A2072" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2072" t="n">
-        <v>660</v>
+        <v>2920</v>
       </c>
       <c r="C2072" t="n">
-        <v>9.07999992370605</v>
+        <v>9.02000045776367</v>
       </c>
       <c r="D2072" t="n">
-        <v>8.97999954223633</v>
+        <v>8.89999961853027</v>
       </c>
       <c r="E2072" t="n">
-        <v>9</v>
+        <v>8.89999961853027</v>
       </c>
       <c r="F2072" t="n">
-        <v>9.03999996185303</v>
+        <v>9.02000045776367</v>
       </c>
       <c r="G2072" t="s">
         <v>7</v>
@@ -48030,22 +48030,22 @@
     </row>
     <row r="2073">
       <c r="A2073" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2073" t="n">
-        <v>4693</v>
+        <v>660</v>
       </c>
       <c r="C2073" t="n">
-        <v>9.10000038146973</v>
+        <v>9.07999992370605</v>
       </c>
       <c r="D2073" t="n">
-        <v>8.84000015258789</v>
+        <v>8.97999954223633</v>
       </c>
       <c r="E2073" t="n">
-        <v>9.10000038146973</v>
+        <v>9</v>
       </c>
       <c r="F2073" t="n">
-        <v>8.92000007629395</v>
+        <v>9.03999996185303</v>
       </c>
       <c r="G2073" t="s">
         <v>7</v>
@@ -48053,24 +48053,47 @@
     </row>
     <row r="2074">
       <c r="A2074" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2074" t="n">
-        <v>2978</v>
+        <v>4693</v>
       </c>
       <c r="C2074" t="n">
-        <v>8.9399995803833</v>
+        <v>9.10000038146973</v>
       </c>
       <c r="D2074" t="n">
-        <v>8.77999973297119</v>
+        <v>8.84000015258789</v>
       </c>
       <c r="E2074" t="n">
-        <v>8.80000019073486</v>
+        <v>9.10000038146973</v>
       </c>
       <c r="F2074" t="n">
+        <v>8.92000007629395</v>
+      </c>
+      <c r="G2074" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2075" t="n">
+        <v>37666</v>
+      </c>
+      <c r="C2075" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="D2075" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E2075" t="n">
         <v>9.0600004196167</v>
       </c>
-      <c r="G2074" t="s">
+      <c r="F2075" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G2075" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G2" t="n">
-        <v>2.57321286201477</v>
+        <v>2.57321238517761</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.91050004959106</v>
       </c>
       <c r="G5" t="n">
-        <v>2.77382779121399</v>
+        <v>2.77382802963257</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.98749995231628</v>
       </c>
       <c r="G6" t="n">
-        <v>2.84721207618713</v>
+        <v>2.84721231460571</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84006428718567</v>
+        <v>2.84006452560425</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.97449994087219</v>
       </c>
       <c r="G10" t="n">
-        <v>2.83482241630554</v>
+        <v>2.83482265472412</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.9614999294281</v>
       </c>
       <c r="G11" t="n">
-        <v>2.82243323326111</v>
+        <v>2.82243275642395</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.98900008201599</v>
       </c>
       <c r="G13" t="n">
-        <v>2.84864187240601</v>
+        <v>2.84864163398743</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G14" t="n">
-        <v>2.76572680473328</v>
+        <v>2.76572704315186</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.97449994087219</v>
       </c>
       <c r="G16" t="n">
-        <v>2.83482241630554</v>
+        <v>2.83482265472412</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>2.70663857460022</v>
+        <v>2.7066388130188</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.70663857460022</v>
+        <v>2.7066388130188</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G29" t="n">
-        <v>2.61895823478699</v>
+        <v>2.61895871162415</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G35" t="n">
-        <v>2.67232871055603</v>
+        <v>2.67232894897461</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.67804741859436</v>
+        <v>2.67804765701294</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.05550003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>2.9120192527771</v>
+        <v>2.91201901435852</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01161193847656</v>
+        <v>3.01161217689514</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G54" t="n">
-        <v>2.96395969390869</v>
+        <v>2.96395993232727</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>2.9163076877594</v>
+        <v>2.91630792617798</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>2.9734902381897</v>
+        <v>2.97349047660828</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G60" t="n">
-        <v>2.9734902381897</v>
+        <v>2.97349047660828</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G63" t="n">
-        <v>2.88771653175354</v>
+        <v>2.88771677017212</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G69" t="n">
-        <v>2.84482979774475</v>
+        <v>2.84482955932617</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3</v>
       </c>
       <c r="G74" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3</v>
       </c>
       <c r="G75" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.89100003242493</v>
       </c>
       <c r="G78" t="n">
-        <v>2.75524401664734</v>
+        <v>2.75524353981018</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.90549993515015</v>
       </c>
       <c r="G80" t="n">
-        <v>2.76906275749207</v>
+        <v>2.76906299591064</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>2.77335166931152</v>
+        <v>2.77335143089294</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G83" t="n">
-        <v>2.88771653175354</v>
+        <v>2.88771677017212</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G85" t="n">
-        <v>2.92202591896057</v>
+        <v>2.92202615737915</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>2.9163076877594</v>
+        <v>2.91630792617798</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.99950003623962</v>
       </c>
       <c r="G87" t="n">
-        <v>2.85864901542664</v>
+        <v>2.85864877700806</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.04900002479553</v>
       </c>
       <c r="G88" t="n">
-        <v>2.9058244228363</v>
+        <v>2.90582418441772</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G89" t="n">
-        <v>2.85054779052734</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G90" t="n">
-        <v>2.85054779052734</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G91" t="n">
-        <v>2.85054779052734</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.93050003051758</v>
       </c>
       <c r="G92" t="n">
-        <v>2.792888879776</v>
+        <v>2.79288864135742</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.90899991989136</v>
       </c>
       <c r="G93" t="n">
-        <v>2.7723982334137</v>
+        <v>2.77239799499512</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.90899991989136</v>
       </c>
       <c r="G94" t="n">
-        <v>2.7723982334137</v>
+        <v>2.77239799499512</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G96" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.98850011825562</v>
       </c>
       <c r="G105" t="n">
-        <v>2.8481650352478</v>
+        <v>2.84816527366638</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G109" t="n">
-        <v>2.72045731544495</v>
+        <v>2.7204577922821</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G110" t="n">
-        <v>2.72045731544495</v>
+        <v>2.7204577922821</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G116" t="n">
-        <v>2.84959506988525</v>
+        <v>2.84959483146667</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.92549991607666</v>
       </c>
       <c r="G117" t="n">
-        <v>2.7881236076355</v>
+        <v>2.78812336921692</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G119" t="n">
-        <v>2.85436034202576</v>
+        <v>2.85436010360718</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3</v>
       </c>
       <c r="G121" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.92249989509583</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78526473045349</v>
+        <v>2.78526449203491</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3</v>
       </c>
       <c r="G141" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3</v>
       </c>
       <c r="G143" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.02950000762939</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88723993301392</v>
+        <v>2.8872401714325</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.00650000572205</v>
       </c>
       <c r="G145" t="n">
-        <v>2.86532020568848</v>
+        <v>2.8653199672699</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.00650000572205</v>
       </c>
       <c r="G147" t="n">
-        <v>2.86532020568848</v>
+        <v>2.8653199672699</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>2.9163076877594</v>
+        <v>2.91630792617798</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.24049997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>3.08833193778992</v>
+        <v>3.0883321762085</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>3.05926394462585</v>
+        <v>3.05926418304443</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.27649998664856</v>
       </c>
       <c r="G152" t="n">
-        <v>3.12264132499695</v>
+        <v>3.12264156341553</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G154" t="n">
-        <v>3.24987268447876</v>
+        <v>3.2498722076416</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.40949988365173</v>
       </c>
       <c r="G155" t="n">
-        <v>3.24939560890198</v>
+        <v>3.24939584732056</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G157" t="n">
-        <v>3.18315935134888</v>
+        <v>3.18315958976746</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.35349988937378</v>
       </c>
       <c r="G158" t="n">
-        <v>3.19602560997009</v>
+        <v>3.19602537155151</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>3.24034214019775</v>
+        <v>3.24034190177917</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.43549990653992</v>
       </c>
       <c r="G161" t="n">
-        <v>3.27417469024658</v>
+        <v>3.27417492866516</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G162" t="n">
-        <v>3.21175050735474</v>
+        <v>3.21175074577332</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.41700005531311</v>
       </c>
       <c r="G163" t="n">
-        <v>3.2565438747406</v>
+        <v>3.25654363632202</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>3.21175050735474</v>
+        <v>3.21175074577332</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>3.21175050735474</v>
+        <v>3.21175074577332</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.25463771820068</v>
+        <v>3.2546374797821</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.59450006484985</v>
       </c>
       <c r="G171" t="n">
-        <v>3.42570853233337</v>
+        <v>3.42570877075195</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>3.58343720436096</v>
+        <v>3.5834367275238</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.47860288619995</v>
+        <v>3.47860264778137</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G178" t="n">
-        <v>3.76451516151428</v>
+        <v>3.7645149230957</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>3.84075856208801</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>3.75498485565186</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G181" t="n">
-        <v>3.75498485565186</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G182" t="n">
-        <v>3.62155842781067</v>
+        <v>3.62155866622925</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G183" t="n">
-        <v>3.5453155040741</v>
+        <v>3.54531526565552</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>3.62155842781067</v>
+        <v>3.62155866622925</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G185" t="n">
-        <v>3.66921091079712</v>
+        <v>3.66921043395996</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G186" t="n">
-        <v>3.66921091079712</v>
+        <v>3.66921043395996</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G187" t="n">
-        <v>3.71686267852783</v>
+        <v>3.71686291694641</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>3.71686267852783</v>
+        <v>3.71686291694641</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>3.65014982223511</v>
+        <v>3.65015006065369</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>3.84075856208801</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G192" t="n">
-        <v>3.84075856208801</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>3.95512318611145</v>
+        <v>3.95512366294861</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4</v>
       </c>
       <c r="G194" t="n">
-        <v>3.81216669082642</v>
+        <v>3.812166929245</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4</v>
       </c>
       <c r="G195" t="n">
-        <v>3.81216669082642</v>
+        <v>3.812166929245</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>3.85028862953186</v>
+        <v>3.85028886795044</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>3.75498485565186</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>3.75498485565186</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G200" t="n">
-        <v>3.77414298057556</v>
+        <v>3.77414274215698</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83161664009094</v>
+        <v>3.83161687850952</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>3.8890917301178</v>
+        <v>3.88909149169922</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G206" t="n">
-        <v>3.80288028717041</v>
+        <v>3.80288004875183</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>3.77414298057556</v>
+        <v>3.77414274215698</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>3.83161664009094</v>
+        <v>3.83161687850952</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.93698692321777</v>
+        <v>3.93698668479919</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G218" t="n">
-        <v>3.9465651512146</v>
+        <v>3.94656491279602</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>4.02319765090942</v>
+        <v>4.02319812774658</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>4.03277683258057</v>
+        <v>4.03277730941772</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.21477842330933</v>
+        <v>4.21477890014648</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>4.10940933227539</v>
+        <v>4.10940885543823</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G223" t="n">
-        <v>4.1477255821228</v>
+        <v>4.14772510528564</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G225" t="n">
-        <v>4.39678049087524</v>
+        <v>4.39678001403809</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.5</v>
       </c>
       <c r="G227" t="n">
-        <v>4.31056976318359</v>
+        <v>4.31056928634644</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>4.38720178604126</v>
+        <v>4.3872013092041</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G231" t="n">
-        <v>4.48299217224121</v>
+        <v>4.48299169540405</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G232" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>4.69373083114624</v>
+        <v>4.6937313079834</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>4.66499328613281</v>
+        <v>4.66499376296997</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G237" t="n">
-        <v>4.96194362640381</v>
+        <v>4.96194410324097</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>4.80867862701416</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G241" t="n">
-        <v>4.94278621673584</v>
+        <v>4.94278573989868</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G249" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G250" t="n">
-        <v>4.65541410446167</v>
+        <v>4.65541458129883</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G251" t="n">
-        <v>4.65541410446167</v>
+        <v>4.65541458129883</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G256" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G257" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G258" t="n">
-        <v>4.48299217224121</v>
+        <v>4.48299169540405</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>4.6362566947937</v>
+        <v>4.63625717163086</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G260" t="n">
-        <v>4.66499328613281</v>
+        <v>4.66499376296997</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>4.66499328613281</v>
+        <v>4.66499376296997</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G262" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583587646484</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G264" t="n">
-        <v>4.69373083114624</v>
+        <v>4.6937313079834</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G265" t="n">
-        <v>4.69373083114624</v>
+        <v>4.6937313079834</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>4.69373083114624</v>
+        <v>4.6937313079834</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>4.59793996810913</v>
+        <v>4.59794092178345</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>4.59793996810913</v>
+        <v>4.59794092178345</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G269" t="n">
-        <v>4.59793996810913</v>
+        <v>4.59794092178345</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G271" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G272" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>4.57878255844116</v>
+        <v>4.578782081604</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>4.76078414916992</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G275" t="n">
-        <v>4.76078414916992</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G276" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>4.6266770362854</v>
+        <v>4.62667751312256</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G278" t="n">
-        <v>4.65541410446167</v>
+        <v>4.65541458129883</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G279" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G280" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583587646484</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583587646484</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G285" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G289" t="n">
-        <v>4.80867862701416</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>4.80867862701416</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>4.80867862701416</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>4.69373083114624</v>
+        <v>4.6937313079834</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G294" t="n">
-        <v>4.76078414916992</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G297" t="n">
-        <v>4.70330953598022</v>
+        <v>4.70330905914307</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>4.69373083114624</v>
+        <v>4.6937313079834</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G299" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>4.69373083114624</v>
+        <v>4.6937313079834</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G301" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G302" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G303" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G306" t="n">
-        <v>4.69373083114624</v>
+        <v>4.6937313079834</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>4.80867862701416</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G314" t="n">
-        <v>4.77994155883789</v>
+        <v>4.77994203567505</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.76078414916992</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>4.69373083114624</v>
+        <v>4.6937313079834</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>4.80867862701416</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.1343674659729</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>5.17268371582031</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.1152081489563</v>
+        <v>5.11520910263062</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>5.5</v>
       </c>
       <c r="G347" t="n">
-        <v>5.26847362518311</v>
+        <v>5.26847314834595</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.1343674659729</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G351" t="n">
-        <v>5.1343674659729</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G352" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G353" t="n">
-        <v>5.09605073928833</v>
+        <v>5.09605026245117</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>5.17268371582031</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>5.17268371582031</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G358" t="n">
-        <v>5.17268371582031</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G359" t="n">
-        <v>5.01941776275635</v>
+        <v>5.01941823959351</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.1343674659729</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>5.28763198852539</v>
+        <v>5.28763151168823</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>5.36426401138306</v>
+        <v>5.3642635345459</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G369" t="n">
-        <v>5.53668689727783</v>
+        <v>5.53668642044067</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G370" t="n">
-        <v>5.53668689727783</v>
+        <v>5.53668642044067</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>5.68995141983032</v>
+        <v>5.68995046615601</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>5.84321641921997</v>
+        <v>5.8432149887085</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6</v>
       </c>
       <c r="G375" t="n">
-        <v>5.74742603302002</v>
+        <v>5.7474250793457</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G376" t="n">
-        <v>5.91984796524048</v>
+        <v>5.91984844207764</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G377" t="n">
-        <v>5.90068912506104</v>
+        <v>5.90068960189819</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G379" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G384" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G386" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>5.82405805587769</v>
+        <v>5.82405853271484</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G391" t="n">
-        <v>5.91984796524048</v>
+        <v>5.91984844207764</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G393" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G394" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G395" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>6.07311296463013</v>
+        <v>6.07311344146729</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G401" t="n">
-        <v>6.36048412322998</v>
+        <v>6.36048364639282</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G404" t="n">
-        <v>6.39880037307739</v>
+        <v>6.39879989624023</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>6.36048412322998</v>
+        <v>6.36048364639282</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>6.41795778274536</v>
+        <v>6.41795825958252</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>6.5</v>
       </c>
       <c r="G409" t="n">
-        <v>6.22637701034546</v>
+        <v>6.22637748718262</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G414" t="n">
-        <v>6.07311296463013</v>
+        <v>6.07311344146729</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>6</v>
       </c>
       <c r="G416" t="n">
-        <v>5.74742603302002</v>
+        <v>5.7474250793457</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G417" t="n">
-        <v>5.90068912506104</v>
+        <v>5.90068960189819</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G419" t="n">
-        <v>5.90068912506104</v>
+        <v>5.90068960189819</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>5.70910930633545</v>
+        <v>5.70910978317261</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>5.70910930633545</v>
+        <v>5.70910978317261</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G424" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>6.07311296463013</v>
+        <v>6.07311344146729</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>6.30300951004028</v>
+        <v>6.30300998687744</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>6.41795778274536</v>
+        <v>6.41795825958252</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>6.41795778274536</v>
+        <v>6.41795825958252</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>6.64785575866699</v>
+        <v>6.64785480499268</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G444" t="n">
-        <v>6.78196239471436</v>
+        <v>6.78196144104004</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>6.9927020072937</v>
+        <v>6.99270153045654</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>7.5</v>
       </c>
       <c r="G447" t="n">
-        <v>7.18428230285645</v>
+        <v>7.1842827796936</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G448" t="n">
-        <v>7.50996923446655</v>
+        <v>7.50996971130371</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G449" t="n">
-        <v>7.79734182357788</v>
+        <v>7.79734086990356</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G450" t="n">
-        <v>7.68239212036133</v>
+        <v>7.68239259719849</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G451" t="n">
-        <v>8.00807857513428</v>
+        <v>8.00807952880859</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>8.13305473327637</v>
+        <v>8.13305568695068</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.5</v>
       </c>
       <c r="G454" t="n">
-        <v>8.17150974273682</v>
+        <v>8.17151069641113</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537460327148</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G457" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537460327148</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.5</v>
       </c>
       <c r="G458" t="n">
-        <v>8.17150974273682</v>
+        <v>8.17151069641113</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>8.13305473327637</v>
+        <v>8.13305568695068</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G461" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537460327148</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537460327148</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>7.53701543807983</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>7.22938251495361</v>
+        <v>7.22938203811646</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>7.3255181312561</v>
+        <v>7.32551765441895</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G469" t="n">
-        <v>7.26783657073975</v>
+        <v>7.2678370475769</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>7.5</v>
       </c>
       <c r="G471" t="n">
-        <v>7.21015548706055</v>
+        <v>7.21015596389771</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.5</v>
       </c>
       <c r="G473" t="n">
-        <v>7.21015548706055</v>
+        <v>7.21015596389771</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G474" t="n">
-        <v>7.07556629180908</v>
+        <v>7.07556581497192</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G477" t="n">
-        <v>7.57546997070312</v>
+        <v>7.57546949386597</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>7.57546997070312</v>
+        <v>7.57546949386597</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315200805664</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>7.57546997070312</v>
+        <v>7.57546949386597</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>7.57546997070312</v>
+        <v>7.57546949386597</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G492" t="n">
-        <v>7.57546997070312</v>
+        <v>7.57546949386597</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G493" t="n">
-        <v>7.57546997070312</v>
+        <v>7.57546949386597</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>7.53701543807983</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>7.53701543807983</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G496" t="n">
-        <v>7.51778936386108</v>
+        <v>7.51778888702393</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G497" t="n">
-        <v>7.53701543807983</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315200805664</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G502" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315200805664</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G510" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G511" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9</v>
       </c>
       <c r="G512" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G513" t="n">
-        <v>8.74832153320312</v>
+        <v>8.74832248687744</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>9.24822616577148</v>
+        <v>9.24822521209717</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G518" t="n">
-        <v>9.305908203125</v>
+        <v>9.30590915679932</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G519" t="n">
-        <v>9.305908203125</v>
+        <v>9.30590915679932</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G521" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G523" t="n">
-        <v>9.47895240783691</v>
+        <v>9.4789514541626</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G524" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G525" t="n">
-        <v>9.34436225891113</v>
+        <v>9.34436130523682</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G527" t="n">
-        <v>9.01750087738037</v>
+        <v>9.01750183105469</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G530" t="n">
-        <v>8.70986747741699</v>
+        <v>8.70986843109131</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G532" t="n">
-        <v>9.07518291473389</v>
+        <v>9.07518196105957</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G538" t="n">
-        <v>8.74832153320312</v>
+        <v>8.74832248687744</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>8.69064044952393</v>
+        <v>8.69063949584961</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>9</v>
       </c>
       <c r="G540" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9</v>
       </c>
       <c r="G542" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>8.61373138427734</v>
+        <v>8.61373233795166</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G545" t="n">
-        <v>8.26764583587646</v>
+        <v>8.26764678955078</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G559" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G560" t="n">
-        <v>8.59450531005859</v>
+        <v>8.59450340270996</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G567" t="n">
-        <v>9.19054508209229</v>
+        <v>9.19054412841797</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G568" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G569" t="n">
-        <v>9.28668022155762</v>
+        <v>9.2866792678833</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G570" t="n">
-        <v>9.03672695159912</v>
+        <v>9.03672790527344</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G571" t="n">
-        <v>9.07518291473389</v>
+        <v>9.07518196105957</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>9.07518291473389</v>
+        <v>9.07518196105957</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G574" t="n">
-        <v>9.01750087738037</v>
+        <v>9.01750183105469</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>9</v>
       </c>
       <c r="G576" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G582" t="n">
-        <v>8.70986747741699</v>
+        <v>8.70986843109131</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9</v>
       </c>
       <c r="G584" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.69064044952393</v>
+        <v>8.69063949584961</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>8.74832153320312</v>
+        <v>8.74832248687744</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G587" t="n">
-        <v>8.70986747741699</v>
+        <v>8.70986843109131</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G588" t="n">
-        <v>8.70986747741699</v>
+        <v>8.70986843109131</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G589" t="n">
-        <v>8.67141246795654</v>
+        <v>8.67141342163086</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>9</v>
       </c>
       <c r="G590" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>9</v>
       </c>
       <c r="G591" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G592" t="n">
-        <v>8.59450531005859</v>
+        <v>8.59450340270996</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9</v>
       </c>
       <c r="G593" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>9.32513523101807</v>
+        <v>9.32513427734375</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G600" t="n">
-        <v>9.34436225891113</v>
+        <v>9.34436130523682</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G601" t="n">
-        <v>9.15209102630615</v>
+        <v>9.15209007263184</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>9.32513523101807</v>
+        <v>9.32513427734375</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G606" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22900104522705</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G608" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G613" t="n">
-        <v>9.15209102630615</v>
+        <v>9.15209007263184</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G616" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22900104522705</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G617" t="n">
-        <v>9.15209102630615</v>
+        <v>9.15209007263184</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G619" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22900104522705</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G620" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22900104522705</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G622" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22900104522705</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G623" t="n">
-        <v>9.44049644470215</v>
+        <v>9.44049549102783</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G624" t="n">
-        <v>9.42126941680908</v>
+        <v>9.4212703704834</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>9.75774383544922</v>
+        <v>9.75774478912354</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>10.5</v>
       </c>
       <c r="G627" t="n">
-        <v>10.094217300415</v>
+        <v>10.0942163467407</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G628" t="n">
-        <v>10.2864894866943</v>
+        <v>10.28648853302</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>10.2864894866943</v>
+        <v>10.28648853302</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G630" t="n">
-        <v>10.2864894866943</v>
+        <v>10.28648853302</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>10.1422863006592</v>
+        <v>10.1422853469849</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G632" t="n">
-        <v>10.1422863006592</v>
+        <v>10.1422853469849</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>10.5</v>
       </c>
       <c r="G633" t="n">
-        <v>10.094217300415</v>
+        <v>10.0942163467407</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>9.9500150680542</v>
+        <v>9.95001411437988</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>10.5</v>
       </c>
       <c r="G635" t="n">
-        <v>10.094217300415</v>
+        <v>10.0942163467407</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G636" t="n">
-        <v>10.0461483001709</v>
+        <v>10.0461492538452</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>10.5</v>
       </c>
       <c r="G637" t="n">
-        <v>10.094217300415</v>
+        <v>10.0942163467407</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>10.2864894866943</v>
+        <v>10.28648853302</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>10.5268268585205</v>
+        <v>10.5268278121948</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>10.4787588119507</v>
+        <v>10.4787578582764</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>10.3826246261597</v>
+        <v>10.3826236724854</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G645" t="n">
-        <v>10.3826246261597</v>
+        <v>10.3826236724854</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>10.4787588119507</v>
+        <v>10.4787578582764</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>10.767165184021</v>
+        <v>10.7671642303467</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>11.5</v>
       </c>
       <c r="G651" t="n">
-        <v>11.0555725097656</v>
+        <v>11.0555715560913</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>11.5</v>
       </c>
       <c r="G652" t="n">
-        <v>11.0555725097656</v>
+        <v>11.0555715560913</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>12.5</v>
       </c>
       <c r="G655" t="n">
-        <v>12.0169258117676</v>
+        <v>12.0169267654419</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G658" t="n">
-        <v>12.5937376022339</v>
+        <v>12.5937385559082</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>12.5937376022339</v>
+        <v>12.5937385559082</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G663" t="n">
-        <v>12.7860088348389</v>
+        <v>12.7860097885132</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G664" t="n">
-        <v>12.8821449279785</v>
+        <v>12.8821439743042</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>12.6418056488037</v>
+        <v>12.641806602478</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>12.7860088348389</v>
+        <v>12.7860097885132</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>12.7860088348389</v>
+        <v>12.7860097885132</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>12.7860088348389</v>
+        <v>12.7860097885132</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>12.5937376022339</v>
+        <v>12.5937385559082</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G674" t="n">
-        <v>13.507022857666</v>
+        <v>13.5070238113403</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>14.5</v>
       </c>
       <c r="G675" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>14.5</v>
       </c>
       <c r="G676" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>14.5</v>
       </c>
       <c r="G677" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>13.795431137085</v>
+        <v>13.7954301834106</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>13.507022857666</v>
+        <v>13.5070238113403</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838356018066</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838356018066</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G687" t="n">
-        <v>13.9877014160156</v>
+        <v>13.9877004623413</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>13.795431137085</v>
+        <v>13.7954301834106</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>14.5</v>
       </c>
       <c r="G690" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>14.5</v>
       </c>
       <c r="G691" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>13.7473630905151</v>
+        <v>13.7473640441895</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G701" t="n">
-        <v>13.7473630905151</v>
+        <v>13.7473640441895</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>13.9877014160156</v>
+        <v>13.9877004623413</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838356018066</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838356018066</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>14.3631277084351</v>
+        <v>14.3631267547607</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>15.9536714553833</v>
+        <v>15.9536752700806</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G713" t="n">
-        <v>16.6766510009766</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910614013672</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>16.5802555084229</v>
+        <v>16.5802574157715</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>16.8212490081787</v>
+        <v>16.8212471008301</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>17</v>
       </c>
       <c r="G725" t="n">
-        <v>16.3874588012695</v>
+        <v>16.3874607086182</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910614013672</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>16.5802555084229</v>
+        <v>16.5802574157715</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G733" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910614013672</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>16.1946659088135</v>
+        <v>16.1946678161621</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>16.0982723236084</v>
+        <v>16.0982685089111</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>16.1946659088135</v>
+        <v>16.1946678161621</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>16.0982723236084</v>
+        <v>16.0982685089111</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G740" t="n">
-        <v>15.2306985855103</v>
+        <v>15.2306995391846</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>15.3752927780151</v>
+        <v>15.3752937316895</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>15.2788963317871</v>
+        <v>15.2788972854614</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G746" t="n">
-        <v>15.2306985855103</v>
+        <v>15.2306995391846</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G748" t="n">
-        <v>14.8933095932007</v>
+        <v>14.8933086395264</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G750" t="n">
-        <v>14.8933095932007</v>
+        <v>14.8933086395264</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>15.2788963317871</v>
+        <v>15.2788972854614</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>15.2306985855103</v>
+        <v>15.2306995391846</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G755" t="n">
-        <v>15.3752927780151</v>
+        <v>15.3752937316895</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>15.2788963317871</v>
+        <v>15.2788972854614</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G758" t="n">
-        <v>15.8572788238525</v>
+        <v>15.8572778701782</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>15.7126817703247</v>
+        <v>15.7126798629761</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>15.6162853240967</v>
+        <v>15.616286277771</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G761" t="n">
-        <v>15.4716901779175</v>
+        <v>15.4716892242432</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G764" t="n">
-        <v>15.6162853240967</v>
+        <v>15.616286277771</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>15.6162853240967</v>
+        <v>15.616286277771</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G770" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910614013672</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>18</v>
       </c>
       <c r="G774" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>17.158634185791</v>
+        <v>17.1586322784424</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G778" t="n">
-        <v>16.8212490081787</v>
+        <v>16.8212471008301</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G779" t="n">
-        <v>16.6766510009766</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>16.6766510009766</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>16.6766510009766</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G788" t="n">
-        <v>17.2550296783447</v>
+        <v>17.2550315856934</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>17.2550296783447</v>
+        <v>17.2550315856934</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>17.158634185791</v>
+        <v>17.1586322784424</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>17.75</v>
       </c>
       <c r="G795" t="n">
-        <v>17.1104373931885</v>
+        <v>17.1104354858398</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G796" t="n">
-        <v>17.2550296783447</v>
+        <v>17.2550315856934</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>17.6888179779053</v>
+        <v>17.6888160705566</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2671985626221</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>18.700984954834</v>
+        <v>18.7009830474854</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G806" t="n">
-        <v>18.6527843475342</v>
+        <v>18.6527862548828</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>18.5081901550293</v>
+        <v>18.5081920623779</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G811" t="n">
-        <v>18.4117965698242</v>
+        <v>18.4117946624756</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2671985626221</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2671985626221</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>18.2189979553223</v>
+        <v>18.2189998626709</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2671985626221</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>17.9780082702637</v>
+        <v>17.978006362915</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2671985626221</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>17.6888179779053</v>
+        <v>17.6888160705566</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>18.1226005554199</v>
+        <v>18.1226024627686</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G833" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2671985626221</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406173706055</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>18.5</v>
       </c>
       <c r="G839" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334121704102</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406173706055</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406173706055</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406173706055</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>18.5</v>
       </c>
       <c r="G848" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334121704102</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>17.6888179779053</v>
+        <v>17.6888160705566</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>17.4960231781006</v>
+        <v>17.496021270752</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>18</v>
       </c>
       <c r="G851" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G852" t="n">
-        <v>17.5442218780518</v>
+        <v>17.5442237854004</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G853" t="n">
-        <v>17.9780082702637</v>
+        <v>17.978006362915</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>18</v>
       </c>
       <c r="G855" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>18.5</v>
       </c>
       <c r="G858" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334121704102</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>18.25</v>
       </c>
       <c r="G859" t="n">
-        <v>17.5924205780029</v>
+        <v>17.5924224853516</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>18.25</v>
       </c>
       <c r="G860" t="n">
-        <v>17.5924205780029</v>
+        <v>17.5924224853516</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>18</v>
       </c>
       <c r="G862" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>18</v>
       </c>
       <c r="G863" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G866" t="n">
-        <v>17.4960231781006</v>
+        <v>17.496021270752</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G867" t="n">
-        <v>17.5442218780518</v>
+        <v>17.5442237854004</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>18</v>
       </c>
       <c r="G868" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>17.9780082702637</v>
+        <v>17.978006362915</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>18.1226005554199</v>
+        <v>18.1226024627686</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G874" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2671985626221</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G875" t="n">
-        <v>18.5081901550293</v>
+        <v>18.5081920623779</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G877" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G878" t="n">
-        <v>18.2189979553223</v>
+        <v>18.2189998626709</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>18.5081901550293</v>
+        <v>18.5081920623779</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>19.1829662322998</v>
+        <v>19.1829681396484</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G884" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>18.4599933624268</v>
+        <v>18.4599914550781</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G887" t="n">
-        <v>18.9901752471924</v>
+        <v>18.9901733398438</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>18.9901752471924</v>
+        <v>18.9901733398438</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>18.9901752471924</v>
+        <v>18.9901733398438</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>18.1226005554199</v>
+        <v>18.1226024627686</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>18.5</v>
       </c>
       <c r="G892" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334121704102</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>18.5</v>
       </c>
       <c r="G893" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334121704102</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>17.4960231781006</v>
+        <v>17.496021270752</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G897" t="n">
-        <v>17.4960231781006</v>
+        <v>17.496021270752</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>18.25</v>
       </c>
       <c r="G899" t="n">
-        <v>17.5924205780029</v>
+        <v>17.5924224853516</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>18.25</v>
       </c>
       <c r="G900" t="n">
-        <v>17.5924205780029</v>
+        <v>17.5924224853516</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>18</v>
       </c>
       <c r="G903" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>17.5442218780518</v>
+        <v>17.5442237854004</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>17.2550296783447</v>
+        <v>17.2550315856934</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>17.2550296783447</v>
+        <v>17.2550315856934</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>18</v>
       </c>
       <c r="G908" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>16.8212490081787</v>
+        <v>16.8212471008301</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G912" t="n">
-        <v>16.5802555084229</v>
+        <v>16.5802574157715</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G915" t="n">
-        <v>15.3752927780151</v>
+        <v>15.3752937316895</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>15.3270950317383</v>
+        <v>15.327094078064</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>15.3270950317383</v>
+        <v>15.327094078064</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>15.25</v>
       </c>
       <c r="G921" t="n">
-        <v>14.700514793396</v>
+        <v>14.7005157470703</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>13.9293403625488</v>
+        <v>13.9293394088745</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>14.1221351623535</v>
+        <v>14.1221342086792</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>15.7126817703247</v>
+        <v>15.7126798629761</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>16.0018711090088</v>
+        <v>16.0018749237061</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>16.1946659088135</v>
+        <v>16.1946678161621</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>15.7126817703247</v>
+        <v>15.7126798629761</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G934" t="n">
-        <v>15.2306985855103</v>
+        <v>15.2306995391846</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G937" t="n">
-        <v>14.4113254547119</v>
+        <v>14.4113245010376</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G938" t="n">
-        <v>14.3631277084351</v>
+        <v>14.3631267547607</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>15.3270950317383</v>
+        <v>15.327094078064</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G940" t="n">
-        <v>15.3752927780151</v>
+        <v>15.3752937316895</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>15.2788963317871</v>
+        <v>15.2788972854614</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>15.2306985855103</v>
+        <v>15.2306995391846</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>15.3752927780151</v>
+        <v>15.3752937316895</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G948" t="n">
-        <v>15.2306985855103</v>
+        <v>15.2306995391846</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>15</v>
       </c>
       <c r="G950" t="n">
-        <v>14.4595232009888</v>
+        <v>14.4595241546631</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>14.3631277084351</v>
+        <v>14.3631267547607</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G954" t="n">
-        <v>14.3631277084351</v>
+        <v>14.3631267547607</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15</v>
       </c>
       <c r="G955" t="n">
-        <v>14.4595232009888</v>
+        <v>14.4595241546631</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>14.4113254547119</v>
+        <v>14.4113245010376</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>14.3631277084351</v>
+        <v>14.3631267547607</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>14.5</v>
       </c>
       <c r="G959" t="n">
-        <v>13.9775390625</v>
+        <v>13.9775400161743</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>14.5</v>
       </c>
       <c r="G962" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G963" t="n">
-        <v>13.2624034881592</v>
+        <v>13.2624025344849</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>14.5</v>
       </c>
       <c r="G966" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G969" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>14.6176862716675</v>
+        <v>14.6176872253418</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G974" t="n">
-        <v>14.4240741729736</v>
+        <v>14.4240732192993</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G979" t="n">
-        <v>13.1171951293945</v>
+        <v>13.1171941757202</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G980" t="n">
-        <v>13.6012229919434</v>
+        <v>13.6012239456177</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G981" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G986" t="n">
-        <v>15.3921327590942</v>
+        <v>15.3921318054199</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>15.343729019165</v>
+        <v>15.3437299728394</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>14.4240741729736</v>
+        <v>14.4240732192993</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1005" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1009" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.0203886032104</v>
+        <v>13.0203895568848</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1018" t="n">
-        <v>12.8751802444458</v>
+        <v>12.8751811981201</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1019" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1021" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1029" t="n">
-        <v>13.6012229919434</v>
+        <v>13.6012239456177</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>14.5</v>
       </c>
       <c r="G1030" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>14.3756704330444</v>
+        <v>14.3756713867188</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1040" t="n">
-        <v>14.6176862716675</v>
+        <v>14.6176872253418</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>14.5</v>
       </c>
       <c r="G1048" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1058" t="n">
-        <v>13.6012229919434</v>
+        <v>13.6012239456177</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1059" t="n">
-        <v>13.6012229919434</v>
+        <v>13.6012239456177</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1060" t="n">
-        <v>13.2624034881592</v>
+        <v>13.2624025344849</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1064" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1066" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1070" t="n">
-        <v>11.7135095596313</v>
+        <v>11.7135105133057</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>12.25</v>
       </c>
       <c r="G1071" t="n">
-        <v>11.858717918396</v>
+        <v>11.8587188720703</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1072" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1075" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1076" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>12.8751802444458</v>
+        <v>12.8751811981201</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1106" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1114" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1121" t="n">
-        <v>12.8751802444458</v>
+        <v>12.8751811981201</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>12.9719867706299</v>
+        <v>12.9719858169556</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1123" t="n">
-        <v>13.0203886032104</v>
+        <v>13.0203895568848</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>12.9719867706299</v>
+        <v>12.9719858169556</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>13.0203886032104</v>
+        <v>13.0203895568848</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1127" t="n">
-        <v>12.9719867706299</v>
+        <v>12.9719858169556</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>13.21399974823</v>
+        <v>13.2140007019043</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1138" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1141" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>15.25</v>
       </c>
       <c r="G1146" t="n">
-        <v>14.7628936767578</v>
+        <v>14.7628946304321</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>14.5</v>
       </c>
       <c r="G1152" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>14.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>14.5</v>
       </c>
       <c r="G1158" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>14.5</v>
       </c>
       <c r="G1165" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1176" t="n">
-        <v>12.8751802444458</v>
+        <v>12.8751811981201</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1180" t="n">
-        <v>12.8751802444458</v>
+        <v>12.8751811981201</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1183" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>12.9719867706299</v>
+        <v>12.9719858169556</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1185" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1194" t="n">
-        <v>13.0203886032104</v>
+        <v>13.0203895568848</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>13.2624034881592</v>
+        <v>13.2624025344849</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1215" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1217" t="n">
-        <v>13.0203886032104</v>
+        <v>13.0203895568848</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -54374,6 +54374,32 @@
         <v>8.64000034332275</v>
       </c>
       <c r="H2077" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2078" t="n">
+        <v>1704</v>
+      </c>
+      <c r="C2078" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>8.64000034332275</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>8.64000034332275</v>
+      </c>
+      <c r="F2078" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="G2078" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="H2078" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G2" t="n">
-        <v>2.57321238517761</v>
+        <v>2.57321286201477</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.87050008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7357063293457</v>
+        <v>2.73570656776428</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G4" t="n">
-        <v>2.83053421974182</v>
+        <v>2.83053374290466</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G7" t="n">
-        <v>2.80670809745789</v>
+        <v>2.80670785903931</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84006452560425</v>
+        <v>2.84006428718567</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.85912537574768</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.97449994087219</v>
       </c>
       <c r="G10" t="n">
-        <v>2.83482265472412</v>
+        <v>2.8348228931427</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.9614999294281</v>
       </c>
       <c r="G11" t="n">
-        <v>2.82243275642395</v>
+        <v>2.82243299484253</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G12" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.98900008201599</v>
       </c>
       <c r="G13" t="n">
-        <v>2.84864163398743</v>
+        <v>2.84864211082458</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.85912537574768</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.97449994087219</v>
       </c>
       <c r="G16" t="n">
-        <v>2.83482265472412</v>
+        <v>2.8348228931427</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>2.7066388130188</v>
+        <v>2.70663857460022</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.7066388130188</v>
+        <v>2.70663857460022</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G26" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G29" t="n">
-        <v>2.61895871162415</v>
+        <v>2.61895895004272</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.75</v>
       </c>
       <c r="G30" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.75</v>
       </c>
       <c r="G31" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.75</v>
       </c>
       <c r="G32" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.75</v>
       </c>
       <c r="G33" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.75</v>
       </c>
       <c r="G34" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G35" t="n">
-        <v>2.67232894897461</v>
+        <v>2.67232918739319</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.67804765701294</v>
+        <v>2.67804718017578</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288173675537</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G38" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>2.85912537574768</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G42" t="n">
-        <v>2.83053421974182</v>
+        <v>2.83053374290466</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G43" t="n">
-        <v>2.83053421974182</v>
+        <v>2.83053374290466</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.79241251945496</v>
+        <v>2.79241228103638</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>2.85912537574768</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87818622589111</v>
+        <v>2.87818598747253</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.05550003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>2.91201901435852</v>
+        <v>2.9120192527771</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G51" t="n">
-        <v>2.92583775520325</v>
+        <v>2.92583823204041</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01161217689514</v>
+        <v>3.01161193847656</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G54" t="n">
-        <v>2.96395993232727</v>
+        <v>2.96395945549011</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>2.91630792617798</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>2.97349047660828</v>
+        <v>2.97348999977112</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G60" t="n">
-        <v>2.97349047660828</v>
+        <v>2.97348999977112</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G63" t="n">
-        <v>2.88771677017212</v>
+        <v>2.88771629333496</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>2.87818622589111</v>
+        <v>2.87818598747253</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G67" t="n">
-        <v>2.83053421974182</v>
+        <v>2.83053374290466</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83053421974182</v>
+        <v>2.83053374290466</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80670809745789</v>
+        <v>2.80670785903931</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>2.85912537574768</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>2.82100367546082</v>
+        <v>2.82100391387939</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3</v>
       </c>
       <c r="G74" t="n">
-        <v>2.85912537574768</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3</v>
       </c>
       <c r="G75" t="n">
-        <v>2.85912537574768</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G76" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288173675537</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.89100003242493</v>
       </c>
       <c r="G78" t="n">
-        <v>2.75524353981018</v>
+        <v>2.75524377822876</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.90549993515015</v>
       </c>
       <c r="G80" t="n">
-        <v>2.76906299591064</v>
+        <v>2.76906275749207</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>2.77335143089294</v>
+        <v>2.77335166931152</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G83" t="n">
-        <v>2.88771677017212</v>
+        <v>2.88771629333496</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>2.85912537574768</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G85" t="n">
-        <v>2.92202615737915</v>
+        <v>2.92202663421631</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>2.91630792617798</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.99950003623962</v>
       </c>
       <c r="G87" t="n">
-        <v>2.85864877700806</v>
+        <v>2.85864901542664</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G89" t="n">
-        <v>2.85054802894592</v>
+        <v>2.8505482673645</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G90" t="n">
-        <v>2.85054802894592</v>
+        <v>2.8505482673645</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G91" t="n">
-        <v>2.85054802894592</v>
+        <v>2.8505482673645</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.93050003051758</v>
       </c>
       <c r="G92" t="n">
-        <v>2.79288864135742</v>
+        <v>2.792888879776</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.90899991989136</v>
       </c>
       <c r="G93" t="n">
-        <v>2.77239799499512</v>
+        <v>2.77239847183228</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.90899991989136</v>
       </c>
       <c r="G94" t="n">
-        <v>2.77239799499512</v>
+        <v>2.77239847183228</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G95" t="n">
-        <v>2.82576870918274</v>
+        <v>2.82576894760132</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G96" t="n">
-        <v>2.82100367546082</v>
+        <v>2.82100391387939</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.98850011825562</v>
       </c>
       <c r="G105" t="n">
-        <v>2.84816527366638</v>
+        <v>2.8481650352478</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.82100367546082</v>
+        <v>2.82100391387939</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.82100367546082</v>
+        <v>2.82100391387939</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G109" t="n">
-        <v>2.7204577922821</v>
+        <v>2.72045755386353</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G110" t="n">
-        <v>2.7204577922821</v>
+        <v>2.72045755386353</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>2.85912537574768</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G116" t="n">
-        <v>2.84959483146667</v>
+        <v>2.84959506988525</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.92549991607666</v>
       </c>
       <c r="G117" t="n">
-        <v>2.78812336921692</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G119" t="n">
-        <v>2.85436010360718</v>
+        <v>2.8543598651886</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85912537574768</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3</v>
       </c>
       <c r="G121" t="n">
-        <v>2.85912537574768</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G126" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288173675537</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288173675537</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G131" t="n">
-        <v>2.83053421974182</v>
+        <v>2.83053374290466</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G132" t="n">
-        <v>2.83053421974182</v>
+        <v>2.83053374290466</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.92249989509583</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78526449203491</v>
+        <v>2.78526425361633</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>2.83053421974182</v>
+        <v>2.83053374290466</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.83053421974182</v>
+        <v>2.83053374290466</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G136" t="n">
-        <v>2.83053421974182</v>
+        <v>2.83053374290466</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G137" t="n">
-        <v>2.83053421974182</v>
+        <v>2.83053374290466</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G138" t="n">
-        <v>2.79241251945496</v>
+        <v>2.79241228103638</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.95700001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.81814455986023</v>
+        <v>2.81814479827881</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G140" t="n">
-        <v>2.87818622589111</v>
+        <v>2.87818598747253</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3</v>
       </c>
       <c r="G141" t="n">
-        <v>2.85912537574768</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G142" t="n">
-        <v>2.88390445709229</v>
+        <v>2.88390398025513</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3</v>
       </c>
       <c r="G143" t="n">
-        <v>2.85912537574768</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.02950000762939</v>
       </c>
       <c r="G144" t="n">
-        <v>2.8872401714325</v>
+        <v>2.88724040985107</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>2.91630792617798</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.24049997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>3.0883321762085</v>
+        <v>3.08833193778992</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>3.05926418304443</v>
+        <v>3.05926394462585</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.27649998664856</v>
       </c>
       <c r="G152" t="n">
-        <v>3.12264156341553</v>
+        <v>3.12264132499695</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G154" t="n">
-        <v>3.2498722076416</v>
+        <v>3.24987244606018</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G156" t="n">
-        <v>3.22890543937683</v>
+        <v>3.22890567779541</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.35349988937378</v>
       </c>
       <c r="G158" t="n">
-        <v>3.19602537155151</v>
+        <v>3.19602584838867</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.43549990653992</v>
       </c>
       <c r="G161" t="n">
-        <v>3.27417492866516</v>
+        <v>3.27417469024658</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G162" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175026893616</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.41700005531311</v>
       </c>
       <c r="G163" t="n">
-        <v>3.25654363632202</v>
+        <v>3.2565438747406</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175026893616</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175026893616</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>3.31658506393433</v>
+        <v>3.31658530235291</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>3.31658506393433</v>
+        <v>3.31658530235291</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G172" t="n">
-        <v>3.50242853164673</v>
+        <v>3.50242877006531</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>3.5834367275238</v>
+        <v>3.58343720436096</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.47860264778137</v>
+        <v>3.47860240936279</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G175" t="n">
-        <v>3.5548460483551</v>
+        <v>3.55484580993652</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.75</v>
       </c>
       <c r="G176" t="n">
-        <v>3.57390666007996</v>
+        <v>3.57390689849854</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.75</v>
       </c>
       <c r="G177" t="n">
-        <v>3.57390666007996</v>
+        <v>3.57390689849854</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G178" t="n">
-        <v>3.7645149230957</v>
+        <v>3.76451516151428</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>3.84075832366943</v>
+        <v>3.84075880050659</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G182" t="n">
-        <v>3.62155866622925</v>
+        <v>3.62155842781067</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>3.62155866622925</v>
+        <v>3.62155842781067</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G185" t="n">
-        <v>3.66921043395996</v>
+        <v>3.66921067237854</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G186" t="n">
-        <v>3.66921043395996</v>
+        <v>3.66921067237854</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G187" t="n">
-        <v>3.71686291694641</v>
+        <v>3.71686315536499</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>3.71686291694641</v>
+        <v>3.71686315536499</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>3.65015006065369</v>
+        <v>3.65014958381653</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>3.84075832366943</v>
+        <v>3.84075880050659</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G192" t="n">
-        <v>3.84075832366943</v>
+        <v>3.84075880050659</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>3.95512366294861</v>
+        <v>3.95512294769287</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4</v>
       </c>
       <c r="G194" t="n">
-        <v>3.812166929245</v>
+        <v>3.81216716766357</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4</v>
       </c>
       <c r="G195" t="n">
-        <v>3.812166929245</v>
+        <v>3.81216716766357</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>3.85028886795044</v>
+        <v>3.85028839111328</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G200" t="n">
-        <v>3.77414274215698</v>
+        <v>3.77414298057556</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83161687850952</v>
+        <v>3.8316171169281</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>3.92740750312805</v>
+        <v>3.92740726470947</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>3.87951231002808</v>
+        <v>3.87951278686523</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>3.88909149169922</v>
+        <v>3.88909125328064</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G206" t="n">
-        <v>3.80288004875183</v>
+        <v>3.80287981033325</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>3.77414274215698</v>
+        <v>3.77414298057556</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G209" t="n">
-        <v>3.69751048088074</v>
+        <v>3.69751024246216</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G210" t="n">
-        <v>3.69751048088074</v>
+        <v>3.69751024246216</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>3.83161687850952</v>
+        <v>3.8316171169281</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>3.87951231002808</v>
+        <v>3.87951278686523</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>3.87951231002808</v>
+        <v>3.87951278686523</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>3.78372192382812</v>
+        <v>3.78372168540955</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>3.87951231002808</v>
+        <v>3.87951278686523</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>3.87951231002808</v>
+        <v>3.87951278686523</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.93698668479919</v>
+        <v>3.93698620796204</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G218" t="n">
-        <v>3.94656491279602</v>
+        <v>3.9465651512146</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>4.02319812774658</v>
+        <v>4.02319765090942</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>4.03277730941772</v>
+        <v>4.03277778625488</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>4.10940885543823</v>
+        <v>4.10940933227539</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G225" t="n">
-        <v>4.39678001403809</v>
+        <v>4.39678049087524</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>4.50214958190918</v>
+        <v>4.50215005874634</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>4.45425510406494</v>
+        <v>4.45425462722778</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G229" t="n">
-        <v>4.4350962638855</v>
+        <v>4.43509674072266</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G232" t="n">
-        <v>4.50214958190918</v>
+        <v>4.50215005874634</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>4.66499376296997</v>
+        <v>4.66499328613281</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G235" t="n">
-        <v>4.6841516494751</v>
+        <v>4.68415212631226</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>5.07689237594604</v>
+        <v>5.0768928527832</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G237" t="n">
-        <v>4.96194410324097</v>
+        <v>4.96194362640381</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>4.90446996688843</v>
+        <v>4.90446949005127</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G241" t="n">
-        <v>4.94278573989868</v>
+        <v>4.94278526306152</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G249" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036285400391</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036285400391</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036285400391</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G256" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457294464111</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G257" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457294464111</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G260" t="n">
-        <v>4.66499376296997</v>
+        <v>4.66499328613281</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>4.66499376296997</v>
+        <v>4.66499328613281</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G262" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457294464111</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G264" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G265" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>4.59794092178345</v>
+        <v>4.59794044494629</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>4.59794092178345</v>
+        <v>4.59794044494629</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G269" t="n">
-        <v>4.59794092178345</v>
+        <v>4.59794044494629</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>4.50214958190918</v>
+        <v>4.50215005874634</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G271" t="n">
-        <v>4.50214958190918</v>
+        <v>4.50215005874634</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G272" t="n">
-        <v>4.50214958190918</v>
+        <v>4.50215005874634</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078319549561</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G275" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078319549561</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G276" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036285400391</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>4.62667751312256</v>
+        <v>4.62667798995972</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G279" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457294464111</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G280" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457294464111</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>4.75120449066162</v>
+        <v>4.75120544433594</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G289" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G294" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078319549561</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457294464111</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457294464111</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G297" t="n">
-        <v>4.70330905914307</v>
+        <v>4.70330953598022</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G306" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G314" t="n">
-        <v>4.77994203567505</v>
+        <v>4.77994155883789</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078319549561</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036285400391</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036285400391</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>4.75120449066162</v>
+        <v>4.75120544433594</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036285400391</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G339" t="n">
-        <v>4.88531160354614</v>
+        <v>4.88531112670898</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.98110151290894</v>
+        <v>4.98110198974609</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.88531160354614</v>
+        <v>4.88531112670898</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>4.98110151290894</v>
+        <v>4.98110198974609</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.13436698913574</v>
+        <v>5.13436651229858</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G348" t="n">
-        <v>5.32594776153564</v>
+        <v>5.32594728469849</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.13436698913574</v>
+        <v>5.13436651229858</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G351" t="n">
-        <v>5.13436698913574</v>
+        <v>5.13436651229858</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G352" t="n">
-        <v>5.07689237594604</v>
+        <v>5.0768928527832</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G353" t="n">
-        <v>5.09605026245117</v>
+        <v>5.09605073928833</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>5.07689237594604</v>
+        <v>5.0768928527832</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G358" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G359" t="n">
-        <v>5.01941823959351</v>
+        <v>5.01941776275635</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>5.07689237594604</v>
+        <v>5.0768928527832</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>5.07689237594604</v>
+        <v>5.0768928527832</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.13436698913574</v>
+        <v>5.13436651229858</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>5.32594776153564</v>
+        <v>5.32594728469849</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>5.28763151168823</v>
+        <v>5.28763198852539</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G368" t="n">
-        <v>5.47921228408813</v>
+        <v>5.47921180725098</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G369" t="n">
-        <v>5.53668642044067</v>
+        <v>5.53668689727783</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G370" t="n">
-        <v>5.53668642044067</v>
+        <v>5.53668689727783</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>5.68995046615601</v>
+        <v>5.68995189666748</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>5.8432149887085</v>
+        <v>5.84321546554565</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6</v>
       </c>
       <c r="G375" t="n">
-        <v>5.7474250793457</v>
+        <v>5.74742603302002</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G376" t="n">
-        <v>5.91984844207764</v>
+        <v>5.91984748840332</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G377" t="n">
-        <v>5.90068960189819</v>
+        <v>5.90069055557251</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G379" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G384" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G386" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>5.82405853271484</v>
+        <v>5.82405757904053</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G391" t="n">
-        <v>5.91984844207764</v>
+        <v>5.91984748840332</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G394" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G395" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479623794556</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311296463013</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G401" t="n">
-        <v>6.36048364639282</v>
+        <v>6.36048460006714</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G403" t="n">
-        <v>6.45627403259277</v>
+        <v>6.45627450942993</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G404" t="n">
-        <v>6.39879989624023</v>
+        <v>6.39880037307739</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>6.36048364639282</v>
+        <v>6.36048460006714</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G407" t="n">
-        <v>6.49459075927734</v>
+        <v>6.49459171295166</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479623794556</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479623794556</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G412" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479623794556</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G414" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311296463013</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.55584478378296</v>
+        <v>5.55584383010864</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>6</v>
       </c>
       <c r="G416" t="n">
-        <v>5.7474250793457</v>
+        <v>5.74742603302002</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G417" t="n">
-        <v>5.90068960189819</v>
+        <v>5.90069055557251</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>5.72826814651489</v>
+        <v>5.72826719284058</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G419" t="n">
-        <v>5.90068960189819</v>
+        <v>5.90069055557251</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>5.70910978317261</v>
+        <v>5.70910882949829</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>5.70910978317261</v>
+        <v>5.70910882949829</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G427" t="n">
-        <v>5.9964804649353</v>
+        <v>5.99648094177246</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311296463013</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479623794556</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G437" t="n">
-        <v>6.62869787216187</v>
+        <v>6.62869691848755</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>6.64785480499268</v>
+        <v>6.64785575866699</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>6.68617153167725</v>
+        <v>6.6861720085144</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G444" t="n">
-        <v>6.78196144104004</v>
+        <v>6.7819619178772</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>6.99270153045654</v>
+        <v>6.99270105361938</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>7.165123462677</v>
+        <v>7.16512393951416</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>7.5</v>
       </c>
       <c r="G447" t="n">
-        <v>7.1842827796936</v>
+        <v>7.18428182601929</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G449" t="n">
-        <v>7.79734086990356</v>
+        <v>7.79734039306641</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.5</v>
       </c>
       <c r="G454" t="n">
-        <v>8.17151069641113</v>
+        <v>8.17150974273682</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G455" t="n">
-        <v>7.99846458435059</v>
+        <v>7.99846506118774</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.07537460327148</v>
+        <v>8.07537364959717</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G457" t="n">
-        <v>8.07537460327148</v>
+        <v>8.07537364959717</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.5</v>
       </c>
       <c r="G458" t="n">
-        <v>8.17151069641113</v>
+        <v>8.17150974273682</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G461" t="n">
-        <v>8.07537460327148</v>
+        <v>8.07537364959717</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.07537460327148</v>
+        <v>8.07537364959717</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>7.13324689865112</v>
+        <v>7.13324737548828</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>7.22938203811646</v>
+        <v>7.22938251495361</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>7.32551765441895</v>
+        <v>7.3255181312561</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G469" t="n">
-        <v>7.2678370475769</v>
+        <v>7.26783657073975</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G470" t="n">
-        <v>7.24860954284668</v>
+        <v>7.24861001968384</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>7.5</v>
       </c>
       <c r="G471" t="n">
-        <v>7.21015596389771</v>
+        <v>7.21015501022339</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>7.19092798233032</v>
+        <v>7.19092845916748</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.5</v>
       </c>
       <c r="G473" t="n">
-        <v>7.21015596389771</v>
+        <v>7.21015501022339</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G474" t="n">
-        <v>7.07556581497192</v>
+        <v>7.07556629180908</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>7.59469747543335</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G477" t="n">
-        <v>7.57546949386597</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>7.57546949386597</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>7.63315200805664</v>
+        <v>7.63315105438232</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>7.59469747543335</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G481" t="n">
-        <v>7.61392402648926</v>
+        <v>7.61392450332642</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>7.59469747543335</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>7.57546949386597</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>7.59469747543335</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>7.59469747543335</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>7.61392402648926</v>
+        <v>7.61392450332642</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>7.59469747543335</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>7.57546949386597</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G490" t="n">
-        <v>7.55624341964722</v>
+        <v>7.55624294281006</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G491" t="n">
-        <v>7.46010780334473</v>
+        <v>7.46010732650757</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G492" t="n">
-        <v>7.57546949386597</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G493" t="n">
-        <v>7.57546949386597</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G496" t="n">
-        <v>7.51778888702393</v>
+        <v>7.51778841018677</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G497" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.61392402648926</v>
+        <v>7.61392450332642</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63315200805664</v>
+        <v>7.63315105438232</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>7.76774120330811</v>
+        <v>7.76774024963379</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>7.76774120330811</v>
+        <v>7.76774024963379</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G502" t="n">
-        <v>7.63315200805664</v>
+        <v>7.63315105438232</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G506" t="n">
-        <v>8.15228176116943</v>
+        <v>8.15228271484375</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G507" t="n">
-        <v>8.34455299377441</v>
+        <v>8.34455394744873</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G508" t="n">
-        <v>8.38300800323486</v>
+        <v>8.38300704956055</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>8.45991516113281</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9</v>
       </c>
       <c r="G512" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G513" t="n">
-        <v>8.74832248687744</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G515" t="n">
-        <v>8.78677558898926</v>
+        <v>8.78677654266357</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>9.5</v>
       </c>
       <c r="G516" t="n">
-        <v>9.13286399841309</v>
+        <v>9.13286304473877</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G517" t="n">
-        <v>9.3635892868042</v>
+        <v>9.36358833312988</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G518" t="n">
-        <v>9.30590915679932</v>
+        <v>9.30590724945068</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G519" t="n">
-        <v>9.30590915679932</v>
+        <v>9.30590724945068</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>9.5</v>
       </c>
       <c r="G520" t="n">
-        <v>9.13286399841309</v>
+        <v>9.13286304473877</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G521" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>9.49817752838135</v>
+        <v>9.49817848205566</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G523" t="n">
-        <v>9.4789514541626</v>
+        <v>9.47895050048828</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G524" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G525" t="n">
-        <v>9.34436130523682</v>
+        <v>9.34436225891113</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G526" t="n">
-        <v>9.3635892868042</v>
+        <v>9.36358833312988</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G531" t="n">
-        <v>8.94059371948242</v>
+        <v>8.94059276580811</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G532" t="n">
-        <v>9.07518196105957</v>
+        <v>9.07518291473389</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G533" t="n">
-        <v>8.99827480316162</v>
+        <v>8.9982738494873</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>8.94059371948242</v>
+        <v>8.94059276580811</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>8.94059371948242</v>
+        <v>8.94059276580811</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G536" t="n">
-        <v>8.92136478424072</v>
+        <v>8.92136573791504</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G538" t="n">
-        <v>8.74832248687744</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>8.69063949584961</v>
+        <v>8.69064044952393</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>9</v>
       </c>
       <c r="G540" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G541" t="n">
-        <v>8.63296031951904</v>
+        <v>8.63295841217041</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9</v>
       </c>
       <c r="G542" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G545" t="n">
-        <v>8.26764678955078</v>
+        <v>8.26764488220215</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G546" t="n">
-        <v>8.38300800323486</v>
+        <v>8.38300704956055</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>8.38300800323486</v>
+        <v>8.38300704956055</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>8.45991516113281</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G549" t="n">
-        <v>8.45991516113281</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G550" t="n">
-        <v>8.421462059021</v>
+        <v>8.42146110534668</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G551" t="n">
-        <v>8.421462059021</v>
+        <v>8.42146110534668</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G553" t="n">
-        <v>8.421462059021</v>
+        <v>8.42146110534668</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G554" t="n">
-        <v>8.421462059021</v>
+        <v>8.42146110534668</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>8.45991516113281</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.45991516113281</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G560" t="n">
-        <v>8.59450340270996</v>
+        <v>8.59450531005859</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G561" t="n">
-        <v>8.78677558898926</v>
+        <v>8.78677654266357</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G562" t="n">
-        <v>8.95981884002686</v>
+        <v>8.95981979370117</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G563" t="n">
-        <v>8.90213871002197</v>
+        <v>8.90213966369629</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>8.94059371948242</v>
+        <v>8.94059276580811</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G566" t="n">
-        <v>8.95981884002686</v>
+        <v>8.95981979370117</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G568" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G569" t="n">
-        <v>9.2866792678833</v>
+        <v>9.28668117523193</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G571" t="n">
-        <v>9.07518196105957</v>
+        <v>9.07518291473389</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>9.07518196105957</v>
+        <v>9.07518291473389</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>9</v>
       </c>
       <c r="G576" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G577" t="n">
-        <v>8.78677558898926</v>
+        <v>8.78677654266357</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G579" t="n">
-        <v>8.90213871002197</v>
+        <v>8.90213966369629</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9</v>
       </c>
       <c r="G584" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.69063949584961</v>
+        <v>8.69064044952393</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>8.74832248687744</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G589" t="n">
-        <v>8.67141342163086</v>
+        <v>8.67141437530518</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>9</v>
       </c>
       <c r="G590" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>9</v>
       </c>
       <c r="G591" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G592" t="n">
-        <v>8.59450340270996</v>
+        <v>8.59450531005859</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9</v>
       </c>
       <c r="G593" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G595" t="n">
-        <v>8.78677558898926</v>
+        <v>8.78677654266357</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>9.32513427734375</v>
+        <v>9.32513618469238</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>9.5</v>
       </c>
       <c r="G599" t="n">
-        <v>9.13286399841309</v>
+        <v>9.13286304473877</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G600" t="n">
-        <v>9.34436130523682</v>
+        <v>9.34436225891113</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G601" t="n">
-        <v>9.15209007263184</v>
+        <v>9.15209102630615</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>9.32513427734375</v>
+        <v>9.32513618469238</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G604" t="n">
-        <v>9.26745319366455</v>
+        <v>9.26745414733887</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G605" t="n">
-        <v>9.3635892868042</v>
+        <v>9.36358833312988</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G606" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>9.22900104522705</v>
+        <v>9.2289981842041</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G608" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.5</v>
       </c>
       <c r="G611" t="n">
-        <v>9.13286399841309</v>
+        <v>9.13286304473877</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G612" t="n">
-        <v>9.17131805419922</v>
+        <v>9.1713171005249</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G613" t="n">
-        <v>9.15209007263184</v>
+        <v>9.15209102630615</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G616" t="n">
-        <v>9.22900104522705</v>
+        <v>9.2289981842041</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G617" t="n">
-        <v>9.15209007263184</v>
+        <v>9.15209102630615</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.13286399841309</v>
+        <v>9.13286304473877</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G619" t="n">
-        <v>9.22900104522705</v>
+        <v>9.2289981842041</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G620" t="n">
-        <v>9.22900104522705</v>
+        <v>9.2289981842041</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>9.17131805419922</v>
+        <v>9.1713171005249</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G622" t="n">
-        <v>9.22900104522705</v>
+        <v>9.2289981842041</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>9.99808216094971</v>
+        <v>9.99808120727539</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>10.5</v>
       </c>
       <c r="G627" t="n">
-        <v>10.0942163467407</v>
+        <v>10.0942182540894</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G628" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G630" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>10.5</v>
       </c>
       <c r="G633" t="n">
-        <v>10.0942163467407</v>
+        <v>10.0942182540894</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>10.5</v>
       </c>
       <c r="G635" t="n">
-        <v>10.0942163467407</v>
+        <v>10.0942182540894</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G636" t="n">
-        <v>10.0461492538452</v>
+        <v>10.0461502075195</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>10.5</v>
       </c>
       <c r="G637" t="n">
-        <v>10.0942163467407</v>
+        <v>10.0942182540894</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>10.1903524398804</v>
+        <v>10.1903553009033</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>10.4787578582764</v>
+        <v>10.4787588119507</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>10.75</v>
       </c>
       <c r="G642" t="n">
-        <v>10.3345565795898</v>
+        <v>10.3345556259155</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.75</v>
       </c>
       <c r="G643" t="n">
-        <v>10.3345565795898</v>
+        <v>10.3345556259155</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>10.75</v>
       </c>
       <c r="G646" t="n">
-        <v>10.3345565795898</v>
+        <v>10.3345556259155</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>10.4787578582764</v>
+        <v>10.4787588119507</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>10.6710300445557</v>
+        <v>10.67103099823</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>10.6710300445557</v>
+        <v>10.67103099823</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>10.7671642303467</v>
+        <v>10.767165184021</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>11.5</v>
       </c>
       <c r="G651" t="n">
-        <v>11.0555715560913</v>
+        <v>11.0555725097656</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>11.5</v>
       </c>
       <c r="G652" t="n">
-        <v>11.0555715560913</v>
+        <v>11.0555725097656</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>11.6323843002319</v>
+        <v>11.6323852539062</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8246545791626</v>
+        <v>11.8246555328369</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>12.5</v>
       </c>
       <c r="G655" t="n">
-        <v>12.0169267654419</v>
+        <v>12.0169258117676</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>12.3053312301636</v>
+        <v>12.3053321838379</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G658" t="n">
-        <v>12.5937385559082</v>
+        <v>12.5937395095825</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G660" t="n">
-        <v>12.8340759277344</v>
+        <v>12.8340768814087</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>12.5937385559082</v>
+        <v>12.5937395095825</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>12.641806602478</v>
+        <v>12.6418056488037</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>12.8340759277344</v>
+        <v>12.8340768814087</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>12.5937385559082</v>
+        <v>12.5937395095825</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G674" t="n">
-        <v>13.5070238113403</v>
+        <v>13.507025718689</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>14.5</v>
       </c>
       <c r="G675" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396352767944</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>14.5</v>
       </c>
       <c r="G676" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396352767944</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>14.5</v>
       </c>
       <c r="G677" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396352767944</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>13.7954301834106</v>
+        <v>13.7954320907593</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>13.5070238113403</v>
+        <v>13.507025718689</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>13.6512269973755</v>
+        <v>13.6512279510498</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>14.0838356018066</v>
+        <v>14.083836555481</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>14.1319055557251</v>
+        <v>14.1319046020508</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G685" t="n">
-        <v>14.1319055557251</v>
+        <v>14.1319046020508</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>14.0838356018066</v>
+        <v>14.083836555481</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G687" t="n">
-        <v>13.9877004623413</v>
+        <v>13.9877023696899</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>13.7954301834106</v>
+        <v>13.7954320907593</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>14.5</v>
       </c>
       <c r="G690" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396352767944</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>14.5</v>
       </c>
       <c r="G691" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396352767944</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>14.25</v>
       </c>
       <c r="G695" t="n">
-        <v>13.6992959976196</v>
+        <v>13.6992950439453</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>13.6031608581543</v>
+        <v>13.60315990448</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>13.7473640441895</v>
+        <v>13.7473621368408</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G701" t="n">
-        <v>13.7473640441895</v>
+        <v>13.7473621368408</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>13.9877004623413</v>
+        <v>13.9877023696899</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>14.0838356018066</v>
+        <v>14.083836555481</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>14.0838356018066</v>
+        <v>14.083836555481</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>14.3631267547607</v>
+        <v>14.3631258010864</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>15.5</v>
       </c>
       <c r="G707" t="n">
-        <v>14.9415082931519</v>
+        <v>14.9415073394775</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>15.5</v>
       </c>
       <c r="G708" t="n">
-        <v>14.9415082931519</v>
+        <v>14.9415073394775</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>15.9536752700806</v>
+        <v>15.9536733627319</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G713" t="n">
-        <v>16.6766490936279</v>
+        <v>16.6766510009766</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>16.2910614013672</v>
+        <v>16.2910633087158</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>16.5802574157715</v>
+        <v>16.5802536010742</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>16.965841293335</v>
+        <v>16.9658432006836</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>16.8212471008301</v>
+        <v>16.8212490081787</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>17</v>
       </c>
       <c r="G725" t="n">
-        <v>16.3874607086182</v>
+        <v>16.3874626159668</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>16.2910614013672</v>
+        <v>16.2910633087158</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>16.5802574157715</v>
+        <v>16.5802536010742</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G733" t="n">
-        <v>16.2910614013672</v>
+        <v>16.2910633087158</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>16.1946678161621</v>
+        <v>16.1946659088135</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>16.0982685089111</v>
+        <v>16.0982704162598</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>16.1946678161621</v>
+        <v>16.1946659088135</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>16.2428646087646</v>
+        <v>16.2428665161133</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>16.0982685089111</v>
+        <v>16.0982704162598</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G740" t="n">
-        <v>15.2306995391846</v>
+        <v>15.2306985855103</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>15.3752937316895</v>
+        <v>15.3752927780151</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G746" t="n">
-        <v>15.2306995391846</v>
+        <v>15.2306985855103</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G748" t="n">
-        <v>14.8933086395264</v>
+        <v>14.8933095932007</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G749" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G750" t="n">
-        <v>14.8933086395264</v>
+        <v>14.8933095932007</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>15.75</v>
       </c>
       <c r="G751" t="n">
-        <v>15.1824998855591</v>
+        <v>15.1825008392334</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>15.75</v>
       </c>
       <c r="G753" t="n">
-        <v>15.1824998855591</v>
+        <v>15.1825008392334</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>15.2306995391846</v>
+        <v>15.2306985855103</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G755" t="n">
-        <v>15.3752937316895</v>
+        <v>15.3752927780151</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>16.25</v>
       </c>
       <c r="G757" t="n">
-        <v>15.6644840240479</v>
+        <v>15.6644830703735</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G758" t="n">
-        <v>15.8572778701782</v>
+        <v>15.8572788238525</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>15.7126798629761</v>
+        <v>15.7126817703247</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162872314453</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>16.25</v>
       </c>
       <c r="G762" t="n">
-        <v>15.6644840240479</v>
+        <v>15.6644830703735</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G764" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162872314453</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162872314453</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G770" t="n">
-        <v>16.2910614013672</v>
+        <v>16.2910633087158</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>18</v>
       </c>
       <c r="G774" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G778" t="n">
-        <v>16.8212471008301</v>
+        <v>16.8212490081787</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G779" t="n">
-        <v>16.6766490936279</v>
+        <v>16.6766510009766</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>17.5</v>
       </c>
       <c r="G780" t="n">
-        <v>16.8694438934326</v>
+        <v>16.869441986084</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>16.6766490936279</v>
+        <v>16.6766510009766</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G782" t="n">
-        <v>16.7730464935303</v>
+        <v>16.7730484008789</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>16.6766490936279</v>
+        <v>16.6766510009766</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>16.532054901123</v>
+        <v>16.5320568084717</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>17.5</v>
       </c>
       <c r="G786" t="n">
-        <v>16.8694438934326</v>
+        <v>16.869441986084</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>17.75</v>
       </c>
       <c r="G795" t="n">
-        <v>17.1104354858398</v>
+        <v>17.1104373931885</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>17.5</v>
       </c>
       <c r="G798" t="n">
-        <v>16.8694438934326</v>
+        <v>16.869441986084</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>18.7009830474854</v>
+        <v>18.7009868621826</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>18.2189998626709</v>
+        <v>18.2189979553223</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>17.978006362915</v>
+        <v>17.9780082702637</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>17.8816089630127</v>
+        <v>17.8816108703613</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G833" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>18.5</v>
       </c>
       <c r="G839" t="n">
-        <v>17.8334121704102</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>17.8816089630127</v>
+        <v>17.8816108703613</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>18.5</v>
       </c>
       <c r="G848" t="n">
-        <v>17.8334121704102</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>17.496021270752</v>
+        <v>17.4960231781006</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>18</v>
       </c>
       <c r="G851" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G852" t="n">
-        <v>17.5442237854004</v>
+        <v>17.5442218780518</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G853" t="n">
-        <v>17.978006362915</v>
+        <v>17.9780082702637</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>18</v>
       </c>
       <c r="G855" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>17.9298114776611</v>
+        <v>17.9298095703125</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>18.5</v>
       </c>
       <c r="G858" t="n">
-        <v>17.8334121704102</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>18.25</v>
       </c>
       <c r="G859" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>18.25</v>
       </c>
       <c r="G860" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>18</v>
       </c>
       <c r="G862" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>18</v>
       </c>
       <c r="G863" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G866" t="n">
-        <v>17.496021270752</v>
+        <v>17.4960231781006</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G867" t="n">
-        <v>17.5442237854004</v>
+        <v>17.5442218780518</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>18</v>
       </c>
       <c r="G868" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>17.978006362915</v>
+        <v>17.9780082702637</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G874" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>17.9298114776611</v>
+        <v>17.9298095703125</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G878" t="n">
-        <v>18.2189998626709</v>
+        <v>18.2189979553223</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>19.1829681396484</v>
+        <v>19.1829662322998</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G887" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>18.5</v>
       </c>
       <c r="G892" t="n">
-        <v>17.8334121704102</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>18.5</v>
       </c>
       <c r="G893" t="n">
-        <v>17.8334121704102</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>17.25</v>
       </c>
       <c r="G895" t="n">
-        <v>16.6284523010254</v>
+        <v>16.6284503936768</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>17.496021270752</v>
+        <v>17.4960231781006</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G897" t="n">
-        <v>17.496021270752</v>
+        <v>17.4960231781006</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>18.25</v>
       </c>
       <c r="G899" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>18.25</v>
       </c>
       <c r="G900" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>17.8816089630127</v>
+        <v>17.8816108703613</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>18</v>
       </c>
       <c r="G903" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>17.5442237854004</v>
+        <v>17.5442218780518</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>18</v>
       </c>
       <c r="G908" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>17.5</v>
       </c>
       <c r="G909" t="n">
-        <v>16.8694438934326</v>
+        <v>16.869441986084</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>16.8212471008301</v>
+        <v>16.8212490081787</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G912" t="n">
-        <v>16.5802574157715</v>
+        <v>16.5802536010742</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G915" t="n">
-        <v>15.3752937316895</v>
+        <v>15.3752927780151</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>14.6523170471191</v>
+        <v>14.6523180007935</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>15.5</v>
       </c>
       <c r="G920" t="n">
-        <v>14.9415082931519</v>
+        <v>14.9415073394775</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>13.9293394088745</v>
+        <v>13.9293403625488</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G924" t="n">
-        <v>12.9653730392456</v>
+        <v>12.9653739929199</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>14.1221342086792</v>
+        <v>14.1221351623535</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>15.7126798629761</v>
+        <v>15.7126817703247</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>16.0018749237061</v>
+        <v>16.0018730163574</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>16.1946678161621</v>
+        <v>16.1946659088135</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>15.7126798629761</v>
+        <v>15.7126817703247</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>15.75</v>
       </c>
       <c r="G933" t="n">
-        <v>15.1824998855591</v>
+        <v>15.1825008392334</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G934" t="n">
-        <v>15.2306995391846</v>
+        <v>15.2306985855103</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>15.0861024856567</v>
+        <v>15.0861034393311</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G937" t="n">
-        <v>14.4113245010376</v>
+        <v>14.4113254547119</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G938" t="n">
-        <v>14.3631267547607</v>
+        <v>14.3631258010864</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G940" t="n">
-        <v>15.3752937316895</v>
+        <v>15.3752927780151</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G941" t="n">
-        <v>15.0861024856567</v>
+        <v>15.0861034393311</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>15.2306995391846</v>
+        <v>15.2306985855103</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>15.75</v>
       </c>
       <c r="G945" t="n">
-        <v>15.1824998855591</v>
+        <v>15.1825008392334</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>15.3752937316895</v>
+        <v>15.3752927780151</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G947" t="n">
-        <v>15.0861024856567</v>
+        <v>15.0861034393311</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G948" t="n">
-        <v>15.2306995391846</v>
+        <v>15.2306985855103</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>14.6523170471191</v>
+        <v>14.6523180007935</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>15</v>
       </c>
       <c r="G950" t="n">
-        <v>14.4595241546631</v>
+        <v>14.4595232009888</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>14.3631267547607</v>
+        <v>14.3631258010864</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G954" t="n">
-        <v>14.3631267547607</v>
+        <v>14.3631258010864</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15</v>
       </c>
       <c r="G955" t="n">
-        <v>14.4595241546631</v>
+        <v>14.4595232009888</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>14.4113245010376</v>
+        <v>14.4113254547119</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>14.3631267547607</v>
+        <v>14.3631258010864</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G960" t="n">
-        <v>13.6401510238647</v>
+        <v>13.6401500701904</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>13.6883487701416</v>
+        <v>13.6883497238159</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -54400,6 +54400,32 @@
         <v>8.80000019073486</v>
       </c>
       <c r="H2078" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2079" t="n">
+        <v>4052</v>
+      </c>
+      <c r="C2079" t="n">
+        <v>8.81999969482422</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>8.69999980926514</v>
+      </c>
+      <c r="E2079" t="n">
+        <v>8.81999969482422</v>
+      </c>
+      <c r="F2079" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="G2079" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="H2079" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G2" t="n">
-        <v>2.57321286201477</v>
+        <v>2.57321262359619</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.87050008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>2.73570656776428</v>
+        <v>2.73570680618286</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G4" t="n">
-        <v>2.83053374290466</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G7" t="n">
-        <v>2.80670785903931</v>
+        <v>2.80670809745789</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84006428718567</v>
+        <v>2.84006452560425</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.97449994087219</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8348228931427</v>
+        <v>2.83482265472412</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.9614999294281</v>
       </c>
       <c r="G11" t="n">
-        <v>2.82243299484253</v>
+        <v>2.82243323326111</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G12" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.98900008201599</v>
       </c>
       <c r="G13" t="n">
-        <v>2.84864211082458</v>
+        <v>2.84864187240601</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.97449994087219</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8348228931427</v>
+        <v>2.83482265472412</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78764677047729</v>
+        <v>2.78764724731445</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>2.71616911888123</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>2.70663857460022</v>
+        <v>2.70663833618164</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.70663857460022</v>
+        <v>2.70663833618164</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G26" t="n">
-        <v>2.71616911888123</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.71616911888123</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.71616911888123</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G29" t="n">
-        <v>2.61895895004272</v>
+        <v>2.61895871162415</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.75</v>
       </c>
       <c r="G30" t="n">
-        <v>2.62086510658264</v>
+        <v>2.62086486816406</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.75</v>
       </c>
       <c r="G31" t="n">
-        <v>2.62086510658264</v>
+        <v>2.62086486816406</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.75</v>
       </c>
       <c r="G32" t="n">
-        <v>2.62086510658264</v>
+        <v>2.62086486816406</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.75</v>
       </c>
       <c r="G33" t="n">
-        <v>2.62086510658264</v>
+        <v>2.62086486816406</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.75</v>
       </c>
       <c r="G34" t="n">
-        <v>2.62086510658264</v>
+        <v>2.62086486816406</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G35" t="n">
-        <v>2.67232918739319</v>
+        <v>2.67232894897461</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>2.78288173675537</v>
+        <v>2.78288245201111</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G38" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G42" t="n">
-        <v>2.83053374290466</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G43" t="n">
-        <v>2.83053374290466</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87818598747253</v>
+        <v>2.87818622589111</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.02049994468689</v>
       </c>
       <c r="G48" t="n">
-        <v>2.87866258621216</v>
+        <v>2.87866234779358</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.05550003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>2.9120192527771</v>
+        <v>2.91201901435852</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01161193847656</v>
+        <v>3.01161170005798</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.00208163261414</v>
+        <v>3.00208187103271</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G54" t="n">
-        <v>2.96395945549011</v>
+        <v>2.96395969390869</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>3.00208163261414</v>
+        <v>3.00208187103271</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>2.9163076877594</v>
+        <v>2.91630744934082</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>2.87818598747253</v>
+        <v>2.87818622589111</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G67" t="n">
-        <v>2.83053374290466</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G69" t="n">
-        <v>2.84482955932617</v>
+        <v>2.84482979774475</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83053374290466</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80670785903931</v>
+        <v>2.80670809745789</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3</v>
       </c>
       <c r="G74" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3</v>
       </c>
       <c r="G75" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G76" t="n">
-        <v>2.78288173675537</v>
+        <v>2.78288245201111</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.90549993515015</v>
       </c>
       <c r="G80" t="n">
-        <v>2.76906275749207</v>
+        <v>2.76906251907349</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>2.77335166931152</v>
+        <v>2.77335119247437</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G85" t="n">
-        <v>2.92202663421631</v>
+        <v>2.92202615737915</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>2.9163076877594</v>
+        <v>2.91630744934082</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.04900002479553</v>
       </c>
       <c r="G88" t="n">
-        <v>2.90582418441772</v>
+        <v>2.9058244228363</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G89" t="n">
-        <v>2.8505482673645</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G90" t="n">
-        <v>2.8505482673645</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G91" t="n">
-        <v>2.8505482673645</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.93050003051758</v>
       </c>
       <c r="G92" t="n">
-        <v>2.792888879776</v>
+        <v>2.79288911819458</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G95" t="n">
-        <v>2.82576894760132</v>
+        <v>2.82576847076416</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G97" t="n">
-        <v>2.83815813064575</v>
+        <v>2.83815836906433</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G98" t="n">
-        <v>2.83815813064575</v>
+        <v>2.83815836906433</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.98850011825562</v>
       </c>
       <c r="G105" t="n">
-        <v>2.8481650352478</v>
+        <v>2.84816551208496</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G109" t="n">
-        <v>2.72045755386353</v>
+        <v>2.7204577922821</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G110" t="n">
-        <v>2.72045755386353</v>
+        <v>2.7204577922821</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.91700005531311</v>
       </c>
       <c r="G111" t="n">
-        <v>2.78002285957336</v>
+        <v>2.78002309799194</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.05949997901917</v>
       </c>
       <c r="G113" t="n">
-        <v>2.91583108901978</v>
+        <v>2.91583132743835</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.05949997901917</v>
       </c>
       <c r="G114" t="n">
-        <v>2.91583108901978</v>
+        <v>2.91583132743835</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G116" t="n">
-        <v>2.84959506988525</v>
+        <v>2.84959483146667</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.92549991607666</v>
       </c>
       <c r="G117" t="n">
-        <v>2.7881236076355</v>
+        <v>2.78812384605408</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G118" t="n">
-        <v>2.79622459411621</v>
+        <v>2.79622483253479</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3</v>
       </c>
       <c r="G121" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.95149993896484</v>
       </c>
       <c r="G122" t="n">
-        <v>2.81290292739868</v>
+        <v>2.8129026889801</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G126" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78288173675537</v>
+        <v>2.78288245201111</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>2.78288173675537</v>
+        <v>2.78288245201111</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G131" t="n">
-        <v>2.83053374290466</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G132" t="n">
-        <v>2.83053374290466</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.92249989509583</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78526425361633</v>
+        <v>2.78526449203491</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>2.83053374290466</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.83053374290466</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G136" t="n">
-        <v>2.83053374290466</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G137" t="n">
-        <v>2.83053374290466</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.95700001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.81814479827881</v>
+        <v>2.81814432144165</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G140" t="n">
-        <v>2.87818598747253</v>
+        <v>2.87818622589111</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3</v>
       </c>
       <c r="G141" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G142" t="n">
-        <v>2.88390398025513</v>
+        <v>2.88390445709229</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3</v>
       </c>
       <c r="G143" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.02950000762939</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88724040985107</v>
+        <v>2.8872401714325</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>2.9163076877594</v>
+        <v>2.91630744934082</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>2.9830207824707</v>
+        <v>2.98302054405212</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>3.05926394462585</v>
+        <v>3.05926418304443</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.32949995994568</v>
       </c>
       <c r="G153" t="n">
-        <v>3.17315244674683</v>
+        <v>3.17315220832825</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.40949988365173</v>
       </c>
       <c r="G155" t="n">
-        <v>3.24939584732056</v>
+        <v>3.2493953704834</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G156" t="n">
-        <v>3.22890567779541</v>
+        <v>3.22890543937683</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G157" t="n">
-        <v>3.18315958976746</v>
+        <v>3.18315935134888</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.35349988937378</v>
       </c>
       <c r="G158" t="n">
-        <v>3.19602584838867</v>
+        <v>3.19602560997009</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>3.28799390792847</v>
+        <v>3.28799414634705</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>3.24034190177917</v>
+        <v>3.24034237861633</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.43549990653992</v>
       </c>
       <c r="G161" t="n">
-        <v>3.27417469024658</v>
+        <v>3.27417492866516</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G162" t="n">
-        <v>3.21175026893616</v>
+        <v>3.21175074577332</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>3.21175026893616</v>
+        <v>3.21175074577332</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>3.21175026893616</v>
+        <v>3.21175074577332</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.2546374797821</v>
+        <v>3.25463771820068</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>3.26893329620361</v>
+        <v>3.26893377304077</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>3.31658530235291</v>
+        <v>3.31658506393433</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>3.31658530235291</v>
+        <v>3.31658506393433</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.59450006484985</v>
       </c>
       <c r="G171" t="n">
-        <v>3.42570877075195</v>
+        <v>3.42570829391479</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.47860240936279</v>
+        <v>3.47860264778137</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G175" t="n">
-        <v>3.55484580993652</v>
+        <v>3.55484557151794</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.75</v>
       </c>
       <c r="G176" t="n">
-        <v>3.57390689849854</v>
+        <v>3.57390666007996</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.75</v>
       </c>
       <c r="G177" t="n">
-        <v>3.57390689849854</v>
+        <v>3.57390666007996</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G178" t="n">
-        <v>3.76451516151428</v>
+        <v>3.7645149230957</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>3.84075880050659</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>3.75498461723328</v>
+        <v>3.75498485565186</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G181" t="n">
-        <v>3.75498461723328</v>
+        <v>3.75498485565186</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G182" t="n">
-        <v>3.62155842781067</v>
+        <v>3.62155866622925</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G183" t="n">
-        <v>3.54531526565552</v>
+        <v>3.5453155040741</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>3.62155842781067</v>
+        <v>3.62155866622925</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>3.65014958381653</v>
+        <v>3.65015006065369</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>3.84075880050659</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G192" t="n">
-        <v>3.84075880050659</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>3.95512294769287</v>
+        <v>3.95512342453003</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4</v>
       </c>
       <c r="G194" t="n">
-        <v>3.81216716766357</v>
+        <v>3.812166929245</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4</v>
       </c>
       <c r="G195" t="n">
-        <v>3.81216716766357</v>
+        <v>3.812166929245</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>3.75498461723328</v>
+        <v>3.75498485565186</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>3.75498461723328</v>
+        <v>3.75498485565186</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>3.87951278686523</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>3.88909125328064</v>
+        <v>3.88909149169922</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82203793525696</v>
+        <v>3.82203769683838</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>3.70708918571472</v>
+        <v>3.7070894241333</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>3.87951278686523</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>3.87951278686523</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>3.78372168540955</v>
+        <v>3.78372144699097</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>3.87951278686523</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>3.87951278686523</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.93698620796204</v>
+        <v>3.93698644638062</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G218" t="n">
-        <v>3.9465651512146</v>
+        <v>3.94656562805176</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>4.02319765090942</v>
+        <v>4.02319812774658</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>4.03277778625488</v>
+        <v>4.03277683258057</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.21477890014648</v>
+        <v>4.21477937698364</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G225" t="n">
-        <v>4.39678049087524</v>
+        <v>4.3967809677124</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>4.45425462722778</v>
+        <v>4.45425510406494</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G229" t="n">
-        <v>4.43509674072266</v>
+        <v>4.4350962638855</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G237" t="n">
-        <v>4.96194362640381</v>
+        <v>4.96194410324097</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G238" t="n">
-        <v>5.00025939941406</v>
+        <v>5.00026035308838</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>4.90446949005127</v>
+        <v>4.90446996688843</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G241" t="n">
-        <v>4.94278526306152</v>
+        <v>4.94278621673584</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5</v>
       </c>
       <c r="G242" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5</v>
       </c>
       <c r="G243" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5</v>
       </c>
       <c r="G245" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>4.71288919448853</v>
+        <v>4.71288871765137</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>4.71288919448853</v>
+        <v>4.71288871765137</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G248" t="n">
-        <v>4.71288919448853</v>
+        <v>4.71288871765137</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5</v>
       </c>
       <c r="G255" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>4.63625717163086</v>
+        <v>4.6362566947937</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>4.64583587646484</v>
+        <v>4.64583539962769</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>4.59794044494629</v>
+        <v>4.59793996810913</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>4.59794044494629</v>
+        <v>4.59793996810913</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G269" t="n">
-        <v>4.59794044494629</v>
+        <v>4.59793996810913</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>4.578782081604</v>
+        <v>4.57878303527832</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>4.76078319549561</v>
+        <v>4.76078462600708</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G275" t="n">
-        <v>4.76078319549561</v>
+        <v>4.76078462600708</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>4.62667798995972</v>
+        <v>4.6266770362854</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>4.71288919448853</v>
+        <v>4.71288871765137</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.64583587646484</v>
+        <v>4.64583539962769</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>4.64583587646484</v>
+        <v>4.64583539962769</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G285" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>4.75120544433594</v>
+        <v>4.75120496749878</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G294" t="n">
-        <v>4.76078319549561</v>
+        <v>4.76078462600708</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G299" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G301" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G302" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G303" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5</v>
       </c>
       <c r="G304" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5</v>
       </c>
       <c r="G311" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5</v>
       </c>
       <c r="G312" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G314" t="n">
-        <v>4.77994155883789</v>
+        <v>4.77994203567505</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.76078319549561</v>
+        <v>4.76078462600708</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5</v>
       </c>
       <c r="G316" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5</v>
       </c>
       <c r="G322" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5</v>
       </c>
       <c r="G326" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5</v>
       </c>
       <c r="G330" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5</v>
       </c>
       <c r="G333" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>4.75120544433594</v>
+        <v>4.75120496749878</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5</v>
       </c>
       <c r="G336" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G343" t="n">
-        <v>5.00025939941406</v>
+        <v>5.00026035308838</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.13436651229858</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.11520910263062</v>
+        <v>5.11520862579346</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>5.5</v>
       </c>
       <c r="G347" t="n">
-        <v>5.26847314834595</v>
+        <v>5.26847410202026</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G348" t="n">
-        <v>5.32594728469849</v>
+        <v>5.32594776153564</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G349" t="n">
-        <v>5.21099901199341</v>
+        <v>5.21099948883057</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.13436651229858</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G351" t="n">
-        <v>5.13436651229858</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G352" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G361" t="n">
-        <v>5.21099901199341</v>
+        <v>5.21099948883057</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.13436651229858</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>5.32594728469849</v>
+        <v>5.32594776153564</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>5.28763198852539</v>
+        <v>5.28763151168823</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>5.3642635345459</v>
+        <v>5.36426401138306</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G368" t="n">
-        <v>5.47921180725098</v>
+        <v>5.47921228408813</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>5.68995189666748</v>
+        <v>5.68995141983032</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>5.84321546554565</v>
+        <v>5.84321594238281</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6</v>
       </c>
       <c r="G375" t="n">
-        <v>5.74742603302002</v>
+        <v>5.74742555618286</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G377" t="n">
-        <v>5.90069055557251</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>5.86237382888794</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G379" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>5.86237382888794</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G384" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G386" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G388" t="n">
-        <v>5.97732210159302</v>
+        <v>5.9773211479187</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G393" t="n">
-        <v>5.86237382888794</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G394" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G395" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>6.03479623794556</v>
+        <v>6.03479719161987</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>6.07311296463013</v>
+        <v>6.07311344146729</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964200973511</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G399" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964200973511</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G401" t="n">
-        <v>6.36048460006714</v>
+        <v>6.36048412322998</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G402" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964200973511</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G403" t="n">
-        <v>6.45627450942993</v>
+        <v>6.45627498626709</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>6.36048460006714</v>
+        <v>6.36048412322998</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>6.5</v>
       </c>
       <c r="G409" t="n">
-        <v>6.22637748718262</v>
+        <v>6.22637701034546</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>6.03479623794556</v>
+        <v>6.03479719161987</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>6.03479623794556</v>
+        <v>6.03479719161987</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G412" t="n">
-        <v>6.03479623794556</v>
+        <v>6.03479719161987</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>5.86237382888794</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G414" t="n">
-        <v>6.07311296463013</v>
+        <v>6.07311344146729</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.55584383010864</v>
+        <v>5.55584526062012</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>6</v>
       </c>
       <c r="G416" t="n">
-        <v>5.74742603302002</v>
+        <v>5.74742555618286</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G417" t="n">
-        <v>5.90069055557251</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>5.72826719284058</v>
+        <v>5.72826814651489</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G419" t="n">
-        <v>5.90069055557251</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>5.70910882949829</v>
+        <v>5.70910930633545</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>5.70910882949829</v>
+        <v>5.70910930633545</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>5.67079305648804</v>
+        <v>5.67079401016235</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G423" t="n">
-        <v>5.67079305648804</v>
+        <v>5.67079401016235</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G424" t="n">
-        <v>5.86237382888794</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G426" t="n">
-        <v>5.97732210159302</v>
+        <v>5.9773211479187</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>6.07311296463013</v>
+        <v>6.07311344146729</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>6.03479623794556</v>
+        <v>6.03479719161987</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G430" t="n">
-        <v>6.053955078125</v>
+        <v>6.05395460128784</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G431" t="n">
-        <v>6.053955078125</v>
+        <v>6.05395460128784</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G432" t="n">
-        <v>6.11142921447754</v>
+        <v>6.11142873764038</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>6.30300998687744</v>
+        <v>6.30300951004028</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G436" t="n">
-        <v>6.57122325897217</v>
+        <v>6.57122373580933</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7</v>
       </c>
       <c r="G438" t="n">
-        <v>6.70532989501953</v>
+        <v>6.70532941818237</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>7</v>
       </c>
       <c r="G439" t="n">
-        <v>6.70532989501953</v>
+        <v>6.70532941818237</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>6.64785575866699</v>
+        <v>6.64785528182983</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7</v>
       </c>
       <c r="G441" t="n">
-        <v>6.70532989501953</v>
+        <v>6.70532941818237</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>6.6861720085144</v>
+        <v>6.68617153167725</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>7</v>
       </c>
       <c r="G443" t="n">
-        <v>6.70532989501953</v>
+        <v>6.70532941818237</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G444" t="n">
-        <v>6.7819619178772</v>
+        <v>6.78196239471436</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>6.99270105361938</v>
+        <v>6.99270153045654</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>7.16512393951416</v>
+        <v>7.165123462677</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>7.5</v>
       </c>
       <c r="G447" t="n">
-        <v>7.18428182601929</v>
+        <v>7.1842827796936</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G448" t="n">
-        <v>7.50996971130371</v>
+        <v>7.50996923446655</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G449" t="n">
-        <v>7.79734039306641</v>
+        <v>7.79734086990356</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G450" t="n">
-        <v>7.68239259719849</v>
+        <v>7.68239212036133</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G451" t="n">
-        <v>8.00807952880859</v>
+        <v>8.00807857513428</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.5</v>
       </c>
       <c r="G454" t="n">
-        <v>8.17150974273682</v>
+        <v>8.17151069641113</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G455" t="n">
-        <v>7.99846506118774</v>
+        <v>7.99846458435059</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.5</v>
       </c>
       <c r="G458" t="n">
-        <v>8.17150974273682</v>
+        <v>8.17151069641113</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>7.80619478225708</v>
+        <v>7.8061957359314</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>7.53701639175415</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>7.13324737548828</v>
+        <v>7.13324785232544</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>7.3255181312561</v>
+        <v>7.32551765441895</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G469" t="n">
-        <v>7.26783657073975</v>
+        <v>7.2678370475769</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G470" t="n">
-        <v>7.24861001968384</v>
+        <v>7.24860954284668</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>7.5</v>
       </c>
       <c r="G471" t="n">
-        <v>7.21015501022339</v>
+        <v>7.21015596389771</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.5</v>
       </c>
       <c r="G473" t="n">
-        <v>7.21015501022339</v>
+        <v>7.21015596389771</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469652175903</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G477" t="n">
-        <v>7.57547044754028</v>
+        <v>7.57547092437744</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>7.57547044754028</v>
+        <v>7.57547092437744</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469652175903</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469652175903</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>7.57547044754028</v>
+        <v>7.57547092437744</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469652175903</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469652175903</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469652175903</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>7.57547044754028</v>
+        <v>7.57547092437744</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G490" t="n">
-        <v>7.55624294281006</v>
+        <v>7.55624341964722</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G492" t="n">
-        <v>7.57547044754028</v>
+        <v>7.57547092437744</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G493" t="n">
-        <v>7.57547044754028</v>
+        <v>7.57547092437744</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>7.53701639175415</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>7.53701639175415</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G496" t="n">
-        <v>7.51778841018677</v>
+        <v>7.51778888702393</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G497" t="n">
-        <v>7.53701639175415</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>7.76774024963379</v>
+        <v>7.76774072647095</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>7.76774024963379</v>
+        <v>7.76774072647095</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G504" t="n">
-        <v>7.8254222869873</v>
+        <v>7.82542276382446</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G506" t="n">
-        <v>8.15228271484375</v>
+        <v>8.15228176116943</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G507" t="n">
-        <v>8.34455394744873</v>
+        <v>8.34455299377441</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>8.45991611480713</v>
+        <v>8.45991706848145</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G510" t="n">
-        <v>8.55605030059814</v>
+        <v>8.55605125427246</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G511" t="n">
-        <v>8.55605030059814</v>
+        <v>8.55605125427246</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9</v>
       </c>
       <c r="G512" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G513" t="n">
-        <v>8.74832153320312</v>
+        <v>8.74832344055176</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>9.24822521209717</v>
+        <v>9.24822616577148</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>9.5</v>
       </c>
       <c r="G516" t="n">
-        <v>9.13286304473877</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G518" t="n">
-        <v>9.30590724945068</v>
+        <v>9.305908203125</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G519" t="n">
-        <v>9.30590724945068</v>
+        <v>9.305908203125</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>9.5</v>
       </c>
       <c r="G520" t="n">
-        <v>9.13286304473877</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>9.49817848205566</v>
+        <v>9.49817752838135</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G527" t="n">
-        <v>9.01750183105469</v>
+        <v>9.01750087738037</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G532" t="n">
-        <v>9.07518291473389</v>
+        <v>9.07518196105957</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G538" t="n">
-        <v>8.74832153320312</v>
+        <v>8.74832344055176</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>8.69064044952393</v>
+        <v>8.69064140319824</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>9</v>
       </c>
       <c r="G540" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9</v>
       </c>
       <c r="G542" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>8.61373233795166</v>
+        <v>8.61373329162598</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>8.45991611480713</v>
+        <v>8.45991706848145</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G549" t="n">
-        <v>8.45991611480713</v>
+        <v>8.45991706848145</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G550" t="n">
-        <v>8.42146110534668</v>
+        <v>8.421462059021</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G551" t="n">
-        <v>8.42146110534668</v>
+        <v>8.421462059021</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G552" t="n">
-        <v>8.36378002166748</v>
+        <v>8.36377906799316</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G553" t="n">
-        <v>8.42146110534668</v>
+        <v>8.421462059021</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G554" t="n">
-        <v>8.42146110534668</v>
+        <v>8.421462059021</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G555" t="n">
-        <v>8.36378002166748</v>
+        <v>8.36377906799316</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>8.45991611480713</v>
+        <v>8.45991706848145</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.45991611480713</v>
+        <v>8.45991706848145</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>8.55605030059814</v>
+        <v>8.55605125427246</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G559" t="n">
-        <v>8.55605030059814</v>
+        <v>8.55605125427246</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G560" t="n">
-        <v>8.59450531005859</v>
+        <v>8.59450340270996</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G562" t="n">
-        <v>8.95981979370117</v>
+        <v>8.95981884002686</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G563" t="n">
-        <v>8.90213966369629</v>
+        <v>8.90213871002197</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>8.97904682159424</v>
+        <v>8.97904777526855</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G566" t="n">
-        <v>8.95981979370117</v>
+        <v>8.95981884002686</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G567" t="n">
-        <v>9.19054412841797</v>
+        <v>9.1905460357666</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G569" t="n">
-        <v>9.28668117523193</v>
+        <v>9.28668022155762</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G571" t="n">
-        <v>9.07518291473389</v>
+        <v>9.07518196105957</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G572" t="n">
-        <v>9.0559549331665</v>
+        <v>9.05595588684082</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>9.07518291473389</v>
+        <v>9.07518196105957</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G574" t="n">
-        <v>9.01750183105469</v>
+        <v>9.01750087738037</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>9</v>
       </c>
       <c r="G576" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G578" t="n">
-        <v>8.97904682159424</v>
+        <v>8.97904777526855</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G579" t="n">
-        <v>8.90213966369629</v>
+        <v>8.90213871002197</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G580" t="n">
-        <v>8.86368560791016</v>
+        <v>8.86368465423584</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>8.72909545898438</v>
+        <v>8.72909450531006</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9</v>
       </c>
       <c r="G584" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.69064044952393</v>
+        <v>8.69064140319824</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>8.74832153320312</v>
+        <v>8.74832344055176</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>9</v>
       </c>
       <c r="G590" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>9</v>
       </c>
       <c r="G591" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G592" t="n">
-        <v>8.59450531005859</v>
+        <v>8.59450340270996</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9</v>
       </c>
       <c r="G593" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>8.76754856109619</v>
+        <v>8.76754951477051</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G597" t="n">
-        <v>9.11363697052002</v>
+        <v>9.1136360168457</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>9.32513618469238</v>
+        <v>9.32513332366943</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>9.5</v>
       </c>
       <c r="G599" t="n">
-        <v>9.13286304473877</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>9.32513618469238</v>
+        <v>9.32513332366943</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G603" t="n">
-        <v>9.20977210998535</v>
+        <v>9.20977115631104</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>9.2289981842041</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G609" t="n">
-        <v>9.11363697052002</v>
+        <v>9.1136360168457</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G610" t="n">
-        <v>9.11363697052002</v>
+        <v>9.1136360168457</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.5</v>
       </c>
       <c r="G611" t="n">
-        <v>9.13286304473877</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G614" t="n">
-        <v>9.20977210998535</v>
+        <v>9.20977115631104</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>9.20977210998535</v>
+        <v>9.20977115631104</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G616" t="n">
-        <v>9.2289981842041</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.13286304473877</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G619" t="n">
-        <v>9.2289981842041</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G620" t="n">
-        <v>9.2289981842041</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G622" t="n">
-        <v>9.2289981842041</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>9.75774478912354</v>
+        <v>9.7577428817749</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>9.99808120727539</v>
+        <v>9.99808216094971</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G628" t="n">
-        <v>10.2864875793457</v>
+        <v>10.28648853302</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>10.2864875793457</v>
+        <v>10.28648853302</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G630" t="n">
-        <v>10.2864875793457</v>
+        <v>10.28648853302</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>10.1422853469849</v>
+        <v>10.1422872543335</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G632" t="n">
-        <v>10.1422853469849</v>
+        <v>10.1422872543335</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>9.95001411437988</v>
+        <v>9.9500150680542</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G636" t="n">
-        <v>10.0461502075195</v>
+        <v>10.0461483001709</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>10.1903553009033</v>
+        <v>10.1903524398804</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>10.2864875793457</v>
+        <v>10.28648853302</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>10.75</v>
       </c>
       <c r="G642" t="n">
-        <v>10.3345556259155</v>
+        <v>10.3345546722412</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.75</v>
       </c>
       <c r="G643" t="n">
-        <v>10.3345556259155</v>
+        <v>10.3345546722412</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>10.75</v>
       </c>
       <c r="G646" t="n">
-        <v>10.3345556259155</v>
+        <v>10.3345546722412</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>10.67103099823</v>
+        <v>10.6710290908813</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>10.67103099823</v>
+        <v>10.6710290908813</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>10.767165184021</v>
+        <v>10.7671661376953</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>11.6323852539062</v>
+        <v>11.6323843002319</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>13.25</v>
       </c>
       <c r="G657" t="n">
-        <v>12.7379417419434</v>
+        <v>12.737940788269</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G658" t="n">
-        <v>12.5937395095825</v>
+        <v>12.5937385559082</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G660" t="n">
-        <v>12.8340768814087</v>
+        <v>12.834077835083</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>12.5937395095825</v>
+        <v>12.5937385559082</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>12.1130619049072</v>
+        <v>12.1130628585815</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G664" t="n">
-        <v>12.8821439743042</v>
+        <v>12.8821430206299</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>12.8340768814087</v>
+        <v>12.834077835083</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>12.5937395095825</v>
+        <v>12.5937385559082</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>13.25</v>
       </c>
       <c r="G671" t="n">
-        <v>12.7379417419434</v>
+        <v>12.737940788269</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>13.25</v>
       </c>
       <c r="G672" t="n">
-        <v>12.7379417419434</v>
+        <v>12.737940788269</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G673" t="n">
-        <v>13.0263481140137</v>
+        <v>13.0263471603394</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G674" t="n">
-        <v>13.507025718689</v>
+        <v>13.5070247650146</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>14.5</v>
       </c>
       <c r="G675" t="n">
-        <v>13.9396352767944</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>14.5</v>
       </c>
       <c r="G676" t="n">
-        <v>13.9396352767944</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>14.5</v>
       </c>
       <c r="G677" t="n">
-        <v>13.9396352767944</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>13.7954320907593</v>
+        <v>13.795431137085</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>13.507025718689</v>
+        <v>13.5070247650146</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>13.6512279510498</v>
+        <v>13.6512269973755</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>14.1319046020508</v>
+        <v>14.1319055557251</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G685" t="n">
-        <v>14.1319046020508</v>
+        <v>14.1319055557251</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>13.7954320907593</v>
+        <v>13.795431137085</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>14.5</v>
       </c>
       <c r="G690" t="n">
-        <v>13.9396352767944</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>14.5</v>
       </c>
       <c r="G691" t="n">
-        <v>13.9396352767944</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>14.25</v>
       </c>
       <c r="G695" t="n">
-        <v>13.6992950439453</v>
+        <v>13.6992959976196</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>14</v>
       </c>
       <c r="G696" t="n">
-        <v>13.4589567184448</v>
+        <v>13.4589557647705</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>14</v>
       </c>
       <c r="G697" t="n">
-        <v>13.4589567184448</v>
+        <v>13.4589557647705</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G698" t="n">
-        <v>13.5550928115845</v>
+        <v>13.5550937652588</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>13.60315990448</v>
+        <v>13.6031589508057</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>14.75</v>
       </c>
       <c r="G705" t="n">
-        <v>14.1799716949463</v>
+        <v>14.1799726486206</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G709" t="n">
-        <v>15.1343011856079</v>
+        <v>15.1343021392822</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G713" t="n">
-        <v>16.6766510009766</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>16.7248477935791</v>
+        <v>16.7248497009277</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>16.8212490081787</v>
+        <v>16.8212471008301</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838542938232</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>16.5</v>
       </c>
       <c r="G726" t="n">
-        <v>15.9054746627808</v>
+        <v>15.9054756164551</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>16.05006980896</v>
+        <v>16.0500679016113</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838542938232</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838542938232</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>16.0982704162598</v>
+        <v>16.0982723236084</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>16.0982704162598</v>
+        <v>16.0982723236084</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G740" t="n">
-        <v>15.2306985855103</v>
+        <v>15.2306976318359</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>14.8451108932495</v>
+        <v>14.8451099395752</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>15.5198879241943</v>
+        <v>15.5198888778687</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G746" t="n">
-        <v>15.2306985855103</v>
+        <v>15.2306976318359</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>14.8451108932495</v>
+        <v>14.8451099395752</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G749" t="n">
-        <v>14.8451108932495</v>
+        <v>14.8451099395752</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>15.2306985855103</v>
+        <v>15.2306976318359</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>16.25</v>
       </c>
       <c r="G757" t="n">
-        <v>15.6644830703735</v>
+        <v>15.6644849777222</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>15.7126817703247</v>
+        <v>15.7126808166504</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>15.6162872314453</v>
+        <v>15.616286277771</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G761" t="n">
-        <v>15.4716892242432</v>
+        <v>15.4716901779175</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>16.25</v>
       </c>
       <c r="G762" t="n">
-        <v>15.6644830703735</v>
+        <v>15.6644849777222</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>15.5198879241943</v>
+        <v>15.5198888778687</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G764" t="n">
-        <v>15.6162872314453</v>
+        <v>15.616286277771</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>15.6162872314453</v>
+        <v>15.616286277771</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G769" t="n">
-        <v>15.5680875778198</v>
+        <v>15.5680866241455</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>16.7248477935791</v>
+        <v>16.7248497009277</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>17.1586322784424</v>
+        <v>17.1586360931396</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G778" t="n">
-        <v>16.8212490081787</v>
+        <v>16.8212471008301</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G779" t="n">
-        <v>16.6766510009766</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>17.5</v>
       </c>
       <c r="G780" t="n">
-        <v>16.869441986084</v>
+        <v>16.8694458007812</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>16.6766510009766</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G782" t="n">
-        <v>16.7730484008789</v>
+        <v>16.7730445861816</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>16.6766510009766</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>16.5320568084717</v>
+        <v>16.532054901123</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G785" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838542938232</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>17.5</v>
       </c>
       <c r="G786" t="n">
-        <v>16.869441986084</v>
+        <v>16.8694458007812</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>17.2068347930908</v>
+        <v>17.2068328857422</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>17.1586322784424</v>
+        <v>17.1586360931396</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>17.75</v>
       </c>
       <c r="G795" t="n">
-        <v>17.1104373931885</v>
+        <v>17.1104354858398</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>17.5</v>
       </c>
       <c r="G798" t="n">
-        <v>16.869441986084</v>
+        <v>16.8694458007812</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>17.6888160705566</v>
+        <v>17.6888179779053</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>18.7009868621826</v>
+        <v>18.7009811401367</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G807" t="n">
-        <v>18.7491817474365</v>
+        <v>18.7491836547852</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>18.604585647583</v>
+        <v>18.6045875549316</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>18.5081920623779</v>
+        <v>18.5081901550293</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G810" t="n">
-        <v>18.3635921478271</v>
+        <v>18.3635940551758</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G811" t="n">
-        <v>18.4117946624756</v>
+        <v>18.411792755127</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>19</v>
       </c>
       <c r="G814" t="n">
-        <v>18.3153972625732</v>
+        <v>18.3153991699219</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>19</v>
       </c>
       <c r="G815" t="n">
-        <v>18.3153972625732</v>
+        <v>18.3153991699219</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>18.2189979553223</v>
+        <v>18.2189998626709</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>17.9780082702637</v>
+        <v>17.9780044555664</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>17.6888160705566</v>
+        <v>17.6888179779053</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>18.1226024627686</v>
+        <v>18.1226005554199</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>17.8816108703613</v>
+        <v>17.88161277771</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G833" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>19</v>
       </c>
       <c r="G834" t="n">
-        <v>18.3153972625732</v>
+        <v>18.3153991699219</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406173706055</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>18.5</v>
       </c>
       <c r="G839" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334102630615</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406173706055</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>17.8816108703613</v>
+        <v>17.88161277771</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406173706055</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406173706055</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>18.5</v>
       </c>
       <c r="G848" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334102630615</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>17.6888160705566</v>
+        <v>17.6888179779053</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G853" t="n">
-        <v>17.9780082702637</v>
+        <v>17.9780044555664</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>18.5</v>
       </c>
       <c r="G858" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334102630615</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>18.25</v>
       </c>
       <c r="G859" t="n">
-        <v>17.5924205780029</v>
+        <v>17.5924224853516</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>18.25</v>
       </c>
       <c r="G860" t="n">
-        <v>17.5924205780029</v>
+        <v>17.5924224853516</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>17.2068347930908</v>
+        <v>17.2068328857422</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>17.9780082702637</v>
+        <v>17.9780044555664</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>18.1226024627686</v>
+        <v>18.1226005554199</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>19</v>
       </c>
       <c r="G872" t="n">
-        <v>18.3153972625732</v>
+        <v>18.3153991699219</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>19</v>
       </c>
       <c r="G873" t="n">
-        <v>18.3153972625732</v>
+        <v>18.3153991699219</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G874" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G875" t="n">
-        <v>18.5081920623779</v>
+        <v>18.5081901550293</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G878" t="n">
-        <v>18.2189979553223</v>
+        <v>18.2189998626709</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>18.5081920623779</v>
+        <v>18.5081901550293</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G880" t="n">
-        <v>19.1347713470459</v>
+        <v>19.1347694396973</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>19.1829662322998</v>
+        <v>19.1829681396484</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G882" t="n">
-        <v>18.7491817474365</v>
+        <v>18.7491836547852</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G887" t="n">
-        <v>18.9901752471924</v>
+        <v>18.9901733398438</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>18.9901752471924</v>
+        <v>18.9901733398438</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>18.9901752471924</v>
+        <v>18.9901733398438</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>18.3635921478271</v>
+        <v>18.3635940551758</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>18.1226024627686</v>
+        <v>18.1226005554199</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>18.5</v>
       </c>
       <c r="G892" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334102630615</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>18.5</v>
       </c>
       <c r="G893" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334102630615</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>17.25</v>
       </c>
       <c r="G895" t="n">
-        <v>16.6284503936768</v>
+        <v>16.6284523010254</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>18.25</v>
       </c>
       <c r="G899" t="n">
-        <v>17.5924205780029</v>
+        <v>17.5924224853516</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>18.25</v>
       </c>
       <c r="G900" t="n">
-        <v>17.5924205780029</v>
+        <v>17.5924224853516</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>17.8816108703613</v>
+        <v>17.88161277771</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>17.2068347930908</v>
+        <v>17.2068328857422</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>17.5</v>
       </c>
       <c r="G909" t="n">
-        <v>16.869441986084</v>
+        <v>16.8694458007812</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>16.8212490081787</v>
+        <v>16.8212471008301</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>16.5</v>
       </c>
       <c r="G913" t="n">
-        <v>15.9054746627808</v>
+        <v>15.9054756164551</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>14.6523180007935</v>
+        <v>14.6523170471191</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>15.327094078064</v>
+        <v>15.3270950317383</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>15.327094078064</v>
+        <v>15.3270950317383</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>14.2667303085327</v>
+        <v>14.2667293548584</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>13.9293403625488</v>
+        <v>13.9293413162231</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G924" t="n">
-        <v>12.9653739929199</v>
+        <v>12.9653720855713</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>14.1221351623535</v>
+        <v>14.1221342086792</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>15.5198879241943</v>
+        <v>15.5198888778687</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>15.7126817703247</v>
+        <v>15.7126808166504</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>16.5</v>
       </c>
       <c r="G929" t="n">
-        <v>15.9054746627808</v>
+        <v>15.9054756164551</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>15.7126817703247</v>
+        <v>15.7126808166504</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G934" t="n">
-        <v>15.2306985855103</v>
+        <v>15.2306976318359</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>15.0861034393311</v>
+        <v>15.0861015319824</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>14.8451108932495</v>
+        <v>14.8451099395752</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G937" t="n">
-        <v>14.4113254547119</v>
+        <v>14.4113245010376</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>15.327094078064</v>
+        <v>15.3270950317383</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G941" t="n">
-        <v>15.0861034393311</v>
+        <v>15.0861015319824</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>15.1343011856079</v>
+        <v>15.1343021392822</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>15.2306985855103</v>
+        <v>15.2306976318359</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G947" t="n">
-        <v>15.0861034393311</v>
+        <v>15.0861015319824</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G948" t="n">
-        <v>15.2306985855103</v>
+        <v>15.2306976318359</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>14.6523180007935</v>
+        <v>14.6523170471191</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>15</v>
       </c>
       <c r="G950" t="n">
-        <v>14.4595232009888</v>
+        <v>14.4595251083374</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G952" t="n">
-        <v>14.604118347168</v>
+        <v>14.6041193008423</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15</v>
       </c>
       <c r="G955" t="n">
-        <v>14.4595232009888</v>
+        <v>14.4595251083374</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>14.4113254547119</v>
+        <v>14.4113245010376</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>14.2667303085327</v>
+        <v>14.2667293548584</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>13.6883497238159</v>
+        <v>13.6883478164673</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>14.5</v>
       </c>
       <c r="G962" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>13.75</v>
       </c>
       <c r="G964" t="n">
-        <v>13.3108072280884</v>
+        <v>13.3108062744141</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>14.5</v>
       </c>
       <c r="G966" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G969" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>14.13365650177</v>
+        <v>14.1336574554443</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G972" t="n">
-        <v>14.4724769592285</v>
+        <v>14.4724760055542</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>14.6176872253418</v>
+        <v>14.6176862716675</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>14.75</v>
       </c>
       <c r="G976" t="n">
-        <v>14.2788648605347</v>
+        <v>14.2788639068604</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>13.9400434494019</v>
+        <v>13.9400444030762</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G979" t="n">
-        <v>13.1171941757202</v>
+        <v>13.1171951293945</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G981" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>15.75</v>
       </c>
       <c r="G982" t="n">
-        <v>15.2469244003296</v>
+        <v>15.246922492981</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>16</v>
       </c>
       <c r="G984" t="n">
-        <v>15.4889392852783</v>
+        <v>15.488938331604</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>15.4405345916748</v>
+        <v>15.4405355453491</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G993" t="n">
-        <v>13.9400434494019</v>
+        <v>13.9400444030762</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>14.75</v>
       </c>
       <c r="G994" t="n">
-        <v>14.2788648605347</v>
+        <v>14.2788639068604</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.6980295181274</v>
+        <v>13.6980304718018</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.6980295181274</v>
+        <v>13.6980304718018</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1005" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1009" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.0203895568848</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>13.25</v>
       </c>
       <c r="G1016" t="n">
-        <v>12.8267774581909</v>
+        <v>12.8267765045166</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>13.25</v>
       </c>
       <c r="G1017" t="n">
-        <v>12.8267774581909</v>
+        <v>12.8267765045166</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1018" t="n">
-        <v>12.8751811981201</v>
+        <v>12.8751792907715</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>13.75</v>
       </c>
       <c r="G1027" t="n">
-        <v>13.3108072280884</v>
+        <v>13.3108062744141</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>14.5</v>
       </c>
       <c r="G1030" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>14.3272686004639</v>
+        <v>14.3272676467896</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1032" t="n">
-        <v>14.4724769592285</v>
+        <v>14.4724760055542</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.4724769592285</v>
+        <v>14.4724760055542</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1036" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>14.75</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.2788648605347</v>
+        <v>14.2788639068604</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1040" t="n">
-        <v>14.6176872253418</v>
+        <v>14.6176862716675</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>14.75</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.2788648605347</v>
+        <v>14.2788639068604</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.13365650177</v>
+        <v>14.1336574554443</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1045" t="n">
-        <v>13.8916425704956</v>
+        <v>13.8916416168213</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.13365650177</v>
+        <v>14.1336574554443</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>14.5</v>
       </c>
       <c r="G1048" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1049" t="n">
-        <v>14.13365650177</v>
+        <v>14.1336574554443</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1051" t="n">
-        <v>14.13365650177</v>
+        <v>14.1336574554443</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1052" t="n">
-        <v>13.9400434494019</v>
+        <v>13.9400444030762</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>13.9400434494019</v>
+        <v>13.9400444030762</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>13.5</v>
       </c>
       <c r="G1062" t="n">
-        <v>13.0687913894653</v>
+        <v>13.0687923431396</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>13.5</v>
       </c>
       <c r="G1063" t="n">
-        <v>13.0687913894653</v>
+        <v>13.0687923431396</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1064" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1066" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1069" t="n">
-        <v>11.9071216583252</v>
+        <v>11.9071207046509</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>12.1975393295288</v>
+        <v>12.1975402832031</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1075" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1076" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>13.25</v>
       </c>
       <c r="G1077" t="n">
-        <v>12.8267774581909</v>
+        <v>12.8267765045166</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1079" t="n">
-        <v>12.6331644058228</v>
+        <v>12.6331663131714</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>13.25</v>
       </c>
       <c r="G1080" t="n">
-        <v>12.8267774581909</v>
+        <v>12.8267765045166</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>12.6331644058228</v>
+        <v>12.6331663131714</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1086" t="n">
-        <v>12.6331644058228</v>
+        <v>12.6331663131714</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1087" t="n">
-        <v>12.6331644058228</v>
+        <v>12.6331663131714</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1092" t="n">
-        <v>12.6331644058228</v>
+        <v>12.6331663131714</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>12.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>12.75</v>
       </c>
       <c r="G1095" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1096" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1097" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>12.8751811981201</v>
+        <v>12.8751792907715</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>12.75</v>
       </c>
       <c r="G1100" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>12.75</v>
       </c>
       <c r="G1101" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>12.75</v>
       </c>
       <c r="G1104" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>12.75</v>
       </c>
       <c r="G1107" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>12.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1121" t="n">
-        <v>12.8751811981201</v>
+        <v>12.8751792907715</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1123" t="n">
-        <v>13.0203895568848</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>13.5</v>
       </c>
       <c r="G1125" t="n">
-        <v>13.0687913894653</v>
+        <v>13.0687923431396</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>13.0203895568848</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1136" t="n">
-        <v>13.9400434494019</v>
+        <v>13.9400444030762</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1138" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1140" t="n">
-        <v>13.9400434494019</v>
+        <v>13.9400444030762</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1141" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1145" t="n">
-        <v>14.3272686004639</v>
+        <v>14.3272676467896</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>15.25</v>
       </c>
       <c r="G1146" t="n">
-        <v>14.7628946304321</v>
+        <v>14.7628936767578</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1148" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>14.75</v>
       </c>
       <c r="G1151" t="n">
-        <v>14.2788648605347</v>
+        <v>14.2788639068604</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>14.5</v>
       </c>
       <c r="G1152" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1153" t="n">
-        <v>14.13365650177</v>
+        <v>14.1336574554443</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1154" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>14.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1157" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>14.5</v>
       </c>
       <c r="G1158" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1159" t="n">
-        <v>14.4724769592285</v>
+        <v>14.4724760055542</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1160" t="n">
-        <v>14.3272686004639</v>
+        <v>14.3272676467896</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1162" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>14.13365650177</v>
+        <v>14.1336574554443</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1164" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>14.5</v>
       </c>
       <c r="G1165" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1166" t="n">
-        <v>13.9400434494019</v>
+        <v>13.9400444030762</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>13.8916425704956</v>
+        <v>13.8916416168213</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>13.8916425704956</v>
+        <v>13.8916416168213</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>13.75</v>
       </c>
       <c r="G1174" t="n">
-        <v>13.3108072280884</v>
+        <v>13.3108062744141</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>13.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>13.3108072280884</v>
+        <v>13.3108062744141</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1176" t="n">
-        <v>12.8751811981201</v>
+        <v>12.8751792907715</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>13.5</v>
       </c>
       <c r="G1178" t="n">
-        <v>13.0687913894653</v>
+        <v>13.0687923431396</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>13.25</v>
       </c>
       <c r="G1179" t="n">
-        <v>12.8267774581909</v>
+        <v>12.8267765045166</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1180" t="n">
-        <v>12.8751811981201</v>
+        <v>12.8751792907715</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1182" t="n">
-        <v>12.9235830307007</v>
+        <v>12.923583984375</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1183" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1189" t="n">
-        <v>12.6331644058228</v>
+        <v>12.6331663131714</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>12.75</v>
       </c>
       <c r="G1190" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1193" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1194" t="n">
-        <v>13.0203895568848</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.9235830307007</v>
+        <v>12.923583984375</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1203" t="n">
-        <v>12.6331644058228</v>
+        <v>12.6331663131714</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.6331644058228</v>
+        <v>12.6331663131714</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1207" t="n">
-        <v>12.1975393295288</v>
+        <v>12.1975402832031</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1215" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1217" t="n">
-        <v>13.0203895568848</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>13.25</v>
       </c>
       <c r="G1218" t="n">
-        <v>12.8267774581909</v>
+        <v>12.8267765045166</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>13</v>
       </c>
       <c r="G1222" t="n">
-        <v>12.6539630889893</v>
+        <v>12.6539640426636</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>13</v>
       </c>
       <c r="G1223" t="n">
-        <v>12.6539630889893</v>
+        <v>12.6539640426636</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>12.75</v>
       </c>
       <c r="G1224" t="n">
-        <v>12.4106187820435</v>
+        <v>12.4106178283691</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1225" t="n">
-        <v>12.36194896698</v>
+        <v>12.3619480133057</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1226" t="n">
-        <v>12.5566253662109</v>
+        <v>12.5566244125366</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>12.5</v>
       </c>
       <c r="G1229" t="n">
-        <v>12.1672716140747</v>
+        <v>12.167272567749</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>12.25</v>
       </c>
       <c r="G1231" t="n">
-        <v>11.9239273071289</v>
+        <v>11.9239263534546</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1235" t="n">
-        <v>11.7779197692871</v>
+        <v>11.7779207229614</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1236" t="n">
-        <v>11.7779197692871</v>
+        <v>11.7779207229614</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>12</v>
       </c>
       <c r="G1237" t="n">
-        <v>11.6805810928345</v>
+        <v>11.6805820465088</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>12</v>
       </c>
       <c r="G1238" t="n">
-        <v>11.6805810928345</v>
+        <v>11.6805820465088</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>12</v>
       </c>
       <c r="G1240" t="n">
-        <v>11.6805810928345</v>
+        <v>11.6805820465088</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1241" t="n">
-        <v>11.5832433700562</v>
+        <v>11.5832424163818</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1243" t="n">
-        <v>11.4859046936035</v>
+        <v>11.4859056472778</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1245" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1246" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1247" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1250" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1253" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1256" t="n">
-        <v>11.3885669708252</v>
+        <v>11.3885660171509</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1259" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1260" t="n">
-        <v>11.3885669708252</v>
+        <v>11.3885660171509</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1262" t="n">
-        <v>10.9992141723633</v>
+        <v>10.9992151260376</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1264" t="n">
-        <v>10.9992141723633</v>
+        <v>10.9992151260376</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1265" t="n">
-        <v>10.9992141723633</v>
+        <v>10.9992151260376</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1266" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1267" t="n">
-        <v>10.9992141723633</v>
+        <v>10.9992151260376</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1273" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1275" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1283" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1292" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1295" t="n">
-        <v>11.3885669708252</v>
+        <v>11.3885660171509</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1300" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1302" t="n">
-        <v>10.9992141723633</v>
+        <v>10.9992151260376</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1303" t="n">
-        <v>10.9992141723633</v>
+        <v>10.9992151260376</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1304" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1305" t="n">
-        <v>10.9992141723633</v>
+        <v>10.9992151260376</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1318" t="n">
-        <v>10.6585302352905</v>
+        <v>10.6585311889648</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1319" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1322" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>10.3178482055664</v>
+        <v>10.3178472518921</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>9.78248691558838</v>
+        <v>9.7824878692627</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1331" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1333" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>10.5</v>
       </c>
       <c r="G1334" t="n">
-        <v>10.2205085754395</v>
+        <v>10.2205095291138</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1335" t="n">
-        <v>9.78248691558838</v>
+        <v>9.7824878692627</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1336" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718397140503</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1337" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718397140503</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1339" t="n">
-        <v>9.92849445343018</v>
+        <v>9.92849349975586</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1340" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1358" t="n">
-        <v>9.55860996246338</v>
+        <v>9.55860805511475</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1365" t="n">
-        <v>9.40286827087402</v>
+        <v>9.40286731719971</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1371" t="n">
-        <v>9.03298377990723</v>
+        <v>9.03298282623291</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1375" t="n">
-        <v>10.4151859283447</v>
+        <v>10.4151849746704</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1377" t="n">
-        <v>10.9992141723633</v>
+        <v>10.9992151260376</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1379" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1383" t="n">
-        <v>10.3178482055664</v>
+        <v>10.3178472518921</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1385" t="n">
-        <v>10.6585302352905</v>
+        <v>10.6585311889648</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1387" t="n">
-        <v>10.6585302352905</v>
+        <v>10.6585311889648</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1391" t="n">
-        <v>10.6585302352905</v>
+        <v>10.6585311889648</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1393" t="n">
-        <v>10.6585302352905</v>
+        <v>10.6585311889648</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1398" t="n">
-        <v>10.6585302352905</v>
+        <v>10.6585311889648</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1401" t="n">
-        <v>10.6585302352905</v>
+        <v>10.6585311889648</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1404" t="n">
-        <v>10.6585302352905</v>
+        <v>10.6585311889648</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1414" t="n">
-        <v>10.6585302352905</v>
+        <v>10.6585311889648</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1420" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>10.3178482055664</v>
+        <v>10.3178472518921</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1426" t="n">
-        <v>9.78248691558838</v>
+        <v>9.7824878692627</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1427" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1430" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1431" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1432" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718397140503</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1433" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718397140503</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1438" t="n">
-        <v>9.36393356323242</v>
+        <v>9.36393260955811</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1441" t="n">
-        <v>9.3055305480957</v>
+        <v>9.30553150177002</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1445" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1449" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1450" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1451" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718397140503</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1453" t="n">
-        <v>9.92849445343018</v>
+        <v>9.92849349975586</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1454" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1459" t="n">
-        <v>9.55860996246338</v>
+        <v>9.55860805511475</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1461" t="n">
-        <v>9.22765922546387</v>
+        <v>9.22765827178955</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1462" t="n">
-        <v>9.55860996246338</v>
+        <v>9.55860805511475</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1464" t="n">
-        <v>9.59754467010498</v>
+        <v>9.59754371643066</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1467" t="n">
-        <v>9.18872356414795</v>
+        <v>9.18872451782227</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1474" t="n">
-        <v>9.05245018005371</v>
+        <v>9.05245113372803</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -54426,6 +54426,32 @@
         <v>8.80000019073486</v>
       </c>
       <c r="H2079" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2080" t="n">
+        <v>2170</v>
+      </c>
+      <c r="C2080" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>8.5600004196167</v>
+      </c>
+      <c r="E2080" t="n">
+        <v>8.5600004196167</v>
+      </c>
+      <c r="F2080" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="G2080" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="H2080" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G4" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.91050004959106</v>
       </c>
       <c r="G5" t="n">
-        <v>2.77382802963257</v>
+        <v>2.77382826805115</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G7" t="n">
-        <v>2.80670809745789</v>
+        <v>2.80670785903931</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.97449994087219</v>
       </c>
       <c r="G10" t="n">
-        <v>2.83482265472412</v>
+        <v>2.83482313156128</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G12" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.98900008201599</v>
       </c>
       <c r="G13" t="n">
-        <v>2.84864187240601</v>
+        <v>2.84864211082458</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.97449994087219</v>
       </c>
       <c r="G16" t="n">
-        <v>2.83482265472412</v>
+        <v>2.83482313156128</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.93099999427795</v>
       </c>
       <c r="G17" t="n">
-        <v>2.79336547851562</v>
+        <v>2.7933657169342</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78764724731445</v>
+        <v>2.78764700889587</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>2.70663833618164</v>
+        <v>2.70663857460022</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.70663833618164</v>
+        <v>2.70663857460022</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G26" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G29" t="n">
-        <v>2.61895871162415</v>
+        <v>2.61895895004272</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.75</v>
       </c>
       <c r="G30" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.75</v>
       </c>
       <c r="G31" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.75</v>
       </c>
       <c r="G32" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.75</v>
       </c>
       <c r="G33" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.75</v>
       </c>
       <c r="G34" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G35" t="n">
-        <v>2.67232894897461</v>
+        <v>2.67232918739319</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>2.78288245201111</v>
+        <v>2.78288197517395</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G38" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G42" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G43" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.79241228103638</v>
+        <v>2.7924120426178</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.02049994468689</v>
       </c>
       <c r="G48" t="n">
-        <v>2.87866234779358</v>
+        <v>2.87866258621216</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G51" t="n">
-        <v>2.92583823204041</v>
+        <v>2.92583847045898</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.00208187103271</v>
+        <v>3.00208163261414</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>3.00208187103271</v>
+        <v>3.00208163261414</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>2.91630744934082</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.97300004959106</v>
       </c>
       <c r="G66" t="n">
-        <v>2.83339309692383</v>
+        <v>2.83339357376099</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G67" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80670809745789</v>
+        <v>2.80670785903931</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G76" t="n">
-        <v>2.78288245201111</v>
+        <v>2.78288197517395</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.89100003242493</v>
       </c>
       <c r="G78" t="n">
-        <v>2.75524377822876</v>
+        <v>2.75524401664734</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.90549993515015</v>
       </c>
       <c r="G80" t="n">
-        <v>2.76906251907349</v>
+        <v>2.76906299591064</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>2.77335119247437</v>
+        <v>2.7733519077301</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>2.91630744934082</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G89" t="n">
-        <v>2.85054802894592</v>
+        <v>2.8505482673645</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G90" t="n">
-        <v>2.85054802894592</v>
+        <v>2.8505482673645</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G91" t="n">
-        <v>2.85054802894592</v>
+        <v>2.8505482673645</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.93050003051758</v>
       </c>
       <c r="G92" t="n">
-        <v>2.79288911819458</v>
+        <v>2.792888879776</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.90899991989136</v>
       </c>
       <c r="G93" t="n">
-        <v>2.77239847183228</v>
+        <v>2.77239871025085</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.90899991989136</v>
       </c>
       <c r="G94" t="n">
-        <v>2.77239847183228</v>
+        <v>2.77239871025085</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G95" t="n">
-        <v>2.82576847076416</v>
+        <v>2.82576870918274</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G97" t="n">
-        <v>2.83815836906433</v>
+        <v>2.83815813064575</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G98" t="n">
-        <v>2.83815836906433</v>
+        <v>2.83815813064575</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G101" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.98850011825562</v>
       </c>
       <c r="G105" t="n">
-        <v>2.84816551208496</v>
+        <v>2.84816527366638</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G107" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G109" t="n">
-        <v>2.7204577922821</v>
+        <v>2.72045755386353</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G110" t="n">
-        <v>2.7204577922821</v>
+        <v>2.72045755386353</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.91700005531311</v>
       </c>
       <c r="G111" t="n">
-        <v>2.78002309799194</v>
+        <v>2.78002262115479</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.05949997901917</v>
       </c>
       <c r="G113" t="n">
-        <v>2.91583132743835</v>
+        <v>2.91583108901978</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.05949997901917</v>
       </c>
       <c r="G114" t="n">
-        <v>2.91583132743835</v>
+        <v>2.91583108901978</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G116" t="n">
-        <v>2.84959483146667</v>
+        <v>2.84959506988525</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.92549991607666</v>
       </c>
       <c r="G117" t="n">
-        <v>2.78812384605408</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G118" t="n">
-        <v>2.79622483253479</v>
+        <v>2.79622459411621</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.95149993896484</v>
       </c>
       <c r="G122" t="n">
-        <v>2.8129026889801</v>
+        <v>2.81290292739868</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G126" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78288245201111</v>
+        <v>2.78288197517395</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>2.78288245201111</v>
+        <v>2.78288197517395</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G131" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G132" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G136" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G137" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G138" t="n">
-        <v>2.79241228103638</v>
+        <v>2.7924120426178</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.95700001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.81814432144165</v>
+        <v>2.81814479827881</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G142" t="n">
-        <v>2.88390445709229</v>
+        <v>2.88390421867371</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.00650000572205</v>
       </c>
       <c r="G145" t="n">
-        <v>2.8653199672699</v>
+        <v>2.86532020568848</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.00650000572205</v>
       </c>
       <c r="G147" t="n">
-        <v>2.8653199672699</v>
+        <v>2.86532020568848</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>2.91630744934082</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>2.98302054405212</v>
+        <v>2.9830207824707</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.24049997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>3.08833193778992</v>
+        <v>3.0883321762085</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.27649998664856</v>
       </c>
       <c r="G152" t="n">
-        <v>3.12264132499695</v>
+        <v>3.12264108657837</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.32949995994568</v>
       </c>
       <c r="G153" t="n">
-        <v>3.17315220832825</v>
+        <v>3.17315244674683</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G154" t="n">
-        <v>3.24987244606018</v>
+        <v>3.24987268447876</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.40949988365173</v>
       </c>
       <c r="G155" t="n">
-        <v>3.2493953704834</v>
+        <v>3.24939560890198</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.35349988937378</v>
       </c>
       <c r="G158" t="n">
-        <v>3.19602560997009</v>
+        <v>3.19602537155151</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>3.24034237861633</v>
+        <v>3.24034190177917</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.43549990653992</v>
       </c>
       <c r="G161" t="n">
-        <v>3.27417492866516</v>
+        <v>3.27417469024658</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G162" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175026893616</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175026893616</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175026893616</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>3.26893377304077</v>
+        <v>3.26893329620361</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.34517669677734</v>
+        <v>3.34517693519592</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.59450006484985</v>
       </c>
       <c r="G171" t="n">
-        <v>3.42570829391479</v>
+        <v>3.42570853233337</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G172" t="n">
-        <v>3.50242877006531</v>
+        <v>3.50242853164673</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>3.58343720436096</v>
+        <v>3.58343696594238</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.47860264778137</v>
+        <v>3.47860240936279</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G175" t="n">
-        <v>3.55484557151794</v>
+        <v>3.55484580993652</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.75</v>
       </c>
       <c r="G176" t="n">
-        <v>3.57390666007996</v>
+        <v>3.57390642166138</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.75</v>
       </c>
       <c r="G177" t="n">
-        <v>3.57390666007996</v>
+        <v>3.57390642166138</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>3.84075832366943</v>
+        <v>3.84075880050659</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>3.75498485565186</v>
+        <v>3.7549843788147</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G181" t="n">
-        <v>3.75498485565186</v>
+        <v>3.7549843788147</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G182" t="n">
-        <v>3.62155866622925</v>
+        <v>3.62155890464783</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G183" t="n">
-        <v>3.5453155040741</v>
+        <v>3.54531526565552</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>3.62155866622925</v>
+        <v>3.62155890464783</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G185" t="n">
-        <v>3.66921067237854</v>
+        <v>3.6692111492157</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G186" t="n">
-        <v>3.66921067237854</v>
+        <v>3.6692111492157</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G187" t="n">
-        <v>3.71686315536499</v>
+        <v>3.71686291694641</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>3.71686315536499</v>
+        <v>3.71686291694641</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>3.84075832366943</v>
+        <v>3.84075880050659</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G192" t="n">
-        <v>3.84075832366943</v>
+        <v>3.84075880050659</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>3.95512342453003</v>
+        <v>3.95512270927429</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>3.85028839111328</v>
+        <v>3.85028886795044</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>3.75498485565186</v>
+        <v>3.7549843788147</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>3.75498485565186</v>
+        <v>3.7549843788147</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>3.92740726470947</v>
+        <v>3.92740702629089</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>3.87951254844666</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>3.88909149169922</v>
+        <v>3.88909125328064</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82203769683838</v>
+        <v>3.82203841209412</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>3.7070894241333</v>
+        <v>3.70708918571472</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G209" t="n">
-        <v>3.69751024246216</v>
+        <v>3.69751048088074</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G210" t="n">
-        <v>3.69751024246216</v>
+        <v>3.69751048088074</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>3.87951254844666</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>3.87951254844666</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>3.78372144699097</v>
+        <v>3.78372168540955</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>3.87951254844666</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>3.87951254844666</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.93698644638062</v>
+        <v>3.93698620796204</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G218" t="n">
-        <v>3.94656562805176</v>
+        <v>3.94656538963318</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>4.02319812774658</v>
+        <v>4.02319717407227</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>4.03277683258057</v>
+        <v>4.03277730941772</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.21477937698364</v>
+        <v>4.21477842330933</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>4.10940933227539</v>
+        <v>4.10940885543823</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G225" t="n">
-        <v>4.3967809677124</v>
+        <v>4.39678049087524</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>4.45425510406494</v>
+        <v>4.45425415039062</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G232" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G235" t="n">
-        <v>4.68415212631226</v>
+        <v>4.6841516494751</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G237" t="n">
-        <v>4.96194410324097</v>
+        <v>4.96194362640381</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G238" t="n">
-        <v>5.00026035308838</v>
+        <v>5.00025987625122</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G241" t="n">
-        <v>4.94278621673584</v>
+        <v>4.94278526306152</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G256" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G257" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>4.6362566947937</v>
+        <v>4.63625717163086</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G262" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>4.59793996810913</v>
+        <v>4.59794044494629</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>4.59793996810913</v>
+        <v>4.59794044494629</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G269" t="n">
-        <v>4.59793996810913</v>
+        <v>4.59794044494629</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G271" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G272" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>4.57878303527832</v>
+        <v>4.57878255844116</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>4.76078462600708</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G275" t="n">
-        <v>4.76078462600708</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G279" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G280" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G285" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G294" t="n">
-        <v>4.76078462600708</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G299" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G301" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G302" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G303" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G314" t="n">
-        <v>4.77994203567505</v>
+        <v>4.77994155883789</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.76078462600708</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G339" t="n">
-        <v>4.88531112670898</v>
+        <v>4.88531064987183</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.88531112670898</v>
+        <v>4.88531064987183</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G343" t="n">
-        <v>5.00026035308838</v>
+        <v>5.00025987625122</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>5.5</v>
       </c>
       <c r="G347" t="n">
-        <v>5.26847410202026</v>
+        <v>5.26847362518311</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G348" t="n">
-        <v>5.32594776153564</v>
+        <v>5.32594728469849</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G349" t="n">
-        <v>5.21099948883057</v>
+        <v>5.21099901199341</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G361" t="n">
-        <v>5.21099948883057</v>
+        <v>5.21099901199341</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>5.32594776153564</v>
+        <v>5.32594728469849</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>5.28763151168823</v>
+        <v>5.28763103485107</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>5.36426401138306</v>
+        <v>5.36426305770874</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G368" t="n">
-        <v>5.47921228408813</v>
+        <v>5.47921180725098</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>5.65163516998291</v>
+        <v>5.65163469314575</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>5.84321594238281</v>
+        <v>5.84321546554565</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G376" t="n">
-        <v>5.91984748840332</v>
+        <v>5.91984796524048</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G379" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G384" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G386" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G388" t="n">
-        <v>5.9773211479187</v>
+        <v>5.97732257843018</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G391" t="n">
-        <v>5.91984748840332</v>
+        <v>5.91984796524048</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G393" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G394" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G395" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311296463013</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>6.37964200973511</v>
+        <v>6.37964248657227</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G399" t="n">
-        <v>6.37964200973511</v>
+        <v>6.37964248657227</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G401" t="n">
-        <v>6.36048412322998</v>
+        <v>6.36048364639282</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G402" t="n">
-        <v>6.37964200973511</v>
+        <v>6.37964248657227</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G403" t="n">
-        <v>6.45627498626709</v>
+        <v>6.45627450942993</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G404" t="n">
-        <v>6.39880037307739</v>
+        <v>6.39879989624023</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>6.36048412322998</v>
+        <v>6.36048364639282</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>6.5</v>
       </c>
       <c r="G409" t="n">
-        <v>6.22637701034546</v>
+        <v>6.22637748718262</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G412" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G414" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311296463013</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.55584526062012</v>
+        <v>5.5558443069458</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>5.72826814651489</v>
+        <v>5.72826719284058</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>5.70910930633545</v>
+        <v>5.70910882949829</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>5.70910930633545</v>
+        <v>5.70910882949829</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>5.67079401016235</v>
+        <v>5.67079305648804</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G423" t="n">
-        <v>5.67079401016235</v>
+        <v>5.67079305648804</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G424" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G426" t="n">
-        <v>5.9773211479187</v>
+        <v>5.97732257843018</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G427" t="n">
-        <v>5.99648094177246</v>
+        <v>5.9964804649353</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311296463013</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G430" t="n">
-        <v>6.05395460128784</v>
+        <v>6.053955078125</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G431" t="n">
-        <v>6.05395460128784</v>
+        <v>6.053955078125</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G432" t="n">
-        <v>6.11142873764038</v>
+        <v>6.11142921447754</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>6.30300951004028</v>
+        <v>6.30300998687744</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G436" t="n">
-        <v>6.57122373580933</v>
+        <v>6.57122325897217</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G437" t="n">
-        <v>6.62869691848755</v>
+        <v>6.62869739532471</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>6.64785528182983</v>
+        <v>6.64785575866699</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>6.68617153167725</v>
+        <v>6.6861720085144</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>7.165123462677</v>
+        <v>7.16512393951416</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>7.5</v>
       </c>
       <c r="G447" t="n">
-        <v>7.1842827796936</v>
+        <v>7.18428182601929</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G449" t="n">
-        <v>7.79734086990356</v>
+        <v>7.79734039306641</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G450" t="n">
-        <v>7.68239212036133</v>
+        <v>7.68239259719849</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.5</v>
       </c>
       <c r="G454" t="n">
-        <v>8.17151069641113</v>
+        <v>8.1715087890625</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G455" t="n">
-        <v>7.99846458435059</v>
+        <v>7.99846410751343</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537269592285</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G457" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537269592285</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.5</v>
       </c>
       <c r="G458" t="n">
-        <v>8.17151069641113</v>
+        <v>8.1715087890625</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G460" t="n">
-        <v>8.01769256591797</v>
+        <v>8.01769351959229</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G461" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537269592285</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537269592285</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>7.8061957359314</v>
+        <v>7.80619525909424</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>7.13324785232544</v>
+        <v>7.13324689865112</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>7.22938251495361</v>
+        <v>7.22938299179077</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>7.5</v>
       </c>
       <c r="G471" t="n">
-        <v>7.21015596389771</v>
+        <v>7.21015548706055</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.5</v>
       </c>
       <c r="G473" t="n">
-        <v>7.21015596389771</v>
+        <v>7.21015548706055</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>7.59469652175903</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G477" t="n">
-        <v>7.57547092437744</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>7.57547092437744</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>7.59469652175903</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>7.59469652175903</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>7.57547092437744</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>7.59469652175903</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>7.59469652175903</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>7.59469652175903</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>7.57547092437744</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G489" t="n">
-        <v>7.47933483123779</v>
+        <v>7.47933530807495</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G490" t="n">
-        <v>7.55624341964722</v>
+        <v>7.55624294281006</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G491" t="n">
-        <v>7.46010732650757</v>
+        <v>7.46010780334473</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G492" t="n">
-        <v>7.57547092437744</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G493" t="n">
-        <v>7.57547092437744</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G496" t="n">
-        <v>7.51778888702393</v>
+        <v>7.51778841018677</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G502" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G503" t="n">
-        <v>7.67160511016846</v>
+        <v>7.67160606384277</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G504" t="n">
-        <v>7.82542276382446</v>
+        <v>7.8254222869873</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>8.01769256591797</v>
+        <v>8.01769351959229</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>8.45991706848145</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G510" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55604934692383</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G511" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55604934692383</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9</v>
       </c>
       <c r="G512" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G513" t="n">
-        <v>8.74832344055176</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>9.24822616577148</v>
+        <v>9.24822521209717</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G518" t="n">
-        <v>9.305908203125</v>
+        <v>9.30590724945068</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G519" t="n">
-        <v>9.305908203125</v>
+        <v>9.30590724945068</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G521" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>9.49817752838135</v>
+        <v>9.49817848205566</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G524" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G538" t="n">
-        <v>8.74832344055176</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>8.69064140319824</v>
+        <v>8.69064044952393</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>9</v>
       </c>
       <c r="G540" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9</v>
       </c>
       <c r="G542" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>8.61373329162598</v>
+        <v>8.61373233795166</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G544" t="n">
-        <v>8.4791431427002</v>
+        <v>8.47914218902588</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>8.45991706848145</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G549" t="n">
-        <v>8.45991706848145</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G550" t="n">
-        <v>8.421462059021</v>
+        <v>8.42146015167236</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G551" t="n">
-        <v>8.421462059021</v>
+        <v>8.42146015167236</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G552" t="n">
-        <v>8.36377906799316</v>
+        <v>8.36378002166748</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G553" t="n">
-        <v>8.421462059021</v>
+        <v>8.42146015167236</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G554" t="n">
-        <v>8.421462059021</v>
+        <v>8.42146015167236</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G555" t="n">
-        <v>8.36377906799316</v>
+        <v>8.36378002166748</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>8.45991706848145</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.45991706848145</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55604934692383</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G559" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55604934692383</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G563" t="n">
-        <v>8.90213871002197</v>
+        <v>8.90213775634766</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>8.97904777526855</v>
+        <v>8.97904682159424</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G567" t="n">
-        <v>9.1905460357666</v>
+        <v>9.19054508209229</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G568" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G569" t="n">
-        <v>9.28668022155762</v>
+        <v>9.2866792678833</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G572" t="n">
-        <v>9.05595588684082</v>
+        <v>9.0559549331665</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>9</v>
       </c>
       <c r="G576" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G578" t="n">
-        <v>8.97904777526855</v>
+        <v>8.97904682159424</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G579" t="n">
-        <v>8.90213871002197</v>
+        <v>8.90213775634766</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G580" t="n">
-        <v>8.86368465423584</v>
+        <v>8.86368560791016</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9</v>
       </c>
       <c r="G584" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.69064140319824</v>
+        <v>8.69064044952393</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>8.74832344055176</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>9</v>
       </c>
       <c r="G590" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>9</v>
       </c>
       <c r="G591" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9</v>
       </c>
       <c r="G593" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>8.76754951477051</v>
+        <v>8.76754760742188</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G597" t="n">
-        <v>9.1136360168457</v>
+        <v>9.11363506317139</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>9.32513332366943</v>
+        <v>9.32513427734375</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>9.32513332366943</v>
+        <v>9.32513427734375</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G603" t="n">
-        <v>9.20977115631104</v>
+        <v>9.20977210998535</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G604" t="n">
-        <v>9.26745414733887</v>
+        <v>9.26745319366455</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G606" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>9.22899913787842</v>
+        <v>9.2289981842041</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G608" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G609" t="n">
-        <v>9.1136360168457</v>
+        <v>9.11363506317139</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G610" t="n">
-        <v>9.1136360168457</v>
+        <v>9.11363506317139</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G614" t="n">
-        <v>9.20977115631104</v>
+        <v>9.20977210998535</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>9.20977115631104</v>
+        <v>9.20977210998535</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G616" t="n">
-        <v>9.22899913787842</v>
+        <v>9.2289981842041</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G619" t="n">
-        <v>9.22899913787842</v>
+        <v>9.2289981842041</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G620" t="n">
-        <v>9.22899913787842</v>
+        <v>9.2289981842041</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G622" t="n">
-        <v>9.22899913787842</v>
+        <v>9.2289981842041</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>9.99808216094971</v>
+        <v>9.99808120727539</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G628" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G630" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>10.1422872543335</v>
+        <v>10.1422853469849</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G632" t="n">
-        <v>10.1422872543335</v>
+        <v>10.1422853469849</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G636" t="n">
-        <v>10.0461483001709</v>
+        <v>10.0461492538452</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>10.1903524398804</v>
+        <v>10.1903533935547</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>10.5268278121948</v>
+        <v>10.5268268585205</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>10.75</v>
       </c>
       <c r="G642" t="n">
-        <v>10.3345546722412</v>
+        <v>10.3345556259155</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.75</v>
       </c>
       <c r="G643" t="n">
-        <v>10.3345546722412</v>
+        <v>10.3345556259155</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>10.75</v>
       </c>
       <c r="G646" t="n">
-        <v>10.3345546722412</v>
+        <v>10.3345556259155</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>10.6710290908813</v>
+        <v>10.6710300445557</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>10.6710290908813</v>
+        <v>10.6710300445557</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>10.7671661376953</v>
+        <v>10.7671642303467</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>11.6323843002319</v>
+        <v>11.6323852539062</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G660" t="n">
-        <v>12.834077835083</v>
+        <v>12.8340768814087</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>12.1130628585815</v>
+        <v>12.1130619049072</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G664" t="n">
-        <v>12.8821430206299</v>
+        <v>12.8821439743042</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>12.834077835083</v>
+        <v>12.8340768814087</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G673" t="n">
-        <v>13.0263471603394</v>
+        <v>13.026349067688</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915672302246</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>13.795431137085</v>
+        <v>13.7954301834106</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915672302246</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>13.795431137085</v>
+        <v>13.7954301834106</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915672302246</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915672302246</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915672302246</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>14.25</v>
       </c>
       <c r="G695" t="n">
-        <v>13.6992959976196</v>
+        <v>13.6992950439453</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>14</v>
       </c>
       <c r="G696" t="n">
-        <v>13.4589557647705</v>
+        <v>13.4589567184448</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>14</v>
       </c>
       <c r="G697" t="n">
-        <v>13.4589557647705</v>
+        <v>13.4589567184448</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>13.6031589508057</v>
+        <v>13.60315990448</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>14.75</v>
       </c>
       <c r="G705" t="n">
-        <v>14.1799726486206</v>
+        <v>14.1799716949463</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>15.9536733627319</v>
+        <v>15.9536714553833</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910614013672</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>16.5802536010742</v>
+        <v>16.5802555084229</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>16.4838542938232</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>17</v>
       </c>
       <c r="G725" t="n">
-        <v>16.3874626159668</v>
+        <v>16.3874607086182</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>16.5</v>
       </c>
       <c r="G726" t="n">
-        <v>15.9054756164551</v>
+        <v>15.9054765701294</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>16.0500679016113</v>
+        <v>16.05006980896</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910614013672</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>16.5802536010742</v>
+        <v>16.5802555084229</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>16.4838542938232</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>16.4838542938232</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G733" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910614013672</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>16.1946659088135</v>
+        <v>16.1946678161621</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>16.0982723236084</v>
+        <v>16.0982704162598</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>16.1946659088135</v>
+        <v>16.1946678161621</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>16.2428665161133</v>
+        <v>16.2428646087646</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>16.75</v>
       </c>
       <c r="G738" t="n">
-        <v>16.1464691162109</v>
+        <v>16.1464672088623</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>16.0982723236084</v>
+        <v>16.0982704162598</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>15.5198888778687</v>
+        <v>15.519889831543</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>15.2788972854614</v>
+        <v>15.2788963317871</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G748" t="n">
-        <v>14.8933095932007</v>
+        <v>14.8933086395264</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G750" t="n">
-        <v>14.8933095932007</v>
+        <v>14.8933086395264</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>15.2788972854614</v>
+        <v>15.2788963317871</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>15.2788972854614</v>
+        <v>15.2788963317871</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>15.7126808166504</v>
+        <v>15.7126817703247</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162853240967</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>15.5198888778687</v>
+        <v>15.519889831543</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G764" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162853240967</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162853240967</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>16</v>
       </c>
       <c r="G767" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>16</v>
       </c>
       <c r="G768" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G769" t="n">
-        <v>15.5680866241455</v>
+        <v>15.5680875778198</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G770" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910614013672</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G771" t="n">
-        <v>17.0622386932373</v>
+        <v>17.0622367858887</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>17.1586360931396</v>
+        <v>17.1586322784424</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>17.5</v>
       </c>
       <c r="G780" t="n">
-        <v>16.8694458007812</v>
+        <v>16.8694438934326</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G782" t="n">
-        <v>16.7730445861816</v>
+        <v>16.7730484008789</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>16.532054901123</v>
+        <v>16.5320568084717</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G785" t="n">
-        <v>16.4838542938232</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>17.5</v>
       </c>
       <c r="G786" t="n">
-        <v>16.8694458007812</v>
+        <v>16.8694438934326</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G792" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>17.1586360931396</v>
+        <v>17.1586322784424</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>17.0622386932373</v>
+        <v>17.0622367858887</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>17.5</v>
       </c>
       <c r="G798" t="n">
-        <v>16.8694458007812</v>
+        <v>16.8694438934326</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>17.6888179779053</v>
+        <v>17.6888160705566</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>18.7009811401367</v>
+        <v>18.700984954834</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>19.2311668395996</v>
+        <v>19.231164932251</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G807" t="n">
-        <v>18.7491836547852</v>
+        <v>18.7491817474365</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>18.6045875549316</v>
+        <v>18.604585647583</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>18.5081901550293</v>
+        <v>18.5081920623779</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G810" t="n">
-        <v>18.3635940551758</v>
+        <v>18.3635921478271</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>17.9780044555664</v>
+        <v>17.978006362915</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>18.75</v>
       </c>
       <c r="G825" t="n">
-        <v>18.0744037628174</v>
+        <v>18.074405670166</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>17.6888179779053</v>
+        <v>17.6888160705566</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>18.1226005554199</v>
+        <v>18.1226024627686</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>17.88161277771</v>
+        <v>17.8816108703613</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G833" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>18.5</v>
       </c>
       <c r="G839" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>17.88161277771</v>
+        <v>17.8816108703613</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>18.5</v>
       </c>
       <c r="G848" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>17.6888179779053</v>
+        <v>17.6888160705566</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>17.4960231781006</v>
+        <v>17.496021270752</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G853" t="n">
-        <v>17.9780044555664</v>
+        <v>17.978006362915</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>17.9298095703125</v>
+        <v>17.9298076629639</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>18.5</v>
       </c>
       <c r="G858" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>18.25</v>
       </c>
       <c r="G859" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>18.25</v>
       </c>
       <c r="G860" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G866" t="n">
-        <v>17.4960231781006</v>
+        <v>17.496021270752</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>17.9780044555664</v>
+        <v>17.978006362915</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>18.1226005554199</v>
+        <v>18.1226024627686</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G874" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G875" t="n">
-        <v>18.5081901550293</v>
+        <v>18.5081920623779</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>17.9298095703125</v>
+        <v>17.9298076629639</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G877" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>18.5081901550293</v>
+        <v>18.5081920623779</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G880" t="n">
-        <v>19.1347694396973</v>
+        <v>19.1347713470459</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G882" t="n">
-        <v>18.7491836547852</v>
+        <v>18.7491817474365</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G884" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G887" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>18.3635940551758</v>
+        <v>18.3635921478271</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>18.1226005554199</v>
+        <v>18.1226024627686</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>18.5</v>
       </c>
       <c r="G892" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>18.5</v>
       </c>
       <c r="G893" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>17.4960231781006</v>
+        <v>17.496021270752</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G897" t="n">
-        <v>17.4960231781006</v>
+        <v>17.496021270752</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>18.25</v>
       </c>
       <c r="G899" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>18.25</v>
       </c>
       <c r="G900" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>17.88161277771</v>
+        <v>17.8816108703613</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>17.5</v>
       </c>
       <c r="G909" t="n">
-        <v>16.8694458007812</v>
+        <v>16.8694438934326</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>17.0622386932373</v>
+        <v>17.0622367858887</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G912" t="n">
-        <v>16.5802536010742</v>
+        <v>16.5802555084229</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>16.5</v>
       </c>
       <c r="G913" t="n">
-        <v>15.9054756164551</v>
+        <v>15.9054765701294</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>16</v>
       </c>
       <c r="G914" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>16</v>
       </c>
       <c r="G916" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>14.6523170471191</v>
+        <v>14.6523180007935</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>15.3270950317383</v>
+        <v>15.327094078064</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>15.3270950317383</v>
+        <v>15.327094078064</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>14.2667293548584</v>
+        <v>14.2667303085327</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G924" t="n">
-        <v>12.9653720855713</v>
+        <v>12.9653730392456</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>14.1221342086792</v>
+        <v>14.1221351623535</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>15.5198888778687</v>
+        <v>15.519889831543</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>15.7126808166504</v>
+        <v>15.7126817703247</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>16.5</v>
       </c>
       <c r="G929" t="n">
-        <v>15.9054756164551</v>
+        <v>15.9054765701294</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>16</v>
       </c>
       <c r="G930" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>16.1946659088135</v>
+        <v>16.1946678161621</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>15.7126808166504</v>
+        <v>15.7126817703247</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>15.0861015319824</v>
+        <v>15.0861043930054</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>15.3270950317383</v>
+        <v>15.327094078064</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G941" t="n">
-        <v>15.0861015319824</v>
+        <v>15.0861043930054</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>15.2788972854614</v>
+        <v>15.2788963317871</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G947" t="n">
-        <v>15.0861015319824</v>
+        <v>15.0861043930054</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>14.6523170471191</v>
+        <v>14.6523180007935</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>15</v>
       </c>
       <c r="G950" t="n">
-        <v>14.4595251083374</v>
+        <v>14.4595232009888</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G952" t="n">
-        <v>14.6041193008423</v>
+        <v>14.604118347168</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15</v>
       </c>
       <c r="G955" t="n">
-        <v>14.4595251083374</v>
+        <v>14.4595232009888</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>14.2667293548584</v>
+        <v>14.2667303085327</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>14.5</v>
       </c>
       <c r="G959" t="n">
-        <v>13.9775400161743</v>
+        <v>13.9775390625</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>13.6883478164673</v>
+        <v>13.6883487701416</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G969" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>14</v>
       </c>
       <c r="G970" t="n">
-        <v>13.5528211593628</v>
+        <v>13.5528221130371</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>14.75</v>
       </c>
       <c r="G976" t="n">
-        <v>14.2788639068604</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G979" t="n">
-        <v>13.1171951293945</v>
+        <v>13.1171960830688</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G981" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>15.75</v>
       </c>
       <c r="G982" t="n">
-        <v>15.246922492981</v>
+        <v>15.2469244003296</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G983" t="n">
-        <v>15.2953271865845</v>
+        <v>15.2953262329102</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>15.4405355453491</v>
+        <v>15.4405345916748</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>15.3437299728394</v>
+        <v>15.343729019165</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G988" t="n">
-        <v>15.1501178741455</v>
+        <v>15.1501188278198</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>14.75</v>
       </c>
       <c r="G994" t="n">
-        <v>14.2788639068604</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>13.9884471893311</v>
+        <v>13.9884481430054</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>14.25</v>
       </c>
       <c r="G998" t="n">
-        <v>13.7948360443115</v>
+        <v>13.7948350906372</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>14</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.5528211593628</v>
+        <v>13.5528221130371</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.6980304718018</v>
+        <v>13.6980295181274</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.6980304718018</v>
+        <v>13.6980295181274</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1009" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1011" t="n">
-        <v>13.3592100143433</v>
+        <v>13.3592090606689</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1018" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>12.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.1007328033447</v>
+        <v>12.100733757019</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>14.3272676467896</v>
+        <v>14.3272686004639</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1036" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>14.75</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.2788639068604</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>14.75</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.2788639068604</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1049" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1051" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>14.25</v>
       </c>
       <c r="G1055" t="n">
-        <v>13.7948360443115</v>
+        <v>13.7948350906372</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>14.25</v>
       </c>
       <c r="G1057" t="n">
-        <v>13.7948360443115</v>
+        <v>13.7948350906372</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1061" t="n">
-        <v>13.3592100143433</v>
+        <v>13.3592090606689</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>13.5</v>
       </c>
       <c r="G1062" t="n">
-        <v>13.0687923431396</v>
+        <v>13.0687913894653</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>13.5</v>
       </c>
       <c r="G1063" t="n">
-        <v>13.0687923431396</v>
+        <v>13.0687913894653</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1064" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1066" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1069" t="n">
-        <v>11.9071207046509</v>
+        <v>11.9071216583252</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>12.25</v>
       </c>
       <c r="G1071" t="n">
-        <v>11.8587188720703</v>
+        <v>11.858717918396</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>12.1975402832031</v>
+        <v>12.1975393295288</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1075" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1076" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1079" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1081" t="n">
-        <v>12.7299709320068</v>
+        <v>12.7299718856812</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1082" t="n">
-        <v>12.7299709320068</v>
+        <v>12.7299718856812</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1086" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1087" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1092" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1121" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>13.5</v>
       </c>
       <c r="G1125" t="n">
-        <v>13.0687923431396</v>
+        <v>13.0687913894653</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1134" t="n">
-        <v>13.9884471893311</v>
+        <v>13.9884481430054</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>14</v>
       </c>
       <c r="G1137" t="n">
-        <v>13.5528211593628</v>
+        <v>13.5528221130371</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>14.25</v>
       </c>
       <c r="G1139" t="n">
-        <v>13.7948360443115</v>
+        <v>13.7948350906372</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>14.25</v>
       </c>
       <c r="G1142" t="n">
-        <v>13.7948360443115</v>
+        <v>13.7948350906372</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1145" t="n">
-        <v>14.3272676467896</v>
+        <v>14.3272686004639</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>15.25</v>
       </c>
       <c r="G1146" t="n">
-        <v>14.7628936767578</v>
+        <v>14.7628946304321</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1148" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>14.75</v>
       </c>
       <c r="G1151" t="n">
-        <v>14.2788639068604</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1153" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1154" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1156" t="n">
-        <v>13.9884471893311</v>
+        <v>13.9884481430054</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1157" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1160" t="n">
-        <v>14.3272676467896</v>
+        <v>14.3272686004639</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1162" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1164" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1176" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1177" t="n">
-        <v>13.3592100143433</v>
+        <v>13.3592090606689</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>13.5</v>
       </c>
       <c r="G1178" t="n">
-        <v>13.0687923431396</v>
+        <v>13.0687913894653</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1180" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1182" t="n">
-        <v>12.923583984375</v>
+        <v>12.9235830307007</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1183" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1189" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.923583984375</v>
+        <v>12.9235830307007</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1203" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1207" t="n">
-        <v>12.1975402832031</v>
+        <v>12.1975393295288</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1215" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>12.7299709320068</v>
+        <v>12.7299718856812</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>13</v>
       </c>
       <c r="G1222" t="n">
-        <v>12.6539640426636</v>
+        <v>12.6539630889893</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>13</v>
       </c>
       <c r="G1223" t="n">
-        <v>12.6539640426636</v>
+        <v>12.6539630889893</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1226" t="n">
-        <v>12.5566244125366</v>
+        <v>12.5566253662109</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1227" t="n">
-        <v>12.2646112442017</v>
+        <v>12.264612197876</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>12.2646112442017</v>
+        <v>12.264612197876</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>12.25</v>
       </c>
       <c r="G1231" t="n">
-        <v>11.9239263534546</v>
+        <v>11.9239273071289</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.9725961685181</v>
+        <v>11.9725971221924</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1239" t="n">
-        <v>11.8265886306763</v>
+        <v>11.826587677002</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1241" t="n">
-        <v>11.5832424163818</v>
+        <v>11.5832433700562</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1243" t="n">
-        <v>11.4859056472778</v>
+        <v>11.4859046936035</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1256" t="n">
-        <v>11.3885660171509</v>
+        <v>11.3885669708252</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1260" t="n">
-        <v>11.3885660171509</v>
+        <v>11.3885669708252</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1262" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1264" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1265" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1267" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1268" t="n">
-        <v>10.7558689117432</v>
+        <v>10.7558698654175</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1273" t="n">
-        <v>11.0965518951416</v>
+        <v>11.0965528488159</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>11.5</v>
       </c>
       <c r="G1274" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1275" t="n">
-        <v>11.0965518951416</v>
+        <v>11.0965528488159</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>11.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>10.8532066345215</v>
+        <v>10.8532056808472</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>11.5</v>
       </c>
       <c r="G1285" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>11.5</v>
       </c>
       <c r="G1286" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>11.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>11.0965518951416</v>
+        <v>11.0965528488159</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1289" t="n">
-        <v>10.8532066345215</v>
+        <v>10.8532056808472</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1295" t="n">
-        <v>11.3885660171509</v>
+        <v>11.3885669708252</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>11.5</v>
       </c>
       <c r="G1296" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1298" t="n">
-        <v>10.8532066345215</v>
+        <v>10.8532056808472</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>11.0965518951416</v>
+        <v>11.0965528488159</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1302" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1303" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1305" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>11.0965518951416</v>
+        <v>11.0965528488159</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>11.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1314" t="n">
-        <v>10.7558689117432</v>
+        <v>10.7558698654175</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1317" t="n">
-        <v>10.7558689117432</v>
+        <v>10.7558698654175</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1318" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1319" t="n">
-        <v>11.0965518951416</v>
+        <v>11.0965528488159</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1331" t="n">
-        <v>10.0258331298828</v>
+        <v>10.0258321762085</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1333" t="n">
-        <v>10.0258331298828</v>
+        <v>10.0258321762085</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1339" t="n">
-        <v>9.92849349975586</v>
+        <v>9.92849445343018</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1340" t="n">
-        <v>9.83115673065186</v>
+        <v>9.83115577697754</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1350" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1351" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1358" t="n">
-        <v>9.55860805511475</v>
+        <v>9.55860900878906</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1360" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1361" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1364" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1366" t="n">
-        <v>9.28606224060059</v>
+        <v>9.28606128692627</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1368" t="n">
-        <v>9.28606224060059</v>
+        <v>9.28606128692627</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1371" t="n">
-        <v>9.03298282623291</v>
+        <v>9.03298377990723</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1376" t="n">
-        <v>10.6098623275757</v>
+        <v>10.6098613739014</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1377" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1378" t="n">
-        <v>10.6098623275757</v>
+        <v>10.6098613739014</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1380" t="n">
-        <v>10.7558689117432</v>
+        <v>10.7558698654175</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1385" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>10.6098623275757</v>
+        <v>10.6098613739014</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1387" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1391" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1393" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1394" t="n">
-        <v>10.7558689117432</v>
+        <v>10.7558698654175</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1396" t="n">
-        <v>10.7558689117432</v>
+        <v>10.7558698654175</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1397" t="n">
-        <v>10.7558689117432</v>
+        <v>10.7558698654175</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1398" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1400" t="n">
-        <v>10.7558689117432</v>
+        <v>10.7558698654175</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1401" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1404" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1406" t="n">
-        <v>10.7558689117432</v>
+        <v>10.7558698654175</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1414" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1420" t="n">
-        <v>10.0258331298828</v>
+        <v>10.0258321762085</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1427" t="n">
-        <v>9.83115673065186</v>
+        <v>9.83115577697754</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1430" t="n">
-        <v>9.83115673065186</v>
+        <v>9.83115577697754</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1431" t="n">
-        <v>10.0258331298828</v>
+        <v>10.0258321762085</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>9.83115673065186</v>
+        <v>9.83115577697754</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1441" t="n">
-        <v>9.30553150177002</v>
+        <v>9.3055305480957</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1445" t="n">
-        <v>9.83115673065186</v>
+        <v>9.83115577697754</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1449" t="n">
-        <v>10.0258331298828</v>
+        <v>10.0258321762085</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1450" t="n">
-        <v>10.0258331298828</v>
+        <v>10.0258321762085</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1453" t="n">
-        <v>9.92849349975586</v>
+        <v>9.92849445343018</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1454" t="n">
-        <v>10.0258331298828</v>
+        <v>10.0258321762085</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1459" t="n">
-        <v>9.55860805511475</v>
+        <v>9.55860900878906</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1462" t="n">
-        <v>9.55860805511475</v>
+        <v>9.55860900878906</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1470" t="n">
-        <v>9.20819187164307</v>
+        <v>9.20819282531738</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -54452,6 +54452,32 @@
         <v>8.80000019073486</v>
       </c>
       <c r="H2080" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2081" t="n">
+        <v>42723</v>
+      </c>
+      <c r="C2081" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>8.65999984741211</v>
+      </c>
+      <c r="E2081" t="n">
+        <v>8.65999984741211</v>
+      </c>
+      <c r="F2081" t="n">
+        <v>9.07999992370605</v>
+      </c>
+      <c r="G2081" t="n">
+        <v>9.07999992370605</v>
+      </c>
+      <c r="H2081" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G4" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.91050004959106</v>
       </c>
       <c r="G5" t="n">
-        <v>2.77382826805115</v>
+        <v>2.77382802963257</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.98749995231628</v>
       </c>
       <c r="G6" t="n">
-        <v>2.84721231460571</v>
+        <v>2.84721207618713</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G7" t="n">
-        <v>2.80670762062073</v>
+        <v>2.80670785903931</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84006452560425</v>
+        <v>2.84006428718567</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.85912489891052</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.9614999294281</v>
       </c>
       <c r="G11" t="n">
-        <v>2.82243323326111</v>
+        <v>2.82243275642395</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.98900008201599</v>
       </c>
       <c r="G13" t="n">
-        <v>2.84864211082458</v>
+        <v>2.84864187240601</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.85912489891052</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.93099999427795</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7933657169342</v>
+        <v>2.79336547851562</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78764700889587</v>
+        <v>2.78764677047729</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>2.71616864204407</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G22" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>2.70663809776306</v>
+        <v>2.70663857460022</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.70663809776306</v>
+        <v>2.70663857460022</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G26" t="n">
-        <v>2.71616864204407</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.71616864204407</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.71616864204407</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G29" t="n">
-        <v>2.61895895004272</v>
+        <v>2.61895871162415</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.75</v>
       </c>
       <c r="G30" t="n">
-        <v>2.62086510658264</v>
+        <v>2.6208643913269</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.75</v>
       </c>
       <c r="G31" t="n">
-        <v>2.62086510658264</v>
+        <v>2.6208643913269</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.75</v>
       </c>
       <c r="G32" t="n">
-        <v>2.62086510658264</v>
+        <v>2.6208643913269</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.75</v>
       </c>
       <c r="G33" t="n">
-        <v>2.62086510658264</v>
+        <v>2.6208643913269</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.75</v>
       </c>
       <c r="G34" t="n">
-        <v>2.62086510658264</v>
+        <v>2.6208643913269</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G35" t="n">
-        <v>2.67232918739319</v>
+        <v>2.67232871055603</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.67804718017578</v>
+        <v>2.67804765701294</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288221359253</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>2.85912489891052</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G42" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G43" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.79241251945496</v>
+        <v>2.79241228103638</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>2.85912489891052</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87818598747253</v>
+        <v>2.87818622589111</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.05550003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>2.91201949119568</v>
+        <v>2.9120192527771</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.00208163261414</v>
+        <v>3.00208139419556</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>3.00208163261414</v>
+        <v>3.00208139419556</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>2.91630792617798</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>2.97349071502686</v>
+        <v>2.97348999977112</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G60" t="n">
-        <v>2.97349071502686</v>
+        <v>2.97348999977112</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G63" t="n">
-        <v>2.88771629333496</v>
+        <v>2.88771653175354</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>2.87818598747253</v>
+        <v>2.87818622589111</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G67" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80670762062073</v>
+        <v>2.80670785903931</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>2.85912489891052</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3</v>
       </c>
       <c r="G74" t="n">
-        <v>2.85912489891052</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3</v>
       </c>
       <c r="G75" t="n">
-        <v>2.85912489891052</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G76" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288221359253</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.90549993515015</v>
       </c>
       <c r="G80" t="n">
-        <v>2.76906251907349</v>
+        <v>2.76906299591064</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>2.77335166931152</v>
+        <v>2.77335143089294</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G83" t="n">
-        <v>2.88771629333496</v>
+        <v>2.88771653175354</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>2.85912489891052</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G85" t="n">
-        <v>2.92202639579773</v>
+        <v>2.92202591896057</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>2.91630792617798</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.04900002479553</v>
       </c>
       <c r="G88" t="n">
-        <v>2.90582418441772</v>
+        <v>2.9058244228363</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.90899991989136</v>
       </c>
       <c r="G93" t="n">
-        <v>2.77239871025085</v>
+        <v>2.77239847183228</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.90899991989136</v>
       </c>
       <c r="G94" t="n">
-        <v>2.77239871025085</v>
+        <v>2.77239847183228</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G95" t="n">
-        <v>2.82576894760132</v>
+        <v>2.82576870918274</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G96" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G97" t="n">
-        <v>2.83815813064575</v>
+        <v>2.83815860748291</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G98" t="n">
-        <v>2.83815813064575</v>
+        <v>2.83815860748291</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G101" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.98850011825562</v>
       </c>
       <c r="G105" t="n">
-        <v>2.84816527366638</v>
+        <v>2.84816551208496</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G107" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.91700005531311</v>
       </c>
       <c r="G111" t="n">
-        <v>2.78002285957336</v>
+        <v>2.78002262115479</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>2.85912489891052</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.92549991607666</v>
       </c>
       <c r="G117" t="n">
-        <v>2.78812336921692</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G119" t="n">
-        <v>2.85435962677002</v>
+        <v>2.85436010360718</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85912489891052</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>3</v>
       </c>
       <c r="G121" t="n">
-        <v>2.85912489891052</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.95149993896484</v>
       </c>
       <c r="G122" t="n">
-        <v>2.81290292739868</v>
+        <v>2.81290245056152</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288221359253</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288221359253</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G131" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G132" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G136" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G137" t="n">
-        <v>2.83053398132324</v>
+        <v>2.83053421974182</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G138" t="n">
-        <v>2.79241251945496</v>
+        <v>2.79241228103638</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.95700001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.81814479827881</v>
+        <v>2.81814455986023</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G140" t="n">
-        <v>2.87818598747253</v>
+        <v>2.87818622589111</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3</v>
       </c>
       <c r="G141" t="n">
-        <v>2.85912489891052</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G142" t="n">
-        <v>2.88390445709229</v>
+        <v>2.88390421867371</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3</v>
       </c>
       <c r="G143" t="n">
-        <v>2.85912489891052</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>2.90201258659363</v>
+        <v>2.90201210975647</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>2.91630792617798</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.24049997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>3.0883321762085</v>
+        <v>3.08833169937134</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.27649998664856</v>
       </c>
       <c r="G152" t="n">
-        <v>3.12264084815979</v>
+        <v>3.12264132499695</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.32949995994568</v>
       </c>
       <c r="G153" t="n">
-        <v>3.17315244674683</v>
+        <v>3.17315268516541</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G154" t="n">
-        <v>3.24987268447876</v>
+        <v>3.24987244606018</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.40949988365173</v>
       </c>
       <c r="G155" t="n">
-        <v>3.24939584732056</v>
+        <v>3.24939560890198</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G157" t="n">
-        <v>3.18315958976746</v>
+        <v>3.1831591129303</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.35349988937378</v>
       </c>
       <c r="G158" t="n">
-        <v>3.19602584838867</v>
+        <v>3.19602560997009</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>3.28799414634705</v>
+        <v>3.28799390792847</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.41700005531311</v>
       </c>
       <c r="G163" t="n">
-        <v>3.2565438747406</v>
+        <v>3.25654363632202</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.25463771820068</v>
+        <v>3.2546374797821</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>3.26893329620361</v>
+        <v>3.26893305778503</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>3.31658506393433</v>
+        <v>3.31658554077148</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>3.31658506393433</v>
+        <v>3.31658554077148</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.34517693519592</v>
+        <v>3.34517669677734</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.59450006484985</v>
       </c>
       <c r="G171" t="n">
-        <v>3.42570853233337</v>
+        <v>3.42570877075195</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>3.58343720436096</v>
+        <v>3.58343696594238</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G175" t="n">
-        <v>3.55484557151794</v>
+        <v>3.5548460483551</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>3.7549843788147</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G181" t="n">
-        <v>3.7549843788147</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G182" t="n">
-        <v>3.62155890464783</v>
+        <v>3.62155842781067</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G183" t="n">
-        <v>3.54531526565552</v>
+        <v>3.5453155040741</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>3.62155890464783</v>
+        <v>3.62155842781067</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G185" t="n">
-        <v>3.66921067237854</v>
+        <v>3.66921091079712</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G186" t="n">
-        <v>3.66921067237854</v>
+        <v>3.66921091079712</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G190" t="n">
-        <v>3.79310607910156</v>
+        <v>3.79310631752014</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>3.95512342453003</v>
+        <v>3.95512294769287</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G196" t="n">
-        <v>3.80263686180115</v>
+        <v>3.80263638496399</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>3.85028910636902</v>
+        <v>3.85028886795044</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>3.7549843788147</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>3.7549843788147</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G200" t="n">
-        <v>3.77414274215698</v>
+        <v>3.77414298057556</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83161687850952</v>
+        <v>3.83161664009094</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>3.92740702629089</v>
+        <v>3.92740726470947</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>3.87951302528381</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>3.88909125328064</v>
+        <v>3.88909101486206</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82203841209412</v>
+        <v>3.82203793525696</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G206" t="n">
-        <v>3.80287957191467</v>
+        <v>3.80287981033325</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>3.77414274215698</v>
+        <v>3.77414298057556</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>3.70708918571472</v>
+        <v>3.7070894241333</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G209" t="n">
-        <v>3.69751024246216</v>
+        <v>3.69751048088074</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G210" t="n">
-        <v>3.69751024246216</v>
+        <v>3.69751048088074</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>3.83161687850952</v>
+        <v>3.83161664009094</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>3.87951302528381</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>3.87951302528381</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>3.87951302528381</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>3.87951302528381</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.93698620796204</v>
+        <v>3.93698596954346</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>4.03277730941772</v>
+        <v>4.03277635574341</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.21477842330933</v>
+        <v>4.21477890014648</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>4.10940885543823</v>
+        <v>4.10940933227539</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G224" t="n">
-        <v>4.19562149047852</v>
+        <v>4.1956205368042</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G225" t="n">
-        <v>4.3967809677124</v>
+        <v>4.39678001403809</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.5</v>
       </c>
       <c r="G227" t="n">
-        <v>4.31056976318359</v>
+        <v>4.31056928634644</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>4.45425415039062</v>
+        <v>4.45425462722778</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G229" t="n">
-        <v>4.43509674072266</v>
+        <v>4.4350962638855</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G231" t="n">
-        <v>4.48299264907837</v>
+        <v>4.48299169540405</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G232" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G235" t="n">
-        <v>4.6841516494751</v>
+        <v>4.68415212631226</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G237" t="n">
-        <v>4.96194362640381</v>
+        <v>4.96194410324097</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G238" t="n">
-        <v>5.00025987625122</v>
+        <v>5.00026035308838</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G241" t="n">
-        <v>4.94278573989868</v>
+        <v>4.94278621673584</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5</v>
       </c>
       <c r="G242" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5</v>
       </c>
       <c r="G243" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5</v>
       </c>
       <c r="G245" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G249" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036237716675</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036237716675</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036237716675</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5</v>
       </c>
       <c r="G255" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G256" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457342147827</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G257" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457342147827</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G258" t="n">
-        <v>4.48299264907837</v>
+        <v>4.48299169540405</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>4.63625717163086</v>
+        <v>4.6362566947937</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G262" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457342147827</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583587646484</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G264" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G265" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G271" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G272" t="n">
-        <v>4.50215005874634</v>
+        <v>4.50214958190918</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>4.57878303527832</v>
+        <v>4.57878255844116</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>4.76078319549561</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G275" t="n">
-        <v>4.76078319549561</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G276" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036237716675</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>4.62667751312256</v>
+        <v>4.6266770362854</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G279" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457342147827</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G280" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457342147827</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583587646484</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583587646484</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G289" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G294" t="n">
-        <v>4.76078319549561</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457342147827</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457342147827</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5</v>
       </c>
       <c r="G304" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G306" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5</v>
       </c>
       <c r="G311" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5</v>
       </c>
       <c r="G312" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.76078319549561</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5</v>
       </c>
       <c r="G316" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036237716675</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036237716675</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5</v>
       </c>
       <c r="G322" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5</v>
       </c>
       <c r="G326" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5</v>
       </c>
       <c r="G330" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5</v>
       </c>
       <c r="G333" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036237716675</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5</v>
       </c>
       <c r="G336" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.98110198974609</v>
+        <v>4.98110151290894</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>4.98110198974609</v>
+        <v>4.98110151290894</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G343" t="n">
-        <v>5.00025987625122</v>
+        <v>5.00026035308838</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.13436651229858</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.11520862579346</v>
+        <v>5.11520910263062</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>5.5</v>
       </c>
       <c r="G347" t="n">
-        <v>5.26847362518311</v>
+        <v>5.26847314834595</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G348" t="n">
-        <v>5.32594776153564</v>
+        <v>5.32594728469849</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G349" t="n">
-        <v>5.21099901199341</v>
+        <v>5.21099853515625</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.13436651229858</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G351" t="n">
-        <v>5.13436651229858</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G353" t="n">
-        <v>5.09605073928833</v>
+        <v>5.09605121612549</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G355" t="n">
-        <v>5.05773401260376</v>
+        <v>5.05773496627808</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G358" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G359" t="n">
-        <v>5.01941871643066</v>
+        <v>5.01941823959351</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G361" t="n">
-        <v>5.21099901199341</v>
+        <v>5.21099853515625</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.13436651229858</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G364" t="n">
-        <v>5.15352535247803</v>
+        <v>5.15352439880371</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>5.32594776153564</v>
+        <v>5.32594728469849</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>5.28763103485107</v>
+        <v>5.28763151168823</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>5.36426305770874</v>
+        <v>5.36426448822021</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G368" t="n">
-        <v>5.47921180725098</v>
+        <v>5.47921228408813</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6</v>
       </c>
       <c r="G375" t="n">
-        <v>5.7474250793457</v>
+        <v>5.74742555618286</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G376" t="n">
-        <v>5.91984796524048</v>
+        <v>5.91984844207764</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G377" t="n">
-        <v>5.90069055557251</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>5.8623743057251</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G379" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>5.8623743057251</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G384" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G386" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G388" t="n">
-        <v>5.97732257843018</v>
+        <v>5.97732210159302</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>5.82405805587769</v>
+        <v>5.82405853271484</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G391" t="n">
-        <v>5.91984796524048</v>
+        <v>5.91984844207764</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G393" t="n">
-        <v>5.8623743057251</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G394" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G395" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964296340942</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G399" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964296340942</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>6.32216739654541</v>
+        <v>6.32216835021973</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G401" t="n">
-        <v>6.36048460006714</v>
+        <v>6.36048412322998</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G402" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964296340942</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G403" t="n">
-        <v>6.45627450942993</v>
+        <v>6.45627403259277</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G404" t="n">
-        <v>6.39880037307739</v>
+        <v>6.39879989624023</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>6.32216739654541</v>
+        <v>6.32216835021973</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>6.36048460006714</v>
+        <v>6.36048412322998</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>6.41795825958252</v>
+        <v>6.41795778274536</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>6.5</v>
       </c>
       <c r="G409" t="n">
-        <v>6.22637748718262</v>
+        <v>6.22637701034546</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>5.8623743057251</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.5558443069458</v>
+        <v>5.55584478378296</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>6</v>
       </c>
       <c r="G416" t="n">
-        <v>5.7474250793457</v>
+        <v>5.74742555618286</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G417" t="n">
-        <v>5.90069055557251</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G419" t="n">
-        <v>5.90069055557251</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>5.70910930633545</v>
+        <v>5.70910978317261</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>5.70910930633545</v>
+        <v>5.70910978317261</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>5.67079305648804</v>
+        <v>5.67079257965088</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G423" t="n">
-        <v>5.67079305648804</v>
+        <v>5.67079257965088</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G424" t="n">
-        <v>5.8623743057251</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G426" t="n">
-        <v>5.97732257843018</v>
+        <v>5.97732210159302</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G427" t="n">
-        <v>5.99648094177246</v>
+        <v>5.99647998809814</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>6.30300951004028</v>
+        <v>6.30300998687744</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>6.41795825958252</v>
+        <v>6.41795778274536</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>6.41795825958252</v>
+        <v>6.41795778274536</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G436" t="n">
-        <v>6.57122325897217</v>
+        <v>6.57122278213501</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G437" t="n">
-        <v>6.62869691848755</v>
+        <v>6.62869739532471</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7</v>
       </c>
       <c r="G438" t="n">
-        <v>6.70532894134521</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>7</v>
       </c>
       <c r="G439" t="n">
-        <v>6.70532894134521</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7</v>
       </c>
       <c r="G441" t="n">
-        <v>6.70532894134521</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>6.6861720085144</v>
+        <v>6.68617153167725</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>7</v>
       </c>
       <c r="G443" t="n">
-        <v>6.70532894134521</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G444" t="n">
-        <v>6.78196144104004</v>
+        <v>6.78196239471436</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>7.165123462677</v>
+        <v>7.16512441635132</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>8.13305568695068</v>
+        <v>8.13305473327637</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.5</v>
       </c>
       <c r="G454" t="n">
-        <v>8.1715087890625</v>
+        <v>8.17150974273682</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G455" t="n">
-        <v>7.99846506118774</v>
+        <v>7.9984655380249</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537269592285</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G457" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537269592285</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.5</v>
       </c>
       <c r="G458" t="n">
-        <v>8.1715087890625</v>
+        <v>8.17150974273682</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>8.13305568695068</v>
+        <v>8.13305473327637</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G460" t="n">
-        <v>8.01769351959229</v>
+        <v>8.01769161224365</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G461" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537269592285</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537269592285</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>7.80619478225708</v>
+        <v>7.80619430541992</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>7.22938299179077</v>
+        <v>7.22938251495361</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>7.32551765441895</v>
+        <v>7.3255181312561</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G470" t="n">
-        <v>7.24860954284668</v>
+        <v>7.24861001968384</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>7.19092798233032</v>
+        <v>7.19092893600464</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G474" t="n">
-        <v>7.07556629180908</v>
+        <v>7.07556581497192</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G475" t="n">
-        <v>7.4985613822937</v>
+        <v>7.49856185913086</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G481" t="n">
-        <v>7.61392450332642</v>
+        <v>7.61392498016357</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>7.61392450332642</v>
+        <v>7.61392498016357</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G489" t="n">
-        <v>7.47933483123779</v>
+        <v>7.47933530807495</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G490" t="n">
-        <v>7.55624294281006</v>
+        <v>7.55624341964722</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G491" t="n">
-        <v>7.46010780334473</v>
+        <v>7.46010732650757</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.61392450332642</v>
+        <v>7.61392498016357</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>7.76774120330811</v>
+        <v>7.76774072647095</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>7.76774120330811</v>
+        <v>7.76774072647095</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G502" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G503" t="n">
-        <v>7.67160606384277</v>
+        <v>7.67160558700562</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G504" t="n">
-        <v>7.82542276382446</v>
+        <v>7.8254222869873</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>8.01769351959229</v>
+        <v>8.01769161224365</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G510" t="n">
-        <v>8.55604934692383</v>
+        <v>8.55605125427246</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G511" t="n">
-        <v>8.55604934692383</v>
+        <v>8.55605125427246</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9</v>
       </c>
       <c r="G512" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G513" t="n">
-        <v>8.74832248687744</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>9.24822521209717</v>
+        <v>9.2482271194458</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G515" t="n">
-        <v>8.78677654266357</v>
+        <v>8.78677558898926</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G517" t="n">
-        <v>9.3635892868042</v>
+        <v>9.36358833312988</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G518" t="n">
-        <v>9.30590724945068</v>
+        <v>9.305908203125</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G519" t="n">
-        <v>9.30590724945068</v>
+        <v>9.305908203125</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G521" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>9.49817943572998</v>
+        <v>9.49817848205566</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G523" t="n">
-        <v>9.47895050048828</v>
+        <v>9.4789514541626</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G524" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G525" t="n">
-        <v>9.34436225891113</v>
+        <v>9.34436130523682</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G526" t="n">
-        <v>9.3635892868042</v>
+        <v>9.36358833312988</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G527" t="n">
-        <v>9.01750183105469</v>
+        <v>9.01750087738037</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G528" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G530" t="n">
-        <v>8.70986843109131</v>
+        <v>8.70986747741699</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G531" t="n">
-        <v>8.94059276580811</v>
+        <v>8.94059181213379</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G533" t="n">
-        <v>8.99827480316162</v>
+        <v>8.9982738494873</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>8.94059276580811</v>
+        <v>8.94059181213379</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>8.94059276580811</v>
+        <v>8.94059181213379</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G537" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G538" t="n">
-        <v>8.74832248687744</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>8.69064140319824</v>
+        <v>8.69064044952393</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>9</v>
       </c>
       <c r="G540" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G541" t="n">
-        <v>8.63295936584473</v>
+        <v>8.63296031951904</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9</v>
       </c>
       <c r="G542" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G544" t="n">
-        <v>8.47914218902588</v>
+        <v>8.4791431427002</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G545" t="n">
-        <v>8.26764488220215</v>
+        <v>8.26764583587646</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G550" t="n">
-        <v>8.42146110534668</v>
+        <v>8.421462059021</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G551" t="n">
-        <v>8.42146110534668</v>
+        <v>8.421462059021</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G553" t="n">
-        <v>8.42146110534668</v>
+        <v>8.421462059021</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G554" t="n">
-        <v>8.42146110534668</v>
+        <v>8.421462059021</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>8.55604934692383</v>
+        <v>8.55605125427246</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G559" t="n">
-        <v>8.55604934692383</v>
+        <v>8.55605125427246</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G560" t="n">
-        <v>8.59450435638428</v>
+        <v>8.59450531005859</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G561" t="n">
-        <v>8.78677654266357</v>
+        <v>8.78677558898926</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G562" t="n">
-        <v>8.95981884002686</v>
+        <v>8.95981979370117</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G563" t="n">
-        <v>8.90213871002197</v>
+        <v>8.90213775634766</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>8.94059276580811</v>
+        <v>8.94059181213379</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>8.97904777526855</v>
+        <v>8.97904682159424</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G566" t="n">
-        <v>8.95981884002686</v>
+        <v>8.95981979370117</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G568" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G572" t="n">
-        <v>9.05595588684082</v>
+        <v>9.05595397949219</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G574" t="n">
-        <v>9.01750183105469</v>
+        <v>9.01750087738037</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G575" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>9</v>
       </c>
       <c r="G576" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G577" t="n">
-        <v>8.78677654266357</v>
+        <v>8.78677558898926</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G578" t="n">
-        <v>8.97904777526855</v>
+        <v>8.97904682159424</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G579" t="n">
-        <v>8.90213871002197</v>
+        <v>8.90213775634766</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G581" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G582" t="n">
-        <v>8.70986843109131</v>
+        <v>8.70986747741699</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>8.72909545898438</v>
+        <v>8.72909450531006</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9</v>
       </c>
       <c r="G584" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.69064140319824</v>
+        <v>8.69064044952393</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>8.74832248687744</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G587" t="n">
-        <v>8.70986843109131</v>
+        <v>8.70986747741699</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G588" t="n">
-        <v>8.70986843109131</v>
+        <v>8.70986747741699</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G589" t="n">
-        <v>8.67141532897949</v>
+        <v>8.67141342163086</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>9</v>
       </c>
       <c r="G590" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>9</v>
       </c>
       <c r="G591" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G592" t="n">
-        <v>8.59450435638428</v>
+        <v>8.59450531005859</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9</v>
       </c>
       <c r="G593" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G594" t="n">
-        <v>8.80600357055664</v>
+        <v>8.80600261688232</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G595" t="n">
-        <v>8.78677654266357</v>
+        <v>8.78677558898926</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G600" t="n">
-        <v>9.34436225891113</v>
+        <v>9.34436130523682</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G604" t="n">
-        <v>9.26745319366455</v>
+        <v>9.26745414733887</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G605" t="n">
-        <v>9.3635892868042</v>
+        <v>9.36358833312988</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G606" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>9.2289981842041</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G608" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G612" t="n">
-        <v>9.1713171005249</v>
+        <v>9.17131805419922</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G616" t="n">
-        <v>9.2289981842041</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G619" t="n">
-        <v>9.2289981842041</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G620" t="n">
-        <v>9.2289981842041</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>9.1713171005249</v>
+        <v>9.17131805419922</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G622" t="n">
-        <v>9.2289981842041</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G623" t="n">
-        <v>9.44049644470215</v>
+        <v>9.44049739837646</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>9.75774383544922</v>
+        <v>9.75774478912354</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>9.99808120727539</v>
+        <v>9.99808216094971</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>10.5</v>
       </c>
       <c r="G627" t="n">
-        <v>10.0942182540894</v>
+        <v>10.094217300415</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G628" t="n">
-        <v>10.2864875793457</v>
+        <v>10.2864894866943</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>10.2864875793457</v>
+        <v>10.2864894866943</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G630" t="n">
-        <v>10.2864875793457</v>
+        <v>10.2864894866943</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>10.1422853469849</v>
+        <v>10.1422863006592</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G632" t="n">
-        <v>10.1422853469849</v>
+        <v>10.1422863006592</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>10.5</v>
       </c>
       <c r="G633" t="n">
-        <v>10.0942182540894</v>
+        <v>10.094217300415</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>9.95001411437988</v>
+        <v>9.9500150680542</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>10.5</v>
       </c>
       <c r="G635" t="n">
-        <v>10.0942182540894</v>
+        <v>10.094217300415</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>10.5</v>
       </c>
       <c r="G637" t="n">
-        <v>10.0942182540894</v>
+        <v>10.094217300415</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>10.190354347229</v>
+        <v>10.1903533935547</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>10.2864875793457</v>
+        <v>10.2864894866943</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>10.3826246261597</v>
+        <v>10.3826236724854</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G645" t="n">
-        <v>10.3826246261597</v>
+        <v>10.3826236724854</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>10.67103099823</v>
+        <v>10.6710300445557</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>10.67103099823</v>
+        <v>10.6710300445557</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>10.7671642303467</v>
+        <v>10.7671661376953</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>11.5</v>
       </c>
       <c r="G651" t="n">
-        <v>11.0555725097656</v>
+        <v>11.0555734634399</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>11.5</v>
       </c>
       <c r="G652" t="n">
-        <v>11.0555725097656</v>
+        <v>11.0555734634399</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>13.25</v>
       </c>
       <c r="G657" t="n">
-        <v>12.7379417419434</v>
+        <v>12.737940788269</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G658" t="n">
-        <v>12.5937385559082</v>
+        <v>12.5937376022339</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>12.930212020874</v>
+        <v>12.9302110671997</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G660" t="n">
-        <v>12.834077835083</v>
+        <v>12.8340768814087</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>12.5937385559082</v>
+        <v>12.5937376022339</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>12.1130619049072</v>
+        <v>12.1130609512329</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G663" t="n">
-        <v>12.7860107421875</v>
+        <v>12.7860088348389</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G664" t="n">
-        <v>12.8821439743042</v>
+        <v>12.8821430206299</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>12.6418037414551</v>
+        <v>12.6418056488037</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>12.7860107421875</v>
+        <v>12.7860088348389</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>12.7860107421875</v>
+        <v>12.7860088348389</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>12.834077835083</v>
+        <v>12.8340768814087</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>12.7860107421875</v>
+        <v>12.7860088348389</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>12.5937385559082</v>
+        <v>12.5937376022339</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>13.25</v>
       </c>
       <c r="G671" t="n">
-        <v>12.7379417419434</v>
+        <v>12.737940788269</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>13.25</v>
       </c>
       <c r="G672" t="n">
-        <v>12.7379417419434</v>
+        <v>12.737940788269</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G674" t="n">
-        <v>13.5070247650146</v>
+        <v>13.5070238113403</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>13.8915672302246</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>13.795431137085</v>
+        <v>13.7954301834106</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>13.5070247650146</v>
+        <v>13.5070238113403</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>13.6512279510498</v>
+        <v>13.6512269973755</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>13.8915672302246</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838356018066</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838356018066</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G687" t="n">
-        <v>13.9877014160156</v>
+        <v>13.9877033233643</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>13.795431137085</v>
+        <v>13.7954301834106</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>13.8915672302246</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>13.8915672302246</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>13.8915672302246</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>14</v>
       </c>
       <c r="G696" t="n">
-        <v>13.4589557647705</v>
+        <v>13.4589567184448</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>14</v>
       </c>
       <c r="G697" t="n">
-        <v>13.4589557647705</v>
+        <v>13.4589567184448</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G698" t="n">
-        <v>13.5550937652588</v>
+        <v>13.5550928115845</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>13.60315990448</v>
+        <v>13.6031608581543</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>13.7473630905151</v>
+        <v>13.7473621368408</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G701" t="n">
-        <v>13.7473630905151</v>
+        <v>13.7473621368408</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>13.9877014160156</v>
+        <v>13.9877033233643</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838356018066</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838356018066</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>14.3631258010864</v>
+        <v>14.3631277084351</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>15.5</v>
       </c>
       <c r="G707" t="n">
-        <v>14.9415073394775</v>
+        <v>14.9415082931519</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>15.5</v>
       </c>
       <c r="G708" t="n">
-        <v>14.9415073394775</v>
+        <v>14.9415082931519</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G709" t="n">
-        <v>15.1343011856079</v>
+        <v>15.1343021392822</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>15.9536714553833</v>
+        <v>15.9536733627319</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>16.9658432006836</v>
+        <v>16.965841293335</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>16.7248477935791</v>
+        <v>16.7248497009277</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>16.05006980896</v>
+        <v>16.0500717163086</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>16.2428665161133</v>
+        <v>16.2428646087646</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G740" t="n">
-        <v>15.2306976318359</v>
+        <v>15.2306995391846</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>14.8451108932495</v>
+        <v>14.8451099395752</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>15.5198888778687</v>
+        <v>15.5198879241943</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G746" t="n">
-        <v>15.2306976318359</v>
+        <v>15.2306995391846</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>14.8451108932495</v>
+        <v>14.8451099395752</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G749" t="n">
-        <v>14.8451108932495</v>
+        <v>14.8451099395752</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>15.75</v>
       </c>
       <c r="G751" t="n">
-        <v>15.1825008392334</v>
+        <v>15.1824998855591</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>15.75</v>
       </c>
       <c r="G753" t="n">
-        <v>15.1825008392334</v>
+        <v>15.1824998855591</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>15.2306976318359</v>
+        <v>15.2306995391846</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>16.25</v>
       </c>
       <c r="G757" t="n">
-        <v>15.6644830703735</v>
+        <v>15.6644849777222</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G758" t="n">
-        <v>15.8572788238525</v>
+        <v>15.8572778701782</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162853240967</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G761" t="n">
-        <v>15.4716892242432</v>
+        <v>15.4716901779175</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>16.25</v>
       </c>
       <c r="G762" t="n">
-        <v>15.6644830703735</v>
+        <v>15.6644849777222</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>15.5198888778687</v>
+        <v>15.5198879241943</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G764" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162853240967</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162853240967</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G771" t="n">
-        <v>17.0622367858887</v>
+        <v>17.0622406005859</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>18</v>
       </c>
       <c r="G774" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>16.7248477935791</v>
+        <v>16.7248497009277</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G782" t="n">
-        <v>16.7730484008789</v>
+        <v>16.7730464935303</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>16.5320568084717</v>
+        <v>16.532054901123</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>17.0622367858887</v>
+        <v>17.0622406005859</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>17.6888160705566</v>
+        <v>17.6888179779053</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>18.7009868621826</v>
+        <v>18.7009830474854</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>18.5081920623779</v>
+        <v>18.5081901550293</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G810" t="n">
-        <v>18.3635921478271</v>
+        <v>18.3635940551758</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>19</v>
       </c>
       <c r="G814" t="n">
-        <v>18.3153972625732</v>
+        <v>18.3153991699219</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>19</v>
       </c>
       <c r="G815" t="n">
-        <v>18.3153972625732</v>
+        <v>18.3153991699219</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>17.6888160705566</v>
+        <v>17.6888179779053</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>18.1226005554199</v>
+        <v>18.1226024627686</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>17.8816108703613</v>
+        <v>17.8816089630127</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G833" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>19</v>
       </c>
       <c r="G834" t="n">
-        <v>18.3153972625732</v>
+        <v>18.3153991699219</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>18.5</v>
       </c>
       <c r="G839" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334102630615</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>17.8816108703613</v>
+        <v>17.8816089630127</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>18.5</v>
       </c>
       <c r="G848" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334102630615</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>17.6888160705566</v>
+        <v>17.6888179779053</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>18</v>
       </c>
       <c r="G851" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>18</v>
       </c>
       <c r="G855" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>17.785213470459</v>
+        <v>17.7852153778076</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>17.9298076629639</v>
+        <v>17.9298095703125</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>18.5</v>
       </c>
       <c r="G858" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334102630615</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>18</v>
       </c>
       <c r="G862" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>18</v>
       </c>
       <c r="G863" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>18</v>
       </c>
       <c r="G868" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>18.1226005554199</v>
+        <v>18.1226024627686</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>19</v>
       </c>
       <c r="G872" t="n">
-        <v>18.3153972625732</v>
+        <v>18.3153991699219</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>19</v>
       </c>
       <c r="G873" t="n">
-        <v>18.3153972625732</v>
+        <v>18.3153991699219</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G874" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G875" t="n">
-        <v>18.5081920623779</v>
+        <v>18.5081901550293</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>17.9298076629639</v>
+        <v>17.9298095703125</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>18.5081920623779</v>
+        <v>18.5081901550293</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G887" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>18.3635921478271</v>
+        <v>18.3635940551758</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>18.1226005554199</v>
+        <v>18.1226024627686</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>18.5</v>
       </c>
       <c r="G892" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334102630615</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>18.5</v>
       </c>
       <c r="G893" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334102630615</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>17.25</v>
       </c>
       <c r="G895" t="n">
-        <v>16.6284503936768</v>
+        <v>16.6284523010254</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>17.8816108703613</v>
+        <v>17.8816089630127</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>18</v>
       </c>
       <c r="G903" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>18</v>
       </c>
       <c r="G908" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>17.0622367858887</v>
+        <v>17.0622406005859</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>14.6523189544678</v>
+        <v>14.6523170471191</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>15.327094078064</v>
+        <v>15.3270950317383</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>15.327094078064</v>
+        <v>15.3270950317383</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>15.5</v>
       </c>
       <c r="G920" t="n">
-        <v>14.9415073394775</v>
+        <v>14.9415082931519</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G924" t="n">
-        <v>12.9653739929199</v>
+        <v>12.9653720855713</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>15.5198888778687</v>
+        <v>15.5198879241943</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>16.0018730163574</v>
+        <v>16.0018711090088</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>15.75</v>
       </c>
       <c r="G933" t="n">
-        <v>15.1825008392334</v>
+        <v>15.1824998855591</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G934" t="n">
-        <v>15.2306976318359</v>
+        <v>15.2306995391846</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>15.0861034393311</v>
+        <v>15.0861015319824</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>14.8451108932495</v>
+        <v>14.8451099395752</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G938" t="n">
-        <v>14.3631258010864</v>
+        <v>14.3631277084351</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>15.327094078064</v>
+        <v>15.3270950317383</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G941" t="n">
-        <v>15.0861034393311</v>
+        <v>15.0861015319824</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>15.1343011856079</v>
+        <v>15.1343021392822</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>15.2306976318359</v>
+        <v>15.2306995391846</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>15.75</v>
       </c>
       <c r="G945" t="n">
-        <v>15.1825008392334</v>
+        <v>15.1824998855591</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G947" t="n">
-        <v>15.0861034393311</v>
+        <v>15.0861015319824</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G948" t="n">
-        <v>15.2306976318359</v>
+        <v>15.2306995391846</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>14.6523189544678</v>
+        <v>14.6523170471191</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G952" t="n">
-        <v>14.604118347168</v>
+        <v>14.6041193008423</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>14.3631258010864</v>
+        <v>14.3631277084351</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G954" t="n">
-        <v>14.3631258010864</v>
+        <v>14.3631277084351</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>14.3631258010864</v>
+        <v>14.3631277084351</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G960" t="n">
-        <v>13.6401500701904</v>
+        <v>13.6401510238647</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G963" t="n">
-        <v>13.2624025344849</v>
+        <v>13.2624034881592</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>13.75</v>
       </c>
       <c r="G964" t="n">
-        <v>13.3108062744141</v>
+        <v>13.3108072280884</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>13.4076137542725</v>
+        <v>13.4076128005981</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G969" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>14</v>
       </c>
       <c r="G970" t="n">
-        <v>13.5528221130371</v>
+        <v>13.5528211593628</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G972" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G974" t="n">
-        <v>14.4240732192993</v>
+        <v>14.4240741729736</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>14.75</v>
       </c>
       <c r="G976" t="n">
-        <v>14.278865814209</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>13.9400444030762</v>
+        <v>13.9400434494019</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>13.4076137542725</v>
+        <v>13.4076128005981</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G981" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G983" t="n">
-        <v>15.2953262329102</v>
+        <v>15.2953271865845</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>16</v>
       </c>
       <c r="G984" t="n">
-        <v>15.488938331604</v>
+        <v>15.4889392852783</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>15.4405355453491</v>
+        <v>15.4405345916748</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G986" t="n">
-        <v>15.3921318054199</v>
+        <v>15.3921327590942</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>14.4240732192993</v>
+        <v>14.4240741729736</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G993" t="n">
-        <v>13.9400444030762</v>
+        <v>13.9400434494019</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>14.75</v>
       </c>
       <c r="G994" t="n">
-        <v>14.278865814209</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>14.25</v>
       </c>
       <c r="G998" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>13.6496267318726</v>
+        <v>13.6496276855469</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.4076137542725</v>
+        <v>13.4076128005981</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>14</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.5528221130371</v>
+        <v>13.5528211593628</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1005" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>13.6496267318726</v>
+        <v>13.6496276855469</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1009" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>13.1655969619751</v>
+        <v>13.1655979156494</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1013" t="n">
-        <v>13.4076137542725</v>
+        <v>13.4076128005981</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>13.1655969619751</v>
+        <v>13.1655979156494</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.0203895568848</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1019" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1021" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1024" t="n">
-        <v>12.2459421157837</v>
+        <v>12.2459411621094</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>13.75</v>
       </c>
       <c r="G1027" t="n">
-        <v>13.3108062744141</v>
+        <v>13.3108072280884</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1032" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>14.7144927978516</v>
+        <v>14.7144918441772</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>14.3756713867188</v>
+        <v>14.3756704330444</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>14.75</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.278865814209</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>14.75</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.278865814209</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1052" t="n">
-        <v>13.9400444030762</v>
+        <v>13.9400434494019</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.6496267318726</v>
+        <v>13.6496276855469</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1054" t="n">
-        <v>13.6496267318726</v>
+        <v>13.6496276855469</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>14.25</v>
       </c>
       <c r="G1055" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>13.9400444030762</v>
+        <v>13.9400434494019</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>14.25</v>
       </c>
       <c r="G1057" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1060" t="n">
-        <v>13.2624025344849</v>
+        <v>13.2624034881592</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1064" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1066" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>12.2459421157837</v>
+        <v>12.2459411621094</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1070" t="n">
-        <v>11.7135105133057</v>
+        <v>11.7135095596313</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>12.25</v>
       </c>
       <c r="G1071" t="n">
-        <v>11.8587188720703</v>
+        <v>11.858717918396</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1072" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1075" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1076" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1079" t="n">
-        <v>12.6331653594971</v>
+        <v>12.6331644058228</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>12.6331653594971</v>
+        <v>12.6331644058228</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1086" t="n">
-        <v>12.6331653594971</v>
+        <v>12.6331644058228</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1087" t="n">
-        <v>12.6331653594971</v>
+        <v>12.6331644058228</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1092" t="n">
-        <v>12.6331653594971</v>
+        <v>12.6331644058228</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>12.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>12.75</v>
       </c>
       <c r="G1095" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1096" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1097" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>12.75</v>
       </c>
       <c r="G1100" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>12.75</v>
       </c>
       <c r="G1101" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>12.75</v>
       </c>
       <c r="G1104" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1105" t="n">
-        <v>12.2459421157837</v>
+        <v>12.2459411621094</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1106" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>12.75</v>
       </c>
       <c r="G1107" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>12.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1114" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>12.9719858169556</v>
+        <v>12.9719867706299</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1123" t="n">
-        <v>13.0203895568848</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>12.9719858169556</v>
+        <v>12.9719867706299</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>13.0203895568848</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1127" t="n">
-        <v>12.9719858169556</v>
+        <v>12.9719867706299</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>13.2140007019043</v>
+        <v>13.21399974823</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1129" t="n">
-        <v>13.1655969619751</v>
+        <v>13.1655979156494</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1130" t="n">
-        <v>13.1655969619751</v>
+        <v>13.1655979156494</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1133" t="n">
-        <v>13.6496267318726</v>
+        <v>13.6496276855469</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1136" t="n">
-        <v>13.9400444030762</v>
+        <v>13.9400434494019</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>14</v>
       </c>
       <c r="G1137" t="n">
-        <v>13.5528221130371</v>
+        <v>13.5528211593628</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1138" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>14.25</v>
       </c>
       <c r="G1139" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1140" t="n">
-        <v>13.9400444030762</v>
+        <v>13.9400434494019</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1141" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>14.25</v>
       </c>
       <c r="G1142" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>15.25</v>
       </c>
       <c r="G1146" t="n">
-        <v>14.7628946304321</v>
+        <v>14.7628936767578</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1149" t="n">
-        <v>14.1820583343506</v>
+        <v>14.1820592880249</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1150" t="n">
-        <v>14.1820583343506</v>
+        <v>14.1820592880249</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>14.75</v>
       </c>
       <c r="G1151" t="n">
-        <v>14.278865814209</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1159" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1161" t="n">
-        <v>14.1820583343506</v>
+        <v>14.1820592880249</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1166" t="n">
-        <v>13.9400444030762</v>
+        <v>13.9400434494019</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1168" t="n">
-        <v>13.6496267318726</v>
+        <v>13.6496276855469</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>13.4076137542725</v>
+        <v>13.4076128005981</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>13.75</v>
       </c>
       <c r="G1174" t="n">
-        <v>13.3108062744141</v>
+        <v>13.3108072280884</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>13.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>13.3108062744141</v>
+        <v>13.3108072280884</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1183" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>12.9719858169556</v>
+        <v>12.9719867706299</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1185" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1189" t="n">
-        <v>12.6331653594971</v>
+        <v>12.6331644058228</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>12.75</v>
       </c>
       <c r="G1190" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1193" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1194" t="n">
-        <v>13.0203895568848</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1196" t="n">
-        <v>13.1655969619751</v>
+        <v>13.1655979156494</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1198" t="n">
-        <v>13.1655969619751</v>
+        <v>13.1655979156494</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>13.2624025344849</v>
+        <v>13.2624034881592</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>13.1655969619751</v>
+        <v>13.1655979156494</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1203" t="n">
-        <v>12.6331653594971</v>
+        <v>12.6331644058228</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.6331653594971</v>
+        <v>12.6331644058228</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.2459421157837</v>
+        <v>12.2459411621094</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1215" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1217" t="n">
-        <v>13.0203895568848</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>12.75</v>
       </c>
       <c r="G1224" t="n">
-        <v>12.4106178283691</v>
+        <v>12.4106187820435</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1225" t="n">
-        <v>12.3619480133057</v>
+        <v>12.36194896698</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1227" t="n">
-        <v>12.264612197876</v>
+        <v>12.2646112442017</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>12.5</v>
       </c>
       <c r="G1229" t="n">
-        <v>12.167272567749</v>
+        <v>12.1672716140747</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>12.264612197876</v>
+        <v>12.2646112442017</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.9725971221924</v>
+        <v>11.9725961685181</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1235" t="n">
-        <v>11.7779207229614</v>
+        <v>11.7779197692871</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1236" t="n">
-        <v>11.7779207229614</v>
+        <v>11.7779197692871</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>12</v>
       </c>
       <c r="G1237" t="n">
-        <v>11.6805820465088</v>
+        <v>11.6805810928345</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>12</v>
       </c>
       <c r="G1238" t="n">
-        <v>11.6805820465088</v>
+        <v>11.6805810928345</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1239" t="n">
-        <v>11.826587677002</v>
+        <v>11.8265886306763</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>12</v>
       </c>
       <c r="G1240" t="n">
-        <v>11.6805820465088</v>
+        <v>11.6805810928345</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1245" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1246" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1247" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1250" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1253" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1259" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1266" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1268" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>11.5</v>
       </c>
       <c r="G1274" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>11.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>10.8532056808472</v>
+        <v>10.8532066345215</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1283" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>11.5</v>
       </c>
       <c r="G1285" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>11.5</v>
       </c>
       <c r="G1286" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>11.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1289" t="n">
-        <v>10.8532056808472</v>
+        <v>10.8532066345215</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1292" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>11.5</v>
       </c>
       <c r="G1296" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1298" t="n">
-        <v>10.8532056808472</v>
+        <v>10.8532066345215</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1300" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1304" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>11.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1314" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1317" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1322" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>10.3178472518921</v>
+        <v>10.3178482055664</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>9.7824878692627</v>
+        <v>9.78248691558838</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>10.5</v>
       </c>
       <c r="G1334" t="n">
-        <v>10.2205095291138</v>
+        <v>10.2205085754395</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1335" t="n">
-        <v>9.7824878692627</v>
+        <v>9.78248691558838</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1336" t="n">
-        <v>10.1718397140503</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1337" t="n">
-        <v>10.1718397140503</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1350" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1351" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1358" t="n">
-        <v>9.55860900878906</v>
+        <v>9.55860996246338</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1360" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1361" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1364" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1365" t="n">
-        <v>9.40286731719971</v>
+        <v>9.40286827087402</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1366" t="n">
-        <v>9.28606128692627</v>
+        <v>9.28606224060059</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1368" t="n">
-        <v>9.28606128692627</v>
+        <v>9.28606224060059</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1375" t="n">
-        <v>10.4151849746704</v>
+        <v>10.4151859283447</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1376" t="n">
-        <v>10.6098613739014</v>
+        <v>10.6098623275757</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1378" t="n">
-        <v>10.6098613739014</v>
+        <v>10.6098623275757</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1379" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1380" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1383" t="n">
-        <v>10.3178472518921</v>
+        <v>10.3178482055664</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>10.6098613739014</v>
+        <v>10.6098623275757</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1394" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1396" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1397" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1400" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1406" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>10.3178472518921</v>
+        <v>10.3178482055664</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1426" t="n">
-        <v>9.7824878692627</v>
+        <v>9.78248691558838</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1432" t="n">
-        <v>10.1718397140503</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1433" t="n">
-        <v>10.1718397140503</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1438" t="n">
-        <v>9.36393260955811</v>
+        <v>9.36393356323242</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1451" t="n">
-        <v>10.1718397140503</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1459" t="n">
-        <v>9.55860900878906</v>
+        <v>9.55860996246338</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1461" t="n">
-        <v>9.22765827178955</v>
+        <v>9.22765922546387</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1462" t="n">
-        <v>9.55860900878906</v>
+        <v>9.55860996246338</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1464" t="n">
-        <v>9.59754371643066</v>
+        <v>9.59754467010498</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1467" t="n">
-        <v>9.18872451782227</v>
+        <v>9.18872356414795</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1470" t="n">
-        <v>9.20819282531738</v>
+        <v>9.20819187164307</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1474" t="n">
-        <v>9.05245113372803</v>
+        <v>9.05245018005371</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -54530,6 +54530,32 @@
         <v>9.02000045776367</v>
       </c>
       <c r="H2083" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2084" t="n">
+        <v>2928</v>
+      </c>
+      <c r="C2084" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>8.84000015258789</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="G2084" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="H2084" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -48358,7 +48358,7 @@
         <v>562</v>
       </c>
       <c r="C2087" t="n">
-        <v>8.89999961853027</v>
+        <v>8.96000003814697</v>
       </c>
       <c r="D2087" t="n">
         <v>8.80000019073486</v>
@@ -48366,8 +48366,31 @@
       <c r="E2087" t="n">
         <v>8.80000019073486</v>
       </c>
-      <c r="F2087"/>
+      <c r="F2087" t="n">
+        <v>8.96000003814697</v>
+      </c>
       <c r="G2087" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2088" t="n">
+        <v>2706</v>
+      </c>
+      <c r="C2088" t="n">
+        <v>8.9399995803833</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>8.72000026702881</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="F2088"/>
+      <c r="G2088" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -48381,7 +48381,7 @@
         <v>2706</v>
       </c>
       <c r="C2088" t="n">
-        <v>8.9399995803833</v>
+        <v>8.97999954223633</v>
       </c>
       <c r="D2088" t="n">
         <v>8.72000026702881</v>
@@ -48389,8 +48389,31 @@
       <c r="E2088" t="n">
         <v>8.80000019073486</v>
       </c>
-      <c r="F2088"/>
+      <c r="F2088" t="n">
+        <v>8.97999954223633</v>
+      </c>
       <c r="G2088" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2089" t="n">
+        <v>2101</v>
+      </c>
+      <c r="C2089" t="n">
+        <v>8.96000003814697</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>8.72000026702881</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>8.96000003814697</v>
+      </c>
+      <c r="F2089"/>
+      <c r="G2089" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -48412,8 +48412,31 @@
       <c r="E2089" t="n">
         <v>8.96000003814697</v>
       </c>
-      <c r="F2089"/>
+      <c r="F2089" t="n">
+        <v>8.80000019073486</v>
+      </c>
       <c r="G2089" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2090" t="n">
+        <v>4362</v>
+      </c>
+      <c r="C2090" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>8.69999980926514</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="F2090"/>
+      <c r="G2090" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -48435,8 +48435,31 @@
       <c r="E2090" t="n">
         <v>8.80000019073486</v>
       </c>
-      <c r="F2090"/>
+      <c r="F2090" t="n">
+        <v>8.89999961853027</v>
+      </c>
       <c r="G2090" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2091" t="n">
+        <v>114</v>
+      </c>
+      <c r="C2091" t="n">
+        <v>8.88000011444092</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>8.88000011444092</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>8.88000011444092</v>
+      </c>
+      <c r="F2091"/>
+      <c r="G2091" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -48465,6 +48465,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2092">
+      <c r="A2092" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2092" t="n">
+        <v>4300</v>
+      </c>
+      <c r="C2092" t="n">
+        <v>8.88000011444092</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>8.85999965667725</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>8.88000011444092</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>8.88000011444092</v>
+      </c>
+      <c r="G2092" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G2" t="n">
-        <v>2.57321262359619</v>
+        <v>2.57321286201477</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.87050008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>2.73570656776428</v>
+        <v>2.73570609092712</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.91050004959106</v>
       </c>
       <c r="G5" t="n">
-        <v>2.77382826805115</v>
+        <v>2.77382802963257</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.98749995231628</v>
       </c>
       <c r="G6" t="n">
-        <v>2.84721183776855</v>
+        <v>2.84721231460571</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G7" t="n">
-        <v>2.80670785903931</v>
+        <v>2.80670809745789</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.9614999294281</v>
       </c>
       <c r="G11" t="n">
-        <v>2.82243299484253</v>
+        <v>2.82243275642395</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G12" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.98900008201599</v>
       </c>
       <c r="G13" t="n">
-        <v>2.84864211082458</v>
+        <v>2.84864187240601</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78764724731445</v>
+        <v>2.78764700889587</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>2.7066388130188</v>
+        <v>2.70663857460022</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.7066388130188</v>
+        <v>2.70663857460022</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G26" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G29" t="n">
-        <v>2.61895847320557</v>
+        <v>2.61895871162415</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.75</v>
       </c>
       <c r="G30" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086462974548</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.75</v>
       </c>
       <c r="G31" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086462974548</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.75</v>
       </c>
       <c r="G32" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086462974548</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.75</v>
       </c>
       <c r="G33" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086462974548</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.75</v>
       </c>
       <c r="G34" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086462974548</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G35" t="n">
-        <v>2.67232918739319</v>
+        <v>2.67232894897461</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288221359253</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G38" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87818622589111</v>
+        <v>2.87818598747253</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.02049994468689</v>
       </c>
       <c r="G48" t="n">
-        <v>2.87866234779358</v>
+        <v>2.87866258621216</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.05550003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>2.91201901435852</v>
+        <v>2.9120192527771</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G51" t="n">
-        <v>2.92583799362183</v>
+        <v>2.92583823204041</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01161193847656</v>
+        <v>3.01161217689514</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.00208163261414</v>
+        <v>3.00208115577698</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>3.00208163261414</v>
+        <v>3.00208115577698</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G58" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>2.97348999977112</v>
+        <v>2.97349047660828</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G60" t="n">
-        <v>2.97348999977112</v>
+        <v>2.97349047660828</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G63" t="n">
-        <v>2.88771653175354</v>
+        <v>2.88771677017212</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>2.87818622589111</v>
+        <v>2.87818598747253</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.97300004959106</v>
       </c>
       <c r="G66" t="n">
-        <v>2.83339309692383</v>
+        <v>2.83339357376099</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80670785903931</v>
+        <v>2.80670809745789</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G76" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288221359253</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.89100003242493</v>
       </c>
       <c r="G78" t="n">
-        <v>2.75524401664734</v>
+        <v>2.75524353981018</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.90549993515015</v>
       </c>
       <c r="G80" t="n">
-        <v>2.76906299591064</v>
+        <v>2.76906323432922</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>2.77335143089294</v>
+        <v>2.77335166931152</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G83" t="n">
-        <v>2.88771653175354</v>
+        <v>2.88771677017212</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.04900002479553</v>
       </c>
       <c r="G88" t="n">
-        <v>2.90582466125488</v>
+        <v>2.9058244228363</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G89" t="n">
-        <v>2.85054779052734</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G90" t="n">
-        <v>2.85054779052734</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G91" t="n">
-        <v>2.85054779052734</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G95" t="n">
-        <v>2.82576847076416</v>
+        <v>2.82576894760132</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G97" t="n">
-        <v>2.83815860748291</v>
+        <v>2.83815813064575</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G98" t="n">
-        <v>2.83815860748291</v>
+        <v>2.83815813064575</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.98850011825562</v>
       </c>
       <c r="G105" t="n">
-        <v>2.84816551208496</v>
+        <v>2.84816527366638</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G109" t="n">
-        <v>2.7204577922821</v>
+        <v>2.72045803070068</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G110" t="n">
-        <v>2.7204577922821</v>
+        <v>2.72045803070068</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.91700005531311</v>
       </c>
       <c r="G111" t="n">
-        <v>2.78002262115479</v>
+        <v>2.78002285957336</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G115" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G116" t="n">
-        <v>2.8495945930481</v>
+        <v>2.84959483146667</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G118" t="n">
-        <v>2.79622459411621</v>
+        <v>2.79622483253479</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G119" t="n">
-        <v>2.85435962677002</v>
+        <v>2.85436034202576</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.95149993896484</v>
       </c>
       <c r="G122" t="n">
-        <v>2.8129026889801</v>
+        <v>2.81290292739868</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G126" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288221359253</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288221359253</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.92249989509583</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78526425361633</v>
+        <v>2.78526449203491</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.95700001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.81814455986023</v>
+        <v>2.81814432144165</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G140" t="n">
-        <v>2.87818622589111</v>
+        <v>2.87818598747253</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G142" t="n">
-        <v>2.88390398025513</v>
+        <v>2.88390421867371</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.00650000572205</v>
       </c>
       <c r="G145" t="n">
-        <v>2.86532020568848</v>
+        <v>2.8653199672699</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>2.90201258659363</v>
+        <v>2.90201234817505</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.00650000572205</v>
       </c>
       <c r="G147" t="n">
-        <v>2.86532020568848</v>
+        <v>2.8653199672699</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>2.98302054405212</v>
+        <v>2.9830207824707</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.24049997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>3.0883321762085</v>
+        <v>3.08833193778992</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>3.05926442146301</v>
+        <v>3.05926394462585</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.27649998664856</v>
       </c>
       <c r="G152" t="n">
-        <v>3.12264132499695</v>
+        <v>3.12264108657837</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.40949988365173</v>
       </c>
       <c r="G155" t="n">
-        <v>3.24939560890198</v>
+        <v>3.24939584732056</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.35349988937378</v>
       </c>
       <c r="G158" t="n">
-        <v>3.19602537155151</v>
+        <v>3.19602560997009</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>3.28799414634705</v>
+        <v>3.28799390792847</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.43549990653992</v>
       </c>
       <c r="G161" t="n">
-        <v>3.27417516708374</v>
+        <v>3.27417492866516</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G162" t="n">
-        <v>3.21175026893616</v>
+        <v>3.21175074577332</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.41700005531311</v>
       </c>
       <c r="G163" t="n">
-        <v>3.25654363632202</v>
+        <v>3.25654339790344</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>3.21175026893616</v>
+        <v>3.21175074577332</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>3.21175026893616</v>
+        <v>3.21175074577332</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>3.26893329620361</v>
+        <v>3.26893305778503</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.34517669677734</v>
+        <v>3.34517645835876</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>3.58343744277954</v>
+        <v>3.58343696594238</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G175" t="n">
-        <v>3.55484580993652</v>
+        <v>3.5548460483551</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.75</v>
       </c>
       <c r="G176" t="n">
-        <v>3.57390666007996</v>
+        <v>3.57390642166138</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.75</v>
       </c>
       <c r="G177" t="n">
-        <v>3.57390666007996</v>
+        <v>3.57390642166138</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>3.84075856208801</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G183" t="n">
-        <v>3.5453155040741</v>
+        <v>3.54531526565552</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G185" t="n">
-        <v>3.66921091079712</v>
+        <v>3.66921067237854</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G186" t="n">
-        <v>3.66921091079712</v>
+        <v>3.66921067237854</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G187" t="n">
-        <v>3.71686291694641</v>
+        <v>3.71686267852783</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>3.71686291694641</v>
+        <v>3.71686267852783</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>3.65014934539795</v>
+        <v>3.65014982223511</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G190" t="n">
-        <v>3.79310631752014</v>
+        <v>3.79310655593872</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>3.84075856208801</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G192" t="n">
-        <v>3.84075856208801</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>3.95512342453003</v>
+        <v>3.95512318611145</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4</v>
       </c>
       <c r="G194" t="n">
-        <v>3.81216716766357</v>
+        <v>3.81216669082642</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4</v>
       </c>
       <c r="G195" t="n">
-        <v>3.81216716766357</v>
+        <v>3.81216669082642</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>3.85028862953186</v>
+        <v>3.85028886795044</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83161664009094</v>
+        <v>3.83161687850952</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>3.92740702629089</v>
+        <v>3.92740750312805</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>3.87951231002808</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>3.8890917301178</v>
+        <v>3.88909149169922</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82203817367554</v>
+        <v>3.82203793525696</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G209" t="n">
-        <v>3.69751000404358</v>
+        <v>3.69751048088074</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G210" t="n">
-        <v>3.69751000404358</v>
+        <v>3.69751048088074</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>3.83161664009094</v>
+        <v>3.83161687850952</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>3.87951231002808</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>3.87951231002808</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>3.87951231002808</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>3.87951231002808</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.93698668479919</v>
+        <v>3.93698620796204</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G218" t="n">
-        <v>3.94656491279602</v>
+        <v>3.94656562805176</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>4.03277683258057</v>
+        <v>4.03277635574341</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.21477842330933</v>
+        <v>4.21477890014648</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>4.10940837860107</v>
+        <v>4.10940933227539</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G229" t="n">
-        <v>4.43509721755981</v>
+        <v>4.4350962638855</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>4.38720226287842</v>
+        <v>4.38720178604126</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G231" t="n">
-        <v>4.48299121856689</v>
+        <v>4.48299217224121</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G235" t="n">
-        <v>4.68415212631226</v>
+        <v>4.6841516494751</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G238" t="n">
-        <v>5.00026035308838</v>
+        <v>5.00025987625122</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G241" t="n">
-        <v>4.94278621673584</v>
+        <v>4.94278573989868</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5</v>
       </c>
       <c r="G242" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5</v>
       </c>
       <c r="G243" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5</v>
       </c>
       <c r="G245" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G249" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036285400391</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G250" t="n">
-        <v>4.65541410446167</v>
+        <v>4.65541458129883</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G251" t="n">
-        <v>4.65541410446167</v>
+        <v>4.65541458129883</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036285400391</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036285400391</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5</v>
       </c>
       <c r="G255" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G258" t="n">
-        <v>4.48299121856689</v>
+        <v>4.48299217224121</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>4.59794092178345</v>
+        <v>4.59794044494629</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>4.59794092178345</v>
+        <v>4.59794044494629</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G269" t="n">
-        <v>4.59794092178345</v>
+        <v>4.59794044494629</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>4.76078462600708</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G275" t="n">
-        <v>4.76078462600708</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G276" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036285400391</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>4.6266770362854</v>
+        <v>4.62667751312256</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G278" t="n">
-        <v>4.65541410446167</v>
+        <v>4.65541458129883</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G285" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>4.75120449066162</v>
+        <v>4.75120496749878</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G290" t="n">
-        <v>4.84699535369873</v>
+        <v>4.84699583053589</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G294" t="n">
-        <v>4.76078462600708</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G297" t="n">
-        <v>4.70331001281738</v>
+        <v>4.70330953598022</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G299" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G301" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G302" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G303" t="n">
-        <v>4.74162578582764</v>
+        <v>4.74162626266479</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5</v>
       </c>
       <c r="G304" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>4.84699535369873</v>
+        <v>4.84699583053589</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G309" t="n">
-        <v>4.84699535369873</v>
+        <v>4.84699583053589</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G310" t="n">
-        <v>4.84699535369873</v>
+        <v>4.84699583053589</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5</v>
       </c>
       <c r="G311" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5</v>
       </c>
       <c r="G312" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.76078462600708</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5</v>
       </c>
       <c r="G316" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036285400391</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036285400391</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5</v>
       </c>
       <c r="G322" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5</v>
       </c>
       <c r="G326" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>4.84699535369873</v>
+        <v>4.84699583053589</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5</v>
       </c>
       <c r="G330" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.84699535369873</v>
+        <v>4.84699583053589</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5</v>
       </c>
       <c r="G333" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>4.75120449066162</v>
+        <v>4.75120496749878</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036285400391</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5</v>
       </c>
       <c r="G336" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G339" t="n">
-        <v>4.88531112670898</v>
+        <v>4.88531160354614</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.98110103607178</v>
+        <v>4.98110151290894</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.88531112670898</v>
+        <v>4.88531160354614</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>4.98110103607178</v>
+        <v>4.98110151290894</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G343" t="n">
-        <v>5.00026035308838</v>
+        <v>5.00025987625122</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.1343674659729</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>5.17268323898315</v>
+        <v>5.17268371582031</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.1343674659729</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G351" t="n">
-        <v>5.1343674659729</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G353" t="n">
-        <v>5.09605073928833</v>
+        <v>5.09605026245117</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>5.17268323898315</v>
+        <v>5.17268371582031</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>5.17268323898315</v>
+        <v>5.17268371582031</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G358" t="n">
-        <v>5.17268323898315</v>
+        <v>5.17268371582031</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G359" t="n">
-        <v>5.01941823959351</v>
+        <v>5.01941776275635</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.1343674659729</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G364" t="n">
-        <v>5.15352439880371</v>
+        <v>5.15352535247803</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>5.28763198852539</v>
+        <v>5.28763151168823</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G367" t="n">
-        <v>5.36426401138306</v>
+        <v>5.3642635345459</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G369" t="n">
-        <v>5.53668642044067</v>
+        <v>5.53668689727783</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G370" t="n">
-        <v>5.53668642044067</v>
+        <v>5.53668689727783</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>5.65163564682007</v>
+        <v>5.65163516998291</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G376" t="n">
-        <v>5.91984844207764</v>
+        <v>5.91984796524048</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G379" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G388" t="n">
-        <v>5.97732257843018</v>
+        <v>5.97732210159302</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>5.82405853271484</v>
+        <v>5.82405805587769</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G391" t="n">
-        <v>5.91984844207764</v>
+        <v>5.91984796524048</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>6.07311296463013</v>
+        <v>6.07311344146729</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>6.37964200973511</v>
+        <v>6.37964248657227</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G399" t="n">
-        <v>6.37964200973511</v>
+        <v>6.37964248657227</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>6.32216835021973</v>
+        <v>6.32216787338257</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G401" t="n">
-        <v>6.36048364639282</v>
+        <v>6.36048412322998</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G402" t="n">
-        <v>6.37964200973511</v>
+        <v>6.37964248657227</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G403" t="n">
-        <v>6.45627403259277</v>
+        <v>6.45627450942993</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>6.32216835021973</v>
+        <v>6.32216787338257</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>6.36048364639282</v>
+        <v>6.36048412322998</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>6.4179573059082</v>
+        <v>6.41795778274536</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G412" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G414" t="n">
-        <v>6.07311296463013</v>
+        <v>6.07311344146729</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>5.72826719284058</v>
+        <v>5.72826766967773</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>5.70910930633545</v>
+        <v>5.70910978317261</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>5.70910930633545</v>
+        <v>5.70910978317261</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>5.67079210281372</v>
+        <v>5.6707935333252</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G423" t="n">
-        <v>5.67079210281372</v>
+        <v>5.6707935333252</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G426" t="n">
-        <v>5.97732257843018</v>
+        <v>5.97732210159302</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G427" t="n">
-        <v>5.99648141860962</v>
+        <v>5.9964804649353</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>6.07311296463013</v>
+        <v>6.07311344146729</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>6.03479719161987</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G430" t="n">
-        <v>6.05395555496216</v>
+        <v>6.053955078125</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G431" t="n">
-        <v>6.05395555496216</v>
+        <v>6.053955078125</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G432" t="n">
-        <v>6.1114296913147</v>
+        <v>6.11142921447754</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>6.4179573059082</v>
+        <v>6.41795778274536</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>6.4179573059082</v>
+        <v>6.41795778274536</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G437" t="n">
-        <v>6.62869739532471</v>
+        <v>6.62869787216187</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7</v>
       </c>
       <c r="G438" t="n">
-        <v>6.70532941818237</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>7</v>
       </c>
       <c r="G439" t="n">
-        <v>6.70532941818237</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7</v>
       </c>
       <c r="G441" t="n">
-        <v>6.70532941818237</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>6.68617105484009</v>
+        <v>6.68617153167725</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>7</v>
       </c>
       <c r="G443" t="n">
-        <v>6.70532941818237</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G444" t="n">
-        <v>6.7819619178772</v>
+        <v>6.78196144104004</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>6.99270153045654</v>
+        <v>6.9927020072937</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>7.16512393951416</v>
+        <v>7.165123462677</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G449" t="n">
-        <v>7.79734134674072</v>
+        <v>7.79734039306641</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>8.13305568695068</v>
+        <v>8.13305473327637</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.5</v>
       </c>
       <c r="G454" t="n">
-        <v>8.17151069641113</v>
+        <v>8.1715087890625</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G455" t="n">
-        <v>7.9984655380249</v>
+        <v>7.99846458435059</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.5</v>
       </c>
       <c r="G458" t="n">
-        <v>8.17151069641113</v>
+        <v>8.1715087890625</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>8.13305568695068</v>
+        <v>8.13305473327637</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701543807983</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>7.13324737548828</v>
+        <v>7.13324689865112</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>7.22938251495361</v>
+        <v>7.22938299179077</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G470" t="n">
-        <v>7.24861001968384</v>
+        <v>7.24860954284668</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>7.5</v>
       </c>
       <c r="G471" t="n">
-        <v>7.21015596389771</v>
+        <v>7.21015548706055</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>7.19092845916748</v>
+        <v>7.19092798233032</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.5</v>
       </c>
       <c r="G473" t="n">
-        <v>7.21015596389771</v>
+        <v>7.21015548706055</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G474" t="n">
-        <v>7.07556629180908</v>
+        <v>7.07556581497192</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G475" t="n">
-        <v>7.4985613822937</v>
+        <v>7.49856185913086</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G490" t="n">
-        <v>7.5562424659729</v>
+        <v>7.55624341964722</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G491" t="n">
-        <v>7.46010732650757</v>
+        <v>7.46010780334473</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701543807983</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701543807983</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G497" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701543807983</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G502" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G504" t="n">
-        <v>7.82542276382446</v>
+        <v>7.8254222869873</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G506" t="n">
-        <v>8.15228080749512</v>
+        <v>8.15228271484375</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G508" t="n">
-        <v>8.38300704956055</v>
+        <v>8.38300800323486</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>8.45991516113281</v>
+        <v>8.4599142074585</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9</v>
       </c>
       <c r="G512" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G513" t="n">
-        <v>8.74832344055176</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>9.24822521209717</v>
+        <v>9.2482271194458</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G515" t="n">
-        <v>8.78677654266357</v>
+        <v>8.78677558898926</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>9.5</v>
       </c>
       <c r="G516" t="n">
-        <v>9.13286304473877</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G517" t="n">
-        <v>9.36358737945557</v>
+        <v>9.3635892868042</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>9.5</v>
       </c>
       <c r="G520" t="n">
-        <v>9.13286304473877</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>9.49817848205566</v>
+        <v>9.49817657470703</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G523" t="n">
-        <v>9.4789514541626</v>
+        <v>9.47895240783691</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G525" t="n">
-        <v>9.34436130523682</v>
+        <v>9.34436225891113</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G526" t="n">
-        <v>9.36358737945557</v>
+        <v>9.3635892868042</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G528" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G530" t="n">
-        <v>8.70986843109131</v>
+        <v>8.70986747741699</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G531" t="n">
-        <v>8.94059371948242</v>
+        <v>8.94059276580811</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>8.94059371948242</v>
+        <v>8.94059276580811</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>8.94059371948242</v>
+        <v>8.94059276580811</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G537" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G538" t="n">
-        <v>8.74832344055176</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>8.69064044952393</v>
+        <v>8.69063949584961</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>9</v>
       </c>
       <c r="G540" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G541" t="n">
-        <v>8.63295936584473</v>
+        <v>8.63296031951904</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9</v>
       </c>
       <c r="G542" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>8.61373138427734</v>
+        <v>8.61373233795166</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G546" t="n">
-        <v>8.38300704956055</v>
+        <v>8.38300800323486</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>8.38300704956055</v>
+        <v>8.38300800323486</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>8.45991516113281</v>
+        <v>8.4599142074585</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G549" t="n">
-        <v>8.45991516113281</v>
+        <v>8.4599142074585</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>8.45991516113281</v>
+        <v>8.4599142074585</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.45991516113281</v>
+        <v>8.4599142074585</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G560" t="n">
-        <v>8.59450531005859</v>
+        <v>8.59450435638428</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G561" t="n">
-        <v>8.78677654266357</v>
+        <v>8.78677558898926</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G562" t="n">
-        <v>8.95981884002686</v>
+        <v>8.95981979370117</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G563" t="n">
-        <v>8.90213966369629</v>
+        <v>8.90213871002197</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>8.94059371948242</v>
+        <v>8.94059276580811</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>8.97904682159424</v>
+        <v>8.97904586791992</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G566" t="n">
-        <v>8.95981884002686</v>
+        <v>8.95981979370117</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G569" t="n">
-        <v>9.2866792678833</v>
+        <v>9.28668022155762</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G570" t="n">
-        <v>9.03672790527344</v>
+        <v>9.03672695159912</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G575" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>9</v>
       </c>
       <c r="G576" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G577" t="n">
-        <v>8.78677654266357</v>
+        <v>8.78677558898926</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G578" t="n">
-        <v>8.97904682159424</v>
+        <v>8.97904586791992</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G579" t="n">
-        <v>8.90213966369629</v>
+        <v>8.90213871002197</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G581" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G582" t="n">
-        <v>8.70986843109131</v>
+        <v>8.70986747741699</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>8.72909450531006</v>
+        <v>8.72909545898438</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9</v>
       </c>
       <c r="G584" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.69064044952393</v>
+        <v>8.69063949584961</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>8.74832344055176</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G587" t="n">
-        <v>8.70986843109131</v>
+        <v>8.70986747741699</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G588" t="n">
-        <v>8.70986843109131</v>
+        <v>8.70986747741699</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G589" t="n">
-        <v>8.67141437530518</v>
+        <v>8.67141342163086</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>9</v>
       </c>
       <c r="G590" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>9</v>
       </c>
       <c r="G591" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G592" t="n">
-        <v>8.59450531005859</v>
+        <v>8.59450435638428</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9</v>
       </c>
       <c r="G593" t="n">
-        <v>8.65218734741211</v>
+        <v>8.65218639373779</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G595" t="n">
-        <v>8.78677654266357</v>
+        <v>8.78677558898926</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>8.76754760742188</v>
+        <v>8.76754856109619</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G597" t="n">
-        <v>9.1136360168457</v>
+        <v>9.11363697052002</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>9.5</v>
       </c>
       <c r="G599" t="n">
-        <v>9.13286304473877</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G600" t="n">
-        <v>9.34436130523682</v>
+        <v>9.34436225891113</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G601" t="n">
-        <v>9.15209197998047</v>
+        <v>9.15209102630615</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G604" t="n">
-        <v>9.26745319366455</v>
+        <v>9.26745223999023</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G605" t="n">
-        <v>9.36358737945557</v>
+        <v>9.3635892868042</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G609" t="n">
-        <v>9.1136360168457</v>
+        <v>9.11363697052002</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G610" t="n">
-        <v>9.1136360168457</v>
+        <v>9.11363697052002</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9.5</v>
       </c>
       <c r="G611" t="n">
-        <v>9.13286304473877</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G612" t="n">
-        <v>9.1713171005249</v>
+        <v>9.17131805419922</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G613" t="n">
-        <v>9.15209197998047</v>
+        <v>9.15209102630615</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G617" t="n">
-        <v>9.15209197998047</v>
+        <v>9.15209102630615</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.13286304473877</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>9.1713171005249</v>
+        <v>9.17131805419922</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G623" t="n">
-        <v>9.44049549102783</v>
+        <v>9.44049644470215</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>9.7577428817749</v>
+        <v>9.75774383544922</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>10.5</v>
       </c>
       <c r="G627" t="n">
-        <v>10.0942182540894</v>
+        <v>10.094217300415</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G628" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864894866943</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864894866943</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G630" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864894866943</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>10.1422863006592</v>
+        <v>10.1422853469849</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G632" t="n">
-        <v>10.1422863006592</v>
+        <v>10.1422853469849</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>10.5</v>
       </c>
       <c r="G633" t="n">
-        <v>10.0942182540894</v>
+        <v>10.094217300415</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>9.95001411437988</v>
+        <v>9.9500150680542</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>10.5</v>
       </c>
       <c r="G635" t="n">
-        <v>10.0942182540894</v>
+        <v>10.094217300415</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G636" t="n">
-        <v>10.0461492538452</v>
+        <v>10.0461483001709</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>10.5</v>
       </c>
       <c r="G637" t="n">
-        <v>10.0942182540894</v>
+        <v>10.094217300415</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864894866943</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>10.4787588119507</v>
+        <v>10.478759765625</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>10.4787588119507</v>
+        <v>10.478759765625</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>10.67103099823</v>
+        <v>10.6710300445557</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>10.67103099823</v>
+        <v>10.6710300445557</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>11.5</v>
       </c>
       <c r="G651" t="n">
-        <v>11.0555725097656</v>
+        <v>11.0555734634399</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>11.5</v>
       </c>
       <c r="G652" t="n">
-        <v>11.0555725097656</v>
+        <v>11.0555734634399</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8246545791626</v>
+        <v>11.8246536254883</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>12.5</v>
       </c>
       <c r="G655" t="n">
-        <v>12.0169267654419</v>
+        <v>12.0169258117676</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>12.3053331375122</v>
+        <v>12.3053312301636</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G658" t="n">
-        <v>12.5937395095825</v>
+        <v>12.5937376022339</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>12.930212020874</v>
+        <v>12.9302110671997</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G660" t="n">
-        <v>12.834077835083</v>
+        <v>12.8340759277344</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>12.5937395095825</v>
+        <v>12.5937376022339</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>12.1130628585815</v>
+        <v>12.1130609512329</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G663" t="n">
-        <v>12.7860097885132</v>
+        <v>12.7860088348389</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>12.7860097885132</v>
+        <v>12.7860088348389</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>12.7860097885132</v>
+        <v>12.7860088348389</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>12.834077835083</v>
+        <v>12.8340759277344</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>12.7860097885132</v>
+        <v>12.7860088348389</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>12.5937395095825</v>
+        <v>12.5937376022339</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G673" t="n">
-        <v>13.0263471603394</v>
+        <v>13.0263481140137</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G674" t="n">
-        <v>13.5070247650146</v>
+        <v>13.507022857666</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>13.8915672302246</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>13.5070247650146</v>
+        <v>13.507022857666</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>13.8915672302246</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>14.1319046020508</v>
+        <v>14.1319065093994</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G685" t="n">
-        <v>14.1319046020508</v>
+        <v>14.1319065093994</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>13.8915672302246</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>13.8915672302246</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>13.8915672302246</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>14.25</v>
       </c>
       <c r="G695" t="n">
-        <v>13.6992959976196</v>
+        <v>13.6992950439453</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G698" t="n">
-        <v>13.5550937652588</v>
+        <v>13.5550928115845</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>13.60315990448</v>
+        <v>13.6031608581543</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>13.7473640441895</v>
+        <v>13.7473630905151</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G701" t="n">
-        <v>13.7473640441895</v>
+        <v>13.7473630905151</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G709" t="n">
-        <v>15.1343002319336</v>
+        <v>15.1343011856079</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G710" t="n">
-        <v>15.8090782165527</v>
+        <v>15.8090801239014</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>15.8090782165527</v>
+        <v>15.8090801239014</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>15.9536733627319</v>
+        <v>15.9536714553833</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>16.8212471008301</v>
+        <v>16.8212490081787</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>16.4838581085205</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>17</v>
       </c>
       <c r="G725" t="n">
-        <v>16.3874588012695</v>
+        <v>16.3874568939209</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>16.5</v>
       </c>
       <c r="G726" t="n">
-        <v>15.9054765701294</v>
+        <v>15.9054746627808</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>16.0500717163086</v>
+        <v>16.05006980896</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>16.4838581085205</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>16.4838581085205</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>16.1946678161621</v>
+        <v>16.1946659088135</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>16.0982685089111</v>
+        <v>16.0982723236084</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>16.1946678161621</v>
+        <v>16.1946659088135</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>16.2428646087646</v>
+        <v>16.2428665161133</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>16.75</v>
       </c>
       <c r="G738" t="n">
-        <v>16.1464691162109</v>
+        <v>16.1464672088623</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>16.0982685089111</v>
+        <v>16.0982723236084</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>15.5198879241943</v>
+        <v>15.5198888778687</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>15.8090782165527</v>
+        <v>15.8090801239014</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G748" t="n">
-        <v>14.8933095932007</v>
+        <v>14.8933086395264</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G750" t="n">
-        <v>14.8933095932007</v>
+        <v>14.8933086395264</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>16.25</v>
       </c>
       <c r="G757" t="n">
-        <v>15.6644840240479</v>
+        <v>15.6644849777222</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G758" t="n">
-        <v>15.8572778701782</v>
+        <v>15.8572788238525</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>15.7126808166504</v>
+        <v>15.7126817703247</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162853240967</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>16.25</v>
       </c>
       <c r="G762" t="n">
-        <v>15.6644840240479</v>
+        <v>15.6644849777222</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>15.5198879241943</v>
+        <v>15.5198888778687</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G764" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162853240967</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>15.8090782165527</v>
+        <v>15.8090801239014</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162853240967</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>16</v>
       </c>
       <c r="G767" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>16</v>
       </c>
       <c r="G768" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G769" t="n">
-        <v>15.5680866241455</v>
+        <v>15.5680875778198</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>17.3032321929932</v>
+        <v>17.3032302856445</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>17.1586322784424</v>
+        <v>17.158634185791</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G778" t="n">
-        <v>16.8212471008301</v>
+        <v>16.8212490081787</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G782" t="n">
-        <v>16.7730484008789</v>
+        <v>16.7730464935303</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>16.5320529937744</v>
+        <v>16.532054901123</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G785" t="n">
-        <v>16.4838581085205</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G788" t="n">
-        <v>17.2550296783447</v>
+        <v>17.2550315856934</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>17.2550296783447</v>
+        <v>17.2550315856934</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>17.3032321929932</v>
+        <v>17.3032302856445</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G792" t="n">
-        <v>17.3032321929932</v>
+        <v>17.3032302856445</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>17.1586322784424</v>
+        <v>17.158634185791</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>17.3032321929932</v>
+        <v>17.3032302856445</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G796" t="n">
-        <v>17.2550296783447</v>
+        <v>17.2550315856934</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>17.3032321929932</v>
+        <v>17.3032302856445</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>18.700984954834</v>
+        <v>18.7009830474854</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G811" t="n">
-        <v>18.4117946624756</v>
+        <v>18.4117965698242</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1708011627197</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>18.2189979553223</v>
+        <v>18.2189998626709</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1708011627197</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>17.978006362915</v>
+        <v>17.9780082702637</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1708011627197</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1708011627197</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1708011627197</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G833" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>17.496021270752</v>
+        <v>17.4960231781006</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G852" t="n">
-        <v>17.5442237854004</v>
+        <v>17.5442218780518</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G853" t="n">
-        <v>17.978006362915</v>
+        <v>17.9780082702637</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>17.3032321929932</v>
+        <v>17.3032302856445</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G866" t="n">
-        <v>17.496021270752</v>
+        <v>17.4960231781006</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G867" t="n">
-        <v>17.5442237854004</v>
+        <v>17.5442218780518</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>17.978006362915</v>
+        <v>17.9780082702637</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G874" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2671966552734</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G878" t="n">
-        <v>18.2189979553223</v>
+        <v>18.2189998626709</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>19.1829681396484</v>
+        <v>19.1829662322998</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>18.8455772399902</v>
+        <v>18.8455791473389</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>18.4599914550781</v>
+        <v>18.4599933624268</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G886" t="n">
-        <v>18.8455772399902</v>
+        <v>18.8455791473389</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G887" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>17.496021270752</v>
+        <v>17.4960231781006</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G897" t="n">
-        <v>17.496021270752</v>
+        <v>17.4960231781006</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>17.3032321929932</v>
+        <v>17.3032302856445</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>17.5442237854004</v>
+        <v>17.5442218780518</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>17.2550296783447</v>
+        <v>17.2550315856934</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>17.2550296783447</v>
+        <v>17.2550315856934</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>16.8212471008301</v>
+        <v>16.8212490081787</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>16.5</v>
       </c>
       <c r="G913" t="n">
-        <v>15.9054765701294</v>
+        <v>15.9054746627808</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>16</v>
       </c>
       <c r="G914" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>16</v>
       </c>
       <c r="G916" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>14.6523170471191</v>
+        <v>14.6523160934448</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>15.25</v>
       </c>
       <c r="G921" t="n">
-        <v>14.700514793396</v>
+        <v>14.7005157470703</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>14.266731262207</v>
+        <v>14.2667303085327</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>13.9293394088745</v>
+        <v>13.9293403625488</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G924" t="n">
-        <v>12.9653730392456</v>
+        <v>12.9653720855713</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>14.1221342086792</v>
+        <v>14.1221351623535</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>15.5198879241943</v>
+        <v>15.5198888778687</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>15.7126808166504</v>
+        <v>15.7126817703247</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>16.0018730163574</v>
+        <v>16.0018711090088</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>16.5</v>
       </c>
       <c r="G929" t="n">
-        <v>15.9054765701294</v>
+        <v>15.9054746627808</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>16</v>
       </c>
       <c r="G930" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>16.1946678161621</v>
+        <v>16.1946659088135</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>15.7126808166504</v>
+        <v>15.7126817703247</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>15.1343002319336</v>
+        <v>15.1343011856079</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>14.6523170471191</v>
+        <v>14.6523160934448</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>15</v>
       </c>
       <c r="G950" t="n">
-        <v>14.4595241546631</v>
+        <v>14.4595232009888</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15</v>
       </c>
       <c r="G955" t="n">
-        <v>14.4595241546631</v>
+        <v>14.4595232009888</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>14.266731262207</v>
+        <v>14.2667303085327</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>14.5</v>
       </c>
       <c r="G959" t="n">
-        <v>13.9775400161743</v>
+        <v>13.9775390625</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G960" t="n">
-        <v>13.6401500701904</v>
+        <v>13.6401510238647</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>13.6883487701416</v>
+        <v>13.6883497238159</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G963" t="n">
-        <v>13.2624025344849</v>
+        <v>13.2624034881592</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>14</v>
       </c>
       <c r="G970" t="n">
-        <v>13.5528221130371</v>
+        <v>13.5528211593628</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G972" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>14.6176862716675</v>
+        <v>14.6176853179932</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>14.75</v>
       </c>
       <c r="G976" t="n">
-        <v>14.2788648605347</v>
+        <v>14.278865814209</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G979" t="n">
-        <v>13.1171960830688</v>
+        <v>13.1171951293945</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G980" t="n">
-        <v>13.6012239456177</v>
+        <v>13.6012229919434</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G981" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G983" t="n">
-        <v>15.2953262329102</v>
+        <v>15.2953271865845</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>15.4405345916748</v>
+        <v>15.4405355453491</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G986" t="n">
-        <v>15.3921318054199</v>
+        <v>15.3921327590942</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G987" t="n">
-        <v>15.343729019165</v>
+        <v>15.3437299728394</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G988" t="n">
-        <v>15.1501188278198</v>
+        <v>15.1501178741455</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>15.0533123016357</v>
+        <v>15.0533132553101</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>14.75</v>
       </c>
       <c r="G994" t="n">
-        <v>14.2788648605347</v>
+        <v>14.278865814209</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>13.9884481430054</v>
+        <v>13.9884471893311</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>14</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.5528221130371</v>
+        <v>13.5528211593628</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1005" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1011" t="n">
-        <v>13.3592090606689</v>
+        <v>13.3592100143433</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.0203886032104</v>
+        <v>13.0203876495361</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1019" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>12.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.100733757019</v>
+        <v>12.1007328033447</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1021" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1024" t="n">
-        <v>12.2459411621094</v>
+        <v>12.2459421157837</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.7783737182617</v>
+        <v>12.778374671936</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1028" t="n">
-        <v>13.4560146331787</v>
+        <v>13.456015586853</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1029" t="n">
-        <v>13.6012239456177</v>
+        <v>13.6012229919434</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1032" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>14.7144918441772</v>
+        <v>14.7144908905029</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>14.3756713867188</v>
+        <v>14.3756704330444</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1036" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>14.75</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.2788648605347</v>
+        <v>14.278865814209</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1040" t="n">
-        <v>14.6176862716675</v>
+        <v>14.6176853179932</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>14.75</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.2788648605347</v>
+        <v>14.278865814209</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1045" t="n">
-        <v>13.8916416168213</v>
+        <v>13.8916425704956</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1058" t="n">
-        <v>13.6012239456177</v>
+        <v>13.6012229919434</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1059" t="n">
-        <v>13.6012239456177</v>
+        <v>13.6012229919434</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1060" t="n">
-        <v>13.2624025344849</v>
+        <v>13.2624034881592</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1061" t="n">
-        <v>13.3592090606689</v>
+        <v>13.3592100143433</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>13.5</v>
       </c>
       <c r="G1062" t="n">
-        <v>13.0687913894653</v>
+        <v>13.0687923431396</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>13.5</v>
       </c>
       <c r="G1063" t="n">
-        <v>13.0687913894653</v>
+        <v>13.0687923431396</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1064" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1066" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>12.2459411621094</v>
+        <v>12.2459421157837</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1069" t="n">
-        <v>11.9071216583252</v>
+        <v>11.9071207046509</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1070" t="n">
-        <v>11.7135105133057</v>
+        <v>11.7135095596313</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1072" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>12.1975393295288</v>
+        <v>12.1975383758545</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1075" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1076" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1078" t="n">
-        <v>12.5363597869873</v>
+        <v>12.5363607406616</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1081" t="n">
-        <v>12.7299718856812</v>
+        <v>12.7299709320068</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1082" t="n">
-        <v>12.7299718856812</v>
+        <v>12.7299709320068</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>12.7783737182617</v>
+        <v>12.778374671936</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1090" t="n">
-        <v>12.7783737182617</v>
+        <v>12.778374671936</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>12.5363597869873</v>
+        <v>12.5363607406616</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>12.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>12.75</v>
       </c>
       <c r="G1095" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1096" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1097" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>12.75</v>
       </c>
       <c r="G1100" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>12.75</v>
       </c>
       <c r="G1101" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1102" t="n">
-        <v>12.5363597869873</v>
+        <v>12.5363607406616</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>12.75</v>
       </c>
       <c r="G1104" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1105" t="n">
-        <v>12.2459411621094</v>
+        <v>12.2459421157837</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1106" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>12.75</v>
       </c>
       <c r="G1107" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>12.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1114" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1118" t="n">
-        <v>12.5363597869873</v>
+        <v>12.5363607406616</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>12.5363597869873</v>
+        <v>12.5363607406616</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1120" t="n">
-        <v>12.7783737182617</v>
+        <v>12.778374671936</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1123" t="n">
-        <v>13.0203886032104</v>
+        <v>13.0203876495361</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>13.5</v>
       </c>
       <c r="G1125" t="n">
-        <v>13.0687913894653</v>
+        <v>13.0687923431396</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>13.0203886032104</v>
+        <v>13.0203876495361</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>13.2140007019043</v>
+        <v>13.21399974823</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1131" t="n">
-        <v>13.4560146331787</v>
+        <v>13.456015586853</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>13.4560146331787</v>
+        <v>13.456015586853</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1134" t="n">
-        <v>13.9884481430054</v>
+        <v>13.9884471893311</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>14</v>
       </c>
       <c r="G1137" t="n">
-        <v>13.5528221130371</v>
+        <v>13.5528211593628</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1138" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1141" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1148" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>14.75</v>
       </c>
       <c r="G1151" t="n">
-        <v>14.2788648605347</v>
+        <v>14.278865814209</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1154" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1156" t="n">
-        <v>13.9884481430054</v>
+        <v>13.9884471893311</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1157" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1159" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1162" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1164" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>13.8916416168213</v>
+        <v>13.8916425704956</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>13.8916416168213</v>
+        <v>13.8916425704956</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1172" t="n">
-        <v>13.4560146331787</v>
+        <v>13.456015586853</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1177" t="n">
-        <v>13.3592090606689</v>
+        <v>13.3592100143433</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>13.5</v>
       </c>
       <c r="G1178" t="n">
-        <v>13.0687913894653</v>
+        <v>13.0687923431396</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1183" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1185" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1186" t="n">
-        <v>12.7783737182617</v>
+        <v>12.778374671936</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>12.75</v>
       </c>
       <c r="G1190" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1193" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1194" t="n">
-        <v>13.0203886032104</v>
+        <v>13.0203876495361</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>12.7783737182617</v>
+        <v>12.778374671936</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1197" t="n">
-        <v>12.7783737182617</v>
+        <v>12.778374671936</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>13.2624025344849</v>
+        <v>13.2624034881592</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1207" t="n">
-        <v>12.1975393295288</v>
+        <v>12.1975383758545</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.2459411621094</v>
+        <v>12.2459421157837</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1215" t="n">
-        <v>12.6815690994263</v>
+        <v>12.681568145752</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1217" t="n">
-        <v>13.0203886032104</v>
+        <v>13.0203876495361</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>12.7299718856812</v>
+        <v>12.7299709320068</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>12.75</v>
       </c>
       <c r="G1224" t="n">
-        <v>12.4106178283691</v>
+        <v>12.4106187820435</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1225" t="n">
-        <v>12.3619480133057</v>
+        <v>12.36194896698</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1227" t="n">
-        <v>12.264612197876</v>
+        <v>12.2646112442017</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>12.5</v>
       </c>
       <c r="G1229" t="n">
-        <v>12.167272567749</v>
+        <v>12.1672716140747</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>12.264612197876</v>
+        <v>12.2646112442017</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.9725971221924</v>
+        <v>11.9725961685181</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1235" t="n">
-        <v>11.7779207229614</v>
+        <v>11.7779197692871</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1236" t="n">
-        <v>11.7779207229614</v>
+        <v>11.7779197692871</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>12</v>
       </c>
       <c r="G1237" t="n">
-        <v>11.6805820465088</v>
+        <v>11.6805810928345</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>12</v>
       </c>
       <c r="G1238" t="n">
-        <v>11.6805820465088</v>
+        <v>11.6805810928345</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1239" t="n">
-        <v>11.826587677002</v>
+        <v>11.8265886306763</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>12</v>
       </c>
       <c r="G1240" t="n">
-        <v>11.6805820465088</v>
+        <v>11.6805810928345</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1245" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1246" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1247" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1250" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1253" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1259" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1266" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1268" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>11.5</v>
       </c>
       <c r="G1274" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>11.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1281" t="n">
-        <v>10.8532056808472</v>
+        <v>10.8532066345215</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1283" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>11.5</v>
       </c>
       <c r="G1285" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>11.5</v>
       </c>
       <c r="G1286" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>11.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1289" t="n">
-        <v>10.8532056808472</v>
+        <v>10.8532066345215</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1292" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>11.5</v>
       </c>
       <c r="G1296" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1298" t="n">
-        <v>10.8532056808472</v>
+        <v>10.8532066345215</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1300" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1304" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>11.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1314" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1317" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1322" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>10.3178472518921</v>
+        <v>10.3178482055664</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>9.7824878692627</v>
+        <v>9.78248691558838</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>10.5</v>
       </c>
       <c r="G1334" t="n">
-        <v>10.2205095291138</v>
+        <v>10.2205085754395</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1335" t="n">
-        <v>9.7824878692627</v>
+        <v>9.78248691558838</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1336" t="n">
-        <v>10.1718397140503</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1337" t="n">
-        <v>10.1718397140503</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1350" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1351" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1358" t="n">
-        <v>9.55860900878906</v>
+        <v>9.55860996246338</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1360" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1361" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1364" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1365" t="n">
-        <v>9.40286731719971</v>
+        <v>9.40286827087402</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1366" t="n">
-        <v>9.28606128692627</v>
+        <v>9.28606224060059</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G1368" t="n">
-        <v>9.28606128692627</v>
+        <v>9.28606224060059</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1375" t="n">
-        <v>10.4151849746704</v>
+        <v>10.4151859283447</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1376" t="n">
-        <v>10.6098613739014</v>
+        <v>10.6098623275757</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1378" t="n">
-        <v>10.6098613739014</v>
+        <v>10.6098623275757</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1379" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1380" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1383" t="n">
-        <v>10.3178472518921</v>
+        <v>10.3178482055664</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>10.6098613739014</v>
+        <v>10.6098623275757</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1394" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1396" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1397" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1400" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1406" t="n">
-        <v>10.7558698654175</v>
+        <v>10.7558689117432</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>10.3178472518921</v>
+        <v>10.3178482055664</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1426" t="n">
-        <v>9.7824878692627</v>
+        <v>9.78248691558838</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1432" t="n">
-        <v>10.1718397140503</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1433" t="n">
-        <v>10.1718397140503</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1438" t="n">
-        <v>9.36393260955811</v>
+        <v>9.36393356323242</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1451" t="n">
-        <v>10.1718397140503</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1459" t="n">
-        <v>9.55860900878906</v>
+        <v>9.55860996246338</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1461" t="n">
-        <v>9.22765827178955</v>
+        <v>9.22765922546387</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1462" t="n">
-        <v>9.55860900878906</v>
+        <v>9.55860996246338</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1464" t="n">
-        <v>9.59754371643066</v>
+        <v>9.59754467010498</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1467" t="n">
-        <v>9.18872451782227</v>
+        <v>9.18872356414795</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1470" t="n">
-        <v>9.20819282531738</v>
+        <v>9.20819187164307</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1474" t="n">
-        <v>9.05245113372803</v>
+        <v>9.05245018005371</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -54816,6 +54816,32 @@
         <v>8.89999961853027</v>
       </c>
       <c r="H2094" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2095" t="n">
+        <v>752</v>
+      </c>
+      <c r="C2095" t="n">
+        <v>8.84000015258789</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>8.73999977111816</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>8.73999977111816</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>8.84000015258789</v>
+      </c>
+      <c r="G2095" t="n">
+        <v>8.84000015258789</v>
+      </c>
+      <c r="H2095" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.87050008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>2.73570609092712</v>
+        <v>2.7357063293457</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.9614999294281</v>
       </c>
       <c r="G11" t="n">
-        <v>2.82243275642395</v>
+        <v>2.82243299484253</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G12" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78764700889587</v>
+        <v>2.78764724731445</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>2.71616911888123</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G22" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G26" t="n">
-        <v>2.71616911888123</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.71616911888123</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.71616911888123</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G29" t="n">
-        <v>2.61895871162415</v>
+        <v>2.61895847320557</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.75</v>
       </c>
       <c r="G30" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.75</v>
       </c>
       <c r="G31" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.75</v>
       </c>
       <c r="G32" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.75</v>
       </c>
       <c r="G33" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.75</v>
       </c>
       <c r="G34" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G35" t="n">
-        <v>2.67232894897461</v>
+        <v>2.67232847213745</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G38" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.79241251945496</v>
+        <v>2.79241275787354</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87818598747253</v>
+        <v>2.87818622589111</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.02049994468689</v>
       </c>
       <c r="G48" t="n">
-        <v>2.87866258621216</v>
+        <v>2.87866234779358</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.05550003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>2.9120192527771</v>
+        <v>2.91201901435852</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01161217689514</v>
+        <v>3.01161193847656</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.00208115577698</v>
+        <v>3.00208210945129</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G54" t="n">
-        <v>2.96395969390869</v>
+        <v>2.96395993232727</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>3.00208115577698</v>
+        <v>3.00208210945129</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>2.91630792617798</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G58" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>2.97349047660828</v>
+        <v>2.97348999977112</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G60" t="n">
-        <v>2.97349047660828</v>
+        <v>2.97348999977112</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G63" t="n">
-        <v>2.88771677017212</v>
+        <v>2.88771653175354</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>2.87818598747253</v>
+        <v>2.87818622589111</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.89100003242493</v>
       </c>
       <c r="G78" t="n">
-        <v>2.75524353981018</v>
+        <v>2.75524377822876</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.90549993515015</v>
       </c>
       <c r="G80" t="n">
-        <v>2.76906323432922</v>
+        <v>2.76906299591064</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>2.77335166931152</v>
+        <v>2.77335143089294</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G83" t="n">
-        <v>2.88771677017212</v>
+        <v>2.88771653175354</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>2.91630792617798</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.04900002479553</v>
       </c>
       <c r="G88" t="n">
-        <v>2.9058244228363</v>
+        <v>2.90582418441772</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G89" t="n">
-        <v>2.85054802894592</v>
+        <v>2.85054779052734</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G90" t="n">
-        <v>2.85054802894592</v>
+        <v>2.85054779052734</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G91" t="n">
-        <v>2.85054802894592</v>
+        <v>2.85054779052734</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G96" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G97" t="n">
-        <v>2.83815813064575</v>
+        <v>2.83815836906433</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G98" t="n">
-        <v>2.83815813064575</v>
+        <v>2.83815836906433</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G101" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.98850011825562</v>
       </c>
       <c r="G105" t="n">
-        <v>2.84816527366638</v>
+        <v>2.84816551208496</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G107" t="n">
-        <v>2.76382112503052</v>
+        <v>2.7638213634491</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G109" t="n">
-        <v>2.72045803070068</v>
+        <v>2.72045755386353</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G110" t="n">
-        <v>2.72045803070068</v>
+        <v>2.72045755386353</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.05949997901917</v>
       </c>
       <c r="G113" t="n">
-        <v>2.91583132743835</v>
+        <v>2.91583156585693</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.05949997901917</v>
       </c>
       <c r="G114" t="n">
-        <v>2.91583132743835</v>
+        <v>2.91583156585693</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G115" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.92549991607666</v>
       </c>
       <c r="G117" t="n">
-        <v>2.7881236076355</v>
+        <v>2.78812384605408</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G119" t="n">
-        <v>2.85436034202576</v>
+        <v>2.85436010360718</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.95149993896484</v>
       </c>
       <c r="G122" t="n">
-        <v>2.81290292739868</v>
+        <v>2.8129026889801</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G126" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.92249989509583</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78526449203491</v>
+        <v>2.78526473045349</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G138" t="n">
-        <v>2.79241251945496</v>
+        <v>2.79241275787354</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G140" t="n">
-        <v>2.87818598747253</v>
+        <v>2.87818622589111</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.00650000572205</v>
       </c>
       <c r="G145" t="n">
-        <v>2.8653199672699</v>
+        <v>2.86532020568848</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>2.90201234817505</v>
+        <v>2.90201210975647</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.00650000572205</v>
       </c>
       <c r="G147" t="n">
-        <v>2.8653199672699</v>
+        <v>2.86532020568848</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>2.91630792617798</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.24049997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>3.08833193778992</v>
+        <v>3.08833169937134</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>3.05926394462585</v>
+        <v>3.05926370620728</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.27649998664856</v>
       </c>
       <c r="G152" t="n">
-        <v>3.12264108657837</v>
+        <v>3.12264132499695</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.32949995994568</v>
       </c>
       <c r="G153" t="n">
-        <v>3.17315268516541</v>
+        <v>3.17315220832825</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G154" t="n">
-        <v>3.24987268447876</v>
+        <v>3.24987244606018</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G156" t="n">
-        <v>3.22890543937683</v>
+        <v>3.22890567779541</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>3.28799390792847</v>
+        <v>3.28799414634705</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>3.24034214019775</v>
+        <v>3.24034190177917</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.43549990653992</v>
       </c>
       <c r="G161" t="n">
-        <v>3.27417492866516</v>
+        <v>3.27417469024658</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G162" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175050735474</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.41700005531311</v>
       </c>
       <c r="G163" t="n">
-        <v>3.25654339790344</v>
+        <v>3.25654411315918</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175050735474</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175050735474</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>3.26893305778503</v>
+        <v>3.26893329620361</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>3.31658530235291</v>
+        <v>3.31658554077148</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>3.31658530235291</v>
+        <v>3.31658554077148</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>3.59450006484985</v>
       </c>
       <c r="G171" t="n">
-        <v>3.42570877075195</v>
+        <v>3.42570853233337</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G172" t="n">
-        <v>3.50242853164673</v>
+        <v>3.50242829322815</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.47860264778137</v>
+        <v>3.47860240936279</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G175" t="n">
-        <v>3.5548460483551</v>
+        <v>3.55484580993652</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G178" t="n">
-        <v>3.76451516151428</v>
+        <v>3.7645149230957</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>3.84075832366943</v>
+        <v>3.84075880050659</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G182" t="n">
-        <v>3.62155866622925</v>
+        <v>3.62155890464783</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>3.62155866622925</v>
+        <v>3.62155890464783</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G187" t="n">
-        <v>3.71686267852783</v>
+        <v>3.71686315536499</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>3.71686267852783</v>
+        <v>3.71686315536499</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>3.65014982223511</v>
+        <v>3.65015006065369</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G190" t="n">
-        <v>3.79310655593872</v>
+        <v>3.79310607910156</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>3.84075832366943</v>
+        <v>3.84075880050659</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G192" t="n">
-        <v>3.84075832366943</v>
+        <v>3.84075880050659</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>3.95512318611145</v>
+        <v>3.95512366294861</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4</v>
       </c>
       <c r="G194" t="n">
-        <v>3.81216669082642</v>
+        <v>3.81216716766357</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4</v>
       </c>
       <c r="G195" t="n">
-        <v>3.81216669082642</v>
+        <v>3.81216716766357</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G200" t="n">
-        <v>3.77414298057556</v>
+        <v>3.77414274215698</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83161687850952</v>
+        <v>3.8316171169281</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>3.92740750312805</v>
+        <v>3.92740726470947</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>3.88909149169922</v>
+        <v>3.8890917301178</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82203793525696</v>
+        <v>3.82203769683838</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G206" t="n">
-        <v>3.80287981033325</v>
+        <v>3.80288028717041</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>3.77414298057556</v>
+        <v>3.77414274215698</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>3.7070894241333</v>
+        <v>3.70708918571472</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G209" t="n">
-        <v>3.69751048088074</v>
+        <v>3.69751024246216</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G210" t="n">
-        <v>3.69751048088074</v>
+        <v>3.69751024246216</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>3.83161687850952</v>
+        <v>3.8316171169281</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>3.78372168540955</v>
+        <v>3.78372144699097</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.93698620796204</v>
+        <v>3.93698644638062</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G218" t="n">
-        <v>3.94656562805176</v>
+        <v>3.94656586647034</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>4.02319765090942</v>
+        <v>4.02319717407227</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>4.03277635574341</v>
+        <v>4.03277730941772</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>4.10940933227539</v>
+        <v>4.10940885543823</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G223" t="n">
-        <v>4.1477255821228</v>
+        <v>4.14772605895996</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G224" t="n">
-        <v>4.1956205368042</v>
+        <v>4.19562005996704</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G225" t="n">
-        <v>4.39678049087524</v>
+        <v>4.3967809677124</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G231" t="n">
-        <v>4.48299217224121</v>
+        <v>4.48299169540405</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>4.69373035430908</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>4.66499328613281</v>
+        <v>4.66499280929565</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G238" t="n">
-        <v>5.00025987625122</v>
+        <v>5.00026035308838</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>4.80867910385132</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5</v>
       </c>
       <c r="G242" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5</v>
       </c>
       <c r="G243" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5</v>
       </c>
       <c r="G245" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>4.71288871765137</v>
+        <v>4.71288967132568</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>4.71288871765137</v>
+        <v>4.71288967132568</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G248" t="n">
-        <v>4.71288871765137</v>
+        <v>4.71288967132568</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G249" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G250" t="n">
-        <v>4.65541458129883</v>
+        <v>4.65541410446167</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G251" t="n">
-        <v>4.65541458129883</v>
+        <v>4.65541410446167</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5</v>
       </c>
       <c r="G255" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G258" t="n">
-        <v>4.48299217224121</v>
+        <v>4.48299169540405</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>4.63625621795654</v>
+        <v>4.6362566947937</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G260" t="n">
-        <v>4.66499328613281</v>
+        <v>4.66499280929565</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>4.66499328613281</v>
+        <v>4.66499280929565</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>4.64583587646484</v>
+        <v>4.64583539962769</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G264" t="n">
-        <v>4.69373035430908</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G265" t="n">
-        <v>4.69373035430908</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>4.69373035430908</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>4.57878255844116</v>
+        <v>4.57878160476685</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078414916992</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G275" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078414916992</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G276" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>4.62667751312256</v>
+        <v>4.62667798995972</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G278" t="n">
-        <v>4.65541458129883</v>
+        <v>4.65541410446167</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>4.71288871765137</v>
+        <v>4.71288967132568</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.64583587646484</v>
+        <v>4.64583539962769</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>4.64583587646484</v>
+        <v>4.64583539962769</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162530899048</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G285" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162530899048</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162530899048</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162530899048</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G289" t="n">
-        <v>4.80867910385132</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G290" t="n">
-        <v>4.84699583053589</v>
+        <v>4.84699535369873</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>4.80867910385132</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>4.80867910385132</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>4.69373035430908</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G294" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078414916992</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G297" t="n">
-        <v>4.70330953598022</v>
+        <v>4.70331001281738</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>4.69373035430908</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G299" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162530899048</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>4.69373035430908</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G301" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162530899048</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G302" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162530899048</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G303" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162530899048</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5</v>
       </c>
       <c r="G304" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G306" t="n">
-        <v>4.69373035430908</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>4.84699583053589</v>
+        <v>4.84699535369873</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>4.80867910385132</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G309" t="n">
-        <v>4.84699583053589</v>
+        <v>4.84699535369873</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G310" t="n">
-        <v>4.84699583053589</v>
+        <v>4.84699535369873</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5</v>
       </c>
       <c r="G311" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5</v>
       </c>
       <c r="G312" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078414916992</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5</v>
       </c>
       <c r="G316" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>4.69373035430908</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5</v>
       </c>
       <c r="G322" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>4.80867910385132</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5</v>
       </c>
       <c r="G326" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>4.84699583053589</v>
+        <v>4.84699535369873</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5</v>
       </c>
       <c r="G330" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.84699583053589</v>
+        <v>4.84699535369873</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5</v>
       </c>
       <c r="G333" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5</v>
       </c>
       <c r="G336" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G339" t="n">
-        <v>4.88531160354614</v>
+        <v>4.8853120803833</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.98110151290894</v>
+        <v>4.98110246658325</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.88531160354614</v>
+        <v>4.8853120803833</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>4.98110151290894</v>
+        <v>4.98110246658325</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G343" t="n">
-        <v>5.00025987625122</v>
+        <v>5.00026035308838</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>5.17268371582031</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>5.5</v>
       </c>
       <c r="G347" t="n">
-        <v>5.26847410202026</v>
+        <v>5.26847362518311</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G352" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G353" t="n">
-        <v>5.09605026245117</v>
+        <v>5.09605073928833</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>5.17268371582031</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G355" t="n">
-        <v>5.05773448944092</v>
+        <v>5.05773544311523</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>5.17268371582031</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G358" t="n">
-        <v>5.17268371582031</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G359" t="n">
-        <v>5.01941776275635</v>
+        <v>5.01941728591919</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G364" t="n">
-        <v>5.15352535247803</v>
+        <v>5.15352487564087</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G366" t="n">
-        <v>5.28763151168823</v>
+        <v>5.28763198852539</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G368" t="n">
-        <v>5.47921228408813</v>
+        <v>5.47921180725098</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G369" t="n">
-        <v>5.53668689727783</v>
+        <v>5.53668642044067</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G370" t="n">
-        <v>5.53668689727783</v>
+        <v>5.53668642044067</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>5.68995141983032</v>
+        <v>5.68995094299316</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>5.65163516998291</v>
+        <v>5.65163564682007</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900680541992</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G377" t="n">
-        <v>5.90068960189819</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G379" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G384" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900680541992</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900680541992</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G386" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900680541992</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900680541992</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900680541992</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900680541992</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G394" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900680541992</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G395" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900680541992</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>6.03479671478271</v>
+        <v>6.03479719161987</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311248779297</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964200973511</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G399" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964200973511</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>6.32216787338257</v>
+        <v>6.32216835021973</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G401" t="n">
-        <v>6.36048412322998</v>
+        <v>6.36048364639282</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G402" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964200973511</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>6.32216787338257</v>
+        <v>6.32216835021973</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>6.36048412322998</v>
+        <v>6.36048364639282</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G407" t="n">
-        <v>6.4945912361145</v>
+        <v>6.49459171295166</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>6.41795778274536</v>
+        <v>6.41795825958252</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>6.03479671478271</v>
+        <v>6.03479719161987</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>6.03479671478271</v>
+        <v>6.03479719161987</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G412" t="n">
-        <v>6.03479671478271</v>
+        <v>6.03479719161987</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G414" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311248779297</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.55584478378296</v>
+        <v>5.55584573745728</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G417" t="n">
-        <v>5.90068960189819</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>5.72826766967773</v>
+        <v>5.72826814651489</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G419" t="n">
-        <v>5.90068960189819</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>5.70910978317261</v>
+        <v>5.70910930633545</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>5.70910978317261</v>
+        <v>5.70910930633545</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900680541992</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G427" t="n">
-        <v>5.9964804649353</v>
+        <v>5.99648094177246</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311248779297</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>6.03479671478271</v>
+        <v>6.03479719161987</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G430" t="n">
-        <v>6.053955078125</v>
+        <v>6.05395460128784</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G431" t="n">
-        <v>6.053955078125</v>
+        <v>6.05395460128784</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G432" t="n">
-        <v>6.11142921447754</v>
+        <v>6.1114296913147</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>6.30300998687744</v>
+        <v>6.30300903320312</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>6.41795778274536</v>
+        <v>6.41795825958252</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>6.41795778274536</v>
+        <v>6.41795825958252</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G436" t="n">
-        <v>6.57122278213501</v>
+        <v>6.57122325897217</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G437" t="n">
-        <v>6.62869787216187</v>
+        <v>6.62869691848755</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>6.68617153167725</v>
+        <v>6.6861720085144</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G444" t="n">
-        <v>6.78196144104004</v>
+        <v>6.78196287155151</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>6.9927020072937</v>
+        <v>6.99270105361938</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>7.165123462677</v>
+        <v>7.16512441635132</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>7.5</v>
       </c>
       <c r="G447" t="n">
-        <v>7.18428182601929</v>
+        <v>7.18428134918213</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G448" t="n">
-        <v>7.50996971130371</v>
+        <v>7.50997018814087</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G451" t="n">
-        <v>8.00807857513428</v>
+        <v>8.00807952880859</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>8.13305473327637</v>
+        <v>8.133056640625</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.5</v>
       </c>
       <c r="G454" t="n">
-        <v>8.1715087890625</v>
+        <v>8.17151069641113</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G455" t="n">
-        <v>7.99846458435059</v>
+        <v>7.9984655380249</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537460327148</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G457" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537460327148</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.5</v>
       </c>
       <c r="G458" t="n">
-        <v>8.1715087890625</v>
+        <v>8.17151069641113</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>8.13305473327637</v>
+        <v>8.133056640625</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G460" t="n">
-        <v>8.01769256591797</v>
+        <v>8.01769161224365</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G461" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537460327148</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537460327148</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>7.80619478225708</v>
+        <v>7.80619525909424</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>7.53701543807983</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>7.22938299179077</v>
+        <v>7.22938251495361</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>7.5</v>
       </c>
       <c r="G471" t="n">
-        <v>7.21015548706055</v>
+        <v>7.21015501022339</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>7.19092798233032</v>
+        <v>7.19092845916748</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>7.5</v>
       </c>
       <c r="G473" t="n">
-        <v>7.21015548706055</v>
+        <v>7.21015501022339</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G474" t="n">
-        <v>7.07556581497192</v>
+        <v>7.07556629180908</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G491" t="n">
-        <v>7.46010780334473</v>
+        <v>7.46010828018188</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>7.53701543807983</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>7.53701543807983</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G497" t="n">
-        <v>7.53701543807983</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>8.01769256591797</v>
+        <v>8.01769161224365</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G507" t="n">
-        <v>8.34455299377441</v>
+        <v>8.34455490112305</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G508" t="n">
-        <v>8.38300800323486</v>
+        <v>8.38300704956055</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>8.4599142074585</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G510" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G511" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>9.2482271194458</v>
+        <v>9.24822521209717</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G517" t="n">
-        <v>9.3635892868042</v>
+        <v>9.36358737945557</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>9.49817657470703</v>
+        <v>9.49817752838135</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G525" t="n">
-        <v>9.34436225891113</v>
+        <v>9.3443603515625</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G526" t="n">
-        <v>9.3635892868042</v>
+        <v>9.36358737945557</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G527" t="n">
-        <v>9.01750183105469</v>
+        <v>9.01750087738037</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G530" t="n">
-        <v>8.70986747741699</v>
+        <v>8.70986843109131</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G531" t="n">
-        <v>8.94059276580811</v>
+        <v>8.94059181213379</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G533" t="n">
-        <v>8.99827480316162</v>
+        <v>8.99827289581299</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G534" t="n">
-        <v>8.94059276580811</v>
+        <v>8.94059181213379</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>8.94059276580811</v>
+        <v>8.94059181213379</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G536" t="n">
-        <v>8.92136478424072</v>
+        <v>8.92136669158936</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>8.69063949584961</v>
+        <v>8.69064044952393</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G541" t="n">
-        <v>8.63296031951904</v>
+        <v>8.63295936584473</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G545" t="n">
-        <v>8.26764583587646</v>
+        <v>8.26764488220215</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G546" t="n">
-        <v>8.38300800323486</v>
+        <v>8.38300704956055</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>8.38300800323486</v>
+        <v>8.38300704956055</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>8.4599142074585</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G549" t="n">
-        <v>8.4599142074585</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>8.4599142074585</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.4599142074585</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G559" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>8.94059276580811</v>
+        <v>8.94059181213379</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>8.97904586791992</v>
+        <v>8.97904777526855</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G567" t="n">
-        <v>9.19054508209229</v>
+        <v>9.19054412841797</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G574" t="n">
-        <v>9.01750183105469</v>
+        <v>9.01750087738037</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G578" t="n">
-        <v>8.97904586791992</v>
+        <v>8.97904777526855</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G582" t="n">
-        <v>8.70986747741699</v>
+        <v>8.70986843109131</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>8.72909545898438</v>
+        <v>8.72909450531006</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.69063949584961</v>
+        <v>8.69064044952393</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G587" t="n">
-        <v>8.70986747741699</v>
+        <v>8.70986843109131</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G588" t="n">
-        <v>8.70986747741699</v>
+        <v>8.70986843109131</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G589" t="n">
-        <v>8.67141342163086</v>
+        <v>8.67141437530518</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>8.76754856109619</v>
+        <v>8.76754951477051</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G600" t="n">
-        <v>9.34436225891113</v>
+        <v>9.3443603515625</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G601" t="n">
-        <v>9.15209102630615</v>
+        <v>9.15209007263184</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G604" t="n">
-        <v>9.26745223999023</v>
+        <v>9.26745414733887</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G605" t="n">
-        <v>9.3635892868042</v>
+        <v>9.36358737945557</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G613" t="n">
-        <v>9.15209102630615</v>
+        <v>9.15209007263184</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G616" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G617" t="n">
-        <v>9.15209102630615</v>
+        <v>9.15209007263184</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G619" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G620" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G622" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G623" t="n">
-        <v>9.44049644470215</v>
+        <v>9.44049739837646</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>9.99808216094971</v>
+        <v>9.99808311462402</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G628" t="n">
-        <v>10.2864894866943</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>10.2864894866943</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G630" t="n">
-        <v>10.2864894866943</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G636" t="n">
-        <v>10.0461483001709</v>
+        <v>10.0461502075195</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>10.1903533935547</v>
+        <v>10.1903524398804</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>10.2864894866943</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>10.478759765625</v>
+        <v>10.4787588119507</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>10.75</v>
       </c>
       <c r="G642" t="n">
-        <v>10.3345565795898</v>
+        <v>10.3345556259155</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>10.75</v>
       </c>
       <c r="G643" t="n">
-        <v>10.3345565795898</v>
+        <v>10.3345556259155</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>10.3826246261597</v>
+        <v>10.3826236724854</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G645" t="n">
-        <v>10.3826246261597</v>
+        <v>10.3826236724854</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>10.75</v>
       </c>
       <c r="G646" t="n">
-        <v>10.3345565795898</v>
+        <v>10.3345556259155</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>10.478759765625</v>
+        <v>10.4787588119507</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>11.5</v>
       </c>
       <c r="G651" t="n">
-        <v>11.0555734634399</v>
+        <v>11.055570602417</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>11.5</v>
       </c>
       <c r="G652" t="n">
-        <v>11.0555734634399</v>
+        <v>11.055570602417</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>11.6323843002319</v>
+        <v>11.6323852539062</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8246536254883</v>
+        <v>11.8246555328369</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>12.5</v>
       </c>
       <c r="G655" t="n">
-        <v>12.0169258117676</v>
+        <v>12.0169248580933</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>12.3053312301636</v>
+        <v>12.3053321838379</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>13.25</v>
       </c>
       <c r="G657" t="n">
-        <v>12.737940788269</v>
+        <v>12.7379398345947</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G658" t="n">
-        <v>12.5937376022339</v>
+        <v>12.5937385559082</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>12.9302110671997</v>
+        <v>12.930212020874</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G660" t="n">
-        <v>12.8340759277344</v>
+        <v>12.8340787887573</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>12.5937376022339</v>
+        <v>12.5937385559082</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>12.1130609512329</v>
+        <v>12.1130619049072</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>12.6418056488037</v>
+        <v>12.6418046951294</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>12.8340759277344</v>
+        <v>12.8340787887573</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>12.5937376022339</v>
+        <v>12.5937385559082</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>13.25</v>
       </c>
       <c r="G671" t="n">
-        <v>12.737940788269</v>
+        <v>12.7379398345947</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>13.25</v>
       </c>
       <c r="G672" t="n">
-        <v>12.737940788269</v>
+        <v>12.7379398345947</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G673" t="n">
-        <v>13.0263481140137</v>
+        <v>13.026349067688</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G674" t="n">
-        <v>13.507022857666</v>
+        <v>13.507025718689</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>14.5</v>
       </c>
       <c r="G675" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>14.5</v>
       </c>
       <c r="G676" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>14.5</v>
       </c>
       <c r="G677" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>13.507022857666</v>
+        <v>13.507025718689</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>13.6512279510498</v>
+        <v>13.6512269973755</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838356018066</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>14.1319065093994</v>
+        <v>14.1319036483765</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G685" t="n">
-        <v>14.1319065093994</v>
+        <v>14.1319036483765</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838356018066</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>14.5</v>
       </c>
       <c r="G690" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>14.5</v>
       </c>
       <c r="G691" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>13.8434991836548</v>
+        <v>13.8434972763062</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>14.25</v>
       </c>
       <c r="G695" t="n">
-        <v>13.6992950439453</v>
+        <v>13.6992959976196</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>14</v>
       </c>
       <c r="G696" t="n">
-        <v>13.4589567184448</v>
+        <v>13.4589576721191</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>14</v>
       </c>
       <c r="G697" t="n">
-        <v>13.4589567184448</v>
+        <v>13.4589576721191</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838356018066</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838356018066</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>14.3631267547607</v>
+        <v>14.3631258010864</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>15.5</v>
       </c>
       <c r="G707" t="n">
-        <v>14.9415073394775</v>
+        <v>14.9415082931519</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>15.5</v>
       </c>
       <c r="G708" t="n">
-        <v>14.9415073394775</v>
+        <v>14.9415082931519</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G710" t="n">
-        <v>15.8090801239014</v>
+        <v>15.8090791702271</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>15.8090801239014</v>
+        <v>15.8090791702271</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>15.9536714553833</v>
+        <v>15.9536743164062</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G713" t="n">
-        <v>16.6766510009766</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>16.2910614013672</v>
+        <v>16.2910633087158</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>16.9176425933838</v>
+        <v>16.9176406860352</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>16.9658393859863</v>
+        <v>16.965841293335</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>17.0140399932861</v>
+        <v>17.0140380859375</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G719" t="n">
-        <v>16.9176425933838</v>
+        <v>16.9176406860352</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>16.7248477935791</v>
+        <v>16.7248497009277</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>16.8212490081787</v>
+        <v>16.8212451934814</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838581085205</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>17</v>
       </c>
       <c r="G725" t="n">
-        <v>16.3874568939209</v>
+        <v>16.3874626159668</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>16.5</v>
       </c>
       <c r="G726" t="n">
-        <v>15.9054746627808</v>
+        <v>15.905478477478</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>16.2910614013672</v>
+        <v>16.2910633087158</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838581085205</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838581085205</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G733" t="n">
-        <v>16.2910614013672</v>
+        <v>16.2910633087158</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>16.0982723236084</v>
+        <v>16.0982704162598</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>16.2428665161133</v>
+        <v>16.2428646087646</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>16.0982723236084</v>
+        <v>16.0982704162598</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>15.5198888778687</v>
+        <v>15.519889831543</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>15.8090801239014</v>
+        <v>15.8090791702271</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>15.3752937316895</v>
+        <v>15.3752927780151</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>15.2788972854614</v>
+        <v>15.2788963317871</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G748" t="n">
-        <v>14.8933086395264</v>
+        <v>14.8933095932007</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G749" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G750" t="n">
-        <v>14.8933086395264</v>
+        <v>14.8933095932007</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>15.2788972854614</v>
+        <v>15.2788963317871</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G755" t="n">
-        <v>15.3752937316895</v>
+        <v>15.3752927780151</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G756" t="n">
-        <v>15.2788972854614</v>
+        <v>15.2788963317871</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>16.25</v>
       </c>
       <c r="G757" t="n">
-        <v>15.6644849777222</v>
+        <v>15.6644840240479</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G758" t="n">
-        <v>15.8572788238525</v>
+        <v>15.8572769165039</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>15.6162853240967</v>
+        <v>15.6162872314453</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>16.25</v>
       </c>
       <c r="G762" t="n">
-        <v>15.6644849777222</v>
+        <v>15.6644840240479</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>15.5198888778687</v>
+        <v>15.519889831543</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G764" t="n">
-        <v>15.6162853240967</v>
+        <v>15.6162872314453</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>15.8090801239014</v>
+        <v>15.8090791702271</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>15.6162853240967</v>
+        <v>15.6162872314453</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G769" t="n">
-        <v>15.5680875778198</v>
+        <v>15.5680866241455</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G770" t="n">
-        <v>16.2910614013672</v>
+        <v>16.2910633087158</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G771" t="n">
-        <v>17.0622406005859</v>
+        <v>17.0622386932373</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>18</v>
       </c>
       <c r="G774" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>16.7248477935791</v>
+        <v>16.7248497009277</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>17.158634185791</v>
+        <v>17.1586322784424</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G778" t="n">
-        <v>16.8212490081787</v>
+        <v>16.8212451934814</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G779" t="n">
-        <v>16.6766510009766</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>17.5</v>
       </c>
       <c r="G780" t="n">
-        <v>16.8694438934326</v>
+        <v>16.8694458007812</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>16.6766510009766</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G782" t="n">
-        <v>16.7730464935303</v>
+        <v>16.7730484008789</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>16.6766510009766</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>16.532054901123</v>
+        <v>16.5320529937744</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G785" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838581085205</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>17.5</v>
       </c>
       <c r="G786" t="n">
-        <v>16.8694438934326</v>
+        <v>16.8694458007812</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>16.9176425933838</v>
+        <v>16.9176406860352</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G788" t="n">
-        <v>17.2550315856934</v>
+        <v>17.2550296783447</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>17.2550315856934</v>
+        <v>17.2550296783447</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>17.2068347930908</v>
+        <v>17.2068328857422</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G792" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>17.158634185791</v>
+        <v>17.1586322784424</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G796" t="n">
-        <v>17.2550315856934</v>
+        <v>17.2550296783447</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>17.0622406005859</v>
+        <v>17.0622386932373</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>17.5</v>
       </c>
       <c r="G798" t="n">
-        <v>16.8694438934326</v>
+        <v>16.8694458007812</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G799" t="n">
-        <v>17.0140399932861</v>
+        <v>17.0140380859375</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>18.604585647583</v>
+        <v>18.6045837402344</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G810" t="n">
-        <v>18.3635921478271</v>
+        <v>18.3635940551758</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G811" t="n">
-        <v>18.4117965698242</v>
+        <v>18.411792755127</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>18.1708011627197</v>
+        <v>18.1708030700684</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>18.1708011627197</v>
+        <v>18.1708030700684</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>17.9780082702637</v>
+        <v>17.978006362915</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>18.1708011627197</v>
+        <v>18.1708030700684</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>18.75</v>
       </c>
       <c r="G825" t="n">
-        <v>18.074405670166</v>
+        <v>18.0744037628174</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>18.1708011627197</v>
+        <v>18.1708030700684</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>17.8816089630127</v>
+        <v>17.88161277771</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>18.1708011627197</v>
+        <v>18.1708030700684</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G833" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406154632568</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>18.5</v>
       </c>
       <c r="G839" t="n">
-        <v>17.8334121704102</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406154632568</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>17.8816089630127</v>
+        <v>17.88161277771</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406154632568</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406154632568</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>18.5</v>
       </c>
       <c r="G848" t="n">
-        <v>17.8334121704102</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>18</v>
       </c>
       <c r="G851" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G853" t="n">
-        <v>17.9780082702637</v>
+        <v>17.978006362915</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>18</v>
       </c>
       <c r="G855" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>17.785213470459</v>
+        <v>17.7852153778076</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>17.9298095703125</v>
+        <v>17.9298076629639</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>18.5</v>
       </c>
       <c r="G858" t="n">
-        <v>17.8334121704102</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>18</v>
       </c>
       <c r="G862" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>18</v>
       </c>
       <c r="G863" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>17.2068347930908</v>
+        <v>17.2068328857422</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>18</v>
       </c>
       <c r="G868" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>17.9780082702637</v>
+        <v>17.978006362915</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G874" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>17.9298095703125</v>
+        <v>17.9298076629639</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G877" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>19.1829662322998</v>
+        <v>19.1829681396484</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G884" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G887" t="n">
-        <v>18.9901752471924</v>
+        <v>18.990177154541</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>18.9901752471924</v>
+        <v>18.990177154541</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>18.9901752471924</v>
+        <v>18.990177154541</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>18.3635921478271</v>
+        <v>18.3635940551758</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>18.5</v>
       </c>
       <c r="G892" t="n">
-        <v>17.8334121704102</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>18.5</v>
       </c>
       <c r="G893" t="n">
-        <v>17.8334121704102</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G894" t="n">
-        <v>17.0140399932861</v>
+        <v>17.0140380859375</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>17.8816089630127</v>
+        <v>17.88161277771</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>18</v>
       </c>
       <c r="G903" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>17.2068347930908</v>
+        <v>17.2068328857422</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G906" t="n">
-        <v>17.2550315856934</v>
+        <v>17.2550296783447</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G907" t="n">
-        <v>17.2550315856934</v>
+        <v>17.2550296783447</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>18</v>
       </c>
       <c r="G908" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>17.5</v>
       </c>
       <c r="G909" t="n">
-        <v>16.8694438934326</v>
+        <v>16.8694458007812</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>17.0622406005859</v>
+        <v>17.0622386932373</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>16.8212490081787</v>
+        <v>16.8212451934814</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>16.5</v>
       </c>
       <c r="G913" t="n">
-        <v>15.9054746627808</v>
+        <v>15.905478477478</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G915" t="n">
-        <v>15.3752937316895</v>
+        <v>15.3752927780151</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>14.6523160934448</v>
+        <v>14.6523170471191</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>15.3270950317383</v>
+        <v>15.3270959854126</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>15.3270950317383</v>
+        <v>15.3270959854126</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>15.5</v>
       </c>
       <c r="G920" t="n">
-        <v>14.9415073394775</v>
+        <v>14.9415082931519</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>15.25</v>
       </c>
       <c r="G921" t="n">
-        <v>14.7005157470703</v>
+        <v>14.7005167007446</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>14.1221351623535</v>
+        <v>14.1221342086792</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>15.5198888778687</v>
+        <v>15.519889831543</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>16.0018711090088</v>
+        <v>16.0018749237061</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>16.5</v>
       </c>
       <c r="G929" t="n">
-        <v>15.9054746627808</v>
+        <v>15.905478477478</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G938" t="n">
-        <v>14.3631267547607</v>
+        <v>14.3631258010864</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>15.3270950317383</v>
+        <v>15.3270959854126</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G940" t="n">
-        <v>15.3752937316895</v>
+        <v>15.3752927780151</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>15.2788972854614</v>
+        <v>15.2788963317871</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>15.3752937316895</v>
+        <v>15.3752927780151</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>14.6523160934448</v>
+        <v>14.6523170471191</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G952" t="n">
-        <v>14.604118347168</v>
+        <v>14.6041193008423</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>14.3631267547607</v>
+        <v>14.3631258010864</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G954" t="n">
-        <v>14.3631267547607</v>
+        <v>14.3631258010864</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>14.3631267547607</v>
+        <v>14.3631258010864</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>14.5</v>
       </c>
       <c r="G959" t="n">
-        <v>13.9775390625</v>
+        <v>13.9775400161743</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>13.6883497238159</v>
+        <v>13.6883478164673</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G963" t="n">
-        <v>13.2624034881592</v>
+        <v>13.2624044418335</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>13.75</v>
       </c>
       <c r="G964" t="n">
-        <v>13.3108062744141</v>
+        <v>13.3108072280884</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G969" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>14</v>
       </c>
       <c r="G970" t="n">
-        <v>13.5528211593628</v>
+        <v>13.5528202056885</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>14.6176853179932</v>
+        <v>14.6176862716675</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>14.75</v>
       </c>
       <c r="G976" t="n">
-        <v>14.278865814209</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>13.9400444030762</v>
+        <v>13.9400434494019</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G980" t="n">
-        <v>13.6012229919434</v>
+        <v>13.6012239456177</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G981" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>15.75</v>
       </c>
       <c r="G982" t="n">
-        <v>15.2469244003296</v>
+        <v>15.2469234466553</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>15.4405355453491</v>
+        <v>15.4405345916748</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>15.0533132553101</v>
+        <v>15.0533123016357</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G990" t="n">
-        <v>14.666088104248</v>
+        <v>14.6660890579224</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G993" t="n">
-        <v>13.9400444030762</v>
+        <v>13.9400434494019</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>14.75</v>
       </c>
       <c r="G994" t="n">
-        <v>14.278865814209</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>14.25</v>
       </c>
       <c r="G998" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>13.6496276855469</v>
+        <v>13.6496267318726</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>14</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.5528211593628</v>
+        <v>13.5528202056885</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.6980295181274</v>
+        <v>13.6980304718018</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.6980295181274</v>
+        <v>13.6980304718018</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1005" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>13.6496276855469</v>
+        <v>13.6496267318726</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1009" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.0203876495361</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1019" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>12.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.1007328033447</v>
+        <v>12.100733757019</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1021" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1023" t="n">
-        <v>12.4395542144775</v>
+        <v>12.4395532608032</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1024" t="n">
-        <v>12.2459421157837</v>
+        <v>12.2459411621094</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.778374671936</v>
+        <v>12.7783737182617</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>13.75</v>
       </c>
       <c r="G1027" t="n">
-        <v>13.3108062744141</v>
+        <v>13.3108072280884</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1028" t="n">
-        <v>13.456015586853</v>
+        <v>13.4560146331787</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1029" t="n">
-        <v>13.6012229919434</v>
+        <v>13.6012239456177</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>14.3272686004639</v>
+        <v>14.3272676467896</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1036" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>14.75</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.278865814209</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1040" t="n">
-        <v>14.6176853179932</v>
+        <v>14.6176862716675</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>14.75</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.278865814209</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1052" t="n">
-        <v>13.9400444030762</v>
+        <v>13.9400434494019</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.6496276855469</v>
+        <v>13.6496267318726</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1054" t="n">
-        <v>13.6496276855469</v>
+        <v>13.6496267318726</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>14.25</v>
       </c>
       <c r="G1055" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>13.9400444030762</v>
+        <v>13.9400434494019</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>14.25</v>
       </c>
       <c r="G1057" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1058" t="n">
-        <v>13.6012229919434</v>
+        <v>13.6012239456177</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G1059" t="n">
-        <v>13.6012229919434</v>
+        <v>13.6012239456177</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1060" t="n">
-        <v>13.2624034881592</v>
+        <v>13.2624044418335</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>12.2459421157837</v>
+        <v>12.2459411621094</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1069" t="n">
-        <v>11.9071207046509</v>
+        <v>11.9071216583252</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1070" t="n">
-        <v>11.7135095596313</v>
+        <v>11.7135105133057</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1072" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>12.1975383758545</v>
+        <v>12.1975402832031</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1078" t="n">
-        <v>12.5363607406616</v>
+        <v>12.5363597869873</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1083" t="n">
-        <v>12.4395542144775</v>
+        <v>12.4395532608032</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>12.778374671936</v>
+        <v>12.7783737182617</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1090" t="n">
-        <v>12.778374671936</v>
+        <v>12.7783737182617</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>12.5363607406616</v>
+        <v>12.5363597869873</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>12.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>12.75</v>
       </c>
       <c r="G1095" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1096" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1097" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>12.75</v>
       </c>
       <c r="G1100" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>12.75</v>
       </c>
       <c r="G1101" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1102" t="n">
-        <v>12.5363607406616</v>
+        <v>12.5363597869873</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>12.75</v>
       </c>
       <c r="G1104" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1105" t="n">
-        <v>12.2459421157837</v>
+        <v>12.2459411621094</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1106" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>12.75</v>
       </c>
       <c r="G1107" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1109" t="n">
-        <v>12.4395542144775</v>
+        <v>12.4395532608032</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>12.4395542144775</v>
+        <v>12.4395532608032</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>12.4395542144775</v>
+        <v>12.4395532608032</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>12.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1114" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1118" t="n">
-        <v>12.5363607406616</v>
+        <v>12.5363597869873</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>12.5363607406616</v>
+        <v>12.5363597869873</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1120" t="n">
-        <v>12.778374671936</v>
+        <v>12.7783737182617</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1123" t="n">
-        <v>13.0203876495361</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>13.0203876495361</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1131" t="n">
-        <v>13.456015586853</v>
+        <v>13.4560146331787</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>13.456015586853</v>
+        <v>13.4560146331787</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1133" t="n">
-        <v>13.6496276855469</v>
+        <v>13.6496267318726</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1136" t="n">
-        <v>13.9400444030762</v>
+        <v>13.9400434494019</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>14</v>
       </c>
       <c r="G1137" t="n">
-        <v>13.5528211593628</v>
+        <v>13.5528202056885</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1138" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>14.25</v>
       </c>
       <c r="G1139" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1140" t="n">
-        <v>13.9400444030762</v>
+        <v>13.9400434494019</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1141" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>14.25</v>
       </c>
       <c r="G1142" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1145" t="n">
-        <v>14.3272686004639</v>
+        <v>14.3272676467896</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1148" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1149" t="n">
-        <v>14.1820592880249</v>
+        <v>14.1820583343506</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1150" t="n">
-        <v>14.1820592880249</v>
+        <v>14.1820583343506</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>14.75</v>
       </c>
       <c r="G1151" t="n">
-        <v>14.278865814209</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1154" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1157" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1160" t="n">
-        <v>14.3272686004639</v>
+        <v>14.3272676467896</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1161" t="n">
-        <v>14.1820592880249</v>
+        <v>14.1820583343506</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1162" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1164" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1166" t="n">
-        <v>13.9400444030762</v>
+        <v>13.9400434494019</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1168" t="n">
-        <v>13.6496276855469</v>
+        <v>13.6496267318726</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1172" t="n">
-        <v>13.456015586853</v>
+        <v>13.4560146331787</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>13.75</v>
       </c>
       <c r="G1174" t="n">
-        <v>13.3108062744141</v>
+        <v>13.3108072280884</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>13.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>13.3108062744141</v>
+        <v>13.3108072280884</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1182" t="n">
-        <v>12.9235830307007</v>
+        <v>12.923583984375</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1185" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1186" t="n">
-        <v>12.778374671936</v>
+        <v>12.7783737182617</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>12.75</v>
       </c>
       <c r="G1190" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1193" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1194" t="n">
-        <v>13.0203876495361</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>12.778374671936</v>
+        <v>12.7783737182617</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1197" t="n">
-        <v>12.778374671936</v>
+        <v>12.7783737182617</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>13.2624034881592</v>
+        <v>13.2624044418335</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.9235830307007</v>
+        <v>12.923583984375</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.2943449020386</v>
+        <v>12.2943439483643</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1207" t="n">
-        <v>12.1975383758545</v>
+        <v>12.1975402832031</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1208" t="n">
-        <v>12.4395542144775</v>
+        <v>12.4395532608032</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1209" t="n">
-        <v>12.4395542144775</v>
+        <v>12.4395532608032</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.2459421157837</v>
+        <v>12.2459411621094</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1216" t="n">
-        <v>12.4395542144775</v>
+        <v>12.4395532608032</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G1217" t="n">
-        <v>13.0203876495361</v>
+        <v>13.0203886032104</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>13</v>
       </c>
       <c r="G1222" t="n">
-        <v>12.6539630889893</v>
+        <v>12.6539640426636</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>13</v>
       </c>
       <c r="G1223" t="n">
-        <v>12.6539630889893</v>
+        <v>12.6539640426636</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>12.75</v>
       </c>
       <c r="G1224" t="n">
-        <v>12.4106187820435</v>
+        <v>12.4106178283691</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1226" t="n">
-        <v>12.5566253662109</v>
+        <v>12.5566244125366</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>12.5</v>
       </c>
       <c r="G1229" t="n">
-        <v>12.1672716140747</v>
+        <v>12.167272567749</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>11.8752574920654</v>
+        <v>11.8752584457397</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>12.0699338912964</v>
+        <v>12.0699348449707</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1235" t="n">
-        <v>11.7779197692871</v>
+        <v>11.7779207229614</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1236" t="n">
-        <v>11.7779197692871</v>
+        <v>11.7779207229614</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>12</v>
       </c>
       <c r="G1237" t="n">
-        <v>11.6805810928345</v>
+        <v>11.6805820465088</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>12</v>
       </c>
       <c r="G1238" t="n">
-        <v>11.6805810928345</v>
+        <v>11.6805820465088</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>12</v>
       </c>
       <c r="G1240" t="n">
-        <v>11.6805810928345</v>
+        <v>11.6805820465088</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1243" t="n">
-        <v>11.4859046936035</v>
+        <v>11.4859066009521</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1244" t="n">
-        <v>11.2425603866577</v>
+        <v>11.2425594329834</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1245" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1246" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1247" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1248" t="n">
-        <v>11.2425603866577</v>
+        <v>11.2425594329834</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1250" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1253" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1259" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>10.8045387268066</v>
+        <v>10.8045377731323</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1273" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>11.5</v>
       </c>
       <c r="G1274" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1275" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>11.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1277" t="n">
-        <v>11.1452217102051</v>
+        <v>11.1452207565308</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>11.25</v>
       </c>
       <c r="G1278" t="n">
-        <v>10.9505453109741</v>
+        <v>10.9505443572998</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1282" t="n">
-        <v>10.8045387268066</v>
+        <v>10.8045377731323</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>11.25</v>
       </c>
       <c r="G1284" t="n">
-        <v>10.9505453109741</v>
+        <v>10.9505443572998</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>11.5</v>
       </c>
       <c r="G1285" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>11.5</v>
       </c>
       <c r="G1286" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>11.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1291" t="n">
-        <v>10.8045387268066</v>
+        <v>10.8045377731323</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1293" t="n">
-        <v>11.1452217102051</v>
+        <v>11.1452207565308</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1294" t="n">
-        <v>11.3398971557617</v>
+        <v>11.339898109436</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>11.5</v>
       </c>
       <c r="G1296" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1297" t="n">
-        <v>10.8045387268066</v>
+        <v>10.8045377731323</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>11.25</v>
       </c>
       <c r="G1306" t="n">
-        <v>10.9505453109741</v>
+        <v>10.9505443572998</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1309" t="n">
-        <v>11.1452217102051</v>
+        <v>11.1452207565308</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1310" t="n">
-        <v>11.1452217102051</v>
+        <v>11.1452207565308</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>11.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>11.25</v>
       </c>
       <c r="G1315" t="n">
-        <v>10.9505453109741</v>
+        <v>10.9505443572998</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1319" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1320" t="n">
-        <v>10.5611925125122</v>
+        <v>10.5611934661865</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>9.78248691558838</v>
+        <v>9.7824878692627</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1331" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>10</v>
       </c>
       <c r="G1332" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1333" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1335" t="n">
-        <v>9.78248691558838</v>
+        <v>9.7824878692627</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1336" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718406677246</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1337" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718406677246</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1340" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>10</v>
       </c>
       <c r="G1341" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>10</v>
       </c>
       <c r="G1342" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>10</v>
       </c>
       <c r="G1343" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1344" t="n">
-        <v>9.7143497467041</v>
+        <v>9.71435070037842</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1345" t="n">
-        <v>9.57807731628418</v>
+        <v>9.5780782699585</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1348" t="n">
-        <v>9.7143497467041</v>
+        <v>9.71435070037842</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1349" t="n">
-        <v>9.7143497467041</v>
+        <v>9.71435070037842</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1350" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1351" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1355" t="n">
-        <v>9.57807731628418</v>
+        <v>9.5780782699585</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1356" t="n">
-        <v>9.53914165496826</v>
+        <v>9.53914260864258</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1357" t="n">
-        <v>9.8798246383667</v>
+        <v>9.87982559204102</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1359" t="n">
-        <v>9.53914165496826</v>
+        <v>9.53914260864258</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1360" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1361" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1364" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1367" t="n">
-        <v>9.3249979019165</v>
+        <v>9.32499694824219</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>9.5</v>
       </c>
       <c r="G1370" t="n">
-        <v>9.24712753295898</v>
+        <v>9.24712657928467</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1371" t="n">
-        <v>9.03298377990723</v>
+        <v>9.03298282623291</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>9.53914165496826</v>
+        <v>9.53914260864258</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>10</v>
       </c>
       <c r="G1373" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1375" t="n">
-        <v>10.4151859283447</v>
+        <v>10.4151849746704</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1376" t="n">
-        <v>10.6098623275757</v>
+        <v>10.6098613739014</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1378" t="n">
-        <v>10.6098623275757</v>
+        <v>10.6098613739014</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>11.25</v>
       </c>
       <c r="G1381" t="n">
-        <v>10.9505453109741</v>
+        <v>10.9505443572998</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>10.6098623275757</v>
+        <v>10.6098613739014</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1390" t="n">
-        <v>10.3665151596069</v>
+        <v>10.3665161132812</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1395" t="n">
-        <v>10.8045387268066</v>
+        <v>10.8045377731323</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>10.5611925125122</v>
+        <v>10.5611934661865</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1402" t="n">
-        <v>10.5611925125122</v>
+        <v>10.5611934661865</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1405" t="n">
-        <v>10.5611925125122</v>
+        <v>10.5611934661865</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1409" t="n">
-        <v>10.8045387268066</v>
+        <v>10.8045377731323</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>10.3665151596069</v>
+        <v>10.3665161132812</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1418" t="n">
-        <v>10.5611925125122</v>
+        <v>10.5611934661865</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1420" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1422" t="n">
-        <v>10.3665151596069</v>
+        <v>10.3665161132812</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1424" t="n">
-        <v>10.3665151596069</v>
+        <v>10.3665161132812</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1426" t="n">
-        <v>9.78248691558838</v>
+        <v>9.7824878692627</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1427" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>10.25</v>
       </c>
       <c r="G1428" t="n">
-        <v>9.97716331481934</v>
+        <v>9.97716426849365</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>10.25</v>
       </c>
       <c r="G1429" t="n">
-        <v>9.97716331481934</v>
+        <v>9.97716426849365</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1430" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1431" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1432" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718406677246</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1433" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718406677246</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>10.25</v>
       </c>
       <c r="G1435" t="n">
-        <v>9.97716331481934</v>
+        <v>9.97716426849365</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1436" t="n">
-        <v>9.6364803314209</v>
+        <v>9.63647937774658</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1437" t="n">
-        <v>9.6364803314209</v>
+        <v>9.63647937774658</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1438" t="n">
-        <v>9.36393356323242</v>
+        <v>9.36393260955811</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>9.5</v>
       </c>
       <c r="G1439" t="n">
-        <v>9.24712753295898</v>
+        <v>9.24712657928467</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>9.5</v>
       </c>
       <c r="G1440" t="n">
-        <v>9.24712753295898</v>
+        <v>9.24712657928467</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1441" t="n">
-        <v>9.3055305480957</v>
+        <v>9.30552959442139</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1443" t="n">
-        <v>9.7143497467041</v>
+        <v>9.71435070037842</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>10</v>
       </c>
       <c r="G1444" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1445" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>10</v>
       </c>
       <c r="G1446" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1449" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1450" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1451" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718406677246</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1454" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>10</v>
       </c>
       <c r="G1455" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1456" t="n">
-        <v>9.57807731628418</v>
+        <v>9.5780782699585</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1460" t="n">
-        <v>9.6364803314209</v>
+        <v>9.63647937774658</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1463" t="n">
-        <v>9.53914165496826</v>
+        <v>9.53914260864258</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>9.3249979019165</v>
+        <v>9.32499694824219</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1475" t="n">
-        <v>9.48539447784424</v>
+        <v>9.48539352416992</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1476" t="n">
-        <v>9.60346984863281</v>
+        <v>9.6034688949585</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1483" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1487" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1489" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1490" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1497" t="n">
-        <v>9.6428279876709</v>
+        <v>9.64282894134521</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1498" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1499" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1500" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1501" t="n">
-        <v>9.6428279876709</v>
+        <v>9.64282894134521</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1504" t="n">
-        <v>9.56411170959473</v>
+        <v>9.56411075592041</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1505" t="n">
-        <v>9.66250610351562</v>
+        <v>9.66250705718994</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1506" t="n">
-        <v>9.54443168640137</v>
+        <v>9.54443073272705</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1507" t="n">
-        <v>9.66250610351562</v>
+        <v>9.66250705718994</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1515" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1528" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>10.25</v>
       </c>
       <c r="G1531" t="n">
-        <v>10.0856103897095</v>
+        <v>10.0856113433838</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1541" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1545" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1546" t="n">
-        <v>9.6428279876709</v>
+        <v>9.64282894134521</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1547" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1555" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1562" t="n">
-        <v>9.6428279876709</v>
+        <v>9.64282894134521</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1563" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1571" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1572" t="n">
-        <v>10.3808002471924</v>
+        <v>10.3807992935181</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1575" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1576" t="n">
-        <v>11.1187715530396</v>
+        <v>11.1187705993652</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1582" t="n">
-        <v>11.1679697036743</v>
+        <v>11.16796875</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>11.5</v>
       </c>
       <c r="G1584" t="n">
-        <v>11.3155641555786</v>
+        <v>11.3155632019043</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1585" t="n">
-        <v>11.512354850769</v>
+        <v>11.5123558044434</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>13</v>
       </c>
       <c r="G1591" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1592" t="n">
-        <v>12.49631690979</v>
+        <v>12.4963178634644</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1594" t="n">
-        <v>12.8407049179077</v>
+        <v>12.8407039642334</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1595" t="n">
-        <v>12.8407049179077</v>
+        <v>12.8407039642334</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>13</v>
       </c>
       <c r="G1596" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>13</v>
       </c>
       <c r="G1607" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>13.5</v>
       </c>
       <c r="G1609" t="n">
-        <v>13.2834873199463</v>
+        <v>13.2834882736206</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1611" t="n">
-        <v>12.8407049179077</v>
+        <v>12.8407039642334</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>13</v>
       </c>
       <c r="G1612" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>13</v>
       </c>
       <c r="G1613" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>13</v>
       </c>
       <c r="G1614" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1615" t="n">
-        <v>12.7423086166382</v>
+        <v>12.7423076629639</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1616" t="n">
-        <v>12.49631690979</v>
+        <v>12.4963178634644</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>11.3647623062134</v>
+        <v>11.3647613525391</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>12.25</v>
       </c>
       <c r="G1625" t="n">
-        <v>12.0535345077515</v>
+        <v>12.0535354614258</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1636" t="n">
-        <v>11.1187715530396</v>
+        <v>11.1187705993652</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1638" t="n">
-        <v>11.1187715530396</v>
+        <v>11.1187705993652</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1639" t="n">
-        <v>10.7743844985962</v>
+        <v>10.7743835449219</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1646" t="n">
-        <v>10.7251863479614</v>
+        <v>10.7251853942871</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1647" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>10.5</v>
       </c>
       <c r="G1650" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1651" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1652" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1653" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1655" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>10.5</v>
       </c>
       <c r="G1656" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1658" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1659" t="n">
-        <v>10.3808002471924</v>
+        <v>10.3807992935181</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>10.5</v>
       </c>
       <c r="G1660" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>10.5</v>
       </c>
       <c r="G1661" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>10.5</v>
       </c>
       <c r="G1662" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1666" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1668" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1671" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>10.5</v>
       </c>
       <c r="G1674" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1676" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1679" t="n">
-        <v>10.3808002471924</v>
+        <v>10.3807992935181</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1688" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1691" t="n">
-        <v>10.7251863479614</v>
+        <v>10.7251853942871</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1698" t="n">
-        <v>10.7251863479614</v>
+        <v>10.7251853942871</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1705" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>10.5</v>
       </c>
       <c r="G1706" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1707" t="n">
-        <v>10.3808002471924</v>
+        <v>10.3807992935181</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1709" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1712" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>10.5</v>
       </c>
       <c r="G1714" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1718" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1724" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1728" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -54842,6 +54842,32 @@
         <v>8.84000015258789</v>
       </c>
       <c r="H2095" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2096" t="n">
+        <v>2852</v>
+      </c>
+      <c r="C2096" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>8.73999977111816</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="G2096" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="H2096" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.87050008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>2.73570680618286</v>
+        <v>2.7357063293457</v>
       </c>
       <c r="H3" t="n">
         <v>364500</v>
@@ -514,7 +514,7 @@
         <v>2.91050004959106</v>
       </c>
       <c r="G5" t="n">
-        <v>2.77382802963257</v>
+        <v>2.77382826805115</v>
       </c>
       <c r="H5" t="n">
         <v>88500</v>
@@ -572,7 +572,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G7" t="n">
-        <v>2.80670809745789</v>
+        <v>2.80670785903931</v>
       </c>
       <c r="H7" t="n">
         <v>71500</v>
@@ -601,7 +601,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84006452560425</v>
+        <v>2.84006428718567</v>
       </c>
       <c r="H8" t="n">
         <v>25000</v>
@@ -630,7 +630,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912489891052</v>
       </c>
       <c r="H9" t="n">
         <v>26000</v>
@@ -688,7 +688,7 @@
         <v>2.9614999294281</v>
       </c>
       <c r="G11" t="n">
-        <v>2.82243299484253</v>
+        <v>2.82243275642395</v>
       </c>
       <c r="H11" t="n">
         <v>20000</v>
@@ -717,7 +717,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G12" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H12" t="n">
         <v>7500</v>
@@ -746,7 +746,7 @@
         <v>2.98900008201599</v>
       </c>
       <c r="G13" t="n">
-        <v>2.84864187240601</v>
+        <v>2.84864211082458</v>
       </c>
       <c r="H13" t="n">
         <v>8500</v>
@@ -775,7 +775,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G14" t="n">
-        <v>2.76572728157043</v>
+        <v>2.76572680473328</v>
       </c>
       <c r="H14" t="n">
         <v>5500</v>
@@ -804,7 +804,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912489891052</v>
       </c>
       <c r="H15" t="n">
         <v>22500</v>
@@ -862,7 +862,7 @@
         <v>2.93099999427795</v>
       </c>
       <c r="G17" t="n">
-        <v>2.79336547851562</v>
+        <v>2.79336524009705</v>
       </c>
       <c r="H17" t="n">
         <v>5000</v>
@@ -891,7 +891,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78764748573303</v>
+        <v>2.78764724731445</v>
       </c>
       <c r="H18" t="n">
         <v>10000</v>
@@ -920,7 +920,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H19" t="n">
         <v>8000</v>
@@ -949,7 +949,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H20" t="n">
         <v>2000</v>
@@ -1007,7 +1007,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H22" t="n">
         <v>6000</v>
@@ -1036,7 +1036,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H23" t="n">
         <v>3500</v>
@@ -1210,7 +1210,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G29" t="n">
-        <v>2.61895871162415</v>
+        <v>2.61895895004272</v>
       </c>
       <c r="H29" t="n">
         <v>14500</v>
@@ -1239,7 +1239,7 @@
         <v>2.75</v>
       </c>
       <c r="G30" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H30" t="n">
         <v>6500</v>
@@ -1268,7 +1268,7 @@
         <v>2.75</v>
       </c>
       <c r="G31" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>2.75</v>
       </c>
       <c r="G32" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H32" t="n">
         <v>1500</v>
@@ -1326,7 +1326,7 @@
         <v>2.75</v>
       </c>
       <c r="G33" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H33" t="n">
         <v>1500</v>
@@ -1355,7 +1355,7 @@
         <v>2.75</v>
       </c>
       <c r="G34" t="n">
-        <v>2.62086486816406</v>
+        <v>2.62086510658264</v>
       </c>
       <c r="H34" t="n">
         <v>3500</v>
@@ -1384,7 +1384,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G35" t="n">
-        <v>2.67232871055603</v>
+        <v>2.67232918739319</v>
       </c>
       <c r="H35" t="n">
         <v>5500</v>
@@ -1413,7 +1413,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.6780469417572</v>
+        <v>2.67804718017578</v>
       </c>
       <c r="H36" t="n">
         <v>18500</v>
@@ -1442,7 +1442,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288173675537</v>
       </c>
       <c r="H37" t="n">
         <v>23500</v>
@@ -1471,7 +1471,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G38" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H38" t="n">
         <v>17000</v>
@@ -1500,7 +1500,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H39" t="n">
         <v>21500</v>
@@ -1529,7 +1529,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H40" t="n">
         <v>20000</v>
@@ -1558,7 +1558,7 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912489891052</v>
       </c>
       <c r="H41" t="n">
         <v>18500</v>
@@ -1645,7 +1645,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.7924120426178</v>
+        <v>2.79241228103638</v>
       </c>
       <c r="H44" t="n">
         <v>1500</v>
@@ -1674,7 +1674,7 @@
         <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912489891052</v>
       </c>
       <c r="H45" t="n">
         <v>18000</v>
@@ -1732,7 +1732,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87818622589111</v>
+        <v>2.87818646430969</v>
       </c>
       <c r="H47" t="n">
         <v>9000</v>
@@ -1848,7 +1848,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G51" t="n">
-        <v>2.92583823204041</v>
+        <v>2.92583799362183</v>
       </c>
       <c r="H51" t="n">
         <v>9000</v>
@@ -1877,7 +1877,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01161170005798</v>
+        <v>3.01161193847656</v>
       </c>
       <c r="H52" t="n">
         <v>15500</v>
@@ -1906,7 +1906,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.00208163261414</v>
+        <v>3.00208139419556</v>
       </c>
       <c r="H53" t="n">
         <v>58000</v>
@@ -1964,7 +1964,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>3.00208163261414</v>
+        <v>3.00208139419556</v>
       </c>
       <c r="H55" t="n">
         <v>5500</v>
@@ -2080,7 +2080,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>2.97348976135254</v>
+        <v>2.97348999977112</v>
       </c>
       <c r="H59" t="n">
         <v>7500</v>
@@ -2109,7 +2109,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G60" t="n">
-        <v>2.97348976135254</v>
+        <v>2.97348999977112</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2254,7 +2254,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>2.87818622589111</v>
+        <v>2.87818646430969</v>
       </c>
       <c r="H65" t="n">
         <v>4000</v>
@@ -2341,7 +2341,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H68" t="n">
         <v>18500</v>
@@ -2370,7 +2370,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G69" t="n">
-        <v>2.84482955932617</v>
+        <v>2.84482932090759</v>
       </c>
       <c r="H69" t="n">
         <v>1500</v>
@@ -2428,7 +2428,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80670809745789</v>
+        <v>2.80670785903931</v>
       </c>
       <c r="H71" t="n">
         <v>8000</v>
@@ -2457,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912489891052</v>
       </c>
       <c r="H72" t="n">
         <v>7500</v>
@@ -2486,7 +2486,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H73" t="n">
         <v>6000</v>
@@ -2515,7 +2515,7 @@
         <v>3</v>
       </c>
       <c r="G74" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912489891052</v>
       </c>
       <c r="H74" t="n">
         <v>3000</v>
@@ -2544,7 +2544,7 @@
         <v>3</v>
       </c>
       <c r="G75" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912489891052</v>
       </c>
       <c r="H75" t="n">
         <v>3000</v>
@@ -2573,7 +2573,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G76" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288173675537</v>
       </c>
       <c r="H76" t="n">
         <v>4000</v>
@@ -2602,7 +2602,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H77" t="n">
         <v>10000</v>
@@ -2631,7 +2631,7 @@
         <v>2.89100003242493</v>
       </c>
       <c r="G78" t="n">
-        <v>2.75524377822876</v>
+        <v>2.7552433013916</v>
       </c>
       <c r="H78" t="n">
         <v>23000</v>
@@ -2660,7 +2660,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H79" t="n">
         <v>12000</v>
@@ -2689,7 +2689,7 @@
         <v>2.90549993515015</v>
       </c>
       <c r="G80" t="n">
-        <v>2.76906251907349</v>
+        <v>2.76906275749207</v>
       </c>
       <c r="H80" t="n">
         <v>4500</v>
@@ -2718,7 +2718,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H81" t="n">
         <v>3000</v>
@@ -2747,7 +2747,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>2.77335143089294</v>
+        <v>2.77335166931152</v>
       </c>
       <c r="H82" t="n">
         <v>1000</v>
@@ -2805,7 +2805,7 @@
         <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912489891052</v>
       </c>
       <c r="H84" t="n">
         <v>12500</v>
@@ -2892,7 +2892,7 @@
         <v>2.99950003623962</v>
       </c>
       <c r="G87" t="n">
-        <v>2.85864877700806</v>
+        <v>2.85864901542664</v>
       </c>
       <c r="H87" t="n">
         <v>14000</v>
@@ -2921,7 +2921,7 @@
         <v>3.04900002479553</v>
       </c>
       <c r="G88" t="n">
-        <v>2.90582418441772</v>
+        <v>2.9058244228363</v>
       </c>
       <c r="H88" t="n">
         <v>2500</v>
@@ -2950,7 +2950,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G89" t="n">
-        <v>2.85054779052734</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H89" t="n">
         <v>3000</v>
@@ -2979,7 +2979,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G90" t="n">
-        <v>2.85054779052734</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H90" t="n">
         <v>4500</v>
@@ -3008,7 +3008,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G91" t="n">
-        <v>2.85054779052734</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>2.93050003051758</v>
       </c>
       <c r="G92" t="n">
-        <v>2.79288911819458</v>
+        <v>2.79288864135742</v>
       </c>
       <c r="H92" t="n">
         <v>500</v>
@@ -3124,7 +3124,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G95" t="n">
-        <v>2.82576870918274</v>
+        <v>2.82576894760132</v>
       </c>
       <c r="H95" t="n">
         <v>3500</v>
@@ -3153,7 +3153,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G96" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H96" t="n">
         <v>1000</v>
@@ -3182,7 +3182,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G97" t="n">
-        <v>2.83815813064575</v>
+        <v>2.83815836906433</v>
       </c>
       <c r="H97" t="n">
         <v>15000</v>
@@ -3211,7 +3211,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G98" t="n">
-        <v>2.83815813064575</v>
+        <v>2.83815836906433</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H99" t="n">
         <v>3000</v>
@@ -3269,7 +3269,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G101" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H101" t="n">
         <v>3000</v>
@@ -3327,7 +3327,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>2.98850011825562</v>
       </c>
       <c r="G105" t="n">
-        <v>2.84816575050354</v>
+        <v>2.84816527366638</v>
       </c>
       <c r="H105" t="n">
         <v>2500</v>
@@ -3443,7 +3443,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H106" t="n">
         <v>2000</v>
@@ -3472,7 +3472,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G107" t="n">
-        <v>2.7638213634491</v>
+        <v>2.76382112503052</v>
       </c>
       <c r="H107" t="n">
         <v>9500</v>
@@ -3501,7 +3501,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.82100391387939</v>
+        <v>2.82100367546082</v>
       </c>
       <c r="H108" t="n">
         <v>10000</v>
@@ -3588,7 +3588,7 @@
         <v>2.91700005531311</v>
       </c>
       <c r="G111" t="n">
-        <v>2.78002285957336</v>
+        <v>2.78002262115479</v>
       </c>
       <c r="H111" t="n">
         <v>16500</v>
@@ -3617,7 +3617,7 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912489891052</v>
       </c>
       <c r="H112" t="n">
         <v>8000</v>
@@ -3646,7 +3646,7 @@
         <v>3.05949997901917</v>
       </c>
       <c r="G113" t="n">
-        <v>2.91583132743835</v>
+        <v>2.91583156585693</v>
       </c>
       <c r="H113" t="n">
         <v>17500</v>
@@ -3675,7 +3675,7 @@
         <v>3.05949997901917</v>
       </c>
       <c r="G114" t="n">
-        <v>2.91583132743835</v>
+        <v>2.91583156585693</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>2.92549991607666</v>
       </c>
       <c r="G117" t="n">
-        <v>2.7881236076355</v>
+        <v>2.78812336921692</v>
       </c>
       <c r="H117" t="n">
         <v>9000</v>
@@ -3820,7 +3820,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G119" t="n">
-        <v>2.8543598651886</v>
+        <v>2.85436010360718</v>
       </c>
       <c r="H119" t="n">
         <v>2500</v>
@@ -3849,7 +3849,7 @@
         <v>3</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912489891052</v>
       </c>
       <c r="H120" t="n">
         <v>2000</v>
@@ -3878,7 +3878,7 @@
         <v>3</v>
       </c>
       <c r="G121" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912489891052</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>2.95149993896484</v>
       </c>
       <c r="G122" t="n">
-        <v>2.81290245056152</v>
+        <v>2.81290292739868</v>
       </c>
       <c r="H122" t="n">
         <v>4500</v>
@@ -3936,7 +3936,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H123" t="n">
         <v>500</v>
@@ -3965,7 +3965,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G126" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H126" t="n">
         <v>1000</v>
@@ -4052,7 +4052,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288173675537</v>
       </c>
       <c r="H129" t="n">
         <v>9000</v>
@@ -4139,7 +4139,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>2.78288197517395</v>
+        <v>2.78288173675537</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>2.92249989509583</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78526449203491</v>
+        <v>2.78526473045349</v>
       </c>
       <c r="H133" t="n">
         <v>1500</v>
@@ -4371,7 +4371,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G138" t="n">
-        <v>2.7924120426178</v>
+        <v>2.79241228103638</v>
       </c>
       <c r="H138" t="n">
         <v>6500</v>
@@ -4400,7 +4400,7 @@
         <v>2.95700001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.81814432144165</v>
+        <v>2.81814479827881</v>
       </c>
       <c r="H139" t="n">
         <v>4500</v>
@@ -4429,7 +4429,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G140" t="n">
-        <v>2.87818622589111</v>
+        <v>2.87818646430969</v>
       </c>
       <c r="H140" t="n">
         <v>11500</v>
@@ -4458,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="G141" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912489891052</v>
       </c>
       <c r="H141" t="n">
         <v>500</v>
@@ -4487,7 +4487,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G142" t="n">
-        <v>2.88390445709229</v>
+        <v>2.88390421867371</v>
       </c>
       <c r="H142" t="n">
         <v>500</v>
@@ -4516,7 +4516,7 @@
         <v>3</v>
       </c>
       <c r="G143" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912489891052</v>
       </c>
       <c r="H143" t="n">
         <v>13500</v>
@@ -4690,7 +4690,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>2.9830207824707</v>
+        <v>2.98302102088928</v>
       </c>
       <c r="H149" t="n">
         <v>31500</v>
@@ -4748,7 +4748,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>3.05926418304443</v>
+        <v>3.05926394462585</v>
       </c>
       <c r="H151" t="n">
         <v>12000</v>
@@ -4806,7 +4806,7 @@
         <v>3.32949995994568</v>
       </c>
       <c r="G153" t="n">
-        <v>3.17315220832825</v>
+        <v>3.17315268516541</v>
       </c>
       <c r="H153" t="n">
         <v>8000</v>
@@ -4835,7 +4835,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G154" t="n">
-        <v>3.24987268447876</v>
+        <v>3.24987244606018</v>
       </c>
       <c r="H154" t="n">
         <v>19000</v>
@@ -4864,7 +4864,7 @@
         <v>3.40949988365173</v>
       </c>
       <c r="G155" t="n">
-        <v>3.24939560890198</v>
+        <v>3.24939584732056</v>
       </c>
       <c r="H155" t="n">
         <v>13000</v>
@@ -4980,7 +4980,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>3.28799414634705</v>
+        <v>3.28799390792847</v>
       </c>
       <c r="H159" t="n">
         <v>11000</v>
@@ -5009,7 +5009,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>3.24034214019775</v>
+        <v>3.24034190177917</v>
       </c>
       <c r="H160" t="n">
         <v>5000</v>
@@ -5067,7 +5067,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G162" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175050735474</v>
       </c>
       <c r="H162" t="n">
         <v>6500</v>
@@ -5125,7 +5125,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175050735474</v>
       </c>
       <c r="H164" t="n">
         <v>3500</v>
@@ -5154,7 +5154,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175050735474</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.2546374797821</v>
+        <v>3.25463771820068</v>
       </c>
       <c r="H166" t="n">
         <v>14000</v>
@@ -5212,7 +5212,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>3.26893353462219</v>
+        <v>3.26893329620361</v>
       </c>
       <c r="H167" t="n">
         <v>14500</v>
@@ -5328,7 +5328,7 @@
         <v>3.59450006484985</v>
       </c>
       <c r="G171" t="n">
-        <v>3.42570829391479</v>
+        <v>3.42570853233337</v>
       </c>
       <c r="H171" t="n">
         <v>61000</v>
@@ -5357,7 +5357,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G172" t="n">
-        <v>3.50242877006531</v>
+        <v>3.50242829322815</v>
       </c>
       <c r="H172" t="n">
         <v>10000</v>
@@ -5386,7 +5386,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>3.58343696594238</v>
+        <v>3.58343720436096</v>
       </c>
       <c r="H173" t="n">
         <v>6500</v>
@@ -5473,7 +5473,7 @@
         <v>3.75</v>
       </c>
       <c r="G176" t="n">
-        <v>3.57390713691711</v>
+        <v>3.57390689849854</v>
       </c>
       <c r="H176" t="n">
         <v>6500</v>
@@ -5502,7 +5502,7 @@
         <v>3.75</v>
       </c>
       <c r="G177" t="n">
-        <v>3.57390713691711</v>
+        <v>3.57390689849854</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G178" t="n">
-        <v>3.7645149230957</v>
+        <v>3.76451516151428</v>
       </c>
       <c r="H178" t="n">
         <v>4000</v>
@@ -5560,7 +5560,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>3.84075856208801</v>
+        <v>3.84075808525085</v>
       </c>
       <c r="H179" t="n">
         <v>10000</v>
@@ -5589,7 +5589,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>3.75498485565186</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H180" t="n">
         <v>24000</v>
@@ -5618,7 +5618,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G181" t="n">
-        <v>3.75498485565186</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H181" t="n">
         <v>10000</v>
@@ -5647,7 +5647,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G182" t="n">
-        <v>3.62155842781067</v>
+        <v>3.62155890464783</v>
       </c>
       <c r="H182" t="n">
         <v>13500</v>
@@ -5676,7 +5676,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G183" t="n">
-        <v>3.5453155040741</v>
+        <v>3.54531526565552</v>
       </c>
       <c r="H183" t="n">
         <v>19500</v>
@@ -5705,7 +5705,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>3.62155842781067</v>
+        <v>3.62155890464783</v>
       </c>
       <c r="H184" t="n">
         <v>9500</v>
@@ -5850,7 +5850,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>3.65015029907227</v>
+        <v>3.65015006065369</v>
       </c>
       <c r="H189" t="n">
         <v>4350</v>
@@ -5908,7 +5908,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>3.84075856208801</v>
+        <v>3.84075808525085</v>
       </c>
       <c r="H191" t="n">
         <v>18218</v>
@@ -5937,7 +5937,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G192" t="n">
-        <v>3.84075856208801</v>
+        <v>3.84075808525085</v>
       </c>
       <c r="H192" t="n">
         <v>2550</v>
@@ -5966,7 +5966,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>3.95512342453003</v>
+        <v>3.95512390136719</v>
       </c>
       <c r="H193" t="n">
         <v>3120</v>
@@ -5995,7 +5995,7 @@
         <v>4</v>
       </c>
       <c r="G194" t="n">
-        <v>3.81216716766357</v>
+        <v>3.812166929245</v>
       </c>
       <c r="H194" t="n">
         <v>9902</v>
@@ -6024,7 +6024,7 @@
         <v>4</v>
       </c>
       <c r="G195" t="n">
-        <v>3.81216716766357</v>
+        <v>3.812166929245</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G196" t="n">
-        <v>3.80263638496399</v>
+        <v>3.80263662338257</v>
       </c>
       <c r="H196" t="n">
         <v>3767</v>
@@ -6082,7 +6082,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>3.85028862953186</v>
+        <v>3.85028910636902</v>
       </c>
       <c r="H197" t="n">
         <v>810</v>
@@ -6111,7 +6111,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>3.75498485565186</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H198" t="n">
         <v>10740</v>
@@ -6140,7 +6140,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>3.75498485565186</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G200" t="n">
-        <v>3.77414298057556</v>
+        <v>3.77414274215698</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>4</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83161735534668</v>
+        <v>3.83161687850952</v>
       </c>
       <c r="H201" t="n">
         <v>14910</v>
@@ -6227,7 +6227,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>3.92740750312805</v>
+        <v>3.92740702629089</v>
       </c>
       <c r="H202" t="n">
         <v>6500</v>
@@ -6256,7 +6256,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H203" t="n">
         <v>3200</v>
@@ -6314,7 +6314,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G205" t="n">
-        <v>3.82203769683838</v>
+        <v>3.82203793525696</v>
       </c>
       <c r="H205" t="n">
         <v>5100</v>
@@ -6372,7 +6372,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>3.77414298057556</v>
+        <v>3.77414274215698</v>
       </c>
       <c r="H207" t="n">
         <v>6680</v>
@@ -6401,7 +6401,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>3.70708966255188</v>
+        <v>3.70708918571472</v>
       </c>
       <c r="H208" t="n">
         <v>1000</v>
@@ -6430,7 +6430,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G209" t="n">
-        <v>3.69751000404358</v>
+        <v>3.69751024246216</v>
       </c>
       <c r="H209" t="n">
         <v>500</v>
@@ -6459,7 +6459,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G210" t="n">
-        <v>3.69751000404358</v>
+        <v>3.69751024246216</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>3.83161735534668</v>
+        <v>3.83161687850952</v>
       </c>
       <c r="H211" t="n">
         <v>12500</v>
@@ -6517,7 +6517,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H212" t="n">
         <v>12189</v>
@@ -6546,7 +6546,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>3.78372168540955</v>
+        <v>3.78372192382812</v>
       </c>
       <c r="H214" t="n">
         <v>3800</v>
@@ -6604,7 +6604,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H215" t="n">
         <v>1090</v>
@@ -6633,7 +6633,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H216" t="n">
         <v>1000</v>
@@ -6662,7 +6662,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.93698620796204</v>
+        <v>3.93698692321777</v>
       </c>
       <c r="H217" t="n">
         <v>4860</v>
@@ -6691,7 +6691,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G218" t="n">
-        <v>3.9465651512146</v>
+        <v>3.94656562805176</v>
       </c>
       <c r="H218" t="n">
         <v>18231</v>
@@ -6749,7 +6749,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>4.03277730941772</v>
+        <v>4.03277683258057</v>
       </c>
       <c r="H220" t="n">
         <v>4360</v>
@@ -6778,7 +6778,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.2147798538208</v>
+        <v>4.21477842330933</v>
       </c>
       <c r="H221" t="n">
         <v>5788</v>
@@ -6865,7 +6865,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G224" t="n">
-        <v>4.19562005996704</v>
+        <v>4.19562101364136</v>
       </c>
       <c r="H224" t="n">
         <v>6059</v>
@@ -6894,7 +6894,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G225" t="n">
-        <v>4.39678144454956</v>
+        <v>4.3967809677124</v>
       </c>
       <c r="H225" t="n">
         <v>12211</v>
@@ -6952,7 +6952,7 @@
         <v>4.5</v>
       </c>
       <c r="G227" t="n">
-        <v>4.31056928634644</v>
+        <v>4.31056880950928</v>
       </c>
       <c r="H227" t="n">
         <v>15408</v>
@@ -6981,7 +6981,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>4.45425510406494</v>
+        <v>4.45425415039062</v>
       </c>
       <c r="H228" t="n">
         <v>14610</v>
@@ -7039,7 +7039,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>4.38720083236694</v>
+        <v>4.3872013092041</v>
       </c>
       <c r="H230" t="n">
         <v>3150</v>
@@ -7068,7 +7068,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G231" t="n">
-        <v>4.48299169540405</v>
+        <v>4.48299264907837</v>
       </c>
       <c r="H231" t="n">
         <v>3020</v>
@@ -7126,7 +7126,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H233" t="n">
         <v>20142</v>
@@ -7155,7 +7155,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>4.66499376296997</v>
+        <v>4.66499328613281</v>
       </c>
       <c r="H234" t="n">
         <v>11495</v>
@@ -7213,7 +7213,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>5.07689237594604</v>
+        <v>5.0768928527832</v>
       </c>
       <c r="H236" t="n">
         <v>74862</v>
@@ -7300,7 +7300,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>4.80868005752563</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H239" t="n">
         <v>29610</v>
@@ -7387,7 +7387,7 @@
         <v>5</v>
       </c>
       <c r="G242" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H242" t="n">
         <v>16194</v>
@@ -7416,7 +7416,7 @@
         <v>5</v>
       </c>
       <c r="G243" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H243" t="n">
         <v>18850</v>
@@ -7445,7 +7445,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H244" t="n">
         <v>3855</v>
@@ -7474,7 +7474,7 @@
         <v>5</v>
       </c>
       <c r="G245" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H245" t="n">
         <v>1200</v>
@@ -7503,7 +7503,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>4.71288871765137</v>
+        <v>4.71288967132568</v>
       </c>
       <c r="H246" t="n">
         <v>5934</v>
@@ -7532,7 +7532,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>4.71288871765137</v>
+        <v>4.71288967132568</v>
       </c>
       <c r="H247" t="n">
         <v>4150</v>
@@ -7561,7 +7561,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G248" t="n">
-        <v>4.71288871765137</v>
+        <v>4.71288967132568</v>
       </c>
       <c r="H248" t="n">
         <v>3000</v>
@@ -7619,7 +7619,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G250" t="n">
-        <v>4.65541505813599</v>
+        <v>4.65541553497314</v>
       </c>
       <c r="H250" t="n">
         <v>750</v>
@@ -7648,7 +7648,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G251" t="n">
-        <v>4.65541505813599</v>
+        <v>4.65541553497314</v>
       </c>
       <c r="H251" t="n">
         <v>1500</v>
@@ -7706,7 +7706,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H253" t="n">
         <v>3900</v>
@@ -7764,7 +7764,7 @@
         <v>5</v>
       </c>
       <c r="G255" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H255" t="n">
         <v>13400</v>
@@ -7793,7 +7793,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G256" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457294464111</v>
       </c>
       <c r="H256" t="n">
         <v>960</v>
@@ -7822,7 +7822,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G257" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457294464111</v>
       </c>
       <c r="H257" t="n">
         <v>1620</v>
@@ -7851,7 +7851,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G258" t="n">
-        <v>4.48299169540405</v>
+        <v>4.48299264907837</v>
       </c>
       <c r="H258" t="n">
         <v>11514</v>
@@ -7909,7 +7909,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G260" t="n">
-        <v>4.66499376296997</v>
+        <v>4.66499328613281</v>
       </c>
       <c r="H260" t="n">
         <v>1936</v>
@@ -7938,7 +7938,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>4.66499376296997</v>
+        <v>4.66499328613281</v>
       </c>
       <c r="H261" t="n">
         <v>12495</v>
@@ -7967,7 +7967,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G262" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457294464111</v>
       </c>
       <c r="H262" t="n">
         <v>3699</v>
@@ -7996,7 +7996,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583492279053</v>
       </c>
       <c r="H263" t="n">
         <v>581</v>
@@ -8025,7 +8025,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G264" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H264" t="n">
         <v>514</v>
@@ -8054,7 +8054,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G265" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H265" t="n">
         <v>4435</v>
@@ -8083,7 +8083,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G266" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H266" t="n">
         <v>1940</v>
@@ -8112,7 +8112,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>4.59794044494629</v>
+        <v>4.59794092178345</v>
       </c>
       <c r="H267" t="n">
         <v>1400</v>
@@ -8141,7 +8141,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>4.59794044494629</v>
+        <v>4.59794092178345</v>
       </c>
       <c r="H268" t="n">
         <v>1635</v>
@@ -8170,7 +8170,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G269" t="n">
-        <v>4.59794044494629</v>
+        <v>4.59794092178345</v>
       </c>
       <c r="H269" t="n">
         <v>4049</v>
@@ -8286,7 +8286,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>4.57878303527832</v>
+        <v>4.57878255844116</v>
       </c>
       <c r="H273" t="n">
         <v>700</v>
@@ -8315,7 +8315,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>4.76078414916992</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H274" t="n">
         <v>4784</v>
@@ -8344,7 +8344,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G275" t="n">
-        <v>4.76078414916992</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>4.62667751312256</v>
+        <v>4.62667798995972</v>
       </c>
       <c r="H277" t="n">
         <v>5557</v>
@@ -8431,7 +8431,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G278" t="n">
-        <v>4.65541505813599</v>
+        <v>4.65541553497314</v>
       </c>
       <c r="H278" t="n">
         <v>500</v>
@@ -8460,7 +8460,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G279" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457294464111</v>
       </c>
       <c r="H279" t="n">
         <v>4220</v>
@@ -8489,7 +8489,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G280" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457294464111</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>4.71288871765137</v>
+        <v>4.71288967132568</v>
       </c>
       <c r="H281" t="n">
         <v>1663</v>
@@ -8547,7 +8547,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583492279053</v>
       </c>
       <c r="H282" t="n">
         <v>2700</v>
@@ -8576,7 +8576,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583492279053</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H284" t="n">
         <v>1762</v>
@@ -8634,7 +8634,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G285" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H285" t="n">
         <v>1130</v>
@@ -8663,7 +8663,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H286" t="n">
         <v>3002</v>
@@ -8692,7 +8692,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G289" t="n">
-        <v>4.80868005752563</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H289" t="n">
         <v>13078</v>
@@ -8808,7 +8808,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>4.80868005752563</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H291" t="n">
         <v>3150</v>
@@ -8837,7 +8837,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>4.80868005752563</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H293" t="n">
         <v>1400</v>
@@ -8895,7 +8895,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G294" t="n">
-        <v>4.76078414916992</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H294" t="n">
         <v>2200</v>
@@ -8924,7 +8924,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457294464111</v>
       </c>
       <c r="H295" t="n">
         <v>2811</v>
@@ -8953,7 +8953,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457294464111</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G298" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H298" t="n">
         <v>400</v>
@@ -9040,7 +9040,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G299" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H299" t="n">
         <v>492</v>
@@ -9069,7 +9069,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G300" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H300" t="n">
         <v>5266</v>
@@ -9098,7 +9098,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G301" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H301" t="n">
         <v>150</v>
@@ -9127,7 +9127,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G302" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G303" t="n">
-        <v>4.74162626266479</v>
+        <v>4.74162578582764</v>
       </c>
       <c r="H303" t="n">
         <v>510</v>
@@ -9185,7 +9185,7 @@
         <v>5</v>
       </c>
       <c r="G304" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H304" t="n">
         <v>25540</v>
@@ -9214,7 +9214,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H305" t="n">
         <v>4750</v>
@@ -9243,7 +9243,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G306" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H306" t="n">
         <v>3900</v>
@@ -9301,7 +9301,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>4.80868005752563</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H308" t="n">
         <v>2465</v>
@@ -9388,7 +9388,7 @@
         <v>5</v>
       </c>
       <c r="G311" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H311" t="n">
         <v>5186</v>
@@ -9417,7 +9417,7 @@
         <v>5</v>
       </c>
       <c r="G312" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.76078414916992</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H315" t="n">
         <v>2985</v>
@@ -9533,7 +9533,7 @@
         <v>5</v>
       </c>
       <c r="G316" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H316" t="n">
         <v>402</v>
@@ -9620,7 +9620,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G319" t="n">
-        <v>4.6937313079834</v>
+        <v>4.69373083114624</v>
       </c>
       <c r="H319" t="n">
         <v>1270</v>
@@ -9649,7 +9649,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H320" t="n">
         <v>100</v>
@@ -9678,7 +9678,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>5</v>
       </c>
       <c r="G322" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H322" t="n">
         <v>3400</v>
@@ -9736,7 +9736,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H323" t="n">
         <v>54154</v>
@@ -9765,7 +9765,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>4.80868005752563</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H324" t="n">
         <v>26052</v>
@@ -9794,7 +9794,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H325" t="n">
         <v>1040</v>
@@ -9823,7 +9823,7 @@
         <v>5</v>
       </c>
       <c r="G326" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H326" t="n">
         <v>3000</v>
@@ -9881,7 +9881,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H328" t="n">
         <v>170</v>
@@ -9910,7 +9910,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>5</v>
       </c>
       <c r="G330" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H330" t="n">
         <v>7750</v>
@@ -9997,7 +9997,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H332" t="n">
         <v>4683</v>
@@ -10026,7 +10026,7 @@
         <v>5</v>
       </c>
       <c r="G333" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H333" t="n">
         <v>1125</v>
@@ -10113,7 +10113,7 @@
         <v>5</v>
       </c>
       <c r="G336" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H336" t="n">
         <v>17100</v>
@@ -10142,7 +10142,7 @@
         <v>5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952169418335</v>
       </c>
       <c r="H337" t="n">
         <v>12410</v>
@@ -10171,7 +10171,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>4.82783699035645</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H338" t="n">
         <v>6710</v>
@@ -10229,7 +10229,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.98110198974609</v>
+        <v>4.98110151290894</v>
       </c>
       <c r="H340" t="n">
         <v>8709</v>
@@ -10287,7 +10287,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>4.98110198974609</v>
+        <v>4.98110151290894</v>
       </c>
       <c r="H342" t="n">
         <v>12262</v>
@@ -10345,7 +10345,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.13436698913574</v>
+        <v>5.13436651229858</v>
       </c>
       <c r="H344" t="n">
         <v>6260</v>
@@ -10403,7 +10403,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.11520862579346</v>
+        <v>5.11520910263062</v>
       </c>
       <c r="H346" t="n">
         <v>11091</v>
@@ -10461,7 +10461,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G348" t="n">
-        <v>5.32594728469849</v>
+        <v>5.32594776153564</v>
       </c>
       <c r="H348" t="n">
         <v>20019</v>
@@ -10490,7 +10490,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G349" t="n">
-        <v>5.21099948883057</v>
+        <v>5.21099901199341</v>
       </c>
       <c r="H349" t="n">
         <v>3837</v>
@@ -10519,7 +10519,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.13436698913574</v>
+        <v>5.13436651229858</v>
       </c>
       <c r="H350" t="n">
         <v>5572</v>
@@ -10548,7 +10548,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G351" t="n">
-        <v>5.13436698913574</v>
+        <v>5.13436651229858</v>
       </c>
       <c r="H351" t="n">
         <v>2712</v>
@@ -10577,7 +10577,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G352" t="n">
-        <v>5.07689237594604</v>
+        <v>5.0768928527832</v>
       </c>
       <c r="H352" t="n">
         <v>14027</v>
@@ -10606,7 +10606,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G353" t="n">
-        <v>5.09605073928833</v>
+        <v>5.09605121612549</v>
       </c>
       <c r="H353" t="n">
         <v>1649</v>
@@ -10664,7 +10664,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G355" t="n">
-        <v>5.05773496627808</v>
+        <v>5.05773448944092</v>
       </c>
       <c r="H355" t="n">
         <v>7380</v>
@@ -10693,7 +10693,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>5.07689237594604</v>
+        <v>5.0768928527832</v>
       </c>
       <c r="H356" t="n">
         <v>10934</v>
@@ -10780,7 +10780,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G359" t="n">
-        <v>5.01941776275635</v>
+        <v>5.01941823959351</v>
       </c>
       <c r="H359" t="n">
         <v>5962</v>
@@ -10809,7 +10809,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>5.07689237594604</v>
+        <v>5.0768928527832</v>
       </c>
       <c r="H360" t="n">
         <v>2670</v>
@@ -10838,7 +10838,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G361" t="n">
-        <v>5.21099948883057</v>
+        <v>5.21099901199341</v>
       </c>
       <c r="H361" t="n">
         <v>5616</v>
@@ -10867,7 +10867,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>5.07689237594604</v>
+        <v>5.0768928527832</v>
       </c>
       <c r="H362" t="n">
         <v>2700</v>
@@ -10896,7 +10896,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.13436698913574</v>
+        <v>5.13436651229858</v>
       </c>
       <c r="H363" t="n">
         <v>9005</v>
@@ -10925,7 +10925,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G364" t="n">
-        <v>5.15352439880371</v>
+        <v>5.15352535247803</v>
       </c>
       <c r="H364" t="n">
         <v>6000</v>
@@ -10954,7 +10954,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>5.32594728469849</v>
+        <v>5.32594776153564</v>
       </c>
       <c r="H365" t="n">
         <v>16013</v>
@@ -11041,7 +11041,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G368" t="n">
-        <v>5.47921228408813</v>
+        <v>5.47921133041382</v>
       </c>
       <c r="H368" t="n">
         <v>12600</v>
@@ -11186,7 +11186,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>5.84321546554565</v>
+        <v>5.84321641921997</v>
       </c>
       <c r="H373" t="n">
         <v>42690</v>
@@ -11302,7 +11302,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G377" t="n">
-        <v>5.90069007873535</v>
+        <v>5.90069055557251</v>
       </c>
       <c r="H377" t="n">
         <v>7100</v>
@@ -11360,7 +11360,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G379" t="n">
-        <v>5.88153266906738</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H379" t="n">
         <v>9296</v>
@@ -11389,7 +11389,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>5.88153266906738</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H380" t="n">
         <v>9397</v>
@@ -11418,7 +11418,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>5.88153266906738</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H381" t="n">
         <v>7655</v>
@@ -11447,7 +11447,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>5.88153266906738</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H382" t="n">
         <v>6996</v>
@@ -11621,7 +11621,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G388" t="n">
-        <v>5.9773211479187</v>
+        <v>5.97732210159302</v>
       </c>
       <c r="H388" t="n">
         <v>6806</v>
@@ -11650,7 +11650,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>5.82405757904053</v>
+        <v>5.82405805587769</v>
       </c>
       <c r="H389" t="n">
         <v>8803</v>
@@ -11853,7 +11853,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>6.03479719161987</v>
+        <v>6.0347957611084</v>
       </c>
       <c r="H396" t="n">
         <v>4428</v>
@@ -11969,7 +11969,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>6.32216787338257</v>
+        <v>6.32216739654541</v>
       </c>
       <c r="H400" t="n">
         <v>11804</v>
@@ -11998,7 +11998,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G401" t="n">
-        <v>6.36048412322998</v>
+        <v>6.36048460006714</v>
       </c>
       <c r="H401" t="n">
         <v>5726</v>
@@ -12114,7 +12114,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>6.32216787338257</v>
+        <v>6.32216739654541</v>
       </c>
       <c r="H405" t="n">
         <v>37562</v>
@@ -12143,7 +12143,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>6.36048412322998</v>
+        <v>6.36048460006714</v>
       </c>
       <c r="H406" t="n">
         <v>10355</v>
@@ -12172,7 +12172,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G407" t="n">
-        <v>6.4945912361145</v>
+        <v>6.49459075927734</v>
       </c>
       <c r="H407" t="n">
         <v>9368</v>
@@ -12201,7 +12201,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>6.41795778274536</v>
+        <v>6.41795873641968</v>
       </c>
       <c r="H408" t="n">
         <v>8123</v>
@@ -12230,7 +12230,7 @@
         <v>6.5</v>
       </c>
       <c r="G409" t="n">
-        <v>6.22637796401978</v>
+        <v>6.22637701034546</v>
       </c>
       <c r="H409" t="n">
         <v>17409</v>
@@ -12259,7 +12259,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>6.03479719161987</v>
+        <v>6.0347957611084</v>
       </c>
       <c r="H410" t="n">
         <v>28571</v>
@@ -12288,7 +12288,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>6.03479719161987</v>
+        <v>6.0347957611084</v>
       </c>
       <c r="H411" t="n">
         <v>18050</v>
@@ -12317,7 +12317,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G412" t="n">
-        <v>6.03479719161987</v>
+        <v>6.0347957611084</v>
       </c>
       <c r="H412" t="n">
         <v>14848</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.55584526062012</v>
+        <v>5.55584478378296</v>
       </c>
       <c r="H415" t="n">
         <v>21916</v>
@@ -12462,7 +12462,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G417" t="n">
-        <v>5.90069007873535</v>
+        <v>5.90069055557251</v>
       </c>
       <c r="H417" t="n">
         <v>11796</v>
@@ -12491,7 +12491,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>5.72826766967773</v>
+        <v>5.72826719284058</v>
       </c>
       <c r="H418" t="n">
         <v>21988</v>
@@ -12520,7 +12520,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G419" t="n">
-        <v>5.90069007873535</v>
+        <v>5.90069055557251</v>
       </c>
       <c r="H419" t="n">
         <v>4174</v>
@@ -12607,7 +12607,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>5.6707935333252</v>
+        <v>5.67079257965088</v>
       </c>
       <c r="H422" t="n">
         <v>18735</v>
@@ -12636,7 +12636,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G423" t="n">
-        <v>5.6707935333252</v>
+        <v>5.67079257965088</v>
       </c>
       <c r="H423" t="n">
         <v>2501</v>
@@ -12723,7 +12723,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G426" t="n">
-        <v>5.9773211479187</v>
+        <v>5.97732210159302</v>
       </c>
       <c r="H426" t="n">
         <v>8830</v>
@@ -12752,7 +12752,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G427" t="n">
-        <v>5.99648141860962</v>
+        <v>5.99648094177246</v>
       </c>
       <c r="H427" t="n">
         <v>8596</v>
@@ -12810,7 +12810,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>6.03479719161987</v>
+        <v>6.0347957611084</v>
       </c>
       <c r="H429" t="n">
         <v>6859</v>
@@ -12839,7 +12839,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G430" t="n">
-        <v>6.05395412445068</v>
+        <v>6.053955078125</v>
       </c>
       <c r="H430" t="n">
         <v>3535</v>
@@ -12868,7 +12868,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G431" t="n">
-        <v>6.05395412445068</v>
+        <v>6.053955078125</v>
       </c>
       <c r="H431" t="n">
         <v>1471</v>
@@ -12926,7 +12926,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>6.30300998687744</v>
+        <v>6.30300951004028</v>
       </c>
       <c r="H433" t="n">
         <v>5881</v>
@@ -12955,7 +12955,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>6.41795778274536</v>
+        <v>6.41795873641968</v>
       </c>
       <c r="H434" t="n">
         <v>27535</v>
@@ -12984,7 +12984,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>6.41795778274536</v>
+        <v>6.41795873641968</v>
       </c>
       <c r="H435" t="n">
         <v>5559</v>
@@ -13042,7 +13042,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G437" t="n">
-        <v>6.62869739532471</v>
+        <v>6.62869787216187</v>
       </c>
       <c r="H437" t="n">
         <v>19470</v>
@@ -13071,7 +13071,7 @@
         <v>7</v>
       </c>
       <c r="G438" t="n">
-        <v>6.70532941818237</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H438" t="n">
         <v>17634</v>
@@ -13100,7 +13100,7 @@
         <v>7</v>
       </c>
       <c r="G439" t="n">
-        <v>6.70532941818237</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H439" t="n">
         <v>12013</v>
@@ -13129,7 +13129,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>6.64785528182983</v>
+        <v>6.64785575866699</v>
       </c>
       <c r="H440" t="n">
         <v>3991</v>
@@ -13158,7 +13158,7 @@
         <v>7</v>
       </c>
       <c r="G441" t="n">
-        <v>6.70532941818237</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H441" t="n">
         <v>8061</v>
@@ -13187,7 +13187,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>6.68617153167725</v>
+        <v>6.6861720085144</v>
       </c>
       <c r="H442" t="n">
         <v>4094</v>
@@ -13216,7 +13216,7 @@
         <v>7</v>
       </c>
       <c r="G443" t="n">
-        <v>6.70532941818237</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H443" t="n">
         <v>701</v>
@@ -13245,7 +13245,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G444" t="n">
-        <v>6.7819619178772</v>
+        <v>6.78196144104004</v>
       </c>
       <c r="H444" t="n">
         <v>9214</v>
@@ -13332,7 +13332,7 @@
         <v>7.5</v>
       </c>
       <c r="G447" t="n">
-        <v>7.1842827796936</v>
+        <v>7.18428230285645</v>
       </c>
       <c r="H447" t="n">
         <v>16792</v>
@@ -13361,7 +13361,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G448" t="n">
-        <v>7.50996923446655</v>
+        <v>7.50997018814087</v>
       </c>
       <c r="H448" t="n">
         <v>21129</v>
@@ -13390,7 +13390,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G449" t="n">
-        <v>7.79734134674072</v>
+        <v>7.79734086990356</v>
       </c>
       <c r="H449" t="n">
         <v>25454</v>
@@ -13419,7 +13419,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G450" t="n">
-        <v>7.68239212036133</v>
+        <v>7.68239307403564</v>
       </c>
       <c r="H450" t="n">
         <v>46433</v>
@@ -13448,7 +13448,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G451" t="n">
-        <v>8.00807952880859</v>
+        <v>8.00807857513428</v>
       </c>
       <c r="H451" t="n">
         <v>28419</v>
@@ -13477,7 +13477,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G452" t="n">
-        <v>8.11382675170898</v>
+        <v>8.1138277053833</v>
       </c>
       <c r="H452" t="n">
         <v>11712</v>
@@ -13506,7 +13506,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>8.13305568695068</v>
+        <v>8.133056640625</v>
       </c>
       <c r="H453" t="n">
         <v>8878</v>
@@ -13535,7 +13535,7 @@
         <v>8.5</v>
       </c>
       <c r="G454" t="n">
-        <v>8.17151069641113</v>
+        <v>8.1715087890625</v>
       </c>
       <c r="H454" t="n">
         <v>44078</v>
@@ -13564,7 +13564,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G455" t="n">
-        <v>7.9984655380249</v>
+        <v>7.99846506118774</v>
       </c>
       <c r="H455" t="n">
         <v>13585</v>
@@ -13593,7 +13593,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537460327148</v>
       </c>
       <c r="H456" t="n">
         <v>15884</v>
@@ -13622,7 +13622,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G457" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537460327148</v>
       </c>
       <c r="H457" t="n">
         <v>8749</v>
@@ -13651,7 +13651,7 @@
         <v>8.5</v>
       </c>
       <c r="G458" t="n">
-        <v>8.17151069641113</v>
+        <v>8.1715087890625</v>
       </c>
       <c r="H458" t="n">
         <v>10004</v>
@@ -13680,7 +13680,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>8.13305568695068</v>
+        <v>8.133056640625</v>
       </c>
       <c r="H459" t="n">
         <v>5157</v>
@@ -13709,7 +13709,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G460" t="n">
-        <v>8.01769256591797</v>
+        <v>8.01769351959229</v>
       </c>
       <c r="H460" t="n">
         <v>2888</v>
@@ -13738,7 +13738,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G461" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537460327148</v>
       </c>
       <c r="H461" t="n">
         <v>4060</v>
@@ -13767,7 +13767,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G462" t="n">
-        <v>8.11382675170898</v>
+        <v>8.1138277053833</v>
       </c>
       <c r="H462" t="n">
         <v>6009</v>
@@ -13796,7 +13796,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537460327148</v>
       </c>
       <c r="H463" t="n">
         <v>3875</v>
@@ -13854,7 +13854,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H465" t="n">
         <v>22593</v>
@@ -13912,7 +13912,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>7.22938251495361</v>
+        <v>7.22938299179077</v>
       </c>
       <c r="H467" t="n">
         <v>4220</v>
@@ -13941,7 +13941,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>7.3255181312561</v>
+        <v>7.32551765441895</v>
       </c>
       <c r="H468" t="n">
         <v>7825</v>
@@ -13999,7 +13999,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G470" t="n">
-        <v>7.24860954284668</v>
+        <v>7.24861001968384</v>
       </c>
       <c r="H470" t="n">
         <v>1139</v>
@@ -14028,7 +14028,7 @@
         <v>7.5</v>
       </c>
       <c r="G471" t="n">
-        <v>7.21015644073486</v>
+        <v>7.21015596389771</v>
       </c>
       <c r="H471" t="n">
         <v>4606</v>
@@ -14086,7 +14086,7 @@
         <v>7.5</v>
       </c>
       <c r="G473" t="n">
-        <v>7.21015644073486</v>
+        <v>7.21015596389771</v>
       </c>
       <c r="H473" t="n">
         <v>577622</v>
@@ -14115,7 +14115,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G474" t="n">
-        <v>7.07556629180908</v>
+        <v>7.07556676864624</v>
       </c>
       <c r="H474" t="n">
         <v>13451</v>
@@ -14173,7 +14173,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H476" t="n">
         <v>6071</v>
@@ -14202,7 +14202,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G477" t="n">
-        <v>7.57547044754028</v>
+        <v>7.57546997070312</v>
       </c>
       <c r="H477" t="n">
         <v>5817</v>
@@ -14231,7 +14231,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>7.57547044754028</v>
+        <v>7.57546997070312</v>
       </c>
       <c r="H478" t="n">
         <v>7258</v>
@@ -14260,7 +14260,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H479" t="n">
         <v>7940</v>
@@ -14289,7 +14289,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H480" t="n">
         <v>5804</v>
@@ -14318,7 +14318,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G481" t="n">
-        <v>7.61392450332642</v>
+        <v>7.61392402648926</v>
       </c>
       <c r="H481" t="n">
         <v>6569</v>
@@ -14347,7 +14347,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H482" t="n">
         <v>3228</v>
@@ -14376,7 +14376,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>7.57547044754028</v>
+        <v>7.57546997070312</v>
       </c>
       <c r="H483" t="n">
         <v>400</v>
@@ -14405,7 +14405,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H484" t="n">
         <v>2166</v>
@@ -14434,7 +14434,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H485" t="n">
         <v>10</v>
@@ -14463,7 +14463,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>7.61392450332642</v>
+        <v>7.61392402648926</v>
       </c>
       <c r="H486" t="n">
         <v>6297</v>
@@ -14492,7 +14492,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469747543335</v>
       </c>
       <c r="H487" t="n">
         <v>63</v>
@@ -14521,7 +14521,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>7.57547044754028</v>
+        <v>7.57546997070312</v>
       </c>
       <c r="H488" t="n">
         <v>1100</v>
@@ -14579,7 +14579,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G490" t="n">
-        <v>7.55624341964722</v>
+        <v>7.55624294281006</v>
       </c>
       <c r="H490" t="n">
         <v>2759</v>
@@ -14637,7 +14637,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G492" t="n">
-        <v>7.57547044754028</v>
+        <v>7.57546997070312</v>
       </c>
       <c r="H492" t="n">
         <v>220</v>
@@ -14666,7 +14666,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G493" t="n">
-        <v>7.57547044754028</v>
+        <v>7.57546997070312</v>
       </c>
       <c r="H493" t="n">
         <v>1235</v>
@@ -14695,7 +14695,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H494" t="n">
         <v>1276</v>
@@ -14724,7 +14724,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H495" t="n">
         <v>3732</v>
@@ -14782,7 +14782,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G497" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H497" t="n">
         <v>370</v>
@@ -14811,7 +14811,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.61392450332642</v>
+        <v>7.61392402648926</v>
       </c>
       <c r="H498" t="n">
         <v>19417</v>
@@ -14840,7 +14840,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H499" t="n">
         <v>6971</v>
@@ -14869,7 +14869,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>7.76774072647095</v>
+        <v>7.76774120330811</v>
       </c>
       <c r="H500" t="n">
         <v>19279</v>
@@ -14898,7 +14898,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>7.76774072647095</v>
+        <v>7.76774120330811</v>
       </c>
       <c r="H501" t="n">
         <v>1200</v>
@@ -14927,7 +14927,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G502" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H502" t="n">
         <v>7166</v>
@@ -14956,7 +14956,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G503" t="n">
-        <v>7.67160511016846</v>
+        <v>7.67160558700562</v>
       </c>
       <c r="H503" t="n">
         <v>23875</v>
@@ -14985,7 +14985,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G504" t="n">
-        <v>7.82542276382446</v>
+        <v>7.8254222869873</v>
       </c>
       <c r="H504" t="n">
         <v>8213</v>
@@ -15014,7 +15014,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>8.01769256591797</v>
+        <v>8.01769351959229</v>
       </c>
       <c r="H505" t="n">
         <v>6595</v>
@@ -15072,7 +15072,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G507" t="n">
-        <v>8.34455299377441</v>
+        <v>8.34455394744873</v>
       </c>
       <c r="H507" t="n">
         <v>18075</v>
@@ -15101,7 +15101,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G508" t="n">
-        <v>8.38300704956055</v>
+        <v>8.38300800323486</v>
       </c>
       <c r="H508" t="n">
         <v>13336</v>
@@ -15130,7 +15130,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>8.45991802215576</v>
+        <v>8.45991516113281</v>
       </c>
       <c r="H509" t="n">
         <v>2968</v>
@@ -15275,7 +15275,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>9.24822521209717</v>
+        <v>9.24822616577148</v>
       </c>
       <c r="H514" t="n">
         <v>17324</v>
@@ -15304,7 +15304,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G515" t="n">
-        <v>8.78677558898926</v>
+        <v>8.78677654266357</v>
       </c>
       <c r="H515" t="n">
         <v>9509</v>
@@ -15362,7 +15362,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G517" t="n">
-        <v>9.36358833312988</v>
+        <v>9.36358737945557</v>
       </c>
       <c r="H517" t="n">
         <v>19813</v>
@@ -15478,7 +15478,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G521" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H521" t="n">
         <v>5058</v>
@@ -15565,7 +15565,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G524" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H524" t="n">
         <v>3582</v>
@@ -15594,7 +15594,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G525" t="n">
-        <v>9.34436225891113</v>
+        <v>9.34436321258545</v>
       </c>
       <c r="H525" t="n">
         <v>2160</v>
@@ -15623,7 +15623,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G526" t="n">
-        <v>9.36358833312988</v>
+        <v>9.36358737945557</v>
       </c>
       <c r="H526" t="n">
         <v>5384</v>
@@ -15681,7 +15681,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G528" t="n">
-        <v>8.84445667266846</v>
+        <v>8.84445762634277</v>
       </c>
       <c r="H528" t="n">
         <v>4558</v>
@@ -15710,7 +15710,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>8.84445667266846</v>
+        <v>8.84445762634277</v>
       </c>
       <c r="H529" t="n">
         <v>1878</v>
@@ -15739,7 +15739,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G530" t="n">
-        <v>8.70986843109131</v>
+        <v>8.70986938476562</v>
       </c>
       <c r="H530" t="n">
         <v>13372</v>
@@ -15826,7 +15826,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G533" t="n">
-        <v>8.9982738494873</v>
+        <v>8.99827480316162</v>
       </c>
       <c r="H533" t="n">
         <v>2235</v>
@@ -15942,7 +15942,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G537" t="n">
-        <v>8.84445667266846</v>
+        <v>8.84445762634277</v>
       </c>
       <c r="H537" t="n">
         <v>3601</v>
@@ -16000,7 +16000,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>8.69064140319824</v>
+        <v>8.69064044952393</v>
       </c>
       <c r="H539" t="n">
         <v>10503</v>
@@ -16116,7 +16116,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>8.61373329162598</v>
+        <v>8.61373233795166</v>
       </c>
       <c r="H543" t="n">
         <v>3178</v>
@@ -16145,7 +16145,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G544" t="n">
-        <v>8.47914218902588</v>
+        <v>8.4791431427002</v>
       </c>
       <c r="H544" t="n">
         <v>4043</v>
@@ -16174,7 +16174,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G545" t="n">
-        <v>8.26764488220215</v>
+        <v>8.26764583587646</v>
       </c>
       <c r="H545" t="n">
         <v>17714</v>
@@ -16203,7 +16203,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G546" t="n">
-        <v>8.38300704956055</v>
+        <v>8.38300800323486</v>
       </c>
       <c r="H546" t="n">
         <v>12892</v>
@@ -16232,7 +16232,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>8.38300704956055</v>
+        <v>8.38300800323486</v>
       </c>
       <c r="H547" t="n">
         <v>2415</v>
@@ -16261,7 +16261,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>8.45991802215576</v>
+        <v>8.45991516113281</v>
       </c>
       <c r="H548" t="n">
         <v>1190</v>
@@ -16290,7 +16290,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G549" t="n">
-        <v>8.45991802215576</v>
+        <v>8.45991516113281</v>
       </c>
       <c r="H549" t="n">
         <v>1246</v>
@@ -16319,7 +16319,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G550" t="n">
-        <v>8.42146110534668</v>
+        <v>8.421462059021</v>
       </c>
       <c r="H550" t="n">
         <v>2370</v>
@@ -16348,7 +16348,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G551" t="n">
-        <v>8.42146110534668</v>
+        <v>8.421462059021</v>
       </c>
       <c r="H551" t="n">
         <v>669</v>
@@ -16377,7 +16377,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G552" t="n">
-        <v>8.36377906799316</v>
+        <v>8.36378002166748</v>
       </c>
       <c r="H552" t="n">
         <v>2520</v>
@@ -16406,7 +16406,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G553" t="n">
-        <v>8.42146110534668</v>
+        <v>8.421462059021</v>
       </c>
       <c r="H553" t="n">
         <v>1890</v>
@@ -16435,7 +16435,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G554" t="n">
-        <v>8.42146110534668</v>
+        <v>8.421462059021</v>
       </c>
       <c r="H554" t="n">
         <v>1260</v>
@@ -16464,7 +16464,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G555" t="n">
-        <v>8.36377906799316</v>
+        <v>8.36378002166748</v>
       </c>
       <c r="H555" t="n">
         <v>2093</v>
@@ -16493,7 +16493,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>8.45991802215576</v>
+        <v>8.45991516113281</v>
       </c>
       <c r="H556" t="n">
         <v>5315</v>
@@ -16522,7 +16522,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.45991802215576</v>
+        <v>8.45991516113281</v>
       </c>
       <c r="H557" t="n">
         <v>2498</v>
@@ -16609,7 +16609,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G560" t="n">
-        <v>8.59450435638428</v>
+        <v>8.59450531005859</v>
       </c>
       <c r="H560" t="n">
         <v>5860</v>
@@ -16638,7 +16638,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G561" t="n">
-        <v>8.78677558898926</v>
+        <v>8.78677654266357</v>
       </c>
       <c r="H561" t="n">
         <v>6343</v>
@@ -16667,7 +16667,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G562" t="n">
-        <v>8.95981884002686</v>
+        <v>8.95981979370117</v>
       </c>
       <c r="H562" t="n">
         <v>13014</v>
@@ -16754,7 +16754,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>8.97904777526855</v>
+        <v>8.97904682159424</v>
       </c>
       <c r="H565" t="n">
         <v>5437</v>
@@ -16783,7 +16783,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G566" t="n">
-        <v>8.95981884002686</v>
+        <v>8.95981979370117</v>
       </c>
       <c r="H566" t="n">
         <v>4531</v>
@@ -16812,7 +16812,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G567" t="n">
-        <v>9.1905460357666</v>
+        <v>9.19054508209229</v>
       </c>
       <c r="H567" t="n">
         <v>36349</v>
@@ -16841,7 +16841,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G568" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H568" t="n">
         <v>17237</v>
@@ -16899,7 +16899,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G570" t="n">
-        <v>9.03672695159912</v>
+        <v>9.03672790527344</v>
       </c>
       <c r="H570" t="n">
         <v>9621</v>
@@ -17044,7 +17044,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G575" t="n">
-        <v>8.84445667266846</v>
+        <v>8.84445762634277</v>
       </c>
       <c r="H575" t="n">
         <v>8026</v>
@@ -17102,7 +17102,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G577" t="n">
-        <v>8.78677558898926</v>
+        <v>8.78677654266357</v>
       </c>
       <c r="H577" t="n">
         <v>3392</v>
@@ -17131,7 +17131,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G578" t="n">
-        <v>8.97904777526855</v>
+        <v>8.97904682159424</v>
       </c>
       <c r="H578" t="n">
         <v>1588</v>
@@ -17189,7 +17189,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G580" t="n">
-        <v>8.86368560791016</v>
+        <v>8.86368465423584</v>
       </c>
       <c r="H580" t="n">
         <v>7665</v>
@@ -17218,7 +17218,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G581" t="n">
-        <v>8.84445667266846</v>
+        <v>8.84445762634277</v>
       </c>
       <c r="H581" t="n">
         <v>4098</v>
@@ -17247,7 +17247,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G582" t="n">
-        <v>8.70986843109131</v>
+        <v>8.70986938476562</v>
       </c>
       <c r="H582" t="n">
         <v>2983</v>
@@ -17334,7 +17334,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.69064140319824</v>
+        <v>8.69064044952393</v>
       </c>
       <c r="H585" t="n">
         <v>6475</v>
@@ -17392,7 +17392,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G587" t="n">
-        <v>8.70986843109131</v>
+        <v>8.70986938476562</v>
       </c>
       <c r="H587" t="n">
         <v>4690</v>
@@ -17421,7 +17421,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G588" t="n">
-        <v>8.70986843109131</v>
+        <v>8.70986938476562</v>
       </c>
       <c r="H588" t="n">
         <v>3314</v>
@@ -17537,7 +17537,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G592" t="n">
-        <v>8.59450435638428</v>
+        <v>8.59450531005859</v>
       </c>
       <c r="H592" t="n">
         <v>1305</v>
@@ -17624,7 +17624,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G595" t="n">
-        <v>8.78677558898926</v>
+        <v>8.78677654266357</v>
       </c>
       <c r="H595" t="n">
         <v>14401</v>
@@ -17711,7 +17711,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>9.32513332366943</v>
+        <v>9.32513427734375</v>
       </c>
       <c r="H598" t="n">
         <v>35354</v>
@@ -17769,7 +17769,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G600" t="n">
-        <v>9.34436225891113</v>
+        <v>9.34436321258545</v>
       </c>
       <c r="H600" t="n">
         <v>5708</v>
@@ -17798,7 +17798,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G601" t="n">
-        <v>9.15209102630615</v>
+        <v>9.15209007263184</v>
       </c>
       <c r="H601" t="n">
         <v>10060</v>
@@ -17827,7 +17827,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>9.32513332366943</v>
+        <v>9.32513427734375</v>
       </c>
       <c r="H602" t="n">
         <v>7188</v>
@@ -17856,7 +17856,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G603" t="n">
-        <v>9.20977115631104</v>
+        <v>9.20977210998535</v>
       </c>
       <c r="H603" t="n">
         <v>8280</v>
@@ -17885,7 +17885,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G604" t="n">
-        <v>9.26745414733887</v>
+        <v>9.26745223999023</v>
       </c>
       <c r="H604" t="n">
         <v>4700</v>
@@ -17914,7 +17914,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G605" t="n">
-        <v>9.36358833312988</v>
+        <v>9.36358737945557</v>
       </c>
       <c r="H605" t="n">
         <v>13690</v>
@@ -17943,7 +17943,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G606" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H606" t="n">
         <v>3670</v>
@@ -18001,7 +18001,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G608" t="n">
-        <v>9.40204334259033</v>
+        <v>9.40204238891602</v>
       </c>
       <c r="H608" t="n">
         <v>1810</v>
@@ -18117,7 +18117,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G612" t="n">
-        <v>9.1713171005249</v>
+        <v>9.17131900787354</v>
       </c>
       <c r="H612" t="n">
         <v>1833</v>
@@ -18146,7 +18146,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G613" t="n">
-        <v>9.15209102630615</v>
+        <v>9.15209007263184</v>
       </c>
       <c r="H613" t="n">
         <v>3820</v>
@@ -18175,7 +18175,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G614" t="n">
-        <v>9.20977115631104</v>
+        <v>9.20977210998535</v>
       </c>
       <c r="H614" t="n">
         <v>4084</v>
@@ -18204,7 +18204,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>9.20977115631104</v>
+        <v>9.20977210998535</v>
       </c>
       <c r="H615" t="n">
         <v>2315</v>
@@ -18262,7 +18262,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G617" t="n">
-        <v>9.15209102630615</v>
+        <v>9.15209007263184</v>
       </c>
       <c r="H617" t="n">
         <v>668</v>
@@ -18378,7 +18378,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>9.1713171005249</v>
+        <v>9.17131900787354</v>
       </c>
       <c r="H621" t="n">
         <v>3769</v>
@@ -18436,7 +18436,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G623" t="n">
-        <v>9.44049549102783</v>
+        <v>9.44049644470215</v>
       </c>
       <c r="H623" t="n">
         <v>12143</v>
@@ -18465,7 +18465,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G624" t="n">
-        <v>9.42127132415771</v>
+        <v>9.4212703704834</v>
       </c>
       <c r="H624" t="n">
         <v>23348</v>
@@ -18494,7 +18494,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>9.75774383544922</v>
+        <v>9.75774478912354</v>
       </c>
       <c r="H625" t="n">
         <v>44805</v>
@@ -18523,7 +18523,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>9.99808216094971</v>
+        <v>9.99808120727539</v>
       </c>
       <c r="H626" t="n">
         <v>32614</v>
@@ -18668,7 +18668,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>10.1422863006592</v>
+        <v>10.1422853469849</v>
       </c>
       <c r="H631" t="n">
         <v>5772</v>
@@ -18697,7 +18697,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G632" t="n">
-        <v>10.1422863006592</v>
+        <v>10.1422853469849</v>
       </c>
       <c r="H632" t="n">
         <v>5416</v>
@@ -18755,7 +18755,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>9.9500150680542</v>
+        <v>9.95001411437988</v>
       </c>
       <c r="H634" t="n">
         <v>8284</v>
@@ -18813,7 +18813,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G636" t="n">
-        <v>10.0461483001709</v>
+        <v>10.0461502075195</v>
       </c>
       <c r="H636" t="n">
         <v>2509</v>
@@ -18871,7 +18871,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>10.1903524398804</v>
+        <v>10.190354347229</v>
       </c>
       <c r="H638" t="n">
         <v>4002</v>
@@ -18929,7 +18929,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>10.5268278121948</v>
+        <v>10.5268268585205</v>
       </c>
       <c r="H640" t="n">
         <v>31497</v>
@@ -18958,7 +18958,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>10.478759765625</v>
+        <v>10.4787588119507</v>
       </c>
       <c r="H641" t="n">
         <v>6326</v>
@@ -18987,7 +18987,7 @@
         <v>10.75</v>
       </c>
       <c r="G642" t="n">
-        <v>10.3345546722412</v>
+        <v>10.3345575332642</v>
       </c>
       <c r="H642" t="n">
         <v>5010</v>
@@ -19016,7 +19016,7 @@
         <v>10.75</v>
       </c>
       <c r="G643" t="n">
-        <v>10.3345546722412</v>
+        <v>10.3345575332642</v>
       </c>
       <c r="H643" t="n">
         <v>2849</v>
@@ -19103,7 +19103,7 @@
         <v>10.75</v>
       </c>
       <c r="G646" t="n">
-        <v>10.3345546722412</v>
+        <v>10.3345575332642</v>
       </c>
       <c r="H646" t="n">
         <v>6485</v>
@@ -19132,7 +19132,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>10.478759765625</v>
+        <v>10.4787588119507</v>
       </c>
       <c r="H647" t="n">
         <v>9307</v>
@@ -19161,7 +19161,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>10.6710290908813</v>
+        <v>10.67103099823</v>
       </c>
       <c r="H648" t="n">
         <v>11173</v>
@@ -19190,7 +19190,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>10.6710290908813</v>
+        <v>10.67103099823</v>
       </c>
       <c r="H649" t="n">
         <v>2351</v>
@@ -19248,7 +19248,7 @@
         <v>11.5</v>
       </c>
       <c r="G651" t="n">
-        <v>11.0555715560913</v>
+        <v>11.055570602417</v>
       </c>
       <c r="H651" t="n">
         <v>18312</v>
@@ -19277,7 +19277,7 @@
         <v>11.5</v>
       </c>
       <c r="G652" t="n">
-        <v>11.0555715560913</v>
+        <v>11.055570602417</v>
       </c>
       <c r="H652" t="n">
         <v>27024</v>
@@ -19306,7 +19306,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>11.6323833465576</v>
+        <v>11.6323843002319</v>
       </c>
       <c r="H653" t="n">
         <v>42790</v>
@@ -19335,7 +19335,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8246555328369</v>
+        <v>11.8246545791626</v>
       </c>
       <c r="H654" t="n">
         <v>17953</v>
@@ -19364,7 +19364,7 @@
         <v>12.5</v>
       </c>
       <c r="G655" t="n">
-        <v>12.0169258117676</v>
+        <v>12.0169267654419</v>
       </c>
       <c r="H655" t="n">
         <v>11862</v>
@@ -19393,7 +19393,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>12.3053321838379</v>
+        <v>12.3053331375122</v>
       </c>
       <c r="H656" t="n">
         <v>14410</v>
@@ -19451,7 +19451,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G658" t="n">
-        <v>12.5937385559082</v>
+        <v>12.5937395095825</v>
       </c>
       <c r="H658" t="n">
         <v>24363</v>
@@ -19480,7 +19480,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>12.930212020874</v>
+        <v>12.9302129745483</v>
       </c>
       <c r="H659" t="n">
         <v>22441</v>
@@ -19538,7 +19538,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>12.5937385559082</v>
+        <v>12.5937395095825</v>
       </c>
       <c r="H661" t="n">
         <v>12281</v>
@@ -19567,7 +19567,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>12.1130628585815</v>
+        <v>12.1130599975586</v>
       </c>
       <c r="H662" t="n">
         <v>25415</v>
@@ -19596,7 +19596,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G663" t="n">
-        <v>12.7860088348389</v>
+        <v>12.7860097885132</v>
       </c>
       <c r="H663" t="n">
         <v>12196</v>
@@ -19625,7 +19625,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G664" t="n">
-        <v>12.8821430206299</v>
+        <v>12.8821449279785</v>
       </c>
       <c r="H664" t="n">
         <v>11286</v>
@@ -19683,7 +19683,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>12.7860088348389</v>
+        <v>12.7860097885132</v>
       </c>
       <c r="H666" t="n">
         <v>8354</v>
@@ -19712,7 +19712,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>12.7860088348389</v>
+        <v>12.7860097885132</v>
       </c>
       <c r="H667" t="n">
         <v>10497</v>
@@ -19770,7 +19770,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>12.7860088348389</v>
+        <v>12.7860097885132</v>
       </c>
       <c r="H669" t="n">
         <v>5925</v>
@@ -19799,7 +19799,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>12.5937385559082</v>
+        <v>12.5937395095825</v>
       </c>
       <c r="H670" t="n">
         <v>4230</v>
@@ -19915,7 +19915,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G674" t="n">
-        <v>13.5070247650146</v>
+        <v>13.507025718689</v>
       </c>
       <c r="H674" t="n">
         <v>9056</v>
@@ -20089,7 +20089,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>13.5070247650146</v>
+        <v>13.507025718689</v>
       </c>
       <c r="H680" t="n">
         <v>7178</v>
@@ -20118,7 +20118,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>13.6512260437012</v>
+        <v>13.6512279510498</v>
       </c>
       <c r="H681" t="n">
         <v>21605</v>
@@ -20176,7 +20176,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838375091553</v>
       </c>
       <c r="H683" t="n">
         <v>12362</v>
@@ -20205,7 +20205,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>14.1319055557251</v>
+        <v>14.1319036483765</v>
       </c>
       <c r="H684" t="n">
         <v>13280</v>
@@ -20234,7 +20234,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G685" t="n">
-        <v>14.1319055557251</v>
+        <v>14.1319036483765</v>
       </c>
       <c r="H685" t="n">
         <v>10052</v>
@@ -20263,7 +20263,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838375091553</v>
       </c>
       <c r="H686" t="n">
         <v>12855</v>
@@ -20495,7 +20495,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>13.8434982299805</v>
+        <v>13.8434972763062</v>
       </c>
       <c r="H694" t="n">
         <v>3277</v>
@@ -20611,7 +20611,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G698" t="n">
-        <v>13.5550928115845</v>
+        <v>13.5550918579102</v>
       </c>
       <c r="H698" t="n">
         <v>6847</v>
@@ -20756,7 +20756,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838375091553</v>
       </c>
       <c r="H703" t="n">
         <v>1315</v>
@@ -20785,7 +20785,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838375091553</v>
       </c>
       <c r="H704" t="n">
         <v>8696</v>
@@ -20872,7 +20872,7 @@
         <v>15.5</v>
       </c>
       <c r="G707" t="n">
-        <v>14.9415073394775</v>
+        <v>14.9415082931519</v>
       </c>
       <c r="H707" t="n">
         <v>14252</v>
@@ -20901,7 +20901,7 @@
         <v>15.5</v>
       </c>
       <c r="G708" t="n">
-        <v>14.9415073394775</v>
+        <v>14.9415082931519</v>
       </c>
       <c r="H708" t="n">
         <v>5682</v>
@@ -20930,7 +20930,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G709" t="n">
-        <v>15.1343021392822</v>
+        <v>15.1343011856079</v>
       </c>
       <c r="H709" t="n">
         <v>14768</v>
@@ -20959,7 +20959,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G710" t="n">
-        <v>15.8090791702271</v>
+        <v>15.8090810775757</v>
       </c>
       <c r="H710" t="n">
         <v>17022</v>
@@ -20988,7 +20988,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>15.8090791702271</v>
+        <v>15.8090810775757</v>
       </c>
       <c r="H711" t="n">
         <v>27543</v>
@@ -21075,7 +21075,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910652160645</v>
       </c>
       <c r="H714" t="n">
         <v>15736</v>
@@ -21104,7 +21104,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>16.5802536010742</v>
+        <v>16.5802555084229</v>
       </c>
       <c r="H715" t="n">
         <v>22030</v>
@@ -21133,7 +21133,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>16.9176425933838</v>
+        <v>16.9176406860352</v>
       </c>
       <c r="H716" t="n">
         <v>15375</v>
@@ -21162,7 +21162,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>16.9658432006836</v>
+        <v>16.965841293335</v>
       </c>
       <c r="H717" t="n">
         <v>10720</v>
@@ -21191,7 +21191,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>17.0140380859375</v>
+        <v>17.0140399932861</v>
       </c>
       <c r="H718" t="n">
         <v>8516</v>
@@ -21220,7 +21220,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G719" t="n">
-        <v>16.9176425933838</v>
+        <v>16.9176406860352</v>
       </c>
       <c r="H719" t="n">
         <v>10063</v>
@@ -21336,7 +21336,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>16.4838542938232</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H723" t="n">
         <v>4063</v>
@@ -21394,7 +21394,7 @@
         <v>17</v>
       </c>
       <c r="G725" t="n">
-        <v>16.3874626159668</v>
+        <v>16.3874607086182</v>
       </c>
       <c r="H725" t="n">
         <v>4851</v>
@@ -21423,7 +21423,7 @@
         <v>16.5</v>
       </c>
       <c r="G726" t="n">
-        <v>15.9054756164551</v>
+        <v>15.9054765701294</v>
       </c>
       <c r="H726" t="n">
         <v>13151</v>
@@ -21452,7 +21452,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G727" t="n">
-        <v>16.0500679016113</v>
+        <v>16.05006980896</v>
       </c>
       <c r="H727" t="n">
         <v>8423</v>
@@ -21481,7 +21481,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910652160645</v>
       </c>
       <c r="H728" t="n">
         <v>9170</v>
@@ -21539,7 +21539,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>16.5802536010742</v>
+        <v>16.5802555084229</v>
       </c>
       <c r="H730" t="n">
         <v>5817</v>
@@ -21568,7 +21568,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>16.4838542938232</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H731" t="n">
         <v>7493</v>
@@ -21597,7 +21597,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>16.4838542938232</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H732" t="n">
         <v>8992</v>
@@ -21626,7 +21626,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G733" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910652160645</v>
       </c>
       <c r="H733" t="n">
         <v>5388</v>
@@ -21655,7 +21655,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>16.1946659088135</v>
+        <v>16.1946678161621</v>
       </c>
       <c r="H734" t="n">
         <v>4299</v>
@@ -21713,7 +21713,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>16.1946659088135</v>
+        <v>16.1946678161621</v>
       </c>
       <c r="H736" t="n">
         <v>11338</v>
@@ -21742,7 +21742,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>16.2428665161133</v>
+        <v>16.242862701416</v>
       </c>
       <c r="H737" t="n">
         <v>1646</v>
@@ -21771,7 +21771,7 @@
         <v>16.75</v>
       </c>
       <c r="G738" t="n">
-        <v>16.1464691162109</v>
+        <v>16.1464672088623</v>
       </c>
       <c r="H738" t="n">
         <v>22483</v>
@@ -21858,7 +21858,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H741" t="n">
         <v>16758</v>
@@ -21887,7 +21887,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>15.5198888778687</v>
+        <v>15.519889831543</v>
       </c>
       <c r="H742" t="n">
         <v>9416</v>
@@ -21916,7 +21916,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>15.8090791702271</v>
+        <v>15.8090810775757</v>
       </c>
       <c r="H743" t="n">
         <v>1158</v>
@@ -21945,7 +21945,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>15.3752927780151</v>
+        <v>15.3752937316895</v>
       </c>
       <c r="H744" t="n">
         <v>2351</v>
@@ -22032,7 +22032,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H747" t="n">
         <v>13532</v>
@@ -22090,7 +22090,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G749" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H749" t="n">
         <v>6063</v>
@@ -22148,7 +22148,7 @@
         <v>15.75</v>
       </c>
       <c r="G751" t="n">
-        <v>15.1825008392334</v>
+        <v>15.1824998855591</v>
       </c>
       <c r="H751" t="n">
         <v>1284</v>
@@ -22206,7 +22206,7 @@
         <v>15.75</v>
       </c>
       <c r="G753" t="n">
-        <v>15.1825008392334</v>
+        <v>15.1824998855591</v>
       </c>
       <c r="H753" t="n">
         <v>5094</v>
@@ -22264,7 +22264,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G755" t="n">
-        <v>15.3752927780151</v>
+        <v>15.3752937316895</v>
       </c>
       <c r="H755" t="n">
         <v>1530</v>
@@ -22322,7 +22322,7 @@
         <v>16.25</v>
       </c>
       <c r="G757" t="n">
-        <v>15.6644849777222</v>
+        <v>15.6644840240479</v>
       </c>
       <c r="H757" t="n">
         <v>2755</v>
@@ -22351,7 +22351,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G758" t="n">
-        <v>15.8572788238525</v>
+        <v>15.8572778701782</v>
       </c>
       <c r="H758" t="n">
         <v>5944</v>
@@ -22380,7 +22380,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>15.7126808166504</v>
+        <v>15.7126836776733</v>
       </c>
       <c r="H759" t="n">
         <v>3425</v>
@@ -22438,7 +22438,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G761" t="n">
-        <v>15.4716901779175</v>
+        <v>15.4716892242432</v>
       </c>
       <c r="H761" t="n">
         <v>5096</v>
@@ -22467,7 +22467,7 @@
         <v>16.25</v>
       </c>
       <c r="G762" t="n">
-        <v>15.6644849777222</v>
+        <v>15.6644840240479</v>
       </c>
       <c r="H762" t="n">
         <v>3876</v>
@@ -22496,7 +22496,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>15.5198888778687</v>
+        <v>15.519889831543</v>
       </c>
       <c r="H763" t="n">
         <v>4072</v>
@@ -22554,7 +22554,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>15.8090791702271</v>
+        <v>15.8090810775757</v>
       </c>
       <c r="H765" t="n">
         <v>2799</v>
@@ -22699,7 +22699,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G770" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910652160645</v>
       </c>
       <c r="H770" t="n">
         <v>23740</v>
@@ -22728,7 +22728,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G771" t="n">
-        <v>17.0622386932373</v>
+        <v>17.0622367858887</v>
       </c>
       <c r="H771" t="n">
         <v>21378</v>
@@ -22902,7 +22902,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>17.1586360931396</v>
+        <v>17.158634185791</v>
       </c>
       <c r="H777" t="n">
         <v>3670</v>
@@ -22989,7 +22989,7 @@
         <v>17.5</v>
       </c>
       <c r="G780" t="n">
-        <v>16.8694458007812</v>
+        <v>16.869441986084</v>
       </c>
       <c r="H780" t="n">
         <v>7917</v>
@@ -23047,7 +23047,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G782" t="n">
-        <v>16.7730445861816</v>
+        <v>16.7730484008789</v>
       </c>
       <c r="H782" t="n">
         <v>1829</v>
@@ -23105,7 +23105,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>16.532054901123</v>
+        <v>16.5320568084717</v>
       </c>
       <c r="H784" t="n">
         <v>2334</v>
@@ -23134,7 +23134,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G785" t="n">
-        <v>16.4838542938232</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H785" t="n">
         <v>3050</v>
@@ -23163,7 +23163,7 @@
         <v>17.5</v>
       </c>
       <c r="G786" t="n">
-        <v>16.8694458007812</v>
+        <v>16.869441986084</v>
       </c>
       <c r="H786" t="n">
         <v>5398</v>
@@ -23192,7 +23192,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>16.9176425933838</v>
+        <v>16.9176406860352</v>
       </c>
       <c r="H787" t="n">
         <v>5321</v>
@@ -23308,7 +23308,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>17.2068328857422</v>
+        <v>17.2068347930908</v>
       </c>
       <c r="H791" t="n">
         <v>3420</v>
@@ -23366,7 +23366,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>17.1586360931396</v>
+        <v>17.158634185791</v>
       </c>
       <c r="H793" t="n">
         <v>1275</v>
@@ -23424,7 +23424,7 @@
         <v>17.75</v>
       </c>
       <c r="G795" t="n">
-        <v>17.1104354858398</v>
+        <v>17.1104335784912</v>
       </c>
       <c r="H795" t="n">
         <v>2578</v>
@@ -23482,7 +23482,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>17.0622386932373</v>
+        <v>17.0622367858887</v>
       </c>
       <c r="H797" t="n">
         <v>4120</v>
@@ -23511,7 +23511,7 @@
         <v>17.5</v>
       </c>
       <c r="G798" t="n">
-        <v>16.8694458007812</v>
+        <v>16.869441986084</v>
       </c>
       <c r="H798" t="n">
         <v>17956</v>
@@ -23540,7 +23540,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G799" t="n">
-        <v>17.0140380859375</v>
+        <v>17.0140399932861</v>
       </c>
       <c r="H799" t="n">
         <v>2123</v>
@@ -23598,7 +23598,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>17.6888179779053</v>
+        <v>17.6888160705566</v>
       </c>
       <c r="H801" t="n">
         <v>12968</v>
@@ -23656,7 +23656,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H803" t="n">
         <v>13681</v>
@@ -23685,7 +23685,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>18.7009811401367</v>
+        <v>18.7009830474854</v>
       </c>
       <c r="H804" t="n">
         <v>25471</v>
@@ -23714,7 +23714,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>19.2311668395996</v>
+        <v>19.231164932251</v>
       </c>
       <c r="H805" t="n">
         <v>23355</v>
@@ -23772,7 +23772,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G807" t="n">
-        <v>18.7491836547852</v>
+        <v>18.7491817474365</v>
       </c>
       <c r="H807" t="n">
         <v>9901</v>
@@ -23801,7 +23801,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>18.6045875549316</v>
+        <v>18.604585647583</v>
       </c>
       <c r="H808" t="n">
         <v>14307</v>
@@ -23946,7 +23946,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H813" t="n">
         <v>3298</v>
@@ -23975,7 +23975,7 @@
         <v>19</v>
       </c>
       <c r="G814" t="n">
-        <v>18.3153991699219</v>
+        <v>18.3153972625732</v>
       </c>
       <c r="H814" t="n">
         <v>4369</v>
@@ -24004,7 +24004,7 @@
         <v>19</v>
       </c>
       <c r="G815" t="n">
-        <v>18.3153991699219</v>
+        <v>18.3153972625732</v>
       </c>
       <c r="H815" t="n">
         <v>3021</v>
@@ -24033,7 +24033,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1708011627197</v>
       </c>
       <c r="H816" t="n">
         <v>2568</v>
@@ -24062,7 +24062,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H817" t="n">
         <v>6913</v>
@@ -24120,7 +24120,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1708011627197</v>
       </c>
       <c r="H819" t="n">
         <v>5941</v>
@@ -24149,7 +24149,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H820" t="n">
         <v>5621</v>
@@ -24178,7 +24178,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>17.9780044555664</v>
+        <v>17.9780082702637</v>
       </c>
       <c r="H821" t="n">
         <v>10417</v>
@@ -24236,7 +24236,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H823" t="n">
         <v>7777</v>
@@ -24265,7 +24265,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1708011627197</v>
       </c>
       <c r="H824" t="n">
         <v>10467</v>
@@ -24294,7 +24294,7 @@
         <v>18.75</v>
       </c>
       <c r="G825" t="n">
-        <v>18.0744037628174</v>
+        <v>18.074405670166</v>
       </c>
       <c r="H825" t="n">
         <v>9281</v>
@@ -24352,7 +24352,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>17.6888179779053</v>
+        <v>17.6888160705566</v>
       </c>
       <c r="H827" t="n">
         <v>9976</v>
@@ -24439,7 +24439,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1708011627197</v>
       </c>
       <c r="H830" t="n">
         <v>1749</v>
@@ -24468,7 +24468,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>17.88161277771</v>
+        <v>17.8816108703613</v>
       </c>
       <c r="H831" t="n">
         <v>4940</v>
@@ -24497,7 +24497,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1708011627197</v>
       </c>
       <c r="H832" t="n">
         <v>1475</v>
@@ -24526,7 +24526,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G833" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H833" t="n">
         <v>4556</v>
@@ -24555,7 +24555,7 @@
         <v>19</v>
       </c>
       <c r="G834" t="n">
-        <v>18.3153991699219</v>
+        <v>18.3153972625732</v>
       </c>
       <c r="H834" t="n">
         <v>14459</v>
@@ -24642,7 +24642,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H837" t="n">
         <v>40035</v>
@@ -24700,7 +24700,7 @@
         <v>18.5</v>
       </c>
       <c r="G839" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H839" t="n">
         <v>1836</v>
@@ -24729,7 +24729,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H840" t="n">
         <v>3485</v>
@@ -24758,7 +24758,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>17.88161277771</v>
+        <v>17.8816108703613</v>
       </c>
       <c r="H841" t="n">
         <v>3677</v>
@@ -24816,7 +24816,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H843" t="n">
         <v>11897</v>
@@ -24903,7 +24903,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406192779541</v>
       </c>
       <c r="H846" t="n">
         <v>2528</v>
@@ -24961,7 +24961,7 @@
         <v>18.5</v>
       </c>
       <c r="G848" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H848" t="n">
         <v>5754</v>
@@ -24990,7 +24990,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>17.6888179779053</v>
+        <v>17.6888160705566</v>
       </c>
       <c r="H849" t="n">
         <v>2579</v>
@@ -25106,7 +25106,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G853" t="n">
-        <v>17.9780044555664</v>
+        <v>17.9780082702637</v>
       </c>
       <c r="H853" t="n">
         <v>12579</v>
@@ -25222,7 +25222,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>17.9298095703125</v>
+        <v>17.9298076629639</v>
       </c>
       <c r="H857" t="n">
         <v>5075</v>
@@ -25251,7 +25251,7 @@
         <v>18.5</v>
       </c>
       <c r="G858" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H858" t="n">
         <v>5325</v>
@@ -25280,7 +25280,7 @@
         <v>18.25</v>
       </c>
       <c r="G859" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H859" t="n">
         <v>5378</v>
@@ -25309,7 +25309,7 @@
         <v>18.25</v>
       </c>
       <c r="G860" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H860" t="n">
         <v>2515</v>
@@ -25425,7 +25425,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>17.2068328857422</v>
+        <v>17.2068347930908</v>
       </c>
       <c r="H864" t="n">
         <v>2311</v>
@@ -25570,7 +25570,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>17.9780044555664</v>
+        <v>17.9780082702637</v>
       </c>
       <c r="H869" t="n">
         <v>11422</v>
@@ -25657,7 +25657,7 @@
         <v>19</v>
       </c>
       <c r="G872" t="n">
-        <v>18.3153991699219</v>
+        <v>18.3153972625732</v>
       </c>
       <c r="H872" t="n">
         <v>6457</v>
@@ -25686,7 +25686,7 @@
         <v>19</v>
       </c>
       <c r="G873" t="n">
-        <v>18.3153991699219</v>
+        <v>18.3153972625732</v>
       </c>
       <c r="H873" t="n">
         <v>5070</v>
@@ -25715,7 +25715,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G874" t="n">
-        <v>18.2671966552734</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H874" t="n">
         <v>1553</v>
@@ -25773,7 +25773,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>17.9298095703125</v>
+        <v>17.9298076629639</v>
       </c>
       <c r="H876" t="n">
         <v>7398</v>
@@ -25947,7 +25947,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G882" t="n">
-        <v>18.7491836547852</v>
+        <v>18.7491817474365</v>
       </c>
       <c r="H882" t="n">
         <v>3786</v>
@@ -26034,7 +26034,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>18.4599914550781</v>
+        <v>18.4599933624268</v>
       </c>
       <c r="H885" t="n">
         <v>4951</v>
@@ -26092,7 +26092,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G887" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H887" t="n">
         <v>9206</v>
@@ -26121,7 +26121,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H888" t="n">
         <v>4533</v>
@@ -26150,7 +26150,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H889" t="n">
         <v>10126</v>
@@ -26237,7 +26237,7 @@
         <v>18.5</v>
       </c>
       <c r="G892" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H892" t="n">
         <v>13651</v>
@@ -26266,7 +26266,7 @@
         <v>18.5</v>
       </c>
       <c r="G893" t="n">
-        <v>17.8334102630615</v>
+        <v>17.8334140777588</v>
       </c>
       <c r="H893" t="n">
         <v>4177</v>
@@ -26295,7 +26295,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G894" t="n">
-        <v>17.0140380859375</v>
+        <v>17.0140399932861</v>
       </c>
       <c r="H894" t="n">
         <v>15135</v>
@@ -26324,7 +26324,7 @@
         <v>17.25</v>
       </c>
       <c r="G895" t="n">
-        <v>16.6284523010254</v>
+        <v>16.6284503936768</v>
       </c>
       <c r="H895" t="n">
         <v>10256</v>
@@ -26440,7 +26440,7 @@
         <v>18.25</v>
       </c>
       <c r="G899" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H899" t="n">
         <v>4107</v>
@@ -26469,7 +26469,7 @@
         <v>18.25</v>
       </c>
       <c r="G900" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H900" t="n">
         <v>1122</v>
@@ -26527,7 +26527,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>17.88161277771</v>
+        <v>17.8816108703613</v>
       </c>
       <c r="H902" t="n">
         <v>3011</v>
@@ -26614,7 +26614,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>17.2068328857422</v>
+        <v>17.2068347930908</v>
       </c>
       <c r="H905" t="n">
         <v>950</v>
@@ -26730,7 +26730,7 @@
         <v>17.5</v>
       </c>
       <c r="G909" t="n">
-        <v>16.8694458007812</v>
+        <v>16.869441986084</v>
       </c>
       <c r="H909" t="n">
         <v>20573</v>
@@ -26759,7 +26759,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>17.0622386932373</v>
+        <v>17.0622367858887</v>
       </c>
       <c r="H910" t="n">
         <v>5430</v>
@@ -26817,7 +26817,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G912" t="n">
-        <v>16.5802536010742</v>
+        <v>16.5802555084229</v>
       </c>
       <c r="H912" t="n">
         <v>4259</v>
@@ -26846,7 +26846,7 @@
         <v>16.5</v>
       </c>
       <c r="G913" t="n">
-        <v>15.9054756164551</v>
+        <v>15.9054765701294</v>
       </c>
       <c r="H913" t="n">
         <v>13709</v>
@@ -26904,7 +26904,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G915" t="n">
-        <v>15.3752927780151</v>
+        <v>15.3752937316895</v>
       </c>
       <c r="H915" t="n">
         <v>15172</v>
@@ -26962,7 +26962,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>14.6523170471191</v>
+        <v>14.6523180007935</v>
       </c>
       <c r="H917" t="n">
         <v>28900</v>
@@ -27049,7 +27049,7 @@
         <v>15.5</v>
       </c>
       <c r="G920" t="n">
-        <v>14.9415073394775</v>
+        <v>14.9415082931519</v>
       </c>
       <c r="H920" t="n">
         <v>1828</v>
@@ -27165,7 +27165,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G924" t="n">
-        <v>12.9653720855713</v>
+        <v>12.9653730392456</v>
       </c>
       <c r="H924" t="n">
         <v>18799</v>
@@ -27223,7 +27223,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>15.5198888778687</v>
+        <v>15.519889831543</v>
       </c>
       <c r="H926" t="n">
         <v>12774</v>
@@ -27252,7 +27252,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>15.7126808166504</v>
+        <v>15.7126836776733</v>
       </c>
       <c r="H927" t="n">
         <v>5052</v>
@@ -27310,7 +27310,7 @@
         <v>16.5</v>
       </c>
       <c r="G929" t="n">
-        <v>15.9054756164551</v>
+        <v>15.9054765701294</v>
       </c>
       <c r="H929" t="n">
         <v>13874</v>
@@ -27368,7 +27368,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>16.1946659088135</v>
+        <v>16.1946678161621</v>
       </c>
       <c r="H931" t="n">
         <v>10440</v>
@@ -27397,7 +27397,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>15.7126808166504</v>
+        <v>15.7126836776733</v>
       </c>
       <c r="H932" t="n">
         <v>17688</v>
@@ -27426,7 +27426,7 @@
         <v>15.75</v>
       </c>
       <c r="G933" t="n">
-        <v>15.1825008392334</v>
+        <v>15.1824998855591</v>
       </c>
       <c r="H933" t="n">
         <v>5274</v>
@@ -27484,7 +27484,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>15.0861015319824</v>
+        <v>15.0861034393311</v>
       </c>
       <c r="H935" t="n">
         <v>1447</v>
@@ -27513,7 +27513,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H936" t="n">
         <v>3565</v>
@@ -27629,7 +27629,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G940" t="n">
-        <v>15.3752927780151</v>
+        <v>15.3752937316895</v>
       </c>
       <c r="H940" t="n">
         <v>5182</v>
@@ -27658,7 +27658,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G941" t="n">
-        <v>15.0861015319824</v>
+        <v>15.0861034393311</v>
       </c>
       <c r="H941" t="n">
         <v>1106</v>
@@ -27716,7 +27716,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G943" t="n">
-        <v>15.1343021392822</v>
+        <v>15.1343011856079</v>
       </c>
       <c r="H943" t="n">
         <v>2718</v>
@@ -27774,7 +27774,7 @@
         <v>15.75</v>
       </c>
       <c r="G945" t="n">
-        <v>15.1825008392334</v>
+        <v>15.1824998855591</v>
       </c>
       <c r="H945" t="n">
         <v>4177</v>
@@ -27803,7 +27803,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>15.3752927780151</v>
+        <v>15.3752937316895</v>
       </c>
       <c r="H946" t="n">
         <v>2563</v>
@@ -27832,7 +27832,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G947" t="n">
-        <v>15.0861015319824</v>
+        <v>15.0861034393311</v>
       </c>
       <c r="H947" t="n">
         <v>723</v>
@@ -27890,7 +27890,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>14.6523170471191</v>
+        <v>14.6523180007935</v>
       </c>
       <c r="H949" t="n">
         <v>2874</v>
@@ -27919,7 +27919,7 @@
         <v>15</v>
       </c>
       <c r="G950" t="n">
-        <v>14.4595251083374</v>
+        <v>14.4595232009888</v>
       </c>
       <c r="H950" t="n">
         <v>8299</v>
@@ -28064,7 +28064,7 @@
         <v>15</v>
       </c>
       <c r="G955" t="n">
-        <v>14.4595251083374</v>
+        <v>14.4595232009888</v>
       </c>
       <c r="H955" t="n">
         <v>3589</v>
@@ -28180,7 +28180,7 @@
         <v>14.5</v>
       </c>
       <c r="G959" t="n">
-        <v>13.9775400161743</v>
+        <v>13.9775390625</v>
       </c>
       <c r="H959" t="n">
         <v>3572</v>
@@ -28209,7 +28209,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G960" t="n">
-        <v>13.6401500701904</v>
+        <v>13.6401510238647</v>
       </c>
       <c r="H960" t="n">
         <v>1673</v>
@@ -28238,7 +28238,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>13.6883478164673</v>
+        <v>13.6883497238159</v>
       </c>
       <c r="H961" t="n">
         <v>1030</v>
@@ -28296,7 +28296,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G963" t="n">
-        <v>13.2624025344849</v>
+        <v>13.2624034881592</v>
       </c>
       <c r="H963" t="n">
         <v>21968</v>
@@ -28441,7 +28441,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H968" t="n">
         <v>2720</v>
@@ -28470,7 +28470,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G969" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H969" t="n">
         <v>820</v>
@@ -28499,7 +28499,7 @@
         <v>14</v>
       </c>
       <c r="G970" t="n">
-        <v>13.5528211593628</v>
+        <v>13.5528202056885</v>
       </c>
       <c r="H970" t="n">
         <v>964</v>
@@ -28528,7 +28528,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H971" t="n">
         <v>14283</v>
@@ -28818,7 +28818,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G981" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H981" t="n">
         <v>13144</v>
@@ -28847,7 +28847,7 @@
         <v>15.75</v>
       </c>
       <c r="G982" t="n">
-        <v>15.246922492981</v>
+        <v>15.2469234466553</v>
       </c>
       <c r="H982" t="n">
         <v>13824</v>
@@ -28876,7 +28876,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G983" t="n">
-        <v>15.2953271865845</v>
+        <v>15.2953262329102</v>
       </c>
       <c r="H983" t="n">
         <v>3160</v>
@@ -28905,7 +28905,7 @@
         <v>16</v>
       </c>
       <c r="G984" t="n">
-        <v>15.488938331604</v>
+        <v>15.4889392852783</v>
       </c>
       <c r="H984" t="n">
         <v>55822</v>
@@ -28963,7 +28963,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G986" t="n">
-        <v>15.3921318054199</v>
+        <v>15.3921327590942</v>
       </c>
       <c r="H986" t="n">
         <v>2809</v>
@@ -29079,7 +29079,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G990" t="n">
-        <v>14.666088104248</v>
+        <v>14.6660890579224</v>
       </c>
       <c r="H990" t="n">
         <v>6059</v>
@@ -29137,7 +29137,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G992" t="n">
-        <v>14.0852537155151</v>
+        <v>14.0852527618408</v>
       </c>
       <c r="H992" t="n">
         <v>5402</v>
@@ -29224,7 +29224,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>13.9884471893311</v>
+        <v>13.9884481430054</v>
       </c>
       <c r="H995" t="n">
         <v>1244</v>
@@ -29282,7 +29282,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G997" t="n">
-        <v>14.0852537155151</v>
+        <v>14.0852527618408</v>
       </c>
       <c r="H997" t="n">
         <v>291</v>
@@ -29340,7 +29340,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>13.6496276855469</v>
+        <v>13.6496267318726</v>
       </c>
       <c r="H999" t="n">
         <v>9929</v>
@@ -29398,7 +29398,7 @@
         <v>14</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.5528211593628</v>
+        <v>13.5528202056885</v>
       </c>
       <c r="H1001" t="n">
         <v>4003</v>
@@ -29427,7 +29427,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1002" t="n">
         <v>1279</v>
@@ -29514,7 +29514,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1005" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1005" t="n">
         <v>143</v>
@@ -29543,7 +29543,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -29572,7 +29572,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>13.6496276855469</v>
+        <v>13.6496267318726</v>
       </c>
       <c r="H1007" t="n">
         <v>5169</v>
@@ -29601,7 +29601,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H1008" t="n">
         <v>3771</v>
@@ -29630,7 +29630,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1009" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H1009" t="n">
         <v>1127</v>
@@ -29659,7 +29659,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>13.5044183731079</v>
+        <v>13.5044174194336</v>
       </c>
       <c r="H1010" t="n">
         <v>1586</v>
@@ -29717,7 +29717,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>13.1655979156494</v>
+        <v>13.1655988693237</v>
       </c>
       <c r="H1012" t="n">
         <v>3407</v>
@@ -29775,7 +29775,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>13.1655979156494</v>
+        <v>13.1655988693237</v>
       </c>
       <c r="H1014" t="n">
         <v>1001</v>
@@ -29891,7 +29891,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1018" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1018" t="n">
         <v>722</v>
@@ -29949,7 +29949,7 @@
         <v>12.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.1007328033447</v>
+        <v>12.100733757019</v>
       </c>
       <c r="H1020" t="n">
         <v>1200</v>
@@ -30007,7 +30007,7 @@
         <v>13</v>
       </c>
       <c r="G1022" t="n">
-        <v>12.5847625732422</v>
+        <v>12.5847616195679</v>
       </c>
       <c r="H1022" t="n">
         <v>916</v>
@@ -30123,7 +30123,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.7783737182617</v>
+        <v>12.7783727645874</v>
       </c>
       <c r="H1026" t="n">
         <v>3409</v>
@@ -30355,7 +30355,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>14.3756713867188</v>
+        <v>14.3756704330444</v>
       </c>
       <c r="H1034" t="n">
         <v>412</v>
@@ -30413,7 +30413,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1036" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1036" t="n">
         <v>501</v>
@@ -30500,7 +30500,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H1039" t="n">
         <v>2364</v>
@@ -30645,7 +30645,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1044" t="n">
         <v>2945</v>
@@ -30674,7 +30674,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1045" t="n">
-        <v>13.8916416168213</v>
+        <v>13.8916425704956</v>
       </c>
       <c r="H1045" t="n">
         <v>605</v>
@@ -30703,7 +30703,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1046" t="n">
         <v>124</v>
@@ -30732,7 +30732,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1047" t="n">
         <v>1102</v>
@@ -30790,7 +30790,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1049" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1049" t="n">
         <v>93</v>
@@ -30819,7 +30819,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1050" t="n">
-        <v>14.0852537155151</v>
+        <v>14.0852527618408</v>
       </c>
       <c r="H1050" t="n">
         <v>2468</v>
@@ -30848,7 +30848,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1051" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1051" t="n">
         <v>322</v>
@@ -30906,7 +30906,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.6496276855469</v>
+        <v>13.6496267318726</v>
       </c>
       <c r="H1053" t="n">
         <v>720</v>
@@ -30935,7 +30935,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1054" t="n">
-        <v>13.6496276855469</v>
+        <v>13.6496267318726</v>
       </c>
       <c r="H1054" t="n">
         <v>525</v>
@@ -31109,7 +31109,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1060" t="n">
-        <v>13.2624025344849</v>
+        <v>13.2624034881592</v>
       </c>
       <c r="H1060" t="n">
         <v>289</v>
@@ -31254,7 +31254,7 @@
         <v>13</v>
       </c>
       <c r="G1065" t="n">
-        <v>12.5847625732422</v>
+        <v>12.5847616195679</v>
       </c>
       <c r="H1065" t="n">
         <v>1451</v>
@@ -31312,7 +31312,7 @@
         <v>13</v>
       </c>
       <c r="G1067" t="n">
-        <v>12.5847625732422</v>
+        <v>12.5847616195679</v>
       </c>
       <c r="H1067" t="n">
         <v>346</v>
@@ -31370,7 +31370,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1069" t="n">
-        <v>11.9071207046509</v>
+        <v>11.9071216583252</v>
       </c>
       <c r="H1069" t="n">
         <v>3852</v>
@@ -31428,7 +31428,7 @@
         <v>12.25</v>
       </c>
       <c r="G1071" t="n">
-        <v>11.8587188720703</v>
+        <v>11.858717918396</v>
       </c>
       <c r="H1071" t="n">
         <v>1155</v>
@@ -31631,7 +31631,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1078" t="n">
-        <v>12.5363597869873</v>
+        <v>12.536358833313</v>
       </c>
       <c r="H1078" t="n">
         <v>284</v>
@@ -31660,7 +31660,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1079" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1079" t="n">
         <v>69</v>
@@ -31805,7 +31805,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>12.7783737182617</v>
+        <v>12.7783727645874</v>
       </c>
       <c r="H1084" t="n">
         <v>809</v>
@@ -31834,7 +31834,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1085" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1085" t="n">
         <v>264</v>
@@ -31863,7 +31863,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1086" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1086" t="n">
         <v>1249</v>
@@ -31892,7 +31892,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1087" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1087" t="n">
         <v>19</v>
@@ -31950,7 +31950,7 @@
         <v>13</v>
       </c>
       <c r="G1089" t="n">
-        <v>12.5847625732422</v>
+        <v>12.5847616195679</v>
       </c>
       <c r="H1089" t="n">
         <v>478</v>
@@ -31979,7 +31979,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1090" t="n">
-        <v>12.7783737182617</v>
+        <v>12.7783727645874</v>
       </c>
       <c r="H1090" t="n">
         <v>306</v>
@@ -32037,7 +32037,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1092" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1092" t="n">
         <v>1415</v>
@@ -32066,7 +32066,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>12.5363597869873</v>
+        <v>12.536358833313</v>
       </c>
       <c r="H1093" t="n">
         <v>4420</v>
@@ -32240,7 +32240,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1099" t="n">
         <v>8687</v>
@@ -32327,7 +32327,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1102" t="n">
-        <v>12.5363597869873</v>
+        <v>12.536358833313</v>
       </c>
       <c r="H1102" t="n">
         <v>6218</v>
@@ -32791,7 +32791,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1118" t="n">
-        <v>12.5363597869873</v>
+        <v>12.536358833313</v>
       </c>
       <c r="H1118" t="n">
         <v>3355</v>
@@ -32820,7 +32820,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>12.5363597869873</v>
+        <v>12.536358833313</v>
       </c>
       <c r="H1119" t="n">
         <v>610</v>
@@ -32849,7 +32849,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1120" t="n">
-        <v>12.7783737182617</v>
+        <v>12.7783727645874</v>
       </c>
       <c r="H1120" t="n">
         <v>3820</v>
@@ -32878,7 +32878,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1121" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1121" t="n">
         <v>3291</v>
@@ -32907,7 +32907,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>12.9719858169556</v>
+        <v>12.9719867706299</v>
       </c>
       <c r="H1122" t="n">
         <v>24918</v>
@@ -32965,7 +32965,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>12.9719858169556</v>
+        <v>12.9719867706299</v>
       </c>
       <c r="H1124" t="n">
         <v>30157</v>
@@ -33052,7 +33052,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1127" t="n">
-        <v>12.9719858169556</v>
+        <v>12.9719867706299</v>
       </c>
       <c r="H1127" t="n">
         <v>32113</v>
@@ -33110,7 +33110,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1129" t="n">
-        <v>13.1655979156494</v>
+        <v>13.1655988693237</v>
       </c>
       <c r="H1129" t="n">
         <v>390</v>
@@ -33139,7 +33139,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1130" t="n">
-        <v>13.1655979156494</v>
+        <v>13.1655988693237</v>
       </c>
       <c r="H1130" t="n">
         <v>1118</v>
@@ -33226,7 +33226,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1133" t="n">
-        <v>13.6496276855469</v>
+        <v>13.6496267318726</v>
       </c>
       <c r="H1133" t="n">
         <v>1050</v>
@@ -33255,7 +33255,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1134" t="n">
-        <v>13.9884471893311</v>
+        <v>13.9884481430054</v>
       </c>
       <c r="H1134" t="n">
         <v>1819</v>
@@ -33342,7 +33342,7 @@
         <v>14</v>
       </c>
       <c r="G1137" t="n">
-        <v>13.5528211593628</v>
+        <v>13.5528202056885</v>
       </c>
       <c r="H1137" t="n">
         <v>8177</v>
@@ -33371,7 +33371,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1138" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1138" t="n">
         <v>5357</v>
@@ -33458,7 +33458,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1141" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1141" t="n">
         <v>4771</v>
@@ -33516,7 +33516,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>13.7464323043823</v>
+        <v>13.7464332580566</v>
       </c>
       <c r="H1143" t="n">
         <v>720</v>
@@ -33603,7 +33603,7 @@
         <v>15.25</v>
       </c>
       <c r="G1146" t="n">
-        <v>14.7628936767578</v>
+        <v>14.7628946304321</v>
       </c>
       <c r="H1146" t="n">
         <v>2000</v>
@@ -33632,7 +33632,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H1147" t="n">
         <v>5496</v>
@@ -33661,7 +33661,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1148" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1148" t="n">
         <v>3537</v>
@@ -33690,7 +33690,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1149" t="n">
-        <v>14.1820592880249</v>
+        <v>14.1820583343506</v>
       </c>
       <c r="H1149" t="n">
         <v>807</v>
@@ -33719,7 +33719,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1150" t="n">
-        <v>14.1820592880249</v>
+        <v>14.1820583343506</v>
       </c>
       <c r="H1150" t="n">
         <v>9057</v>
@@ -33806,7 +33806,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1153" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1153" t="n">
         <v>497</v>
@@ -33835,7 +33835,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1154" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1154" t="n">
         <v>368</v>
@@ -33893,7 +33893,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1156" t="n">
-        <v>13.9884471893311</v>
+        <v>13.9884481430054</v>
       </c>
       <c r="H1156" t="n">
         <v>1337</v>
@@ -33922,7 +33922,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1157" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1157" t="n">
         <v>52</v>
@@ -34038,7 +34038,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1161" t="n">
-        <v>14.1820592880249</v>
+        <v>14.1820583343506</v>
       </c>
       <c r="H1161" t="n">
         <v>1598</v>
@@ -34067,7 +34067,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1162" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1162" t="n">
         <v>1367</v>
@@ -34096,7 +34096,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1163" t="n">
         <v>3148</v>
@@ -34125,7 +34125,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1164" t="n">
-        <v>14.2304630279541</v>
+        <v>14.2304620742798</v>
       </c>
       <c r="H1164" t="n">
         <v>1557</v>
@@ -34241,7 +34241,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1168" t="n">
-        <v>13.6496276855469</v>
+        <v>13.6496267318726</v>
       </c>
       <c r="H1168" t="n">
         <v>5180</v>
@@ -34270,7 +34270,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>13.8916416168213</v>
+        <v>13.8916425704956</v>
       </c>
       <c r="H1169" t="n">
         <v>3227</v>
@@ -34299,7 +34299,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>13.8916416168213</v>
+        <v>13.8916425704956</v>
       </c>
       <c r="H1170" t="n">
         <v>1513</v>
@@ -34473,7 +34473,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1176" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1176" t="n">
         <v>4234</v>
@@ -34589,7 +34589,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1180" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1180" t="n">
         <v>657</v>
@@ -34705,7 +34705,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>12.9719858169556</v>
+        <v>12.9719867706299</v>
       </c>
       <c r="H1184" t="n">
         <v>1248</v>
@@ -34763,7 +34763,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1186" t="n">
-        <v>12.7783737182617</v>
+        <v>12.7783727645874</v>
       </c>
       <c r="H1186" t="n">
         <v>1146</v>
@@ -34792,7 +34792,7 @@
         <v>13</v>
       </c>
       <c r="G1187" t="n">
-        <v>12.5847625732422</v>
+        <v>12.5847616195679</v>
       </c>
       <c r="H1187" t="n">
         <v>213</v>
@@ -34850,7 +34850,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1189" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1189" t="n">
         <v>2001</v>
@@ -34908,7 +34908,7 @@
         <v>13</v>
       </c>
       <c r="G1191" t="n">
-        <v>12.5847625732422</v>
+        <v>12.5847616195679</v>
       </c>
       <c r="H1191" t="n">
         <v>1985</v>
@@ -35024,7 +35024,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>12.7783737182617</v>
+        <v>12.7783727645874</v>
       </c>
       <c r="H1195" t="n">
         <v>3177</v>
@@ -35053,7 +35053,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1196" t="n">
-        <v>13.1655979156494</v>
+        <v>13.1655988693237</v>
       </c>
       <c r="H1196" t="n">
         <v>449</v>
@@ -35082,7 +35082,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1197" t="n">
-        <v>12.7783737182617</v>
+        <v>12.7783727645874</v>
       </c>
       <c r="H1197" t="n">
         <v>389</v>
@@ -35111,7 +35111,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1198" t="n">
-        <v>13.1655979156494</v>
+        <v>13.1655988693237</v>
       </c>
       <c r="H1198" t="n">
         <v>781</v>
@@ -35140,7 +35140,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>13.2624025344849</v>
+        <v>13.2624034881592</v>
       </c>
       <c r="H1199" t="n">
         <v>4768</v>
@@ -35169,7 +35169,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>13.1655979156494</v>
+        <v>13.1655988693237</v>
       </c>
       <c r="H1200" t="n">
         <v>2548</v>
@@ -35256,7 +35256,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1203" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1203" t="n">
         <v>2471</v>
@@ -35285,7 +35285,7 @@
         <v>13</v>
       </c>
       <c r="G1204" t="n">
-        <v>12.5847625732422</v>
+        <v>12.5847616195679</v>
       </c>
       <c r="H1204" t="n">
         <v>6582</v>
@@ -35314,7 +35314,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.6331663131714</v>
+        <v>12.6331653594971</v>
       </c>
       <c r="H1205" t="n">
         <v>1890</v>
@@ -35546,7 +35546,7 @@
         <v>13</v>
       </c>
       <c r="G1213" t="n">
-        <v>12.5847625732422</v>
+        <v>12.5847616195679</v>
       </c>
       <c r="H1213" t="n">
         <v>563</v>
@@ -35575,7 +35575,7 @@
         <v>13</v>
       </c>
       <c r="G1214" t="n">
-        <v>12.5847625732422</v>
+        <v>12.5847616195679</v>
       </c>
       <c r="H1214" t="n">
         <v>60</v>
@@ -35749,7 +35749,7 @@
         <v>13</v>
       </c>
       <c r="G1220" t="n">
-        <v>12.5847625732422</v>
+        <v>12.5847616195679</v>
       </c>
       <c r="H1220" t="n">
         <v>54</v>
@@ -35894,7 +35894,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1225" t="n">
-        <v>12.3619480133057</v>
+        <v>12.36194896698</v>
       </c>
       <c r="H1225" t="n">
         <v>1114</v>
@@ -36068,7 +36068,7 @@
         <v>12.25</v>
       </c>
       <c r="G1231" t="n">
-        <v>11.9239263534546</v>
+        <v>11.9239273071289</v>
       </c>
       <c r="H1231" t="n">
         <v>3166</v>
@@ -36126,7 +36126,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>11.8752574920654</v>
+        <v>11.8752584457397</v>
       </c>
       <c r="H1233" t="n">
         <v>575</v>
@@ -36155,7 +36155,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>12.0699338912964</v>
+        <v>12.0699348449707</v>
       </c>
       <c r="H1234" t="n">
         <v>429</v>
@@ -36358,7 +36358,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1241" t="n">
-        <v>11.5832424163818</v>
+        <v>11.5832433700562</v>
       </c>
       <c r="H1241" t="n">
         <v>1619</v>
@@ -36416,7 +36416,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1243" t="n">
-        <v>11.4859056472778</v>
+        <v>11.4859066009521</v>
       </c>
       <c r="H1243" t="n">
         <v>63750</v>
@@ -36445,7 +36445,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1244" t="n">
-        <v>11.2425603866577</v>
+        <v>11.2425594329834</v>
       </c>
       <c r="H1244" t="n">
         <v>2233</v>
@@ -36561,7 +36561,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1248" t="n">
-        <v>11.2425603866577</v>
+        <v>11.2425594329834</v>
       </c>
       <c r="H1248" t="n">
         <v>3045</v>
@@ -36793,7 +36793,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1256" t="n">
-        <v>11.3885660171509</v>
+        <v>11.3885669708252</v>
       </c>
       <c r="H1256" t="n">
         <v>164</v>
@@ -36909,7 +36909,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1260" t="n">
-        <v>11.3885660171509</v>
+        <v>11.3885669708252</v>
       </c>
       <c r="H1260" t="n">
         <v>311</v>
@@ -36967,7 +36967,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1262" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1262" t="n">
         <v>10597</v>
@@ -36996,7 +36996,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1263" t="n">
         <v>4199</v>
@@ -37025,7 +37025,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1264" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1264" t="n">
         <v>2065</v>
@@ -37054,7 +37054,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1265" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1265" t="n">
         <v>739</v>
@@ -37083,7 +37083,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1266" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1266" t="n">
         <v>5610</v>
@@ -37112,7 +37112,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1267" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1267" t="n">
         <v>952</v>
@@ -37228,7 +37228,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>10.8045387268066</v>
+        <v>10.8045377731323</v>
       </c>
       <c r="H1271" t="n">
         <v>2225</v>
@@ -37315,7 +37315,7 @@
         <v>11.5</v>
       </c>
       <c r="G1274" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1274" t="n">
         <v>3017</v>
@@ -37373,7 +37373,7 @@
         <v>11.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1276" t="n">
         <v>4176</v>
@@ -37402,7 +37402,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1277" t="n">
-        <v>11.1452217102051</v>
+        <v>11.1452207565308</v>
       </c>
       <c r="H1277" t="n">
         <v>45</v>
@@ -37431,7 +37431,7 @@
         <v>11.25</v>
       </c>
       <c r="G1278" t="n">
-        <v>10.9505453109741</v>
+        <v>10.9505443572998</v>
       </c>
       <c r="H1278" t="n">
         <v>1619</v>
@@ -37547,7 +37547,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1282" t="n">
-        <v>10.8045387268066</v>
+        <v>10.8045377731323</v>
       </c>
       <c r="H1282" t="n">
         <v>280</v>
@@ -37576,7 +37576,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1283" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1283" t="n">
         <v>484</v>
@@ -37605,7 +37605,7 @@
         <v>11.25</v>
       </c>
       <c r="G1284" t="n">
-        <v>10.9505453109741</v>
+        <v>10.9505443572998</v>
       </c>
       <c r="H1284" t="n">
         <v>1467</v>
@@ -37634,7 +37634,7 @@
         <v>11.5</v>
       </c>
       <c r="G1285" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1285" t="n">
         <v>625</v>
@@ -37663,7 +37663,7 @@
         <v>11.5</v>
       </c>
       <c r="G1286" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1286" t="n">
         <v>21790</v>
@@ -37692,7 +37692,7 @@
         <v>11.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1287" t="n">
         <v>44</v>
@@ -37808,7 +37808,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1291" t="n">
-        <v>10.8045387268066</v>
+        <v>10.8045377731323</v>
       </c>
       <c r="H1291" t="n">
         <v>946</v>
@@ -37837,7 +37837,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1292" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1292" t="n">
         <v>140</v>
@@ -37866,7 +37866,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1293" t="n">
-        <v>11.1452217102051</v>
+        <v>11.1452207565308</v>
       </c>
       <c r="H1293" t="n">
         <v>513</v>
@@ -37895,7 +37895,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1294" t="n">
-        <v>11.3398971557617</v>
+        <v>11.339898109436</v>
       </c>
       <c r="H1294" t="n">
         <v>589</v>
@@ -37924,7 +37924,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1295" t="n">
-        <v>11.3885660171509</v>
+        <v>11.3885669708252</v>
       </c>
       <c r="H1295" t="n">
         <v>1752</v>
@@ -37953,7 +37953,7 @@
         <v>11.5</v>
       </c>
       <c r="G1296" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1296" t="n">
         <v>9</v>
@@ -37982,7 +37982,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1297" t="n">
-        <v>10.8045387268066</v>
+        <v>10.8045377731323</v>
       </c>
       <c r="H1297" t="n">
         <v>5116</v>
@@ -38040,7 +38040,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1299" t="n">
         <v>540</v>
@@ -38069,7 +38069,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1300" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1300" t="n">
         <v>2317</v>
@@ -38127,7 +38127,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1302" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1302" t="n">
         <v>190</v>
@@ -38156,7 +38156,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1303" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1303" t="n">
         <v>383</v>
@@ -38185,7 +38185,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1304" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1304" t="n">
         <v>733</v>
@@ -38214,7 +38214,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1305" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1305" t="n">
         <v>11235</v>
@@ -38243,7 +38243,7 @@
         <v>11.25</v>
       </c>
       <c r="G1306" t="n">
-        <v>10.9505453109741</v>
+        <v>10.9505443572998</v>
       </c>
       <c r="H1306" t="n">
         <v>2917</v>
@@ -38330,7 +38330,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1309" t="n">
-        <v>11.1452217102051</v>
+        <v>11.1452207565308</v>
       </c>
       <c r="H1309" t="n">
         <v>1167</v>
@@ -38359,7 +38359,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1310" t="n">
-        <v>11.1452217102051</v>
+        <v>11.1452207565308</v>
       </c>
       <c r="H1310" t="n">
         <v>2481</v>
@@ -38388,7 +38388,7 @@
         <v>11.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1311" t="n">
         <v>588</v>
@@ -38504,7 +38504,7 @@
         <v>11.25</v>
       </c>
       <c r="G1315" t="n">
-        <v>10.9505453109741</v>
+        <v>10.9505443572998</v>
       </c>
       <c r="H1315" t="n">
         <v>9088</v>
@@ -38591,7 +38591,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1318" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1318" t="n">
         <v>9023</v>
@@ -38649,7 +38649,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1320" t="n">
-        <v>10.5611925125122</v>
+        <v>10.5611934661865</v>
       </c>
       <c r="H1320" t="n">
         <v>3193</v>
@@ -38707,7 +38707,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1322" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1322" t="n">
         <v>6625</v>
@@ -38881,7 +38881,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1328" t="n">
-        <v>10.3178472518921</v>
+        <v>10.3178482055664</v>
       </c>
       <c r="H1328" t="n">
         <v>5188</v>
@@ -38997,7 +38997,7 @@
         <v>10</v>
       </c>
       <c r="G1332" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1332" t="n">
         <v>3047</v>
@@ -39055,7 +39055,7 @@
         <v>10.5</v>
       </c>
       <c r="G1334" t="n">
-        <v>10.2205095291138</v>
+        <v>10.2205085754395</v>
       </c>
       <c r="H1334" t="n">
         <v>4680</v>
@@ -39113,7 +39113,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1336" t="n">
-        <v>10.1718397140503</v>
+        <v>10.1718406677246</v>
       </c>
       <c r="H1336" t="n">
         <v>174</v>
@@ -39142,7 +39142,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1337" t="n">
-        <v>10.1718397140503</v>
+        <v>10.1718406677246</v>
       </c>
       <c r="H1337" t="n">
         <v>1784</v>
@@ -39200,7 +39200,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1339" t="n">
-        <v>9.92849349975586</v>
+        <v>9.92849445343018</v>
       </c>
       <c r="H1339" t="n">
         <v>7301</v>
@@ -39258,7 +39258,7 @@
         <v>10</v>
       </c>
       <c r="G1341" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1341" t="n">
         <v>2744</v>
@@ -39287,7 +39287,7 @@
         <v>10</v>
       </c>
       <c r="G1342" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1342" t="n">
         <v>928</v>
@@ -39316,7 +39316,7 @@
         <v>10</v>
       </c>
       <c r="G1343" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1343" t="n">
         <v>4647</v>
@@ -39345,7 +39345,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1344" t="n">
-        <v>9.7143497467041</v>
+        <v>9.71435070037842</v>
       </c>
       <c r="H1344" t="n">
         <v>2342</v>
@@ -39374,7 +39374,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1345" t="n">
-        <v>9.57807731628418</v>
+        <v>9.5780782699585</v>
       </c>
       <c r="H1345" t="n">
         <v>376</v>
@@ -39461,7 +39461,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1348" t="n">
-        <v>9.7143497467041</v>
+        <v>9.71435070037842</v>
       </c>
       <c r="H1348" t="n">
         <v>2959</v>
@@ -39490,7 +39490,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1349" t="n">
-        <v>9.7143497467041</v>
+        <v>9.71435070037842</v>
       </c>
       <c r="H1349" t="n">
         <v>2594</v>
@@ -39519,7 +39519,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1350" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1350" t="n">
         <v>3050</v>
@@ -39548,7 +39548,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1351" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1351" t="n">
         <v>5171</v>
@@ -39664,7 +39664,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1355" t="n">
-        <v>9.57807731628418</v>
+        <v>9.5780782699585</v>
       </c>
       <c r="H1355" t="n">
         <v>1043</v>
@@ -39693,7 +39693,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1356" t="n">
-        <v>9.53914165496826</v>
+        <v>9.53914260864258</v>
       </c>
       <c r="H1356" t="n">
         <v>852</v>
@@ -39722,7 +39722,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1357" t="n">
-        <v>9.8798246383667</v>
+        <v>9.87982559204102</v>
       </c>
       <c r="H1357" t="n">
         <v>16434</v>
@@ -39751,7 +39751,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1358" t="n">
-        <v>9.55860805511475</v>
+        <v>9.55860996246338</v>
       </c>
       <c r="H1358" t="n">
         <v>7909</v>
@@ -39780,7 +39780,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1359" t="n">
-        <v>9.53914165496826</v>
+        <v>9.53914260864258</v>
       </c>
       <c r="H1359" t="n">
         <v>6586</v>
@@ -39809,7 +39809,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1360" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1360" t="n">
         <v>9524</v>
@@ -39838,7 +39838,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1361" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1361" t="n">
         <v>604</v>
@@ -39925,7 +39925,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1364" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1364" t="n">
         <v>426</v>
@@ -39954,7 +39954,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1365" t="n">
-        <v>9.40286731719971</v>
+        <v>9.40286827087402</v>
       </c>
       <c r="H1365" t="n">
         <v>2541</v>
@@ -40012,7 +40012,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1367" t="n">
-        <v>9.3249979019165</v>
+        <v>9.32499694824219</v>
       </c>
       <c r="H1367" t="n">
         <v>1217</v>
@@ -40099,7 +40099,7 @@
         <v>9.5</v>
       </c>
       <c r="G1370" t="n">
-        <v>9.24712753295898</v>
+        <v>9.24712657928467</v>
       </c>
       <c r="H1370" t="n">
         <v>942</v>
@@ -40157,7 +40157,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>9.53914165496826</v>
+        <v>9.53914260864258</v>
       </c>
       <c r="H1372" t="n">
         <v>30727</v>
@@ -40186,7 +40186,7 @@
         <v>10</v>
       </c>
       <c r="G1373" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1373" t="n">
         <v>10690</v>
@@ -40273,7 +40273,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1376" t="n">
-        <v>10.6098623275757</v>
+        <v>10.6098613739014</v>
       </c>
       <c r="H1376" t="n">
         <v>23886</v>
@@ -40302,7 +40302,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1377" t="n">
-        <v>10.9992151260376</v>
+        <v>10.9992141723633</v>
       </c>
       <c r="H1377" t="n">
         <v>7467</v>
@@ -40331,7 +40331,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1378" t="n">
-        <v>10.6098623275757</v>
+        <v>10.6098613739014</v>
       </c>
       <c r="H1378" t="n">
         <v>4680</v>
@@ -40360,7 +40360,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1379" t="n">
-        <v>10.9018754959106</v>
+        <v>10.901876449585</v>
       </c>
       <c r="H1379" t="n">
         <v>1160</v>
@@ -40418,7 +40418,7 @@
         <v>11.25</v>
       </c>
       <c r="G1381" t="n">
-        <v>10.9505453109741</v>
+        <v>10.9505443572998</v>
       </c>
       <c r="H1381" t="n">
         <v>849</v>
@@ -40476,7 +40476,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1383" t="n">
-        <v>10.3178472518921</v>
+        <v>10.3178482055664</v>
       </c>
       <c r="H1383" t="n">
         <v>6765</v>
@@ -40534,7 +40534,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1385" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1385" t="n">
         <v>1252</v>
@@ -40563,7 +40563,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>10.6098623275757</v>
+        <v>10.6098613739014</v>
       </c>
       <c r="H1386" t="n">
         <v>741</v>
@@ -40592,7 +40592,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1387" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1387" t="n">
         <v>2810</v>
@@ -40679,7 +40679,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1390" t="n">
-        <v>10.3665151596069</v>
+        <v>10.3665161132812</v>
       </c>
       <c r="H1390" t="n">
         <v>3426</v>
@@ -40708,7 +40708,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1391" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1391" t="n">
         <v>815</v>
@@ -40766,7 +40766,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1393" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1393" t="n">
         <v>1038</v>
@@ -40824,7 +40824,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1395" t="n">
-        <v>10.8045387268066</v>
+        <v>10.8045377731323</v>
       </c>
       <c r="H1395" t="n">
         <v>2651</v>
@@ -40911,7 +40911,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1398" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1398" t="n">
         <v>4615</v>
@@ -40940,7 +40940,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>10.5611925125122</v>
+        <v>10.5611934661865</v>
       </c>
       <c r="H1399" t="n">
         <v>3084</v>
@@ -40998,7 +40998,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1401" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1401" t="n">
         <v>6873</v>
@@ -41027,7 +41027,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1402" t="n">
-        <v>10.5611925125122</v>
+        <v>10.5611934661865</v>
       </c>
       <c r="H1402" t="n">
         <v>2341</v>
@@ -41085,7 +41085,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1404" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1404" t="n">
         <v>1635</v>
@@ -41114,7 +41114,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1405" t="n">
-        <v>10.5611925125122</v>
+        <v>10.5611934661865</v>
       </c>
       <c r="H1405" t="n">
         <v>9659</v>
@@ -41230,7 +41230,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1409" t="n">
-        <v>10.8045387268066</v>
+        <v>10.8045377731323</v>
       </c>
       <c r="H1409" t="n">
         <v>6133</v>
@@ -41375,7 +41375,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1414" t="n">
-        <v>10.6585311889648</v>
+        <v>10.6585302352905</v>
       </c>
       <c r="H1414" t="n">
         <v>614</v>
@@ -41433,7 +41433,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>10.3665151596069</v>
+        <v>10.3665161132812</v>
       </c>
       <c r="H1416" t="n">
         <v>1588</v>
@@ -41491,7 +41491,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1418" t="n">
-        <v>10.5611925125122</v>
+        <v>10.5611934661865</v>
       </c>
       <c r="H1418" t="n">
         <v>2341</v>
@@ -41607,7 +41607,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1422" t="n">
-        <v>10.3665151596069</v>
+        <v>10.3665161132812</v>
       </c>
       <c r="H1422" t="n">
         <v>1545</v>
@@ -41636,7 +41636,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1423" t="n">
-        <v>10.3178472518921</v>
+        <v>10.3178482055664</v>
       </c>
       <c r="H1423" t="n">
         <v>1395</v>
@@ -41665,7 +41665,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1424" t="n">
-        <v>10.3665151596069</v>
+        <v>10.3665161132812</v>
       </c>
       <c r="H1424" t="n">
         <v>117</v>
@@ -41781,7 +41781,7 @@
         <v>10.25</v>
       </c>
       <c r="G1428" t="n">
-        <v>9.97716331481934</v>
+        <v>9.97716426849365</v>
       </c>
       <c r="H1428" t="n">
         <v>1017</v>
@@ -41810,7 +41810,7 @@
         <v>10.25</v>
       </c>
       <c r="G1429" t="n">
-        <v>9.97716331481934</v>
+        <v>9.97716426849365</v>
       </c>
       <c r="H1429" t="n">
         <v>483</v>
@@ -41897,7 +41897,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1432" t="n">
-        <v>10.1718397140503</v>
+        <v>10.1718406677246</v>
       </c>
       <c r="H1432" t="n">
         <v>1224</v>
@@ -41926,7 +41926,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1433" t="n">
-        <v>10.1718397140503</v>
+        <v>10.1718406677246</v>
       </c>
       <c r="H1433" t="n">
         <v>900</v>
@@ -41984,7 +41984,7 @@
         <v>10.25</v>
       </c>
       <c r="G1435" t="n">
-        <v>9.97716331481934</v>
+        <v>9.97716426849365</v>
       </c>
       <c r="H1435" t="n">
         <v>1234</v>
@@ -42013,7 +42013,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1436" t="n">
-        <v>9.6364803314209</v>
+        <v>9.63647937774658</v>
       </c>
       <c r="H1436" t="n">
         <v>3844</v>
@@ -42042,7 +42042,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1437" t="n">
-        <v>9.6364803314209</v>
+        <v>9.63647937774658</v>
       </c>
       <c r="H1437" t="n">
         <v>6673</v>
@@ -42100,7 +42100,7 @@
         <v>9.5</v>
       </c>
       <c r="G1439" t="n">
-        <v>9.24712753295898</v>
+        <v>9.24712657928467</v>
       </c>
       <c r="H1439" t="n">
         <v>2619</v>
@@ -42129,7 +42129,7 @@
         <v>9.5</v>
       </c>
       <c r="G1440" t="n">
-        <v>9.24712753295898</v>
+        <v>9.24712657928467</v>
       </c>
       <c r="H1440" t="n">
         <v>389</v>
@@ -42158,7 +42158,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1441" t="n">
-        <v>9.30553150177002</v>
+        <v>9.30552959442139</v>
       </c>
       <c r="H1441" t="n">
         <v>1731</v>
@@ -42216,7 +42216,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1443" t="n">
-        <v>9.7143497467041</v>
+        <v>9.71435070037842</v>
       </c>
       <c r="H1443" t="n">
         <v>6140</v>
@@ -42245,7 +42245,7 @@
         <v>10</v>
       </c>
       <c r="G1444" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1444" t="n">
         <v>3684</v>
@@ -42303,7 +42303,7 @@
         <v>10</v>
       </c>
       <c r="G1446" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1446" t="n">
         <v>10320</v>
@@ -42448,7 +42448,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1451" t="n">
-        <v>10.1718397140503</v>
+        <v>10.1718406677246</v>
       </c>
       <c r="H1451" t="n">
         <v>2025</v>
@@ -42506,7 +42506,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1453" t="n">
-        <v>9.92849349975586</v>
+        <v>9.92849445343018</v>
       </c>
       <c r="H1453" t="n">
         <v>2062</v>
@@ -42564,7 +42564,7 @@
         <v>10</v>
       </c>
       <c r="G1455" t="n">
-        <v>9.73381805419922</v>
+        <v>9.73381900787354</v>
       </c>
       <c r="H1455" t="n">
         <v>5681</v>
@@ -42593,7 +42593,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1456" t="n">
-        <v>9.57807731628418</v>
+        <v>9.5780782699585</v>
       </c>
       <c r="H1456" t="n">
         <v>2192</v>
@@ -42680,7 +42680,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1459" t="n">
-        <v>9.55860805511475</v>
+        <v>9.55860996246338</v>
       </c>
       <c r="H1459" t="n">
         <v>2192</v>
@@ -42709,7 +42709,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1460" t="n">
-        <v>9.6364803314209</v>
+        <v>9.63647937774658</v>
       </c>
       <c r="H1460" t="n">
         <v>6323</v>
@@ -42738,7 +42738,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1461" t="n">
-        <v>9.22765827178955</v>
+        <v>9.22765922546387</v>
       </c>
       <c r="H1461" t="n">
         <v>8053</v>
@@ -42767,7 +42767,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1462" t="n">
-        <v>9.55860805511475</v>
+        <v>9.55860996246338</v>
       </c>
       <c r="H1462" t="n">
         <v>3541</v>
@@ -42796,7 +42796,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1463" t="n">
-        <v>9.53914165496826</v>
+        <v>9.53914260864258</v>
       </c>
       <c r="H1463" t="n">
         <v>15014</v>
@@ -42825,7 +42825,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1464" t="n">
-        <v>9.59754371643066</v>
+        <v>9.59754467010498</v>
       </c>
       <c r="H1464" t="n">
         <v>708</v>
@@ -42912,7 +42912,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1467" t="n">
-        <v>9.18872451782227</v>
+        <v>9.18872356414795</v>
       </c>
       <c r="H1467" t="n">
         <v>8612</v>
@@ -43028,7 +43028,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>9.3249979019165</v>
+        <v>9.32499694824219</v>
       </c>
       <c r="H1471" t="n">
         <v>2430</v>
@@ -43115,7 +43115,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1474" t="n">
-        <v>9.05245113372803</v>
+        <v>9.05245018005371</v>
       </c>
       <c r="H1474" t="n">
         <v>9828</v>
@@ -43144,7 +43144,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1475" t="n">
-        <v>9.48539447784424</v>
+        <v>9.48539352416992</v>
       </c>
       <c r="H1475" t="n">
         <v>2617</v>
@@ -43173,7 +43173,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1476" t="n">
-        <v>9.60346984863281</v>
+        <v>9.6034688949585</v>
       </c>
       <c r="H1476" t="n">
         <v>1845</v>
@@ -43376,7 +43376,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1483" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1483" t="n">
         <v>5070</v>
@@ -43492,7 +43492,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1487" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1487" t="n">
         <v>2088</v>
@@ -43550,7 +43550,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1489" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1489" t="n">
         <v>2036</v>
@@ -43579,7 +43579,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1490" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1490" t="n">
         <v>1424</v>
@@ -43608,7 +43608,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1491" t="n">
         <v>934</v>
@@ -43782,7 +43782,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1497" t="n">
-        <v>9.6428279876709</v>
+        <v>9.64282894134521</v>
       </c>
       <c r="H1497" t="n">
         <v>3285</v>
@@ -43811,7 +43811,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1498" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1498" t="n">
         <v>5790</v>
@@ -43840,7 +43840,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1499" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1499" t="n">
         <v>602</v>
@@ -43869,7 +43869,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1500" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1500" t="n">
         <v>357</v>
@@ -43898,7 +43898,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1501" t="n">
-        <v>9.6428279876709</v>
+        <v>9.64282894134521</v>
       </c>
       <c r="H1501" t="n">
         <v>2832</v>
@@ -43985,7 +43985,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1504" t="n">
-        <v>9.56411170959473</v>
+        <v>9.56411075592041</v>
       </c>
       <c r="H1504" t="n">
         <v>3685</v>
@@ -44014,7 +44014,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1505" t="n">
-        <v>9.66250610351562</v>
+        <v>9.66250705718994</v>
       </c>
       <c r="H1505" t="n">
         <v>1013</v>
@@ -44043,7 +44043,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1506" t="n">
-        <v>9.54443168640137</v>
+        <v>9.54443073272705</v>
       </c>
       <c r="H1506" t="n">
         <v>1877</v>
@@ -44072,7 +44072,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1507" t="n">
-        <v>9.66250610351562</v>
+        <v>9.66250705718994</v>
       </c>
       <c r="H1507" t="n">
         <v>50791</v>
@@ -44304,7 +44304,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1515" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1515" t="n">
         <v>10583</v>
@@ -44623,7 +44623,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1526" t="n">
         <v>2144</v>
@@ -44681,7 +44681,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1528" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1528" t="n">
         <v>3063</v>
@@ -44768,7 +44768,7 @@
         <v>10.25</v>
       </c>
       <c r="G1531" t="n">
-        <v>10.0856103897095</v>
+        <v>10.0856113433838</v>
       </c>
       <c r="H1531" t="n">
         <v>636</v>
@@ -45058,7 +45058,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1541" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1541" t="n">
         <v>227</v>
@@ -45174,7 +45174,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1545" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1545" t="n">
         <v>232</v>
@@ -45203,7 +45203,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1546" t="n">
-        <v>9.6428279876709</v>
+        <v>9.64282894134521</v>
       </c>
       <c r="H1546" t="n">
         <v>2868</v>
@@ -45232,7 +45232,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1547" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1547" t="n">
         <v>400</v>
@@ -45464,7 +45464,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1555" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1555" t="n">
         <v>323</v>
@@ -45667,7 +45667,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1562" t="n">
-        <v>9.6428279876709</v>
+        <v>9.64282894134521</v>
       </c>
       <c r="H1562" t="n">
         <v>1757</v>
@@ -45696,7 +45696,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1563" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1563" t="n">
         <v>135</v>
@@ -45928,7 +45928,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1571" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1571" t="n">
         <v>2980</v>
@@ -45957,7 +45957,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1572" t="n">
-        <v>10.3808002471924</v>
+        <v>10.3807992935181</v>
       </c>
       <c r="H1572" t="n">
         <v>1240</v>
@@ -46015,7 +46015,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1574" t="n">
         <v>1210</v>
@@ -46044,7 +46044,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1575" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1575" t="n">
         <v>4872</v>
@@ -46073,7 +46073,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1576" t="n">
-        <v>11.1187715530396</v>
+        <v>11.1187705993652</v>
       </c>
       <c r="H1576" t="n">
         <v>12413</v>
@@ -46247,7 +46247,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1582" t="n">
-        <v>11.1679697036743</v>
+        <v>11.16796875</v>
       </c>
       <c r="H1582" t="n">
         <v>3025</v>
@@ -46305,7 +46305,7 @@
         <v>11.5</v>
       </c>
       <c r="G1584" t="n">
-        <v>11.3155641555786</v>
+        <v>11.3155632019043</v>
       </c>
       <c r="H1584" t="n">
         <v>11365</v>
@@ -46334,7 +46334,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1585" t="n">
-        <v>11.512354850769</v>
+        <v>11.5123558044434</v>
       </c>
       <c r="H1585" t="n">
         <v>11195</v>
@@ -46508,7 +46508,7 @@
         <v>13</v>
       </c>
       <c r="G1591" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1591" t="n">
         <v>14387</v>
@@ -46537,7 +46537,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1592" t="n">
-        <v>12.49631690979</v>
+        <v>12.4963178634644</v>
       </c>
       <c r="H1592" t="n">
         <v>10300</v>
@@ -46595,7 +46595,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1594" t="n">
-        <v>12.8407049179077</v>
+        <v>12.8407039642334</v>
       </c>
       <c r="H1594" t="n">
         <v>7943</v>
@@ -46624,7 +46624,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1595" t="n">
-        <v>12.8407049179077</v>
+        <v>12.8407039642334</v>
       </c>
       <c r="H1595" t="n">
         <v>5751</v>
@@ -46653,7 +46653,7 @@
         <v>13</v>
       </c>
       <c r="G1596" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1596" t="n">
         <v>9007</v>
@@ -46972,7 +46972,7 @@
         <v>13</v>
       </c>
       <c r="G1607" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1607" t="n">
         <v>45489</v>
@@ -47030,7 +47030,7 @@
         <v>13.5</v>
       </c>
       <c r="G1609" t="n">
-        <v>13.2834873199463</v>
+        <v>13.2834882736206</v>
       </c>
       <c r="H1609" t="n">
         <v>39949</v>
@@ -47088,7 +47088,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1611" t="n">
-        <v>12.8407049179077</v>
+        <v>12.8407039642334</v>
       </c>
       <c r="H1611" t="n">
         <v>13940</v>
@@ -47117,7 +47117,7 @@
         <v>13</v>
       </c>
       <c r="G1612" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1612" t="n">
         <v>1327</v>
@@ -47146,7 +47146,7 @@
         <v>13</v>
       </c>
       <c r="G1613" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1613" t="n">
         <v>20557</v>
@@ -47175,7 +47175,7 @@
         <v>13</v>
       </c>
       <c r="G1614" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1614" t="n">
         <v>15556</v>
@@ -47204,7 +47204,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1615" t="n">
-        <v>12.7423086166382</v>
+        <v>12.7423076629639</v>
       </c>
       <c r="H1615" t="n">
         <v>3096</v>
@@ -47233,7 +47233,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1616" t="n">
-        <v>12.49631690979</v>
+        <v>12.4963178634644</v>
       </c>
       <c r="H1616" t="n">
         <v>3076</v>
@@ -47378,7 +47378,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>11.3647623062134</v>
+        <v>11.3647613525391</v>
       </c>
       <c r="H1621" t="n">
         <v>6291</v>
@@ -47494,7 +47494,7 @@
         <v>12.25</v>
       </c>
       <c r="G1625" t="n">
-        <v>12.0535345077515</v>
+        <v>12.0535354614258</v>
       </c>
       <c r="H1625" t="n">
         <v>4284</v>
@@ -47813,7 +47813,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1636" t="n">
-        <v>11.1187715530396</v>
+        <v>11.1187705993652</v>
       </c>
       <c r="H1636" t="n">
         <v>507</v>
@@ -47871,7 +47871,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1638" t="n">
-        <v>11.1187715530396</v>
+        <v>11.1187705993652</v>
       </c>
       <c r="H1638" t="n">
         <v>4347</v>
@@ -47900,7 +47900,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1639" t="n">
-        <v>10.7743844985962</v>
+        <v>10.7743835449219</v>
       </c>
       <c r="H1639" t="n">
         <v>8536</v>
@@ -48103,7 +48103,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1646" t="n">
-        <v>10.7251863479614</v>
+        <v>10.7251853942871</v>
       </c>
       <c r="H1646" t="n">
         <v>9044</v>
@@ -48132,7 +48132,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1647" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1647" t="n">
         <v>3122</v>
@@ -48161,7 +48161,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1648" t="n">
         <v>5642</v>
@@ -48219,7 +48219,7 @@
         <v>10.5</v>
       </c>
       <c r="G1650" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1650" t="n">
         <v>56910</v>
@@ -48248,7 +48248,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1651" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1651" t="n">
         <v>2497</v>
@@ -48277,7 +48277,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1652" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1652" t="n">
         <v>10295</v>
@@ -48306,7 +48306,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1653" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1653" t="n">
         <v>9615</v>
@@ -48364,7 +48364,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1655" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1655" t="n">
         <v>1424</v>
@@ -48393,7 +48393,7 @@
         <v>10.5</v>
       </c>
       <c r="G1656" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1656" t="n">
         <v>6026</v>
@@ -48451,7 +48451,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1658" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1658" t="n">
         <v>5157</v>
@@ -48480,7 +48480,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1659" t="n">
-        <v>10.3808002471924</v>
+        <v>10.3807992935181</v>
       </c>
       <c r="H1659" t="n">
         <v>3675</v>
@@ -48509,7 +48509,7 @@
         <v>10.5</v>
       </c>
       <c r="G1660" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1660" t="n">
         <v>2242</v>
@@ -48538,7 +48538,7 @@
         <v>10.5</v>
       </c>
       <c r="G1661" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1661" t="n">
         <v>2158</v>
@@ -48567,7 +48567,7 @@
         <v>10.5</v>
       </c>
       <c r="G1662" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1662" t="n">
         <v>1216</v>
@@ -48683,7 +48683,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1666" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1666" t="n">
         <v>4693</v>
@@ -48741,7 +48741,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1668" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1668" t="n">
         <v>8608</v>
@@ -48828,7 +48828,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1671" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1671" t="n">
         <v>3688</v>
@@ -48915,7 +48915,7 @@
         <v>10.5</v>
       </c>
       <c r="G1674" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1674" t="n">
         <v>1380</v>
@@ -48973,7 +48973,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1676" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1676" t="n">
         <v>6725</v>
@@ -49060,7 +49060,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1679" t="n">
-        <v>10.3808002471924</v>
+        <v>10.3807992935181</v>
       </c>
       <c r="H1679" t="n">
         <v>3353</v>
@@ -49321,7 +49321,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1688" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1688" t="n">
         <v>2743</v>
@@ -49408,7 +49408,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1691" t="n">
-        <v>10.7251863479614</v>
+        <v>10.7251853942871</v>
       </c>
       <c r="H1691" t="n">
         <v>1253</v>
@@ -49611,7 +49611,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1698" t="n">
-        <v>10.7251863479614</v>
+        <v>10.7251853942871</v>
       </c>
       <c r="H1698" t="n">
         <v>206</v>
@@ -49814,7 +49814,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1705" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1705" t="n">
         <v>2007</v>
@@ -49843,7 +49843,7 @@
         <v>10.5</v>
       </c>
       <c r="G1706" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1706" t="n">
         <v>2121</v>
@@ -49872,7 +49872,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1707" t="n">
-        <v>10.3808002471924</v>
+        <v>10.3807992935181</v>
       </c>
       <c r="H1707" t="n">
         <v>2077</v>
@@ -49930,7 +49930,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1709" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1709" t="n">
         <v>1483</v>
@@ -50017,7 +50017,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1712" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1712" t="n">
         <v>1833</v>
@@ -50075,7 +50075,7 @@
         <v>10.5</v>
       </c>
       <c r="G1714" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1714" t="n">
         <v>56</v>
@@ -50191,7 +50191,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1718" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1718" t="n">
         <v>3461</v>
@@ -50365,7 +50365,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1724" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1724" t="n">
         <v>4639</v>
@@ -50481,7 +50481,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1728" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1728" t="n">
         <v>6196</v>
@@ -61159,6 +61159,64 @@
         <v>2852</v>
       </c>
       <c r="I2096" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2097" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2097" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>8.69999980926514</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="G2097" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="H2097" t="n">
+        <v>1052</v>
+      </c>
+      <c r="I2097" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2098" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2098" t="n">
+        <v>8.68000030517578</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>8.73999977111816</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>8.68000030517578</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>8.73999977111816</v>
+      </c>
+      <c r="G2098" t="n">
+        <v>8.73999977111816</v>
+      </c>
+      <c r="H2098" t="n">
+        <v>109</v>
+      </c>
+      <c r="I2098" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G2" t="n">
-        <v>2.57321286201477</v>
+        <v>2.57321262359619</v>
       </c>
       <c r="H2" t="n">
         <v>511000</v>
@@ -456,7 +456,7 @@
         <v>2.87050008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7357063293457</v>
+        <v>2.73570656776428</v>
       </c>
       <c r="H3" t="n">
         <v>364500</v>
@@ -485,7 +485,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G4" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H4" t="n">
         <v>233500</v>
@@ -543,7 +543,7 @@
         <v>2.98749995231628</v>
       </c>
       <c r="G6" t="n">
-        <v>2.84721231460571</v>
+        <v>2.84721255302429</v>
       </c>
       <c r="H6" t="n">
         <v>72500</v>
@@ -572,7 +572,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G7" t="n">
-        <v>2.80670785903931</v>
+        <v>2.80670809745789</v>
       </c>
       <c r="H7" t="n">
         <v>71500</v>
@@ -601,7 +601,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84006428718567</v>
+        <v>2.84006452560425</v>
       </c>
       <c r="H8" t="n">
         <v>25000</v>
@@ -630,7 +630,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.85912489891052</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H9" t="n">
         <v>26000</v>
@@ -659,7 +659,7 @@
         <v>2.97449994087219</v>
       </c>
       <c r="G10" t="n">
-        <v>2.83482265472412</v>
+        <v>2.8348228931427</v>
       </c>
       <c r="H10" t="n">
         <v>25000</v>
@@ -717,7 +717,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G12" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H12" t="n">
         <v>7500</v>
@@ -775,7 +775,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G14" t="n">
-        <v>2.76572680473328</v>
+        <v>2.76572704315186</v>
       </c>
       <c r="H14" t="n">
         <v>5500</v>
@@ -804,7 +804,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.85912489891052</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H15" t="n">
         <v>22500</v>
@@ -833,7 +833,7 @@
         <v>2.97449994087219</v>
       </c>
       <c r="G16" t="n">
-        <v>2.83482265472412</v>
+        <v>2.8348228931427</v>
       </c>
       <c r="H16" t="n">
         <v>6000</v>
@@ -862,7 +862,7 @@
         <v>2.93099999427795</v>
       </c>
       <c r="G17" t="n">
-        <v>2.79336524009705</v>
+        <v>2.79336500167847</v>
       </c>
       <c r="H17" t="n">
         <v>5000</v>
@@ -891,7 +891,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78764724731445</v>
+        <v>2.78764700889587</v>
       </c>
       <c r="H18" t="n">
         <v>10000</v>
@@ -1065,7 +1065,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>2.70663857460022</v>
+        <v>2.70663833618164</v>
       </c>
       <c r="H24" t="n">
         <v>9500</v>
@@ -1094,7 +1094,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.70663857460022</v>
+        <v>2.70663833618164</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G29" t="n">
-        <v>2.61895895004272</v>
+        <v>2.6189591884613</v>
       </c>
       <c r="H29" t="n">
         <v>14500</v>
@@ -1239,7 +1239,7 @@
         <v>2.75</v>
       </c>
       <c r="G30" t="n">
-        <v>2.62086510658264</v>
+        <v>2.6208643913269</v>
       </c>
       <c r="H30" t="n">
         <v>6500</v>
@@ -1268,7 +1268,7 @@
         <v>2.75</v>
       </c>
       <c r="G31" t="n">
-        <v>2.62086510658264</v>
+        <v>2.6208643913269</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>2.75</v>
       </c>
       <c r="G32" t="n">
-        <v>2.62086510658264</v>
+        <v>2.6208643913269</v>
       </c>
       <c r="H32" t="n">
         <v>1500</v>
@@ -1326,7 +1326,7 @@
         <v>2.75</v>
       </c>
       <c r="G33" t="n">
-        <v>2.62086510658264</v>
+        <v>2.6208643913269</v>
       </c>
       <c r="H33" t="n">
         <v>1500</v>
@@ -1355,7 +1355,7 @@
         <v>2.75</v>
       </c>
       <c r="G34" t="n">
-        <v>2.62086510658264</v>
+        <v>2.6208643913269</v>
       </c>
       <c r="H34" t="n">
         <v>3500</v>
@@ -1384,7 +1384,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G35" t="n">
-        <v>2.67232918739319</v>
+        <v>2.67232894897461</v>
       </c>
       <c r="H35" t="n">
         <v>5500</v>
@@ -1413,7 +1413,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G36" t="n">
-        <v>2.67804718017578</v>
+        <v>2.67804741859436</v>
       </c>
       <c r="H36" t="n">
         <v>18500</v>
@@ -1442,7 +1442,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>2.78288173675537</v>
+        <v>2.78288221359253</v>
       </c>
       <c r="H37" t="n">
         <v>23500</v>
@@ -1471,7 +1471,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G38" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H38" t="n">
         <v>17000</v>
@@ -1500,7 +1500,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H39" t="n">
         <v>21500</v>
@@ -1529,7 +1529,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H40" t="n">
         <v>20000</v>
@@ -1558,7 +1558,7 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>2.85912489891052</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H41" t="n">
         <v>18500</v>
@@ -1587,7 +1587,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G42" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H42" t="n">
         <v>5500</v>
@@ -1616,7 +1616,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G43" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H43" t="n">
         <v>1000</v>
@@ -1645,7 +1645,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.79241228103638</v>
+        <v>2.79241251945496</v>
       </c>
       <c r="H44" t="n">
         <v>1500</v>
@@ -1674,7 +1674,7 @@
         <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>2.85912489891052</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H45" t="n">
         <v>18000</v>
@@ -1703,7 +1703,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442891120911</v>
       </c>
       <c r="H46" t="n">
         <v>12000</v>
@@ -1732,7 +1732,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87818646430969</v>
+        <v>2.87818622589111</v>
       </c>
       <c r="H47" t="n">
         <v>9000</v>
@@ -1761,7 +1761,7 @@
         <v>3.02049994468689</v>
       </c>
       <c r="G48" t="n">
-        <v>2.87866234779358</v>
+        <v>2.87866258621216</v>
       </c>
       <c r="H48" t="n">
         <v>4500</v>
@@ -1819,7 +1819,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442891120911</v>
       </c>
       <c r="H50" t="n">
         <v>13000</v>
@@ -1935,7 +1935,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G54" t="n">
-        <v>2.96395969390869</v>
+        <v>2.96395945549011</v>
       </c>
       <c r="H54" t="n">
         <v>8500</v>
@@ -2022,7 +2022,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442891120911</v>
       </c>
       <c r="H57" t="n">
         <v>2000</v>
@@ -2051,7 +2051,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G58" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442891120911</v>
       </c>
       <c r="H58" t="n">
         <v>9500</v>
@@ -2080,7 +2080,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>2.97348999977112</v>
+        <v>2.97349047660828</v>
       </c>
       <c r="H59" t="n">
         <v>7500</v>
@@ -2109,7 +2109,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G60" t="n">
-        <v>2.97348999977112</v>
+        <v>2.97349047660828</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2138,7 +2138,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442891120911</v>
       </c>
       <c r="H61" t="n">
         <v>1000</v>
@@ -2167,7 +2167,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442891120911</v>
       </c>
       <c r="H62" t="n">
         <v>3000</v>
@@ -2225,7 +2225,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442891120911</v>
       </c>
       <c r="H64" t="n">
         <v>2500</v>
@@ -2254,7 +2254,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>2.87818646430969</v>
+        <v>2.87818622589111</v>
       </c>
       <c r="H65" t="n">
         <v>4000</v>
@@ -2312,7 +2312,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G67" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H67" t="n">
         <v>5000</v>
@@ -2341,7 +2341,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H68" t="n">
         <v>18500</v>
@@ -2370,7 +2370,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G69" t="n">
-        <v>2.84482932090759</v>
+        <v>2.84482955932617</v>
       </c>
       <c r="H69" t="n">
         <v>1500</v>
@@ -2399,7 +2399,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H70" t="n">
         <v>7500</v>
@@ -2428,7 +2428,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80670785903931</v>
+        <v>2.80670809745789</v>
       </c>
       <c r="H71" t="n">
         <v>8000</v>
@@ -2457,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>2.85912489891052</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H72" t="n">
         <v>7500</v>
@@ -2515,7 +2515,7 @@
         <v>3</v>
       </c>
       <c r="G74" t="n">
-        <v>2.85912489891052</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H74" t="n">
         <v>3000</v>
@@ -2544,7 +2544,7 @@
         <v>3</v>
       </c>
       <c r="G75" t="n">
-        <v>2.85912489891052</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H75" t="n">
         <v>3000</v>
@@ -2573,7 +2573,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G76" t="n">
-        <v>2.78288173675537</v>
+        <v>2.78288221359253</v>
       </c>
       <c r="H76" t="n">
         <v>4000</v>
@@ -2631,7 +2631,7 @@
         <v>2.89100003242493</v>
       </c>
       <c r="G78" t="n">
-        <v>2.7552433013916</v>
+        <v>2.75524377822876</v>
       </c>
       <c r="H78" t="n">
         <v>23000</v>
@@ -2718,7 +2718,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H81" t="n">
         <v>3000</v>
@@ -2747,7 +2747,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>2.77335166931152</v>
+        <v>2.77335143089294</v>
       </c>
       <c r="H82" t="n">
         <v>1000</v>
@@ -2805,7 +2805,7 @@
         <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>2.85912489891052</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H84" t="n">
         <v>12500</v>
@@ -2834,7 +2834,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G85" t="n">
-        <v>2.92202615737915</v>
+        <v>2.92202591896057</v>
       </c>
       <c r="H85" t="n">
         <v>1500</v>
@@ -2892,7 +2892,7 @@
         <v>2.99950003623962</v>
       </c>
       <c r="G87" t="n">
-        <v>2.85864901542664</v>
+        <v>2.85864877700806</v>
       </c>
       <c r="H87" t="n">
         <v>14000</v>
@@ -2950,7 +2950,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G89" t="n">
-        <v>2.85054802894592</v>
+        <v>2.85054779052734</v>
       </c>
       <c r="H89" t="n">
         <v>3000</v>
@@ -2979,7 +2979,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G90" t="n">
-        <v>2.85054802894592</v>
+        <v>2.85054779052734</v>
       </c>
       <c r="H90" t="n">
         <v>4500</v>
@@ -3008,7 +3008,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G91" t="n">
-        <v>2.85054802894592</v>
+        <v>2.85054779052734</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>2.93050003051758</v>
       </c>
       <c r="G92" t="n">
-        <v>2.79288864135742</v>
+        <v>2.79288911819458</v>
       </c>
       <c r="H92" t="n">
         <v>500</v>
@@ -3124,7 +3124,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G95" t="n">
-        <v>2.82576894760132</v>
+        <v>2.8257691860199</v>
       </c>
       <c r="H95" t="n">
         <v>3500</v>
@@ -3414,7 +3414,7 @@
         <v>2.98850011825562</v>
       </c>
       <c r="G105" t="n">
-        <v>2.84816527366638</v>
+        <v>2.84816551208496</v>
       </c>
       <c r="H105" t="n">
         <v>2500</v>
@@ -3530,7 +3530,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G109" t="n">
-        <v>2.7204577922821</v>
+        <v>2.72045755386353</v>
       </c>
       <c r="H109" t="n">
         <v>6500</v>
@@ -3559,7 +3559,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G110" t="n">
-        <v>2.7204577922821</v>
+        <v>2.72045755386353</v>
       </c>
       <c r="H110" t="n">
         <v>12500</v>
@@ -3588,7 +3588,7 @@
         <v>2.91700005531311</v>
       </c>
       <c r="G111" t="n">
-        <v>2.78002262115479</v>
+        <v>2.78002285957336</v>
       </c>
       <c r="H111" t="n">
         <v>16500</v>
@@ -3617,7 +3617,7 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>2.85912489891052</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H112" t="n">
         <v>8000</v>
@@ -3646,7 +3646,7 @@
         <v>3.05949997901917</v>
       </c>
       <c r="G113" t="n">
-        <v>2.91583156585693</v>
+        <v>2.91583132743835</v>
       </c>
       <c r="H113" t="n">
         <v>17500</v>
@@ -3675,7 +3675,7 @@
         <v>3.05949997901917</v>
       </c>
       <c r="G114" t="n">
-        <v>2.91583156585693</v>
+        <v>2.91583132743835</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G115" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442891120911</v>
       </c>
       <c r="H115" t="n">
         <v>500</v>
@@ -3762,7 +3762,7 @@
         <v>2.92549991607666</v>
       </c>
       <c r="G117" t="n">
-        <v>2.78812336921692</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H117" t="n">
         <v>9000</v>
@@ -3849,7 +3849,7 @@
         <v>3</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85912489891052</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H120" t="n">
         <v>2000</v>
@@ -3878,7 +3878,7 @@
         <v>3</v>
       </c>
       <c r="G121" t="n">
-        <v>2.85912489891052</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>2.95149993896484</v>
       </c>
       <c r="G122" t="n">
-        <v>2.81290292739868</v>
+        <v>2.81290245056152</v>
       </c>
       <c r="H122" t="n">
         <v>4500</v>
@@ -3936,7 +3936,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H123" t="n">
         <v>500</v>
@@ -3965,7 +3965,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G126" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H126" t="n">
         <v>1000</v>
@@ -4052,7 +4052,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78288173675537</v>
+        <v>2.78288221359253</v>
       </c>
       <c r="H129" t="n">
         <v>9000</v>
@@ -4139,7 +4139,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>2.78288173675537</v>
+        <v>2.78288221359253</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G131" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H131" t="n">
         <v>3500</v>
@@ -4197,7 +4197,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G132" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>2.92249989509583</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78526473045349</v>
+        <v>2.78526449203491</v>
       </c>
       <c r="H133" t="n">
         <v>1500</v>
@@ -4255,7 +4255,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H134" t="n">
         <v>1000</v>
@@ -4284,7 +4284,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H135" t="n">
         <v>500</v>
@@ -4313,7 +4313,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G136" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H136" t="n">
         <v>1000</v>
@@ -4342,7 +4342,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G137" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G138" t="n">
-        <v>2.79241228103638</v>
+        <v>2.79241251945496</v>
       </c>
       <c r="H138" t="n">
         <v>6500</v>
@@ -4400,7 +4400,7 @@
         <v>2.95700001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.81814479827881</v>
+        <v>2.81814455986023</v>
       </c>
       <c r="H139" t="n">
         <v>4500</v>
@@ -4429,7 +4429,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G140" t="n">
-        <v>2.87818646430969</v>
+        <v>2.87818622589111</v>
       </c>
       <c r="H140" t="n">
         <v>11500</v>
@@ -4458,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="G141" t="n">
-        <v>2.85912489891052</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H141" t="n">
         <v>500</v>
@@ -4487,7 +4487,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G142" t="n">
-        <v>2.88390421867371</v>
+        <v>2.88390469551086</v>
       </c>
       <c r="H142" t="n">
         <v>500</v>
@@ -4516,7 +4516,7 @@
         <v>3</v>
       </c>
       <c r="G143" t="n">
-        <v>2.85912489891052</v>
+        <v>2.8591251373291</v>
       </c>
       <c r="H143" t="n">
         <v>13500</v>
@@ -4545,7 +4545,7 @@
         <v>3.02950000762939</v>
       </c>
       <c r="G144" t="n">
-        <v>2.8872401714325</v>
+        <v>2.88723993301392</v>
       </c>
       <c r="H144" t="n">
         <v>43000</v>
@@ -4690,7 +4690,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>2.98302102088928</v>
+        <v>2.9830207824707</v>
       </c>
       <c r="H149" t="n">
         <v>31500</v>
@@ -4748,7 +4748,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>3.05926394462585</v>
+        <v>3.05926418304443</v>
       </c>
       <c r="H151" t="n">
         <v>12000</v>
@@ -4777,7 +4777,7 @@
         <v>3.27649998664856</v>
       </c>
       <c r="G152" t="n">
-        <v>3.12264108657837</v>
+        <v>3.12264132499695</v>
       </c>
       <c r="H152" t="n">
         <v>7500</v>
@@ -4806,7 +4806,7 @@
         <v>3.32949995994568</v>
       </c>
       <c r="G153" t="n">
-        <v>3.17315268516541</v>
+        <v>3.17315244674683</v>
       </c>
       <c r="H153" t="n">
         <v>8000</v>
@@ -4835,7 +4835,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G154" t="n">
-        <v>3.24987244606018</v>
+        <v>3.2498722076416</v>
       </c>
       <c r="H154" t="n">
         <v>19000</v>
@@ -4864,7 +4864,7 @@
         <v>3.40949988365173</v>
       </c>
       <c r="G155" t="n">
-        <v>3.24939584732056</v>
+        <v>3.24939608573914</v>
       </c>
       <c r="H155" t="n">
         <v>13000</v>
@@ -5009,7 +5009,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>3.24034190177917</v>
+        <v>3.24034214019775</v>
       </c>
       <c r="H160" t="n">
         <v>5000</v>
@@ -5067,7 +5067,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G162" t="n">
-        <v>3.21175050735474</v>
+        <v>3.21175074577332</v>
       </c>
       <c r="H162" t="n">
         <v>6500</v>
@@ -5096,7 +5096,7 @@
         <v>3.41700005531311</v>
       </c>
       <c r="G163" t="n">
-        <v>3.2565438747406</v>
+        <v>3.25654363632202</v>
       </c>
       <c r="H163" t="n">
         <v>15500</v>
@@ -5125,7 +5125,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>3.21175050735474</v>
+        <v>3.21175074577332</v>
       </c>
       <c r="H164" t="n">
         <v>3500</v>
@@ -5154,7 +5154,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>3.21175050735474</v>
+        <v>3.21175074577332</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.25463771820068</v>
+        <v>3.2546374797821</v>
       </c>
       <c r="H166" t="n">
         <v>14000</v>
@@ -5241,7 +5241,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>3.31658506393433</v>
+        <v>3.31658530235291</v>
       </c>
       <c r="H168" t="n">
         <v>9000</v>
@@ -5270,7 +5270,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>3.31658506393433</v>
+        <v>3.31658530235291</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G172" t="n">
-        <v>3.50242829322815</v>
+        <v>3.50242805480957</v>
       </c>
       <c r="H172" t="n">
         <v>10000</v>
@@ -5386,7 +5386,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>3.58343720436096</v>
+        <v>3.5834367275238</v>
       </c>
       <c r="H173" t="n">
         <v>6500</v>
@@ -5415,7 +5415,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.47860264778137</v>
+        <v>3.47860240936279</v>
       </c>
       <c r="H174" t="n">
         <v>6000</v>
@@ -5444,7 +5444,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G175" t="n">
-        <v>3.55484580993652</v>
+        <v>3.55484533309937</v>
       </c>
       <c r="H175" t="n">
         <v>4000</v>
@@ -5473,7 +5473,7 @@
         <v>3.75</v>
       </c>
       <c r="G176" t="n">
-        <v>3.57390689849854</v>
+        <v>3.57390666007996</v>
       </c>
       <c r="H176" t="n">
         <v>6500</v>
@@ -5502,7 +5502,7 @@
         <v>3.75</v>
       </c>
       <c r="G177" t="n">
-        <v>3.57390689849854</v>
+        <v>3.57390666007996</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>3.84075808525085</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H179" t="n">
         <v>10000</v>
@@ -5647,7 +5647,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G182" t="n">
-        <v>3.62155890464783</v>
+        <v>3.62155866622925</v>
       </c>
       <c r="H182" t="n">
         <v>13500</v>
@@ -5676,7 +5676,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G183" t="n">
-        <v>3.54531526565552</v>
+        <v>3.5453155040741</v>
       </c>
       <c r="H183" t="n">
         <v>19500</v>
@@ -5705,7 +5705,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>3.62155890464783</v>
+        <v>3.62155866622925</v>
       </c>
       <c r="H184" t="n">
         <v>9500</v>
@@ -5734,7 +5734,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G185" t="n">
-        <v>3.66921043395996</v>
+        <v>3.66921067237854</v>
       </c>
       <c r="H185" t="n">
         <v>10000</v>
@@ -5763,7 +5763,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G186" t="n">
-        <v>3.66921043395996</v>
+        <v>3.66921067237854</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>3.65015006065369</v>
+        <v>3.65014982223511</v>
       </c>
       <c r="H189" t="n">
         <v>4350</v>
@@ -5908,7 +5908,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>3.84075808525085</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H191" t="n">
         <v>18218</v>
@@ -5937,7 +5937,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G192" t="n">
-        <v>3.84075808525085</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H192" t="n">
         <v>2550</v>
@@ -5966,7 +5966,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>3.95512390136719</v>
+        <v>3.95512366294861</v>
       </c>
       <c r="H193" t="n">
         <v>3120</v>
@@ -6053,7 +6053,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G196" t="n">
-        <v>3.80263662338257</v>
+        <v>3.80263638496399</v>
       </c>
       <c r="H196" t="n">
         <v>3767</v>
@@ -6082,7 +6082,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>3.85028910636902</v>
+        <v>3.85028886795044</v>
       </c>
       <c r="H197" t="n">
         <v>810</v>
@@ -6169,7 +6169,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G200" t="n">
-        <v>3.77414274215698</v>
+        <v>3.77414298057556</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>4</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83161687850952</v>
+        <v>3.83161664009094</v>
       </c>
       <c r="H201" t="n">
         <v>14910</v>
@@ -6227,7 +6227,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>3.92740702629089</v>
+        <v>3.92740678787231</v>
       </c>
       <c r="H202" t="n">
         <v>6500</v>
@@ -6256,7 +6256,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>3.87951254844666</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H203" t="n">
         <v>3200</v>
@@ -6285,7 +6285,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>3.88909149169922</v>
+        <v>3.88909101486206</v>
       </c>
       <c r="H204" t="n">
         <v>23362</v>
@@ -6372,7 +6372,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>3.77414274215698</v>
+        <v>3.77414298057556</v>
       </c>
       <c r="H207" t="n">
         <v>6680</v>
@@ -6401,7 +6401,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>3.70708918571472</v>
+        <v>3.70708966255188</v>
       </c>
       <c r="H208" t="n">
         <v>1000</v>
@@ -6430,7 +6430,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G209" t="n">
-        <v>3.69751024246216</v>
+        <v>3.69751048088074</v>
       </c>
       <c r="H209" t="n">
         <v>500</v>
@@ -6459,7 +6459,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G210" t="n">
-        <v>3.69751024246216</v>
+        <v>3.69751048088074</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>3.83161687850952</v>
+        <v>3.83161664009094</v>
       </c>
       <c r="H211" t="n">
         <v>12500</v>
@@ -6517,7 +6517,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>3.87951254844666</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H212" t="n">
         <v>12189</v>
@@ -6546,7 +6546,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>3.87951254844666</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>3.87951254844666</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H215" t="n">
         <v>1090</v>
@@ -6633,7 +6633,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>3.87951254844666</v>
+        <v>3.8795120716095</v>
       </c>
       <c r="H216" t="n">
         <v>1000</v>
@@ -6662,7 +6662,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.93698692321777</v>
+        <v>3.93698644638062</v>
       </c>
       <c r="H217" t="n">
         <v>4860</v>
@@ -6691,7 +6691,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G218" t="n">
-        <v>3.94656562805176</v>
+        <v>3.94656586647034</v>
       </c>
       <c r="H218" t="n">
         <v>18231</v>
@@ -6720,7 +6720,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>4.02319812774658</v>
+        <v>4.02319765090942</v>
       </c>
       <c r="H219" t="n">
         <v>14879</v>
@@ -6836,7 +6836,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G223" t="n">
-        <v>4.14772510528564</v>
+        <v>4.1477255821228</v>
       </c>
       <c r="H223" t="n">
         <v>2021</v>
@@ -6894,7 +6894,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G225" t="n">
-        <v>4.3967809677124</v>
+        <v>4.39678049087524</v>
       </c>
       <c r="H225" t="n">
         <v>12211</v>
@@ -6981,7 +6981,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>4.45425415039062</v>
+        <v>4.45425462722778</v>
       </c>
       <c r="H228" t="n">
         <v>14610</v>
@@ -7010,7 +7010,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G229" t="n">
-        <v>4.43509674072266</v>
+        <v>4.43509721755981</v>
       </c>
       <c r="H229" t="n">
         <v>5450</v>
@@ -7039,7 +7039,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>4.3872013092041</v>
+        <v>4.38720178604126</v>
       </c>
       <c r="H230" t="n">
         <v>3150</v>
@@ -7068,7 +7068,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G231" t="n">
-        <v>4.48299264907837</v>
+        <v>4.48299217224121</v>
       </c>
       <c r="H231" t="n">
         <v>3020</v>
@@ -7155,7 +7155,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>4.66499328613281</v>
+        <v>4.66499376296997</v>
       </c>
       <c r="H234" t="n">
         <v>11495</v>
@@ -7184,7 +7184,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G235" t="n">
-        <v>4.6841516494751</v>
+        <v>4.68415117263794</v>
       </c>
       <c r="H235" t="n">
         <v>6841</v>
@@ -7242,7 +7242,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G237" t="n">
-        <v>4.96194362640381</v>
+        <v>4.96194410324097</v>
       </c>
       <c r="H237" t="n">
         <v>30201</v>
@@ -7387,7 +7387,7 @@
         <v>5</v>
       </c>
       <c r="G242" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H242" t="n">
         <v>16194</v>
@@ -7416,7 +7416,7 @@
         <v>5</v>
       </c>
       <c r="G243" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H243" t="n">
         <v>18850</v>
@@ -7445,7 +7445,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783651351929</v>
       </c>
       <c r="H244" t="n">
         <v>3855</v>
@@ -7474,7 +7474,7 @@
         <v>5</v>
       </c>
       <c r="G245" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H245" t="n">
         <v>1200</v>
@@ -7503,7 +7503,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>4.71288967132568</v>
+        <v>4.71288919448853</v>
       </c>
       <c r="H246" t="n">
         <v>5934</v>
@@ -7532,7 +7532,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>4.71288967132568</v>
+        <v>4.71288919448853</v>
       </c>
       <c r="H247" t="n">
         <v>4150</v>
@@ -7561,7 +7561,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G248" t="n">
-        <v>4.71288967132568</v>
+        <v>4.71288919448853</v>
       </c>
       <c r="H248" t="n">
         <v>3000</v>
@@ -7590,7 +7590,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G249" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H249" t="n">
         <v>140</v>
@@ -7619,7 +7619,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G250" t="n">
-        <v>4.65541553497314</v>
+        <v>4.65541505813599</v>
       </c>
       <c r="H250" t="n">
         <v>750</v>
@@ -7648,7 +7648,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G251" t="n">
-        <v>4.65541553497314</v>
+        <v>4.65541505813599</v>
       </c>
       <c r="H251" t="n">
         <v>1500</v>
@@ -7677,7 +7677,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H252" t="n">
         <v>2483</v>
@@ -7706,7 +7706,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783651351929</v>
       </c>
       <c r="H253" t="n">
         <v>3900</v>
@@ -7735,7 +7735,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H254" t="n">
         <v>9900</v>
@@ -7764,7 +7764,7 @@
         <v>5</v>
       </c>
       <c r="G255" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H255" t="n">
         <v>13400</v>
@@ -7851,7 +7851,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G258" t="n">
-        <v>4.48299264907837</v>
+        <v>4.48299217224121</v>
       </c>
       <c r="H258" t="n">
         <v>11514</v>
@@ -7880,7 +7880,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>4.6362566947937</v>
+        <v>4.63625717163086</v>
       </c>
       <c r="H259" t="n">
         <v>5992</v>
@@ -7909,7 +7909,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G260" t="n">
-        <v>4.66499328613281</v>
+        <v>4.66499376296997</v>
       </c>
       <c r="H260" t="n">
         <v>1936</v>
@@ -7938,7 +7938,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>4.66499328613281</v>
+        <v>4.66499376296997</v>
       </c>
       <c r="H261" t="n">
         <v>12495</v>
@@ -7996,7 +7996,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>4.64583492279053</v>
+        <v>4.64583539962769</v>
       </c>
       <c r="H263" t="n">
         <v>581</v>
@@ -8112,7 +8112,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>4.59794092178345</v>
+        <v>4.59793996810913</v>
       </c>
       <c r="H267" t="n">
         <v>1400</v>
@@ -8141,7 +8141,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>4.59794092178345</v>
+        <v>4.59793996810913</v>
       </c>
       <c r="H268" t="n">
         <v>1635</v>
@@ -8170,7 +8170,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G269" t="n">
-        <v>4.59794092178345</v>
+        <v>4.59793996810913</v>
       </c>
       <c r="H269" t="n">
         <v>4049</v>
@@ -8315,7 +8315,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078414916992</v>
       </c>
       <c r="H274" t="n">
         <v>4784</v>
@@ -8344,7 +8344,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G275" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078414916992</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G276" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H276" t="n">
         <v>900</v>
@@ -8431,7 +8431,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G278" t="n">
-        <v>4.65541553497314</v>
+        <v>4.65541505813599</v>
       </c>
       <c r="H278" t="n">
         <v>500</v>
@@ -8518,7 +8518,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>4.71288967132568</v>
+        <v>4.71288919448853</v>
       </c>
       <c r="H281" t="n">
         <v>1663</v>
@@ -8547,7 +8547,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.64583492279053</v>
+        <v>4.64583539962769</v>
       </c>
       <c r="H282" t="n">
         <v>2700</v>
@@ -8576,7 +8576,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>4.64583492279053</v>
+        <v>4.64583539962769</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G294" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078414916992</v>
       </c>
       <c r="H294" t="n">
         <v>2200</v>
@@ -9185,7 +9185,7 @@
         <v>5</v>
       </c>
       <c r="G304" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H304" t="n">
         <v>25540</v>
@@ -9214,7 +9214,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783651351929</v>
       </c>
       <c r="H305" t="n">
         <v>4750</v>
@@ -9388,7 +9388,7 @@
         <v>5</v>
       </c>
       <c r="G311" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H311" t="n">
         <v>5186</v>
@@ -9417,7 +9417,7 @@
         <v>5</v>
       </c>
       <c r="G312" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078414916992</v>
       </c>
       <c r="H315" t="n">
         <v>2985</v>
@@ -9533,7 +9533,7 @@
         <v>5</v>
       </c>
       <c r="G316" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H316" t="n">
         <v>402</v>
@@ -9562,7 +9562,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H317" t="n">
         <v>6452</v>
@@ -9591,7 +9591,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783651351929</v>
       </c>
       <c r="H320" t="n">
         <v>100</v>
@@ -9678,7 +9678,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783651351929</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>5</v>
       </c>
       <c r="G322" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H322" t="n">
         <v>3400</v>
@@ -9736,7 +9736,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783651351929</v>
       </c>
       <c r="H323" t="n">
         <v>54154</v>
@@ -9794,7 +9794,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783651351929</v>
       </c>
       <c r="H325" t="n">
         <v>1040</v>
@@ -9823,7 +9823,7 @@
         <v>5</v>
       </c>
       <c r="G326" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H326" t="n">
         <v>3000</v>
@@ -9881,7 +9881,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783651351929</v>
       </c>
       <c r="H328" t="n">
         <v>170</v>
@@ -9910,7 +9910,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783651351929</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>5</v>
       </c>
       <c r="G330" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H330" t="n">
         <v>7750</v>
@@ -9997,7 +9997,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783651351929</v>
       </c>
       <c r="H332" t="n">
         <v>4683</v>
@@ -10026,7 +10026,7 @@
         <v>5</v>
       </c>
       <c r="G333" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H333" t="n">
         <v>1125</v>
@@ -10084,7 +10084,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.77036285400391</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H335" t="n">
         <v>16377</v>
@@ -10113,7 +10113,7 @@
         <v>5</v>
       </c>
       <c r="G336" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H336" t="n">
         <v>17100</v>
@@ -10142,7 +10142,7 @@
         <v>5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.78952169418335</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H337" t="n">
         <v>12410</v>
@@ -10171,7 +10171,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783651351929</v>
       </c>
       <c r="H338" t="n">
         <v>6710</v>
@@ -10200,7 +10200,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G339" t="n">
-        <v>4.88531160354614</v>
+        <v>4.88531112670898</v>
       </c>
       <c r="H339" t="n">
         <v>7300</v>
@@ -10258,7 +10258,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.88531160354614</v>
+        <v>4.88531112670898</v>
       </c>
       <c r="H341" t="n">
         <v>8729</v>
@@ -10374,7 +10374,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>5.172682762146</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H345" t="n">
         <v>14432</v>
@@ -10403,7 +10403,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.11520910263062</v>
+        <v>5.1152081489563</v>
       </c>
       <c r="H346" t="n">
         <v>11091</v>
@@ -10432,7 +10432,7 @@
         <v>5.5</v>
       </c>
       <c r="G347" t="n">
-        <v>5.26847362518311</v>
+        <v>5.26847314834595</v>
       </c>
       <c r="H347" t="n">
         <v>19952</v>
@@ -10461,7 +10461,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G348" t="n">
-        <v>5.32594776153564</v>
+        <v>5.32594728469849</v>
       </c>
       <c r="H348" t="n">
         <v>20019</v>
@@ -10490,7 +10490,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G349" t="n">
-        <v>5.21099901199341</v>
+        <v>5.21099996566772</v>
       </c>
       <c r="H349" t="n">
         <v>3837</v>
@@ -10606,7 +10606,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G353" t="n">
-        <v>5.09605121612549</v>
+        <v>5.09605073928833</v>
       </c>
       <c r="H353" t="n">
         <v>1649</v>
@@ -10635,7 +10635,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>5.172682762146</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H354" t="n">
         <v>10600</v>
@@ -10722,7 +10722,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>5.172682762146</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H357" t="n">
         <v>2620</v>
@@ -10751,7 +10751,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G358" t="n">
-        <v>5.172682762146</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H358" t="n">
         <v>2200</v>
@@ -10780,7 +10780,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G359" t="n">
-        <v>5.01941823959351</v>
+        <v>5.01941776275635</v>
       </c>
       <c r="H359" t="n">
         <v>5962</v>
@@ -10838,7 +10838,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G361" t="n">
-        <v>5.21099901199341</v>
+        <v>5.21099996566772</v>
       </c>
       <c r="H361" t="n">
         <v>5616</v>
@@ -10954,7 +10954,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G365" t="n">
-        <v>5.32594776153564</v>
+        <v>5.32594728469849</v>
       </c>
       <c r="H365" t="n">
         <v>16013</v>
@@ -11041,7 +11041,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G368" t="n">
-        <v>5.47921133041382</v>
+        <v>5.47921180725098</v>
       </c>
       <c r="H368" t="n">
         <v>12600</v>
@@ -11070,7 +11070,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G369" t="n">
-        <v>5.53668689727783</v>
+        <v>5.53668737411499</v>
       </c>
       <c r="H369" t="n">
         <v>11072</v>
@@ -11099,7 +11099,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G370" t="n">
-        <v>5.53668689727783</v>
+        <v>5.53668737411499</v>
       </c>
       <c r="H370" t="n">
         <v>4790</v>
@@ -11128,7 +11128,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>5.68995094299316</v>
+        <v>5.68995189666748</v>
       </c>
       <c r="H371" t="n">
         <v>95523</v>
@@ -11157,7 +11157,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>5.65163516998291</v>
+        <v>5.65163421630859</v>
       </c>
       <c r="H372" t="n">
         <v>10973</v>
@@ -11186,7 +11186,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>5.84321641921997</v>
+        <v>5.84321594238281</v>
       </c>
       <c r="H373" t="n">
         <v>42690</v>
@@ -11215,7 +11215,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H374" t="n">
         <v>28432</v>
@@ -11244,7 +11244,7 @@
         <v>6</v>
       </c>
       <c r="G375" t="n">
-        <v>5.7474250793457</v>
+        <v>5.74742555618286</v>
       </c>
       <c r="H375" t="n">
         <v>36585</v>
@@ -11302,7 +11302,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G377" t="n">
-        <v>5.90069055557251</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H377" t="n">
         <v>7100</v>
@@ -11505,7 +11505,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G384" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H384" t="n">
         <v>4781</v>
@@ -11534,7 +11534,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H385" t="n">
         <v>6939</v>
@@ -11563,7 +11563,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G386" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H386" t="n">
         <v>4823</v>
@@ -11592,7 +11592,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H387" t="n">
         <v>12576</v>
@@ -11621,7 +11621,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G388" t="n">
-        <v>5.97732210159302</v>
+        <v>5.97732305526733</v>
       </c>
       <c r="H388" t="n">
         <v>6806</v>
@@ -11650,7 +11650,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>5.82405805587769</v>
+        <v>5.82405853271484</v>
       </c>
       <c r="H389" t="n">
         <v>8803</v>
@@ -11679,7 +11679,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H390" t="n">
         <v>1250</v>
@@ -11737,7 +11737,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H392" t="n">
         <v>6232</v>
@@ -11795,7 +11795,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G394" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H394" t="n">
         <v>1262</v>
@@ -11824,7 +11824,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G395" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H395" t="n">
         <v>4960</v>
@@ -11853,7 +11853,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>6.0347957611084</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H396" t="n">
         <v>4428</v>
@@ -11882,7 +11882,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311296463013</v>
       </c>
       <c r="H397" t="n">
         <v>4390</v>
@@ -11911,7 +11911,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964200973511</v>
       </c>
       <c r="H398" t="n">
         <v>14389</v>
@@ -11940,7 +11940,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G399" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964200973511</v>
       </c>
       <c r="H399" t="n">
         <v>32191</v>
@@ -11969,7 +11969,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>6.32216739654541</v>
+        <v>6.32216787338257</v>
       </c>
       <c r="H400" t="n">
         <v>11804</v>
@@ -12027,7 +12027,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G402" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964200973511</v>
       </c>
       <c r="H402" t="n">
         <v>7998</v>
@@ -12085,7 +12085,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G404" t="n">
-        <v>6.39880037307739</v>
+        <v>6.39879989624023</v>
       </c>
       <c r="H404" t="n">
         <v>3594</v>
@@ -12114,7 +12114,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>6.32216739654541</v>
+        <v>6.32216787338257</v>
       </c>
       <c r="H405" t="n">
         <v>37562</v>
@@ -12172,7 +12172,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G407" t="n">
-        <v>6.49459075927734</v>
+        <v>6.4945912361145</v>
       </c>
       <c r="H407" t="n">
         <v>9368</v>
@@ -12201,7 +12201,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>6.41795873641968</v>
+        <v>6.41795778274536</v>
       </c>
       <c r="H408" t="n">
         <v>8123</v>
@@ -12230,7 +12230,7 @@
         <v>6.5</v>
       </c>
       <c r="G409" t="n">
-        <v>6.22637701034546</v>
+        <v>6.22637748718262</v>
       </c>
       <c r="H409" t="n">
         <v>17409</v>
@@ -12259,7 +12259,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G410" t="n">
-        <v>6.0347957611084</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H410" t="n">
         <v>28571</v>
@@ -12288,7 +12288,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>6.0347957611084</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H411" t="n">
         <v>18050</v>
@@ -12317,7 +12317,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G412" t="n">
-        <v>6.0347957611084</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H412" t="n">
         <v>14848</v>
@@ -12375,7 +12375,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G414" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311296463013</v>
       </c>
       <c r="H414" t="n">
         <v>26996</v>
@@ -12433,7 +12433,7 @@
         <v>6</v>
       </c>
       <c r="G416" t="n">
-        <v>5.7474250793457</v>
+        <v>5.74742555618286</v>
       </c>
       <c r="H416" t="n">
         <v>12034</v>
@@ -12462,7 +12462,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G417" t="n">
-        <v>5.90069055557251</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H417" t="n">
         <v>11796</v>
@@ -12491,7 +12491,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>5.72826719284058</v>
+        <v>5.72826766967773</v>
       </c>
       <c r="H418" t="n">
         <v>21988</v>
@@ -12520,7 +12520,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G419" t="n">
-        <v>5.90069055557251</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H419" t="n">
         <v>4174</v>
@@ -12549,7 +12549,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>5.70910930633545</v>
+        <v>5.70910978317261</v>
       </c>
       <c r="H420" t="n">
         <v>8111</v>
@@ -12578,7 +12578,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>5.70910930633545</v>
+        <v>5.70910978317261</v>
       </c>
       <c r="H421" t="n">
         <v>18321</v>
@@ -12607,7 +12607,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>5.67079257965088</v>
+        <v>5.67079305648804</v>
       </c>
       <c r="H422" t="n">
         <v>18735</v>
@@ -12636,7 +12636,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G423" t="n">
-        <v>5.67079257965088</v>
+        <v>5.67079305648804</v>
       </c>
       <c r="H423" t="n">
         <v>2501</v>
@@ -12694,7 +12694,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900537490845</v>
       </c>
       <c r="H425" t="n">
         <v>2570</v>
@@ -12723,7 +12723,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G426" t="n">
-        <v>5.97732210159302</v>
+        <v>5.97732305526733</v>
       </c>
       <c r="H426" t="n">
         <v>8830</v>
@@ -12781,7 +12781,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311296463013</v>
       </c>
       <c r="H428" t="n">
         <v>6440</v>
@@ -12810,7 +12810,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G429" t="n">
-        <v>6.0347957611084</v>
+        <v>6.03479671478271</v>
       </c>
       <c r="H429" t="n">
         <v>6859</v>
@@ -12897,7 +12897,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G432" t="n">
-        <v>6.11142873764038</v>
+        <v>6.11142921447754</v>
       </c>
       <c r="H432" t="n">
         <v>9507</v>
@@ -12926,7 +12926,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>6.30300951004028</v>
+        <v>6.3030104637146</v>
       </c>
       <c r="H433" t="n">
         <v>5881</v>
@@ -12955,7 +12955,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>6.41795873641968</v>
+        <v>6.41795778274536</v>
       </c>
       <c r="H434" t="n">
         <v>27535</v>
@@ -12984,7 +12984,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>6.41795873641968</v>
+        <v>6.41795778274536</v>
       </c>
       <c r="H435" t="n">
         <v>5559</v>
@@ -13013,7 +13013,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G436" t="n">
-        <v>6.57122325897217</v>
+        <v>6.57122278213501</v>
       </c>
       <c r="H436" t="n">
         <v>24597</v>
@@ -13042,7 +13042,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G437" t="n">
-        <v>6.62869787216187</v>
+        <v>6.62869691848755</v>
       </c>
       <c r="H437" t="n">
         <v>19470</v>
@@ -13071,7 +13071,7 @@
         <v>7</v>
       </c>
       <c r="G438" t="n">
-        <v>6.70532989501953</v>
+        <v>6.70532894134521</v>
       </c>
       <c r="H438" t="n">
         <v>17634</v>
@@ -13100,7 +13100,7 @@
         <v>7</v>
       </c>
       <c r="G439" t="n">
-        <v>6.70532989501953</v>
+        <v>6.70532894134521</v>
       </c>
       <c r="H439" t="n">
         <v>12013</v>
@@ -13129,7 +13129,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>6.64785575866699</v>
+        <v>6.64785528182983</v>
       </c>
       <c r="H440" t="n">
         <v>3991</v>
@@ -13158,7 +13158,7 @@
         <v>7</v>
       </c>
       <c r="G441" t="n">
-        <v>6.70532989501953</v>
+        <v>6.70532894134521</v>
       </c>
       <c r="H441" t="n">
         <v>8061</v>
@@ -13187,7 +13187,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G442" t="n">
-        <v>6.6861720085144</v>
+        <v>6.68617153167725</v>
       </c>
       <c r="H442" t="n">
         <v>4094</v>
@@ -13216,7 +13216,7 @@
         <v>7</v>
       </c>
       <c r="G443" t="n">
-        <v>6.70532989501953</v>
+        <v>6.70532894134521</v>
       </c>
       <c r="H443" t="n">
         <v>701</v>
@@ -13245,7 +13245,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G444" t="n">
-        <v>6.78196144104004</v>
+        <v>6.7819619178772</v>
       </c>
       <c r="H444" t="n">
         <v>9214</v>
@@ -13274,7 +13274,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>6.99270153045654</v>
+        <v>6.99270057678223</v>
       </c>
       <c r="H445" t="n">
         <v>26998</v>
@@ -13332,7 +13332,7 @@
         <v>7.5</v>
       </c>
       <c r="G447" t="n">
-        <v>7.18428230285645</v>
+        <v>7.18428134918213</v>
       </c>
       <c r="H447" t="n">
         <v>16792</v>
@@ -13361,7 +13361,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G448" t="n">
-        <v>7.50997018814087</v>
+        <v>7.50996923446655</v>
       </c>
       <c r="H448" t="n">
         <v>21129</v>
@@ -13390,7 +13390,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G449" t="n">
-        <v>7.79734086990356</v>
+        <v>7.79734134674072</v>
       </c>
       <c r="H449" t="n">
         <v>25454</v>
@@ -13419,7 +13419,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G450" t="n">
-        <v>7.68239307403564</v>
+        <v>7.68239212036133</v>
       </c>
       <c r="H450" t="n">
         <v>46433</v>
@@ -13535,7 +13535,7 @@
         <v>8.5</v>
       </c>
       <c r="G454" t="n">
-        <v>8.1715087890625</v>
+        <v>8.17150974273682</v>
       </c>
       <c r="H454" t="n">
         <v>44078</v>
@@ -13564,7 +13564,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G455" t="n">
-        <v>7.99846506118774</v>
+        <v>7.99846601486206</v>
       </c>
       <c r="H455" t="n">
         <v>13585</v>
@@ -13651,7 +13651,7 @@
         <v>8.5</v>
       </c>
       <c r="G458" t="n">
-        <v>8.1715087890625</v>
+        <v>8.17150974273682</v>
       </c>
       <c r="H458" t="n">
         <v>10004</v>
@@ -13825,7 +13825,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>7.8061957359314</v>
+        <v>7.80619478225708</v>
       </c>
       <c r="H464" t="n">
         <v>13308</v>
@@ -13854,7 +13854,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>7.53701639175415</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H465" t="n">
         <v>22593</v>
@@ -13912,7 +13912,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>7.22938299179077</v>
+        <v>7.22938203811646</v>
       </c>
       <c r="H467" t="n">
         <v>4220</v>
@@ -13999,7 +13999,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G470" t="n">
-        <v>7.24861001968384</v>
+        <v>7.24860906600952</v>
       </c>
       <c r="H470" t="n">
         <v>1139</v>
@@ -14028,7 +14028,7 @@
         <v>7.5</v>
       </c>
       <c r="G471" t="n">
-        <v>7.21015596389771</v>
+        <v>7.21015548706055</v>
       </c>
       <c r="H471" t="n">
         <v>4606</v>
@@ -14057,7 +14057,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>7.19092798233032</v>
+        <v>7.19092845916748</v>
       </c>
       <c r="H472" t="n">
         <v>4262</v>
@@ -14086,7 +14086,7 @@
         <v>7.5</v>
       </c>
       <c r="G473" t="n">
-        <v>7.21015596389771</v>
+        <v>7.21015548706055</v>
       </c>
       <c r="H473" t="n">
         <v>577622</v>
@@ -14115,7 +14115,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G474" t="n">
-        <v>7.07556676864624</v>
+        <v>7.07556581497192</v>
       </c>
       <c r="H474" t="n">
         <v>13451</v>
@@ -14260,7 +14260,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>7.63315153121948</v>
+        <v>7.63315105438232</v>
       </c>
       <c r="H479" t="n">
         <v>7940</v>
@@ -14318,7 +14318,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G481" t="n">
-        <v>7.61392402648926</v>
+        <v>7.61392450332642</v>
       </c>
       <c r="H481" t="n">
         <v>6569</v>
@@ -14463,7 +14463,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>7.61392402648926</v>
+        <v>7.61392450332642</v>
       </c>
       <c r="H486" t="n">
         <v>6297</v>
@@ -14695,7 +14695,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>7.53701639175415</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H494" t="n">
         <v>1276</v>
@@ -14724,7 +14724,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>7.53701639175415</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H495" t="n">
         <v>3732</v>
@@ -14782,7 +14782,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G497" t="n">
-        <v>7.53701639175415</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H497" t="n">
         <v>370</v>
@@ -14811,7 +14811,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.61392402648926</v>
+        <v>7.61392450332642</v>
       </c>
       <c r="H498" t="n">
         <v>19417</v>
@@ -14840,7 +14840,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63315153121948</v>
+        <v>7.63315105438232</v>
       </c>
       <c r="H499" t="n">
         <v>6971</v>
@@ -14869,7 +14869,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>7.76774120330811</v>
+        <v>7.76774168014526</v>
       </c>
       <c r="H500" t="n">
         <v>19279</v>
@@ -14898,7 +14898,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>7.76774120330811</v>
+        <v>7.76774168014526</v>
       </c>
       <c r="H501" t="n">
         <v>1200</v>
@@ -14927,7 +14927,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G502" t="n">
-        <v>7.63315153121948</v>
+        <v>7.63315105438232</v>
       </c>
       <c r="H502" t="n">
         <v>7166</v>
@@ -14956,7 +14956,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G503" t="n">
-        <v>7.67160558700562</v>
+        <v>7.67160511016846</v>
       </c>
       <c r="H503" t="n">
         <v>23875</v>
@@ -14985,7 +14985,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G504" t="n">
-        <v>7.8254222869873</v>
+        <v>7.82542276382446</v>
       </c>
       <c r="H504" t="n">
         <v>8213</v>
@@ -15072,7 +15072,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G507" t="n">
-        <v>8.34455394744873</v>
+        <v>8.34455299377441</v>
       </c>
       <c r="H507" t="n">
         <v>18075</v>
@@ -15159,7 +15159,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G510" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H510" t="n">
         <v>4438</v>
@@ -15188,7 +15188,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G511" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H511" t="n">
         <v>2825</v>
@@ -15246,7 +15246,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G513" t="n">
-        <v>8.74832248687744</v>
+        <v>8.74832344055176</v>
       </c>
       <c r="H513" t="n">
         <v>3322</v>
@@ -15333,7 +15333,7 @@
         <v>9.5</v>
       </c>
       <c r="G516" t="n">
-        <v>9.1328649520874</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H516" t="n">
         <v>4264</v>
@@ -15362,7 +15362,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G517" t="n">
-        <v>9.36358737945557</v>
+        <v>9.36358833312988</v>
       </c>
       <c r="H517" t="n">
         <v>19813</v>
@@ -15391,7 +15391,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G518" t="n">
-        <v>9.30590724945068</v>
+        <v>9.305908203125</v>
       </c>
       <c r="H518" t="n">
         <v>7428</v>
@@ -15420,7 +15420,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G519" t="n">
-        <v>9.30590724945068</v>
+        <v>9.305908203125</v>
       </c>
       <c r="H519" t="n">
         <v>9652</v>
@@ -15449,7 +15449,7 @@
         <v>9.5</v>
       </c>
       <c r="G520" t="n">
-        <v>9.1328649520874</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H520" t="n">
         <v>6538</v>
@@ -15594,7 +15594,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G525" t="n">
-        <v>9.34436321258545</v>
+        <v>9.34436130523682</v>
       </c>
       <c r="H525" t="n">
         <v>2160</v>
@@ -15623,7 +15623,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G526" t="n">
-        <v>9.36358737945557</v>
+        <v>9.36358833312988</v>
       </c>
       <c r="H526" t="n">
         <v>5384</v>
@@ -15739,7 +15739,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G530" t="n">
-        <v>8.70986938476562</v>
+        <v>8.70986747741699</v>
       </c>
       <c r="H530" t="n">
         <v>13372</v>
@@ -15797,7 +15797,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G532" t="n">
-        <v>9.07518196105957</v>
+        <v>9.07518100738525</v>
       </c>
       <c r="H532" t="n">
         <v>11482</v>
@@ -15971,7 +15971,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G538" t="n">
-        <v>8.74832248687744</v>
+        <v>8.74832344055176</v>
       </c>
       <c r="H538" t="n">
         <v>4284</v>
@@ -16000,7 +16000,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>8.69064044952393</v>
+        <v>8.69064140319824</v>
       </c>
       <c r="H539" t="n">
         <v>10503</v>
@@ -16145,7 +16145,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G544" t="n">
-        <v>8.4791431427002</v>
+        <v>8.47914218902588</v>
       </c>
       <c r="H544" t="n">
         <v>4043</v>
@@ -16377,7 +16377,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G552" t="n">
-        <v>8.36378002166748</v>
+        <v>8.36377906799316</v>
       </c>
       <c r="H552" t="n">
         <v>2520</v>
@@ -16464,7 +16464,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G555" t="n">
-        <v>8.36378002166748</v>
+        <v>8.36377906799316</v>
       </c>
       <c r="H555" t="n">
         <v>2093</v>
@@ -16551,7 +16551,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H558" t="n">
         <v>10958</v>
@@ -16580,7 +16580,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G559" t="n">
-        <v>8.55605125427246</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H559" t="n">
         <v>5484</v>
@@ -16667,7 +16667,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G562" t="n">
-        <v>8.95981979370117</v>
+        <v>8.95982074737549</v>
       </c>
       <c r="H562" t="n">
         <v>13014</v>
@@ -16696,7 +16696,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G563" t="n">
-        <v>8.90213871002197</v>
+        <v>8.90213966369629</v>
       </c>
       <c r="H563" t="n">
         <v>9291</v>
@@ -16754,7 +16754,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>8.97904682159424</v>
+        <v>8.97904777526855</v>
       </c>
       <c r="H565" t="n">
         <v>5437</v>
@@ -16783,7 +16783,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G566" t="n">
-        <v>8.95981979370117</v>
+        <v>8.95982074737549</v>
       </c>
       <c r="H566" t="n">
         <v>4531</v>
@@ -16812,7 +16812,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G567" t="n">
-        <v>9.19054508209229</v>
+        <v>9.1905460357666</v>
       </c>
       <c r="H567" t="n">
         <v>36349</v>
@@ -16870,7 +16870,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G569" t="n">
-        <v>9.28668117523193</v>
+        <v>9.28668022155762</v>
       </c>
       <c r="H569" t="n">
         <v>14841</v>
@@ -16928,7 +16928,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G571" t="n">
-        <v>9.07518196105957</v>
+        <v>9.07518100738525</v>
       </c>
       <c r="H571" t="n">
         <v>10495</v>
@@ -16986,7 +16986,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>9.07518196105957</v>
+        <v>9.07518100738525</v>
       </c>
       <c r="H573" t="n">
         <v>1872</v>
@@ -17131,7 +17131,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G578" t="n">
-        <v>8.97904682159424</v>
+        <v>8.97904777526855</v>
       </c>
       <c r="H578" t="n">
         <v>1588</v>
@@ -17160,7 +17160,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G579" t="n">
-        <v>8.90213871002197</v>
+        <v>8.90213966369629</v>
       </c>
       <c r="H579" t="n">
         <v>6126</v>
@@ -17247,7 +17247,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G582" t="n">
-        <v>8.70986938476562</v>
+        <v>8.70986747741699</v>
       </c>
       <c r="H582" t="n">
         <v>2983</v>
@@ -17276,7 +17276,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>8.72909450531006</v>
+        <v>8.72909545898438</v>
       </c>
       <c r="H583" t="n">
         <v>2214</v>
@@ -17334,7 +17334,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.69064044952393</v>
+        <v>8.69064140319824</v>
       </c>
       <c r="H585" t="n">
         <v>6475</v>
@@ -17363,7 +17363,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>8.74832248687744</v>
+        <v>8.74832344055176</v>
       </c>
       <c r="H586" t="n">
         <v>3747</v>
@@ -17392,7 +17392,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G587" t="n">
-        <v>8.70986938476562</v>
+        <v>8.70986747741699</v>
       </c>
       <c r="H587" t="n">
         <v>4690</v>
@@ -17421,7 +17421,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G588" t="n">
-        <v>8.70986938476562</v>
+        <v>8.70986747741699</v>
       </c>
       <c r="H588" t="n">
         <v>3314</v>
@@ -17450,7 +17450,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G589" t="n">
-        <v>8.67141437530518</v>
+        <v>8.67141342163086</v>
       </c>
       <c r="H589" t="n">
         <v>4377</v>
@@ -17653,7 +17653,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>8.76754951477051</v>
+        <v>8.76754856109619</v>
       </c>
       <c r="H596" t="n">
         <v>819</v>
@@ -17740,7 +17740,7 @@
         <v>9.5</v>
       </c>
       <c r="G599" t="n">
-        <v>9.1328649520874</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H599" t="n">
         <v>6940</v>
@@ -17769,7 +17769,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G600" t="n">
-        <v>9.34436321258545</v>
+        <v>9.34436130523682</v>
       </c>
       <c r="H600" t="n">
         <v>5708</v>
@@ -17798,7 +17798,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G601" t="n">
-        <v>9.15209007263184</v>
+        <v>9.15209102630615</v>
       </c>
       <c r="H601" t="n">
         <v>10060</v>
@@ -17885,7 +17885,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G604" t="n">
-        <v>9.26745223999023</v>
+        <v>9.26745414733887</v>
       </c>
       <c r="H604" t="n">
         <v>4700</v>
@@ -17914,7 +17914,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G605" t="n">
-        <v>9.36358737945557</v>
+        <v>9.36358833312988</v>
       </c>
       <c r="H605" t="n">
         <v>13690</v>
@@ -18088,7 +18088,7 @@
         <v>9.5</v>
       </c>
       <c r="G611" t="n">
-        <v>9.1328649520874</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H611" t="n">
         <v>9008</v>
@@ -18117,7 +18117,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G612" t="n">
-        <v>9.17131900787354</v>
+        <v>9.1713171005249</v>
       </c>
       <c r="H612" t="n">
         <v>1833</v>
@@ -18146,7 +18146,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G613" t="n">
-        <v>9.15209007263184</v>
+        <v>9.15209102630615</v>
       </c>
       <c r="H613" t="n">
         <v>3820</v>
@@ -18262,7 +18262,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G617" t="n">
-        <v>9.15209007263184</v>
+        <v>9.15209102630615</v>
       </c>
       <c r="H617" t="n">
         <v>668</v>
@@ -18291,7 +18291,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.1328649520874</v>
+        <v>9.13286399841309</v>
       </c>
       <c r="H618" t="n">
         <v>5376</v>
@@ -18378,7 +18378,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>9.17131900787354</v>
+        <v>9.1713171005249</v>
       </c>
       <c r="H621" t="n">
         <v>3769</v>
@@ -18465,7 +18465,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G624" t="n">
-        <v>9.4212703704834</v>
+        <v>9.42126941680908</v>
       </c>
       <c r="H624" t="n">
         <v>23348</v>
@@ -18494,7 +18494,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>9.75774478912354</v>
+        <v>9.7577428817749</v>
       </c>
       <c r="H625" t="n">
         <v>44805</v>
@@ -18668,7 +18668,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>10.1422853469849</v>
+        <v>10.1422872543335</v>
       </c>
       <c r="H631" t="n">
         <v>5772</v>
@@ -18697,7 +18697,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G632" t="n">
-        <v>10.1422853469849</v>
+        <v>10.1422872543335</v>
       </c>
       <c r="H632" t="n">
         <v>5416</v>
@@ -18929,7 +18929,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>10.5268268585205</v>
+        <v>10.5268259048462</v>
       </c>
       <c r="H640" t="n">
         <v>31497</v>
@@ -18958,7 +18958,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>10.4787588119507</v>
+        <v>10.4787578582764</v>
       </c>
       <c r="H641" t="n">
         <v>6326</v>
@@ -18987,7 +18987,7 @@
         <v>10.75</v>
       </c>
       <c r="G642" t="n">
-        <v>10.3345575332642</v>
+        <v>10.3345565795898</v>
       </c>
       <c r="H642" t="n">
         <v>5010</v>
@@ -19016,7 +19016,7 @@
         <v>10.75</v>
       </c>
       <c r="G643" t="n">
-        <v>10.3345575332642</v>
+        <v>10.3345565795898</v>
       </c>
       <c r="H643" t="n">
         <v>2849</v>
@@ -19045,7 +19045,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>10.3826236724854</v>
+        <v>10.3826246261597</v>
       </c>
       <c r="H644" t="n">
         <v>5721</v>
@@ -19074,7 +19074,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G645" t="n">
-        <v>10.3826236724854</v>
+        <v>10.3826246261597</v>
       </c>
       <c r="H645" t="n">
         <v>11643</v>
@@ -19103,7 +19103,7 @@
         <v>10.75</v>
       </c>
       <c r="G646" t="n">
-        <v>10.3345575332642</v>
+        <v>10.3345565795898</v>
       </c>
       <c r="H646" t="n">
         <v>6485</v>
@@ -19132,7 +19132,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>10.4787588119507</v>
+        <v>10.4787578582764</v>
       </c>
       <c r="H647" t="n">
         <v>9307</v>
@@ -19161,7 +19161,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>10.67103099823</v>
+        <v>10.6710300445557</v>
       </c>
       <c r="H648" t="n">
         <v>11173</v>
@@ -19190,7 +19190,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>10.67103099823</v>
+        <v>10.6710300445557</v>
       </c>
       <c r="H649" t="n">
         <v>2351</v>
@@ -19219,7 +19219,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>10.767165184021</v>
+        <v>10.7671661376953</v>
       </c>
       <c r="H650" t="n">
         <v>4282</v>
@@ -19248,7 +19248,7 @@
         <v>11.5</v>
       </c>
       <c r="G651" t="n">
-        <v>11.055570602417</v>
+        <v>11.0555725097656</v>
       </c>
       <c r="H651" t="n">
         <v>18312</v>
@@ -19277,7 +19277,7 @@
         <v>11.5</v>
       </c>
       <c r="G652" t="n">
-        <v>11.055570602417</v>
+        <v>11.0555725097656</v>
       </c>
       <c r="H652" t="n">
         <v>27024</v>
@@ -19364,7 +19364,7 @@
         <v>12.5</v>
       </c>
       <c r="G655" t="n">
-        <v>12.0169267654419</v>
+        <v>12.0169258117676</v>
       </c>
       <c r="H655" t="n">
         <v>11862</v>
@@ -19393,7 +19393,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>12.3053331375122</v>
+        <v>12.3053340911865</v>
       </c>
       <c r="H656" t="n">
         <v>14410</v>
@@ -19451,7 +19451,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G658" t="n">
-        <v>12.5937395095825</v>
+        <v>12.5937385559082</v>
       </c>
       <c r="H658" t="n">
         <v>24363</v>
@@ -19538,7 +19538,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G661" t="n">
-        <v>12.5937395095825</v>
+        <v>12.5937385559082</v>
       </c>
       <c r="H661" t="n">
         <v>12281</v>
@@ -19567,7 +19567,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>12.1130599975586</v>
+        <v>12.1130609512329</v>
       </c>
       <c r="H662" t="n">
         <v>25415</v>
@@ -19596,7 +19596,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G663" t="n">
-        <v>12.7860097885132</v>
+        <v>12.7860088348389</v>
       </c>
       <c r="H663" t="n">
         <v>12196</v>
@@ -19625,7 +19625,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G664" t="n">
-        <v>12.8821449279785</v>
+        <v>12.8821439743042</v>
       </c>
       <c r="H664" t="n">
         <v>11286</v>
@@ -19683,7 +19683,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>12.7860097885132</v>
+        <v>12.7860088348389</v>
       </c>
       <c r="H666" t="n">
         <v>8354</v>
@@ -19712,7 +19712,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>12.7860097885132</v>
+        <v>12.7860088348389</v>
       </c>
       <c r="H667" t="n">
         <v>10497</v>
@@ -19770,7 +19770,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>12.7860097885132</v>
+        <v>12.7860088348389</v>
       </c>
       <c r="H669" t="n">
         <v>5925</v>
@@ -19799,7 +19799,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>12.5937395095825</v>
+        <v>12.5937385559082</v>
       </c>
       <c r="H670" t="n">
         <v>4230</v>
@@ -19886,7 +19886,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G673" t="n">
-        <v>13.0263471603394</v>
+        <v>13.0263481140137</v>
       </c>
       <c r="H673" t="n">
         <v>14959</v>
@@ -19944,7 +19944,7 @@
         <v>14.5</v>
       </c>
       <c r="G675" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396333694458</v>
       </c>
       <c r="H675" t="n">
         <v>5327</v>
@@ -19973,7 +19973,7 @@
         <v>14.5</v>
       </c>
       <c r="G676" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396333694458</v>
       </c>
       <c r="H676" t="n">
         <v>16748</v>
@@ -20002,7 +20002,7 @@
         <v>14.5</v>
       </c>
       <c r="G677" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396333694458</v>
       </c>
       <c r="H677" t="n">
         <v>8967</v>
@@ -20031,7 +20031,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>13.8915662765503</v>
+        <v>13.8915672302246</v>
       </c>
       <c r="H678" t="n">
         <v>14525</v>
@@ -20060,7 +20060,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>13.7954320907593</v>
+        <v>13.795431137085</v>
       </c>
       <c r="H679" t="n">
         <v>3476</v>
@@ -20147,7 +20147,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>13.8915662765503</v>
+        <v>13.8915672302246</v>
       </c>
       <c r="H682" t="n">
         <v>8370</v>
@@ -20176,7 +20176,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>14.0838375091553</v>
+        <v>14.083836555481</v>
       </c>
       <c r="H683" t="n">
         <v>12362</v>
@@ -20263,7 +20263,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>14.0838375091553</v>
+        <v>14.083836555481</v>
       </c>
       <c r="H686" t="n">
         <v>12855</v>
@@ -20292,7 +20292,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G687" t="n">
-        <v>13.9877023696899</v>
+        <v>13.9877014160156</v>
       </c>
       <c r="H687" t="n">
         <v>11853</v>
@@ -20321,7 +20321,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>13.7954320907593</v>
+        <v>13.795431137085</v>
       </c>
       <c r="H688" t="n">
         <v>6328</v>
@@ -20350,7 +20350,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>13.8915662765503</v>
+        <v>13.8915672302246</v>
       </c>
       <c r="H689" t="n">
         <v>13501</v>
@@ -20379,7 +20379,7 @@
         <v>14.5</v>
       </c>
       <c r="G690" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396333694458</v>
       </c>
       <c r="H690" t="n">
         <v>26199</v>
@@ -20408,7 +20408,7 @@
         <v>14.5</v>
       </c>
       <c r="G691" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396333694458</v>
       </c>
       <c r="H691" t="n">
         <v>5887</v>
@@ -20437,7 +20437,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>13.8915662765503</v>
+        <v>13.8915672302246</v>
       </c>
       <c r="H692" t="n">
         <v>7855</v>
@@ -20466,7 +20466,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>13.8915662765503</v>
+        <v>13.8915672302246</v>
       </c>
       <c r="H693" t="n">
         <v>3250</v>
@@ -20495,7 +20495,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>13.8434972763062</v>
+        <v>13.8434982299805</v>
       </c>
       <c r="H694" t="n">
         <v>3277</v>
@@ -20611,7 +20611,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G698" t="n">
-        <v>13.5550918579102</v>
+        <v>13.5550947189331</v>
       </c>
       <c r="H698" t="n">
         <v>6847</v>
@@ -20640,7 +20640,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>13.6031589508057</v>
+        <v>13.60315990448</v>
       </c>
       <c r="H699" t="n">
         <v>8458</v>
@@ -20727,7 +20727,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>13.9877023696899</v>
+        <v>13.9877014160156</v>
       </c>
       <c r="H702" t="n">
         <v>3584</v>
@@ -20756,7 +20756,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>14.0838375091553</v>
+        <v>14.083836555481</v>
       </c>
       <c r="H703" t="n">
         <v>1315</v>
@@ -20785,7 +20785,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>14.0838375091553</v>
+        <v>14.083836555481</v>
       </c>
       <c r="H704" t="n">
         <v>8696</v>
@@ -20814,7 +20814,7 @@
         <v>14.75</v>
       </c>
       <c r="G705" t="n">
-        <v>14.1799716949463</v>
+        <v>14.1799736022949</v>
       </c>
       <c r="H705" t="n">
         <v>1719</v>
@@ -20843,7 +20843,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>14.3631258010864</v>
+        <v>14.3631267547607</v>
       </c>
       <c r="H706" t="n">
         <v>8472</v>
@@ -20959,7 +20959,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G710" t="n">
-        <v>15.8090810775757</v>
+        <v>15.8090791702271</v>
       </c>
       <c r="H710" t="n">
         <v>17022</v>
@@ -20988,7 +20988,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>15.8090810775757</v>
+        <v>15.8090791702271</v>
       </c>
       <c r="H711" t="n">
         <v>27543</v>
@@ -21017,7 +21017,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>15.9536733627319</v>
+        <v>15.9536752700806</v>
       </c>
       <c r="H712" t="n">
         <v>41242</v>
@@ -21104,7 +21104,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>16.5802555084229</v>
+        <v>16.5802574157715</v>
       </c>
       <c r="H715" t="n">
         <v>22030</v>
@@ -21162,7 +21162,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>16.965841293335</v>
+        <v>16.9658393859863</v>
       </c>
       <c r="H717" t="n">
         <v>10720</v>
@@ -21278,7 +21278,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>16.8212471008301</v>
+        <v>16.8212451934814</v>
       </c>
       <c r="H721" t="n">
         <v>6464</v>
@@ -21336,7 +21336,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838581085205</v>
       </c>
       <c r="H723" t="n">
         <v>4063</v>
@@ -21423,7 +21423,7 @@
         <v>16.5</v>
       </c>
       <c r="G726" t="n">
-        <v>15.9054765701294</v>
+        <v>15.9054756164551</v>
       </c>
       <c r="H726" t="n">
         <v>13151</v>
@@ -21539,7 +21539,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>16.5802555084229</v>
+        <v>16.5802574157715</v>
       </c>
       <c r="H730" t="n">
         <v>5817</v>
@@ -21568,7 +21568,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838581085205</v>
       </c>
       <c r="H731" t="n">
         <v>7493</v>
@@ -21597,7 +21597,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838581085205</v>
       </c>
       <c r="H732" t="n">
         <v>8992</v>
@@ -21655,7 +21655,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>16.1946678161621</v>
+        <v>16.1946659088135</v>
       </c>
       <c r="H734" t="n">
         <v>4299</v>
@@ -21684,7 +21684,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>16.0982723236084</v>
+        <v>16.0982685089111</v>
       </c>
       <c r="H735" t="n">
         <v>2046</v>
@@ -21713,7 +21713,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>16.1946678161621</v>
+        <v>16.1946659088135</v>
       </c>
       <c r="H736" t="n">
         <v>11338</v>
@@ -21742,7 +21742,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>16.242862701416</v>
+        <v>16.2428646087646</v>
       </c>
       <c r="H737" t="n">
         <v>1646</v>
@@ -21771,7 +21771,7 @@
         <v>16.75</v>
       </c>
       <c r="G738" t="n">
-        <v>16.1464672088623</v>
+        <v>16.1464691162109</v>
       </c>
       <c r="H738" t="n">
         <v>22483</v>
@@ -21800,7 +21800,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>16.0982723236084</v>
+        <v>16.0982685089111</v>
       </c>
       <c r="H739" t="n">
         <v>6854</v>
@@ -21829,7 +21829,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G740" t="n">
-        <v>15.2306976318359</v>
+        <v>15.2306985855103</v>
       </c>
       <c r="H740" t="n">
         <v>9690</v>
@@ -21858,7 +21858,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>14.8451108932495</v>
+        <v>14.8451099395752</v>
       </c>
       <c r="H741" t="n">
         <v>16758</v>
@@ -21887,7 +21887,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>15.519889831543</v>
+        <v>15.5198888778687</v>
       </c>
       <c r="H742" t="n">
         <v>9416</v>
@@ -21916,7 +21916,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>15.8090810775757</v>
+        <v>15.8090791702271</v>
       </c>
       <c r="H743" t="n">
         <v>1158</v>
@@ -22003,7 +22003,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G746" t="n">
-        <v>15.2306976318359</v>
+        <v>15.2306985855103</v>
       </c>
       <c r="H746" t="n">
         <v>4628</v>
@@ -22032,7 +22032,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>14.8451108932495</v>
+        <v>14.8451099395752</v>
       </c>
       <c r="H747" t="n">
         <v>13532</v>
@@ -22090,7 +22090,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G749" t="n">
-        <v>14.8451108932495</v>
+        <v>14.8451099395752</v>
       </c>
       <c r="H749" t="n">
         <v>6063</v>
@@ -22235,7 +22235,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>15.2306976318359</v>
+        <v>15.2306985855103</v>
       </c>
       <c r="H754" t="n">
         <v>7693</v>
@@ -22351,7 +22351,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G758" t="n">
-        <v>15.8572778701782</v>
+        <v>15.8572788238525</v>
       </c>
       <c r="H758" t="n">
         <v>5944</v>
@@ -22380,7 +22380,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>15.7126836776733</v>
+        <v>15.7126798629761</v>
       </c>
       <c r="H759" t="n">
         <v>3425</v>
@@ -22496,7 +22496,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>15.519889831543</v>
+        <v>15.5198888778687</v>
       </c>
       <c r="H763" t="n">
         <v>4072</v>
@@ -22554,7 +22554,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>15.8090810775757</v>
+        <v>15.8090791702271</v>
       </c>
       <c r="H765" t="n">
         <v>2799</v>
@@ -22612,7 +22612,7 @@
         <v>16</v>
       </c>
       <c r="G767" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H767" t="n">
         <v>7691</v>
@@ -22641,7 +22641,7 @@
         <v>16</v>
       </c>
       <c r="G768" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H768" t="n">
         <v>2528</v>
@@ -22728,7 +22728,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G771" t="n">
-        <v>17.0622367858887</v>
+        <v>17.0622386932373</v>
       </c>
       <c r="H771" t="n">
         <v>21378</v>
@@ -22757,7 +22757,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>17.447826385498</v>
+        <v>17.4478244781494</v>
       </c>
       <c r="H772" t="n">
         <v>13430</v>
@@ -22786,7 +22786,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G773" t="n">
-        <v>17.447826385498</v>
+        <v>17.4478244781494</v>
       </c>
       <c r="H773" t="n">
         <v>11725</v>
@@ -22844,7 +22844,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H775" t="n">
         <v>12401</v>
@@ -22931,7 +22931,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G778" t="n">
-        <v>16.8212471008301</v>
+        <v>16.8212451934814</v>
       </c>
       <c r="H778" t="n">
         <v>8752</v>
@@ -22989,7 +22989,7 @@
         <v>17.5</v>
       </c>
       <c r="G780" t="n">
-        <v>16.869441986084</v>
+        <v>16.8694458007812</v>
       </c>
       <c r="H780" t="n">
         <v>7917</v>
@@ -23105,7 +23105,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>16.5320568084717</v>
+        <v>16.5320529937744</v>
       </c>
       <c r="H784" t="n">
         <v>2334</v>
@@ -23134,7 +23134,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G785" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838581085205</v>
       </c>
       <c r="H785" t="n">
         <v>3050</v>
@@ -23163,7 +23163,7 @@
         <v>17.5</v>
       </c>
       <c r="G786" t="n">
-        <v>16.869441986084</v>
+        <v>16.8694458007812</v>
       </c>
       <c r="H786" t="n">
         <v>5398</v>
@@ -23279,7 +23279,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H790" t="n">
         <v>7506</v>
@@ -23308,7 +23308,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>17.2068347930908</v>
+        <v>17.2068328857422</v>
       </c>
       <c r="H791" t="n">
         <v>3420</v>
@@ -23337,7 +23337,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G792" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H792" t="n">
         <v>4523</v>
@@ -23395,7 +23395,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H794" t="n">
         <v>2784</v>
@@ -23482,7 +23482,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>17.0622367858887</v>
+        <v>17.0622386932373</v>
       </c>
       <c r="H797" t="n">
         <v>4120</v>
@@ -23511,7 +23511,7 @@
         <v>17.5</v>
       </c>
       <c r="G798" t="n">
-        <v>16.869441986084</v>
+        <v>16.8694458007812</v>
       </c>
       <c r="H798" t="n">
         <v>17956</v>
@@ -23569,7 +23569,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H800" t="n">
         <v>6644</v>
@@ -23598,7 +23598,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>17.6888160705566</v>
+        <v>17.6888179779053</v>
       </c>
       <c r="H801" t="n">
         <v>12968</v>
@@ -23627,7 +23627,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H802" t="n">
         <v>18762</v>
@@ -23685,7 +23685,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>18.7009830474854</v>
+        <v>18.700984954834</v>
       </c>
       <c r="H804" t="n">
         <v>25471</v>
@@ -23714,7 +23714,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>19.231164932251</v>
+        <v>19.2311687469482</v>
       </c>
       <c r="H805" t="n">
         <v>23355</v>
@@ -23830,7 +23830,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>18.5081901550293</v>
+        <v>18.5081920623779</v>
       </c>
       <c r="H809" t="n">
         <v>5340</v>
@@ -23888,7 +23888,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G811" t="n">
-        <v>18.411792755127</v>
+        <v>18.4117965698242</v>
       </c>
       <c r="H811" t="n">
         <v>4783</v>
@@ -23917,7 +23917,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H812" t="n">
         <v>21969</v>
@@ -24033,7 +24033,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>18.1708011627197</v>
+        <v>18.1707992553711</v>
       </c>
       <c r="H816" t="n">
         <v>2568</v>
@@ -24120,7 +24120,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>18.1708011627197</v>
+        <v>18.1707992553711</v>
       </c>
       <c r="H819" t="n">
         <v>5941</v>
@@ -24178,7 +24178,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>17.9780082702637</v>
+        <v>17.978006362915</v>
       </c>
       <c r="H821" t="n">
         <v>10417</v>
@@ -24207,7 +24207,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H822" t="n">
         <v>2366</v>
@@ -24265,7 +24265,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>18.1708011627197</v>
+        <v>18.1707992553711</v>
       </c>
       <c r="H824" t="n">
         <v>10467</v>
@@ -24323,7 +24323,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G826" t="n">
-        <v>17.447826385498</v>
+        <v>17.4478244781494</v>
       </c>
       <c r="H826" t="n">
         <v>34597</v>
@@ -24352,7 +24352,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>17.6888160705566</v>
+        <v>17.6888179779053</v>
       </c>
       <c r="H827" t="n">
         <v>9976</v>
@@ -24381,7 +24381,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>17.7370147705078</v>
+        <v>17.7370128631592</v>
       </c>
       <c r="H828" t="n">
         <v>8555</v>
@@ -24439,7 +24439,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>18.1708011627197</v>
+        <v>18.1707992553711</v>
       </c>
       <c r="H830" t="n">
         <v>1749</v>
@@ -24468,7 +24468,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>17.8816108703613</v>
+        <v>17.8816089630127</v>
       </c>
       <c r="H831" t="n">
         <v>4940</v>
@@ -24497,7 +24497,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>18.1708011627197</v>
+        <v>18.1707992553711</v>
       </c>
       <c r="H832" t="n">
         <v>1475</v>
@@ -24584,7 +24584,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>17.7370147705078</v>
+        <v>17.7370128631592</v>
       </c>
       <c r="H835" t="n">
         <v>13488</v>
@@ -24613,7 +24613,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G836" t="n">
-        <v>17.447826385498</v>
+        <v>17.4478244781494</v>
       </c>
       <c r="H836" t="n">
         <v>3775</v>
@@ -24671,7 +24671,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H838" t="n">
         <v>3812</v>
@@ -24700,7 +24700,7 @@
         <v>18.5</v>
       </c>
       <c r="G839" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334121704102</v>
       </c>
       <c r="H839" t="n">
         <v>1836</v>
@@ -24758,7 +24758,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>17.8816108703613</v>
+        <v>17.8816089630127</v>
       </c>
       <c r="H841" t="n">
         <v>3677</v>
@@ -24787,7 +24787,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G842" t="n">
-        <v>17.7370147705078</v>
+        <v>17.7370128631592</v>
       </c>
       <c r="H842" t="n">
         <v>3407</v>
@@ -24845,7 +24845,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>17.447826385498</v>
+        <v>17.4478244781494</v>
       </c>
       <c r="H844" t="n">
         <v>6486</v>
@@ -24874,7 +24874,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H845" t="n">
         <v>13179</v>
@@ -24932,7 +24932,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G847" t="n">
-        <v>17.7370147705078</v>
+        <v>17.7370128631592</v>
       </c>
       <c r="H847" t="n">
         <v>3888</v>
@@ -24961,7 +24961,7 @@
         <v>18.5</v>
       </c>
       <c r="G848" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334121704102</v>
       </c>
       <c r="H848" t="n">
         <v>5754</v>
@@ -24990,7 +24990,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>17.6888160705566</v>
+        <v>17.6888179779053</v>
       </c>
       <c r="H849" t="n">
         <v>2579</v>
@@ -25019,7 +25019,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>17.4960231781006</v>
+        <v>17.4960250854492</v>
       </c>
       <c r="H850" t="n">
         <v>4446</v>
@@ -25106,7 +25106,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G853" t="n">
-        <v>17.9780082702637</v>
+        <v>17.978006362915</v>
       </c>
       <c r="H853" t="n">
         <v>12579</v>
@@ -25135,7 +25135,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>17.7370147705078</v>
+        <v>17.7370128631592</v>
       </c>
       <c r="H854" t="n">
         <v>3086</v>
@@ -25222,7 +25222,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>17.9298076629639</v>
+        <v>17.9298095703125</v>
       </c>
       <c r="H857" t="n">
         <v>5075</v>
@@ -25251,7 +25251,7 @@
         <v>18.5</v>
       </c>
       <c r="G858" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334121704102</v>
       </c>
       <c r="H858" t="n">
         <v>5325</v>
@@ -25338,7 +25338,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G861" t="n">
-        <v>17.7370147705078</v>
+        <v>17.7370128631592</v>
       </c>
       <c r="H861" t="n">
         <v>13384</v>
@@ -25425,7 +25425,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>17.2068347930908</v>
+        <v>17.2068328857422</v>
       </c>
       <c r="H864" t="n">
         <v>2311</v>
@@ -25454,7 +25454,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H865" t="n">
         <v>3146</v>
@@ -25483,7 +25483,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G866" t="n">
-        <v>17.4960231781006</v>
+        <v>17.4960250854492</v>
       </c>
       <c r="H866" t="n">
         <v>1387</v>
@@ -25570,7 +25570,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>17.9780082702637</v>
+        <v>17.978006362915</v>
       </c>
       <c r="H869" t="n">
         <v>11422</v>
@@ -25599,7 +25599,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H870" t="n">
         <v>13461</v>
@@ -25744,7 +25744,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G875" t="n">
-        <v>18.5081901550293</v>
+        <v>18.5081920623779</v>
       </c>
       <c r="H875" t="n">
         <v>4420</v>
@@ -25773,7 +25773,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>17.9298076629639</v>
+        <v>17.9298095703125</v>
       </c>
       <c r="H876" t="n">
         <v>7398</v>
@@ -25802,7 +25802,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G877" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H877" t="n">
         <v>4339</v>
@@ -25860,7 +25860,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>18.5081901550293</v>
+        <v>18.5081920623779</v>
       </c>
       <c r="H879" t="n">
         <v>4983</v>
@@ -25889,7 +25889,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G880" t="n">
-        <v>19.1347694396973</v>
+        <v>19.1347675323486</v>
       </c>
       <c r="H880" t="n">
         <v>14689</v>
@@ -25918,7 +25918,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>19.1829681396484</v>
+        <v>19.1829662322998</v>
       </c>
       <c r="H881" t="n">
         <v>10787</v>
@@ -26005,7 +26005,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G884" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262050628662</v>
       </c>
       <c r="H884" t="n">
         <v>23659</v>
@@ -26034,7 +26034,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>18.4599933624268</v>
+        <v>18.4599914550781</v>
       </c>
       <c r="H885" t="n">
         <v>4951</v>
@@ -26237,7 +26237,7 @@
         <v>18.5</v>
       </c>
       <c r="G892" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334121704102</v>
       </c>
       <c r="H892" t="n">
         <v>13651</v>
@@ -26266,7 +26266,7 @@
         <v>18.5</v>
       </c>
       <c r="G893" t="n">
-        <v>17.8334140777588</v>
+        <v>17.8334121704102</v>
       </c>
       <c r="H893" t="n">
         <v>4177</v>
@@ -26324,7 +26324,7 @@
         <v>17.25</v>
       </c>
       <c r="G895" t="n">
-        <v>16.6284503936768</v>
+        <v>16.6284523010254</v>
       </c>
       <c r="H895" t="n">
         <v>10256</v>
@@ -26353,7 +26353,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>17.4960231781006</v>
+        <v>17.4960250854492</v>
       </c>
       <c r="H896" t="n">
         <v>3633</v>
@@ -26382,7 +26382,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G897" t="n">
-        <v>17.4960231781006</v>
+        <v>17.4960250854492</v>
       </c>
       <c r="H897" t="n">
         <v>4176</v>
@@ -26411,7 +26411,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032321929932</v>
       </c>
       <c r="H898" t="n">
         <v>2326</v>
@@ -26498,7 +26498,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G901" t="n">
-        <v>17.7370147705078</v>
+        <v>17.7370128631592</v>
       </c>
       <c r="H901" t="n">
         <v>5230</v>
@@ -26527,7 +26527,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>17.8816108703613</v>
+        <v>17.8816089630127</v>
       </c>
       <c r="H902" t="n">
         <v>3011</v>
@@ -26614,7 +26614,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>17.2068347930908</v>
+        <v>17.2068328857422</v>
       </c>
       <c r="H905" t="n">
         <v>950</v>
@@ -26730,7 +26730,7 @@
         <v>17.5</v>
       </c>
       <c r="G909" t="n">
-        <v>16.869441986084</v>
+        <v>16.8694458007812</v>
       </c>
       <c r="H909" t="n">
         <v>20573</v>
@@ -26759,7 +26759,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>17.0622367858887</v>
+        <v>17.0622386932373</v>
       </c>
       <c r="H910" t="n">
         <v>5430</v>
@@ -26788,7 +26788,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>16.8212471008301</v>
+        <v>16.8212451934814</v>
       </c>
       <c r="H911" t="n">
         <v>2833</v>
@@ -26817,7 +26817,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G912" t="n">
-        <v>16.5802555084229</v>
+        <v>16.5802574157715</v>
       </c>
       <c r="H912" t="n">
         <v>4259</v>
@@ -26846,7 +26846,7 @@
         <v>16.5</v>
       </c>
       <c r="G913" t="n">
-        <v>15.9054765701294</v>
+        <v>15.9054756164551</v>
       </c>
       <c r="H913" t="n">
         <v>13709</v>
@@ -26875,7 +26875,7 @@
         <v>16</v>
       </c>
       <c r="G914" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H914" t="n">
         <v>18103</v>
@@ -26933,7 +26933,7 @@
         <v>16</v>
       </c>
       <c r="G916" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H916" t="n">
         <v>2674</v>
@@ -26962,7 +26962,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>14.6523180007935</v>
+        <v>14.6523170471191</v>
       </c>
       <c r="H917" t="n">
         <v>28900</v>
@@ -26991,7 +26991,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>15.3270950317383</v>
+        <v>15.327094078064</v>
       </c>
       <c r="H918" t="n">
         <v>18627</v>
@@ -27020,7 +27020,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>15.3270950317383</v>
+        <v>15.327094078064</v>
       </c>
       <c r="H919" t="n">
         <v>1224</v>
@@ -27107,7 +27107,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>14.2667293548584</v>
+        <v>14.2667303085327</v>
       </c>
       <c r="H922" t="n">
         <v>4153</v>
@@ -27223,7 +27223,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>15.519889831543</v>
+        <v>15.5198888778687</v>
       </c>
       <c r="H926" t="n">
         <v>12774</v>
@@ -27252,7 +27252,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>15.7126836776733</v>
+        <v>15.7126798629761</v>
       </c>
       <c r="H927" t="n">
         <v>5052</v>
@@ -27310,7 +27310,7 @@
         <v>16.5</v>
       </c>
       <c r="G929" t="n">
-        <v>15.9054765701294</v>
+        <v>15.9054756164551</v>
       </c>
       <c r="H929" t="n">
         <v>13874</v>
@@ -27339,7 +27339,7 @@
         <v>16</v>
       </c>
       <c r="G930" t="n">
-        <v>15.4234924316406</v>
+        <v>15.4234914779663</v>
       </c>
       <c r="H930" t="n">
         <v>1513</v>
@@ -27368,7 +27368,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>16.1946678161621</v>
+        <v>16.1946659088135</v>
       </c>
       <c r="H931" t="n">
         <v>10440</v>
@@ -27397,7 +27397,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>15.7126836776733</v>
+        <v>15.7126798629761</v>
       </c>
       <c r="H932" t="n">
         <v>17688</v>
@@ -27455,7 +27455,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G934" t="n">
-        <v>15.2306976318359</v>
+        <v>15.2306985855103</v>
       </c>
       <c r="H934" t="n">
         <v>865</v>
@@ -27513,7 +27513,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>14.8451108932495</v>
+        <v>14.8451099395752</v>
       </c>
       <c r="H936" t="n">
         <v>3565</v>
@@ -27542,7 +27542,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G937" t="n">
-        <v>14.4113245010376</v>
+        <v>14.4113254547119</v>
       </c>
       <c r="H937" t="n">
         <v>8814</v>
@@ -27571,7 +27571,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G938" t="n">
-        <v>14.3631258010864</v>
+        <v>14.3631267547607</v>
       </c>
       <c r="H938" t="n">
         <v>4432</v>
@@ -27600,7 +27600,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>15.3270950317383</v>
+        <v>15.327094078064</v>
       </c>
       <c r="H939" t="n">
         <v>9151</v>
@@ -27745,7 +27745,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G944" t="n">
-        <v>15.2306976318359</v>
+        <v>15.2306985855103</v>
       </c>
       <c r="H944" t="n">
         <v>1583</v>
@@ -27861,7 +27861,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G948" t="n">
-        <v>15.2306976318359</v>
+        <v>15.2306985855103</v>
       </c>
       <c r="H948" t="n">
         <v>1173</v>
@@ -27890,7 +27890,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>14.6523180007935</v>
+        <v>14.6523170471191</v>
       </c>
       <c r="H949" t="n">
         <v>2874</v>
@@ -27919,7 +27919,7 @@
         <v>15</v>
       </c>
       <c r="G950" t="n">
-        <v>14.4595232009888</v>
+        <v>14.4595241546631</v>
       </c>
       <c r="H950" t="n">
         <v>8299</v>
@@ -27977,7 +27977,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G952" t="n">
-        <v>14.6041193008423</v>
+        <v>14.604118347168</v>
       </c>
       <c r="H952" t="n">
         <v>902</v>
@@ -28006,7 +28006,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G953" t="n">
-        <v>14.3631258010864</v>
+        <v>14.3631267547607</v>
       </c>
       <c r="H953" t="n">
         <v>7060</v>
@@ -28035,7 +28035,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G954" t="n">
-        <v>14.3631258010864</v>
+        <v>14.3631267547607</v>
       </c>
       <c r="H954" t="n">
         <v>3921</v>
@@ -28064,7 +28064,7 @@
         <v>15</v>
       </c>
       <c r="G955" t="n">
-        <v>14.4595232009888</v>
+        <v>14.4595241546631</v>
       </c>
       <c r="H955" t="n">
         <v>3589</v>
@@ -28093,7 +28093,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>14.4113245010376</v>
+        <v>14.4113254547119</v>
       </c>
       <c r="H956" t="n">
         <v>257</v>
@@ -28122,7 +28122,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>14.2667293548584</v>
+        <v>14.2667303085327</v>
       </c>
       <c r="H957" t="n">
         <v>1640</v>
@@ -28151,7 +28151,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>14.3631258010864</v>
+        <v>14.3631267547607</v>
       </c>
       <c r="H958" t="n">
         <v>3257</v>
@@ -28180,7 +28180,7 @@
         <v>14.5</v>
       </c>
       <c r="G959" t="n">
-        <v>13.9775390625</v>
+        <v>13.9775400161743</v>
       </c>
       <c r="H959" t="n">
         <v>3572</v>
@@ -28209,7 +28209,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G960" t="n">
-        <v>13.6401510238647</v>
+        <v>13.6401500701904</v>
       </c>
       <c r="H960" t="n">
         <v>1673</v>
@@ -28238,7 +28238,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>13.6883497238159</v>
+        <v>13.6883487701416</v>
       </c>
       <c r="H961" t="n">
         <v>1030</v>
@@ -28267,7 +28267,7 @@
         <v>14.5</v>
       </c>
       <c r="G962" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H962" t="n">
         <v>2889</v>
@@ -28383,7 +28383,7 @@
         <v>14.5</v>
       </c>
       <c r="G966" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H966" t="n">
         <v>868</v>
@@ -28412,7 +28412,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>13.4076128005981</v>
+        <v>13.4076118469238</v>
       </c>
       <c r="H967" t="n">
         <v>1852</v>
@@ -28441,7 +28441,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H968" t="n">
         <v>2720</v>
@@ -28470,7 +28470,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G969" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H969" t="n">
         <v>820</v>
@@ -28499,7 +28499,7 @@
         <v>14</v>
       </c>
       <c r="G970" t="n">
-        <v>13.5528202056885</v>
+        <v>13.5528221130371</v>
       </c>
       <c r="H970" t="n">
         <v>964</v>
@@ -28528,7 +28528,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>14.13365650177</v>
+        <v>14.1336574554443</v>
       </c>
       <c r="H971" t="n">
         <v>14283</v>
@@ -28557,7 +28557,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G972" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H972" t="n">
         <v>4243</v>
@@ -28586,7 +28586,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G973" t="n">
-        <v>14.6176862716675</v>
+        <v>14.6176853179932</v>
       </c>
       <c r="H973" t="n">
         <v>1717</v>
@@ -28673,7 +28673,7 @@
         <v>14.75</v>
       </c>
       <c r="G976" t="n">
-        <v>14.2788639068604</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H976" t="n">
         <v>14175</v>
@@ -28731,7 +28731,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>13.4076128005981</v>
+        <v>13.4076118469238</v>
       </c>
       <c r="H978" t="n">
         <v>2074</v>
@@ -28760,7 +28760,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G979" t="n">
-        <v>13.1171951293945</v>
+        <v>13.1171941757202</v>
       </c>
       <c r="H979" t="n">
         <v>6255</v>
@@ -28818,7 +28818,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G981" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H981" t="n">
         <v>13144</v>
@@ -28847,7 +28847,7 @@
         <v>15.75</v>
       </c>
       <c r="G982" t="n">
-        <v>15.2469234466553</v>
+        <v>15.2469244003296</v>
       </c>
       <c r="H982" t="n">
         <v>13824</v>
@@ -28876,7 +28876,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G983" t="n">
-        <v>15.2953262329102</v>
+        <v>15.2953271865845</v>
       </c>
       <c r="H983" t="n">
         <v>3160</v>
@@ -28905,7 +28905,7 @@
         <v>16</v>
       </c>
       <c r="G984" t="n">
-        <v>15.4889392852783</v>
+        <v>15.488938331604</v>
       </c>
       <c r="H984" t="n">
         <v>55822</v>
@@ -28963,7 +28963,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G986" t="n">
-        <v>15.3921327590942</v>
+        <v>15.3921318054199</v>
       </c>
       <c r="H986" t="n">
         <v>2809</v>
@@ -29137,7 +29137,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G992" t="n">
-        <v>14.0852527618408</v>
+        <v>14.0852537155151</v>
       </c>
       <c r="H992" t="n">
         <v>5402</v>
@@ -29195,7 +29195,7 @@
         <v>14.75</v>
       </c>
       <c r="G994" t="n">
-        <v>14.2788639068604</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H994" t="n">
         <v>2029</v>
@@ -29224,7 +29224,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G995" t="n">
-        <v>13.9884481430054</v>
+        <v>13.9884471893311</v>
       </c>
       <c r="H995" t="n">
         <v>1244</v>
@@ -29282,7 +29282,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G997" t="n">
-        <v>14.0852527618408</v>
+        <v>14.0852537155151</v>
       </c>
       <c r="H997" t="n">
         <v>291</v>
@@ -29311,7 +29311,7 @@
         <v>14.25</v>
       </c>
       <c r="G998" t="n">
-        <v>13.7948360443115</v>
+        <v>13.7948350906372</v>
       </c>
       <c r="H998" t="n">
         <v>6924</v>
@@ -29340,7 +29340,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>13.6496267318726</v>
+        <v>13.6496276855469</v>
       </c>
       <c r="H999" t="n">
         <v>9929</v>
@@ -29369,7 +29369,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.4076128005981</v>
+        <v>13.4076118469238</v>
       </c>
       <c r="H1000" t="n">
         <v>10424</v>
@@ -29398,7 +29398,7 @@
         <v>14</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.5528202056885</v>
+        <v>13.5528221130371</v>
       </c>
       <c r="H1001" t="n">
         <v>4003</v>
@@ -29427,7 +29427,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1002" t="n">
         <v>1279</v>
@@ -29456,7 +29456,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.6980304718018</v>
+        <v>13.6980295181274</v>
       </c>
       <c r="H1003" t="n">
         <v>1271</v>
@@ -29485,7 +29485,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.6980304718018</v>
+        <v>13.6980295181274</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -29514,7 +29514,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1005" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1005" t="n">
         <v>143</v>
@@ -29543,7 +29543,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1006" t="n">
         <v>0</v>
@@ -29572,7 +29572,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>13.6496267318726</v>
+        <v>13.6496276855469</v>
       </c>
       <c r="H1007" t="n">
         <v>5169</v>
@@ -29601,7 +29601,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1008" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H1008" t="n">
         <v>3771</v>
@@ -29630,7 +29630,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1009" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H1009" t="n">
         <v>1127</v>
@@ -29659,7 +29659,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G1010" t="n">
-        <v>13.5044174194336</v>
+        <v>13.5044183731079</v>
       </c>
       <c r="H1010" t="n">
         <v>1586</v>
@@ -29717,7 +29717,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>13.1655988693237</v>
+        <v>13.1655979156494</v>
       </c>
       <c r="H1012" t="n">
         <v>3407</v>
@@ -29746,7 +29746,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1013" t="n">
-        <v>13.4076128005981</v>
+        <v>13.4076118469238</v>
       </c>
       <c r="H1013" t="n">
         <v>2388</v>
@@ -29775,7 +29775,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>13.1655988693237</v>
+        <v>13.1655979156494</v>
       </c>
       <c r="H1014" t="n">
         <v>1001</v>
@@ -29920,7 +29920,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1019" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1019" t="n">
         <v>6588</v>
@@ -29949,7 +29949,7 @@
         <v>12.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.100733757019</v>
+        <v>12.1007318496704</v>
       </c>
       <c r="H1020" t="n">
         <v>1200</v>
@@ -29978,7 +29978,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1021" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1021" t="n">
         <v>932</v>
@@ -30094,7 +30094,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1025" t="n">
         <v>427</v>
@@ -30123,7 +30123,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.7783727645874</v>
+        <v>12.7783737182617</v>
       </c>
       <c r="H1026" t="n">
         <v>3409</v>
@@ -30181,7 +30181,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1028" t="n">
-        <v>13.4560146331787</v>
+        <v>13.456015586853</v>
       </c>
       <c r="H1028" t="n">
         <v>3899</v>
@@ -30239,7 +30239,7 @@
         <v>14.5</v>
       </c>
       <c r="G1030" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1030" t="n">
         <v>2981</v>
@@ -30268,7 +30268,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>14.3272676467896</v>
+        <v>14.3272686004639</v>
       </c>
       <c r="H1031" t="n">
         <v>1331</v>
@@ -30297,7 +30297,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1032" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H1032" t="n">
         <v>1379</v>
@@ -30326,7 +30326,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>14.7144918441772</v>
+        <v>14.7144908905029</v>
       </c>
       <c r="H1033" t="n">
         <v>1269</v>
@@ -30384,7 +30384,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H1035" t="n">
         <v>1610</v>
@@ -30471,7 +30471,7 @@
         <v>14.75</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.2788639068604</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H1038" t="n">
         <v>159</v>
@@ -30500,7 +30500,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H1039" t="n">
         <v>2364</v>
@@ -30529,7 +30529,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1040" t="n">
-        <v>14.6176862716675</v>
+        <v>14.6176853179932</v>
       </c>
       <c r="H1040" t="n">
         <v>904</v>
@@ -30616,7 +30616,7 @@
         <v>14.75</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.2788639068604</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H1043" t="n">
         <v>2123</v>
@@ -30645,7 +30645,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.13365650177</v>
+        <v>14.1336574554443</v>
       </c>
       <c r="H1044" t="n">
         <v>2945</v>
@@ -30674,7 +30674,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1045" t="n">
-        <v>13.8916425704956</v>
+        <v>13.8916416168213</v>
       </c>
       <c r="H1045" t="n">
         <v>605</v>
@@ -30703,7 +30703,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.13365650177</v>
+        <v>14.1336574554443</v>
       </c>
       <c r="H1046" t="n">
         <v>124</v>
@@ -30761,7 +30761,7 @@
         <v>14.5</v>
       </c>
       <c r="G1048" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1048" t="n">
         <v>5163</v>
@@ -30790,7 +30790,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1049" t="n">
-        <v>14.13365650177</v>
+        <v>14.1336574554443</v>
       </c>
       <c r="H1049" t="n">
         <v>93</v>
@@ -30819,7 +30819,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1050" t="n">
-        <v>14.0852527618408</v>
+        <v>14.0852537155151</v>
       </c>
       <c r="H1050" t="n">
         <v>2468</v>
@@ -30848,7 +30848,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1051" t="n">
-        <v>14.13365650177</v>
+        <v>14.1336574554443</v>
       </c>
       <c r="H1051" t="n">
         <v>322</v>
@@ -30906,7 +30906,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1053" t="n">
-        <v>13.6496267318726</v>
+        <v>13.6496276855469</v>
       </c>
       <c r="H1053" t="n">
         <v>720</v>
@@ -30935,7 +30935,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1054" t="n">
-        <v>13.6496267318726</v>
+        <v>13.6496276855469</v>
       </c>
       <c r="H1054" t="n">
         <v>525</v>
@@ -30964,7 +30964,7 @@
         <v>14.25</v>
       </c>
       <c r="G1055" t="n">
-        <v>13.7948360443115</v>
+        <v>13.7948350906372</v>
       </c>
       <c r="H1055" t="n">
         <v>4231</v>
@@ -31022,7 +31022,7 @@
         <v>14.25</v>
       </c>
       <c r="G1057" t="n">
-        <v>13.7948360443115</v>
+        <v>13.7948350906372</v>
       </c>
       <c r="H1057" t="n">
         <v>1684</v>
@@ -31399,7 +31399,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1070" t="n">
-        <v>11.7135105133057</v>
+        <v>11.7135095596313</v>
       </c>
       <c r="H1070" t="n">
         <v>3678</v>
@@ -31428,7 +31428,7 @@
         <v>12.25</v>
       </c>
       <c r="G1071" t="n">
-        <v>11.858717918396</v>
+        <v>11.8587188720703</v>
       </c>
       <c r="H1071" t="n">
         <v>1155</v>
@@ -31457,7 +31457,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1072" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1072" t="n">
         <v>2681</v>
@@ -31486,7 +31486,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1073" t="n">
-        <v>12.1975402832031</v>
+        <v>12.1975393295288</v>
       </c>
       <c r="H1073" t="n">
         <v>12188</v>
@@ -31515,7 +31515,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1074" t="n">
-        <v>12.3911504745483</v>
+        <v>12.3911514282227</v>
       </c>
       <c r="H1074" t="n">
         <v>1447</v>
@@ -31631,7 +31631,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1078" t="n">
-        <v>12.536358833313</v>
+        <v>12.5363607406616</v>
       </c>
       <c r="H1078" t="n">
         <v>284</v>
@@ -31718,7 +31718,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1081" t="n">
-        <v>12.7299709320068</v>
+        <v>12.7299718856812</v>
       </c>
       <c r="H1081" t="n">
         <v>2529</v>
@@ -31747,7 +31747,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1082" t="n">
-        <v>12.7299709320068</v>
+        <v>12.7299718856812</v>
       </c>
       <c r="H1082" t="n">
         <v>959</v>
@@ -31805,7 +31805,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>12.7783727645874</v>
+        <v>12.7783737182617</v>
       </c>
       <c r="H1084" t="n">
         <v>809</v>
@@ -31979,7 +31979,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1090" t="n">
-        <v>12.7783727645874</v>
+        <v>12.7783737182617</v>
       </c>
       <c r="H1090" t="n">
         <v>306</v>
@@ -32066,7 +32066,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>12.536358833313</v>
+        <v>12.5363607406616</v>
       </c>
       <c r="H1093" t="n">
         <v>4420</v>
@@ -32095,7 +32095,7 @@
         <v>12.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1094" t="n">
         <v>4305</v>
@@ -32124,7 +32124,7 @@
         <v>12.75</v>
       </c>
       <c r="G1095" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1095" t="n">
         <v>2455</v>
@@ -32153,7 +32153,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1096" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1096" t="n">
         <v>5161</v>
@@ -32182,7 +32182,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1097" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1097" t="n">
         <v>7158</v>
@@ -32211,7 +32211,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1098" t="n">
-        <v>12.3911504745483</v>
+        <v>12.3911514282227</v>
       </c>
       <c r="H1098" t="n">
         <v>9408</v>
@@ -32269,7 +32269,7 @@
         <v>12.75</v>
       </c>
       <c r="G1100" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1100" t="n">
         <v>7191</v>
@@ -32298,7 +32298,7 @@
         <v>12.75</v>
       </c>
       <c r="G1101" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1101" t="n">
         <v>5464</v>
@@ -32327,7 +32327,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1102" t="n">
-        <v>12.536358833313</v>
+        <v>12.5363607406616</v>
       </c>
       <c r="H1102" t="n">
         <v>6218</v>
@@ -32356,7 +32356,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1103" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1103" t="n">
         <v>4495</v>
@@ -32385,7 +32385,7 @@
         <v>12.75</v>
       </c>
       <c r="G1104" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1104" t="n">
         <v>1561</v>
@@ -32443,7 +32443,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1106" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1106" t="n">
         <v>3194</v>
@@ -32472,7 +32472,7 @@
         <v>12.75</v>
       </c>
       <c r="G1107" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1107" t="n">
         <v>3881</v>
@@ -32501,7 +32501,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1108" t="n">
-        <v>12.3911504745483</v>
+        <v>12.3911514282227</v>
       </c>
       <c r="H1108" t="n">
         <v>8024</v>
@@ -32617,7 +32617,7 @@
         <v>12.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1112" t="n">
         <v>1131</v>
@@ -32646,7 +32646,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1113" t="n">
-        <v>12.3911504745483</v>
+        <v>12.3911514282227</v>
       </c>
       <c r="H1113" t="n">
         <v>2058</v>
@@ -32675,7 +32675,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1114" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1114" t="n">
         <v>1583</v>
@@ -32704,7 +32704,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>12.3911504745483</v>
+        <v>12.3911514282227</v>
       </c>
       <c r="H1115" t="n">
         <v>865</v>
@@ -32733,7 +32733,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1116" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1116" t="n">
         <v>1113</v>
@@ -32762,7 +32762,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1117" t="n">
-        <v>12.3911504745483</v>
+        <v>12.3911514282227</v>
       </c>
       <c r="H1117" t="n">
         <v>10356</v>
@@ -32791,7 +32791,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1118" t="n">
-        <v>12.536358833313</v>
+        <v>12.5363607406616</v>
       </c>
       <c r="H1118" t="n">
         <v>3355</v>
@@ -32820,7 +32820,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>12.536358833313</v>
+        <v>12.5363607406616</v>
       </c>
       <c r="H1119" t="n">
         <v>610</v>
@@ -32849,7 +32849,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1120" t="n">
-        <v>12.7783727645874</v>
+        <v>12.7783737182617</v>
       </c>
       <c r="H1120" t="n">
         <v>3820</v>
@@ -32907,7 +32907,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>12.9719867706299</v>
+        <v>12.9719858169556</v>
       </c>
       <c r="H1122" t="n">
         <v>24918</v>
@@ -32965,7 +32965,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>12.9719867706299</v>
+        <v>12.9719858169556</v>
       </c>
       <c r="H1124" t="n">
         <v>30157</v>
@@ -33052,7 +33052,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1127" t="n">
-        <v>12.9719867706299</v>
+        <v>12.9719858169556</v>
       </c>
       <c r="H1127" t="n">
         <v>32113</v>
@@ -33081,7 +33081,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>13.2140007019043</v>
+        <v>13.21399974823</v>
       </c>
       <c r="H1128" t="n">
         <v>247</v>
@@ -33110,7 +33110,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1129" t="n">
-        <v>13.1655988693237</v>
+        <v>13.1655979156494</v>
       </c>
       <c r="H1129" t="n">
         <v>390</v>
@@ -33139,7 +33139,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1130" t="n">
-        <v>13.1655988693237</v>
+        <v>13.1655979156494</v>
       </c>
       <c r="H1130" t="n">
         <v>1118</v>
@@ -33168,7 +33168,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1131" t="n">
-        <v>13.4560146331787</v>
+        <v>13.456015586853</v>
       </c>
       <c r="H1131" t="n">
         <v>472</v>
@@ -33197,7 +33197,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>13.4560146331787</v>
+        <v>13.456015586853</v>
       </c>
       <c r="H1132" t="n">
         <v>0</v>
@@ -33226,7 +33226,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1133" t="n">
-        <v>13.6496267318726</v>
+        <v>13.6496276855469</v>
       </c>
       <c r="H1133" t="n">
         <v>1050</v>
@@ -33255,7 +33255,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1134" t="n">
-        <v>13.9884481430054</v>
+        <v>13.9884471893311</v>
       </c>
       <c r="H1134" t="n">
         <v>1819</v>
@@ -33342,7 +33342,7 @@
         <v>14</v>
       </c>
       <c r="G1137" t="n">
-        <v>13.5528202056885</v>
+        <v>13.5528221130371</v>
       </c>
       <c r="H1137" t="n">
         <v>8177</v>
@@ -33371,7 +33371,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1138" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1138" t="n">
         <v>5357</v>
@@ -33400,7 +33400,7 @@
         <v>14.25</v>
       </c>
       <c r="G1139" t="n">
-        <v>13.7948360443115</v>
+        <v>13.7948350906372</v>
       </c>
       <c r="H1139" t="n">
         <v>15245</v>
@@ -33458,7 +33458,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1141" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1141" t="n">
         <v>4771</v>
@@ -33487,7 +33487,7 @@
         <v>14.25</v>
       </c>
       <c r="G1142" t="n">
-        <v>13.7948360443115</v>
+        <v>13.7948350906372</v>
       </c>
       <c r="H1142" t="n">
         <v>4226</v>
@@ -33516,7 +33516,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1143" t="n">
-        <v>13.7464332580566</v>
+        <v>13.7464323043823</v>
       </c>
       <c r="H1143" t="n">
         <v>720</v>
@@ -33574,7 +33574,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1145" t="n">
-        <v>14.3272676467896</v>
+        <v>14.3272686004639</v>
       </c>
       <c r="H1145" t="n">
         <v>7054</v>
@@ -33632,7 +33632,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H1147" t="n">
         <v>5496</v>
@@ -33690,7 +33690,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1149" t="n">
-        <v>14.1820583343506</v>
+        <v>14.1820592880249</v>
       </c>
       <c r="H1149" t="n">
         <v>807</v>
@@ -33719,7 +33719,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1150" t="n">
-        <v>14.1820583343506</v>
+        <v>14.1820592880249</v>
       </c>
       <c r="H1150" t="n">
         <v>9057</v>
@@ -33748,7 +33748,7 @@
         <v>14.75</v>
       </c>
       <c r="G1151" t="n">
-        <v>14.2788639068604</v>
+        <v>14.2788648605347</v>
       </c>
       <c r="H1151" t="n">
         <v>692</v>
@@ -33777,7 +33777,7 @@
         <v>14.5</v>
       </c>
       <c r="G1152" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1152" t="n">
         <v>9610</v>
@@ -33806,7 +33806,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1153" t="n">
-        <v>14.13365650177</v>
+        <v>14.1336574554443</v>
       </c>
       <c r="H1153" t="n">
         <v>497</v>
@@ -33864,7 +33864,7 @@
         <v>14.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1155" t="n">
         <v>40</v>
@@ -33893,7 +33893,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1156" t="n">
-        <v>13.9884481430054</v>
+        <v>13.9884471893311</v>
       </c>
       <c r="H1156" t="n">
         <v>1337</v>
@@ -33951,7 +33951,7 @@
         <v>14.5</v>
       </c>
       <c r="G1158" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1158" t="n">
         <v>8289</v>
@@ -33980,7 +33980,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1159" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H1159" t="n">
         <v>5202</v>
@@ -34009,7 +34009,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1160" t="n">
-        <v>14.3272676467896</v>
+        <v>14.3272686004639</v>
       </c>
       <c r="H1160" t="n">
         <v>671</v>
@@ -34038,7 +34038,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1161" t="n">
-        <v>14.1820583343506</v>
+        <v>14.1820592880249</v>
       </c>
       <c r="H1161" t="n">
         <v>1598</v>
@@ -34096,7 +34096,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>14.13365650177</v>
+        <v>14.1336574554443</v>
       </c>
       <c r="H1163" t="n">
         <v>3148</v>
@@ -34154,7 +34154,7 @@
         <v>14.5</v>
       </c>
       <c r="G1165" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1165" t="n">
         <v>3614</v>
@@ -34241,7 +34241,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1168" t="n">
-        <v>13.6496267318726</v>
+        <v>13.6496276855469</v>
       </c>
       <c r="H1168" t="n">
         <v>5180</v>
@@ -34270,7 +34270,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>13.8916425704956</v>
+        <v>13.8916416168213</v>
       </c>
       <c r="H1169" t="n">
         <v>3227</v>
@@ -34299,7 +34299,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>13.8916425704956</v>
+        <v>13.8916416168213</v>
       </c>
       <c r="H1170" t="n">
         <v>1513</v>
@@ -34357,7 +34357,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1172" t="n">
-        <v>13.4560146331787</v>
+        <v>13.456015586853</v>
       </c>
       <c r="H1172" t="n">
         <v>5243</v>
@@ -34386,7 +34386,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>13.4076128005981</v>
+        <v>13.4076118469238</v>
       </c>
       <c r="H1173" t="n">
         <v>3585</v>
@@ -34647,7 +34647,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1182" t="n">
-        <v>12.923583984375</v>
+        <v>12.9235830307007</v>
       </c>
       <c r="H1182" t="n">
         <v>4712</v>
@@ -34705,7 +34705,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>12.9719867706299</v>
+        <v>12.9719858169556</v>
       </c>
       <c r="H1184" t="n">
         <v>1248</v>
@@ -34734,7 +34734,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1185" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1185" t="n">
         <v>4661</v>
@@ -34763,7 +34763,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1186" t="n">
-        <v>12.7783727645874</v>
+        <v>12.7783737182617</v>
       </c>
       <c r="H1186" t="n">
         <v>1146</v>
@@ -34821,7 +34821,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1188" t="n">
         <v>3537</v>
@@ -34879,7 +34879,7 @@
         <v>12.75</v>
       </c>
       <c r="G1190" t="n">
-        <v>12.3427476882935</v>
+        <v>12.3427486419678</v>
       </c>
       <c r="H1190" t="n">
         <v>2870</v>
@@ -34937,7 +34937,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1192" t="n">
-        <v>12.3911504745483</v>
+        <v>12.3911514282227</v>
       </c>
       <c r="H1192" t="n">
         <v>88</v>
@@ -34966,7 +34966,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1193" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1193" t="n">
         <v>2078</v>
@@ -35024,7 +35024,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>12.7783727645874</v>
+        <v>12.7783737182617</v>
       </c>
       <c r="H1195" t="n">
         <v>3177</v>
@@ -35053,7 +35053,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1196" t="n">
-        <v>13.1655988693237</v>
+        <v>13.1655979156494</v>
       </c>
       <c r="H1196" t="n">
         <v>449</v>
@@ -35082,7 +35082,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1197" t="n">
-        <v>12.7783727645874</v>
+        <v>12.7783737182617</v>
       </c>
       <c r="H1197" t="n">
         <v>389</v>
@@ -35111,7 +35111,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1198" t="n">
-        <v>13.1655988693237</v>
+        <v>13.1655979156494</v>
       </c>
       <c r="H1198" t="n">
         <v>781</v>
@@ -35169,7 +35169,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>13.1655988693237</v>
+        <v>13.1655979156494</v>
       </c>
       <c r="H1200" t="n">
         <v>2548</v>
@@ -35198,7 +35198,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.923583984375</v>
+        <v>12.9235830307007</v>
       </c>
       <c r="H1201" t="n">
         <v>2713</v>
@@ -35343,7 +35343,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1206" t="n">
-        <v>12.2943439483643</v>
+        <v>12.2943449020386</v>
       </c>
       <c r="H1206" t="n">
         <v>1631</v>
@@ -35372,7 +35372,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1207" t="n">
-        <v>12.1975402832031</v>
+        <v>12.1975393295288</v>
       </c>
       <c r="H1207" t="n">
         <v>1186</v>
@@ -35488,7 +35488,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1211" t="n">
         <v>361</v>
@@ -35517,7 +35517,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1212" t="n">
         <v>46</v>
@@ -35720,7 +35720,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>12.7299709320068</v>
+        <v>12.7299718856812</v>
       </c>
       <c r="H1219" t="n">
         <v>347</v>
@@ -35778,7 +35778,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1221" t="n">
-        <v>12.3911504745483</v>
+        <v>12.3911514282227</v>
       </c>
       <c r="H1221" t="n">
         <v>5821</v>
@@ -35807,7 +35807,7 @@
         <v>13</v>
       </c>
       <c r="G1222" t="n">
-        <v>12.6539640426636</v>
+        <v>12.6539630889893</v>
       </c>
       <c r="H1222" t="n">
         <v>166</v>
@@ -35836,7 +35836,7 @@
         <v>13</v>
       </c>
       <c r="G1223" t="n">
-        <v>12.6539640426636</v>
+        <v>12.6539630889893</v>
       </c>
       <c r="H1223" t="n">
         <v>1013</v>
@@ -35865,7 +35865,7 @@
         <v>12.75</v>
       </c>
       <c r="G1224" t="n">
-        <v>12.4106178283691</v>
+        <v>12.4106187820435</v>
       </c>
       <c r="H1224" t="n">
         <v>573</v>
@@ -35923,7 +35923,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1226" t="n">
-        <v>12.5566244125366</v>
+        <v>12.5566253662109</v>
       </c>
       <c r="H1226" t="n">
         <v>771</v>
@@ -36010,7 +36010,7 @@
         <v>12.5</v>
       </c>
       <c r="G1229" t="n">
-        <v>12.167272567749</v>
+        <v>12.1672716140747</v>
       </c>
       <c r="H1229" t="n">
         <v>5999</v>
@@ -36126,7 +36126,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1233" t="n">
-        <v>11.8752584457397</v>
+        <v>11.8752574920654</v>
       </c>
       <c r="H1233" t="n">
         <v>575</v>
@@ -36155,7 +36155,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>12.0699348449707</v>
+        <v>12.0699338912964</v>
       </c>
       <c r="H1234" t="n">
         <v>429</v>
@@ -36184,7 +36184,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1235" t="n">
-        <v>11.7779207229614</v>
+        <v>11.7779197692871</v>
       </c>
       <c r="H1235" t="n">
         <v>1218</v>
@@ -36213,7 +36213,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1236" t="n">
-        <v>11.7779207229614</v>
+        <v>11.7779197692871</v>
       </c>
       <c r="H1236" t="n">
         <v>600</v>
@@ -36242,7 +36242,7 @@
         <v>12</v>
       </c>
       <c r="G1237" t="n">
-        <v>11.6805820465088</v>
+        <v>11.6805810928345</v>
       </c>
       <c r="H1237" t="n">
         <v>1200</v>
@@ -36271,7 +36271,7 @@
         <v>12</v>
       </c>
       <c r="G1238" t="n">
-        <v>11.6805820465088</v>
+        <v>11.6805810928345</v>
       </c>
       <c r="H1238" t="n">
         <v>1207</v>
@@ -36329,7 +36329,7 @@
         <v>12</v>
       </c>
       <c r="G1240" t="n">
-        <v>11.6805820465088</v>
+        <v>11.6805810928345</v>
       </c>
       <c r="H1240" t="n">
         <v>69260</v>
@@ -36416,7 +36416,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1243" t="n">
-        <v>11.4859066009521</v>
+        <v>11.4859046936035</v>
       </c>
       <c r="H1243" t="n">
         <v>63750</v>
@@ -36445,7 +36445,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1244" t="n">
-        <v>11.2425594329834</v>
+        <v>11.2425603866577</v>
       </c>
       <c r="H1244" t="n">
         <v>2233</v>
@@ -36474,7 +36474,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1245" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1245" t="n">
         <v>4356</v>
@@ -36503,7 +36503,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1246" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1246" t="n">
         <v>288</v>
@@ -36532,7 +36532,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1247" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1247" t="n">
         <v>2366</v>
@@ -36561,7 +36561,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1248" t="n">
-        <v>11.2425594329834</v>
+        <v>11.2425603866577</v>
       </c>
       <c r="H1248" t="n">
         <v>3045</v>
@@ -36590,7 +36590,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1249" t="n">
         <v>1944</v>
@@ -36619,7 +36619,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1250" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1250" t="n">
         <v>2377</v>
@@ -36648,7 +36648,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1251" t="n">
         <v>613</v>
@@ -36677,7 +36677,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1252" t="n">
         <v>535</v>
@@ -36706,7 +36706,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1253" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1253" t="n">
         <v>5895</v>
@@ -36735,7 +36735,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1254" t="n">
         <v>1702</v>
@@ -36764,7 +36764,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1255" t="n">
         <v>169</v>
@@ -36851,7 +36851,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1258" t="n">
         <v>4413</v>
@@ -36880,7 +36880,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1259" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1259" t="n">
         <v>129</v>
@@ -36938,7 +36938,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1261" t="n">
         <v>562</v>
@@ -37228,7 +37228,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>10.8045377731323</v>
+        <v>10.8045387268066</v>
       </c>
       <c r="H1271" t="n">
         <v>2225</v>
@@ -37286,7 +37286,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1273" t="n">
-        <v>11.0965518951416</v>
+        <v>11.0965528488159</v>
       </c>
       <c r="H1273" t="n">
         <v>659</v>
@@ -37315,7 +37315,7 @@
         <v>11.5</v>
       </c>
       <c r="G1274" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1274" t="n">
         <v>3017</v>
@@ -37344,7 +37344,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1275" t="n">
-        <v>11.0965518951416</v>
+        <v>11.0965528488159</v>
       </c>
       <c r="H1275" t="n">
         <v>753</v>
@@ -37373,7 +37373,7 @@
         <v>11.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1276" t="n">
         <v>4176</v>
@@ -37402,7 +37402,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1277" t="n">
-        <v>11.1452207565308</v>
+        <v>11.1452217102051</v>
       </c>
       <c r="H1277" t="n">
         <v>45</v>
@@ -37431,7 +37431,7 @@
         <v>11.25</v>
       </c>
       <c r="G1278" t="n">
-        <v>10.9505443572998</v>
+        <v>10.9505453109741</v>
       </c>
       <c r="H1278" t="n">
         <v>1619</v>
@@ -37547,7 +37547,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1282" t="n">
-        <v>10.8045377731323</v>
+        <v>10.8045387268066</v>
       </c>
       <c r="H1282" t="n">
         <v>280</v>
@@ -37605,7 +37605,7 @@
         <v>11.25</v>
       </c>
       <c r="G1284" t="n">
-        <v>10.9505443572998</v>
+        <v>10.9505453109741</v>
       </c>
       <c r="H1284" t="n">
         <v>1467</v>
@@ -37634,7 +37634,7 @@
         <v>11.5</v>
       </c>
       <c r="G1285" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1285" t="n">
         <v>625</v>
@@ -37663,7 +37663,7 @@
         <v>11.5</v>
       </c>
       <c r="G1286" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1286" t="n">
         <v>21790</v>
@@ -37692,7 +37692,7 @@
         <v>11.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1287" t="n">
         <v>44</v>
@@ -37721,7 +37721,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>11.0965518951416</v>
+        <v>11.0965528488159</v>
       </c>
       <c r="H1288" t="n">
         <v>290</v>
@@ -37808,7 +37808,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1291" t="n">
-        <v>10.8045377731323</v>
+        <v>10.8045387268066</v>
       </c>
       <c r="H1291" t="n">
         <v>946</v>
@@ -37866,7 +37866,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1293" t="n">
-        <v>11.1452207565308</v>
+        <v>11.1452217102051</v>
       </c>
       <c r="H1293" t="n">
         <v>513</v>
@@ -37895,7 +37895,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1294" t="n">
-        <v>11.339898109436</v>
+        <v>11.3398971557617</v>
       </c>
       <c r="H1294" t="n">
         <v>589</v>
@@ -37953,7 +37953,7 @@
         <v>11.5</v>
       </c>
       <c r="G1296" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1296" t="n">
         <v>9</v>
@@ -37982,7 +37982,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1297" t="n">
-        <v>10.8045377731323</v>
+        <v>10.8045387268066</v>
       </c>
       <c r="H1297" t="n">
         <v>5116</v>
@@ -38098,7 +38098,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>11.0965518951416</v>
+        <v>11.0965528488159</v>
       </c>
       <c r="H1301" t="n">
         <v>1305</v>
@@ -38243,7 +38243,7 @@
         <v>11.25</v>
       </c>
       <c r="G1306" t="n">
-        <v>10.9505443572998</v>
+        <v>10.9505453109741</v>
       </c>
       <c r="H1306" t="n">
         <v>2917</v>
@@ -38301,7 +38301,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>11.0965518951416</v>
+        <v>11.0965528488159</v>
       </c>
       <c r="H1308" t="n">
         <v>688</v>
@@ -38330,7 +38330,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1309" t="n">
-        <v>11.1452207565308</v>
+        <v>11.1452217102051</v>
       </c>
       <c r="H1309" t="n">
         <v>1167</v>
@@ -38359,7 +38359,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1310" t="n">
-        <v>11.1452207565308</v>
+        <v>11.1452217102051</v>
       </c>
       <c r="H1310" t="n">
         <v>2481</v>
@@ -38388,7 +38388,7 @@
         <v>11.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.1938905715942</v>
+        <v>11.1938915252686</v>
       </c>
       <c r="H1311" t="n">
         <v>588</v>
@@ -38417,7 +38417,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.2912302017212</v>
+        <v>11.2912292480469</v>
       </c>
       <c r="H1312" t="n">
         <v>14882</v>
@@ -38504,7 +38504,7 @@
         <v>11.25</v>
       </c>
       <c r="G1315" t="n">
-        <v>10.9505443572998</v>
+        <v>10.9505453109741</v>
       </c>
       <c r="H1315" t="n">
         <v>9088</v>
@@ -38620,7 +38620,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1319" t="n">
-        <v>11.0965518951416</v>
+        <v>11.0965528488159</v>
       </c>
       <c r="H1319" t="n">
         <v>1529</v>
@@ -38649,7 +38649,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1320" t="n">
-        <v>10.5611934661865</v>
+        <v>10.5611925125122</v>
       </c>
       <c r="H1320" t="n">
         <v>3193</v>
@@ -38939,7 +38939,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>9.7824878692627</v>
+        <v>9.78248691558838</v>
       </c>
       <c r="H1330" t="n">
         <v>8085</v>
@@ -38968,7 +38968,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1331" t="n">
-        <v>10.0258331298828</v>
+        <v>10.0258321762085</v>
       </c>
       <c r="H1331" t="n">
         <v>546</v>
@@ -38997,7 +38997,7 @@
         <v>10</v>
       </c>
       <c r="G1332" t="n">
-        <v>9.73381900787354</v>
+        <v>9.73381805419922</v>
       </c>
       <c r="H1332" t="n">
         <v>3047</v>
@@ -39026,7 +39026,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1333" t="n">
-        <v>10.0258331298828</v>
+        <v>10.0258321762085</v>
       </c>
       <c r="H1333" t="n">
         <v>10370</v>
@@ -39084,7 +39084,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1335" t="n">
-        <v>9.7824878692627</v>
+        <v>9.78248691558838</v>
       </c>
       <c r="H1335" t="n">
         <v>1732</v>
@@ -39113,7 +39113,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1336" t="n">
-        <v>10.1718406677246</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1336" t="n">
         <v>174</v>
@@ -39142,7 +39142,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1337" t="n">
-        <v>10.1718406677246</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1337" t="n">
         <v>1784</v>
@@ -39229,7 +39229,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1340" t="n">
-        <v>9.83115673065186</v>
+        <v>9.83115577697754</v>
       </c>
       <c r="H1340" t="n">
         <v>2708</v>
@@ -39258,7 +39258,7 @@
         <v>10</v>
       </c>
       <c r="G1341" t="n">
-        <v>9.73381900787354</v>
+        <v>9.73381805419922</v>
       </c>
       <c r="H1341" t="n">
         <v>2744</v>
@@ -39287,7 +39287,7 @@
         <v>10</v>
       </c>
       <c r="G1342" t="n">
-        <v>9.73381900787354</v>
+        <v>9.73381805419922</v>
       </c>
       <c r="H1342" t="n">
         <v>928</v>
@@ -39316,7 +39316,7 @@
         <v>10</v>
       </c>
       <c r="G1343" t="n">
-        <v>9.73381900787354</v>
+        <v>9.73381805419922</v>
       </c>
       <c r="H1343" t="n">
         <v>4647</v>
@@ -39345,7 +39345,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1344" t="n">
-        <v>9.71435070037842</v>
+        <v>9.7143497467041</v>
       </c>
       <c r="H1344" t="n">
         <v>2342</v>
@@ -39374,7 +39374,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1345" t="n">
-        <v>9.5780782699585</v>
+        <v>9.57807731628418</v>
       </c>
       <c r="H1345" t="n">
         <v>376</v>
@@ -39461,7 +39461,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1348" t="n">
-        <v>9.71435070037842</v>
+        <v>9.7143497467041</v>
       </c>
       <c r="H1348" t="n">
         <v>2959</v>
@@ -39490,7 +39490,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1349" t="n">
-        <v>9.71435070037842</v>
+        <v>9.7143497467041</v>
       </c>
       <c r="H1349" t="n">
         <v>2594</v>
@@ -39519,7 +39519,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1350" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1350" t="n">
         <v>3050</v>
@@ -39548,7 +39548,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1351" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1351" t="n">
         <v>5171</v>
@@ -39664,7 +39664,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1355" t="n">
-        <v>9.5780782699585</v>
+        <v>9.57807731628418</v>
       </c>
       <c r="H1355" t="n">
         <v>1043</v>
@@ -39693,7 +39693,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1356" t="n">
-        <v>9.53914260864258</v>
+        <v>9.53914165496826</v>
       </c>
       <c r="H1356" t="n">
         <v>852</v>
@@ -39722,7 +39722,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1357" t="n">
-        <v>9.87982559204102</v>
+        <v>9.8798246383667</v>
       </c>
       <c r="H1357" t="n">
         <v>16434</v>
@@ -39780,7 +39780,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1359" t="n">
-        <v>9.53914260864258</v>
+        <v>9.53914165496826</v>
       </c>
       <c r="H1359" t="n">
         <v>6586</v>
@@ -39809,7 +39809,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1360" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1360" t="n">
         <v>9524</v>
@@ -39838,7 +39838,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1361" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1361" t="n">
         <v>604</v>
@@ -39925,7 +39925,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1364" t="n">
-        <v>9.44180297851562</v>
+        <v>9.44180393218994</v>
       </c>
       <c r="H1364" t="n">
         <v>426</v>
@@ -40012,7 +40012,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1367" t="n">
-        <v>9.32499694824219</v>
+        <v>9.3249979019165</v>
       </c>
       <c r="H1367" t="n">
         <v>1217</v>
@@ -40099,7 +40099,7 @@
         <v>9.5</v>
       </c>
       <c r="G1370" t="n">
-        <v>9.24712657928467</v>
+        <v>9.24712753295898</v>
       </c>
       <c r="H1370" t="n">
         <v>942</v>
@@ -40128,7 +40128,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1371" t="n">
-        <v>9.03298282623291</v>
+        <v>9.03298377990723</v>
       </c>
       <c r="H1371" t="n">
         <v>13499</v>
@@ -40157,7 +40157,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>9.53914260864258</v>
+        <v>9.53914165496826</v>
       </c>
       <c r="H1372" t="n">
         <v>30727</v>
@@ -40186,7 +40186,7 @@
         <v>10</v>
       </c>
       <c r="G1373" t="n">
-        <v>9.73381900787354</v>
+        <v>9.73381805419922</v>
       </c>
       <c r="H1373" t="n">
         <v>10690</v>
@@ -40244,7 +40244,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1375" t="n">
-        <v>10.4151849746704</v>
+        <v>10.4151859283447</v>
       </c>
       <c r="H1375" t="n">
         <v>1865</v>
@@ -40273,7 +40273,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1376" t="n">
-        <v>10.6098613739014</v>
+        <v>10.6098623275757</v>
       </c>
       <c r="H1376" t="n">
         <v>23886</v>
@@ -40331,7 +40331,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1378" t="n">
-        <v>10.6098613739014</v>
+        <v>10.6098623275757</v>
       </c>
       <c r="H1378" t="n">
         <v>4680</v>
@@ -40418,7 +40418,7 @@
         <v>11.25</v>
       </c>
       <c r="G1381" t="n">
-        <v>10.9505443572998</v>
+        <v>10.9505453109741</v>
       </c>
       <c r="H1381" t="n">
         <v>849</v>
@@ -40563,7 +40563,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>10.6098613739014</v>
+        <v>10.6098623275757</v>
       </c>
       <c r="H1386" t="n">
         <v>741</v>
@@ -40679,7 +40679,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1390" t="n">
-        <v>10.3665161132812</v>
+        <v>10.3665151596069</v>
       </c>
       <c r="H1390" t="n">
         <v>3426</v>
@@ -40824,7 +40824,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1395" t="n">
-        <v>10.8045377731323</v>
+        <v>10.8045387268066</v>
       </c>
       <c r="H1395" t="n">
         <v>2651</v>
@@ -40940,7 +40940,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1399" t="n">
-        <v>10.5611934661865</v>
+        <v>10.5611925125122</v>
       </c>
       <c r="H1399" t="n">
         <v>3084</v>
@@ -41027,7 +41027,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1402" t="n">
-        <v>10.5611934661865</v>
+        <v>10.5611925125122</v>
       </c>
       <c r="H1402" t="n">
         <v>2341</v>
@@ -41114,7 +41114,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1405" t="n">
-        <v>10.5611934661865</v>
+        <v>10.5611925125122</v>
       </c>
       <c r="H1405" t="n">
         <v>9659</v>
@@ -41230,7 +41230,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1409" t="n">
-        <v>10.8045377731323</v>
+        <v>10.8045387268066</v>
       </c>
       <c r="H1409" t="n">
         <v>6133</v>
@@ -41433,7 +41433,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>10.3665161132812</v>
+        <v>10.3665151596069</v>
       </c>
       <c r="H1416" t="n">
         <v>1588</v>
@@ -41491,7 +41491,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1418" t="n">
-        <v>10.5611934661865</v>
+        <v>10.5611925125122</v>
       </c>
       <c r="H1418" t="n">
         <v>2341</v>
@@ -41549,7 +41549,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1420" t="n">
-        <v>10.0258331298828</v>
+        <v>10.0258321762085</v>
       </c>
       <c r="H1420" t="n">
         <v>3673</v>
@@ -41607,7 +41607,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1422" t="n">
-        <v>10.3665161132812</v>
+        <v>10.3665151596069</v>
       </c>
       <c r="H1422" t="n">
         <v>1545</v>
@@ -41665,7 +41665,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1424" t="n">
-        <v>10.3665161132812</v>
+        <v>10.3665151596069</v>
       </c>
       <c r="H1424" t="n">
         <v>117</v>
@@ -41723,7 +41723,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1426" t="n">
-        <v>9.7824878692627</v>
+        <v>9.78248691558838</v>
       </c>
       <c r="H1426" t="n">
         <v>5097</v>
@@ -41752,7 +41752,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1427" t="n">
-        <v>9.83115673065186</v>
+        <v>9.83115577697754</v>
       </c>
       <c r="H1427" t="n">
         <v>1270</v>
@@ -41781,7 +41781,7 @@
         <v>10.25</v>
       </c>
       <c r="G1428" t="n">
-        <v>9.97716426849365</v>
+        <v>9.97716331481934</v>
       </c>
       <c r="H1428" t="n">
         <v>1017</v>
@@ -41810,7 +41810,7 @@
         <v>10.25</v>
       </c>
       <c r="G1429" t="n">
-        <v>9.97716426849365</v>
+        <v>9.97716331481934</v>
       </c>
       <c r="H1429" t="n">
         <v>483</v>
@@ -41839,7 +41839,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1430" t="n">
-        <v>9.83115673065186</v>
+        <v>9.83115577697754</v>
       </c>
       <c r="H1430" t="n">
         <v>262</v>
@@ -41868,7 +41868,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1431" t="n">
-        <v>10.0258331298828</v>
+        <v>10.0258321762085</v>
       </c>
       <c r="H1431" t="n">
         <v>8388</v>
@@ -41897,7 +41897,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1432" t="n">
-        <v>10.1718406677246</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1432" t="n">
         <v>1224</v>
@@ -41926,7 +41926,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1433" t="n">
-        <v>10.1718406677246</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1433" t="n">
         <v>900</v>
@@ -41955,7 +41955,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>9.83115673065186</v>
+        <v>9.83115577697754</v>
       </c>
       <c r="H1434" t="n">
         <v>6081</v>
@@ -41984,7 +41984,7 @@
         <v>10.25</v>
       </c>
       <c r="G1435" t="n">
-        <v>9.97716426849365</v>
+        <v>9.97716331481934</v>
       </c>
       <c r="H1435" t="n">
         <v>1234</v>
@@ -42013,7 +42013,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1436" t="n">
-        <v>9.63647937774658</v>
+        <v>9.6364803314209</v>
       </c>
       <c r="H1436" t="n">
         <v>3844</v>
@@ -42042,7 +42042,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1437" t="n">
-        <v>9.63647937774658</v>
+        <v>9.6364803314209</v>
       </c>
       <c r="H1437" t="n">
         <v>6673</v>
@@ -42071,7 +42071,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1438" t="n">
-        <v>9.36393260955811</v>
+        <v>9.36393356323242</v>
       </c>
       <c r="H1438" t="n">
         <v>6276</v>
@@ -42100,7 +42100,7 @@
         <v>9.5</v>
       </c>
       <c r="G1439" t="n">
-        <v>9.24712657928467</v>
+        <v>9.24712753295898</v>
       </c>
       <c r="H1439" t="n">
         <v>2619</v>
@@ -42129,7 +42129,7 @@
         <v>9.5</v>
       </c>
       <c r="G1440" t="n">
-        <v>9.24712657928467</v>
+        <v>9.24712753295898</v>
       </c>
       <c r="H1440" t="n">
         <v>389</v>
@@ -42158,7 +42158,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1441" t="n">
-        <v>9.30552959442139</v>
+        <v>9.3055305480957</v>
       </c>
       <c r="H1441" t="n">
         <v>1731</v>
@@ -42216,7 +42216,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1443" t="n">
-        <v>9.71435070037842</v>
+        <v>9.7143497467041</v>
       </c>
       <c r="H1443" t="n">
         <v>6140</v>
@@ -42245,7 +42245,7 @@
         <v>10</v>
       </c>
       <c r="G1444" t="n">
-        <v>9.73381900787354</v>
+        <v>9.73381805419922</v>
       </c>
       <c r="H1444" t="n">
         <v>3684</v>
@@ -42274,7 +42274,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1445" t="n">
-        <v>9.83115673065186</v>
+        <v>9.83115577697754</v>
       </c>
       <c r="H1445" t="n">
         <v>21848</v>
@@ -42303,7 +42303,7 @@
         <v>10</v>
       </c>
       <c r="G1446" t="n">
-        <v>9.73381900787354</v>
+        <v>9.73381805419922</v>
       </c>
       <c r="H1446" t="n">
         <v>10320</v>
@@ -42390,7 +42390,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1449" t="n">
-        <v>10.0258331298828</v>
+        <v>10.0258321762085</v>
       </c>
       <c r="H1449" t="n">
         <v>1767</v>
@@ -42419,7 +42419,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1450" t="n">
-        <v>10.0258331298828</v>
+        <v>10.0258321762085</v>
       </c>
       <c r="H1450" t="n">
         <v>2538</v>
@@ -42448,7 +42448,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1451" t="n">
-        <v>10.1718406677246</v>
+        <v>10.171838760376</v>
       </c>
       <c r="H1451" t="n">
         <v>2025</v>
@@ -42535,7 +42535,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1454" t="n">
-        <v>10.0258331298828</v>
+        <v>10.0258321762085</v>
       </c>
       <c r="H1454" t="n">
         <v>392</v>
@@ -42564,7 +42564,7 @@
         <v>10</v>
       </c>
       <c r="G1455" t="n">
-        <v>9.73381900787354</v>
+        <v>9.73381805419922</v>
       </c>
       <c r="H1455" t="n">
         <v>5681</v>
@@ -42593,7 +42593,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1456" t="n">
-        <v>9.5780782699585</v>
+        <v>9.57807731628418</v>
       </c>
       <c r="H1456" t="n">
         <v>2192</v>
@@ -42709,7 +42709,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1460" t="n">
-        <v>9.63647937774658</v>
+        <v>9.6364803314209</v>
       </c>
       <c r="H1460" t="n">
         <v>6323</v>
@@ -42796,7 +42796,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1463" t="n">
-        <v>9.53914260864258</v>
+        <v>9.53914165496826</v>
       </c>
       <c r="H1463" t="n">
         <v>15014</v>
@@ -43028,7 +43028,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1471" t="n">
-        <v>9.32499694824219</v>
+        <v>9.3249979019165</v>
       </c>
       <c r="H1471" t="n">
         <v>2430</v>
@@ -43144,7 +43144,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1475" t="n">
-        <v>9.48539352416992</v>
+        <v>9.48539447784424</v>
       </c>
       <c r="H1475" t="n">
         <v>2617</v>
@@ -43173,7 +43173,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1476" t="n">
-        <v>9.6034688949585</v>
+        <v>9.60346984863281</v>
       </c>
       <c r="H1476" t="n">
         <v>1845</v>
@@ -43376,7 +43376,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1483" t="n">
-        <v>9.70186614990234</v>
+        <v>9.70186519622803</v>
       </c>
       <c r="H1483" t="n">
         <v>5070</v>
@@ -43492,7 +43492,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1487" t="n">
-        <v>9.70186614990234</v>
+        <v>9.70186519622803</v>
       </c>
       <c r="H1487" t="n">
         <v>2088</v>
@@ -43550,7 +43550,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1489" t="n">
-        <v>9.70186614990234</v>
+        <v>9.70186519622803</v>
       </c>
       <c r="H1489" t="n">
         <v>2036</v>
@@ -43579,7 +43579,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1490" t="n">
-        <v>9.72154521942139</v>
+        <v>9.72154426574707</v>
       </c>
       <c r="H1490" t="n">
         <v>1424</v>
@@ -43608,7 +43608,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>9.76090431213379</v>
+        <v>9.76090335845947</v>
       </c>
       <c r="H1491" t="n">
         <v>934</v>
@@ -43782,7 +43782,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1497" t="n">
-        <v>9.64282894134521</v>
+        <v>9.6428279876709</v>
       </c>
       <c r="H1497" t="n">
         <v>3285</v>
@@ -43811,7 +43811,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1498" t="n">
-        <v>9.70186614990234</v>
+        <v>9.70186519622803</v>
       </c>
       <c r="H1498" t="n">
         <v>5790</v>
@@ -43840,7 +43840,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1499" t="n">
-        <v>9.70186614990234</v>
+        <v>9.70186519622803</v>
       </c>
       <c r="H1499" t="n">
         <v>602</v>
@@ -43869,7 +43869,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1500" t="n">
-        <v>9.72154521942139</v>
+        <v>9.72154426574707</v>
       </c>
       <c r="H1500" t="n">
         <v>357</v>
@@ -43898,7 +43898,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1501" t="n">
-        <v>9.64282894134521</v>
+        <v>9.6428279876709</v>
       </c>
       <c r="H1501" t="n">
         <v>2832</v>
@@ -43985,7 +43985,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1504" t="n">
-        <v>9.56411075592041</v>
+        <v>9.56411170959473</v>
       </c>
       <c r="H1504" t="n">
         <v>3685</v>
@@ -44014,7 +44014,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1505" t="n">
-        <v>9.66250705718994</v>
+        <v>9.66250610351562</v>
       </c>
       <c r="H1505" t="n">
         <v>1013</v>
@@ -44043,7 +44043,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1506" t="n">
-        <v>9.54443073272705</v>
+        <v>9.54443168640137</v>
       </c>
       <c r="H1506" t="n">
         <v>1877</v>
@@ -44072,7 +44072,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1507" t="n">
-        <v>9.66250705718994</v>
+        <v>9.66250610351562</v>
       </c>
       <c r="H1507" t="n">
         <v>50791</v>
@@ -44304,7 +44304,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1515" t="n">
-        <v>9.72154521942139</v>
+        <v>9.72154426574707</v>
       </c>
       <c r="H1515" t="n">
         <v>10583</v>
@@ -44623,7 +44623,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>10.036413192749</v>
+        <v>10.0364122390747</v>
       </c>
       <c r="H1526" t="n">
         <v>2144</v>
@@ -44681,7 +44681,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1528" t="n">
-        <v>10.036413192749</v>
+        <v>10.0364122390747</v>
       </c>
       <c r="H1528" t="n">
         <v>3063</v>
@@ -44768,7 +44768,7 @@
         <v>10.25</v>
       </c>
       <c r="G1531" t="n">
-        <v>10.0856113433838</v>
+        <v>10.0856103897095</v>
       </c>
       <c r="H1531" t="n">
         <v>636</v>
@@ -45058,7 +45058,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1541" t="n">
-        <v>9.76090431213379</v>
+        <v>9.76090335845947</v>
       </c>
       <c r="H1541" t="n">
         <v>227</v>
@@ -45174,7 +45174,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1545" t="n">
-        <v>9.76090431213379</v>
+        <v>9.76090335845947</v>
       </c>
       <c r="H1545" t="n">
         <v>232</v>
@@ -45203,7 +45203,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1546" t="n">
-        <v>9.64282894134521</v>
+        <v>9.6428279876709</v>
       </c>
       <c r="H1546" t="n">
         <v>2868</v>
@@ -45232,7 +45232,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1547" t="n">
-        <v>9.76090431213379</v>
+        <v>9.76090335845947</v>
       </c>
       <c r="H1547" t="n">
         <v>400</v>
@@ -45464,7 +45464,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1555" t="n">
-        <v>9.76090431213379</v>
+        <v>9.76090335845947</v>
       </c>
       <c r="H1555" t="n">
         <v>323</v>
@@ -45667,7 +45667,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1562" t="n">
-        <v>9.64282894134521</v>
+        <v>9.6428279876709</v>
       </c>
       <c r="H1562" t="n">
         <v>1757</v>
@@ -45696,7 +45696,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1563" t="n">
-        <v>9.72154521942139</v>
+        <v>9.72154426574707</v>
       </c>
       <c r="H1563" t="n">
         <v>135</v>
@@ -45928,7 +45928,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1571" t="n">
-        <v>10.4299983978271</v>
+        <v>10.4299974441528</v>
       </c>
       <c r="H1571" t="n">
         <v>2980</v>
@@ -45957,7 +45957,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1572" t="n">
-        <v>10.3807992935181</v>
+        <v>10.3808002471924</v>
       </c>
       <c r="H1572" t="n">
         <v>1240</v>
@@ -46015,7 +46015,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>10.4299983978271</v>
+        <v>10.4299974441528</v>
       </c>
       <c r="H1574" t="n">
         <v>1210</v>
@@ -46044,7 +46044,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1575" t="n">
-        <v>10.4299983978271</v>
+        <v>10.4299974441528</v>
       </c>
       <c r="H1575" t="n">
         <v>4872</v>
@@ -46073,7 +46073,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1576" t="n">
-        <v>11.1187705993652</v>
+        <v>11.1187715530396</v>
       </c>
       <c r="H1576" t="n">
         <v>12413</v>
@@ -46247,7 +46247,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1582" t="n">
-        <v>11.16796875</v>
+        <v>11.1679697036743</v>
       </c>
       <c r="H1582" t="n">
         <v>3025</v>
@@ -46305,7 +46305,7 @@
         <v>11.5</v>
       </c>
       <c r="G1584" t="n">
-        <v>11.3155632019043</v>
+        <v>11.3155641555786</v>
       </c>
       <c r="H1584" t="n">
         <v>11365</v>
@@ -46334,7 +46334,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1585" t="n">
-        <v>11.5123558044434</v>
+        <v>11.512354850769</v>
       </c>
       <c r="H1585" t="n">
         <v>11195</v>
@@ -46508,7 +46508,7 @@
         <v>13</v>
       </c>
       <c r="G1591" t="n">
-        <v>12.7915058135986</v>
+        <v>12.7915067672729</v>
       </c>
       <c r="H1591" t="n">
         <v>14387</v>
@@ -46537,7 +46537,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1592" t="n">
-        <v>12.4963178634644</v>
+        <v>12.49631690979</v>
       </c>
       <c r="H1592" t="n">
         <v>10300</v>
@@ -46595,7 +46595,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1594" t="n">
-        <v>12.8407039642334</v>
+        <v>12.8407049179077</v>
       </c>
       <c r="H1594" t="n">
         <v>7943</v>
@@ -46624,7 +46624,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1595" t="n">
-        <v>12.8407039642334</v>
+        <v>12.8407049179077</v>
       </c>
       <c r="H1595" t="n">
         <v>5751</v>
@@ -46653,7 +46653,7 @@
         <v>13</v>
       </c>
       <c r="G1596" t="n">
-        <v>12.7915058135986</v>
+        <v>12.7915067672729</v>
       </c>
       <c r="H1596" t="n">
         <v>9007</v>
@@ -46972,7 +46972,7 @@
         <v>13</v>
       </c>
       <c r="G1607" t="n">
-        <v>12.7915058135986</v>
+        <v>12.7915067672729</v>
       </c>
       <c r="H1607" t="n">
         <v>45489</v>
@@ -47030,7 +47030,7 @@
         <v>13.5</v>
       </c>
       <c r="G1609" t="n">
-        <v>13.2834882736206</v>
+        <v>13.2834873199463</v>
       </c>
       <c r="H1609" t="n">
         <v>39949</v>
@@ -47088,7 +47088,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1611" t="n">
-        <v>12.8407039642334</v>
+        <v>12.8407049179077</v>
       </c>
       <c r="H1611" t="n">
         <v>13940</v>
@@ -47117,7 +47117,7 @@
         <v>13</v>
       </c>
       <c r="G1612" t="n">
-        <v>12.7915058135986</v>
+        <v>12.7915067672729</v>
       </c>
       <c r="H1612" t="n">
         <v>1327</v>
@@ -47146,7 +47146,7 @@
         <v>13</v>
       </c>
       <c r="G1613" t="n">
-        <v>12.7915058135986</v>
+        <v>12.7915067672729</v>
       </c>
       <c r="H1613" t="n">
         <v>20557</v>
@@ -47175,7 +47175,7 @@
         <v>13</v>
       </c>
       <c r="G1614" t="n">
-        <v>12.7915058135986</v>
+        <v>12.7915067672729</v>
       </c>
       <c r="H1614" t="n">
         <v>15556</v>
@@ -47204,7 +47204,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1615" t="n">
-        <v>12.7423076629639</v>
+        <v>12.7423086166382</v>
       </c>
       <c r="H1615" t="n">
         <v>3096</v>
@@ -47233,7 +47233,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1616" t="n">
-        <v>12.4963178634644</v>
+        <v>12.49631690979</v>
       </c>
       <c r="H1616" t="n">
         <v>3076</v>
@@ -47378,7 +47378,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>11.3647613525391</v>
+        <v>11.3647623062134</v>
       </c>
       <c r="H1621" t="n">
         <v>6291</v>
@@ -47494,7 +47494,7 @@
         <v>12.25</v>
       </c>
       <c r="G1625" t="n">
-        <v>12.0535354614258</v>
+        <v>12.0535345077515</v>
       </c>
       <c r="H1625" t="n">
         <v>4284</v>
@@ -47813,7 +47813,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1636" t="n">
-        <v>11.1187705993652</v>
+        <v>11.1187715530396</v>
       </c>
       <c r="H1636" t="n">
         <v>507</v>
@@ -47871,7 +47871,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1638" t="n">
-        <v>11.1187705993652</v>
+        <v>11.1187715530396</v>
       </c>
       <c r="H1638" t="n">
         <v>4347</v>
@@ -47900,7 +47900,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1639" t="n">
-        <v>10.7743835449219</v>
+        <v>10.7743844985962</v>
       </c>
       <c r="H1639" t="n">
         <v>8536</v>
@@ -48103,7 +48103,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1646" t="n">
-        <v>10.7251853942871</v>
+        <v>10.7251863479614</v>
       </c>
       <c r="H1646" t="n">
         <v>9044</v>
@@ -48132,7 +48132,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1647" t="n">
-        <v>10.4299983978271</v>
+        <v>10.4299974441528</v>
       </c>
       <c r="H1647" t="n">
         <v>3122</v>
@@ -48161,7 +48161,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.4299983978271</v>
+        <v>10.4299974441528</v>
       </c>
       <c r="H1648" t="n">
         <v>5642</v>
@@ -48219,7 +48219,7 @@
         <v>10.5</v>
       </c>
       <c r="G1650" t="n">
-        <v>10.3316011428833</v>
+        <v>10.3316020965576</v>
       </c>
       <c r="H1650" t="n">
         <v>56910</v>
@@ -48248,7 +48248,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1651" t="n">
-        <v>10.4299983978271</v>
+        <v>10.4299974441528</v>
       </c>
       <c r="H1651" t="n">
         <v>2497</v>
@@ -48277,7 +48277,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1652" t="n">
-        <v>10.4299983978271</v>
+        <v>10.4299974441528</v>
       </c>
       <c r="H1652" t="n">
         <v>10295</v>
@@ -48306,7 +48306,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1653" t="n">
-        <v>10.4791955947876</v>
+        <v>10.4791946411133</v>
       </c>
       <c r="H1653" t="n">
         <v>9615</v>
@@ -48364,7 +48364,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1655" t="n">
-        <v>10.4791955947876</v>
+        <v>10.4791946411133</v>
       </c>
       <c r="H1655" t="n">
         <v>1424</v>
@@ -48393,7 +48393,7 @@
         <v>10.5</v>
       </c>
       <c r="G1656" t="n">
-        <v>10.3316011428833</v>
+        <v>10.3316020965576</v>
       </c>
       <c r="H1656" t="n">
         <v>6026</v>
@@ -48451,7 +48451,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1658" t="n">
-        <v>10.4791955947876</v>
+        <v>10.4791946411133</v>
       </c>
       <c r="H1658" t="n">
         <v>5157</v>
@@ -48480,7 +48480,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1659" t="n">
-        <v>10.3807992935181</v>
+        <v>10.3808002471924</v>
       </c>
       <c r="H1659" t="n">
         <v>3675</v>
@@ -48509,7 +48509,7 @@
         <v>10.5</v>
       </c>
       <c r="G1660" t="n">
-        <v>10.3316011428833</v>
+        <v>10.3316020965576</v>
       </c>
       <c r="H1660" t="n">
         <v>2242</v>
@@ -48538,7 +48538,7 @@
         <v>10.5</v>
       </c>
       <c r="G1661" t="n">
-        <v>10.3316011428833</v>
+        <v>10.3316020965576</v>
       </c>
       <c r="H1661" t="n">
         <v>2158</v>
@@ -48567,7 +48567,7 @@
         <v>10.5</v>
       </c>
       <c r="G1662" t="n">
-        <v>10.3316011428833</v>
+        <v>10.3316020965576</v>
       </c>
       <c r="H1662" t="n">
         <v>1216</v>
@@ -48683,7 +48683,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1666" t="n">
-        <v>10.4791955947876</v>
+        <v>10.4791946411133</v>
       </c>
       <c r="H1666" t="n">
         <v>4693</v>
@@ -48741,7 +48741,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1668" t="n">
-        <v>10.4791955947876</v>
+        <v>10.4791946411133</v>
       </c>
       <c r="H1668" t="n">
         <v>8608</v>
@@ -48828,7 +48828,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1671" t="n">
-        <v>10.4299983978271</v>
+        <v>10.4299974441528</v>
       </c>
       <c r="H1671" t="n">
         <v>3688</v>
@@ -48915,7 +48915,7 @@
         <v>10.5</v>
       </c>
       <c r="G1674" t="n">
-        <v>10.3316011428833</v>
+        <v>10.3316020965576</v>
       </c>
       <c r="H1674" t="n">
         <v>1380</v>
@@ -48973,7 +48973,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1676" t="n">
-        <v>10.4299983978271</v>
+        <v>10.4299974441528</v>
       </c>
       <c r="H1676" t="n">
         <v>6725</v>
@@ -49060,7 +49060,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1679" t="n">
-        <v>10.3807992935181</v>
+        <v>10.3808002471924</v>
       </c>
       <c r="H1679" t="n">
         <v>3353</v>
@@ -49321,7 +49321,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1688" t="n">
-        <v>10.4791955947876</v>
+        <v>10.4791946411133</v>
       </c>
       <c r="H1688" t="n">
         <v>2743</v>
@@ -49408,7 +49408,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1691" t="n">
-        <v>10.7251853942871</v>
+        <v>10.7251863479614</v>
       </c>
       <c r="H1691" t="n">
         <v>1253</v>
@@ -49611,7 +49611,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1698" t="n">
-        <v>10.7251853942871</v>
+        <v>10.7251863479614</v>
       </c>
       <c r="H1698" t="n">
         <v>206</v>
@@ -49814,7 +49814,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1705" t="n">
-        <v>10.4791955947876</v>
+        <v>10.4791946411133</v>
       </c>
       <c r="H1705" t="n">
         <v>2007</v>
@@ -49843,7 +49843,7 @@
         <v>10.5</v>
       </c>
       <c r="G1706" t="n">
-        <v>10.3316011428833</v>
+        <v>10.3316020965576</v>
       </c>
       <c r="H1706" t="n">
         <v>2121</v>
@@ -49872,7 +49872,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1707" t="n">
-        <v>10.3807992935181</v>
+        <v>10.3808002471924</v>
       </c>
       <c r="H1707" t="n">
         <v>2077</v>
@@ -49930,7 +49930,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1709" t="n">
-        <v>10.036413192749</v>
+        <v>10.0364122390747</v>
       </c>
       <c r="H1709" t="n">
         <v>1483</v>
@@ -50017,7 +50017,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1712" t="n">
-        <v>10.036413192749</v>
+        <v>10.0364122390747</v>
       </c>
       <c r="H1712" t="n">
         <v>1833</v>
@@ -50075,7 +50075,7 @@
         <v>10.5</v>
       </c>
       <c r="G1714" t="n">
-        <v>10.3316011428833</v>
+        <v>10.3316020965576</v>
       </c>
       <c r="H1714" t="n">
         <v>56</v>
@@ -50191,7 +50191,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1718" t="n">
-        <v>10.036413192749</v>
+        <v>10.0364122390747</v>
       </c>
       <c r="H1718" t="n">
         <v>3461</v>
@@ -50365,7 +50365,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1724" t="n">
-        <v>9.72154521942139</v>
+        <v>9.72154426574707</v>
       </c>
       <c r="H1724" t="n">
         <v>4639</v>
@@ -50481,7 +50481,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1728" t="n">
-        <v>10.036413192749</v>
+        <v>10.0364122390747</v>
       </c>
       <c r="H1728" t="n">
         <v>6196</v>
@@ -61217,6 +61217,35 @@
         <v>109</v>
       </c>
       <c r="I2098" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2099" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2099" t="n">
+        <v>8.68000030517578</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>8.68000030517578</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>8.68000030517578</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="G2099" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="H2099" t="n">
+        <v>290</v>
+      </c>
+      <c r="I2099" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G2" t="n">
-        <v>2.57321262359619</v>
+        <v>2.57321286201477</v>
       </c>
       <c r="H2" t="n">
         <v>511000</v>
@@ -485,7 +485,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H4" t="n">
         <v>233500</v>
@@ -543,7 +543,7 @@
         <v>2.98749995231628</v>
       </c>
       <c r="G6" t="n">
-        <v>2.84721255302429</v>
+        <v>2.84721207618713</v>
       </c>
       <c r="H6" t="n">
         <v>72500</v>
@@ -572,7 +572,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G7" t="n">
-        <v>2.80670809745789</v>
+        <v>2.80670833587646</v>
       </c>
       <c r="H7" t="n">
         <v>71500</v>
@@ -601,7 +601,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84006452560425</v>
+        <v>2.84006428718567</v>
       </c>
       <c r="H8" t="n">
         <v>25000</v>
@@ -630,7 +630,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H9" t="n">
         <v>26000</v>
@@ -659,7 +659,7 @@
         <v>2.97449994087219</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8348228931427</v>
+        <v>2.83482265472412</v>
       </c>
       <c r="H10" t="n">
         <v>25000</v>
@@ -688,7 +688,7 @@
         <v>2.9614999294281</v>
       </c>
       <c r="G11" t="n">
-        <v>2.82243275642395</v>
+        <v>2.82243323326111</v>
       </c>
       <c r="H11" t="n">
         <v>20000</v>
@@ -717,7 +717,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G12" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H12" t="n">
         <v>7500</v>
@@ -746,7 +746,7 @@
         <v>2.98900008201599</v>
       </c>
       <c r="G13" t="n">
-        <v>2.84864211082458</v>
+        <v>2.84864187240601</v>
       </c>
       <c r="H13" t="n">
         <v>8500</v>
@@ -775,7 +775,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G14" t="n">
-        <v>2.76572704315186</v>
+        <v>2.76572728157043</v>
       </c>
       <c r="H14" t="n">
         <v>5500</v>
@@ -804,7 +804,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H15" t="n">
         <v>22500</v>
@@ -833,7 +833,7 @@
         <v>2.97449994087219</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8348228931427</v>
+        <v>2.83482265472412</v>
       </c>
       <c r="H16" t="n">
         <v>6000</v>
@@ -862,7 +862,7 @@
         <v>2.93099999427795</v>
       </c>
       <c r="G17" t="n">
-        <v>2.79336500167847</v>
+        <v>2.79336524009705</v>
       </c>
       <c r="H17" t="n">
         <v>5000</v>
@@ -1065,7 +1065,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>2.70663833618164</v>
+        <v>2.70663857460022</v>
       </c>
       <c r="H24" t="n">
         <v>9500</v>
@@ -1094,7 +1094,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.70663833618164</v>
+        <v>2.70663857460022</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>2.75</v>
       </c>
       <c r="G30" t="n">
-        <v>2.6208643913269</v>
+        <v>2.62086462974548</v>
       </c>
       <c r="H30" t="n">
         <v>6500</v>
@@ -1268,7 +1268,7 @@
         <v>2.75</v>
       </c>
       <c r="G31" t="n">
-        <v>2.6208643913269</v>
+        <v>2.62086462974548</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>2.75</v>
       </c>
       <c r="G32" t="n">
-        <v>2.6208643913269</v>
+        <v>2.62086462974548</v>
       </c>
       <c r="H32" t="n">
         <v>1500</v>
@@ -1326,7 +1326,7 @@
         <v>2.75</v>
       </c>
       <c r="G33" t="n">
-        <v>2.6208643913269</v>
+        <v>2.62086462974548</v>
       </c>
       <c r="H33" t="n">
         <v>1500</v>
@@ -1355,7 +1355,7 @@
         <v>2.75</v>
       </c>
       <c r="G34" t="n">
-        <v>2.6208643913269</v>
+        <v>2.62086462974548</v>
       </c>
       <c r="H34" t="n">
         <v>3500</v>
@@ -1384,7 +1384,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G35" t="n">
-        <v>2.67232894897461</v>
+        <v>2.67232918739319</v>
       </c>
       <c r="H35" t="n">
         <v>5500</v>
@@ -1471,7 +1471,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G38" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H38" t="n">
         <v>17000</v>
@@ -1500,7 +1500,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H39" t="n">
         <v>21500</v>
@@ -1529,7 +1529,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H40" t="n">
         <v>20000</v>
@@ -1558,7 +1558,7 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H41" t="n">
         <v>18500</v>
@@ -1587,7 +1587,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G42" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H42" t="n">
         <v>5500</v>
@@ -1616,7 +1616,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G43" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H43" t="n">
         <v>1000</v>
@@ -1674,7 +1674,7 @@
         <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H45" t="n">
         <v>18000</v>
@@ -1703,7 +1703,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.95442891120911</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H46" t="n">
         <v>12000</v>
@@ -1732,7 +1732,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87818622589111</v>
+        <v>2.87818598747253</v>
       </c>
       <c r="H47" t="n">
         <v>9000</v>
@@ -1790,7 +1790,7 @@
         <v>3.05550003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>2.91201901435852</v>
+        <v>2.91201877593994</v>
       </c>
       <c r="H49" t="n">
         <v>6500</v>
@@ -1819,7 +1819,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.95442891120911</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H50" t="n">
         <v>13000</v>
@@ -1848,7 +1848,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G51" t="n">
-        <v>2.92583799362183</v>
+        <v>2.92583823204041</v>
       </c>
       <c r="H51" t="n">
         <v>9000</v>
@@ -1906,7 +1906,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.00208139419556</v>
+        <v>3.00208163261414</v>
       </c>
       <c r="H53" t="n">
         <v>58000</v>
@@ -1935,7 +1935,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G54" t="n">
-        <v>2.96395945549011</v>
+        <v>2.96395969390869</v>
       </c>
       <c r="H54" t="n">
         <v>8500</v>
@@ -1964,7 +1964,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>3.00208139419556</v>
+        <v>3.00208163261414</v>
       </c>
       <c r="H55" t="n">
         <v>5500</v>
@@ -1993,7 +1993,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>2.9163076877594</v>
+        <v>2.91630744934082</v>
       </c>
       <c r="H56" t="n">
         <v>16000</v>
@@ -2022,7 +2022,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>2.95442891120911</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H57" t="n">
         <v>2000</v>
@@ -2051,7 +2051,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G58" t="n">
-        <v>2.95442891120911</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H58" t="n">
         <v>9500</v>
@@ -2080,7 +2080,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>2.97349047660828</v>
+        <v>2.9734902381897</v>
       </c>
       <c r="H59" t="n">
         <v>7500</v>
@@ -2109,7 +2109,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G60" t="n">
-        <v>2.97349047660828</v>
+        <v>2.9734902381897</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2138,7 +2138,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>2.95442891120911</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H61" t="n">
         <v>1000</v>
@@ -2167,7 +2167,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>2.95442891120911</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H62" t="n">
         <v>3000</v>
@@ -2196,7 +2196,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G63" t="n">
-        <v>2.88771629333496</v>
+        <v>2.88771677017212</v>
       </c>
       <c r="H63" t="n">
         <v>500</v>
@@ -2225,7 +2225,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>2.95442891120911</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H64" t="n">
         <v>2500</v>
@@ -2254,7 +2254,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>2.87818622589111</v>
+        <v>2.87818598747253</v>
       </c>
       <c r="H65" t="n">
         <v>4000</v>
@@ -2283,7 +2283,7 @@
         <v>2.97300004959106</v>
       </c>
       <c r="G66" t="n">
-        <v>2.83339333534241</v>
+        <v>2.83339285850525</v>
       </c>
       <c r="H66" t="n">
         <v>6000</v>
@@ -2312,7 +2312,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G67" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H67" t="n">
         <v>5000</v>
@@ -2341,7 +2341,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H68" t="n">
         <v>18500</v>
@@ -2370,7 +2370,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G69" t="n">
-        <v>2.84482955932617</v>
+        <v>2.84482979774475</v>
       </c>
       <c r="H69" t="n">
         <v>1500</v>
@@ -2399,7 +2399,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G70" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H70" t="n">
         <v>7500</v>
@@ -2428,7 +2428,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80670809745789</v>
+        <v>2.80670833587646</v>
       </c>
       <c r="H71" t="n">
         <v>8000</v>
@@ -2457,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H72" t="n">
         <v>7500</v>
@@ -2515,7 +2515,7 @@
         <v>3</v>
       </c>
       <c r="G74" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H74" t="n">
         <v>3000</v>
@@ -2544,7 +2544,7 @@
         <v>3</v>
       </c>
       <c r="G75" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H75" t="n">
         <v>3000</v>
@@ -2631,7 +2631,7 @@
         <v>2.89100003242493</v>
       </c>
       <c r="G78" t="n">
-        <v>2.75524377822876</v>
+        <v>2.75524353981018</v>
       </c>
       <c r="H78" t="n">
         <v>23000</v>
@@ -2718,7 +2718,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H81" t="n">
         <v>3000</v>
@@ -2776,7 +2776,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G83" t="n">
-        <v>2.88771629333496</v>
+        <v>2.88771677017212</v>
       </c>
       <c r="H83" t="n">
         <v>28000</v>
@@ -2805,7 +2805,7 @@
         <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H84" t="n">
         <v>12500</v>
@@ -2834,7 +2834,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G85" t="n">
-        <v>2.92202591896057</v>
+        <v>2.92202568054199</v>
       </c>
       <c r="H85" t="n">
         <v>1500</v>
@@ -2863,7 +2863,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>2.9163076877594</v>
+        <v>2.91630744934082</v>
       </c>
       <c r="H86" t="n">
         <v>3000</v>
@@ -2921,7 +2921,7 @@
         <v>3.04900002479553</v>
       </c>
       <c r="G88" t="n">
-        <v>2.9058244228363</v>
+        <v>2.90582466125488</v>
       </c>
       <c r="H88" t="n">
         <v>2500</v>
@@ -2950,7 +2950,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G89" t="n">
-        <v>2.85054779052734</v>
+        <v>2.85054755210876</v>
       </c>
       <c r="H89" t="n">
         <v>3000</v>
@@ -2979,7 +2979,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G90" t="n">
-        <v>2.85054779052734</v>
+        <v>2.85054755210876</v>
       </c>
       <c r="H90" t="n">
         <v>4500</v>
@@ -3008,7 +3008,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G91" t="n">
-        <v>2.85054779052734</v>
+        <v>2.85054755210876</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>2.90899991989136</v>
       </c>
       <c r="G93" t="n">
-        <v>2.77239847183228</v>
+        <v>2.7723982334137</v>
       </c>
       <c r="H93" t="n">
         <v>52000</v>
@@ -3095,7 +3095,7 @@
         <v>2.90899991989136</v>
       </c>
       <c r="G94" t="n">
-        <v>2.77239847183228</v>
+        <v>2.7723982334137</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G95" t="n">
-        <v>2.8257691860199</v>
+        <v>2.82576870918274</v>
       </c>
       <c r="H95" t="n">
         <v>3500</v>
@@ -3530,7 +3530,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G109" t="n">
-        <v>2.72045755386353</v>
+        <v>2.72045803070068</v>
       </c>
       <c r="H109" t="n">
         <v>6500</v>
@@ -3559,7 +3559,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G110" t="n">
-        <v>2.72045755386353</v>
+        <v>2.72045803070068</v>
       </c>
       <c r="H110" t="n">
         <v>12500</v>
@@ -3617,7 +3617,7 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H112" t="n">
         <v>8000</v>
@@ -3704,7 +3704,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G115" t="n">
-        <v>2.95442891120911</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H115" t="n">
         <v>500</v>
@@ -3762,7 +3762,7 @@
         <v>2.92549991607666</v>
       </c>
       <c r="G117" t="n">
-        <v>2.7881236076355</v>
+        <v>2.78812384605408</v>
       </c>
       <c r="H117" t="n">
         <v>9000</v>
@@ -3791,7 +3791,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G118" t="n">
-        <v>2.79622483253479</v>
+        <v>2.79622459411621</v>
       </c>
       <c r="H118" t="n">
         <v>6500</v>
@@ -3820,7 +3820,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G119" t="n">
-        <v>2.85436010360718</v>
+        <v>2.8543598651886</v>
       </c>
       <c r="H119" t="n">
         <v>2500</v>
@@ -3849,7 +3849,7 @@
         <v>3</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H120" t="n">
         <v>2000</v>
@@ -3878,7 +3878,7 @@
         <v>3</v>
       </c>
       <c r="G121" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>2.95149993896484</v>
       </c>
       <c r="G122" t="n">
-        <v>2.81290245056152</v>
+        <v>2.8129026889801</v>
       </c>
       <c r="H122" t="n">
         <v>4500</v>
@@ -3936,7 +3936,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H123" t="n">
         <v>500</v>
@@ -3965,7 +3965,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G126" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H126" t="n">
         <v>1000</v>
@@ -4052,7 +4052,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>2.81147289276123</v>
+        <v>2.81147313117981</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G131" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H131" t="n">
         <v>3500</v>
@@ -4197,7 +4197,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G132" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>2.92249989509583</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78526449203491</v>
+        <v>2.78526425361633</v>
       </c>
       <c r="H133" t="n">
         <v>1500</v>
@@ -4255,7 +4255,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H134" t="n">
         <v>1000</v>
@@ -4284,7 +4284,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H135" t="n">
         <v>500</v>
@@ -4313,7 +4313,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G136" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H136" t="n">
         <v>1000</v>
@@ -4342,7 +4342,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G137" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>2.95700001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.81814455986023</v>
+        <v>2.81814479827881</v>
       </c>
       <c r="H139" t="n">
         <v>4500</v>
@@ -4429,7 +4429,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G140" t="n">
-        <v>2.87818622589111</v>
+        <v>2.87818598747253</v>
       </c>
       <c r="H140" t="n">
         <v>11500</v>
@@ -4458,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="G141" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H141" t="n">
         <v>500</v>
@@ -4487,7 +4487,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G142" t="n">
-        <v>2.88390469551086</v>
+        <v>2.88390445709229</v>
       </c>
       <c r="H142" t="n">
         <v>500</v>
@@ -4516,7 +4516,7 @@
         <v>3</v>
       </c>
       <c r="G143" t="n">
-        <v>2.8591251373291</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H143" t="n">
         <v>13500</v>
@@ -4545,7 +4545,7 @@
         <v>3.02950000762939</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88723993301392</v>
+        <v>2.8872401714325</v>
       </c>
       <c r="H144" t="n">
         <v>43000</v>
@@ -4574,7 +4574,7 @@
         <v>3.00650000572205</v>
       </c>
       <c r="G145" t="n">
-        <v>2.86532020568848</v>
+        <v>2.8653199672699</v>
       </c>
       <c r="H145" t="n">
         <v>7000</v>
@@ -4632,7 +4632,7 @@
         <v>3.00650000572205</v>
       </c>
       <c r="G147" t="n">
-        <v>2.86532020568848</v>
+        <v>2.8653199672699</v>
       </c>
       <c r="H147" t="n">
         <v>8000</v>
@@ -4661,7 +4661,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>2.9163076877594</v>
+        <v>2.91630744934082</v>
       </c>
       <c r="H148" t="n">
         <v>2000</v>
@@ -4690,7 +4690,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>2.9830207824707</v>
+        <v>2.98302102088928</v>
       </c>
       <c r="H149" t="n">
         <v>31500</v>
@@ -4748,7 +4748,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>3.05926418304443</v>
+        <v>3.05926394462585</v>
       </c>
       <c r="H151" t="n">
         <v>12000</v>
@@ -4835,7 +4835,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G154" t="n">
-        <v>3.2498722076416</v>
+        <v>3.24987244606018</v>
       </c>
       <c r="H154" t="n">
         <v>19000</v>
@@ -4864,7 +4864,7 @@
         <v>3.40949988365173</v>
       </c>
       <c r="G155" t="n">
-        <v>3.24939608573914</v>
+        <v>3.24939584732056</v>
       </c>
       <c r="H155" t="n">
         <v>13000</v>
@@ -4922,7 +4922,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G157" t="n">
-        <v>3.18315935134888</v>
+        <v>3.18315958976746</v>
       </c>
       <c r="H157" t="n">
         <v>4000</v>
@@ -4980,7 +4980,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>3.28799390792847</v>
+        <v>3.28799438476562</v>
       </c>
       <c r="H159" t="n">
         <v>11000</v>
@@ -5038,7 +5038,7 @@
         <v>3.43549990653992</v>
       </c>
       <c r="G161" t="n">
-        <v>3.27417492866516</v>
+        <v>3.27417516708374</v>
       </c>
       <c r="H161" t="n">
         <v>11500</v>
@@ -5067,7 +5067,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G162" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175098419189</v>
       </c>
       <c r="H162" t="n">
         <v>6500</v>
@@ -5125,7 +5125,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175098419189</v>
       </c>
       <c r="H164" t="n">
         <v>3500</v>
@@ -5154,7 +5154,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>3.21175074577332</v>
+        <v>3.21175098419189</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>3.26893329620361</v>
+        <v>3.26893353462219</v>
       </c>
       <c r="H167" t="n">
         <v>14500</v>
@@ -5299,7 +5299,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.34517669677734</v>
+        <v>3.34517645835876</v>
       </c>
       <c r="H170" t="n">
         <v>32000</v>
@@ -5357,7 +5357,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G172" t="n">
-        <v>3.50242805480957</v>
+        <v>3.50242829322815</v>
       </c>
       <c r="H172" t="n">
         <v>10000</v>
@@ -5386,7 +5386,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>3.5834367275238</v>
+        <v>3.58343696594238</v>
       </c>
       <c r="H173" t="n">
         <v>6500</v>
@@ -5444,7 +5444,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G175" t="n">
-        <v>3.55484533309937</v>
+        <v>3.55484580993652</v>
       </c>
       <c r="H175" t="n">
         <v>4000</v>
@@ -5473,7 +5473,7 @@
         <v>3.75</v>
       </c>
       <c r="G176" t="n">
-        <v>3.57390666007996</v>
+        <v>3.57390689849854</v>
       </c>
       <c r="H176" t="n">
         <v>6500</v>
@@ -5502,7 +5502,7 @@
         <v>3.75</v>
       </c>
       <c r="G177" t="n">
-        <v>3.57390666007996</v>
+        <v>3.57390689849854</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G178" t="n">
-        <v>3.76451516151428</v>
+        <v>3.7645149230957</v>
       </c>
       <c r="H178" t="n">
         <v>4000</v>
@@ -5589,7 +5589,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>3.75498461723328</v>
+        <v>3.7549843788147</v>
       </c>
       <c r="H180" t="n">
         <v>24000</v>
@@ -5618,7 +5618,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G181" t="n">
-        <v>3.75498461723328</v>
+        <v>3.7549843788147</v>
       </c>
       <c r="H181" t="n">
         <v>10000</v>
@@ -5647,7 +5647,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G182" t="n">
-        <v>3.62155866622925</v>
+        <v>3.62155890464783</v>
       </c>
       <c r="H182" t="n">
         <v>13500</v>
@@ -5676,7 +5676,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G183" t="n">
-        <v>3.5453155040741</v>
+        <v>3.54531526565552</v>
       </c>
       <c r="H183" t="n">
         <v>19500</v>
@@ -5705,7 +5705,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G184" t="n">
-        <v>3.62155866622925</v>
+        <v>3.62155890464783</v>
       </c>
       <c r="H184" t="n">
         <v>9500</v>
@@ -5850,7 +5850,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>3.65014982223511</v>
+        <v>3.65015006065369</v>
       </c>
       <c r="H189" t="n">
         <v>4350</v>
@@ -5879,7 +5879,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G190" t="n">
-        <v>3.79310607910156</v>
+        <v>3.79310584068298</v>
       </c>
       <c r="H190" t="n">
         <v>9537</v>
@@ -5966,7 +5966,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>3.95512366294861</v>
+        <v>3.95512390136719</v>
       </c>
       <c r="H193" t="n">
         <v>3120</v>
@@ -6053,7 +6053,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G196" t="n">
-        <v>3.80263638496399</v>
+        <v>3.80263662338257</v>
       </c>
       <c r="H196" t="n">
         <v>3767</v>
@@ -6082,7 +6082,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>3.85028886795044</v>
+        <v>3.85028910636902</v>
       </c>
       <c r="H197" t="n">
         <v>810</v>
@@ -6111,7 +6111,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>3.75498461723328</v>
+        <v>3.7549843788147</v>
       </c>
       <c r="H198" t="n">
         <v>10740</v>
@@ -6140,7 +6140,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>3.75498461723328</v>
+        <v>3.7549843788147</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G200" t="n">
-        <v>3.77414298057556</v>
+        <v>3.7741425037384</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>4</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83161664009094</v>
+        <v>3.83161687850952</v>
       </c>
       <c r="H201" t="n">
         <v>14910</v>
@@ -6227,7 +6227,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>3.92740678787231</v>
+        <v>3.92740774154663</v>
       </c>
       <c r="H202" t="n">
         <v>6500</v>
@@ -6256,7 +6256,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H203" t="n">
         <v>3200</v>
@@ -6372,7 +6372,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>3.77414298057556</v>
+        <v>3.7741425037384</v>
       </c>
       <c r="H207" t="n">
         <v>6680</v>
@@ -6401,7 +6401,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>3.70708966255188</v>
+        <v>3.7070894241333</v>
       </c>
       <c r="H208" t="n">
         <v>1000</v>
@@ -6430,7 +6430,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G209" t="n">
-        <v>3.69751048088074</v>
+        <v>3.69751024246216</v>
       </c>
       <c r="H209" t="n">
         <v>500</v>
@@ -6459,7 +6459,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G210" t="n">
-        <v>3.69751048088074</v>
+        <v>3.69751024246216</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>3.83161664009094</v>
+        <v>3.83161687850952</v>
       </c>
       <c r="H211" t="n">
         <v>12500</v>
@@ -6517,7 +6517,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H212" t="n">
         <v>12189</v>
@@ -6546,7 +6546,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>3.78372192382812</v>
+        <v>3.78372168540955</v>
       </c>
       <c r="H214" t="n">
         <v>3800</v>
@@ -6604,7 +6604,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H215" t="n">
         <v>1090</v>
@@ -6633,7 +6633,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>3.8795120716095</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H216" t="n">
         <v>1000</v>
@@ -6691,7 +6691,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G218" t="n">
-        <v>3.94656586647034</v>
+        <v>3.94656562805176</v>
       </c>
       <c r="H218" t="n">
         <v>18231</v>
@@ -6720,7 +6720,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>4.02319765090942</v>
+        <v>4.02319717407227</v>
       </c>
       <c r="H219" t="n">
         <v>14879</v>
@@ -6778,7 +6778,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.21477842330933</v>
+        <v>4.21477937698364</v>
       </c>
       <c r="H221" t="n">
         <v>5788</v>
@@ -6807,7 +6807,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>4.10940933227539</v>
+        <v>4.10940980911255</v>
       </c>
       <c r="H222" t="n">
         <v>22705</v>
@@ -6836,7 +6836,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G223" t="n">
-        <v>4.1477255821228</v>
+        <v>4.14772510528564</v>
       </c>
       <c r="H223" t="n">
         <v>2021</v>
@@ -6865,7 +6865,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G224" t="n">
-        <v>4.19562101364136</v>
+        <v>4.1956205368042</v>
       </c>
       <c r="H224" t="n">
         <v>6059</v>
@@ -6894,7 +6894,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G225" t="n">
-        <v>4.39678049087524</v>
+        <v>4.3967809677124</v>
       </c>
       <c r="H225" t="n">
         <v>12211</v>
@@ -6923,7 +6923,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>4.50214958190918</v>
+        <v>4.50215005874634</v>
       </c>
       <c r="H226" t="n">
         <v>33604</v>
@@ -6952,7 +6952,7 @@
         <v>4.5</v>
       </c>
       <c r="G227" t="n">
-        <v>4.31056880950928</v>
+        <v>4.31056928634644</v>
       </c>
       <c r="H227" t="n">
         <v>15408</v>
@@ -7010,7 +7010,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G229" t="n">
-        <v>4.43509721755981</v>
+        <v>4.4350962638855</v>
       </c>
       <c r="H229" t="n">
         <v>5450</v>
@@ -7039,7 +7039,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>4.38720178604126</v>
+        <v>4.38720083236694</v>
       </c>
       <c r="H230" t="n">
         <v>3150</v>
@@ -7068,7 +7068,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G231" t="n">
-        <v>4.48299217224121</v>
+        <v>4.48299121856689</v>
       </c>
       <c r="H231" t="n">
         <v>3020</v>
@@ -7097,7 +7097,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G232" t="n">
-        <v>4.50214958190918</v>
+        <v>4.50215005874634</v>
       </c>
       <c r="H232" t="n">
         <v>5830</v>
@@ -7271,7 +7271,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G238" t="n">
-        <v>5.00026035308838</v>
+        <v>5.00025987625122</v>
       </c>
       <c r="H238" t="n">
         <v>16448</v>
@@ -7300,7 +7300,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>4.80867910385132</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H239" t="n">
         <v>29610</v>
@@ -7358,7 +7358,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G241" t="n">
-        <v>4.94278621673584</v>
+        <v>4.94278573989868</v>
       </c>
       <c r="H241" t="n">
         <v>8026</v>
@@ -7387,7 +7387,7 @@
         <v>5</v>
       </c>
       <c r="G242" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H242" t="n">
         <v>16194</v>
@@ -7416,7 +7416,7 @@
         <v>5</v>
       </c>
       <c r="G243" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H243" t="n">
         <v>18850</v>
@@ -7445,7 +7445,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>4.82783651351929</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H244" t="n">
         <v>3855</v>
@@ -7474,7 +7474,7 @@
         <v>5</v>
       </c>
       <c r="G245" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H245" t="n">
         <v>1200</v>
@@ -7503,7 +7503,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>4.71288919448853</v>
+        <v>4.71288871765137</v>
       </c>
       <c r="H246" t="n">
         <v>5934</v>
@@ -7532,7 +7532,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>4.71288919448853</v>
+        <v>4.71288871765137</v>
       </c>
       <c r="H247" t="n">
         <v>4150</v>
@@ -7561,7 +7561,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G248" t="n">
-        <v>4.71288919448853</v>
+        <v>4.71288871765137</v>
       </c>
       <c r="H248" t="n">
         <v>3000</v>
@@ -7619,7 +7619,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G250" t="n">
-        <v>4.65541505813599</v>
+        <v>4.65541458129883</v>
       </c>
       <c r="H250" t="n">
         <v>750</v>
@@ -7648,7 +7648,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G251" t="n">
-        <v>4.65541505813599</v>
+        <v>4.65541458129883</v>
       </c>
       <c r="H251" t="n">
         <v>1500</v>
@@ -7706,7 +7706,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>4.82783651351929</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H253" t="n">
         <v>3900</v>
@@ -7764,7 +7764,7 @@
         <v>5</v>
       </c>
       <c r="G255" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H255" t="n">
         <v>13400</v>
@@ -7851,7 +7851,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G258" t="n">
-        <v>4.48299217224121</v>
+        <v>4.48299121856689</v>
       </c>
       <c r="H258" t="n">
         <v>11514</v>
@@ -7880,7 +7880,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>4.63625717163086</v>
+        <v>4.63625621795654</v>
       </c>
       <c r="H259" t="n">
         <v>5992</v>
@@ -7996,7 +7996,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583587646484</v>
       </c>
       <c r="H263" t="n">
         <v>581</v>
@@ -8112,7 +8112,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>4.59793996810913</v>
+        <v>4.59794044494629</v>
       </c>
       <c r="H267" t="n">
         <v>1400</v>
@@ -8141,7 +8141,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>4.59793996810913</v>
+        <v>4.59794044494629</v>
       </c>
       <c r="H268" t="n">
         <v>1635</v>
@@ -8170,7 +8170,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G269" t="n">
-        <v>4.59793996810913</v>
+        <v>4.59794044494629</v>
       </c>
       <c r="H269" t="n">
         <v>4049</v>
@@ -8199,7 +8199,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>4.50214958190918</v>
+        <v>4.50215005874634</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8228,7 +8228,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G271" t="n">
-        <v>4.50214958190918</v>
+        <v>4.50215005874634</v>
       </c>
       <c r="H271" t="n">
         <v>1925</v>
@@ -8257,7 +8257,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G272" t="n">
-        <v>4.50214958190918</v>
+        <v>4.50215005874634</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>4.62667798995972</v>
+        <v>4.62667751312256</v>
       </c>
       <c r="H277" t="n">
         <v>5557</v>
@@ -8431,7 +8431,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G278" t="n">
-        <v>4.65541505813599</v>
+        <v>4.65541458129883</v>
       </c>
       <c r="H278" t="n">
         <v>500</v>
@@ -8518,7 +8518,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>4.71288919448853</v>
+        <v>4.71288871765137</v>
       </c>
       <c r="H281" t="n">
         <v>1663</v>
@@ -8547,7 +8547,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583587646484</v>
       </c>
       <c r="H282" t="n">
         <v>2700</v>
@@ -8576,7 +8576,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583587646484</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>4.75120496749878</v>
+        <v>4.75120449066162</v>
       </c>
       <c r="H288" t="n">
         <v>550</v>
@@ -8750,7 +8750,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G289" t="n">
-        <v>4.80867910385132</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H289" t="n">
         <v>13078</v>
@@ -8808,7 +8808,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>4.80867910385132</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H291" t="n">
         <v>3150</v>
@@ -8837,7 +8837,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>4.80867910385132</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G297" t="n">
-        <v>4.70330953598022</v>
+        <v>4.70331001281738</v>
       </c>
       <c r="H297" t="n">
         <v>297</v>
@@ -9185,7 +9185,7 @@
         <v>5</v>
       </c>
       <c r="G304" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H304" t="n">
         <v>25540</v>
@@ -9214,7 +9214,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>4.82783651351929</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H305" t="n">
         <v>4750</v>
@@ -9301,7 +9301,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>4.80867910385132</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H308" t="n">
         <v>2465</v>
@@ -9388,7 +9388,7 @@
         <v>5</v>
       </c>
       <c r="G311" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H311" t="n">
         <v>5186</v>
@@ -9417,7 +9417,7 @@
         <v>5</v>
       </c>
       <c r="G312" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>5</v>
       </c>
       <c r="G316" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H316" t="n">
         <v>402</v>
@@ -9649,7 +9649,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.82783651351929</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H320" t="n">
         <v>100</v>
@@ -9678,7 +9678,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>4.82783651351929</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>5</v>
       </c>
       <c r="G322" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H322" t="n">
         <v>3400</v>
@@ -9736,7 +9736,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>4.82783651351929</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H323" t="n">
         <v>54154</v>
@@ -9765,7 +9765,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>4.80867910385132</v>
+        <v>4.80867958068848</v>
       </c>
       <c r="H324" t="n">
         <v>26052</v>
@@ -9794,7 +9794,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>4.82783651351929</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H325" t="n">
         <v>1040</v>
@@ -9823,7 +9823,7 @@
         <v>5</v>
       </c>
       <c r="G326" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H326" t="n">
         <v>3000</v>
@@ -9881,7 +9881,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>4.82783651351929</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H328" t="n">
         <v>170</v>
@@ -9910,7 +9910,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>4.82783651351929</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>5</v>
       </c>
       <c r="G330" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H330" t="n">
         <v>7750</v>
@@ -9997,7 +9997,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>4.82783651351929</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H332" t="n">
         <v>4683</v>
@@ -10026,7 +10026,7 @@
         <v>5</v>
       </c>
       <c r="G333" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H333" t="n">
         <v>1125</v>
@@ -10055,7 +10055,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>4.75120496749878</v>
+        <v>4.75120449066162</v>
       </c>
       <c r="H334" t="n">
         <v>3379</v>
@@ -10113,7 +10113,7 @@
         <v>5</v>
       </c>
       <c r="G336" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H336" t="n">
         <v>17100</v>
@@ -10142,7 +10142,7 @@
         <v>5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.78952121734619</v>
+        <v>4.78952074050903</v>
       </c>
       <c r="H337" t="n">
         <v>12410</v>
@@ -10171,7 +10171,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>4.82783651351929</v>
+        <v>4.8278374671936</v>
       </c>
       <c r="H338" t="n">
         <v>6710</v>
@@ -10200,7 +10200,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G339" t="n">
-        <v>4.88531112670898</v>
+        <v>4.8853120803833</v>
       </c>
       <c r="H339" t="n">
         <v>7300</v>
@@ -10229,7 +10229,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.98110151290894</v>
+        <v>4.98110198974609</v>
       </c>
       <c r="H340" t="n">
         <v>8709</v>
@@ -10258,7 +10258,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.88531112670898</v>
+        <v>4.8853120803833</v>
       </c>
       <c r="H341" t="n">
         <v>8729</v>
@@ -10287,7 +10287,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>4.98110151290894</v>
+        <v>4.98110198974609</v>
       </c>
       <c r="H342" t="n">
         <v>12262</v>
@@ -10316,7 +10316,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G343" t="n">
-        <v>5.00026035308838</v>
+        <v>5.00025987625122</v>
       </c>
       <c r="H343" t="n">
         <v>3300</v>
@@ -10345,7 +10345,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.13436651229858</v>
+        <v>5.1343674659729</v>
       </c>
       <c r="H344" t="n">
         <v>6260</v>
@@ -10374,7 +10374,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H345" t="n">
         <v>14432</v>
@@ -10432,7 +10432,7 @@
         <v>5.5</v>
       </c>
       <c r="G347" t="n">
-        <v>5.26847314834595</v>
+        <v>5.26847362518311</v>
       </c>
       <c r="H347" t="n">
         <v>19952</v>
@@ -10490,7 +10490,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G349" t="n">
-        <v>5.21099996566772</v>
+        <v>5.21099948883057</v>
       </c>
       <c r="H349" t="n">
         <v>3837</v>
@@ -10519,7 +10519,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.13436651229858</v>
+        <v>5.1343674659729</v>
       </c>
       <c r="H350" t="n">
         <v>5572</v>
@@ -10548,7 +10548,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G351" t="n">
-        <v>5.13436651229858</v>
+        <v>5.1343674659729</v>
       </c>
       <c r="H351" t="n">
         <v>2712</v>
@@ -10635,7 +10635,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H354" t="n">
         <v>10600</v>
@@ -10722,7 +10722,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H357" t="n">
         <v>2620</v>
@@ -10751,7 +10751,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G358" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H358" t="n">
         <v>2200</v>
@@ -10780,7 +10780,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G359" t="n">
-        <v>5.01941776275635</v>
+        <v>5.01941823959351</v>
       </c>
       <c r="H359" t="n">
         <v>5962</v>
@@ -10838,7 +10838,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G361" t="n">
-        <v>5.21099996566772</v>
+        <v>5.21099948883057</v>
       </c>
       <c r="H361" t="n">
         <v>5616</v>
@@ -10896,7 +10896,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.13436651229858</v>
+        <v>5.1343674659729</v>
       </c>
       <c r="H363" t="n">
         <v>9005</v>
@@ -11041,7 +11041,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G368" t="n">
-        <v>5.47921180725098</v>
+        <v>5.47921228408813</v>
       </c>
       <c r="H368" t="n">
         <v>12600</v>
@@ -11128,7 +11128,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>5.68995189666748</v>
+        <v>5.68995094299316</v>
       </c>
       <c r="H371" t="n">
         <v>95523</v>
@@ -11157,7 +11157,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G372" t="n">
-        <v>5.65163421630859</v>
+        <v>5.65163516998291</v>
       </c>
       <c r="H372" t="n">
         <v>10973</v>
@@ -11215,7 +11215,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H374" t="n">
         <v>28432</v>
@@ -11273,7 +11273,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G376" t="n">
-        <v>5.91984796524048</v>
+        <v>5.91984748840332</v>
       </c>
       <c r="H376" t="n">
         <v>68584</v>
@@ -11302,7 +11302,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G377" t="n">
-        <v>5.90069007873535</v>
+        <v>5.90069055557251</v>
       </c>
       <c r="H377" t="n">
         <v>7100</v>
@@ -11331,7 +11331,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>5.86237382888794</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H378" t="n">
         <v>4967</v>
@@ -11360,7 +11360,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G379" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H379" t="n">
         <v>9296</v>
@@ -11389,7 +11389,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H380" t="n">
         <v>9397</v>
@@ -11418,7 +11418,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H381" t="n">
         <v>7655</v>
@@ -11447,7 +11447,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>5.88153171539307</v>
+        <v>5.88153219223022</v>
       </c>
       <c r="H382" t="n">
         <v>6996</v>
@@ -11476,7 +11476,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>5.86237382888794</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H383" t="n">
         <v>20723</v>
@@ -11505,7 +11505,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G384" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H384" t="n">
         <v>4781</v>
@@ -11534,7 +11534,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H385" t="n">
         <v>6939</v>
@@ -11563,7 +11563,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G386" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H386" t="n">
         <v>4823</v>
@@ -11592,7 +11592,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H387" t="n">
         <v>12576</v>
@@ -11621,7 +11621,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G388" t="n">
-        <v>5.97732305526733</v>
+        <v>5.97732210159302</v>
       </c>
       <c r="H388" t="n">
         <v>6806</v>
@@ -11650,7 +11650,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>5.82405853271484</v>
+        <v>5.82405805587769</v>
       </c>
       <c r="H389" t="n">
         <v>8803</v>
@@ -11679,7 +11679,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H390" t="n">
         <v>1250</v>
@@ -11708,7 +11708,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G391" t="n">
-        <v>5.91984796524048</v>
+        <v>5.91984748840332</v>
       </c>
       <c r="H391" t="n">
         <v>7410</v>
@@ -11737,7 +11737,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H392" t="n">
         <v>6232</v>
@@ -11766,7 +11766,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G393" t="n">
-        <v>5.86237382888794</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H393" t="n">
         <v>2811</v>
@@ -11795,7 +11795,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G394" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H394" t="n">
         <v>1262</v>
@@ -11824,7 +11824,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G395" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H395" t="n">
         <v>4960</v>
@@ -11882,7 +11882,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>6.07311296463013</v>
+        <v>6.07311344146729</v>
       </c>
       <c r="H397" t="n">
         <v>4390</v>
@@ -11911,7 +11911,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>6.37964200973511</v>
+        <v>6.37964153289795</v>
       </c>
       <c r="H398" t="n">
         <v>14389</v>
@@ -11940,7 +11940,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G399" t="n">
-        <v>6.37964200973511</v>
+        <v>6.37964153289795</v>
       </c>
       <c r="H399" t="n">
         <v>32191</v>
@@ -11998,7 +11998,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G401" t="n">
-        <v>6.36048460006714</v>
+        <v>6.36048412322998</v>
       </c>
       <c r="H401" t="n">
         <v>5726</v>
@@ -12027,7 +12027,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G402" t="n">
-        <v>6.37964200973511</v>
+        <v>6.37964153289795</v>
       </c>
       <c r="H402" t="n">
         <v>7998</v>
@@ -12056,7 +12056,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G403" t="n">
-        <v>6.45627450942993</v>
+        <v>6.45627498626709</v>
       </c>
       <c r="H403" t="n">
         <v>12037</v>
@@ -12085,7 +12085,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G404" t="n">
-        <v>6.39879989624023</v>
+        <v>6.39880037307739</v>
       </c>
       <c r="H404" t="n">
         <v>3594</v>
@@ -12143,7 +12143,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>6.36048460006714</v>
+        <v>6.36048412322998</v>
       </c>
       <c r="H406" t="n">
         <v>10355</v>
@@ -12201,7 +12201,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>6.41795778274536</v>
+        <v>6.41795873641968</v>
       </c>
       <c r="H408" t="n">
         <v>8123</v>
@@ -12346,7 +12346,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>5.86237382888794</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H413" t="n">
         <v>10835</v>
@@ -12375,7 +12375,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G414" t="n">
-        <v>6.07311296463013</v>
+        <v>6.07311344146729</v>
       </c>
       <c r="H414" t="n">
         <v>26996</v>
@@ -12462,7 +12462,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G417" t="n">
-        <v>5.90069007873535</v>
+        <v>5.90069055557251</v>
       </c>
       <c r="H417" t="n">
         <v>11796</v>
@@ -12520,7 +12520,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G419" t="n">
-        <v>5.90069007873535</v>
+        <v>5.90069055557251</v>
       </c>
       <c r="H419" t="n">
         <v>4174</v>
@@ -12549,7 +12549,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>5.70910978317261</v>
+        <v>5.70910882949829</v>
       </c>
       <c r="H420" t="n">
         <v>8111</v>
@@ -12578,7 +12578,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>5.70910978317261</v>
+        <v>5.70910882949829</v>
       </c>
       <c r="H421" t="n">
         <v>18321</v>
@@ -12607,7 +12607,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>5.67079305648804</v>
+        <v>5.6707935333252</v>
       </c>
       <c r="H422" t="n">
         <v>18735</v>
@@ -12636,7 +12636,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G423" t="n">
-        <v>5.67079305648804</v>
+        <v>5.6707935333252</v>
       </c>
       <c r="H423" t="n">
         <v>2501</v>
@@ -12665,7 +12665,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G424" t="n">
-        <v>5.86237382888794</v>
+        <v>5.86237335205078</v>
       </c>
       <c r="H424" t="n">
         <v>4073</v>
@@ -12694,7 +12694,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>5.93900537490845</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H425" t="n">
         <v>2570</v>
@@ -12723,7 +12723,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G426" t="n">
-        <v>5.97732305526733</v>
+        <v>5.97732210159302</v>
       </c>
       <c r="H426" t="n">
         <v>8830</v>
@@ -12752,7 +12752,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G427" t="n">
-        <v>5.99648094177246</v>
+        <v>5.99648141860962</v>
       </c>
       <c r="H427" t="n">
         <v>8596</v>
@@ -12781,7 +12781,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>6.07311296463013</v>
+        <v>6.07311344146729</v>
       </c>
       <c r="H428" t="n">
         <v>6440</v>
@@ -12839,7 +12839,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G430" t="n">
-        <v>6.053955078125</v>
+        <v>6.05395460128784</v>
       </c>
       <c r="H430" t="n">
         <v>3535</v>
@@ -12868,7 +12868,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G431" t="n">
-        <v>6.053955078125</v>
+        <v>6.05395460128784</v>
       </c>
       <c r="H431" t="n">
         <v>1471</v>
@@ -12926,7 +12926,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G433" t="n">
-        <v>6.3030104637146</v>
+        <v>6.30300998687744</v>
       </c>
       <c r="H433" t="n">
         <v>5881</v>
@@ -12955,7 +12955,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>6.41795778274536</v>
+        <v>6.41795873641968</v>
       </c>
       <c r="H434" t="n">
         <v>27535</v>
@@ -12984,7 +12984,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>6.41795778274536</v>
+        <v>6.41795873641968</v>
       </c>
       <c r="H435" t="n">
         <v>5559</v>
@@ -13013,7 +13013,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G436" t="n">
-        <v>6.57122278213501</v>
+        <v>6.57122325897217</v>
       </c>
       <c r="H436" t="n">
         <v>24597</v>
@@ -13245,7 +13245,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G444" t="n">
-        <v>6.7819619178772</v>
+        <v>6.78196144104004</v>
       </c>
       <c r="H444" t="n">
         <v>9214</v>
@@ -13274,7 +13274,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>6.99270057678223</v>
+        <v>6.99270105361938</v>
       </c>
       <c r="H445" t="n">
         <v>26998</v>
@@ -13332,7 +13332,7 @@
         <v>7.5</v>
       </c>
       <c r="G447" t="n">
-        <v>7.18428134918213</v>
+        <v>7.1842827796936</v>
       </c>
       <c r="H447" t="n">
         <v>16792</v>
@@ -13390,7 +13390,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G449" t="n">
-        <v>7.79734134674072</v>
+        <v>7.79734230041504</v>
       </c>
       <c r="H449" t="n">
         <v>25454</v>
@@ -13419,7 +13419,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G450" t="n">
-        <v>7.68239212036133</v>
+        <v>7.68239259719849</v>
       </c>
       <c r="H450" t="n">
         <v>46433</v>
@@ -13448,7 +13448,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G451" t="n">
-        <v>8.00807857513428</v>
+        <v>8.00807952880859</v>
       </c>
       <c r="H451" t="n">
         <v>28419</v>
@@ -13477,7 +13477,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G452" t="n">
-        <v>8.1138277053833</v>
+        <v>8.11382865905762</v>
       </c>
       <c r="H452" t="n">
         <v>11712</v>
@@ -13564,7 +13564,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G455" t="n">
-        <v>7.99846601486206</v>
+        <v>7.99846458435059</v>
       </c>
       <c r="H455" t="n">
         <v>13585</v>
@@ -13593,7 +13593,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.07537460327148</v>
+        <v>8.07537364959717</v>
       </c>
       <c r="H456" t="n">
         <v>15884</v>
@@ -13622,7 +13622,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G457" t="n">
-        <v>8.07537460327148</v>
+        <v>8.07537364959717</v>
       </c>
       <c r="H457" t="n">
         <v>8749</v>
@@ -13709,7 +13709,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G460" t="n">
-        <v>8.01769351959229</v>
+        <v>8.01769256591797</v>
       </c>
       <c r="H460" t="n">
         <v>2888</v>
@@ -13738,7 +13738,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G461" t="n">
-        <v>8.07537460327148</v>
+        <v>8.07537364959717</v>
       </c>
       <c r="H461" t="n">
         <v>4060</v>
@@ -13767,7 +13767,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G462" t="n">
-        <v>8.1138277053833</v>
+        <v>8.11382865905762</v>
       </c>
       <c r="H462" t="n">
         <v>6009</v>
@@ -13796,7 +13796,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.07537460327148</v>
+        <v>8.07537364959717</v>
       </c>
       <c r="H463" t="n">
         <v>3875</v>
@@ -13825,7 +13825,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>7.80619478225708</v>
+        <v>7.80619430541992</v>
       </c>
       <c r="H464" t="n">
         <v>13308</v>
@@ -13854,7 +13854,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H465" t="n">
         <v>22593</v>
@@ -13970,7 +13970,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G469" t="n">
-        <v>7.26783657073975</v>
+        <v>7.2678370475769</v>
       </c>
       <c r="H469" t="n">
         <v>3130</v>
@@ -14028,7 +14028,7 @@
         <v>7.5</v>
       </c>
       <c r="G471" t="n">
-        <v>7.21015548706055</v>
+        <v>7.21015596389771</v>
       </c>
       <c r="H471" t="n">
         <v>4606</v>
@@ -14086,7 +14086,7 @@
         <v>7.5</v>
       </c>
       <c r="G473" t="n">
-        <v>7.21015548706055</v>
+        <v>7.21015596389771</v>
       </c>
       <c r="H473" t="n">
         <v>577622</v>
@@ -14115,7 +14115,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G474" t="n">
-        <v>7.07556581497192</v>
+        <v>7.07556629180908</v>
       </c>
       <c r="H474" t="n">
         <v>13451</v>
@@ -14144,7 +14144,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G475" t="n">
-        <v>7.49856185913086</v>
+        <v>7.4985613822937</v>
       </c>
       <c r="H475" t="n">
         <v>217706</v>
@@ -14173,7 +14173,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>7.59469747543335</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H476" t="n">
         <v>6071</v>
@@ -14289,7 +14289,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>7.59469747543335</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H480" t="n">
         <v>5804</v>
@@ -14318,7 +14318,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G481" t="n">
-        <v>7.61392450332642</v>
+        <v>7.61392402648926</v>
       </c>
       <c r="H481" t="n">
         <v>6569</v>
@@ -14347,7 +14347,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>7.59469747543335</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H482" t="n">
         <v>3228</v>
@@ -14405,7 +14405,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>7.59469747543335</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H484" t="n">
         <v>2166</v>
@@ -14434,7 +14434,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>7.59469747543335</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H485" t="n">
         <v>10</v>
@@ -14463,7 +14463,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>7.61392450332642</v>
+        <v>7.61392402648926</v>
       </c>
       <c r="H486" t="n">
         <v>6297</v>
@@ -14492,7 +14492,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>7.59469747543335</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H487" t="n">
         <v>63</v>
@@ -14550,7 +14550,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G489" t="n">
-        <v>7.47933483123779</v>
+        <v>7.47933435440063</v>
       </c>
       <c r="H489" t="n">
         <v>5775</v>
@@ -14579,7 +14579,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G490" t="n">
-        <v>7.55624294281006</v>
+        <v>7.55624341964722</v>
       </c>
       <c r="H490" t="n">
         <v>2759</v>
@@ -14608,7 +14608,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G491" t="n">
-        <v>7.46010780334473</v>
+        <v>7.46010732650757</v>
       </c>
       <c r="H491" t="n">
         <v>3191</v>
@@ -14695,7 +14695,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H494" t="n">
         <v>1276</v>
@@ -14724,7 +14724,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H495" t="n">
         <v>3732</v>
@@ -14753,7 +14753,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G496" t="n">
-        <v>7.51778888702393</v>
+        <v>7.51778936386108</v>
       </c>
       <c r="H496" t="n">
         <v>648</v>
@@ -14782,7 +14782,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G497" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701639175415</v>
       </c>
       <c r="H497" t="n">
         <v>370</v>
@@ -14811,7 +14811,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.61392450332642</v>
+        <v>7.61392402648926</v>
       </c>
       <c r="H498" t="n">
         <v>19417</v>
@@ -14956,7 +14956,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G503" t="n">
-        <v>7.67160511016846</v>
+        <v>7.67160558700562</v>
       </c>
       <c r="H503" t="n">
         <v>23875</v>
@@ -14985,7 +14985,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G504" t="n">
-        <v>7.82542276382446</v>
+        <v>7.82542324066162</v>
       </c>
       <c r="H504" t="n">
         <v>8213</v>
@@ -15014,7 +15014,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>8.01769351959229</v>
+        <v>8.01769256591797</v>
       </c>
       <c r="H505" t="n">
         <v>6595</v>
@@ -15072,7 +15072,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G507" t="n">
-        <v>8.34455299377441</v>
+        <v>8.34455394744873</v>
       </c>
       <c r="H507" t="n">
         <v>18075</v>
@@ -15101,7 +15101,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G508" t="n">
-        <v>8.38300800323486</v>
+        <v>8.38300704956055</v>
       </c>
       <c r="H508" t="n">
         <v>13336</v>
@@ -15130,7 +15130,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G509" t="n">
-        <v>8.45991516113281</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H509" t="n">
         <v>2968</v>
@@ -15246,7 +15246,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G513" t="n">
-        <v>8.74832344055176</v>
+        <v>8.74832248687744</v>
       </c>
       <c r="H513" t="n">
         <v>3322</v>
@@ -15275,7 +15275,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>9.24822616577148</v>
+        <v>9.24822521209717</v>
       </c>
       <c r="H514" t="n">
         <v>17324</v>
@@ -15362,7 +15362,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G517" t="n">
-        <v>9.36358833312988</v>
+        <v>9.3635892868042</v>
       </c>
       <c r="H517" t="n">
         <v>19813</v>
@@ -15391,7 +15391,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G518" t="n">
-        <v>9.305908203125</v>
+        <v>9.30590724945068</v>
       </c>
       <c r="H518" t="n">
         <v>7428</v>
@@ -15420,7 +15420,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G519" t="n">
-        <v>9.305908203125</v>
+        <v>9.30590724945068</v>
       </c>
       <c r="H519" t="n">
         <v>9652</v>
@@ -15507,7 +15507,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>9.49817848205566</v>
+        <v>9.49817752838135</v>
       </c>
       <c r="H522" t="n">
         <v>4632</v>
@@ -15536,7 +15536,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G523" t="n">
-        <v>9.47895050048828</v>
+        <v>9.47894954681396</v>
       </c>
       <c r="H523" t="n">
         <v>7936</v>
@@ -15594,7 +15594,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G525" t="n">
-        <v>9.34436130523682</v>
+        <v>9.34436225891113</v>
       </c>
       <c r="H525" t="n">
         <v>2160</v>
@@ -15623,7 +15623,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G526" t="n">
-        <v>9.36358833312988</v>
+        <v>9.3635892868042</v>
       </c>
       <c r="H526" t="n">
         <v>5384</v>
@@ -15652,7 +15652,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G527" t="n">
-        <v>9.01750087738037</v>
+        <v>9.017502784729</v>
       </c>
       <c r="H527" t="n">
         <v>5818</v>
@@ -15681,7 +15681,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G528" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H528" t="n">
         <v>4558</v>
@@ -15710,7 +15710,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H529" t="n">
         <v>1878</v>
@@ -15739,7 +15739,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G530" t="n">
-        <v>8.70986747741699</v>
+        <v>8.70986938476562</v>
       </c>
       <c r="H530" t="n">
         <v>13372</v>
@@ -15797,7 +15797,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G532" t="n">
-        <v>9.07518100738525</v>
+        <v>9.07518291473389</v>
       </c>
       <c r="H532" t="n">
         <v>11482</v>
@@ -15826,7 +15826,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G533" t="n">
-        <v>8.99827480316162</v>
+        <v>8.9982738494873</v>
       </c>
       <c r="H533" t="n">
         <v>2235</v>
@@ -15942,7 +15942,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G537" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H537" t="n">
         <v>3601</v>
@@ -15971,7 +15971,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G538" t="n">
-        <v>8.74832344055176</v>
+        <v>8.74832248687744</v>
       </c>
       <c r="H538" t="n">
         <v>4284</v>
@@ -16000,7 +16000,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>8.69064140319824</v>
+        <v>8.69064044952393</v>
       </c>
       <c r="H539" t="n">
         <v>10503</v>
@@ -16116,7 +16116,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>8.61373233795166</v>
+        <v>8.61373329162598</v>
       </c>
       <c r="H543" t="n">
         <v>3178</v>
@@ -16145,7 +16145,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G544" t="n">
-        <v>8.47914218902588</v>
+        <v>8.4791431427002</v>
       </c>
       <c r="H544" t="n">
         <v>4043</v>
@@ -16174,7 +16174,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G545" t="n">
-        <v>8.26764583587646</v>
+        <v>8.26764488220215</v>
       </c>
       <c r="H545" t="n">
         <v>17714</v>
@@ -16203,7 +16203,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G546" t="n">
-        <v>8.38300800323486</v>
+        <v>8.38300704956055</v>
       </c>
       <c r="H546" t="n">
         <v>12892</v>
@@ -16232,7 +16232,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>8.38300800323486</v>
+        <v>8.38300704956055</v>
       </c>
       <c r="H547" t="n">
         <v>2415</v>
@@ -16261,7 +16261,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>8.45991516113281</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H548" t="n">
         <v>1190</v>
@@ -16290,7 +16290,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G549" t="n">
-        <v>8.45991516113281</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H549" t="n">
         <v>1246</v>
@@ -16377,7 +16377,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G552" t="n">
-        <v>8.36377906799316</v>
+        <v>8.3637809753418</v>
       </c>
       <c r="H552" t="n">
         <v>2520</v>
@@ -16464,7 +16464,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G555" t="n">
-        <v>8.36377906799316</v>
+        <v>8.3637809753418</v>
       </c>
       <c r="H555" t="n">
         <v>2093</v>
@@ -16493,7 +16493,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>8.45991516113281</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H556" t="n">
         <v>5315</v>
@@ -16522,7 +16522,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>8.45991516113281</v>
+        <v>8.45991611480713</v>
       </c>
       <c r="H557" t="n">
         <v>2498</v>
@@ -16609,7 +16609,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G560" t="n">
-        <v>8.59450531005859</v>
+        <v>8.59450435638428</v>
       </c>
       <c r="H560" t="n">
         <v>5860</v>
@@ -16667,7 +16667,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G562" t="n">
-        <v>8.95982074737549</v>
+        <v>8.95981979370117</v>
       </c>
       <c r="H562" t="n">
         <v>13014</v>
@@ -16696,7 +16696,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G563" t="n">
-        <v>8.90213966369629</v>
+        <v>8.90213775634766</v>
       </c>
       <c r="H563" t="n">
         <v>9291</v>
@@ -16783,7 +16783,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G566" t="n">
-        <v>8.95982074737549</v>
+        <v>8.95981979370117</v>
       </c>
       <c r="H566" t="n">
         <v>4531</v>
@@ -16812,7 +16812,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G567" t="n">
-        <v>9.1905460357666</v>
+        <v>9.19054508209229</v>
       </c>
       <c r="H567" t="n">
         <v>36349</v>
@@ -16899,7 +16899,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G570" t="n">
-        <v>9.03672790527344</v>
+        <v>9.03672695159912</v>
       </c>
       <c r="H570" t="n">
         <v>9621</v>
@@ -16928,7 +16928,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G571" t="n">
-        <v>9.07518100738525</v>
+        <v>9.07518291473389</v>
       </c>
       <c r="H571" t="n">
         <v>10495</v>
@@ -16957,7 +16957,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G572" t="n">
-        <v>9.05595588684082</v>
+        <v>9.0559549331665</v>
       </c>
       <c r="H572" t="n">
         <v>1422</v>
@@ -16986,7 +16986,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>9.07518100738525</v>
+        <v>9.07518291473389</v>
       </c>
       <c r="H573" t="n">
         <v>1872</v>
@@ -17015,7 +17015,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G574" t="n">
-        <v>9.01750087738037</v>
+        <v>9.017502784729</v>
       </c>
       <c r="H574" t="n">
         <v>3029</v>
@@ -17044,7 +17044,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G575" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H575" t="n">
         <v>8026</v>
@@ -17160,7 +17160,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G579" t="n">
-        <v>8.90213966369629</v>
+        <v>8.90213775634766</v>
       </c>
       <c r="H579" t="n">
         <v>6126</v>
@@ -17189,7 +17189,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G580" t="n">
-        <v>8.86368465423584</v>
+        <v>8.86368560791016</v>
       </c>
       <c r="H580" t="n">
         <v>7665</v>
@@ -17218,7 +17218,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G581" t="n">
-        <v>8.84445762634277</v>
+        <v>8.84445667266846</v>
       </c>
       <c r="H581" t="n">
         <v>4098</v>
@@ -17247,7 +17247,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G582" t="n">
-        <v>8.70986747741699</v>
+        <v>8.70986938476562</v>
       </c>
       <c r="H582" t="n">
         <v>2983</v>
@@ -17334,7 +17334,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.69064140319824</v>
+        <v>8.69064044952393</v>
       </c>
       <c r="H585" t="n">
         <v>6475</v>
@@ -17363,7 +17363,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>8.74832344055176</v>
+        <v>8.74832248687744</v>
       </c>
       <c r="H586" t="n">
         <v>3747</v>
@@ -17392,7 +17392,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G587" t="n">
-        <v>8.70986747741699</v>
+        <v>8.70986938476562</v>
       </c>
       <c r="H587" t="n">
         <v>4690</v>
@@ -17421,7 +17421,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G588" t="n">
-        <v>8.70986747741699</v>
+        <v>8.70986938476562</v>
       </c>
       <c r="H588" t="n">
         <v>3314</v>
@@ -17450,7 +17450,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G589" t="n">
-        <v>8.67141342163086</v>
+        <v>8.67141437530518</v>
       </c>
       <c r="H589" t="n">
         <v>4377</v>
@@ -17537,7 +17537,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G592" t="n">
-        <v>8.59450531005859</v>
+        <v>8.59450435638428</v>
       </c>
       <c r="H592" t="n">
         <v>1305</v>
@@ -17595,7 +17595,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G594" t="n">
-        <v>8.80600261688232</v>
+        <v>8.80600166320801</v>
       </c>
       <c r="H594" t="n">
         <v>19270</v>
@@ -17653,7 +17653,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>8.76754856109619</v>
+        <v>8.76754951477051</v>
       </c>
       <c r="H596" t="n">
         <v>819</v>
@@ -17769,7 +17769,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G600" t="n">
-        <v>9.34436130523682</v>
+        <v>9.34436225891113</v>
       </c>
       <c r="H600" t="n">
         <v>5708</v>
@@ -17885,7 +17885,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G604" t="n">
-        <v>9.26745414733887</v>
+        <v>9.26745319366455</v>
       </c>
       <c r="H604" t="n">
         <v>4700</v>
@@ -17914,7 +17914,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G605" t="n">
-        <v>9.36358833312988</v>
+        <v>9.3635892868042</v>
       </c>
       <c r="H605" t="n">
         <v>13690</v>
@@ -17972,7 +17972,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>9.22899913787842</v>
+        <v>9.22900009155273</v>
       </c>
       <c r="H607" t="n">
         <v>5619</v>
@@ -18233,7 +18233,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G616" t="n">
-        <v>9.22899913787842</v>
+        <v>9.22900009155273</v>
       </c>
       <c r="H616" t="n">
         <v>7286</v>
@@ -18320,7 +18320,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G619" t="n">
-        <v>9.22899913787842</v>
+        <v>9.22900009155273</v>
       </c>
       <c r="H619" t="n">
         <v>2736</v>
@@ -18349,7 +18349,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G620" t="n">
-        <v>9.22899913787842</v>
+        <v>9.22900009155273</v>
       </c>
       <c r="H620" t="n">
         <v>9237</v>
@@ -18407,7 +18407,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G622" t="n">
-        <v>9.22899913787842</v>
+        <v>9.22900009155273</v>
       </c>
       <c r="H622" t="n">
         <v>200</v>
@@ -18465,7 +18465,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G624" t="n">
-        <v>9.42126941680908</v>
+        <v>9.4212703704834</v>
       </c>
       <c r="H624" t="n">
         <v>23348</v>
@@ -18494,7 +18494,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>9.7577428817749</v>
+        <v>9.75774383544922</v>
       </c>
       <c r="H625" t="n">
         <v>44805</v>
@@ -18581,7 +18581,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G628" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H628" t="n">
         <v>8939</v>
@@ -18610,7 +18610,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G629" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H629" t="n">
         <v>6876</v>
@@ -18639,7 +18639,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G630" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H630" t="n">
         <v>2700</v>
@@ -18668,7 +18668,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>10.1422872543335</v>
+        <v>10.1422863006592</v>
       </c>
       <c r="H631" t="n">
         <v>5772</v>
@@ -18697,7 +18697,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G632" t="n">
-        <v>10.1422872543335</v>
+        <v>10.1422863006592</v>
       </c>
       <c r="H632" t="n">
         <v>5416</v>
@@ -18755,7 +18755,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>9.95001411437988</v>
+        <v>9.95001602172852</v>
       </c>
       <c r="H634" t="n">
         <v>8284</v>
@@ -18813,7 +18813,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G636" t="n">
-        <v>10.0461502075195</v>
+        <v>10.0461492538452</v>
       </c>
       <c r="H636" t="n">
         <v>2509</v>
@@ -18871,7 +18871,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>10.190354347229</v>
+        <v>10.1903533935547</v>
       </c>
       <c r="H638" t="n">
         <v>4002</v>
@@ -18900,7 +18900,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G639" t="n">
-        <v>10.28648853302</v>
+        <v>10.2864875793457</v>
       </c>
       <c r="H639" t="n">
         <v>3428</v>
@@ -18929,7 +18929,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>10.5268259048462</v>
+        <v>10.5268278121948</v>
       </c>
       <c r="H640" t="n">
         <v>31497</v>
@@ -18958,7 +18958,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>10.4787578582764</v>
+        <v>10.4787588119507</v>
       </c>
       <c r="H641" t="n">
         <v>6326</v>
@@ -18987,7 +18987,7 @@
         <v>10.75</v>
       </c>
       <c r="G642" t="n">
-        <v>10.3345565795898</v>
+        <v>10.3345556259155</v>
       </c>
       <c r="H642" t="n">
         <v>5010</v>
@@ -19016,7 +19016,7 @@
         <v>10.75</v>
       </c>
       <c r="G643" t="n">
-        <v>10.3345565795898</v>
+        <v>10.3345556259155</v>
       </c>
       <c r="H643" t="n">
         <v>2849</v>
@@ -19045,7 +19045,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>10.3826246261597</v>
+        <v>10.3826236724854</v>
       </c>
       <c r="H644" t="n">
         <v>5721</v>
@@ -19074,7 +19074,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G645" t="n">
-        <v>10.3826246261597</v>
+        <v>10.3826236724854</v>
       </c>
       <c r="H645" t="n">
         <v>11643</v>
@@ -19103,7 +19103,7 @@
         <v>10.75</v>
       </c>
       <c r="G646" t="n">
-        <v>10.3345565795898</v>
+        <v>10.3345556259155</v>
       </c>
       <c r="H646" t="n">
         <v>6485</v>
@@ -19132,7 +19132,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>10.4787578582764</v>
+        <v>10.4787588119507</v>
       </c>
       <c r="H647" t="n">
         <v>9307</v>
@@ -19219,7 +19219,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>10.7671661376953</v>
+        <v>10.767165184021</v>
       </c>
       <c r="H650" t="n">
         <v>4282</v>
@@ -19335,7 +19335,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8246545791626</v>
+        <v>11.8246555328369</v>
       </c>
       <c r="H654" t="n">
         <v>17953</v>
@@ -19364,7 +19364,7 @@
         <v>12.5</v>
       </c>
       <c r="G655" t="n">
-        <v>12.0169258117676</v>
+        <v>12.0169248580933</v>
       </c>
       <c r="H655" t="n">
         <v>11862</v>
@@ -19393,7 +19393,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>12.3053340911865</v>
+        <v>12.3053312301636</v>
       </c>
       <c r="H656" t="n">
         <v>14410</v>
@@ -19422,7 +19422,7 @@
         <v>13.25</v>
       </c>
       <c r="G657" t="n">
-        <v>12.737940788269</v>
+        <v>12.7379417419434</v>
       </c>
       <c r="H657" t="n">
         <v>14875</v>
@@ -19480,7 +19480,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>12.9302129745483</v>
+        <v>12.930212020874</v>
       </c>
       <c r="H659" t="n">
         <v>22441</v>
@@ -19509,7 +19509,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G660" t="n">
-        <v>12.834077835083</v>
+        <v>12.8340768814087</v>
       </c>
       <c r="H660" t="n">
         <v>13566</v>
@@ -19567,7 +19567,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>12.1130609512329</v>
+        <v>12.1130619049072</v>
       </c>
       <c r="H662" t="n">
         <v>25415</v>
@@ -19596,7 +19596,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G663" t="n">
-        <v>12.7860088348389</v>
+        <v>12.7860097885132</v>
       </c>
       <c r="H663" t="n">
         <v>12196</v>
@@ -19654,7 +19654,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>12.6418056488037</v>
+        <v>12.6418037414551</v>
       </c>
       <c r="H665" t="n">
         <v>5141</v>
@@ -19683,7 +19683,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>12.7860088348389</v>
+        <v>12.7860097885132</v>
       </c>
       <c r="H666" t="n">
         <v>8354</v>
@@ -19712,7 +19712,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>12.7860088348389</v>
+        <v>12.7860097885132</v>
       </c>
       <c r="H667" t="n">
         <v>10497</v>
@@ -19741,7 +19741,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>12.834077835083</v>
+        <v>12.8340768814087</v>
       </c>
       <c r="H668" t="n">
         <v>7739</v>
@@ -19770,7 +19770,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>12.7860088348389</v>
+        <v>12.7860097885132</v>
       </c>
       <c r="H669" t="n">
         <v>5925</v>
@@ -19828,7 +19828,7 @@
         <v>13.25</v>
       </c>
       <c r="G671" t="n">
-        <v>12.737940788269</v>
+        <v>12.7379417419434</v>
       </c>
       <c r="H671" t="n">
         <v>2438</v>
@@ -19857,7 +19857,7 @@
         <v>13.25</v>
       </c>
       <c r="G672" t="n">
-        <v>12.737940788269</v>
+        <v>12.7379417419434</v>
       </c>
       <c r="H672" t="n">
         <v>6340</v>
@@ -19915,7 +19915,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G674" t="n">
-        <v>13.507025718689</v>
+        <v>13.5070247650146</v>
       </c>
       <c r="H674" t="n">
         <v>9056</v>
@@ -19944,7 +19944,7 @@
         <v>14.5</v>
       </c>
       <c r="G675" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H675" t="n">
         <v>5327</v>
@@ -19973,7 +19973,7 @@
         <v>14.5</v>
       </c>
       <c r="G676" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H676" t="n">
         <v>16748</v>
@@ -20002,7 +20002,7 @@
         <v>14.5</v>
       </c>
       <c r="G677" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H677" t="n">
         <v>8967</v>
@@ -20031,7 +20031,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>13.8915672302246</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H678" t="n">
         <v>14525</v>
@@ -20089,7 +20089,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G680" t="n">
-        <v>13.507025718689</v>
+        <v>13.5070247650146</v>
       </c>
       <c r="H680" t="n">
         <v>7178</v>
@@ -20118,7 +20118,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>13.6512279510498</v>
+        <v>13.6512269973755</v>
       </c>
       <c r="H681" t="n">
         <v>21605</v>
@@ -20147,7 +20147,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>13.8915672302246</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H682" t="n">
         <v>8370</v>
@@ -20205,7 +20205,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>14.1319036483765</v>
+        <v>14.1319046020508</v>
       </c>
       <c r="H684" t="n">
         <v>13280</v>
@@ -20234,7 +20234,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G685" t="n">
-        <v>14.1319036483765</v>
+        <v>14.1319046020508</v>
       </c>
       <c r="H685" t="n">
         <v>10052</v>
@@ -20350,7 +20350,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>13.8915672302246</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H689" t="n">
         <v>13501</v>
@@ -20379,7 +20379,7 @@
         <v>14.5</v>
       </c>
       <c r="G690" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H690" t="n">
         <v>26199</v>
@@ -20408,7 +20408,7 @@
         <v>14.5</v>
       </c>
       <c r="G691" t="n">
-        <v>13.9396333694458</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H691" t="n">
         <v>5887</v>
@@ -20437,7 +20437,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>13.8915672302246</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H692" t="n">
         <v>7855</v>
@@ -20466,7 +20466,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>13.8915672302246</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H693" t="n">
         <v>3250</v>
@@ -20524,7 +20524,7 @@
         <v>14.25</v>
       </c>
       <c r="G695" t="n">
-        <v>13.6992950439453</v>
+        <v>13.6992969512939</v>
       </c>
       <c r="H695" t="n">
         <v>3752</v>
@@ -20553,7 +20553,7 @@
         <v>14</v>
       </c>
       <c r="G696" t="n">
-        <v>13.4589567184448</v>
+        <v>13.4589557647705</v>
       </c>
       <c r="H696" t="n">
         <v>8970</v>
@@ -20582,7 +20582,7 @@
         <v>14</v>
       </c>
       <c r="G697" t="n">
-        <v>13.4589567184448</v>
+        <v>13.4589557647705</v>
       </c>
       <c r="H697" t="n">
         <v>3209</v>
@@ -20611,7 +20611,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G698" t="n">
-        <v>13.5550947189331</v>
+        <v>13.5550928115845</v>
       </c>
       <c r="H698" t="n">
         <v>6847</v>
@@ -20814,7 +20814,7 @@
         <v>14.75</v>
       </c>
       <c r="G705" t="n">
-        <v>14.1799736022949</v>
+        <v>14.1799726486206</v>
       </c>
       <c r="H705" t="n">
         <v>1719</v>
@@ -20872,7 +20872,7 @@
         <v>15.5</v>
       </c>
       <c r="G707" t="n">
-        <v>14.9415082931519</v>
+        <v>14.9415063858032</v>
       </c>
       <c r="H707" t="n">
         <v>14252</v>
@@ -20901,7 +20901,7 @@
         <v>15.5</v>
       </c>
       <c r="G708" t="n">
-        <v>14.9415082931519</v>
+        <v>14.9415063858032</v>
       </c>
       <c r="H708" t="n">
         <v>5682</v>
@@ -21017,7 +21017,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>15.9536752700806</v>
+        <v>15.9536733627319</v>
       </c>
       <c r="H712" t="n">
         <v>41242</v>
@@ -21046,7 +21046,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G713" t="n">
-        <v>16.6766490936279</v>
+        <v>16.6766471862793</v>
       </c>
       <c r="H713" t="n">
         <v>15283</v>
@@ -21075,7 +21075,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>16.2910652160645</v>
+        <v>16.2910633087158</v>
       </c>
       <c r="H714" t="n">
         <v>15736</v>
@@ -21104,7 +21104,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>16.5802574157715</v>
+        <v>16.5802555084229</v>
       </c>
       <c r="H715" t="n">
         <v>22030</v>
@@ -21162,7 +21162,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>16.9658393859863</v>
+        <v>16.965841293335</v>
       </c>
       <c r="H717" t="n">
         <v>10720</v>
@@ -21336,7 +21336,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>16.4838581085205</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H723" t="n">
         <v>4063</v>
@@ -21481,7 +21481,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>16.2910652160645</v>
+        <v>16.2910633087158</v>
       </c>
       <c r="H728" t="n">
         <v>9170</v>
@@ -21539,7 +21539,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>16.5802574157715</v>
+        <v>16.5802555084229</v>
       </c>
       <c r="H730" t="n">
         <v>5817</v>
@@ -21568,7 +21568,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>16.4838581085205</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H731" t="n">
         <v>7493</v>
@@ -21597,7 +21597,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>16.4838581085205</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H732" t="n">
         <v>8992</v>
@@ -21626,7 +21626,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G733" t="n">
-        <v>16.2910652160645</v>
+        <v>16.2910633087158</v>
       </c>
       <c r="H733" t="n">
         <v>5388</v>
@@ -21655,7 +21655,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>16.1946659088135</v>
+        <v>16.1946640014648</v>
       </c>
       <c r="H734" t="n">
         <v>4299</v>
@@ -21684,7 +21684,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>16.0982685089111</v>
+        <v>16.0982704162598</v>
       </c>
       <c r="H735" t="n">
         <v>2046</v>
@@ -21713,7 +21713,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>16.1946659088135</v>
+        <v>16.1946640014648</v>
       </c>
       <c r="H736" t="n">
         <v>11338</v>
@@ -21742,7 +21742,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>16.2428646087646</v>
+        <v>16.2428684234619</v>
       </c>
       <c r="H737" t="n">
         <v>1646</v>
@@ -21800,7 +21800,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>16.0982685089111</v>
+        <v>16.0982704162598</v>
       </c>
       <c r="H739" t="n">
         <v>6854</v>
@@ -21858,7 +21858,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H741" t="n">
         <v>16758</v>
@@ -21887,7 +21887,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>15.5198888778687</v>
+        <v>15.5198879241943</v>
       </c>
       <c r="H742" t="n">
         <v>9416</v>
@@ -22032,7 +22032,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G747" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H747" t="n">
         <v>13532</v>
@@ -22090,7 +22090,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G749" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H749" t="n">
         <v>6063</v>
@@ -22148,7 +22148,7 @@
         <v>15.75</v>
       </c>
       <c r="G751" t="n">
-        <v>15.1824998855591</v>
+        <v>15.1825008392334</v>
       </c>
       <c r="H751" t="n">
         <v>1284</v>
@@ -22206,7 +22206,7 @@
         <v>15.75</v>
       </c>
       <c r="G753" t="n">
-        <v>15.1824998855591</v>
+        <v>15.1825008392334</v>
       </c>
       <c r="H753" t="n">
         <v>5094</v>
@@ -22322,7 +22322,7 @@
         <v>16.25</v>
       </c>
       <c r="G757" t="n">
-        <v>15.6644840240479</v>
+        <v>15.6644830703735</v>
       </c>
       <c r="H757" t="n">
         <v>2755</v>
@@ -22351,7 +22351,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G758" t="n">
-        <v>15.8572788238525</v>
+        <v>15.8572769165039</v>
       </c>
       <c r="H758" t="n">
         <v>5944</v>
@@ -22467,7 +22467,7 @@
         <v>16.25</v>
       </c>
       <c r="G762" t="n">
-        <v>15.6644840240479</v>
+        <v>15.6644830703735</v>
       </c>
       <c r="H762" t="n">
         <v>3876</v>
@@ -22496,7 +22496,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>15.5198888778687</v>
+        <v>15.5198879241943</v>
       </c>
       <c r="H763" t="n">
         <v>4072</v>
@@ -22670,7 +22670,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G769" t="n">
-        <v>15.5680866241455</v>
+        <v>15.5680875778198</v>
       </c>
       <c r="H769" t="n">
         <v>1915</v>
@@ -22699,7 +22699,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G770" t="n">
-        <v>16.2910652160645</v>
+        <v>16.2910633087158</v>
       </c>
       <c r="H770" t="n">
         <v>23740</v>
@@ -22757,7 +22757,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>17.4478244781494</v>
+        <v>17.447826385498</v>
       </c>
       <c r="H772" t="n">
         <v>13430</v>
@@ -22786,7 +22786,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G773" t="n">
-        <v>17.4478244781494</v>
+        <v>17.447826385498</v>
       </c>
       <c r="H773" t="n">
         <v>11725</v>
@@ -22815,7 +22815,7 @@
         <v>18</v>
       </c>
       <c r="G774" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H774" t="n">
         <v>18784</v>
@@ -22844,7 +22844,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>17.3032321929932</v>
+        <v>17.3032302856445</v>
       </c>
       <c r="H775" t="n">
         <v>12401</v>
@@ -22902,7 +22902,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>17.158634185791</v>
+        <v>17.1586322784424</v>
       </c>
       <c r="H777" t="n">
         <v>3670</v>
@@ -22960,7 +22960,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G779" t="n">
-        <v>16.6766490936279</v>
+        <v>16.6766471862793</v>
       </c>
       <c r="H779" t="n">
         <v>2108</v>
@@ -23018,7 +23018,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>16.6766490936279</v>
+        <v>16.6766471862793</v>
       </c>
       <c r="H781" t="n">
         <v>1807</v>
@@ -23047,7 +23047,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G782" t="n">
-        <v>16.7730484008789</v>
+        <v>16.7730464935303</v>
       </c>
       <c r="H782" t="n">
         <v>1829</v>
@@ -23076,7 +23076,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>16.6766490936279</v>
+        <v>16.6766471862793</v>
       </c>
       <c r="H783" t="n">
         <v>1355</v>
@@ -23105,7 +23105,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>16.5320529937744</v>
+        <v>16.532054901123</v>
       </c>
       <c r="H784" t="n">
         <v>2334</v>
@@ -23134,7 +23134,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G785" t="n">
-        <v>16.4838581085205</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H785" t="n">
         <v>3050</v>
@@ -23279,7 +23279,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>17.3032321929932</v>
+        <v>17.3032302856445</v>
       </c>
       <c r="H790" t="n">
         <v>7506</v>
@@ -23308,7 +23308,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>17.2068328857422</v>
+        <v>17.2068347930908</v>
       </c>
       <c r="H791" t="n">
         <v>3420</v>
@@ -23337,7 +23337,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G792" t="n">
-        <v>17.3032321929932</v>
+        <v>17.3032302856445</v>
       </c>
       <c r="H792" t="n">
         <v>4523</v>
@@ -23366,7 +23366,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>17.158634185791</v>
+        <v>17.1586322784424</v>
       </c>
       <c r="H793" t="n">
         <v>1275</v>
@@ -23395,7 +23395,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>17.3032321929932</v>
+        <v>17.3032302856445</v>
       </c>
       <c r="H794" t="n">
         <v>2784</v>
@@ -23569,7 +23569,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>17.3032321929932</v>
+        <v>17.3032302856445</v>
       </c>
       <c r="H800" t="n">
         <v>6644</v>
@@ -23627,7 +23627,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>18.0262050628662</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H802" t="n">
         <v>18762</v>
@@ -23656,7 +23656,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671985626221</v>
       </c>
       <c r="H803" t="n">
         <v>13681</v>
@@ -23685,7 +23685,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>18.700984954834</v>
+        <v>18.7009830474854</v>
       </c>
       <c r="H804" t="n">
         <v>25471</v>
@@ -23859,7 +23859,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G810" t="n">
-        <v>18.3635940551758</v>
+        <v>18.3635921478271</v>
       </c>
       <c r="H810" t="n">
         <v>8073</v>
@@ -23888,7 +23888,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G811" t="n">
-        <v>18.4117965698242</v>
+        <v>18.4117946624756</v>
       </c>
       <c r="H811" t="n">
         <v>4783</v>
@@ -23917,7 +23917,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>18.0262050628662</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H812" t="n">
         <v>21969</v>
@@ -23946,7 +23946,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671985626221</v>
       </c>
       <c r="H813" t="n">
         <v>3298</v>
@@ -24033,7 +24033,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>18.1707992553711</v>
+        <v>18.1708030700684</v>
       </c>
       <c r="H816" t="n">
         <v>2568</v>
@@ -24062,7 +24062,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671985626221</v>
       </c>
       <c r="H817" t="n">
         <v>6913</v>
@@ -24091,7 +24091,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>18.2189998626709</v>
+        <v>18.2190017700195</v>
       </c>
       <c r="H818" t="n">
         <v>9888</v>
@@ -24120,7 +24120,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>18.1707992553711</v>
+        <v>18.1708030700684</v>
       </c>
       <c r="H819" t="n">
         <v>5941</v>
@@ -24149,7 +24149,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671985626221</v>
       </c>
       <c r="H820" t="n">
         <v>5621</v>
@@ -24207,7 +24207,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>18.0262050628662</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H822" t="n">
         <v>2366</v>
@@ -24236,7 +24236,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671985626221</v>
       </c>
       <c r="H823" t="n">
         <v>7777</v>
@@ -24265,7 +24265,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>18.1707992553711</v>
+        <v>18.1708030700684</v>
       </c>
       <c r="H824" t="n">
         <v>10467</v>
@@ -24294,7 +24294,7 @@
         <v>18.75</v>
       </c>
       <c r="G825" t="n">
-        <v>18.074405670166</v>
+        <v>18.0744037628174</v>
       </c>
       <c r="H825" t="n">
         <v>9281</v>
@@ -24323,7 +24323,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G826" t="n">
-        <v>17.4478244781494</v>
+        <v>17.447826385498</v>
       </c>
       <c r="H826" t="n">
         <v>34597</v>
@@ -24381,7 +24381,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>17.7370128631592</v>
+        <v>17.7370147705078</v>
       </c>
       <c r="H828" t="n">
         <v>8555</v>
@@ -24410,7 +24410,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>18.1226005554199</v>
+        <v>18.1225986480713</v>
       </c>
       <c r="H829" t="n">
         <v>10298</v>
@@ -24439,7 +24439,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>18.1707992553711</v>
+        <v>18.1708030700684</v>
       </c>
       <c r="H830" t="n">
         <v>1749</v>
@@ -24468,7 +24468,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>17.8816089630127</v>
+        <v>17.8816108703613</v>
       </c>
       <c r="H831" t="n">
         <v>4940</v>
@@ -24497,7 +24497,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>18.1707992553711</v>
+        <v>18.1708030700684</v>
       </c>
       <c r="H832" t="n">
         <v>1475</v>
@@ -24526,7 +24526,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G833" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671985626221</v>
       </c>
       <c r="H833" t="n">
         <v>4556</v>
@@ -24584,7 +24584,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>17.7370128631592</v>
+        <v>17.7370147705078</v>
       </c>
       <c r="H835" t="n">
         <v>13488</v>
@@ -24613,7 +24613,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G836" t="n">
-        <v>17.4478244781494</v>
+        <v>17.447826385498</v>
       </c>
       <c r="H836" t="n">
         <v>3775</v>
@@ -24642,7 +24642,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406173706055</v>
       </c>
       <c r="H837" t="n">
         <v>40035</v>
@@ -24671,7 +24671,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>18.0262050628662</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H838" t="n">
         <v>3812</v>
@@ -24729,7 +24729,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406173706055</v>
       </c>
       <c r="H840" t="n">
         <v>3485</v>
@@ -24758,7 +24758,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>17.8816089630127</v>
+        <v>17.8816108703613</v>
       </c>
       <c r="H841" t="n">
         <v>3677</v>
@@ -24787,7 +24787,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G842" t="n">
-        <v>17.7370128631592</v>
+        <v>17.7370147705078</v>
       </c>
       <c r="H842" t="n">
         <v>3407</v>
@@ -24816,7 +24816,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406173706055</v>
       </c>
       <c r="H843" t="n">
         <v>11897</v>
@@ -24845,7 +24845,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>17.4478244781494</v>
+        <v>17.447826385498</v>
       </c>
       <c r="H844" t="n">
         <v>6486</v>
@@ -24874,7 +24874,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>18.0262050628662</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H845" t="n">
         <v>13179</v>
@@ -24903,7 +24903,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>17.6406192779541</v>
+        <v>17.6406173706055</v>
       </c>
       <c r="H846" t="n">
         <v>2528</v>
@@ -24932,7 +24932,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G847" t="n">
-        <v>17.7370128631592</v>
+        <v>17.7370147705078</v>
       </c>
       <c r="H847" t="n">
         <v>3888</v>
@@ -25048,7 +25048,7 @@
         <v>18</v>
       </c>
       <c r="G851" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H851" t="n">
         <v>8735</v>
@@ -25135,7 +25135,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>17.7370128631592</v>
+        <v>17.7370147705078</v>
       </c>
       <c r="H854" t="n">
         <v>3086</v>
@@ -25164,7 +25164,7 @@
         <v>18</v>
       </c>
       <c r="G855" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H855" t="n">
         <v>6014</v>
@@ -25193,7 +25193,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>17.7852153778076</v>
+        <v>17.785213470459</v>
       </c>
       <c r="H856" t="n">
         <v>3767</v>
@@ -25280,7 +25280,7 @@
         <v>18.25</v>
       </c>
       <c r="G859" t="n">
-        <v>17.5924205780029</v>
+        <v>17.5924224853516</v>
       </c>
       <c r="H859" t="n">
         <v>5378</v>
@@ -25309,7 +25309,7 @@
         <v>18.25</v>
       </c>
       <c r="G860" t="n">
-        <v>17.5924205780029</v>
+        <v>17.5924224853516</v>
       </c>
       <c r="H860" t="n">
         <v>2515</v>
@@ -25338,7 +25338,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G861" t="n">
-        <v>17.7370128631592</v>
+        <v>17.7370147705078</v>
       </c>
       <c r="H861" t="n">
         <v>13384</v>
@@ -25367,7 +25367,7 @@
         <v>18</v>
       </c>
       <c r="G862" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H862" t="n">
         <v>16638</v>
@@ -25396,7 +25396,7 @@
         <v>18</v>
       </c>
       <c r="G863" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H863" t="n">
         <v>2051</v>
@@ -25425,7 +25425,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>17.2068328857422</v>
+        <v>17.2068347930908</v>
       </c>
       <c r="H864" t="n">
         <v>2311</v>
@@ -25454,7 +25454,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G865" t="n">
-        <v>17.3032321929932</v>
+        <v>17.3032302856445</v>
       </c>
       <c r="H865" t="n">
         <v>3146</v>
@@ -25541,7 +25541,7 @@
         <v>18</v>
       </c>
       <c r="G868" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H868" t="n">
         <v>4952</v>
@@ -25599,7 +25599,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>18.0262050628662</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H870" t="n">
         <v>13461</v>
@@ -25628,7 +25628,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>18.1226005554199</v>
+        <v>18.1225986480713</v>
       </c>
       <c r="H871" t="n">
         <v>11848</v>
@@ -25715,7 +25715,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G874" t="n">
-        <v>18.2672004699707</v>
+        <v>18.2671985626221</v>
       </c>
       <c r="H874" t="n">
         <v>1553</v>
@@ -25802,7 +25802,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G877" t="n">
-        <v>18.0262050628662</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H877" t="n">
         <v>4339</v>
@@ -25831,7 +25831,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G878" t="n">
-        <v>18.2189998626709</v>
+        <v>18.2190017700195</v>
       </c>
       <c r="H878" t="n">
         <v>579</v>
@@ -25889,7 +25889,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G880" t="n">
-        <v>19.1347675323486</v>
+        <v>19.1347713470459</v>
       </c>
       <c r="H880" t="n">
         <v>14689</v>
@@ -25918,7 +25918,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>19.1829662322998</v>
+        <v>19.1829681396484</v>
       </c>
       <c r="H881" t="n">
         <v>10787</v>
@@ -26005,7 +26005,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G884" t="n">
-        <v>18.0262050628662</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H884" t="n">
         <v>23659</v>
@@ -26034,7 +26034,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>18.4599914550781</v>
+        <v>18.4599933624268</v>
       </c>
       <c r="H885" t="n">
         <v>4951</v>
@@ -26092,7 +26092,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G887" t="n">
-        <v>18.9901752471924</v>
+        <v>18.9901733398438</v>
       </c>
       <c r="H887" t="n">
         <v>9206</v>
@@ -26121,7 +26121,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>18.9901752471924</v>
+        <v>18.9901733398438</v>
       </c>
       <c r="H888" t="n">
         <v>4533</v>
@@ -26150,7 +26150,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>18.9901752471924</v>
+        <v>18.9901733398438</v>
       </c>
       <c r="H889" t="n">
         <v>10126</v>
@@ -26179,7 +26179,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G890" t="n">
-        <v>18.3635940551758</v>
+        <v>18.3635921478271</v>
       </c>
       <c r="H890" t="n">
         <v>9218</v>
@@ -26208,7 +26208,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>18.1226005554199</v>
+        <v>18.1225986480713</v>
       </c>
       <c r="H891" t="n">
         <v>10241</v>
@@ -26411,7 +26411,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>17.3032321929932</v>
+        <v>17.3032302856445</v>
       </c>
       <c r="H898" t="n">
         <v>2326</v>
@@ -26440,7 +26440,7 @@
         <v>18.25</v>
       </c>
       <c r="G899" t="n">
-        <v>17.5924205780029</v>
+        <v>17.5924224853516</v>
       </c>
       <c r="H899" t="n">
         <v>4107</v>
@@ -26469,7 +26469,7 @@
         <v>18.25</v>
       </c>
       <c r="G900" t="n">
-        <v>17.5924205780029</v>
+        <v>17.5924224853516</v>
       </c>
       <c r="H900" t="n">
         <v>1122</v>
@@ -26498,7 +26498,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G901" t="n">
-        <v>17.7370128631592</v>
+        <v>17.7370147705078</v>
       </c>
       <c r="H901" t="n">
         <v>5230</v>
@@ -26527,7 +26527,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>17.8816089630127</v>
+        <v>17.8816108703613</v>
       </c>
       <c r="H902" t="n">
         <v>3011</v>
@@ -26556,7 +26556,7 @@
         <v>18</v>
       </c>
       <c r="G903" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H903" t="n">
         <v>11215</v>
@@ -26614,7 +26614,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>17.2068328857422</v>
+        <v>17.2068347930908</v>
       </c>
       <c r="H905" t="n">
         <v>950</v>
@@ -26701,7 +26701,7 @@
         <v>18</v>
       </c>
       <c r="G908" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H908" t="n">
         <v>4431</v>
@@ -26817,7 +26817,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G912" t="n">
-        <v>16.5802574157715</v>
+        <v>16.5802555084229</v>
       </c>
       <c r="H912" t="n">
         <v>4259</v>
@@ -26991,7 +26991,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>15.327094078064</v>
+        <v>15.3270959854126</v>
       </c>
       <c r="H918" t="n">
         <v>18627</v>
@@ -27020,7 +27020,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>15.327094078064</v>
+        <v>15.3270959854126</v>
       </c>
       <c r="H919" t="n">
         <v>1224</v>
@@ -27049,7 +27049,7 @@
         <v>15.5</v>
       </c>
       <c r="G920" t="n">
-        <v>14.9415082931519</v>
+        <v>14.9415063858032</v>
       </c>
       <c r="H920" t="n">
         <v>1828</v>
@@ -27165,7 +27165,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G924" t="n">
-        <v>12.9653730392456</v>
+        <v>12.9653720855713</v>
       </c>
       <c r="H924" t="n">
         <v>18799</v>
@@ -27223,7 +27223,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>15.5198888778687</v>
+        <v>15.5198879241943</v>
       </c>
       <c r="H926" t="n">
         <v>12774</v>
@@ -27281,7 +27281,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>16.0018730163574</v>
+        <v>16.0018749237061</v>
       </c>
       <c r="H928" t="n">
         <v>8969</v>
@@ -27368,7 +27368,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>16.1946659088135</v>
+        <v>16.1946640014648</v>
       </c>
       <c r="H931" t="n">
         <v>10440</v>
@@ -27426,7 +27426,7 @@
         <v>15.75</v>
       </c>
       <c r="G933" t="n">
-        <v>15.1824998855591</v>
+        <v>15.1825008392334</v>
       </c>
       <c r="H933" t="n">
         <v>5274</v>
@@ -27484,7 +27484,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>15.0861034393311</v>
+        <v>15.0861024856567</v>
       </c>
       <c r="H935" t="n">
         <v>1447</v>
@@ -27513,7 +27513,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>14.8451099395752</v>
+        <v>14.8451108932495</v>
       </c>
       <c r="H936" t="n">
         <v>3565</v>
@@ -27542,7 +27542,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G937" t="n">
-        <v>14.4113254547119</v>
+        <v>14.4113245010376</v>
       </c>
       <c r="H937" t="n">
         <v>8814</v>
@@ -27600,7 +27600,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>15.327094078064</v>
+        <v>15.3270959854126</v>
       </c>
       <c r="H939" t="n">
         <v>9151</v>
@@ -27658,7 +27658,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G941" t="n">
-        <v>15.0861034393311</v>
+        <v>15.0861024856567</v>
       </c>
       <c r="H941" t="n">
         <v>1106</v>
@@ -27774,7 +27774,7 @@
         <v>15.75</v>
       </c>
       <c r="G945" t="n">
-        <v>15.1824998855591</v>
+        <v>15.1825008392334</v>
       </c>
       <c r="H945" t="n">
         <v>4177</v>
@@ -27832,7 +27832,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G947" t="n">
-        <v>15.0861034393311</v>
+        <v>15.0861024856567</v>
       </c>
       <c r="H947" t="n">
         <v>723</v>
@@ -27977,7 +27977,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G952" t="n">
-        <v>14.604118347168</v>
+        <v>14.6041193008423</v>
       </c>
       <c r="H952" t="n">
         <v>902</v>
@@ -28093,7 +28093,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>14.4113254547119</v>
+        <v>14.4113245010376</v>
       </c>
       <c r="H956" t="n">
         <v>257</v>
@@ -28180,7 +28180,7 @@
         <v>14.5</v>
       </c>
       <c r="G959" t="n">
-        <v>13.9775400161743</v>
+        <v>13.9775390625</v>
       </c>
       <c r="H959" t="n">
         <v>3572</v>
@@ -28209,7 +28209,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G960" t="n">
-        <v>13.6401500701904</v>
+        <v>13.6401510238647</v>
       </c>
       <c r="H960" t="n">
         <v>1673</v>
@@ -28238,7 +28238,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>13.6883487701416</v>
+        <v>13.6883478164673</v>
       </c>
       <c r="H961" t="n">
         <v>1030</v>
@@ -28267,7 +28267,7 @@
         <v>14.5</v>
       </c>
       <c r="G962" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H962" t="n">
         <v>2889</v>
@@ -28354,7 +28354,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G965" t="n">
-        <v>13.8432388305664</v>
+        <v>13.8432397842407</v>
       </c>
       <c r="H965" t="n">
         <v>8715</v>
@@ -28383,7 +28383,7 @@
         <v>14.5</v>
       </c>
       <c r="G966" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H966" t="n">
         <v>868</v>
@@ -28412,7 +28412,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G967" t="n">
-        <v>13.4076118469238</v>
+        <v>13.4076128005981</v>
       </c>
       <c r="H967" t="n">
         <v>1852</v>
@@ -28499,7 +28499,7 @@
         <v>14</v>
       </c>
       <c r="G970" t="n">
-        <v>13.5528221130371</v>
+        <v>13.5528211593628</v>
       </c>
       <c r="H970" t="n">
         <v>964</v>
@@ -28528,7 +28528,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G971" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H971" t="n">
         <v>14283</v>
@@ -28557,7 +28557,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G972" t="n">
-        <v>14.4724769592285</v>
+        <v>14.4724760055542</v>
       </c>
       <c r="H972" t="n">
         <v>4243</v>
@@ -28644,7 +28644,7 @@
         <v>15</v>
       </c>
       <c r="G975" t="n">
-        <v>14.5208797454834</v>
+        <v>14.5208787918091</v>
       </c>
       <c r="H975" t="n">
         <v>901</v>
@@ -28731,7 +28731,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>13.4076118469238</v>
+        <v>13.4076128005981</v>
       </c>
       <c r="H978" t="n">
         <v>2074</v>
@@ -28760,7 +28760,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G979" t="n">
-        <v>13.1171941757202</v>
+        <v>13.1171951293945</v>
       </c>
       <c r="H979" t="n">
         <v>6255</v>
@@ -28818,7 +28818,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G981" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H981" t="n">
         <v>13144</v>
@@ -28847,7 +28847,7 @@
         <v>15.75</v>
       </c>
       <c r="G982" t="n">
-        <v>15.2469244003296</v>
+        <v>15.2469234466553</v>
       </c>
       <c r="H982" t="n">
         <v>13824</v>
@@ -29050,7 +29050,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>15.0533123016357</v>
+        <v>15.0533132553101</v>
       </c>
       <c r="H989" t="n">
         <v>3452</v>
@@ -29253,7 +29253,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G996" t="n">
-        <v>13.8432388305664</v>
+        <v>13.8432397842407</v>
       </c>
       <c r="H996" t="n">
         <v>1347</v>
@@ -29311,7 +29311,7 @@
         <v>14.25</v>
       </c>
       <c r="G998" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H998" t="n">
         <v>6924</v>
@@ -29369,7 +29369,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.4076118469238</v>
+        <v>13.4076128005981</v>
       </c>
       <c r="H1000" t="n">
         <v>10424</v>
@@ -29398,7 +29398,7 @@
         <v>14</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.5528221130371</v>
+        <v>13.5528211593628</v>
       </c>
       <c r="H1001" t="n">
         <v>4003</v>
@@ -29746,7 +29746,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1013" t="n">
-        <v>13.4076118469238</v>
+        <v>13.4076128005981</v>
       </c>
       <c r="H1013" t="n">
         <v>2388</v>
@@ -29891,7 +29891,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1018" t="n">
-        <v>12.8751802444458</v>
+        <v>12.8751792907715</v>
       </c>
       <c r="H1018" t="n">
         <v>722</v>
@@ -29949,7 +29949,7 @@
         <v>12.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.1007318496704</v>
+        <v>12.1007328033447</v>
       </c>
       <c r="H1020" t="n">
         <v>1200</v>
@@ -30065,7 +30065,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1024" t="n">
-        <v>12.2459411621094</v>
+        <v>12.2459421157837</v>
       </c>
       <c r="H1024" t="n">
         <v>352</v>
@@ -30094,7 +30094,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1025" t="n">
         <v>427</v>
@@ -30239,7 +30239,7 @@
         <v>14.5</v>
       </c>
       <c r="G1030" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H1030" t="n">
         <v>2981</v>
@@ -30268,7 +30268,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>14.3272686004639</v>
+        <v>14.3272676467896</v>
       </c>
       <c r="H1031" t="n">
         <v>1331</v>
@@ -30297,7 +30297,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1032" t="n">
-        <v>14.4724769592285</v>
+        <v>14.4724760055542</v>
       </c>
       <c r="H1032" t="n">
         <v>1379</v>
@@ -30326,7 +30326,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>14.7144908905029</v>
+        <v>14.7144918441772</v>
       </c>
       <c r="H1033" t="n">
         <v>1269</v>
@@ -30355,7 +30355,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>14.3756704330444</v>
+        <v>14.3756713867188</v>
       </c>
       <c r="H1034" t="n">
         <v>412</v>
@@ -30384,7 +30384,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.4724769592285</v>
+        <v>14.4724760055542</v>
       </c>
       <c r="H1035" t="n">
         <v>1610</v>
@@ -30442,7 +30442,7 @@
         <v>15</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.5208797454834</v>
+        <v>14.5208787918091</v>
       </c>
       <c r="H1037" t="n">
         <v>947</v>
@@ -30500,7 +30500,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H1039" t="n">
         <v>2364</v>
@@ -30558,7 +30558,7 @@
         <v>15</v>
       </c>
       <c r="G1041" t="n">
-        <v>14.5208797454834</v>
+        <v>14.5208787918091</v>
       </c>
       <c r="H1041" t="n">
         <v>73</v>
@@ -30587,7 +30587,7 @@
         <v>15</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.5208797454834</v>
+        <v>14.5208787918091</v>
       </c>
       <c r="H1042" t="n">
         <v>2826</v>
@@ -30645,7 +30645,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1044" t="n">
         <v>2945</v>
@@ -30703,7 +30703,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1046" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1046" t="n">
         <v>124</v>
@@ -30761,7 +30761,7 @@
         <v>14.5</v>
       </c>
       <c r="G1048" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H1048" t="n">
         <v>5163</v>
@@ -30790,7 +30790,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1049" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1049" t="n">
         <v>93</v>
@@ -30848,7 +30848,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1051" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1051" t="n">
         <v>322</v>
@@ -30964,7 +30964,7 @@
         <v>14.25</v>
       </c>
       <c r="G1055" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H1055" t="n">
         <v>4231</v>
@@ -31022,7 +31022,7 @@
         <v>14.25</v>
       </c>
       <c r="G1057" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H1057" t="n">
         <v>1684</v>
@@ -31341,7 +31341,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>12.2459411621094</v>
+        <v>12.2459421157837</v>
       </c>
       <c r="H1068" t="n">
         <v>4296</v>
@@ -31399,7 +31399,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1070" t="n">
-        <v>11.7135095596313</v>
+        <v>11.7135105133057</v>
       </c>
       <c r="H1070" t="n">
         <v>3678</v>
@@ -31428,7 +31428,7 @@
         <v>12.25</v>
       </c>
       <c r="G1071" t="n">
-        <v>11.8587188720703</v>
+        <v>11.8587198257446</v>
       </c>
       <c r="H1071" t="n">
         <v>1155</v>
@@ -31515,7 +31515,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1074" t="n">
-        <v>12.3911514282227</v>
+        <v>12.3911504745483</v>
       </c>
       <c r="H1074" t="n">
         <v>1447</v>
@@ -31631,7 +31631,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1078" t="n">
-        <v>12.5363607406616</v>
+        <v>12.536358833313</v>
       </c>
       <c r="H1078" t="n">
         <v>284</v>
@@ -31718,7 +31718,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1081" t="n">
-        <v>12.7299718856812</v>
+        <v>12.7299699783325</v>
       </c>
       <c r="H1081" t="n">
         <v>2529</v>
@@ -31747,7 +31747,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1082" t="n">
-        <v>12.7299718856812</v>
+        <v>12.7299699783325</v>
       </c>
       <c r="H1082" t="n">
         <v>959</v>
@@ -32066,7 +32066,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>12.5363607406616</v>
+        <v>12.536358833313</v>
       </c>
       <c r="H1093" t="n">
         <v>4420</v>
@@ -32095,7 +32095,7 @@
         <v>12.75</v>
       </c>
       <c r="G1094" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1094" t="n">
         <v>4305</v>
@@ -32124,7 +32124,7 @@
         <v>12.75</v>
       </c>
       <c r="G1095" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1095" t="n">
         <v>2455</v>
@@ -32153,7 +32153,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1096" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1096" t="n">
         <v>5161</v>
@@ -32182,7 +32182,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1097" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1097" t="n">
         <v>7158</v>
@@ -32211,7 +32211,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1098" t="n">
-        <v>12.3911514282227</v>
+        <v>12.3911504745483</v>
       </c>
       <c r="H1098" t="n">
         <v>9408</v>
@@ -32240,7 +32240,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>12.8751802444458</v>
+        <v>12.8751792907715</v>
       </c>
       <c r="H1099" t="n">
         <v>8687</v>
@@ -32269,7 +32269,7 @@
         <v>12.75</v>
       </c>
       <c r="G1100" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1100" t="n">
         <v>7191</v>
@@ -32298,7 +32298,7 @@
         <v>12.75</v>
       </c>
       <c r="G1101" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1101" t="n">
         <v>5464</v>
@@ -32327,7 +32327,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1102" t="n">
-        <v>12.5363607406616</v>
+        <v>12.536358833313</v>
       </c>
       <c r="H1102" t="n">
         <v>6218</v>
@@ -32385,7 +32385,7 @@
         <v>12.75</v>
       </c>
       <c r="G1104" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1104" t="n">
         <v>1561</v>
@@ -32414,7 +32414,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1105" t="n">
-        <v>12.2459411621094</v>
+        <v>12.2459421157837</v>
       </c>
       <c r="H1105" t="n">
         <v>7176</v>
@@ -32472,7 +32472,7 @@
         <v>12.75</v>
       </c>
       <c r="G1107" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1107" t="n">
         <v>3881</v>
@@ -32501,7 +32501,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1108" t="n">
-        <v>12.3911514282227</v>
+        <v>12.3911504745483</v>
       </c>
       <c r="H1108" t="n">
         <v>8024</v>
@@ -32617,7 +32617,7 @@
         <v>12.75</v>
       </c>
       <c r="G1112" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1112" t="n">
         <v>1131</v>
@@ -32646,7 +32646,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1113" t="n">
-        <v>12.3911514282227</v>
+        <v>12.3911504745483</v>
       </c>
       <c r="H1113" t="n">
         <v>2058</v>
@@ -32704,7 +32704,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1115" t="n">
-        <v>12.3911514282227</v>
+        <v>12.3911504745483</v>
       </c>
       <c r="H1115" t="n">
         <v>865</v>
@@ -32762,7 +32762,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1117" t="n">
-        <v>12.3911514282227</v>
+        <v>12.3911504745483</v>
       </c>
       <c r="H1117" t="n">
         <v>10356</v>
@@ -32791,7 +32791,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1118" t="n">
-        <v>12.5363607406616</v>
+        <v>12.536358833313</v>
       </c>
       <c r="H1118" t="n">
         <v>3355</v>
@@ -32820,7 +32820,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>12.5363607406616</v>
+        <v>12.536358833313</v>
       </c>
       <c r="H1119" t="n">
         <v>610</v>
@@ -32878,7 +32878,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1121" t="n">
-        <v>12.8751802444458</v>
+        <v>12.8751792907715</v>
       </c>
       <c r="H1121" t="n">
         <v>3291</v>
@@ -33081,7 +33081,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>13.21399974823</v>
+        <v>13.2140007019043</v>
       </c>
       <c r="H1128" t="n">
         <v>247</v>
@@ -33284,7 +33284,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1135" t="n">
-        <v>13.8432388305664</v>
+        <v>13.8432397842407</v>
       </c>
       <c r="H1135" t="n">
         <v>520</v>
@@ -33342,7 +33342,7 @@
         <v>14</v>
       </c>
       <c r="G1137" t="n">
-        <v>13.5528221130371</v>
+        <v>13.5528211593628</v>
       </c>
       <c r="H1137" t="n">
         <v>8177</v>
@@ -33400,7 +33400,7 @@
         <v>14.25</v>
       </c>
       <c r="G1139" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H1139" t="n">
         <v>15245</v>
@@ -33487,7 +33487,7 @@
         <v>14.25</v>
       </c>
       <c r="G1142" t="n">
-        <v>13.7948350906372</v>
+        <v>13.7948360443115</v>
       </c>
       <c r="H1142" t="n">
         <v>4226</v>
@@ -33545,7 +33545,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1144" t="n">
-        <v>13.8432388305664</v>
+        <v>13.8432397842407</v>
       </c>
       <c r="H1144" t="n">
         <v>14356</v>
@@ -33574,7 +33574,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1145" t="n">
-        <v>14.3272686004639</v>
+        <v>14.3272676467896</v>
       </c>
       <c r="H1145" t="n">
         <v>7054</v>
@@ -33632,7 +33632,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>14.8112964630127</v>
+        <v>14.811297416687</v>
       </c>
       <c r="H1147" t="n">
         <v>5496</v>
@@ -33690,7 +33690,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1149" t="n">
-        <v>14.1820592880249</v>
+        <v>14.1820583343506</v>
       </c>
       <c r="H1149" t="n">
         <v>807</v>
@@ -33719,7 +33719,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1150" t="n">
-        <v>14.1820592880249</v>
+        <v>14.1820583343506</v>
       </c>
       <c r="H1150" t="n">
         <v>9057</v>
@@ -33777,7 +33777,7 @@
         <v>14.5</v>
       </c>
       <c r="G1152" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H1152" t="n">
         <v>9610</v>
@@ -33806,7 +33806,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1153" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1153" t="n">
         <v>497</v>
@@ -33864,7 +33864,7 @@
         <v>14.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H1155" t="n">
         <v>40</v>
@@ -33951,7 +33951,7 @@
         <v>14.5</v>
       </c>
       <c r="G1158" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H1158" t="n">
         <v>8289</v>
@@ -33980,7 +33980,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1159" t="n">
-        <v>14.4724769592285</v>
+        <v>14.4724760055542</v>
       </c>
       <c r="H1159" t="n">
         <v>5202</v>
@@ -34009,7 +34009,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1160" t="n">
-        <v>14.3272686004639</v>
+        <v>14.3272676467896</v>
       </c>
       <c r="H1160" t="n">
         <v>671</v>
@@ -34038,7 +34038,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1161" t="n">
-        <v>14.1820592880249</v>
+        <v>14.1820583343506</v>
       </c>
       <c r="H1161" t="n">
         <v>1598</v>
@@ -34096,7 +34096,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>14.1336574554443</v>
+        <v>14.13365650177</v>
       </c>
       <c r="H1163" t="n">
         <v>3148</v>
@@ -34154,7 +34154,7 @@
         <v>14.5</v>
       </c>
       <c r="G1165" t="n">
-        <v>14.0368509292603</v>
+        <v>14.0368499755859</v>
       </c>
       <c r="H1165" t="n">
         <v>3614</v>
@@ -34212,7 +34212,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1167" t="n">
-        <v>13.8432388305664</v>
+        <v>13.8432397842407</v>
       </c>
       <c r="H1167" t="n">
         <v>8730</v>
@@ -34328,7 +34328,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1171" t="n">
-        <v>13.8432388305664</v>
+        <v>13.8432397842407</v>
       </c>
       <c r="H1171" t="n">
         <v>1112</v>
@@ -34386,7 +34386,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1173" t="n">
-        <v>13.4076118469238</v>
+        <v>13.4076128005981</v>
       </c>
       <c r="H1173" t="n">
         <v>3585</v>
@@ -34473,7 +34473,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1176" t="n">
-        <v>12.8751802444458</v>
+        <v>12.8751792907715</v>
       </c>
       <c r="H1176" t="n">
         <v>4234</v>
@@ -34589,7 +34589,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1180" t="n">
-        <v>12.8751802444458</v>
+        <v>12.8751792907715</v>
       </c>
       <c r="H1180" t="n">
         <v>657</v>
@@ -34647,7 +34647,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1182" t="n">
-        <v>12.9235830307007</v>
+        <v>12.923583984375</v>
       </c>
       <c r="H1182" t="n">
         <v>4712</v>
@@ -34821,7 +34821,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1188" t="n">
         <v>3537</v>
@@ -34879,7 +34879,7 @@
         <v>12.75</v>
       </c>
       <c r="G1190" t="n">
-        <v>12.3427486419678</v>
+        <v>12.3427476882935</v>
       </c>
       <c r="H1190" t="n">
         <v>2870</v>
@@ -34937,7 +34937,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1192" t="n">
-        <v>12.3911514282227</v>
+        <v>12.3911504745483</v>
       </c>
       <c r="H1192" t="n">
         <v>88</v>
@@ -34966,7 +34966,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1193" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1193" t="n">
         <v>2078</v>
@@ -35198,7 +35198,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.9235830307007</v>
+        <v>12.923583984375</v>
       </c>
       <c r="H1201" t="n">
         <v>2713</v>
@@ -35459,7 +35459,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.2459411621094</v>
+        <v>12.2459421157837</v>
       </c>
       <c r="H1210" t="n">
         <v>365</v>
@@ -35488,7 +35488,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1211" t="n">
         <v>361</v>
@@ -35517,7 +35517,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.4879570007324</v>
+        <v>12.4879560470581</v>
       </c>
       <c r="H1212" t="n">
         <v>46</v>
@@ -35720,7 +35720,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>12.7299718856812</v>
+        <v>12.7299699783325</v>
       </c>
       <c r="H1219" t="n">
         <v>347</v>
@@ -35778,7 +35778,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1221" t="n">
-        <v>12.3911514282227</v>
+        <v>12.3911504745483</v>
       </c>
       <c r="H1221" t="n">
         <v>5821</v>
@@ -35865,7 +35865,7 @@
         <v>12.75</v>
       </c>
       <c r="G1224" t="n">
-        <v>12.4106187820435</v>
+        <v>12.4106178283691</v>
       </c>
       <c r="H1224" t="n">
         <v>573</v>
@@ -35923,7 +35923,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1226" t="n">
-        <v>12.5566253662109</v>
+        <v>12.5566244125366</v>
       </c>
       <c r="H1226" t="n">
         <v>771</v>
@@ -35952,7 +35952,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1227" t="n">
-        <v>12.2646112442017</v>
+        <v>12.2646102905273</v>
       </c>
       <c r="H1227" t="n">
         <v>38</v>
@@ -36010,7 +36010,7 @@
         <v>12.5</v>
       </c>
       <c r="G1229" t="n">
-        <v>12.1672716140747</v>
+        <v>12.167272567749</v>
       </c>
       <c r="H1229" t="n">
         <v>5999</v>
@@ -36039,7 +36039,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>12.2646112442017</v>
+        <v>12.2646102905273</v>
       </c>
       <c r="H1230" t="n">
         <v>1890</v>
@@ -36097,7 +36097,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1232" t="n">
-        <v>11.9725961685181</v>
+        <v>11.9725971221924</v>
       </c>
       <c r="H1232" t="n">
         <v>2516</v>
@@ -36184,7 +36184,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1235" t="n">
-        <v>11.7779197692871</v>
+        <v>11.7779207229614</v>
       </c>
       <c r="H1235" t="n">
         <v>1218</v>
@@ -36213,7 +36213,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1236" t="n">
-        <v>11.7779197692871</v>
+        <v>11.7779207229614</v>
       </c>
       <c r="H1236" t="n">
         <v>600</v>
@@ -36242,7 +36242,7 @@
         <v>12</v>
       </c>
       <c r="G1237" t="n">
-        <v>11.6805810928345</v>
+        <v>11.6805820465088</v>
       </c>
       <c r="H1237" t="n">
         <v>1200</v>
@@ -36271,7 +36271,7 @@
         <v>12</v>
       </c>
       <c r="G1238" t="n">
-        <v>11.6805810928345</v>
+        <v>11.6805820465088</v>
       </c>
       <c r="H1238" t="n">
         <v>1207</v>
@@ -36329,7 +36329,7 @@
         <v>12</v>
       </c>
       <c r="G1240" t="n">
-        <v>11.6805810928345</v>
+        <v>11.6805820465088</v>
       </c>
       <c r="H1240" t="n">
         <v>69260</v>
@@ -36387,7 +36387,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1242" t="n">
-        <v>11.534574508667</v>
+        <v>11.5345754623413</v>
       </c>
       <c r="H1242" t="n">
         <v>105</v>
@@ -36416,7 +36416,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1243" t="n">
-        <v>11.4859046936035</v>
+        <v>11.4859056472778</v>
       </c>
       <c r="H1243" t="n">
         <v>63750</v>
@@ -36445,7 +36445,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1244" t="n">
-        <v>11.2425603866577</v>
+        <v>11.2425594329834</v>
       </c>
       <c r="H1244" t="n">
         <v>2233</v>
@@ -36474,7 +36474,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1245" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1245" t="n">
         <v>4356</v>
@@ -36503,7 +36503,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1246" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1246" t="n">
         <v>288</v>
@@ -36532,7 +36532,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1247" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1247" t="n">
         <v>2366</v>
@@ -36561,7 +36561,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1248" t="n">
-        <v>11.2425603866577</v>
+        <v>11.2425594329834</v>
       </c>
       <c r="H1248" t="n">
         <v>3045</v>
@@ -36590,7 +36590,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1249" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1249" t="n">
         <v>1944</v>
@@ -36619,7 +36619,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1250" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1250" t="n">
         <v>2377</v>
@@ -36648,7 +36648,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1251" t="n">
         <v>613</v>
@@ -36677,7 +36677,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1252" t="n">
         <v>535</v>
@@ -36706,7 +36706,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1253" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1253" t="n">
         <v>5895</v>
@@ -36735,7 +36735,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1254" t="n">
         <v>1702</v>
@@ -36764,7 +36764,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1255" t="n">
         <v>169</v>
@@ -36822,7 +36822,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1257" t="n">
-        <v>11.534574508667</v>
+        <v>11.5345754623413</v>
       </c>
       <c r="H1257" t="n">
         <v>862</v>
@@ -36851,7 +36851,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1258" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1258" t="n">
         <v>4413</v>
@@ -36880,7 +36880,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1259" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1259" t="n">
         <v>129</v>
@@ -36938,7 +36938,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1261" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1261" t="n">
         <v>562</v>
@@ -36996,7 +36996,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1263" t="n">
         <v>4199</v>
@@ -37083,7 +37083,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1266" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1266" t="n">
         <v>5610</v>
@@ -37286,7 +37286,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1273" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1273" t="n">
         <v>659</v>
@@ -37315,7 +37315,7 @@
         <v>11.5</v>
       </c>
       <c r="G1274" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1274" t="n">
         <v>3017</v>
@@ -37344,7 +37344,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1275" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1275" t="n">
         <v>753</v>
@@ -37373,7 +37373,7 @@
         <v>11.5</v>
       </c>
       <c r="G1276" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1276" t="n">
         <v>4176</v>
@@ -37576,7 +37576,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1283" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1283" t="n">
         <v>484</v>
@@ -37634,7 +37634,7 @@
         <v>11.5</v>
       </c>
       <c r="G1285" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1285" t="n">
         <v>625</v>
@@ -37663,7 +37663,7 @@
         <v>11.5</v>
       </c>
       <c r="G1286" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1286" t="n">
         <v>21790</v>
@@ -37692,7 +37692,7 @@
         <v>11.5</v>
       </c>
       <c r="G1287" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1287" t="n">
         <v>44</v>
@@ -37721,7 +37721,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1288" t="n">
         <v>290</v>
@@ -37837,7 +37837,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1292" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1292" t="n">
         <v>140</v>
@@ -37895,7 +37895,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1294" t="n">
-        <v>11.3398971557617</v>
+        <v>11.339898109436</v>
       </c>
       <c r="H1294" t="n">
         <v>589</v>
@@ -37953,7 +37953,7 @@
         <v>11.5</v>
       </c>
       <c r="G1296" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1296" t="n">
         <v>9</v>
@@ -38040,7 +38040,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1299" t="n">
         <v>540</v>
@@ -38069,7 +38069,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1300" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1300" t="n">
         <v>2317</v>
@@ -38098,7 +38098,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1301" t="n">
         <v>1305</v>
@@ -38185,7 +38185,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1304" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1304" t="n">
         <v>733</v>
@@ -38272,7 +38272,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1307" t="n">
-        <v>11.0478839874268</v>
+        <v>11.0478830337524</v>
       </c>
       <c r="H1307" t="n">
         <v>2938</v>
@@ -38301,7 +38301,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1308" t="n">
         <v>688</v>
@@ -38388,7 +38388,7 @@
         <v>11.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.1938915252686</v>
+        <v>11.1938905715942</v>
       </c>
       <c r="H1311" t="n">
         <v>588</v>
@@ -38417,7 +38417,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.2912292480469</v>
+        <v>11.2912302017212</v>
       </c>
       <c r="H1312" t="n">
         <v>14882</v>
@@ -38446,7 +38446,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1313" t="n">
-        <v>11.0478839874268</v>
+        <v>11.0478830337524</v>
       </c>
       <c r="H1313" t="n">
         <v>5406</v>
@@ -38620,7 +38620,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1319" t="n">
-        <v>11.0965528488159</v>
+        <v>11.0965518951416</v>
       </c>
       <c r="H1319" t="n">
         <v>1529</v>
@@ -38707,7 +38707,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1322" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1322" t="n">
         <v>6625</v>
@@ -38939,7 +38939,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1330" t="n">
-        <v>9.78248691558838</v>
+        <v>9.7824878692627</v>
       </c>
       <c r="H1330" t="n">
         <v>8085</v>
@@ -38968,7 +38968,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1331" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1331" t="n">
         <v>546</v>
@@ -39026,7 +39026,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1333" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1333" t="n">
         <v>10370</v>
@@ -39084,7 +39084,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1335" t="n">
-        <v>9.78248691558838</v>
+        <v>9.7824878692627</v>
       </c>
       <c r="H1335" t="n">
         <v>1732</v>
@@ -39113,7 +39113,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1336" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718397140503</v>
       </c>
       <c r="H1336" t="n">
         <v>174</v>
@@ -39142,7 +39142,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1337" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718397140503</v>
       </c>
       <c r="H1337" t="n">
         <v>1784</v>
@@ -39171,7 +39171,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1338" t="n">
-        <v>10.2691783905029</v>
+        <v>10.2691774368286</v>
       </c>
       <c r="H1338" t="n">
         <v>95</v>
@@ -39229,7 +39229,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1340" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1340" t="n">
         <v>2708</v>
@@ -39403,7 +39403,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1346" t="n">
-        <v>9.61701202392578</v>
+        <v>9.6170129776001</v>
       </c>
       <c r="H1346" t="n">
         <v>850</v>
@@ -39432,7 +39432,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1347" t="n">
-        <v>9.61701202392578</v>
+        <v>9.6170129776001</v>
       </c>
       <c r="H1347" t="n">
         <v>1209</v>
@@ -39519,7 +39519,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1350" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1350" t="n">
         <v>3050</v>
@@ -39548,7 +39548,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1351" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1351" t="n">
         <v>5171</v>
@@ -39635,7 +39635,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1354" t="n">
-        <v>9.61701202392578</v>
+        <v>9.6170129776001</v>
       </c>
       <c r="H1354" t="n">
         <v>1392</v>
@@ -39693,7 +39693,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1356" t="n">
-        <v>9.53914165496826</v>
+        <v>9.53914260864258</v>
       </c>
       <c r="H1356" t="n">
         <v>852</v>
@@ -39751,7 +39751,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1358" t="n">
-        <v>9.55860996246338</v>
+        <v>9.55860900878906</v>
       </c>
       <c r="H1358" t="n">
         <v>7909</v>
@@ -39780,7 +39780,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1359" t="n">
-        <v>9.53914165496826</v>
+        <v>9.53914260864258</v>
       </c>
       <c r="H1359" t="n">
         <v>6586</v>
@@ -39809,7 +39809,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1360" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1360" t="n">
         <v>9524</v>
@@ -39838,7 +39838,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1361" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1361" t="n">
         <v>604</v>
@@ -39925,7 +39925,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1364" t="n">
-        <v>9.44180393218994</v>
+        <v>9.44180297851562</v>
       </c>
       <c r="H1364" t="n">
         <v>426</v>
@@ -39954,7 +39954,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1365" t="n">
-        <v>9.40286827087402</v>
+        <v>9.40286731719971</v>
       </c>
       <c r="H1365" t="n">
         <v>2541</v>
@@ -40099,7 +40099,7 @@
         <v>9.5</v>
       </c>
       <c r="G1370" t="n">
-        <v>9.24712753295898</v>
+        <v>9.24712657928467</v>
       </c>
       <c r="H1370" t="n">
         <v>942</v>
@@ -40128,7 +40128,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1371" t="n">
-        <v>9.03298377990723</v>
+        <v>9.03298282623291</v>
       </c>
       <c r="H1371" t="n">
         <v>13499</v>
@@ -40157,7 +40157,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>9.53914165496826</v>
+        <v>9.53914260864258</v>
       </c>
       <c r="H1372" t="n">
         <v>30727</v>
@@ -40244,7 +40244,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1375" t="n">
-        <v>10.4151859283447</v>
+        <v>10.4151849746704</v>
       </c>
       <c r="H1375" t="n">
         <v>1865</v>
@@ -40273,7 +40273,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1376" t="n">
-        <v>10.6098623275757</v>
+        <v>10.6098613739014</v>
       </c>
       <c r="H1376" t="n">
         <v>23886</v>
@@ -40331,7 +40331,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1378" t="n">
-        <v>10.6098623275757</v>
+        <v>10.6098613739014</v>
       </c>
       <c r="H1378" t="n">
         <v>4680</v>
@@ -40360,7 +40360,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1379" t="n">
-        <v>10.901876449585</v>
+        <v>10.9018754959106</v>
       </c>
       <c r="H1379" t="n">
         <v>1160</v>
@@ -40563,7 +40563,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1386" t="n">
-        <v>10.6098623275757</v>
+        <v>10.6098613739014</v>
       </c>
       <c r="H1386" t="n">
         <v>741</v>
@@ -40679,7 +40679,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1390" t="n">
-        <v>10.3665151596069</v>
+        <v>10.3665161132812</v>
       </c>
       <c r="H1390" t="n">
         <v>3426</v>
@@ -41433,7 +41433,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>10.3665151596069</v>
+        <v>10.3665161132812</v>
       </c>
       <c r="H1416" t="n">
         <v>1588</v>
@@ -41549,7 +41549,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1420" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1420" t="n">
         <v>3673</v>
@@ -41607,7 +41607,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1422" t="n">
-        <v>10.3665151596069</v>
+        <v>10.3665161132812</v>
       </c>
       <c r="H1422" t="n">
         <v>1545</v>
@@ -41665,7 +41665,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1424" t="n">
-        <v>10.3665151596069</v>
+        <v>10.3665161132812</v>
       </c>
       <c r="H1424" t="n">
         <v>117</v>
@@ -41723,7 +41723,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1426" t="n">
-        <v>9.78248691558838</v>
+        <v>9.7824878692627</v>
       </c>
       <c r="H1426" t="n">
         <v>5097</v>
@@ -41752,7 +41752,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1427" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1427" t="n">
         <v>1270</v>
@@ -41781,7 +41781,7 @@
         <v>10.25</v>
       </c>
       <c r="G1428" t="n">
-        <v>9.97716331481934</v>
+        <v>9.97716426849365</v>
       </c>
       <c r="H1428" t="n">
         <v>1017</v>
@@ -41810,7 +41810,7 @@
         <v>10.25</v>
       </c>
       <c r="G1429" t="n">
-        <v>9.97716331481934</v>
+        <v>9.97716426849365</v>
       </c>
       <c r="H1429" t="n">
         <v>483</v>
@@ -41839,7 +41839,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1430" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1430" t="n">
         <v>262</v>
@@ -41868,7 +41868,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1431" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1431" t="n">
         <v>8388</v>
@@ -41897,7 +41897,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1432" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718397140503</v>
       </c>
       <c r="H1432" t="n">
         <v>1224</v>
@@ -41926,7 +41926,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1433" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718397140503</v>
       </c>
       <c r="H1433" t="n">
         <v>900</v>
@@ -41955,7 +41955,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1434" t="n">
         <v>6081</v>
@@ -41984,7 +41984,7 @@
         <v>10.25</v>
       </c>
       <c r="G1435" t="n">
-        <v>9.97716331481934</v>
+        <v>9.97716426849365</v>
       </c>
       <c r="H1435" t="n">
         <v>1234</v>
@@ -42071,7 +42071,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1438" t="n">
-        <v>9.36393356323242</v>
+        <v>9.36393260955811</v>
       </c>
       <c r="H1438" t="n">
         <v>6276</v>
@@ -42100,7 +42100,7 @@
         <v>9.5</v>
       </c>
       <c r="G1439" t="n">
-        <v>9.24712753295898</v>
+        <v>9.24712657928467</v>
       </c>
       <c r="H1439" t="n">
         <v>2619</v>
@@ -42129,7 +42129,7 @@
         <v>9.5</v>
       </c>
       <c r="G1440" t="n">
-        <v>9.24712753295898</v>
+        <v>9.24712657928467</v>
       </c>
       <c r="H1440" t="n">
         <v>389</v>
@@ -42187,7 +42187,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1442" t="n">
-        <v>9.38340091705322</v>
+        <v>9.38339996337891</v>
       </c>
       <c r="H1442" t="n">
         <v>5310</v>
@@ -42274,7 +42274,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1445" t="n">
-        <v>9.83115577697754</v>
+        <v>9.83115673065186</v>
       </c>
       <c r="H1445" t="n">
         <v>21848</v>
@@ -42332,7 +42332,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1447" t="n">
-        <v>9.61701202392578</v>
+        <v>9.6170129776001</v>
       </c>
       <c r="H1447" t="n">
         <v>9116</v>
@@ -42390,7 +42390,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1449" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1449" t="n">
         <v>1767</v>
@@ -42419,7 +42419,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1450" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1450" t="n">
         <v>2538</v>
@@ -42448,7 +42448,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1451" t="n">
-        <v>10.171838760376</v>
+        <v>10.1718397140503</v>
       </c>
       <c r="H1451" t="n">
         <v>2025</v>
@@ -42535,7 +42535,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1454" t="n">
-        <v>10.0258321762085</v>
+        <v>10.0258331298828</v>
       </c>
       <c r="H1454" t="n">
         <v>392</v>
@@ -42622,7 +42622,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1457" t="n">
-        <v>9.61701202392578</v>
+        <v>9.6170129776001</v>
       </c>
       <c r="H1457" t="n">
         <v>4060</v>
@@ -42651,7 +42651,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1458" t="n">
-        <v>9.61701202392578</v>
+        <v>9.6170129776001</v>
       </c>
       <c r="H1458" t="n">
         <v>2849</v>
@@ -42680,7 +42680,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1459" t="n">
-        <v>9.55860996246338</v>
+        <v>9.55860900878906</v>
       </c>
       <c r="H1459" t="n">
         <v>2192</v>
@@ -42738,7 +42738,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1461" t="n">
-        <v>9.22765922546387</v>
+        <v>9.22765827178955</v>
       </c>
       <c r="H1461" t="n">
         <v>8053</v>
@@ -42767,7 +42767,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1462" t="n">
-        <v>9.55860996246338</v>
+        <v>9.55860900878906</v>
       </c>
       <c r="H1462" t="n">
         <v>3541</v>
@@ -42796,7 +42796,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1463" t="n">
-        <v>9.53914165496826</v>
+        <v>9.53914260864258</v>
       </c>
       <c r="H1463" t="n">
         <v>15014</v>
@@ -43144,7 +43144,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1475" t="n">
-        <v>9.48539447784424</v>
+        <v>9.48539352416992</v>
       </c>
       <c r="H1475" t="n">
         <v>2617</v>
@@ -43173,7 +43173,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1476" t="n">
-        <v>9.60346984863281</v>
+        <v>9.6034688949585</v>
       </c>
       <c r="H1476" t="n">
         <v>1845</v>
@@ -43376,7 +43376,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1483" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1483" t="n">
         <v>5070</v>
@@ -43492,7 +43492,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1487" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1487" t="n">
         <v>2088</v>
@@ -43550,7 +43550,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1489" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1489" t="n">
         <v>2036</v>
@@ -43579,7 +43579,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1490" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1490" t="n">
         <v>1424</v>
@@ -43608,7 +43608,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1491" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1491" t="n">
         <v>934</v>
@@ -43782,7 +43782,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1497" t="n">
-        <v>9.6428279876709</v>
+        <v>9.64282894134521</v>
       </c>
       <c r="H1497" t="n">
         <v>3285</v>
@@ -43811,7 +43811,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1498" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1498" t="n">
         <v>5790</v>
@@ -43840,7 +43840,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G1499" t="n">
-        <v>9.70186519622803</v>
+        <v>9.70186614990234</v>
       </c>
       <c r="H1499" t="n">
         <v>602</v>
@@ -43869,7 +43869,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1500" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1500" t="n">
         <v>357</v>
@@ -43898,7 +43898,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1501" t="n">
-        <v>9.6428279876709</v>
+        <v>9.64282894134521</v>
       </c>
       <c r="H1501" t="n">
         <v>2832</v>
@@ -43985,7 +43985,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1504" t="n">
-        <v>9.56411170959473</v>
+        <v>9.56411075592041</v>
       </c>
       <c r="H1504" t="n">
         <v>3685</v>
@@ -44014,7 +44014,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1505" t="n">
-        <v>9.66250610351562</v>
+        <v>9.66250705718994</v>
       </c>
       <c r="H1505" t="n">
         <v>1013</v>
@@ -44043,7 +44043,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1506" t="n">
-        <v>9.54443168640137</v>
+        <v>9.54443073272705</v>
       </c>
       <c r="H1506" t="n">
         <v>1877</v>
@@ -44072,7 +44072,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G1507" t="n">
-        <v>9.66250610351562</v>
+        <v>9.66250705718994</v>
       </c>
       <c r="H1507" t="n">
         <v>50791</v>
@@ -44304,7 +44304,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1515" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1515" t="n">
         <v>10583</v>
@@ -44623,7 +44623,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1526" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1526" t="n">
         <v>2144</v>
@@ -44681,7 +44681,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1528" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1528" t="n">
         <v>3063</v>
@@ -44768,7 +44768,7 @@
         <v>10.25</v>
       </c>
       <c r="G1531" t="n">
-        <v>10.0856103897095</v>
+        <v>10.0856113433838</v>
       </c>
       <c r="H1531" t="n">
         <v>636</v>
@@ -45058,7 +45058,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1541" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1541" t="n">
         <v>227</v>
@@ -45174,7 +45174,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1545" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1545" t="n">
         <v>232</v>
@@ -45203,7 +45203,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1546" t="n">
-        <v>9.6428279876709</v>
+        <v>9.64282894134521</v>
       </c>
       <c r="H1546" t="n">
         <v>2868</v>
@@ -45232,7 +45232,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1547" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1547" t="n">
         <v>400</v>
@@ -45464,7 +45464,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1555" t="n">
-        <v>9.76090335845947</v>
+        <v>9.76090431213379</v>
       </c>
       <c r="H1555" t="n">
         <v>323</v>
@@ -45667,7 +45667,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1562" t="n">
-        <v>9.6428279876709</v>
+        <v>9.64282894134521</v>
       </c>
       <c r="H1562" t="n">
         <v>1757</v>
@@ -45696,7 +45696,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1563" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1563" t="n">
         <v>135</v>
@@ -45928,7 +45928,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1571" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1571" t="n">
         <v>2980</v>
@@ -45957,7 +45957,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1572" t="n">
-        <v>10.3808002471924</v>
+        <v>10.3807992935181</v>
       </c>
       <c r="H1572" t="n">
         <v>1240</v>
@@ -46015,7 +46015,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1574" t="n">
         <v>1210</v>
@@ -46044,7 +46044,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1575" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1575" t="n">
         <v>4872</v>
@@ -46073,7 +46073,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1576" t="n">
-        <v>11.1187715530396</v>
+        <v>11.1187705993652</v>
       </c>
       <c r="H1576" t="n">
         <v>12413</v>
@@ -46247,7 +46247,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1582" t="n">
-        <v>11.1679697036743</v>
+        <v>11.16796875</v>
       </c>
       <c r="H1582" t="n">
         <v>3025</v>
@@ -46305,7 +46305,7 @@
         <v>11.5</v>
       </c>
       <c r="G1584" t="n">
-        <v>11.3155641555786</v>
+        <v>11.3155632019043</v>
       </c>
       <c r="H1584" t="n">
         <v>11365</v>
@@ -46334,7 +46334,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1585" t="n">
-        <v>11.512354850769</v>
+        <v>11.5123558044434</v>
       </c>
       <c r="H1585" t="n">
         <v>11195</v>
@@ -46508,7 +46508,7 @@
         <v>13</v>
       </c>
       <c r="G1591" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1591" t="n">
         <v>14387</v>
@@ -46537,7 +46537,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1592" t="n">
-        <v>12.49631690979</v>
+        <v>12.4963178634644</v>
       </c>
       <c r="H1592" t="n">
         <v>10300</v>
@@ -46595,7 +46595,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1594" t="n">
-        <v>12.8407049179077</v>
+        <v>12.8407039642334</v>
       </c>
       <c r="H1594" t="n">
         <v>7943</v>
@@ -46624,7 +46624,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1595" t="n">
-        <v>12.8407049179077</v>
+        <v>12.8407039642334</v>
       </c>
       <c r="H1595" t="n">
         <v>5751</v>
@@ -46653,7 +46653,7 @@
         <v>13</v>
       </c>
       <c r="G1596" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1596" t="n">
         <v>9007</v>
@@ -46972,7 +46972,7 @@
         <v>13</v>
       </c>
       <c r="G1607" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1607" t="n">
         <v>45489</v>
@@ -47030,7 +47030,7 @@
         <v>13.5</v>
       </c>
       <c r="G1609" t="n">
-        <v>13.2834873199463</v>
+        <v>13.2834882736206</v>
       </c>
       <c r="H1609" t="n">
         <v>39949</v>
@@ -47088,7 +47088,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1611" t="n">
-        <v>12.8407049179077</v>
+        <v>12.8407039642334</v>
       </c>
       <c r="H1611" t="n">
         <v>13940</v>
@@ -47117,7 +47117,7 @@
         <v>13</v>
       </c>
       <c r="G1612" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1612" t="n">
         <v>1327</v>
@@ -47146,7 +47146,7 @@
         <v>13</v>
       </c>
       <c r="G1613" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1613" t="n">
         <v>20557</v>
@@ -47175,7 +47175,7 @@
         <v>13</v>
       </c>
       <c r="G1614" t="n">
-        <v>12.7915067672729</v>
+        <v>12.7915058135986</v>
       </c>
       <c r="H1614" t="n">
         <v>15556</v>
@@ -47204,7 +47204,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1615" t="n">
-        <v>12.7423086166382</v>
+        <v>12.7423076629639</v>
       </c>
       <c r="H1615" t="n">
         <v>3096</v>
@@ -47233,7 +47233,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1616" t="n">
-        <v>12.49631690979</v>
+        <v>12.4963178634644</v>
       </c>
       <c r="H1616" t="n">
         <v>3076</v>
@@ -47378,7 +47378,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>11.3647623062134</v>
+        <v>11.3647613525391</v>
       </c>
       <c r="H1621" t="n">
         <v>6291</v>
@@ -47494,7 +47494,7 @@
         <v>12.25</v>
       </c>
       <c r="G1625" t="n">
-        <v>12.0535345077515</v>
+        <v>12.0535354614258</v>
       </c>
       <c r="H1625" t="n">
         <v>4284</v>
@@ -47813,7 +47813,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1636" t="n">
-        <v>11.1187715530396</v>
+        <v>11.1187705993652</v>
       </c>
       <c r="H1636" t="n">
         <v>507</v>
@@ -47871,7 +47871,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1638" t="n">
-        <v>11.1187715530396</v>
+        <v>11.1187705993652</v>
       </c>
       <c r="H1638" t="n">
         <v>4347</v>
@@ -47900,7 +47900,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1639" t="n">
-        <v>10.7743844985962</v>
+        <v>10.7743835449219</v>
       </c>
       <c r="H1639" t="n">
         <v>8536</v>
@@ -48103,7 +48103,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1646" t="n">
-        <v>10.7251863479614</v>
+        <v>10.7251853942871</v>
       </c>
       <c r="H1646" t="n">
         <v>9044</v>
@@ -48132,7 +48132,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1647" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1647" t="n">
         <v>3122</v>
@@ -48161,7 +48161,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1648" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1648" t="n">
         <v>5642</v>
@@ -48219,7 +48219,7 @@
         <v>10.5</v>
       </c>
       <c r="G1650" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1650" t="n">
         <v>56910</v>
@@ -48248,7 +48248,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1651" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1651" t="n">
         <v>2497</v>
@@ -48277,7 +48277,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1652" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1652" t="n">
         <v>10295</v>
@@ -48306,7 +48306,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1653" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1653" t="n">
         <v>9615</v>
@@ -48364,7 +48364,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1655" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1655" t="n">
         <v>1424</v>
@@ -48393,7 +48393,7 @@
         <v>10.5</v>
       </c>
       <c r="G1656" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1656" t="n">
         <v>6026</v>
@@ -48451,7 +48451,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1658" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1658" t="n">
         <v>5157</v>
@@ -48480,7 +48480,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1659" t="n">
-        <v>10.3808002471924</v>
+        <v>10.3807992935181</v>
       </c>
       <c r="H1659" t="n">
         <v>3675</v>
@@ -48509,7 +48509,7 @@
         <v>10.5</v>
       </c>
       <c r="G1660" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1660" t="n">
         <v>2242</v>
@@ -48538,7 +48538,7 @@
         <v>10.5</v>
       </c>
       <c r="G1661" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1661" t="n">
         <v>2158</v>
@@ -48567,7 +48567,7 @@
         <v>10.5</v>
       </c>
       <c r="G1662" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1662" t="n">
         <v>1216</v>
@@ -48683,7 +48683,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1666" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1666" t="n">
         <v>4693</v>
@@ -48741,7 +48741,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1668" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1668" t="n">
         <v>8608</v>
@@ -48828,7 +48828,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1671" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1671" t="n">
         <v>3688</v>
@@ -48915,7 +48915,7 @@
         <v>10.5</v>
       </c>
       <c r="G1674" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1674" t="n">
         <v>1380</v>
@@ -48973,7 +48973,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1676" t="n">
-        <v>10.4299974441528</v>
+        <v>10.4299983978271</v>
       </c>
       <c r="H1676" t="n">
         <v>6725</v>
@@ -49060,7 +49060,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1679" t="n">
-        <v>10.3808002471924</v>
+        <v>10.3807992935181</v>
       </c>
       <c r="H1679" t="n">
         <v>3353</v>
@@ -49321,7 +49321,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1688" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1688" t="n">
         <v>2743</v>
@@ -49408,7 +49408,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1691" t="n">
-        <v>10.7251863479614</v>
+        <v>10.7251853942871</v>
       </c>
       <c r="H1691" t="n">
         <v>1253</v>
@@ -49611,7 +49611,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1698" t="n">
-        <v>10.7251863479614</v>
+        <v>10.7251853942871</v>
       </c>
       <c r="H1698" t="n">
         <v>206</v>
@@ -49814,7 +49814,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1705" t="n">
-        <v>10.4791946411133</v>
+        <v>10.4791955947876</v>
       </c>
       <c r="H1705" t="n">
         <v>2007</v>
@@ -49843,7 +49843,7 @@
         <v>10.5</v>
       </c>
       <c r="G1706" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1706" t="n">
         <v>2121</v>
@@ -49872,7 +49872,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1707" t="n">
-        <v>10.3808002471924</v>
+        <v>10.3807992935181</v>
       </c>
       <c r="H1707" t="n">
         <v>2077</v>
@@ -49930,7 +49930,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1709" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1709" t="n">
         <v>1483</v>
@@ -50017,7 +50017,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1712" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1712" t="n">
         <v>1833</v>
@@ -50075,7 +50075,7 @@
         <v>10.5</v>
       </c>
       <c r="G1714" t="n">
-        <v>10.3316020965576</v>
+        <v>10.3316011428833</v>
       </c>
       <c r="H1714" t="n">
         <v>56</v>
@@ -50191,7 +50191,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1718" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1718" t="n">
         <v>3461</v>
@@ -50365,7 +50365,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1724" t="n">
-        <v>9.72154426574707</v>
+        <v>9.72154521942139</v>
       </c>
       <c r="H1724" t="n">
         <v>4639</v>
@@ -50481,7 +50481,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1728" t="n">
-        <v>10.0364122390747</v>
+        <v>10.036413192749</v>
       </c>
       <c r="H1728" t="n">
         <v>6196</v>
@@ -61231,7 +61231,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="D2099" t="n">
-        <v>8.68000030517578</v>
+        <v>8.77999973297119</v>
       </c>
       <c r="E2099" t="n">
         <v>8.68000030517578</v>
@@ -61246,6 +61246,35 @@
         <v>290</v>
       </c>
       <c r="I2099" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2100" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2100" t="n">
+        <v>8.76000022888184</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>8.76000022888184</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>8.65999984741211</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>8.69999980926514</v>
+      </c>
+      <c r="G2100" t="n">
+        <v>8.69999980926514</v>
+      </c>
+      <c r="H2100" t="n">
+        <v>3160</v>
+      </c>
+      <c r="I2100" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.87050008773804</v>
       </c>
       <c r="G3" t="n">
-        <v>2.73570656776428</v>
+        <v>2.7357063293457</v>
       </c>
       <c r="H3" t="n">
         <v>364500</v>
@@ -485,7 +485,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G4" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H4" t="n">
         <v>233500</v>
@@ -514,7 +514,7 @@
         <v>2.91050004959106</v>
       </c>
       <c r="G5" t="n">
-        <v>2.77382826805115</v>
+        <v>2.77382779121399</v>
       </c>
       <c r="H5" t="n">
         <v>88500</v>
@@ -572,7 +572,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G7" t="n">
-        <v>2.80670833587646</v>
+        <v>2.80670785903931</v>
       </c>
       <c r="H7" t="n">
         <v>71500</v>
@@ -601,7 +601,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84006428718567</v>
+        <v>2.84006404876709</v>
       </c>
       <c r="H8" t="n">
         <v>25000</v>
@@ -630,7 +630,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.85912537574768</v>
+        <v>2.85912561416626</v>
       </c>
       <c r="H9" t="n">
         <v>26000</v>
@@ -717,7 +717,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G12" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H12" t="n">
         <v>7500</v>
@@ -775,7 +775,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G14" t="n">
-        <v>2.76572728157043</v>
+        <v>2.76572680473328</v>
       </c>
       <c r="H14" t="n">
         <v>5500</v>
@@ -804,7 +804,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.85912537574768</v>
+        <v>2.85912561416626</v>
       </c>
       <c r="H15" t="n">
         <v>22500</v>
@@ -978,7 +978,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H21" t="n">
         <v>6000</v>
@@ -1065,7 +1065,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G24" t="n">
-        <v>2.70663857460022</v>
+        <v>2.70663833618164</v>
       </c>
       <c r="H24" t="n">
         <v>9500</v>
@@ -1094,7 +1094,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.70663857460022</v>
+        <v>2.70663833618164</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G26" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H26" t="n">
         <v>3000</v>
@@ -1152,7 +1152,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H27" t="n">
         <v>5500</v>
@@ -1181,7 +1181,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.71616888046265</v>
+        <v>2.71616911888123</v>
       </c>
       <c r="H28" t="n">
         <v>3500</v>
@@ -1210,7 +1210,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G29" t="n">
-        <v>2.6189591884613</v>
+        <v>2.61895871162415</v>
       </c>
       <c r="H29" t="n">
         <v>14500</v>
@@ -1239,7 +1239,7 @@
         <v>2.75</v>
       </c>
       <c r="G30" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086486816406</v>
       </c>
       <c r="H30" t="n">
         <v>6500</v>
@@ -1268,7 +1268,7 @@
         <v>2.75</v>
       </c>
       <c r="G31" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086486816406</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>2.75</v>
       </c>
       <c r="G32" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086486816406</v>
       </c>
       <c r="H32" t="n">
         <v>1500</v>
@@ -1326,7 +1326,7 @@
         <v>2.75</v>
       </c>
       <c r="G33" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086486816406</v>
       </c>
       <c r="H33" t="n">
         <v>1500</v>
@@ -1355,7 +1355,7 @@
         <v>2.75</v>
       </c>
       <c r="G34" t="n">
-        <v>2.62086462974548</v>
+        <v>2.62086486816406</v>
       </c>
       <c r="H34" t="n">
         <v>3500</v>
@@ -1384,7 +1384,7 @@
         <v>2.80399990081787</v>
       </c>
       <c r="G35" t="n">
-        <v>2.67232918739319</v>
+        <v>2.67232894897461</v>
       </c>
       <c r="H35" t="n">
         <v>5500</v>
@@ -1442,7 +1442,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>2.78288221359253</v>
+        <v>2.78288173675537</v>
       </c>
       <c r="H37" t="n">
         <v>23500</v>
@@ -1471,7 +1471,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G38" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H38" t="n">
         <v>17000</v>
@@ -1500,7 +1500,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H39" t="n">
         <v>21500</v>
@@ -1529,7 +1529,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H40" t="n">
         <v>20000</v>
@@ -1558,7 +1558,7 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>2.85912537574768</v>
+        <v>2.85912561416626</v>
       </c>
       <c r="H41" t="n">
         <v>18500</v>
@@ -1587,7 +1587,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G42" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H42" t="n">
         <v>5500</v>
@@ -1616,7 +1616,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G43" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H43" t="n">
         <v>1000</v>
@@ -1645,7 +1645,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G44" t="n">
-        <v>2.79241251945496</v>
+        <v>2.79241228103638</v>
       </c>
       <c r="H44" t="n">
         <v>1500</v>
@@ -1674,7 +1674,7 @@
         <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>2.85912537574768</v>
+        <v>2.85912561416626</v>
       </c>
       <c r="H45" t="n">
         <v>18000</v>
@@ -1703,7 +1703,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H46" t="n">
         <v>12000</v>
@@ -1732,7 +1732,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87818598747253</v>
+        <v>2.87818646430969</v>
       </c>
       <c r="H47" t="n">
         <v>9000</v>
@@ -1790,7 +1790,7 @@
         <v>3.05550003051758</v>
       </c>
       <c r="G49" t="n">
-        <v>2.91201877593994</v>
+        <v>2.91201901435852</v>
       </c>
       <c r="H49" t="n">
         <v>6500</v>
@@ -1819,7 +1819,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H50" t="n">
         <v>13000</v>
@@ -1877,7 +1877,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01161193847656</v>
+        <v>3.01161217689514</v>
       </c>
       <c r="H52" t="n">
         <v>15500</v>
@@ -1993,7 +1993,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>2.91630744934082</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H56" t="n">
         <v>16000</v>
@@ -2022,7 +2022,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H57" t="n">
         <v>2000</v>
@@ -2051,7 +2051,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G58" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H58" t="n">
         <v>9500</v>
@@ -2080,7 +2080,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>2.9734902381897</v>
+        <v>2.97348999977112</v>
       </c>
       <c r="H59" t="n">
         <v>7500</v>
@@ -2109,7 +2109,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G60" t="n">
-        <v>2.9734902381897</v>
+        <v>2.97348999977112</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2138,7 +2138,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H61" t="n">
         <v>1000</v>
@@ -2167,7 +2167,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H62" t="n">
         <v>3000</v>
@@ -2196,7 +2196,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G63" t="n">
-        <v>2.88771677017212</v>
+        <v>2.88771629333496</v>
       </c>
       <c r="H63" t="n">
         <v>500</v>
@@ -2225,7 +2225,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H64" t="n">
         <v>2500</v>
@@ -2254,7 +2254,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>2.87818598747253</v>
+        <v>2.87818646430969</v>
       </c>
       <c r="H65" t="n">
         <v>4000</v>
@@ -2283,7 +2283,7 @@
         <v>2.97300004959106</v>
       </c>
       <c r="G66" t="n">
-        <v>2.83339285850525</v>
+        <v>2.83339309692383</v>
       </c>
       <c r="H66" t="n">
         <v>6000</v>
@@ -2312,7 +2312,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G67" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H67" t="n">
         <v>5000</v>
@@ -2341,7 +2341,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H68" t="n">
         <v>18500</v>
@@ -2370,7 +2370,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G69" t="n">
-        <v>2.84482979774475</v>
+        <v>2.84482955932617</v>
       </c>
       <c r="H69" t="n">
         <v>1500</v>
@@ -2399,7 +2399,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H70" t="n">
         <v>7500</v>
@@ -2428,7 +2428,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80670833587646</v>
+        <v>2.80670785903931</v>
       </c>
       <c r="H71" t="n">
         <v>8000</v>
@@ -2457,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>2.85912537574768</v>
+        <v>2.85912561416626</v>
       </c>
       <c r="H72" t="n">
         <v>7500</v>
@@ -2486,7 +2486,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>2.82100367546082</v>
+        <v>2.82100343704224</v>
       </c>
       <c r="H73" t="n">
         <v>6000</v>
@@ -2515,7 +2515,7 @@
         <v>3</v>
       </c>
       <c r="G74" t="n">
-        <v>2.85912537574768</v>
+        <v>2.85912561416626</v>
       </c>
       <c r="H74" t="n">
         <v>3000</v>
@@ -2544,7 +2544,7 @@
         <v>3</v>
       </c>
       <c r="G75" t="n">
-        <v>2.85912537574768</v>
+        <v>2.85912561416626</v>
       </c>
       <c r="H75" t="n">
         <v>3000</v>
@@ -2573,7 +2573,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G76" t="n">
-        <v>2.78288221359253</v>
+        <v>2.78288173675537</v>
       </c>
       <c r="H76" t="n">
         <v>4000</v>
@@ -2631,7 +2631,7 @@
         <v>2.89100003242493</v>
       </c>
       <c r="G78" t="n">
-        <v>2.75524353981018</v>
+        <v>2.75524401664734</v>
       </c>
       <c r="H78" t="n">
         <v>23000</v>
@@ -2689,7 +2689,7 @@
         <v>2.90549993515015</v>
       </c>
       <c r="G80" t="n">
-        <v>2.76906275749207</v>
+        <v>2.76906299591064</v>
       </c>
       <c r="H80" t="n">
         <v>4500</v>
@@ -2718,7 +2718,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H81" t="n">
         <v>3000</v>
@@ -2776,7 +2776,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G83" t="n">
-        <v>2.88771677017212</v>
+        <v>2.88771629333496</v>
       </c>
       <c r="H83" t="n">
         <v>28000</v>
@@ -2805,7 +2805,7 @@
         <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>2.85912537574768</v>
+        <v>2.85912561416626</v>
       </c>
       <c r="H84" t="n">
         <v>12500</v>
@@ -2834,7 +2834,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G85" t="n">
-        <v>2.92202568054199</v>
+        <v>2.92202591896057</v>
       </c>
       <c r="H85" t="n">
         <v>1500</v>
@@ -2863,7 +2863,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>2.91630744934082</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H86" t="n">
         <v>3000</v>
@@ -2921,7 +2921,7 @@
         <v>3.04900002479553</v>
       </c>
       <c r="G88" t="n">
-        <v>2.90582466125488</v>
+        <v>2.9058244228363</v>
       </c>
       <c r="H88" t="n">
         <v>2500</v>
@@ -2950,7 +2950,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G89" t="n">
-        <v>2.85054755210876</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H89" t="n">
         <v>3000</v>
@@ -2979,7 +2979,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G90" t="n">
-        <v>2.85054755210876</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H90" t="n">
         <v>4500</v>
@@ -3008,7 +3008,7 @@
         <v>2.9909999370575</v>
       </c>
       <c r="G91" t="n">
-        <v>2.85054755210876</v>
+        <v>2.85054802894592</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>2.93050003051758</v>
       </c>
       <c r="G92" t="n">
-        <v>2.79288911819458</v>
+        <v>2.792888879776</v>
       </c>
       <c r="H92" t="n">
         <v>500</v>
@@ -3066,7 +3066,7 @@
         <v>2.90899991989136</v>
       </c>
       <c r="G93" t="n">
-        <v>2.7723982334137</v>
+        <v>2.77239871025085</v>
       </c>
       <c r="H93" t="n">
         <v>52000</v>
@@ -3095,7 +3095,7 @@
         <v>2.90899991989136</v>
       </c>
       <c r="G94" t="n">
-        <v>2.7723982334137</v>
+        <v>2.77239871025085</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G96" t="n">
-        <v>2.82100367546082</v>
+        <v>2.82100343704224</v>
       </c>
       <c r="H96" t="n">
         <v>1000</v>
@@ -3443,7 +3443,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.82100367546082</v>
+        <v>2.82100343704224</v>
       </c>
       <c r="H106" t="n">
         <v>2000</v>
@@ -3501,7 +3501,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.82100367546082</v>
+        <v>2.82100343704224</v>
       </c>
       <c r="H108" t="n">
         <v>10000</v>
@@ -3530,7 +3530,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G109" t="n">
-        <v>2.72045803070068</v>
+        <v>2.72045755386353</v>
       </c>
       <c r="H109" t="n">
         <v>6500</v>
@@ -3559,7 +3559,7 @@
         <v>2.85450005531311</v>
       </c>
       <c r="G110" t="n">
-        <v>2.72045803070068</v>
+        <v>2.72045755386353</v>
       </c>
       <c r="H110" t="n">
         <v>12500</v>
@@ -3588,7 +3588,7 @@
         <v>2.91700005531311</v>
       </c>
       <c r="G111" t="n">
-        <v>2.78002285957336</v>
+        <v>2.78002309799194</v>
       </c>
       <c r="H111" t="n">
         <v>16500</v>
@@ -3617,7 +3617,7 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>2.85912537574768</v>
+        <v>2.85912561416626</v>
       </c>
       <c r="H112" t="n">
         <v>8000</v>
@@ -3704,7 +3704,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G115" t="n">
-        <v>2.95442914962769</v>
+        <v>2.95442938804626</v>
       </c>
       <c r="H115" t="n">
         <v>500</v>
@@ -3733,7 +3733,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G116" t="n">
-        <v>2.84959483146667</v>
+        <v>2.84959506988525</v>
       </c>
       <c r="H116" t="n">
         <v>3500</v>
@@ -3762,7 +3762,7 @@
         <v>2.92549991607666</v>
       </c>
       <c r="G117" t="n">
-        <v>2.78812384605408</v>
+        <v>2.7881236076355</v>
       </c>
       <c r="H117" t="n">
         <v>9000</v>
@@ -3820,7 +3820,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G119" t="n">
-        <v>2.8543598651886</v>
+        <v>2.85436034202576</v>
       </c>
       <c r="H119" t="n">
         <v>2500</v>
@@ -3849,7 +3849,7 @@
         <v>3</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85912537574768</v>
+        <v>2.85912561416626</v>
       </c>
       <c r="H120" t="n">
         <v>2000</v>
@@ -3878,7 +3878,7 @@
         <v>3</v>
       </c>
       <c r="G121" t="n">
-        <v>2.85912537574768</v>
+        <v>2.85912561416626</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H123" t="n">
         <v>500</v>
@@ -3965,7 +3965,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G126" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H126" t="n">
         <v>1000</v>
@@ -4052,7 +4052,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>2.81147313117981</v>
+        <v>2.81147336959839</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78288221359253</v>
+        <v>2.78288173675537</v>
       </c>
       <c r="H129" t="n">
         <v>9000</v>
@@ -4139,7 +4139,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G130" t="n">
-        <v>2.78288221359253</v>
+        <v>2.78288173675537</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G131" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H131" t="n">
         <v>3500</v>
@@ -4197,7 +4197,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G132" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>2.92249989509583</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78526425361633</v>
+        <v>2.78526449203491</v>
       </c>
       <c r="H133" t="n">
         <v>1500</v>
@@ -4255,7 +4255,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H134" t="n">
         <v>1000</v>
@@ -4284,7 +4284,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H135" t="n">
         <v>500</v>
@@ -4313,7 +4313,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G136" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H136" t="n">
         <v>1000</v>
@@ -4342,7 +4342,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G137" t="n">
-        <v>2.83053398132324</v>
+        <v>2.8305344581604</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G138" t="n">
-        <v>2.79241251945496</v>
+        <v>2.79241228103638</v>
       </c>
       <c r="H138" t="n">
         <v>6500</v>
@@ -4400,7 +4400,7 @@
         <v>2.95700001716614</v>
       </c>
       <c r="G139" t="n">
-        <v>2.81814479827881</v>
+        <v>2.81814455986023</v>
       </c>
       <c r="H139" t="n">
         <v>4500</v>
@@ -4429,7 +4429,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G140" t="n">
-        <v>2.87818598747253</v>
+        <v>2.87818646430969</v>
       </c>
       <c r="H140" t="n">
         <v>11500</v>
@@ -4458,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="G141" t="n">
-        <v>2.85912537574768</v>
+        <v>2.85912561416626</v>
       </c>
       <c r="H141" t="n">
         <v>500</v>
@@ -4516,7 +4516,7 @@
         <v>3</v>
       </c>
       <c r="G143" t="n">
-        <v>2.85912537574768</v>
+        <v>2.85912561416626</v>
       </c>
       <c r="H143" t="n">
         <v>13500</v>
@@ -4603,7 +4603,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>2.90201234817505</v>
+        <v>2.90201210975647</v>
       </c>
       <c r="H146" t="n">
         <v>12500</v>
@@ -4661,7 +4661,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>2.91630744934082</v>
+        <v>2.9163076877594</v>
       </c>
       <c r="H148" t="n">
         <v>2000</v>
@@ -4690,7 +4690,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>2.98302102088928</v>
+        <v>2.9830207824707</v>
       </c>
       <c r="H149" t="n">
         <v>31500</v>
@@ -4748,7 +4748,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>3.05926394462585</v>
+        <v>3.05926418304443</v>
       </c>
       <c r="H151" t="n">
         <v>12000</v>
@@ -4806,7 +4806,7 @@
         <v>3.32949995994568</v>
       </c>
       <c r="G153" t="n">
-        <v>3.17315244674683</v>
+        <v>3.17315268516541</v>
       </c>
       <c r="H153" t="n">
         <v>8000</v>
@@ -4893,7 +4893,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G156" t="n">
-        <v>3.22890543937683</v>
+        <v>3.22890567779541</v>
       </c>
       <c r="H156" t="n">
         <v>17500</v>
@@ -4922,7 +4922,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G157" t="n">
-        <v>3.18315958976746</v>
+        <v>3.18315935134888</v>
       </c>
       <c r="H157" t="n">
         <v>4000</v>
@@ -4951,7 +4951,7 @@
         <v>3.35349988937378</v>
       </c>
       <c r="G158" t="n">
-        <v>3.19602560997009</v>
+        <v>3.19602537155151</v>
       </c>
       <c r="H158" t="n">
         <v>8500</v>
@@ -4980,7 +4980,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G159" t="n">
-        <v>3.28799438476562</v>
+        <v>3.28799414634705</v>
       </c>
       <c r="H159" t="n">
         <v>11000</v>
@@ -5009,7 +5009,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>3.24034214019775</v>
+        <v>3.24034190177917</v>
       </c>
       <c r="H160" t="n">
         <v>5000</v>
@@ -5038,7 +5038,7 @@
         <v>3.43549990653992</v>
       </c>
       <c r="G161" t="n">
-        <v>3.27417516708374</v>
+        <v>3.27417469024658</v>
       </c>
       <c r="H161" t="n">
         <v>11500</v>
@@ -5183,7 +5183,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.2546374797821</v>
+        <v>3.25463724136353</v>
       </c>
       <c r="H166" t="n">
         <v>14000</v>
@@ -5212,7 +5212,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>3.26893353462219</v>
+        <v>3.26893305778503</v>
       </c>
       <c r="H167" t="n">
         <v>14500</v>
@@ -5241,7 +5241,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>3.31658530235291</v>
+        <v>3.31658506393433</v>
       </c>
       <c r="H168" t="n">
         <v>9000</v>
@@ -5270,7 +5270,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>3.31658530235291</v>
+        <v>3.31658506393433</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G172" t="n">
-        <v>3.50242829322815</v>
+        <v>3.50242853164673</v>
       </c>
       <c r="H172" t="n">
         <v>10000</v>
@@ -5415,7 +5415,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.47860240936279</v>
+        <v>3.47860217094421</v>
       </c>
       <c r="H174" t="n">
         <v>6000</v>
@@ -5444,7 +5444,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G175" t="n">
-        <v>3.55484580993652</v>
+        <v>3.5548460483551</v>
       </c>
       <c r="H175" t="n">
         <v>4000</v>
@@ -5560,7 +5560,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>3.84075832366943</v>
+        <v>3.84075880050659</v>
       </c>
       <c r="H179" t="n">
         <v>10000</v>
@@ -5589,7 +5589,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>3.7549843788147</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H180" t="n">
         <v>24000</v>
@@ -5618,7 +5618,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G181" t="n">
-        <v>3.7549843788147</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H181" t="n">
         <v>10000</v>
@@ -5792,7 +5792,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G187" t="n">
-        <v>3.71686291694641</v>
+        <v>3.71686315536499</v>
       </c>
       <c r="H187" t="n">
         <v>3000</v>
@@ -5821,7 +5821,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>3.71686291694641</v>
+        <v>3.71686315536499</v>
       </c>
       <c r="H188" t="n">
         <v>3000</v>
@@ -5850,7 +5850,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>3.65015006065369</v>
+        <v>3.65014958381653</v>
       </c>
       <c r="H189" t="n">
         <v>4350</v>
@@ -5879,7 +5879,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G190" t="n">
-        <v>3.79310584068298</v>
+        <v>3.79310631752014</v>
       </c>
       <c r="H190" t="n">
         <v>9537</v>
@@ -5908,7 +5908,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>3.84075832366943</v>
+        <v>3.84075880050659</v>
       </c>
       <c r="H191" t="n">
         <v>18218</v>
@@ -5937,7 +5937,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G192" t="n">
-        <v>3.84075832366943</v>
+        <v>3.84075880050659</v>
       </c>
       <c r="H192" t="n">
         <v>2550</v>
@@ -5966,7 +5966,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>3.95512390136719</v>
+        <v>3.95512366294861</v>
       </c>
       <c r="H193" t="n">
         <v>3120</v>
@@ -5995,7 +5995,7 @@
         <v>4</v>
       </c>
       <c r="G194" t="n">
-        <v>3.812166929245</v>
+        <v>3.81216716766357</v>
       </c>
       <c r="H194" t="n">
         <v>9902</v>
@@ -6024,7 +6024,7 @@
         <v>4</v>
       </c>
       <c r="G195" t="n">
-        <v>3.812166929245</v>
+        <v>3.81216716766357</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>3.85028910636902</v>
+        <v>3.85028839111328</v>
       </c>
       <c r="H197" t="n">
         <v>810</v>
@@ -6111,7 +6111,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G198" t="n">
-        <v>3.7549843788147</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H198" t="n">
         <v>10740</v>
@@ -6140,7 +6140,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G199" t="n">
-        <v>3.7549843788147</v>
+        <v>3.75498461723328</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G200" t="n">
-        <v>3.7741425037384</v>
+        <v>3.77414274215698</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>4</v>
       </c>
       <c r="G201" t="n">
-        <v>3.83161687850952</v>
+        <v>3.8316171169281</v>
       </c>
       <c r="H201" t="n">
         <v>14910</v>
@@ -6256,7 +6256,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>3.87951231002808</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H203" t="n">
         <v>3200</v>
@@ -6372,7 +6372,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G207" t="n">
-        <v>3.7741425037384</v>
+        <v>3.77414274215698</v>
       </c>
       <c r="H207" t="n">
         <v>6680</v>
@@ -6401,7 +6401,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>3.7070894241333</v>
+        <v>3.70708918571472</v>
       </c>
       <c r="H208" t="n">
         <v>1000</v>
@@ -6430,7 +6430,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G209" t="n">
-        <v>3.69751024246216</v>
+        <v>3.69751000404358</v>
       </c>
       <c r="H209" t="n">
         <v>500</v>
@@ -6459,7 +6459,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G210" t="n">
-        <v>3.69751024246216</v>
+        <v>3.69751000404358</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>3.83161687850952</v>
+        <v>3.8316171169281</v>
       </c>
       <c r="H211" t="n">
         <v>12500</v>
@@ -6517,7 +6517,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>3.87951231002808</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H212" t="n">
         <v>12189</v>
@@ -6546,7 +6546,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>3.87951231002808</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>3.87951231002808</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H215" t="n">
         <v>1090</v>
@@ -6633,7 +6633,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>3.87951231002808</v>
+        <v>3.87951254844666</v>
       </c>
       <c r="H216" t="n">
         <v>1000</v>
@@ -6662,7 +6662,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.93698644638062</v>
+        <v>3.93698620796204</v>
       </c>
       <c r="H217" t="n">
         <v>4860</v>
@@ -6749,7 +6749,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>4.03277683258057</v>
+        <v>4.03277730941772</v>
       </c>
       <c r="H220" t="n">
         <v>4360</v>
@@ -6778,7 +6778,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>4.21477937698364</v>
+        <v>4.21477842330933</v>
       </c>
       <c r="H221" t="n">
         <v>5788</v>
@@ -6807,7 +6807,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>4.10940980911255</v>
+        <v>4.10940933227539</v>
       </c>
       <c r="H222" t="n">
         <v>22705</v>
@@ -6865,7 +6865,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G224" t="n">
-        <v>4.1956205368042</v>
+        <v>4.19562149047852</v>
       </c>
       <c r="H224" t="n">
         <v>6059</v>
@@ -6894,7 +6894,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G225" t="n">
-        <v>4.3967809677124</v>
+        <v>4.39678049087524</v>
       </c>
       <c r="H225" t="n">
         <v>12211</v>
@@ -6952,7 +6952,7 @@
         <v>4.5</v>
       </c>
       <c r="G227" t="n">
-        <v>4.31056928634644</v>
+        <v>4.31056880950928</v>
       </c>
       <c r="H227" t="n">
         <v>15408</v>
@@ -7010,7 +7010,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G229" t="n">
-        <v>4.4350962638855</v>
+        <v>4.43509674072266</v>
       </c>
       <c r="H229" t="n">
         <v>5450</v>
@@ -7039,7 +7039,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>4.38720083236694</v>
+        <v>4.3872013092041</v>
       </c>
       <c r="H230" t="n">
         <v>3150</v>
@@ -7068,7 +7068,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G231" t="n">
-        <v>4.48299121856689</v>
+        <v>4.48299169540405</v>
       </c>
       <c r="H231" t="n">
         <v>3020</v>
@@ -7242,7 +7242,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G237" t="n">
-        <v>4.96194410324097</v>
+        <v>4.96194362640381</v>
       </c>
       <c r="H237" t="n">
         <v>30201</v>
@@ -7329,7 +7329,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>4.90446949005127</v>
+        <v>4.90446996688843</v>
       </c>
       <c r="H240" t="n">
         <v>12860</v>
@@ -7358,7 +7358,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G241" t="n">
-        <v>4.94278573989868</v>
+        <v>4.94278621673584</v>
       </c>
       <c r="H241" t="n">
         <v>8026</v>
@@ -7387,7 +7387,7 @@
         <v>5</v>
       </c>
       <c r="G242" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H242" t="n">
         <v>16194</v>
@@ -7416,7 +7416,7 @@
         <v>5</v>
       </c>
       <c r="G243" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H243" t="n">
         <v>18850</v>
@@ -7445,7 +7445,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H244" t="n">
         <v>3855</v>
@@ -7474,7 +7474,7 @@
         <v>5</v>
       </c>
       <c r="G245" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H245" t="n">
         <v>1200</v>
@@ -7590,7 +7590,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G249" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036380767822</v>
       </c>
       <c r="H249" t="n">
         <v>140</v>
@@ -7619,7 +7619,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G250" t="n">
-        <v>4.65541458129883</v>
+        <v>4.65541505813599</v>
       </c>
       <c r="H250" t="n">
         <v>750</v>
@@ -7648,7 +7648,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G251" t="n">
-        <v>4.65541458129883</v>
+        <v>4.65541505813599</v>
       </c>
       <c r="H251" t="n">
         <v>1500</v>
@@ -7677,7 +7677,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036380767822</v>
       </c>
       <c r="H252" t="n">
         <v>2483</v>
@@ -7706,7 +7706,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H253" t="n">
         <v>3900</v>
@@ -7735,7 +7735,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036380767822</v>
       </c>
       <c r="H254" t="n">
         <v>9900</v>
@@ -7764,7 +7764,7 @@
         <v>5</v>
       </c>
       <c r="G255" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H255" t="n">
         <v>13400</v>
@@ -7793,7 +7793,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G256" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H256" t="n">
         <v>960</v>
@@ -7822,7 +7822,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G257" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H257" t="n">
         <v>1620</v>
@@ -7851,7 +7851,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G258" t="n">
-        <v>4.48299121856689</v>
+        <v>4.48299169540405</v>
       </c>
       <c r="H258" t="n">
         <v>11514</v>
@@ -7880,7 +7880,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>4.63625621795654</v>
+        <v>4.63625717163086</v>
       </c>
       <c r="H259" t="n">
         <v>5992</v>
@@ -7967,7 +7967,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G262" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H262" t="n">
         <v>3699</v>
@@ -7996,7 +7996,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>4.64583587646484</v>
+        <v>4.64583539962769</v>
       </c>
       <c r="H263" t="n">
         <v>581</v>
@@ -8112,7 +8112,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>4.59794044494629</v>
+        <v>4.59794139862061</v>
       </c>
       <c r="H267" t="n">
         <v>1400</v>
@@ -8141,7 +8141,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>4.59794044494629</v>
+        <v>4.59794139862061</v>
       </c>
       <c r="H268" t="n">
         <v>1635</v>
@@ -8170,7 +8170,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G269" t="n">
-        <v>4.59794044494629</v>
+        <v>4.59794139862061</v>
       </c>
       <c r="H269" t="n">
         <v>4049</v>
@@ -8286,7 +8286,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>4.57878255844116</v>
+        <v>4.57878160476685</v>
       </c>
       <c r="H273" t="n">
         <v>700</v>
@@ -8315,7 +8315,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>4.76078414916992</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H274" t="n">
         <v>4784</v>
@@ -8344,7 +8344,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G275" t="n">
-        <v>4.76078414916992</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G276" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036380767822</v>
       </c>
       <c r="H276" t="n">
         <v>900</v>
@@ -8402,7 +8402,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>4.62667751312256</v>
+        <v>4.62667798995972</v>
       </c>
       <c r="H277" t="n">
         <v>5557</v>
@@ -8431,7 +8431,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G278" t="n">
-        <v>4.65541458129883</v>
+        <v>4.65541505813599</v>
       </c>
       <c r="H278" t="n">
         <v>500</v>
@@ -8460,7 +8460,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G279" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H279" t="n">
         <v>4220</v>
@@ -8489,7 +8489,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G280" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.64583587646484</v>
+        <v>4.64583539962769</v>
       </c>
       <c r="H282" t="n">
         <v>2700</v>
@@ -8576,7 +8576,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>4.64583587646484</v>
+        <v>4.64583539962769</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>4.75120449066162</v>
+        <v>4.75120496749878</v>
       </c>
       <c r="H288" t="n">
         <v>550</v>
@@ -8779,7 +8779,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G290" t="n">
-        <v>4.84699535369873</v>
+        <v>4.84699440002441</v>
       </c>
       <c r="H290" t="n">
         <v>3925</v>
@@ -8895,7 +8895,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G294" t="n">
-        <v>4.76078414916992</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H294" t="n">
         <v>2200</v>
@@ -8924,7 +8924,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H295" t="n">
         <v>2811</v>
@@ -8953,7 +8953,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>4.67457294464111</v>
+        <v>4.67457246780396</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G297" t="n">
-        <v>4.70331001281738</v>
+        <v>4.70330953598022</v>
       </c>
       <c r="H297" t="n">
         <v>297</v>
@@ -9185,7 +9185,7 @@
         <v>5</v>
       </c>
       <c r="G304" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H304" t="n">
         <v>25540</v>
@@ -9214,7 +9214,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H305" t="n">
         <v>4750</v>
@@ -9272,7 +9272,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>4.84699535369873</v>
+        <v>4.84699440002441</v>
       </c>
       <c r="H307" t="n">
         <v>5606</v>
@@ -9330,7 +9330,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G309" t="n">
-        <v>4.84699535369873</v>
+        <v>4.84699440002441</v>
       </c>
       <c r="H309" t="n">
         <v>5000</v>
@@ -9359,7 +9359,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G310" t="n">
-        <v>4.84699535369873</v>
+        <v>4.84699440002441</v>
       </c>
       <c r="H310" t="n">
         <v>4957</v>
@@ -9388,7 +9388,7 @@
         <v>5</v>
       </c>
       <c r="G311" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H311" t="n">
         <v>5186</v>
@@ -9417,7 +9417,7 @@
         <v>5</v>
       </c>
       <c r="G312" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>5</v>
       </c>
       <c r="G313" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.76078414916992</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H315" t="n">
         <v>2985</v>
@@ -9533,7 +9533,7 @@
         <v>5</v>
       </c>
       <c r="G316" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H316" t="n">
         <v>402</v>
@@ -9562,7 +9562,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036380767822</v>
       </c>
       <c r="H317" t="n">
         <v>6452</v>
@@ -9591,7 +9591,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036380767822</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H320" t="n">
         <v>100</v>
@@ -9678,7 +9678,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>5</v>
       </c>
       <c r="G322" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H322" t="n">
         <v>3400</v>
@@ -9736,7 +9736,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H323" t="n">
         <v>54154</v>
@@ -9794,7 +9794,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H325" t="n">
         <v>1040</v>
@@ -9823,7 +9823,7 @@
         <v>5</v>
       </c>
       <c r="G326" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H326" t="n">
         <v>3000</v>
@@ -9852,7 +9852,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>4.84699535369873</v>
+        <v>4.84699440002441</v>
       </c>
       <c r="H327" t="n">
         <v>50</v>
@@ -9881,7 +9881,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H328" t="n">
         <v>170</v>
@@ -9910,7 +9910,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>5</v>
       </c>
       <c r="G330" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H330" t="n">
         <v>7750</v>
@@ -9968,7 +9968,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.84699535369873</v>
+        <v>4.84699440002441</v>
       </c>
       <c r="H331" t="n">
         <v>10342</v>
@@ -9997,7 +9997,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H332" t="n">
         <v>4683</v>
@@ -10026,7 +10026,7 @@
         <v>5</v>
       </c>
       <c r="G333" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H333" t="n">
         <v>1125</v>
@@ -10055,7 +10055,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G334" t="n">
-        <v>4.75120449066162</v>
+        <v>4.75120496749878</v>
       </c>
       <c r="H334" t="n">
         <v>3379</v>
@@ -10084,7 +10084,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.77036333084106</v>
+        <v>4.77036380767822</v>
       </c>
       <c r="H335" t="n">
         <v>16377</v>
@@ -10113,7 +10113,7 @@
         <v>5</v>
       </c>
       <c r="G336" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H336" t="n">
         <v>17100</v>
@@ -10142,7 +10142,7 @@
         <v>5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.78952074050903</v>
+        <v>4.78952121734619</v>
       </c>
       <c r="H337" t="n">
         <v>12410</v>
@@ -10171,7 +10171,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>4.8278374671936</v>
+        <v>4.82783794403076</v>
       </c>
       <c r="H338" t="n">
         <v>6710</v>
@@ -10200,7 +10200,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G339" t="n">
-        <v>4.8853120803833</v>
+        <v>4.88531112670898</v>
       </c>
       <c r="H339" t="n">
         <v>7300</v>
@@ -10258,7 +10258,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.8853120803833</v>
+        <v>4.88531112670898</v>
       </c>
       <c r="H341" t="n">
         <v>8729</v>
@@ -10345,7 +10345,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.1343674659729</v>
+        <v>5.13436651229858</v>
       </c>
       <c r="H344" t="n">
         <v>6260</v>
@@ -10374,7 +10374,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>5.172682762146</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H345" t="n">
         <v>14432</v>
@@ -10403,7 +10403,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.1152081489563</v>
+        <v>5.11520862579346</v>
       </c>
       <c r="H346" t="n">
         <v>11091</v>
@@ -10519,7 +10519,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.1343674659729</v>
+        <v>5.13436651229858</v>
       </c>
       <c r="H350" t="n">
         <v>5572</v>
@@ -10548,7 +10548,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G351" t="n">
-        <v>5.1343674659729</v>
+        <v>5.13436651229858</v>
       </c>
       <c r="H351" t="n">
         <v>2712</v>
@@ -10635,7 +10635,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>5.172682762146</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H354" t="n">
         <v>10600</v>
@@ -10722,7 +10722,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>5.172682762146</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H357" t="n">
         <v>2620</v>
@@ -10751,7 +10751,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G358" t="n">
-        <v>5.172682762146</v>
+        <v>5.17268323898315</v>
       </c>
       <c r="H358" t="n">
         <v>2200</v>
@@ -10780,7 +10780,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G359" t="n">
-        <v>5.01941823959351</v>
+        <v>5.01941776275635</v>
       </c>
       <c r="H359" t="n">
         <v>5962</v>
@@ -10896,7 +10896,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.1343674659729</v>
+        <v>5.13436651229858</v>
       </c>
       <c r="H363" t="n">
         <v>9005</v>
@@ -11070,7 +11070,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G369" t="n">
-        <v>5.53668737411499</v>
+        <v>5.53668642044067</v>
       </c>
       <c r="H369" t="n">
         <v>11072</v>
@@ -11099,7 +11099,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G370" t="n">
-        <v>5.53668737411499</v>
+        <v>5.53668642044067</v>
       </c>
       <c r="H370" t="n">
         <v>4790</v>
@@ -11128,7 +11128,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>5.68995094299316</v>
+        <v>5.68995189666748</v>
       </c>
       <c r="H371" t="n">
         <v>95523</v>
@@ -11186,7 +11186,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>5.84321594238281</v>
+        <v>5.84321546554565</v>
       </c>
       <c r="H373" t="n">
         <v>42690</v>
@@ -11215,7 +11215,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H374" t="n">
         <v>28432</v>
@@ -11244,7 +11244,7 @@
         <v>6</v>
       </c>
       <c r="G375" t="n">
-        <v>5.74742555618286</v>
+        <v>5.74742603302002</v>
       </c>
       <c r="H375" t="n">
         <v>36585</v>
@@ -11273,7 +11273,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G376" t="n">
-        <v>5.91984748840332</v>
+        <v>5.91984796524048</v>
       </c>
       <c r="H376" t="n">
         <v>68584</v>
@@ -11331,7 +11331,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G378" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H378" t="n">
         <v>4967</v>
@@ -11476,7 +11476,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G383" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H383" t="n">
         <v>20723</v>
@@ -11505,7 +11505,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G384" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H384" t="n">
         <v>4781</v>
@@ -11534,7 +11534,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H385" t="n">
         <v>6939</v>
@@ -11563,7 +11563,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G386" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H386" t="n">
         <v>4823</v>
@@ -11592,7 +11592,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H387" t="n">
         <v>12576</v>
@@ -11679,7 +11679,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H390" t="n">
         <v>1250</v>
@@ -11708,7 +11708,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G391" t="n">
-        <v>5.91984748840332</v>
+        <v>5.91984796524048</v>
       </c>
       <c r="H391" t="n">
         <v>7410</v>
@@ -11737,7 +11737,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H392" t="n">
         <v>6232</v>
@@ -11766,7 +11766,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G393" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H393" t="n">
         <v>2811</v>
@@ -11795,7 +11795,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G394" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H394" t="n">
         <v>1262</v>
@@ -11824,7 +11824,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G395" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H395" t="n">
         <v>4960</v>
@@ -11882,7 +11882,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311248779297</v>
       </c>
       <c r="H397" t="n">
         <v>4390</v>
@@ -11911,7 +11911,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>6.37964153289795</v>
+        <v>6.37964248657227</v>
       </c>
       <c r="H398" t="n">
         <v>14389</v>
@@ -11940,7 +11940,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G399" t="n">
-        <v>6.37964153289795</v>
+        <v>6.37964248657227</v>
       </c>
       <c r="H399" t="n">
         <v>32191</v>
@@ -11969,7 +11969,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>6.32216787338257</v>
+        <v>6.32216835021973</v>
       </c>
       <c r="H400" t="n">
         <v>11804</v>
@@ -12027,7 +12027,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G402" t="n">
-        <v>6.37964153289795</v>
+        <v>6.37964248657227</v>
       </c>
       <c r="H402" t="n">
         <v>7998</v>
@@ -12085,7 +12085,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G404" t="n">
-        <v>6.39880037307739</v>
+        <v>6.39879989624023</v>
       </c>
       <c r="H404" t="n">
         <v>3594</v>
@@ -12114,7 +12114,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>6.32216787338257</v>
+        <v>6.32216835021973</v>
       </c>
       <c r="H405" t="n">
         <v>37562</v>
@@ -12172,7 +12172,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G407" t="n">
-        <v>6.4945912361145</v>
+        <v>6.49459171295166</v>
       </c>
       <c r="H407" t="n">
         <v>9368</v>
@@ -12201,7 +12201,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G408" t="n">
-        <v>6.41795873641968</v>
+        <v>6.41795825958252</v>
       </c>
       <c r="H408" t="n">
         <v>8123</v>
@@ -12346,7 +12346,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G413" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H413" t="n">
         <v>10835</v>
@@ -12375,7 +12375,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G414" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311248779297</v>
       </c>
       <c r="H414" t="n">
         <v>26996</v>
@@ -12433,7 +12433,7 @@
         <v>6</v>
       </c>
       <c r="G416" t="n">
-        <v>5.74742555618286</v>
+        <v>5.74742603302002</v>
       </c>
       <c r="H416" t="n">
         <v>12034</v>
@@ -12549,7 +12549,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>5.70910882949829</v>
+        <v>5.70910835266113</v>
       </c>
       <c r="H420" t="n">
         <v>8111</v>
@@ -12578,7 +12578,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>5.70910882949829</v>
+        <v>5.70910835266113</v>
       </c>
       <c r="H421" t="n">
         <v>18321</v>
@@ -12607,7 +12607,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>5.6707935333252</v>
+        <v>5.67079257965088</v>
       </c>
       <c r="H422" t="n">
         <v>18735</v>
@@ -12636,7 +12636,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G423" t="n">
-        <v>5.6707935333252</v>
+        <v>5.67079257965088</v>
       </c>
       <c r="H423" t="n">
         <v>2501</v>
@@ -12665,7 +12665,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G424" t="n">
-        <v>5.86237335205078</v>
+        <v>5.86237382888794</v>
       </c>
       <c r="H424" t="n">
         <v>4073</v>
@@ -12694,7 +12694,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>5.93900585174561</v>
+        <v>5.93900632858276</v>
       </c>
       <c r="H425" t="n">
         <v>2570</v>
@@ -12752,7 +12752,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G427" t="n">
-        <v>5.99648141860962</v>
+        <v>5.99648094177246</v>
       </c>
       <c r="H427" t="n">
         <v>8596</v>
@@ -12781,7 +12781,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G428" t="n">
-        <v>6.07311344146729</v>
+        <v>6.07311248779297</v>
       </c>
       <c r="H428" t="n">
         <v>6440</v>
@@ -12839,7 +12839,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G430" t="n">
-        <v>6.05395460128784</v>
+        <v>6.053955078125</v>
       </c>
       <c r="H430" t="n">
         <v>3535</v>
@@ -12868,7 +12868,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G431" t="n">
-        <v>6.05395460128784</v>
+        <v>6.053955078125</v>
       </c>
       <c r="H431" t="n">
         <v>1471</v>
@@ -12897,7 +12897,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G432" t="n">
-        <v>6.11142921447754</v>
+        <v>6.11142873764038</v>
       </c>
       <c r="H432" t="n">
         <v>9507</v>
@@ -12955,7 +12955,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>6.41795873641968</v>
+        <v>6.41795825958252</v>
       </c>
       <c r="H434" t="n">
         <v>27535</v>
@@ -12984,7 +12984,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>6.41795873641968</v>
+        <v>6.41795825958252</v>
       </c>
       <c r="H435" t="n">
         <v>5559</v>
@@ -13013,7 +13013,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G436" t="n">
-        <v>6.57122325897217</v>
+        <v>6.57122278213501</v>
       </c>
       <c r="H436" t="n">
         <v>24597</v>
@@ -13042,7 +13042,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G437" t="n">
-        <v>6.62869691848755</v>
+        <v>6.62869739532471</v>
       </c>
       <c r="H437" t="n">
         <v>19470</v>
@@ -13071,7 +13071,7 @@
         <v>7</v>
       </c>
       <c r="G438" t="n">
-        <v>6.70532894134521</v>
+        <v>6.70532941818237</v>
       </c>
       <c r="H438" t="n">
         <v>17634</v>
@@ -13100,7 +13100,7 @@
         <v>7</v>
       </c>
       <c r="G439" t="n">
-        <v>6.70532894134521</v>
+        <v>6.70532941818237</v>
       </c>
       <c r="H439" t="n">
         <v>12013</v>
@@ -13129,7 +13129,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G440" t="n">
-        <v>6.64785528182983</v>
+        <v>6.64785575866699</v>
       </c>
       <c r="H440" t="n">
         <v>3991</v>
@@ -13158,7 +13158,7 @@
         <v>7</v>
       </c>
       <c r="G441" t="n">
-        <v>6.70532894134521</v>
+        <v>6.70532941818237</v>
       </c>
       <c r="H441" t="n">
         <v>8061</v>
@@ -13216,7 +13216,7 @@
         <v>7</v>
       </c>
       <c r="G443" t="n">
-        <v>6.70532894134521</v>
+        <v>6.70532941818237</v>
       </c>
       <c r="H443" t="n">
         <v>701</v>
@@ -13274,7 +13274,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>6.99270105361938</v>
+        <v>6.99270057678223</v>
       </c>
       <c r="H445" t="n">
         <v>26998</v>
@@ -13303,7 +13303,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>7.165123462677</v>
+        <v>7.16512393951416</v>
       </c>
       <c r="H446" t="n">
         <v>13821</v>
@@ -13332,7 +13332,7 @@
         <v>7.5</v>
       </c>
       <c r="G447" t="n">
-        <v>7.1842827796936</v>
+        <v>7.18428230285645</v>
       </c>
       <c r="H447" t="n">
         <v>16792</v>
@@ -13361,7 +13361,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G448" t="n">
-        <v>7.50996923446655</v>
+        <v>7.50996971130371</v>
       </c>
       <c r="H448" t="n">
         <v>21129</v>
@@ -13390,7 +13390,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G449" t="n">
-        <v>7.79734230041504</v>
+        <v>7.79734086990356</v>
       </c>
       <c r="H449" t="n">
         <v>25454</v>
@@ -13506,7 +13506,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>8.133056640625</v>
+        <v>8.13305568695068</v>
       </c>
       <c r="H453" t="n">
         <v>8878</v>
@@ -13564,7 +13564,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G455" t="n">
-        <v>7.99846458435059</v>
+        <v>7.99846506118774</v>
       </c>
       <c r="H455" t="n">
         <v>13585</v>
@@ -13593,7 +13593,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537269592285</v>
       </c>
       <c r="H456" t="n">
         <v>15884</v>
@@ -13622,7 +13622,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G457" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537269592285</v>
       </c>
       <c r="H457" t="n">
         <v>8749</v>
@@ -13680,7 +13680,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>8.133056640625</v>
+        <v>8.13305568695068</v>
       </c>
       <c r="H459" t="n">
         <v>5157</v>
@@ -13738,7 +13738,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G461" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537269592285</v>
       </c>
       <c r="H461" t="n">
         <v>4060</v>
@@ -13796,7 +13796,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.07537364959717</v>
+        <v>8.07537269592285</v>
       </c>
       <c r="H463" t="n">
         <v>3875</v>
@@ -13825,7 +13825,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>7.80619430541992</v>
+        <v>7.80619478225708</v>
       </c>
       <c r="H464" t="n">
         <v>13308</v>
@@ -13854,7 +13854,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>7.53701639175415</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H465" t="n">
         <v>22593</v>
@@ -13912,7 +13912,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G467" t="n">
-        <v>7.22938203811646</v>
+        <v>7.22938251495361</v>
       </c>
       <c r="H467" t="n">
         <v>4220</v>
@@ -13941,7 +13941,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G468" t="n">
-        <v>7.32551765441895</v>
+        <v>7.32551717758179</v>
       </c>
       <c r="H468" t="n">
         <v>7825</v>
@@ -13999,7 +13999,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G470" t="n">
-        <v>7.24860906600952</v>
+        <v>7.24860954284668</v>
       </c>
       <c r="H470" t="n">
         <v>1139</v>
@@ -14028,7 +14028,7 @@
         <v>7.5</v>
       </c>
       <c r="G471" t="n">
-        <v>7.21015596389771</v>
+        <v>7.21015548706055</v>
       </c>
       <c r="H471" t="n">
         <v>4606</v>
@@ -14057,7 +14057,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>7.19092845916748</v>
+        <v>7.19092798233032</v>
       </c>
       <c r="H472" t="n">
         <v>4262</v>
@@ -14086,7 +14086,7 @@
         <v>7.5</v>
       </c>
       <c r="G473" t="n">
-        <v>7.21015596389771</v>
+        <v>7.21015548706055</v>
       </c>
       <c r="H473" t="n">
         <v>577622</v>
@@ -14115,7 +14115,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G474" t="n">
-        <v>7.07556629180908</v>
+        <v>7.07556581497192</v>
       </c>
       <c r="H474" t="n">
         <v>13451</v>
@@ -14144,7 +14144,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G475" t="n">
-        <v>7.4985613822937</v>
+        <v>7.49856185913086</v>
       </c>
       <c r="H475" t="n">
         <v>217706</v>
@@ -14173,7 +14173,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469652175903</v>
       </c>
       <c r="H476" t="n">
         <v>6071</v>
@@ -14202,7 +14202,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G477" t="n">
-        <v>7.57546997070312</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H477" t="n">
         <v>5817</v>
@@ -14231,7 +14231,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>7.57546997070312</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H478" t="n">
         <v>7258</v>
@@ -14260,7 +14260,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G479" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H479" t="n">
         <v>7940</v>
@@ -14289,7 +14289,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469652175903</v>
       </c>
       <c r="H480" t="n">
         <v>5804</v>
@@ -14347,7 +14347,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469652175903</v>
       </c>
       <c r="H482" t="n">
         <v>3228</v>
@@ -14376,7 +14376,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>7.57546997070312</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H483" t="n">
         <v>400</v>
@@ -14405,7 +14405,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469652175903</v>
       </c>
       <c r="H484" t="n">
         <v>2166</v>
@@ -14434,7 +14434,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469652175903</v>
       </c>
       <c r="H485" t="n">
         <v>10</v>
@@ -14492,7 +14492,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>7.59469699859619</v>
+        <v>7.59469652175903</v>
       </c>
       <c r="H487" t="n">
         <v>63</v>
@@ -14521,7 +14521,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>7.57546997070312</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H488" t="n">
         <v>1100</v>
@@ -14550,7 +14550,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G489" t="n">
-        <v>7.47933435440063</v>
+        <v>7.47933483123779</v>
       </c>
       <c r="H489" t="n">
         <v>5775</v>
@@ -14637,7 +14637,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G492" t="n">
-        <v>7.57546997070312</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H492" t="n">
         <v>220</v>
@@ -14666,7 +14666,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G493" t="n">
-        <v>7.57546997070312</v>
+        <v>7.57547044754028</v>
       </c>
       <c r="H493" t="n">
         <v>1235</v>
@@ -14695,7 +14695,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>7.53701639175415</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H494" t="n">
         <v>1276</v>
@@ -14724,7 +14724,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>7.53701639175415</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H495" t="n">
         <v>3732</v>
@@ -14753,7 +14753,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G496" t="n">
-        <v>7.51778936386108</v>
+        <v>7.51778888702393</v>
       </c>
       <c r="H496" t="n">
         <v>648</v>
@@ -14782,7 +14782,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G497" t="n">
-        <v>7.53701639175415</v>
+        <v>7.53701591491699</v>
       </c>
       <c r="H497" t="n">
         <v>370</v>
@@ -14840,7 +14840,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G499" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H499" t="n">
         <v>6971</v>
@@ -14869,7 +14869,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>7.76774168014526</v>
+        <v>7.76774024963379</v>
       </c>
       <c r="H500" t="n">
         <v>19279</v>
@@ -14898,7 +14898,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>7.76774168014526</v>
+        <v>7.76774024963379</v>
       </c>
       <c r="H501" t="n">
         <v>1200</v>
@@ -14927,7 +14927,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G502" t="n">
-        <v>7.63315105438232</v>
+        <v>7.63315153121948</v>
       </c>
       <c r="H502" t="n">
         <v>7166</v>
@@ -14985,7 +14985,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G504" t="n">
-        <v>7.82542324066162</v>
+        <v>7.8254222869873</v>
       </c>
       <c r="H504" t="n">
         <v>8213</v>
@@ -15043,7 +15043,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G506" t="n">
-        <v>8.15228176116943</v>
+        <v>8.15228271484375</v>
       </c>
       <c r="H506" t="n">
         <v>23464</v>
@@ -15159,7 +15159,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G510" t="n">
-        <v>8.55605030059814</v>
+        <v>8.55604934692383</v>
       </c>
       <c r="H510" t="n">
         <v>4438</v>
@@ -15188,7 +15188,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G511" t="n">
-        <v>8.55605030059814</v>
+        <v>8.55604934692383</v>
       </c>
       <c r="H511" t="n">
         <v>2825</v>
@@ -15217,7 +15217,7 @@
         <v>9</v>
       </c>
       <c r="G512" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H512" t="n">
         <v>6874</v>
@@ -15275,7 +15275,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>9.24822521209717</v>
+        <v>9.24822616577148</v>
       </c>
       <c r="H514" t="n">
         <v>17324</v>
@@ -15333,7 +15333,7 @@
         <v>9.5</v>
       </c>
       <c r="G516" t="n">
-        <v>9.13286399841309</v>
+        <v>9.13286304473877</v>
       </c>
       <c r="H516" t="n">
         <v>4264</v>
@@ -15362,7 +15362,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G517" t="n">
-        <v>9.3635892868042</v>
+        <v>9.36358737945557</v>
       </c>
       <c r="H517" t="n">
         <v>19813</v>
@@ -15449,7 +15449,7 @@
         <v>9.5</v>
       </c>
       <c r="G520" t="n">
-        <v>9.13286399841309</v>
+        <v>9.13286304473877</v>
       </c>
       <c r="H520" t="n">
         <v>6538</v>
@@ -15507,7 +15507,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>9.49817752838135</v>
+        <v>9.49817943572998</v>
       </c>
       <c r="H522" t="n">
         <v>4632</v>
@@ -15536,7 +15536,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G523" t="n">
-        <v>9.47894954681396</v>
+        <v>9.47895050048828</v>
       </c>
       <c r="H523" t="n">
         <v>7936</v>
@@ -15623,7 +15623,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G526" t="n">
-        <v>9.3635892868042</v>
+        <v>9.36358737945557</v>
       </c>
       <c r="H526" t="n">
         <v>5384</v>
@@ -15652,7 +15652,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G527" t="n">
-        <v>9.017502784729</v>
+        <v>9.01750087738037</v>
       </c>
       <c r="H527" t="n">
         <v>5818</v>
@@ -15739,7 +15739,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G530" t="n">
-        <v>8.70986938476562</v>
+        <v>8.70986843109131</v>
       </c>
       <c r="H530" t="n">
         <v>13372</v>
@@ -15797,7 +15797,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G532" t="n">
-        <v>9.07518291473389</v>
+        <v>9.07518196105957</v>
       </c>
       <c r="H532" t="n">
         <v>11482</v>
@@ -16000,7 +16000,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G539" t="n">
-        <v>8.69064044952393</v>
+        <v>8.69064140319824</v>
       </c>
       <c r="H539" t="n">
         <v>10503</v>
@@ -16029,7 +16029,7 @@
         <v>9</v>
       </c>
       <c r="G540" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H540" t="n">
         <v>2610</v>
@@ -16087,7 +16087,7 @@
         <v>9</v>
       </c>
       <c r="G542" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H542" t="n">
         <v>16471</v>
@@ -16145,7 +16145,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G544" t="n">
-        <v>8.4791431427002</v>
+        <v>8.47914218902588</v>
       </c>
       <c r="H544" t="n">
         <v>4043</v>
@@ -16377,7 +16377,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G552" t="n">
-        <v>8.3637809753418</v>
+        <v>8.36378002166748</v>
       </c>
       <c r="H552" t="n">
         <v>2520</v>
@@ -16464,7 +16464,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G555" t="n">
-        <v>8.3637809753418</v>
+        <v>8.36378002166748</v>
       </c>
       <c r="H555" t="n">
         <v>2093</v>
@@ -16551,7 +16551,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>8.55605030059814</v>
+        <v>8.55604934692383</v>
       </c>
       <c r="H558" t="n">
         <v>10958</v>
@@ -16580,7 +16580,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G559" t="n">
-        <v>8.55605030059814</v>
+        <v>8.55604934692383</v>
       </c>
       <c r="H559" t="n">
         <v>5484</v>
@@ -16609,7 +16609,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G560" t="n">
-        <v>8.59450435638428</v>
+        <v>8.59450531005859</v>
       </c>
       <c r="H560" t="n">
         <v>5860</v>
@@ -16667,7 +16667,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G562" t="n">
-        <v>8.95981979370117</v>
+        <v>8.95982074737549</v>
       </c>
       <c r="H562" t="n">
         <v>13014</v>
@@ -16696,7 +16696,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G563" t="n">
-        <v>8.90213775634766</v>
+        <v>8.90213871002197</v>
       </c>
       <c r="H563" t="n">
         <v>9291</v>
@@ -16783,7 +16783,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G566" t="n">
-        <v>8.95981979370117</v>
+        <v>8.95982074737549</v>
       </c>
       <c r="H566" t="n">
         <v>4531</v>
@@ -16812,7 +16812,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G567" t="n">
-        <v>9.19054508209229</v>
+        <v>9.19054412841797</v>
       </c>
       <c r="H567" t="n">
         <v>36349</v>
@@ -16899,7 +16899,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G570" t="n">
-        <v>9.03672695159912</v>
+        <v>9.03672790527344</v>
       </c>
       <c r="H570" t="n">
         <v>9621</v>
@@ -16928,7 +16928,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G571" t="n">
-        <v>9.07518291473389</v>
+        <v>9.07518196105957</v>
       </c>
       <c r="H571" t="n">
         <v>10495</v>
@@ -16986,7 +16986,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>9.07518291473389</v>
+        <v>9.07518196105957</v>
       </c>
       <c r="H573" t="n">
         <v>1872</v>
@@ -17015,7 +17015,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G574" t="n">
-        <v>9.017502784729</v>
+        <v>9.01750087738037</v>
       </c>
       <c r="H574" t="n">
         <v>3029</v>
@@ -17073,7 +17073,7 @@
         <v>9</v>
       </c>
       <c r="G576" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H576" t="n">
         <v>5096</v>
@@ -17160,7 +17160,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G579" t="n">
-        <v>8.90213775634766</v>
+        <v>8.90213871002197</v>
       </c>
       <c r="H579" t="n">
         <v>6126</v>
@@ -17247,7 +17247,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G582" t="n">
-        <v>8.70986938476562</v>
+        <v>8.70986843109131</v>
       </c>
       <c r="H582" t="n">
         <v>2983</v>
@@ -17305,7 +17305,7 @@
         <v>9</v>
       </c>
       <c r="G584" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H584" t="n">
         <v>967</v>
@@ -17334,7 +17334,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>8.69064044952393</v>
+        <v>8.69064140319824</v>
       </c>
       <c r="H585" t="n">
         <v>6475</v>
@@ -17392,7 +17392,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G587" t="n">
-        <v>8.70986938476562</v>
+        <v>8.70986843109131</v>
       </c>
       <c r="H587" t="n">
         <v>4690</v>
@@ -17421,7 +17421,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G588" t="n">
-        <v>8.70986938476562</v>
+        <v>8.70986843109131</v>
       </c>
       <c r="H588" t="n">
         <v>3314</v>
@@ -17479,7 +17479,7 @@
         <v>9</v>
       </c>
       <c r="G590" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H590" t="n">
         <v>10274</v>
@@ -17508,7 +17508,7 @@
         <v>9</v>
       </c>
       <c r="G591" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H591" t="n">
         <v>4506</v>
@@ -17537,7 +17537,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G592" t="n">
-        <v>8.59450435638428</v>
+        <v>8.59450531005859</v>
       </c>
       <c r="H592" t="n">
         <v>1305</v>
@@ -17566,7 +17566,7 @@
         <v>9</v>
       </c>
       <c r="G593" t="n">
-        <v>8.65218639373779</v>
+        <v>8.65218734741211</v>
       </c>
       <c r="H593" t="n">
         <v>5549</v>
@@ -17595,7 +17595,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G594" t="n">
-        <v>8.80600166320801</v>
+        <v>8.80600261688232</v>
       </c>
       <c r="H594" t="n">
         <v>19270</v>
@@ -17653,7 +17653,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G596" t="n">
-        <v>8.76754951477051</v>
+        <v>8.76754856109619</v>
       </c>
       <c r="H596" t="n">
         <v>819</v>
@@ -17711,7 +17711,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>9.32513427734375</v>
+        <v>9.32513523101807</v>
       </c>
       <c r="H598" t="n">
         <v>35354</v>
@@ -17740,7 +17740,7 @@
         <v>9.5</v>
       </c>
       <c r="G599" t="n">
-        <v>9.13286399841309</v>
+        <v>9.13286304473877</v>
       </c>
       <c r="H599" t="n">
         <v>6940</v>
@@ -17798,7 +17798,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G601" t="n">
-        <v>9.15209102630615</v>
+        <v>9.15209197998047</v>
       </c>
       <c r="H601" t="n">
         <v>10060</v>
@@ -17827,7 +17827,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>9.32513427734375</v>
+        <v>9.32513523101807</v>
       </c>
       <c r="H602" t="n">
         <v>7188</v>
@@ -17856,7 +17856,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G603" t="n">
-        <v>9.20977210998535</v>
+        <v>9.20977306365967</v>
       </c>
       <c r="H603" t="n">
         <v>8280</v>
@@ -17914,7 +17914,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G605" t="n">
-        <v>9.3635892868042</v>
+        <v>9.36358737945557</v>
       </c>
       <c r="H605" t="n">
         <v>13690</v>
@@ -18088,7 +18088,7 @@
         <v>9.5</v>
       </c>
       <c r="G611" t="n">
-        <v>9.13286399841309</v>
+        <v>9.13286304473877</v>
       </c>
       <c r="H611" t="n">
         <v>9008</v>
@@ -18146,7 +18146,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G613" t="n">
-        <v>9.15209102630615</v>
+        <v>9.15209197998047</v>
       </c>
       <c r="H613" t="n">
         <v>3820</v>
@@ -18175,7 +18175,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G614" t="n">
-        <v>9.20977210998535</v>
+        <v>9.20977306365967</v>
       </c>
       <c r="H614" t="n">
         <v>4084</v>
@@ -18204,7 +18204,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>9.20977210998535</v>
+        <v>9.20977306365967</v>
       </c>
       <c r="H615" t="n">
         <v>2315</v>
@@ -18262,7 +18262,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G617" t="n">
-        <v>9.15209102630615</v>
+        <v>9.15209197998047</v>
       </c>
       <c r="H617" t="n">
         <v>668</v>
@@ -18291,7 +18291,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="n">
-        <v>9.13286399841309</v>
+        <v>9.13286304473877</v>
       </c>
       <c r="H618" t="n">
         <v>5376</v>
@@ -18523,7 +18523,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>9.99808120727539</v>
+        <v>9.99808216094971</v>
       </c>
       <c r="H626" t="n">
         <v>32614</v>
@@ -18552,7 +18552,7 @@
         <v>10.5</v>
       </c>
       <c r="G627" t="n">
-        <v>10.0942182540894</v>
+        <v>10.094217300415</v>
       </c>
       <c r="H627" t="n">
         <v>26237</v>
@@ -18668,7 +18668,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>10.1422863006592</v>
+        <v>10.1422853469849</v>
       </c>
       <c r="H631" t="n">
         <v>5772</v>
@@ -18697,7 +18697,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G632" t="n">
-        <v>10.1422863006592</v>
+        <v>10.1422853469849</v>
       </c>
       <c r="H632" t="n">
         <v>5416</v>
@@ -18726,7 +18726,7 @@
         <v>10.5</v>
       </c>
       <c r="G633" t="n">
-        <v>10.0942182540894</v>
+        <v>10.094217300415</v>
       </c>
       <c r="H633" t="n">
         <v>3222</v>
@@ -18755,7 +18755,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>9.95001602172852</v>
+        <v>9.9500150680542</v>
       </c>
       <c r="H634" t="n">
         <v>8284</v>
@@ -18784,7 +18784,7 @@
         <v>10.5</v>
       </c>
       <c r="G635" t="n">
-        <v>10.0942182540894</v>
+        <v>10.094217300415</v>
       </c>
       <c r="H635" t="n">
         <v>1941</v>
@@ -18813,7 +18813,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G636" t="n">
-        <v>10.0461492538452</v>
+        <v>10.0461502075195</v>
       </c>
       <c r="H636" t="n">
         <v>2509</v>
@@ -18842,7 +18842,7 @@
         <v>10.5</v>
       </c>
       <c r="G637" t="n">
-        <v>10.0942182540894</v>
+        <v>10.094217300415</v>
       </c>
       <c r="H637" t="n">
         <v>8159</v>
@@ -18871,7 +18871,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>10.1903533935547</v>
+        <v>10.190354347229</v>
       </c>
       <c r="H638" t="n">
         <v>4002</v>
@@ -18958,7 +18958,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G641" t="n">
-        <v>10.4787588119507</v>
+        <v>10.478759765625</v>
       </c>
       <c r="H641" t="n">
         <v>6326</v>
@@ -18987,7 +18987,7 @@
         <v>10.75</v>
       </c>
       <c r="G642" t="n">
-        <v>10.3345556259155</v>
+        <v>10.3345565795898</v>
       </c>
       <c r="H642" t="n">
         <v>5010</v>
@@ -19016,7 +19016,7 @@
         <v>10.75</v>
       </c>
       <c r="G643" t="n">
-        <v>10.3345556259155</v>
+        <v>10.3345565795898</v>
       </c>
       <c r="H643" t="n">
         <v>2849</v>
@@ -19103,7 +19103,7 @@
         <v>10.75</v>
       </c>
       <c r="G646" t="n">
-        <v>10.3345556259155</v>
+        <v>10.3345565795898</v>
       </c>
       <c r="H646" t="n">
         <v>6485</v>
@@ -19132,7 +19132,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G647" t="n">
-        <v>10.4787588119507</v>
+        <v>10.478759765625</v>
       </c>
       <c r="H647" t="n">
         <v>9307</v>
@@ -19306,7 +19306,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>11.6323843002319</v>
+        <v>11.6323852539062</v>
       </c>
       <c r="H653" t="n">
         <v>42790</v>
@@ -19335,7 +19335,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8246555328369</v>
+        <v>11.8246545791626</v>
       </c>
       <c r="H654" t="n">
         <v>17953</v>
@@ -19422,7 +19422,7 @@
         <v>13.25</v>
       </c>
       <c r="G657" t="n">
-        <v>12.7379417419434</v>
+        <v>12.737940788269</v>
       </c>
       <c r="H657" t="n">
         <v>14875</v>
@@ -19480,7 +19480,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>12.930212020874</v>
+        <v>12.9302129745483</v>
       </c>
       <c r="H659" t="n">
         <v>22441</v>
@@ -19654,7 +19654,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>12.6418037414551</v>
+        <v>12.6418056488037</v>
       </c>
       <c r="H665" t="n">
         <v>5141</v>
@@ -19828,7 +19828,7 @@
         <v>13.25</v>
       </c>
       <c r="G671" t="n">
-        <v>12.7379417419434</v>
+        <v>12.737940788269</v>
       </c>
       <c r="H671" t="n">
         <v>2438</v>
@@ -19857,7 +19857,7 @@
         <v>13.25</v>
       </c>
       <c r="G672" t="n">
-        <v>12.7379417419434</v>
+        <v>12.737940788269</v>
       </c>
       <c r="H672" t="n">
         <v>6340</v>
@@ -19886,7 +19886,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G673" t="n">
-        <v>13.0263481140137</v>
+        <v>13.0263471603394</v>
       </c>
       <c r="H673" t="n">
         <v>14959</v>
@@ -19944,7 +19944,7 @@
         <v>14.5</v>
       </c>
       <c r="G675" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396352767944</v>
       </c>
       <c r="H675" t="n">
         <v>5327</v>
@@ -19973,7 +19973,7 @@
         <v>14.5</v>
       </c>
       <c r="G676" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396352767944</v>
       </c>
       <c r="H676" t="n">
         <v>16748</v>
@@ -20002,7 +20002,7 @@
         <v>14.5</v>
       </c>
       <c r="G677" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396352767944</v>
       </c>
       <c r="H677" t="n">
         <v>8967</v>
@@ -20031,7 +20031,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H678" t="n">
         <v>14525</v>
@@ -20060,7 +20060,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>13.795431137085</v>
+        <v>13.7954320907593</v>
       </c>
       <c r="H679" t="n">
         <v>3476</v>
@@ -20118,7 +20118,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>13.6512269973755</v>
+        <v>13.6512279510498</v>
       </c>
       <c r="H681" t="n">
         <v>21605</v>
@@ -20147,7 +20147,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H682" t="n">
         <v>8370</v>
@@ -20176,7 +20176,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838375091553</v>
       </c>
       <c r="H683" t="n">
         <v>12362</v>
@@ -20263,7 +20263,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G686" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838375091553</v>
       </c>
       <c r="H686" t="n">
         <v>12855</v>
@@ -20292,7 +20292,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G687" t="n">
-        <v>13.9877014160156</v>
+        <v>13.9877023696899</v>
       </c>
       <c r="H687" t="n">
         <v>11853</v>
@@ -20321,7 +20321,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>13.795431137085</v>
+        <v>13.7954320907593</v>
       </c>
       <c r="H688" t="n">
         <v>6328</v>
@@ -20350,7 +20350,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H689" t="n">
         <v>13501</v>
@@ -20379,7 +20379,7 @@
         <v>14.5</v>
       </c>
       <c r="G690" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396352767944</v>
       </c>
       <c r="H690" t="n">
         <v>26199</v>
@@ -20408,7 +20408,7 @@
         <v>14.5</v>
       </c>
       <c r="G691" t="n">
-        <v>13.9396343231201</v>
+        <v>13.9396352767944</v>
       </c>
       <c r="H691" t="n">
         <v>5887</v>
@@ -20437,7 +20437,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H692" t="n">
         <v>7855</v>
@@ -20466,7 +20466,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>13.891565322876</v>
+        <v>13.8915662765503</v>
       </c>
       <c r="H693" t="n">
         <v>3250</v>
@@ -20495,7 +20495,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>13.8434982299805</v>
+        <v>13.8434972763062</v>
       </c>
       <c r="H694" t="n">
         <v>3277</v>
@@ -20524,7 +20524,7 @@
         <v>14.25</v>
       </c>
       <c r="G695" t="n">
-        <v>13.6992969512939</v>
+        <v>13.6992959976196</v>
       </c>
       <c r="H695" t="n">
         <v>3752</v>
@@ -20669,7 +20669,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>13.7473630905151</v>
+        <v>13.7473621368408</v>
       </c>
       <c r="H700" t="n">
         <v>2077</v>
@@ -20698,7 +20698,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G701" t="n">
-        <v>13.7473630905151</v>
+        <v>13.7473621368408</v>
       </c>
       <c r="H701" t="n">
         <v>6476</v>
@@ -20727,7 +20727,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>13.9877014160156</v>
+        <v>13.9877023696899</v>
       </c>
       <c r="H702" t="n">
         <v>3584</v>
@@ -20756,7 +20756,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838375091553</v>
       </c>
       <c r="H703" t="n">
         <v>1315</v>
@@ -20785,7 +20785,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G704" t="n">
-        <v>14.083836555481</v>
+        <v>14.0838375091553</v>
       </c>
       <c r="H704" t="n">
         <v>8696</v>
@@ -20814,7 +20814,7 @@
         <v>14.75</v>
       </c>
       <c r="G705" t="n">
-        <v>14.1799726486206</v>
+        <v>14.1799716949463</v>
       </c>
       <c r="H705" t="n">
         <v>1719</v>
@@ -20872,7 +20872,7 @@
         <v>15.5</v>
       </c>
       <c r="G707" t="n">
-        <v>14.9415063858032</v>
+        <v>14.9415082931519</v>
       </c>
       <c r="H707" t="n">
         <v>14252</v>
@@ -20901,7 +20901,7 @@
         <v>15.5</v>
       </c>
       <c r="G708" t="n">
-        <v>14.9415063858032</v>
+        <v>14.9415082931519</v>
       </c>
       <c r="H708" t="n">
         <v>5682</v>
@@ -20959,7 +20959,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G710" t="n">
-        <v>15.8090791702271</v>
+        <v>15.8090782165527</v>
       </c>
       <c r="H710" t="n">
         <v>17022</v>
@@ -20988,7 +20988,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>15.8090791702271</v>
+        <v>15.8090782165527</v>
       </c>
       <c r="H711" t="n">
         <v>27543</v>
@@ -21046,7 +21046,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G713" t="n">
-        <v>16.6766471862793</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H713" t="n">
         <v>15283</v>
@@ -21191,7 +21191,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>17.0140399932861</v>
+        <v>17.0140380859375</v>
       </c>
       <c r="H718" t="n">
         <v>8516</v>
@@ -21249,7 +21249,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>16.7248497009277</v>
+        <v>16.7248477935791</v>
       </c>
       <c r="H720" t="n">
         <v>9012</v>
@@ -21278,7 +21278,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>16.8212451934814</v>
+        <v>16.8212490081787</v>
       </c>
       <c r="H721" t="n">
         <v>6464</v>
@@ -21336,7 +21336,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838581085205</v>
       </c>
       <c r="H723" t="n">
         <v>4063</v>
@@ -21423,7 +21423,7 @@
         <v>16.5</v>
       </c>
       <c r="G726" t="n">
-        <v>15.9054756164551</v>
+        <v>15.9054746627808</v>
       </c>
       <c r="H726" t="n">
         <v>13151</v>
@@ -21568,7 +21568,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838581085205</v>
       </c>
       <c r="H731" t="n">
         <v>7493</v>
@@ -21597,7 +21597,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838581085205</v>
       </c>
       <c r="H732" t="n">
         <v>8992</v>
@@ -21655,7 +21655,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>16.1946640014648</v>
+        <v>16.1946659088135</v>
       </c>
       <c r="H734" t="n">
         <v>4299</v>
@@ -21684,7 +21684,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>16.0982704162598</v>
+        <v>16.0982685089111</v>
       </c>
       <c r="H735" t="n">
         <v>2046</v>
@@ -21713,7 +21713,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>16.1946640014648</v>
+        <v>16.1946659088135</v>
       </c>
       <c r="H736" t="n">
         <v>11338</v>
@@ -21742,7 +21742,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>16.2428684234619</v>
+        <v>16.2428665161133</v>
       </c>
       <c r="H737" t="n">
         <v>1646</v>
@@ -21800,7 +21800,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>16.0982704162598</v>
+        <v>16.0982685089111</v>
       </c>
       <c r="H739" t="n">
         <v>6854</v>
@@ -21916,7 +21916,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>15.8090791702271</v>
+        <v>15.8090782165527</v>
       </c>
       <c r="H743" t="n">
         <v>1158</v>
@@ -22061,7 +22061,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G748" t="n">
-        <v>14.8933095932007</v>
+        <v>14.8933086395264</v>
       </c>
       <c r="H748" t="n">
         <v>21708</v>
@@ -22119,7 +22119,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G750" t="n">
-        <v>14.8933095932007</v>
+        <v>14.8933086395264</v>
       </c>
       <c r="H750" t="n">
         <v>4468</v>
@@ -22322,7 +22322,7 @@
         <v>16.25</v>
       </c>
       <c r="G757" t="n">
-        <v>15.6644830703735</v>
+        <v>15.6644840240479</v>
       </c>
       <c r="H757" t="n">
         <v>2755</v>
@@ -22351,7 +22351,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G758" t="n">
-        <v>15.8572769165039</v>
+        <v>15.8572778701782</v>
       </c>
       <c r="H758" t="n">
         <v>5944</v>
@@ -22380,7 +22380,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>15.7126798629761</v>
+        <v>15.7126817703247</v>
       </c>
       <c r="H759" t="n">
         <v>3425</v>
@@ -22409,7 +22409,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162853240967</v>
       </c>
       <c r="H760" t="n">
         <v>1154</v>
@@ -22467,7 +22467,7 @@
         <v>16.25</v>
       </c>
       <c r="G762" t="n">
-        <v>15.6644830703735</v>
+        <v>15.6644840240479</v>
       </c>
       <c r="H762" t="n">
         <v>3876</v>
@@ -22525,7 +22525,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G764" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162853240967</v>
       </c>
       <c r="H764" t="n">
         <v>3926</v>
@@ -22554,7 +22554,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>15.8090791702271</v>
+        <v>15.8090782165527</v>
       </c>
       <c r="H765" t="n">
         <v>2799</v>
@@ -22583,7 +22583,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G766" t="n">
-        <v>15.616286277771</v>
+        <v>15.6162853240967</v>
       </c>
       <c r="H766" t="n">
         <v>1970</v>
@@ -22670,7 +22670,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G769" t="n">
-        <v>15.5680875778198</v>
+        <v>15.5680866241455</v>
       </c>
       <c r="H769" t="n">
         <v>1915</v>
@@ -22728,7 +22728,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G771" t="n">
-        <v>17.0622386932373</v>
+        <v>17.0622406005859</v>
       </c>
       <c r="H771" t="n">
         <v>21378</v>
@@ -22815,7 +22815,7 @@
         <v>18</v>
       </c>
       <c r="G774" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H774" t="n">
         <v>18784</v>
@@ -22873,7 +22873,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>16.7248497009277</v>
+        <v>16.7248477935791</v>
       </c>
       <c r="H776" t="n">
         <v>31211</v>
@@ -22902,7 +22902,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>17.1586322784424</v>
+        <v>17.158634185791</v>
       </c>
       <c r="H777" t="n">
         <v>3670</v>
@@ -22931,7 +22931,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G778" t="n">
-        <v>16.8212451934814</v>
+        <v>16.8212490081787</v>
       </c>
       <c r="H778" t="n">
         <v>8752</v>
@@ -22960,7 +22960,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G779" t="n">
-        <v>16.6766471862793</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H779" t="n">
         <v>2108</v>
@@ -22989,7 +22989,7 @@
         <v>17.5</v>
       </c>
       <c r="G780" t="n">
-        <v>16.8694458007812</v>
+        <v>16.8694438934326</v>
       </c>
       <c r="H780" t="n">
         <v>7917</v>
@@ -23018,7 +23018,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>16.6766471862793</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H781" t="n">
         <v>1807</v>
@@ -23047,7 +23047,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G782" t="n">
-        <v>16.7730464935303</v>
+        <v>16.7730484008789</v>
       </c>
       <c r="H782" t="n">
         <v>1829</v>
@@ -23076,7 +23076,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G783" t="n">
-        <v>16.6766471862793</v>
+        <v>16.6766490936279</v>
       </c>
       <c r="H783" t="n">
         <v>1355</v>
@@ -23105,7 +23105,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>16.532054901123</v>
+        <v>16.5320568084717</v>
       </c>
       <c r="H784" t="n">
         <v>2334</v>
@@ -23134,7 +23134,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G785" t="n">
-        <v>16.4838562011719</v>
+        <v>16.4838581085205</v>
       </c>
       <c r="H785" t="n">
         <v>3050</v>
@@ -23163,7 +23163,7 @@
         <v>17.5</v>
       </c>
       <c r="G786" t="n">
-        <v>16.8694458007812</v>
+        <v>16.8694438934326</v>
       </c>
       <c r="H786" t="n">
         <v>5398</v>
@@ -23366,7 +23366,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>17.1586322784424</v>
+        <v>17.158634185791</v>
       </c>
       <c r="H793" t="n">
         <v>1275</v>
@@ -23424,7 +23424,7 @@
         <v>17.75</v>
       </c>
       <c r="G795" t="n">
-        <v>17.1104335784912</v>
+        <v>17.1104354858398</v>
       </c>
       <c r="H795" t="n">
         <v>2578</v>
@@ -23482,7 +23482,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>17.0622386932373</v>
+        <v>17.0622406005859</v>
       </c>
       <c r="H797" t="n">
         <v>4120</v>
@@ -23511,7 +23511,7 @@
         <v>17.5</v>
       </c>
       <c r="G798" t="n">
-        <v>16.8694458007812</v>
+        <v>16.8694438934326</v>
       </c>
       <c r="H798" t="n">
         <v>17956</v>
@@ -23540,7 +23540,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G799" t="n">
-        <v>17.0140399932861</v>
+        <v>17.0140380859375</v>
       </c>
       <c r="H799" t="n">
         <v>2123</v>
@@ -23627,7 +23627,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262088775635</v>
       </c>
       <c r="H802" t="n">
         <v>18762</v>
@@ -23656,7 +23656,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G803" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H803" t="n">
         <v>13681</v>
@@ -23685,7 +23685,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>18.7009830474854</v>
+        <v>18.700984954834</v>
       </c>
       <c r="H804" t="n">
         <v>25471</v>
@@ -23917,7 +23917,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262088775635</v>
       </c>
       <c r="H812" t="n">
         <v>21969</v>
@@ -23946,7 +23946,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H813" t="n">
         <v>3298</v>
@@ -24062,7 +24062,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H817" t="n">
         <v>6913</v>
@@ -24091,7 +24091,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>18.2190017700195</v>
+        <v>18.2189979553223</v>
       </c>
       <c r="H818" t="n">
         <v>9888</v>
@@ -24149,7 +24149,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G820" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H820" t="n">
         <v>5621</v>
@@ -24178,7 +24178,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>17.978006362915</v>
+        <v>17.9780082702637</v>
       </c>
       <c r="H821" t="n">
         <v>10417</v>
@@ -24207,7 +24207,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262088775635</v>
       </c>
       <c r="H822" t="n">
         <v>2366</v>
@@ -24236,7 +24236,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H823" t="n">
         <v>7777</v>
@@ -24294,7 +24294,7 @@
         <v>18.75</v>
       </c>
       <c r="G825" t="n">
-        <v>18.0744037628174</v>
+        <v>18.074405670166</v>
       </c>
       <c r="H825" t="n">
         <v>9281</v>
@@ -24410,7 +24410,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G829" t="n">
-        <v>18.1225986480713</v>
+        <v>18.1226005554199</v>
       </c>
       <c r="H829" t="n">
         <v>10298</v>
@@ -24526,7 +24526,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G833" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H833" t="n">
         <v>4556</v>
@@ -24642,7 +24642,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406154632568</v>
       </c>
       <c r="H837" t="n">
         <v>40035</v>
@@ -24671,7 +24671,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262088775635</v>
       </c>
       <c r="H838" t="n">
         <v>3812</v>
@@ -24729,7 +24729,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406154632568</v>
       </c>
       <c r="H840" t="n">
         <v>3485</v>
@@ -24816,7 +24816,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406154632568</v>
       </c>
       <c r="H843" t="n">
         <v>11897</v>
@@ -24874,7 +24874,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262088775635</v>
       </c>
       <c r="H845" t="n">
         <v>13179</v>
@@ -24903,7 +24903,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>17.6406173706055</v>
+        <v>17.6406154632568</v>
       </c>
       <c r="H846" t="n">
         <v>2528</v>
@@ -25019,7 +25019,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>17.4960250854492</v>
+        <v>17.4960231781006</v>
       </c>
       <c r="H850" t="n">
         <v>4446</v>
@@ -25048,7 +25048,7 @@
         <v>18</v>
       </c>
       <c r="G851" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H851" t="n">
         <v>8735</v>
@@ -25106,7 +25106,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G853" t="n">
-        <v>17.978006362915</v>
+        <v>17.9780082702637</v>
       </c>
       <c r="H853" t="n">
         <v>12579</v>
@@ -25164,7 +25164,7 @@
         <v>18</v>
       </c>
       <c r="G855" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H855" t="n">
         <v>6014</v>
@@ -25193,7 +25193,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>17.785213470459</v>
+        <v>17.7852153778076</v>
       </c>
       <c r="H856" t="n">
         <v>3767</v>
@@ -25222,7 +25222,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>17.9298095703125</v>
+        <v>17.9298076629639</v>
       </c>
       <c r="H857" t="n">
         <v>5075</v>
@@ -25280,7 +25280,7 @@
         <v>18.25</v>
       </c>
       <c r="G859" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H859" t="n">
         <v>5378</v>
@@ -25309,7 +25309,7 @@
         <v>18.25</v>
       </c>
       <c r="G860" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H860" t="n">
         <v>2515</v>
@@ -25367,7 +25367,7 @@
         <v>18</v>
       </c>
       <c r="G862" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H862" t="n">
         <v>16638</v>
@@ -25396,7 +25396,7 @@
         <v>18</v>
       </c>
       <c r="G863" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H863" t="n">
         <v>2051</v>
@@ -25483,7 +25483,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G866" t="n">
-        <v>17.4960250854492</v>
+        <v>17.4960231781006</v>
       </c>
       <c r="H866" t="n">
         <v>1387</v>
@@ -25541,7 +25541,7 @@
         <v>18</v>
       </c>
       <c r="G868" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H868" t="n">
         <v>4952</v>
@@ -25570,7 +25570,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>17.978006362915</v>
+        <v>17.9780082702637</v>
       </c>
       <c r="H869" t="n">
         <v>11422</v>
@@ -25599,7 +25599,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G870" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262088775635</v>
       </c>
       <c r="H870" t="n">
         <v>13461</v>
@@ -25628,7 +25628,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>18.1225986480713</v>
+        <v>18.1226005554199</v>
       </c>
       <c r="H871" t="n">
         <v>11848</v>
@@ -25715,7 +25715,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G874" t="n">
-        <v>18.2671985626221</v>
+        <v>18.2672004699707</v>
       </c>
       <c r="H874" t="n">
         <v>1553</v>
@@ -25773,7 +25773,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G876" t="n">
-        <v>17.9298095703125</v>
+        <v>17.9298076629639</v>
       </c>
       <c r="H876" t="n">
         <v>7398</v>
@@ -25802,7 +25802,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G877" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262088775635</v>
       </c>
       <c r="H877" t="n">
         <v>4339</v>
@@ -25831,7 +25831,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G878" t="n">
-        <v>18.2190017700195</v>
+        <v>18.2189979553223</v>
       </c>
       <c r="H878" t="n">
         <v>579</v>
@@ -25918,7 +25918,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>19.1829681396484</v>
+        <v>19.1829662322998</v>
       </c>
       <c r="H881" t="n">
         <v>10787</v>
@@ -25976,7 +25976,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G883" t="n">
-        <v>18.8455791473389</v>
+        <v>18.8455772399902</v>
       </c>
       <c r="H883" t="n">
         <v>9754</v>
@@ -26005,7 +26005,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G884" t="n">
-        <v>18.0262069702148</v>
+        <v>18.0262088775635</v>
       </c>
       <c r="H884" t="n">
         <v>23659</v>
@@ -26034,7 +26034,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>18.4599933624268</v>
+        <v>18.4599895477295</v>
       </c>
       <c r="H885" t="n">
         <v>4951</v>
@@ -26063,7 +26063,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G886" t="n">
-        <v>18.8455791473389</v>
+        <v>18.8455772399902</v>
       </c>
       <c r="H886" t="n">
         <v>2844</v>
@@ -26092,7 +26092,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G887" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H887" t="n">
         <v>9206</v>
@@ -26121,7 +26121,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G888" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H888" t="n">
         <v>4533</v>
@@ -26150,7 +26150,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>18.9901733398438</v>
+        <v>18.9901752471924</v>
       </c>
       <c r="H889" t="n">
         <v>10126</v>
@@ -26208,7 +26208,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G891" t="n">
-        <v>18.1225986480713</v>
+        <v>18.1226005554199</v>
       </c>
       <c r="H891" t="n">
         <v>10241</v>
@@ -26295,7 +26295,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G894" t="n">
-        <v>17.0140399932861</v>
+        <v>17.0140380859375</v>
       </c>
       <c r="H894" t="n">
         <v>15135</v>
@@ -26324,7 +26324,7 @@
         <v>17.25</v>
       </c>
       <c r="G895" t="n">
-        <v>16.6284523010254</v>
+        <v>16.6284503936768</v>
       </c>
       <c r="H895" t="n">
         <v>10256</v>
@@ -26353,7 +26353,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G896" t="n">
-        <v>17.4960250854492</v>
+        <v>17.4960231781006</v>
       </c>
       <c r="H896" t="n">
         <v>3633</v>
@@ -26382,7 +26382,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G897" t="n">
-        <v>17.4960250854492</v>
+        <v>17.4960231781006</v>
       </c>
       <c r="H897" t="n">
         <v>4176</v>
@@ -26440,7 +26440,7 @@
         <v>18.25</v>
       </c>
       <c r="G899" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H899" t="n">
         <v>4107</v>
@@ -26469,7 +26469,7 @@
         <v>18.25</v>
       </c>
       <c r="G900" t="n">
-        <v>17.5924224853516</v>
+        <v>17.5924205780029</v>
       </c>
       <c r="H900" t="n">
         <v>1122</v>
@@ -26556,7 +26556,7 @@
         <v>18</v>
       </c>
       <c r="G903" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H903" t="n">
         <v>11215</v>
@@ -26701,7 +26701,7 @@
         <v>18</v>
       </c>
       <c r="G908" t="n">
-        <v>17.3514270782471</v>
+        <v>17.3514289855957</v>
       </c>
       <c r="H908" t="n">
         <v>4431</v>
@@ -26730,7 +26730,7 @@
         <v>17.5</v>
       </c>
       <c r="G909" t="n">
-        <v>16.8694458007812</v>
+        <v>16.8694438934326</v>
       </c>
       <c r="H909" t="n">
         <v>20573</v>
@@ -26759,7 +26759,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>17.0622386932373</v>
+        <v>17.0622406005859</v>
       </c>
       <c r="H910" t="n">
         <v>5430</v>
@@ -26788,7 +26788,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>16.8212451934814</v>
+        <v>16.8212490081787</v>
       </c>
       <c r="H911" t="n">
         <v>2833</v>
@@ -26846,7 +26846,7 @@
         <v>16.5</v>
       </c>
       <c r="G913" t="n">
-        <v>15.9054756164551</v>
+        <v>15.9054746627808</v>
       </c>
       <c r="H913" t="n">
         <v>13709</v>
@@ -26962,7 +26962,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G917" t="n">
-        <v>14.6523170471191</v>
+        <v>14.6523180007935</v>
       </c>
       <c r="H917" t="n">
         <v>28900</v>
@@ -26991,7 +26991,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G918" t="n">
-        <v>15.3270959854126</v>
+        <v>15.327094078064</v>
       </c>
       <c r="H918" t="n">
         <v>18627</v>
@@ -27020,7 +27020,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G919" t="n">
-        <v>15.3270959854126</v>
+        <v>15.327094078064</v>
       </c>
       <c r="H919" t="n">
         <v>1224</v>
@@ -27049,7 +27049,7 @@
         <v>15.5</v>
       </c>
       <c r="G920" t="n">
-        <v>14.9415063858032</v>
+        <v>14.9415082931519</v>
       </c>
       <c r="H920" t="n">
         <v>1828</v>
@@ -27107,7 +27107,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>14.2667303085327</v>
+        <v>14.2667293548584</v>
       </c>
       <c r="H922" t="n">
         <v>4153</v>
@@ -27136,7 +27136,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>13.9293413162231</v>
+        <v>13.9293403625488</v>
       </c>
       <c r="H923" t="n">
         <v>23249</v>
@@ -27165,7 +27165,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G924" t="n">
-        <v>12.9653720855713</v>
+        <v>12.9653730392456</v>
       </c>
       <c r="H924" t="n">
         <v>18799</v>
@@ -27252,7 +27252,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G927" t="n">
-        <v>15.7126798629761</v>
+        <v>15.7126817703247</v>
       </c>
       <c r="H927" t="n">
         <v>5052</v>
@@ -27281,7 +27281,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G928" t="n">
-        <v>16.0018749237061</v>
+        <v>16.0018730163574</v>
       </c>
       <c r="H928" t="n">
         <v>8969</v>
@@ -27310,7 +27310,7 @@
         <v>16.5</v>
       </c>
       <c r="G929" t="n">
-        <v>15.9054756164551</v>
+        <v>15.9054746627808</v>
       </c>
       <c r="H929" t="n">
         <v>13874</v>
@@ -27368,7 +27368,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>16.1946640014648</v>
+        <v>16.1946659088135</v>
       </c>
       <c r="H931" t="n">
         <v>10440</v>
@@ -27397,7 +27397,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G932" t="n">
-        <v>15.7126798629761</v>
+        <v>15.7126817703247</v>
       </c>
       <c r="H932" t="n">
         <v>17688</v>
@@ -27484,7 +27484,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>15.0861024856567</v>
+        <v>15.0861034393311</v>
       </c>
       <c r="H935" t="n">
         <v>1447</v>
@@ -27542,7 +27542,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G937" t="n">
-        <v>14.4113245010376</v>
+        <v>14.4113254547119</v>
       </c>
       <c r="H937" t="n">
         <v>8814</v>
@@ -27600,7 +27600,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>15.3270959854126</v>
+        <v>15.327094078064</v>
       </c>
       <c r="H939" t="n">
         <v>9151</v>
@@ -27658,7 +27658,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G941" t="n">
-        <v>15.0861024856567</v>
+        <v>15.0861034393311</v>
       </c>
       <c r="H941" t="n">
         <v>1106</v>
@@ -27832,7 +27832,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G947" t="n">
-        <v>15.0861024856567</v>
+        <v>15.0861034393311</v>
       </c>
       <c r="H947" t="n">
         <v>723</v>
@@ -27890,7 +27890,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>14.6523170471191</v>
+        <v>14.6523180007935</v>
       </c>
       <c r="H949" t="n">
         <v>2874</v>
@@ -27919,7 +27919,7 @@
         <v>15</v>
       </c>
       <c r="G950" t="n">
-        <v>14.4595241546631</v>
+        <v>14.4595232009888</v>
       </c>
       <c r="H950" t="n">
         <v>8299</v>
@@ -27948,7 +27948,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>14.5077219009399</v>
+        <v>14.5077228546143</v>
       </c>
       <c r="H951" t="n">
         <v>1374</v>
@@ -27977,7 +27977,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G952" t="n">
-        <v>14.6041193008423</v>
+        <v>14.6041173934937</v>
       </c>
       <c r="H952" t="n">
         <v>902</v>
@@ -28064,7 +28064,7 @@
         <v>15</v>
       </c>
       <c r="G955" t="n">
-        <v>14.4595241546631</v>
+        <v>14.4595232009888</v>
       </c>
       <c r="H955" t="n">
         <v>3589</v>
@@ -28093,7 +28093,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>14.4113245010376</v>
+        <v>14.4113254547119</v>
       </c>
       <c r="H956" t="n">
         <v>257</v>
@@ -28122,7 +28122,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G957" t="n">
-        <v>14.2667303085327</v>
+        <v>14.2667293548584</v>
       </c>
       <c r="H957" t="n">
         <v>1640</v>
@@ -28180,7 +28180,7 @@
         <v>14.5</v>
       </c>
       <c r="G959" t="n">
-        <v>13.9775390625</v>
+        <v>13.9775400161743</v>
       </c>
       <c r="H959" t="n">
         <v>3572</v>
@@ -28238,7 +28238,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G961" t="n">
-        <v>13.6883478164673</v>
+        <v>13.6883487701416</v>
       </c>
       <c r="H961" t="n">
         <v>1030</v>
@@ -28267,7 +28267,7 @@
         <v>14.5</v>
       </c>
       <c r="G962" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H962" t="n">
         <v>2889</v>
@@ -28325,7 +28325,7 @@
         <v>13.75</v>
       </c>
       <c r="G964" t="n">
-        <v>13.3108062744141</v>
+        <v>13.3108053207397</v>
       </c>
       <c r="H964" t="n">
         <v>5846</v>
@@ -28354,7 +28354,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G965" t="n">
-        <v>13.8432397842407</v>
+        <v>13.8432378768921</v>
       </c>
       <c r="H965" t="n">
         <v>8715</v>
@@ -28383,7 +28383,7 @@
         <v>14.5</v>
       </c>
       <c r="G966" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H966" t="n">
         <v>868</v>
@@ -28557,7 +28557,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G972" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H972" t="n">
         <v>4243</v>
@@ -28615,7 +28615,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G974" t="n">
-        <v>14.4240732192993</v>
+        <v>14.4240741729736</v>
       </c>
       <c r="H974" t="n">
         <v>383</v>
@@ -28644,7 +28644,7 @@
         <v>15</v>
       </c>
       <c r="G975" t="n">
-        <v>14.5208787918091</v>
+        <v>14.5208797454834</v>
       </c>
       <c r="H975" t="n">
         <v>901</v>
@@ -28673,7 +28673,7 @@
         <v>14.75</v>
       </c>
       <c r="G976" t="n">
-        <v>14.2788648605347</v>
+        <v>14.278865814209</v>
       </c>
       <c r="H976" t="n">
         <v>14175</v>
@@ -28760,7 +28760,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G979" t="n">
-        <v>13.1171951293945</v>
+        <v>13.1171941757202</v>
       </c>
       <c r="H979" t="n">
         <v>6255</v>
@@ -28818,7 +28818,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G981" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H981" t="n">
         <v>13144</v>
@@ -28847,7 +28847,7 @@
         <v>15.75</v>
       </c>
       <c r="G982" t="n">
-        <v>15.2469234466553</v>
+        <v>15.2469244003296</v>
       </c>
       <c r="H982" t="n">
         <v>13824</v>
@@ -29050,7 +29050,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G989" t="n">
-        <v>15.0533132553101</v>
+        <v>15.0533113479614</v>
       </c>
       <c r="H989" t="n">
         <v>3452</v>
@@ -29079,7 +29079,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G990" t="n">
-        <v>14.6660890579224</v>
+        <v>14.6660871505737</v>
       </c>
       <c r="H990" t="n">
         <v>6059</v>
@@ -29108,7 +29108,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>14.4240732192993</v>
+        <v>14.4240741729736</v>
       </c>
       <c r="H991" t="n">
         <v>571</v>
@@ -29195,7 +29195,7 @@
         <v>14.75</v>
       </c>
       <c r="G994" t="n">
-        <v>14.2788648605347</v>
+        <v>14.278865814209</v>
       </c>
       <c r="H994" t="n">
         <v>2029</v>
@@ -29253,7 +29253,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G996" t="n">
-        <v>13.8432397842407</v>
+        <v>13.8432378768921</v>
       </c>
       <c r="H996" t="n">
         <v>1347</v>
@@ -29456,7 +29456,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.6980295181274</v>
+        <v>13.6980304718018</v>
       </c>
       <c r="H1003" t="n">
         <v>1271</v>
@@ -29485,7 +29485,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.6980295181274</v>
+        <v>13.6980304718018</v>
       </c>
       <c r="H1004" t="n">
         <v>0</v>
@@ -29717,7 +29717,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>13.1655979156494</v>
+        <v>13.1655969619751</v>
       </c>
       <c r="H1012" t="n">
         <v>3407</v>
@@ -29775,7 +29775,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>13.1655979156494</v>
+        <v>13.1655969619751</v>
       </c>
       <c r="H1014" t="n">
         <v>1001</v>
@@ -29833,7 +29833,7 @@
         <v>13.25</v>
       </c>
       <c r="G1016" t="n">
-        <v>12.8267765045166</v>
+        <v>12.8267774581909</v>
       </c>
       <c r="H1016" t="n">
         <v>8091</v>
@@ -29862,7 +29862,7 @@
         <v>13.25</v>
       </c>
       <c r="G1017" t="n">
-        <v>12.8267765045166</v>
+        <v>12.8267774581909</v>
       </c>
       <c r="H1017" t="n">
         <v>1410</v>
@@ -29891,7 +29891,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1018" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1018" t="n">
         <v>722</v>
@@ -29949,7 +29949,7 @@
         <v>12.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.1007328033447</v>
+        <v>12.1007318496704</v>
       </c>
       <c r="H1020" t="n">
         <v>1200</v>
@@ -30065,7 +30065,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1024" t="n">
-        <v>12.2459421157837</v>
+        <v>12.2459411621094</v>
       </c>
       <c r="H1024" t="n">
         <v>352</v>
@@ -30094,7 +30094,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1025" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1025" t="n">
         <v>427</v>
@@ -30123,7 +30123,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.7783737182617</v>
+        <v>12.778374671936</v>
       </c>
       <c r="H1026" t="n">
         <v>3409</v>
@@ -30152,7 +30152,7 @@
         <v>13.75</v>
       </c>
       <c r="G1027" t="n">
-        <v>13.3108062744141</v>
+        <v>13.3108053207397</v>
       </c>
       <c r="H1027" t="n">
         <v>2689</v>
@@ -30181,7 +30181,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1028" t="n">
-        <v>13.456015586853</v>
+        <v>13.4560146331787</v>
       </c>
       <c r="H1028" t="n">
         <v>3899</v>
@@ -30239,7 +30239,7 @@
         <v>14.5</v>
       </c>
       <c r="G1030" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1030" t="n">
         <v>2981</v>
@@ -30297,7 +30297,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1032" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H1032" t="n">
         <v>1379</v>
@@ -30355,7 +30355,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>14.3756713867188</v>
+        <v>14.3756723403931</v>
       </c>
       <c r="H1034" t="n">
         <v>412</v>
@@ -30384,7 +30384,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1035" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H1035" t="n">
         <v>1610</v>
@@ -30413,7 +30413,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1036" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1036" t="n">
         <v>501</v>
@@ -30442,7 +30442,7 @@
         <v>15</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.5208787918091</v>
+        <v>14.5208797454834</v>
       </c>
       <c r="H1037" t="n">
         <v>947</v>
@@ -30471,7 +30471,7 @@
         <v>14.75</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.2788648605347</v>
+        <v>14.278865814209</v>
       </c>
       <c r="H1038" t="n">
         <v>159</v>
@@ -30500,7 +30500,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H1039" t="n">
         <v>2364</v>
@@ -30558,7 +30558,7 @@
         <v>15</v>
       </c>
       <c r="G1041" t="n">
-        <v>14.5208787918091</v>
+        <v>14.5208797454834</v>
       </c>
       <c r="H1041" t="n">
         <v>73</v>
@@ -30587,7 +30587,7 @@
         <v>15</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.5208787918091</v>
+        <v>14.5208797454834</v>
       </c>
       <c r="H1042" t="n">
         <v>2826</v>
@@ -30616,7 +30616,7 @@
         <v>14.75</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.2788648605347</v>
+        <v>14.278865814209</v>
       </c>
       <c r="H1043" t="n">
         <v>2123</v>
@@ -30732,7 +30732,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1047" t="n">
         <v>1102</v>
@@ -30761,7 +30761,7 @@
         <v>14.5</v>
       </c>
       <c r="G1048" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1048" t="n">
         <v>5163</v>
@@ -31167,7 +31167,7 @@
         <v>13.5</v>
       </c>
       <c r="G1062" t="n">
-        <v>13.0687923431396</v>
+        <v>13.0687913894653</v>
       </c>
       <c r="H1062" t="n">
         <v>3440</v>
@@ -31196,7 +31196,7 @@
         <v>13.5</v>
       </c>
       <c r="G1063" t="n">
-        <v>13.0687923431396</v>
+        <v>13.0687913894653</v>
       </c>
       <c r="H1063" t="n">
         <v>0</v>
@@ -31225,7 +31225,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1064" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1064" t="n">
         <v>285</v>
@@ -31283,7 +31283,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1066" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1066" t="n">
         <v>4351</v>
@@ -31341,7 +31341,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1068" t="n">
-        <v>12.2459421157837</v>
+        <v>12.2459411621094</v>
       </c>
       <c r="H1068" t="n">
         <v>4296</v>
@@ -31428,7 +31428,7 @@
         <v>12.25</v>
       </c>
       <c r="G1071" t="n">
-        <v>11.8587198257446</v>
+        <v>11.8587188720703</v>
       </c>
       <c r="H1071" t="n">
         <v>1155</v>
@@ -31544,7 +31544,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1075" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1075" t="n">
         <v>415</v>
@@ -31573,7 +31573,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1076" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1076" t="n">
         <v>300</v>
@@ -31602,7 +31602,7 @@
         <v>13.25</v>
       </c>
       <c r="G1077" t="n">
-        <v>12.8267765045166</v>
+        <v>12.8267774581909</v>
       </c>
       <c r="H1077" t="n">
         <v>1125</v>
@@ -31631,7 +31631,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1078" t="n">
-        <v>12.536358833313</v>
+        <v>12.5363597869873</v>
       </c>
       <c r="H1078" t="n">
         <v>284</v>
@@ -31689,7 +31689,7 @@
         <v>13.25</v>
       </c>
       <c r="G1080" t="n">
-        <v>12.8267765045166</v>
+        <v>12.8267774581909</v>
       </c>
       <c r="H1080" t="n">
         <v>25204</v>
@@ -31718,7 +31718,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1081" t="n">
-        <v>12.7299699783325</v>
+        <v>12.7299709320068</v>
       </c>
       <c r="H1081" t="n">
         <v>2529</v>
@@ -31747,7 +31747,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1082" t="n">
-        <v>12.7299699783325</v>
+        <v>12.7299709320068</v>
       </c>
       <c r="H1082" t="n">
         <v>959</v>
@@ -31805,7 +31805,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1084" t="n">
-        <v>12.7783737182617</v>
+        <v>12.778374671936</v>
       </c>
       <c r="H1084" t="n">
         <v>809</v>
@@ -31921,7 +31921,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1088" t="n">
         <v>450</v>
@@ -31979,7 +31979,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1090" t="n">
-        <v>12.7783737182617</v>
+        <v>12.778374671936</v>
       </c>
       <c r="H1090" t="n">
         <v>306</v>
@@ -32008,7 +32008,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1091" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1091" t="n">
         <v>2076</v>
@@ -32066,7 +32066,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1093" t="n">
-        <v>12.536358833313</v>
+        <v>12.5363597869873</v>
       </c>
       <c r="H1093" t="n">
         <v>4420</v>
@@ -32153,7 +32153,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1096" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1096" t="n">
         <v>5161</v>
@@ -32182,7 +32182,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1097" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1097" t="n">
         <v>7158</v>
@@ -32240,7 +32240,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1099" t="n">
         <v>8687</v>
@@ -32327,7 +32327,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1102" t="n">
-        <v>12.536358833313</v>
+        <v>12.5363597869873</v>
       </c>
       <c r="H1102" t="n">
         <v>6218</v>
@@ -32414,7 +32414,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1105" t="n">
-        <v>12.2459421157837</v>
+        <v>12.2459411621094</v>
       </c>
       <c r="H1105" t="n">
         <v>7176</v>
@@ -32791,7 +32791,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1118" t="n">
-        <v>12.536358833313</v>
+        <v>12.5363597869873</v>
       </c>
       <c r="H1118" t="n">
         <v>3355</v>
@@ -32820,7 +32820,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1119" t="n">
-        <v>12.536358833313</v>
+        <v>12.5363597869873</v>
       </c>
       <c r="H1119" t="n">
         <v>610</v>
@@ -32849,7 +32849,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1120" t="n">
-        <v>12.7783737182617</v>
+        <v>12.778374671936</v>
       </c>
       <c r="H1120" t="n">
         <v>3820</v>
@@ -32878,7 +32878,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1121" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1121" t="n">
         <v>3291</v>
@@ -32907,7 +32907,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1122" t="n">
-        <v>12.9719858169556</v>
+        <v>12.9719848632812</v>
       </c>
       <c r="H1122" t="n">
         <v>24918</v>
@@ -32965,7 +32965,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1124" t="n">
-        <v>12.9719858169556</v>
+        <v>12.9719848632812</v>
       </c>
       <c r="H1124" t="n">
         <v>30157</v>
@@ -32994,7 +32994,7 @@
         <v>13.5</v>
       </c>
       <c r="G1125" t="n">
-        <v>13.0687923431396</v>
+        <v>13.0687913894653</v>
       </c>
       <c r="H1125" t="n">
         <v>3155</v>
@@ -33052,7 +33052,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1127" t="n">
-        <v>12.9719858169556</v>
+        <v>12.9719848632812</v>
       </c>
       <c r="H1127" t="n">
         <v>32113</v>
@@ -33110,7 +33110,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1129" t="n">
-        <v>13.1655979156494</v>
+        <v>13.1655969619751</v>
       </c>
       <c r="H1129" t="n">
         <v>390</v>
@@ -33139,7 +33139,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1130" t="n">
-        <v>13.1655979156494</v>
+        <v>13.1655969619751</v>
       </c>
       <c r="H1130" t="n">
         <v>1118</v>
@@ -33168,7 +33168,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1131" t="n">
-        <v>13.456015586853</v>
+        <v>13.4560146331787</v>
       </c>
       <c r="H1131" t="n">
         <v>472</v>
@@ -33197,7 +33197,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>13.456015586853</v>
+        <v>13.4560146331787</v>
       </c>
       <c r="H1132" t="n">
         <v>0</v>
@@ -33284,7 +33284,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1135" t="n">
-        <v>13.8432397842407</v>
+        <v>13.8432378768921</v>
       </c>
       <c r="H1135" t="n">
         <v>520</v>
@@ -33545,7 +33545,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1144" t="n">
-        <v>13.8432397842407</v>
+        <v>13.8432378768921</v>
       </c>
       <c r="H1144" t="n">
         <v>14356</v>
@@ -33632,7 +33632,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1147" t="n">
-        <v>14.811297416687</v>
+        <v>14.8112964630127</v>
       </c>
       <c r="H1147" t="n">
         <v>5496</v>
@@ -33661,7 +33661,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1148" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1148" t="n">
         <v>3537</v>
@@ -33748,7 +33748,7 @@
         <v>14.75</v>
       </c>
       <c r="G1151" t="n">
-        <v>14.2788648605347</v>
+        <v>14.278865814209</v>
       </c>
       <c r="H1151" t="n">
         <v>692</v>
@@ -33777,7 +33777,7 @@
         <v>14.5</v>
       </c>
       <c r="G1152" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1152" t="n">
         <v>9610</v>
@@ -33835,7 +33835,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1154" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1154" t="n">
         <v>368</v>
@@ -33864,7 +33864,7 @@
         <v>14.5</v>
       </c>
       <c r="G1155" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1155" t="n">
         <v>40</v>
@@ -33922,7 +33922,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1157" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1157" t="n">
         <v>52</v>
@@ -33951,7 +33951,7 @@
         <v>14.5</v>
       </c>
       <c r="G1158" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1158" t="n">
         <v>8289</v>
@@ -33980,7 +33980,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1159" t="n">
-        <v>14.4724760055542</v>
+        <v>14.4724769592285</v>
       </c>
       <c r="H1159" t="n">
         <v>5202</v>
@@ -34067,7 +34067,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1162" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1162" t="n">
         <v>1367</v>
@@ -34125,7 +34125,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1164" t="n">
-        <v>14.2304620742798</v>
+        <v>14.2304630279541</v>
       </c>
       <c r="H1164" t="n">
         <v>1557</v>
@@ -34154,7 +34154,7 @@
         <v>14.5</v>
       </c>
       <c r="G1165" t="n">
-        <v>14.0368499755859</v>
+        <v>14.0368509292603</v>
       </c>
       <c r="H1165" t="n">
         <v>3614</v>
@@ -34212,7 +34212,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1167" t="n">
-        <v>13.8432397842407</v>
+        <v>13.8432378768921</v>
       </c>
       <c r="H1167" t="n">
         <v>8730</v>
@@ -34328,7 +34328,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1171" t="n">
-        <v>13.8432397842407</v>
+        <v>13.8432378768921</v>
       </c>
       <c r="H1171" t="n">
         <v>1112</v>
@@ -34357,7 +34357,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1172" t="n">
-        <v>13.456015586853</v>
+        <v>13.4560146331787</v>
       </c>
       <c r="H1172" t="n">
         <v>5243</v>
@@ -34415,7 +34415,7 @@
         <v>13.75</v>
       </c>
       <c r="G1174" t="n">
-        <v>13.3108062744141</v>
+        <v>13.3108053207397</v>
       </c>
       <c r="H1174" t="n">
         <v>820</v>
@@ -34444,7 +34444,7 @@
         <v>13.75</v>
       </c>
       <c r="G1175" t="n">
-        <v>13.3108062744141</v>
+        <v>13.3108053207397</v>
       </c>
       <c r="H1175" t="n">
         <v>419</v>
@@ -34473,7 +34473,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1176" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1176" t="n">
         <v>4234</v>
@@ -34531,7 +34531,7 @@
         <v>13.5</v>
       </c>
       <c r="G1178" t="n">
-        <v>13.0687923431396</v>
+        <v>13.0687913894653</v>
       </c>
       <c r="H1178" t="n">
         <v>1750</v>
@@ -34560,7 +34560,7 @@
         <v>13.25</v>
       </c>
       <c r="G1179" t="n">
-        <v>12.8267765045166</v>
+        <v>12.8267774581909</v>
       </c>
       <c r="H1179" t="n">
         <v>270</v>
@@ -34589,7 +34589,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1180" t="n">
-        <v>12.8751792907715</v>
+        <v>12.8751802444458</v>
       </c>
       <c r="H1180" t="n">
         <v>657</v>
@@ -34618,7 +34618,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1181" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1181" t="n">
         <v>3350</v>
@@ -34647,7 +34647,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1182" t="n">
-        <v>12.923583984375</v>
+        <v>12.9235830307007</v>
       </c>
       <c r="H1182" t="n">
         <v>4712</v>
@@ -34676,7 +34676,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1183" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1183" t="n">
         <v>2281</v>
@@ -34705,7 +34705,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>12.9719858169556</v>
+        <v>12.9719848632812</v>
       </c>
       <c r="H1184" t="n">
         <v>1248</v>
@@ -34763,7 +34763,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1186" t="n">
-        <v>12.7783737182617</v>
+        <v>12.778374671936</v>
       </c>
       <c r="H1186" t="n">
         <v>1146</v>
@@ -34821,7 +34821,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1188" t="n">
         <v>3537</v>
@@ -34966,7 +34966,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1193" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1193" t="n">
         <v>2078</v>
@@ -35024,7 +35024,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>12.7783737182617</v>
+        <v>12.778374671936</v>
       </c>
       <c r="H1195" t="n">
         <v>3177</v>
@@ -35053,7 +35053,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1196" t="n">
-        <v>13.1655979156494</v>
+        <v>13.1655969619751</v>
       </c>
       <c r="H1196" t="n">
         <v>449</v>
@@ -35082,7 +35082,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1197" t="n">
-        <v>12.7783737182617</v>
+        <v>12.778374671936</v>
       </c>
       <c r="H1197" t="n">
         <v>389</v>
@@ -35111,7 +35111,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1198" t="n">
-        <v>13.1655979156494</v>
+        <v>13.1655969619751</v>
       </c>
       <c r="H1198" t="n">
         <v>781</v>
@@ -35169,7 +35169,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>13.1655979156494</v>
+        <v>13.1655969619751</v>
       </c>
       <c r="H1200" t="n">
         <v>2548</v>
@@ -35198,7 +35198,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.923583984375</v>
+        <v>12.9235830307007</v>
       </c>
       <c r="H1201" t="n">
         <v>2713</v>
@@ -35227,7 +35227,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1202" t="n">
         <v>5803</v>
@@ -35459,7 +35459,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1210" t="n">
-        <v>12.2459421157837</v>
+        <v>12.2459411621094</v>
       </c>
       <c r="H1210" t="n">
         <v>365</v>
@@ -35488,7 +35488,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1211" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1211" t="n">
         <v>361</v>
@@ -35517,7 +35517,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>12.4879560470581</v>
+        <v>12.4879570007324</v>
       </c>
       <c r="H1212" t="n">
         <v>46</v>
@@ -35604,7 +35604,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G1215" t="n">
-        <v>12.681568145752</v>
+        <v>12.6815690994263</v>
       </c>
       <c r="H1215" t="n">
         <v>39</v>
@@ -35691,7 +35691,7 @@
         <v>13.25</v>
       </c>
       <c r="G1218" t="n">
-        <v>12.8267765045166</v>
+        <v>12.8267774581909</v>
       </c>
       <c r="H1218" t="n">
         <v>481</v>
@@ -35720,7 +35720,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>12.7299699783325</v>
+        <v>12.7299709320068</v>
       </c>
       <c r="H1219" t="n">
         <v>347</v>
@@ -61275,6 +61275,35 @@
         <v>3160</v>
       </c>
       <c r="I2100" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2101" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>8.76000022888184</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>8.76000022888184</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>8.65999984741211</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>8.73999977111816</v>
+      </c>
+      <c r="G2101" t="n">
+        <v>8.73999977111816</v>
+      </c>
+      <c r="H2101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2101" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ITD.MI.xlsx
+++ b/data/ITD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G2" t="n">
-        <v>2.57321286201477</v>
+        <v>2.57321262359619</v>
       </c>
       <c r="H2" t="n">
         <v>511000</v>
@@ -485,7 +485,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H4" t="n">
         <v>233500</v>
@@ -572,7 +572,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G7" t="n">
-        <v>2.80670785903931</v>
+        <v>2.80670833587646</v>
       </c>
       <c r="H7" t="n">
         <v>71500</v>
@@ -630,7 +630,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H9" t="n">
         <v>26000</v>
@@ -717,7 +717,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G12" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H12" t="n">
         <v>7500</v>
@@ -746,7 +746,7 @@
         <v>2.98900008201599</v>
       </c>
       <c r="G13" t="n">
-        <v>2.84864187240601</v>
+        <v>2.84864211082458</v>
       </c>
       <c r="H13" t="n">
         <v>8500</v>
@@ -804,7 +804,7 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H15" t="n">
         <v>22500</v>
@@ -862,7 +862,7 @@
         <v>2.93099999427795</v>
       </c>
       <c r="G17" t="n">
-        <v>2.79336524009705</v>
+        <v>2.7933657169342</v>
       </c>
       <c r="H17" t="n">
         <v>5000</v>
@@ -891,7 +891,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G18" t="n">
-        <v>2.78764700889587</v>
+        <v>2.78764677047729</v>
       </c>
       <c r="H18" t="n">
         <v>10000</v>
@@ -920,7 +920,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>2.76382112503052</v>
+        <v>2.76382160186768</v>
       </c>
       <c r="H19" t="n">
         <v>8000</v>
@@ -949,7 +949,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G20" t="n">
-        <v>2.76382112503052</v>
+        <v>2.76382160186768</v>
       </c>
       <c r="H20" t="n">
         <v>2000</v>
@@ -978,7 +978,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G21" t="n">
-        <v>2.71616911888123</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H21" t="n">
         <v>6000</v>
@@ -1007,7 +1007,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G22" t="n">
-        <v>2.76382112503052</v>
+        <v>2.76382160186768</v>
       </c>
       <c r="H22" t="n">
         <v>6000</v>
@@ -1036,7 +1036,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.76382112503052</v>
+        <v>2.76382160186768</v>
       </c>
       <c r="H23" t="n">
         <v>3500</v>
@@ -1123,7 +1123,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G26" t="n">
-        <v>2.71616911888123</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H26" t="n">
         <v>3000</v>
@@ -1152,7 +1152,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>2.71616911888123</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H27" t="n">
         <v>5500</v>
@@ -1181,7 +1181,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.71616911888123</v>
+        <v>2.71616888046265</v>
       </c>
       <c r="H28" t="n">
         <v>3500</v>
@@ -1471,7 +1471,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G38" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H38" t="n">
         <v>17000</v>
@@ -1500,7 +1500,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G39" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H39" t="n">
         <v>21500</v>
@@ -1529,7 +1529,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G40" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H40" t="n">
         <v>20000</v>
@@ -1558,7 +1558,7 @@
         <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H41" t="n">
         <v>18500</v>
@@ -1587,7 +1587,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G42" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H42" t="n">
         <v>5500</v>
@@ -1616,7 +1616,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G43" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H43" t="n">
         <v>1000</v>
@@ -1674,7 +1674,7 @@
         <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H45" t="n">
         <v>18000</v>
@@ -1703,7 +1703,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H46" t="n">
         <v>12000</v>
@@ -1732,7 +1732,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87818646430969</v>
+        <v>2.87818574905396</v>
       </c>
       <c r="H47" t="n">
         <v>9000</v>
@@ -1761,7 +1761,7 @@
         <v>3.02049994468689</v>
       </c>
       <c r="G48" t="n">
-        <v>2.87866258621216</v>
+        <v>2.87866234779358</v>
       </c>
       <c r="H48" t="n">
         <v>4500</v>
@@ -1819,7 +1819,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H50" t="n">
         <v>13000</v>
@@ -1848,7 +1848,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G51" t="n">
-        <v>2.92583823204041</v>
+        <v>2.92583799362183</v>
       </c>
       <c r="H51" t="n">
         <v>9000</v>
@@ -1877,7 +1877,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G52" t="n">
-        <v>3.01161217689514</v>
+        <v>3.01161193847656</v>
       </c>
       <c r="H52" t="n">
         <v>15500</v>
@@ -1906,7 +1906,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.00208163261414</v>
+        <v>3.00208187103271</v>
       </c>
       <c r="H53" t="n">
         <v>58000</v>
@@ -1964,7 +1964,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>3.00208163261414</v>
+        <v>3.00208187103271</v>
       </c>
       <c r="H55" t="n">
         <v>5500</v>
@@ -1993,7 +1993,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G56" t="n">
-        <v>2.9163076877594</v>
+        <v>2.91630744934082</v>
       </c>
       <c r="H56" t="n">
         <v>16000</v>
@@ -2022,7 +2022,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H57" t="n">
         <v>2000</v>
@@ -2051,7 +2051,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G58" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H58" t="n">
         <v>9500</v>
@@ -2080,7 +2080,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>2.97348999977112</v>
+        <v>2.9734902381897</v>
       </c>
       <c r="H59" t="n">
         <v>7500</v>
@@ -2109,7 +2109,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G60" t="n">
-        <v>2.97348999977112</v>
+        <v>2.9734902381897</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2138,7 +2138,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H61" t="n">
         <v>1000</v>
@@ -2167,7 +2167,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H62" t="n">
         <v>3000</v>
@@ -2225,7 +2225,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H64" t="n">
         <v>2500</v>
@@ -2254,7 +2254,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>2.87818646430969</v>
+        <v>2.87818574905396</v>
       </c>
       <c r="H65" t="n">
         <v>4000</v>
@@ -2283,7 +2283,7 @@
         <v>2.97300004959106</v>
       </c>
       <c r="G66" t="n">
-        <v>2.83339309692383</v>
+        <v>2.83339333534241</v>
       </c>
       <c r="H66" t="n">
         <v>6000</v>
@@ -2312,7 +2312,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G67" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H67" t="n">
         <v>5000</v>
@@ -2341,7 +2341,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G68" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H68" t="n">
         <v>18500</v>
@@ -2399,7 +2399,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G70" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H70" t="n">
         <v>7500</v>
@@ -2428,7 +2428,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80670785903931</v>
+        <v>2.80670833587646</v>
       </c>
       <c r="H71" t="n">
         <v>8000</v>
@@ -2457,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H72" t="n">
         <v>7500</v>
@@ -2515,7 +2515,7 @@
         <v>3</v>
       </c>
       <c r="G74" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H74" t="n">
         <v>3000</v>
@@ -2544,7 +2544,7 @@
         <v>3</v>
       </c>
       <c r="G75" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H75" t="n">
         <v>3000</v>
@@ -2602,7 +2602,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>2.76382112503052</v>
+        <v>2.76382160186768</v>
       </c>
       <c r="H77" t="n">
         <v>10000</v>
@@ -2660,7 +2660,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G79" t="n">
-        <v>2.76382112503052</v>
+        <v>2.76382160186768</v>
       </c>
       <c r="H79" t="n">
         <v>12000</v>
@@ -2689,7 +2689,7 @@
         <v>2.90549993515015</v>
       </c>
       <c r="G80" t="n">
-        <v>2.76906299591064</v>
+        <v>2.76906275749207</v>
       </c>
       <c r="H80" t="n">
         <v>4500</v>
@@ -2718,7 +2718,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H81" t="n">
         <v>3000</v>
@@ -2747,7 +2747,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G82" t="n">
-        <v>2.77335143089294</v>
+        <v>2.77335214614868</v>
       </c>
       <c r="H82" t="n">
         <v>1000</v>
@@ -2805,7 +2805,7 @@
         <v>3</v>
       </c>
       <c r="G84" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H84" t="n">
         <v>12500</v>
@@ -2834,7 +2834,7 @@
         <v>3.06599998474121</v>
       </c>
       <c r="G85" t="n">
-        <v>2.92202591896057</v>
+        <v>2.92202639579773</v>
       </c>
       <c r="H85" t="n">
         <v>1500</v>
@@ -2863,7 +2863,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>2.9163076877594</v>
+        <v>2.91630744934082</v>
       </c>
       <c r="H86" t="n">
         <v>3000</v>
@@ -2892,7 +2892,7 @@
         <v>2.99950003623962</v>
       </c>
       <c r="G87" t="n">
-        <v>2.85864877700806</v>
+        <v>2.85864925384521</v>
       </c>
       <c r="H87" t="n">
         <v>14000</v>
@@ -3037,7 +3037,7 @@
         <v>2.93050003051758</v>
       </c>
       <c r="G92" t="n">
-        <v>2.792888879776</v>
+        <v>2.79288864135742</v>
       </c>
       <c r="H92" t="n">
         <v>500</v>
@@ -3066,7 +3066,7 @@
         <v>2.90899991989136</v>
       </c>
       <c r="G93" t="n">
-        <v>2.77239871025085</v>
+        <v>2.7723982334137</v>
       </c>
       <c r="H93" t="n">
         <v>52000</v>
@@ -3095,7 +3095,7 @@
         <v>2.90899991989136</v>
       </c>
       <c r="G94" t="n">
-        <v>2.77239871025085</v>
+        <v>2.7723982334137</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G97" t="n">
-        <v>2.83815836906433</v>
+        <v>2.83815789222717</v>
       </c>
       <c r="H97" t="n">
         <v>15000</v>
@@ -3211,7 +3211,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G98" t="n">
-        <v>2.83815836906433</v>
+        <v>2.83815789222717</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>2.76382112503052</v>
+        <v>2.76382160186768</v>
       </c>
       <c r="H99" t="n">
         <v>3000</v>
@@ -3269,7 +3269,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G100" t="n">
-        <v>2.76382112503052</v>
+        <v>2.76382160186768</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G101" t="n">
-        <v>2.76382112503052</v>
+        <v>2.76382160186768</v>
       </c>
       <c r="H101" t="n">
         <v>3000</v>
@@ -3327,7 +3327,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G102" t="n">
-        <v>2.76382112503052</v>
+        <v>2.76382160186768</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>2.76382112503052</v>
+        <v>2.76382160186768</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>2.76382112503052</v>
+        <v>2.76382160186768</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G107" t="n">
-        <v>2.76382112503052</v>
+        <v>2.76382160186768</v>
       </c>
       <c r="H107" t="n">
         <v>9500</v>
@@ -3617,7 +3617,7 @@
         <v>3</v>
       </c>
       <c r="G112" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H112" t="n">
         <v>8000</v>
@@ -3646,7 +3646,7 @@
         <v>3.05949997901917</v>
       </c>
       <c r="G113" t="n">
-        <v>2.91583132743835</v>
+        <v>2.91583156585693</v>
       </c>
       <c r="H113" t="n">
         <v>17500</v>
@@ -3675,7 +3675,7 @@
         <v>3.05949997901917</v>
       </c>
       <c r="G114" t="n">
-        <v>2.91583132743835</v>
+        <v>2.91583156585693</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G115" t="n">
-        <v>2.95442938804626</v>
+        <v>2.95442914962769</v>
       </c>
       <c r="H115" t="n">
         <v>500</v>
@@ -3733,7 +3733,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G116" t="n">
-        <v>2.84959506988525</v>
+        <v>2.84959483146667</v>
       </c>
       <c r="H116" t="n">
         <v>3500</v>
@@ -3762,7 +3762,7 @@
         <v>2.92549991607666</v>
       </c>
       <c r="G117" t="n">
-        <v>2.7881236076355</v>
+        <v>2.78812384605408</v>
       </c>
       <c r="H117" t="n">
         <v>9000</v>
@@ -3791,7 +3791,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G118" t="n">
-        <v>2.79622459411621</v>
+        <v>2.79622483253479</v>
       </c>
       <c r="H118" t="n">
         <v>6500</v>
@@ -3820,7 +3820,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G119" t="n">
-        <v>2.85436034202576</v>
+        <v>2.85436010360718</v>
       </c>
       <c r="H119" t="n">
         <v>2500</v>
@@ -3849,7 +3849,7 @@
         <v>3</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H120" t="n">
         <v>2000</v>
@@ -3878,7 +3878,7 @@
         <v>3</v>
       </c>
       <c r="G121" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H123" t="n">
         <v>500</v>
@@ -3965,7 +3965,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G124" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G125" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G126" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H126" t="n">
         <v>1000</v>
@@ -4052,7 +4052,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G127" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>2.81147336959839</v>
+        <v>2.81147289276123</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G131" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H131" t="n">
         <v>3500</v>
@@ -4197,7 +4197,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G132" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>2.92249989509583</v>
       </c>
       <c r="G133" t="n">
-        <v>2.78526449203491</v>
+        <v>2.78526425361633</v>
       </c>
       <c r="H133" t="n">
         <v>1500</v>
@@ -4255,7 +4255,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G134" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H134" t="n">
         <v>1000</v>
@@ -4284,7 +4284,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H135" t="n">
         <v>500</v>
@@ -4313,7 +4313,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G136" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H136" t="n">
         <v>1000</v>
@@ -4342,7 +4342,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G137" t="n">
-        <v>2.8305344581604</v>
+        <v>2.83053398132324</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G140" t="n">
-        <v>2.87818646430969</v>
+        <v>2.87818574905396</v>
       </c>
       <c r="H140" t="n">
         <v>11500</v>
@@ -4458,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="G141" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H141" t="n">
         <v>500</v>
@@ -4516,7 +4516,7 @@
         <v>3</v>
       </c>
       <c r="G143" t="n">
-        <v>2.85912561416626</v>
+        <v>2.85912537574768</v>
       </c>
       <c r="H143" t="n">
         <v>13500</v>
@@ -4545,7 +4545,7 @@
         <v>3.02950000762939</v>
       </c>
       <c r="G144" t="n">
-        <v>2.8872401714325</v>
+        <v>2.88724040985107</v>
       </c>
       <c r="H144" t="n">
         <v>43000</v>
@@ -4603,7 +4603,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>2.90201210975647</v>
+        <v>2.90201258659363</v>
       </c>
       <c r="H146" t="n">
         <v>12500</v>
@@ -4661,7 +4661,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>2.9163076877594</v>
+        <v>2.91630744934082</v>
       </c>
       <c r="H148" t="n">
         <v>2000</v>
@@ -4748,7 +4748,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>3.05926418304443</v>
+        <v>3.05926394462585</v>
       </c>
       <c r="H151" t="n">
         <v>12000</v>
@@ -4806,7 +4806,7 @@
         <v>3.32949995994568</v>
       </c>
       <c r="G153" t="n">
-        <v>3.17315268516541</v>
+        <v>3.17315220832825</v>
       </c>
       <c r="H153" t="n">
         <v>8000</v>
@@ -4835,7 +4835,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G154" t="n">
-        <v>3.24987244606018</v>
+        <v>3.24987268447876</v>
       </c>
       <c r="H154" t="n">
         <v>19000</v>
@@ -4864,7 +4864,7 @@
         <v>3.40949988365173</v>
       </c>
       <c r="G155" t="n">
-        <v>3.24939584732056</v>
+        <v>3.24939560890198</v>
       </c>
       <c r="H155" t="n">
         <v>13000</v>
@@ -4893,7 +4893,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G156" t="n">
-        <v>3.22890567779541</v>
+        <v>3.22890543937683</v>
       </c>
       <c r="H156" t="n">
         <v>17500</v>
@@ -5067,7 +5067,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G162" t="n">
-        <v>3.21175098419189</v>
+        <v>3.21175050735474</v>
       </c>
       <c r="H162" t="n">
         <v>6500</v>
@@ -5096,7 +5096,7 @@
         <v>3.41700005531311</v>
       </c>
       <c r="G163" t="n">
-        <v>3.25654363632202</v>
+        <v>3.2565438747406</v>
       </c>
       <c r="H163" t="n">
         <v>15500</v>
@@ -5125,7 +5125,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G164" t="n">
-        <v>3.21175098419189</v>
+        <v>3.21175050735474</v>
       </c>
       <c r="H164" t="n">
         <v>3500</v>
@@ -5154,7 +5154,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>3.21175098419189</v>
+        <v>3.21175050735474</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>3.25463724136353</v>
+        <v>3.25463795661926</v>
       </c>
       <c r="H166" t="n">
         <v>14000</v>
@@ -5212,7 +5212,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>3.26893305778503</v>
+        <v>3.26893329620361</v>
       </c>
       <c r="H167" t="n">
         <v>14500</v>
@@ -5299,7 +5299,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>3.34517645835876</v>
+        <v>3.34517693519592</v>
       </c>
       <c r="H170" t="n">
         <v>32000</v>
@@ -5328,7 +5328,7 @@
         <v>3.59450006484985</v>
       </c>
       <c r="G171" t="n">
-        <v>3.42570853233337</v>
+        <v>3.42570829391479</v>
       </c>
       <c r="H171" t="n">
         <v>61000</v>
@@ -5357,7 +5357,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G172" t="n">
-        <v>3.50242853164673</v>
+        <v>3.50242829322815</v>
       </c>
       <c r="H172" t="n">
         <v>10000</v>
@@ -5415,7 +5415,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G174" t="n">
-        <v>3.47860217094421</v>
+        <v>3.47860288619995</v>
       </c>
       <c r="H174" t="n">
         <v>6000</v>
@@ -5444,7 +5444,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G175" t="n">
-        <v>3.5548460483551</v>
+        <v>3.55484557151794</v>
       </c>
       <c r="H175" t="n">
         <v>4000</v>
@@ -5473,7 +5473,7 @@
         <v>3.75</v>
       </c>
       <c r="G176" t="n">
-        <v>3.57390689849854</v>
+        <v>3.57390642166138</v>
       </c>
       <c r="H176" t="n">
         <v>6500</v>
@@ -5502,7 +5502,7 @@
         <v>3.75</v>
       </c>
       <c r="G177" t="n">
-        <v>3.57390689849854</v>
+        <v>3.57390642166138</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>3.84075880050659</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H179" t="n">
         <v>10000</v>
@@ -5734,7 +5734,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G185" t="n">
-        <v>3.66921067237854</v>
+        <v>3.66921043395996</v>
       </c>
       <c r="H185" t="n">
         <v>10000</v>
@@ -5763,7 +5763,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G186" t="n">
-        <v>3.66921067237854</v>
+        <v>3.66921043395996</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G187" t="n">
-        <v>3.71686315536499</v>
+        <v>3.71686267852783</v>
       </c>
       <c r="H187" t="n">
         <v>3000</v>
@@ -5821,7 +5821,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>3.71686315536499</v>
+        <v>3.71686267852783</v>
       </c>
       <c r="H188" t="n">
         <v>3000</v>
@@ -5850,7 +5850,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>3.65014958381653</v>
+        <v>3.65015006065369</v>
       </c>
       <c r="H189" t="n">
         <v>4350</v>
@@ -5908,7 +5908,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G191" t="n">
-        <v>3.84075880050659</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H191" t="n">
         <v>18218</v>
@@ -5937,7 +5937,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G192" t="n">
-        <v>3.84075880050659</v>
+        <v>3.84075832366943</v>
       </c>
       <c r="H192" t="n">
         <v>2550</v>
@@ -5966,7 +5966,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>3.95512366294861</v>
+        <v>3.95512342453003</v>
       </c>
       <c r="H193" t="n">
         <v>3120</v>
@@ -5995,7 +5995,7 @@
         <v>4</v>
       </c>
       <c r="G194" t="n">
-        <v>3.81216716766357</v>
+        <v>3.81216669082642</v>
       </c>
       <c r="H194" t="n">
         <v>9902</v>
@@ -6024,7 +6024,7 @@
         <v>4</v>
       </c>
       <c r="G195" t="n">
-        <v>3.81216716766357</v>
+        <v>3.81216669082642</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G196" t="n">
-        <v>3.80263662338257</v>
+        <v>3.80263638496399</v>
       </c>
       <c r="H196" t="n">
         <v>3767</v>
@@ -6082,7 +6082,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>3.85028839111328</v>
+        <v>3.85028862953186</v>
       </c>
       <c r="H197" t="n">
         <v>810</v>
@@ -6198,7 +6198,7 @@
         <v>4</v>
       </c>
       <c r="G201" t="n">
-        <v>3.8316171169281</v>
+        <v>3.83161687850952</v>
       </c>
       <c r="H201" t="n">
         <v>14910</v>
@@ -6227,7 +6227,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G202" t="n">
-        <v>3.92740774154663</v>
+        <v>3.92740702629089</v>
       </c>
       <c r="H202" t="n">
         <v>6500</v>
@@ -6256,7 +6256,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G203" t="n">
-        <v>3.87951254844666</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H203" t="n">
         <v>3200</v>
@@ -6285,7 +6285,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G204" t="n">
-        <v>3.88909101486206</v>
+        <v>3.88909125328064</v>
       </c>
       <c r="H204" t="n">
         <v>23362</v>
@@ -6401,7 +6401,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>3.70708918571472</v>
+        <v>3.7070894241333</v>
       </c>
       <c r="H208" t="n">
         <v>1000</v>
@@ -6488,7 +6488,7 @@
         <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>3.8316171169281</v>
+        <v>3.83161687850952</v>
       </c>
       <c r="H211" t="n">
         <v>12500</v>
@@ -6517,7 +6517,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G212" t="n">
-        <v>3.87951254844666</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H212" t="n">
         <v>12189</v>
@@ -6546,7 +6546,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>3.87951254844666</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G214" t="n">
-        <v>3.78372168540955</v>
+        <v>3.78372144699097</v>
       </c>
       <c r="H214" t="n">
         <v>3800</v>
@@ -6604,7 +6604,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>3.87951254844666</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H215" t="n">
         <v>1090</v>
@@ -6633,7 +6633,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G216" t="n">
-        <v>3.87951254844666</v>
+        <v>3.87951231002808</v>
       </c>
       <c r="H216" t="n">
         <v>1000</v>
@@ -6691,7 +6691,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G218" t="n">
-        <v>3.94656562805176</v>
+        <v>3.9465651512146</v>
       </c>
       <c r="H218" t="n">
         <v>18231</v>
@@ -6720,7 +6720,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G219" t="n">
-        <v>4.02319717407227</v>
+        <v>4.02319765090942</v>
       </c>
       <c r="H219" t="n">
         <v>14879</v>
@@ -6749,7 +6749,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>4.03277730941772</v>
+        <v>4.03277683258057</v>
       </c>
       <c r="H220" t="n">
         <v>4360</v>
@@ -6836,7 +6836,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G223" t="n">
-        <v>4.14772510528564</v>
+        <v>4.1477255821228</v>
       </c>
       <c r="H223" t="n">
         <v>2021</v>
@@ -6865,7 +6865,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G224" t="n">
-        <v>4.19562149047852</v>
+        <v>4.1956205368042</v>
       </c>
       <c r="H224" t="n">
         <v>6059</v>
@@ -6894,7 +6894,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G225" t="n">
-        <v>4.39678049087524</v>
+        <v>4.39678144454956</v>
       </c>
       <c r="H225" t="n">
         <v>12211</v>
@@ -6923,7 +6923,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>4.50215005874634</v>
+        <v>4.5021505355835</v>
       </c>
       <c r="H226" t="n">
         <v>33604</v>
@@ -6952,7 +6952,7 @@
         <v>4.5</v>
       </c>
       <c r="G227" t="n">
-        <v>4.31056880950928</v>
+        <v>4.31056976318359</v>
       </c>
       <c r="H227" t="n">
         <v>15408</v>
@@ -7097,7 +7097,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G232" t="n">
-        <v>4.50215005874634</v>
+        <v>4.5021505355835</v>
       </c>
       <c r="H232" t="n">
         <v>5830</v>
@@ -7155,7 +7155,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>4.66499376296997</v>
+        <v>4.66499423980713</v>
       </c>
       <c r="H234" t="n">
         <v>11495</v>
@@ -7184,7 +7184,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G235" t="n">
-        <v>4.68415117263794</v>
+        <v>4.6841516494751</v>
       </c>
       <c r="H235" t="n">
         <v>6841</v>
@@ -7213,7 +7213,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H236" t="n">
         <v>74862</v>
@@ -7242,7 +7242,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G237" t="n">
-        <v>4.96194362640381</v>
+        <v>4.96194314956665</v>
       </c>
       <c r="H237" t="n">
         <v>30201</v>
@@ -7300,7 +7300,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H239" t="n">
         <v>29610</v>
@@ -7329,7 +7329,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G240" t="n">
-        <v>4.90446996688843</v>
+        <v>4.90446949005127</v>
       </c>
       <c r="H240" t="n">
         <v>12860</v>
@@ -7445,7 +7445,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H244" t="n">
         <v>3855</v>
@@ -7503,7 +7503,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>4.71288871765137</v>
+        <v>4.71288919448853</v>
       </c>
       <c r="H246" t="n">
         <v>5934</v>
@@ -7532,7 +7532,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G247" t="n">
-        <v>4.71288871765137</v>
+        <v>4.71288919448853</v>
       </c>
       <c r="H247" t="n">
         <v>4150</v>
@@ -7561,7 +7561,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G248" t="n">
-        <v>4.71288871765137</v>
+        <v>4.71288919448853</v>
       </c>
       <c r="H248" t="n">
         <v>3000</v>
@@ -7590,7 +7590,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G249" t="n">
-        <v>4.77036380767822</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H249" t="n">
         <v>140</v>
@@ -7677,7 +7677,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>4.77036380767822</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H252" t="n">
         <v>2483</v>
@@ -7706,7 +7706,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G253" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H253" t="n">
         <v>3900</v>
@@ -7735,7 +7735,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G254" t="n">
-        <v>4.77036380767822</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H254" t="n">
         <v>9900</v>
@@ -7793,7 +7793,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G256" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457342147827</v>
       </c>
       <c r="H256" t="n">
         <v>960</v>
@@ -7822,7 +7822,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G257" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457342147827</v>
       </c>
       <c r="H257" t="n">
         <v>1620</v>
@@ -7909,7 +7909,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G260" t="n">
-        <v>4.66499376296997</v>
+        <v>4.66499423980713</v>
       </c>
       <c r="H260" t="n">
         <v>1936</v>
@@ -7938,7 +7938,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G261" t="n">
-        <v>4.66499376296997</v>
+        <v>4.66499423980713</v>
       </c>
       <c r="H261" t="n">
         <v>12495</v>
@@ -7967,7 +7967,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G262" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457342147827</v>
       </c>
       <c r="H262" t="n">
         <v>3699</v>
@@ -7996,7 +7996,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583492279053</v>
       </c>
       <c r="H263" t="n">
         <v>581</v>
@@ -8112,7 +8112,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>4.59794139862061</v>
+        <v>4.59794092178345</v>
       </c>
       <c r="H267" t="n">
         <v>1400</v>
@@ -8141,7 +8141,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>4.59794139862061</v>
+        <v>4.59794092178345</v>
       </c>
       <c r="H268" t="n">
         <v>1635</v>
@@ -8170,7 +8170,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G269" t="n">
-        <v>4.59794139862061</v>
+        <v>4.59794092178345</v>
       </c>
       <c r="H269" t="n">
         <v>4049</v>
@@ -8199,7 +8199,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>4.50215005874634</v>
+        <v>4.5021505355835</v>
       </c>
       <c r="H270" t="n">
         <v>1000</v>
@@ -8228,7 +8228,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G271" t="n">
-        <v>4.50215005874634</v>
+        <v>4.5021505355835</v>
       </c>
       <c r="H271" t="n">
         <v>1925</v>
@@ -8257,7 +8257,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G272" t="n">
-        <v>4.50215005874634</v>
+        <v>4.5021505355835</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>4.57878160476685</v>
+        <v>4.57878303527832</v>
       </c>
       <c r="H273" t="n">
         <v>700</v>
@@ -8315,7 +8315,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078414916992</v>
       </c>
       <c r="H274" t="n">
         <v>4784</v>
@@ -8344,7 +8344,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G275" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078414916992</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G276" t="n">
-        <v>4.77036380767822</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H276" t="n">
         <v>900</v>
@@ -8402,7 +8402,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>4.62667798995972</v>
+        <v>4.6266770362854</v>
       </c>
       <c r="H277" t="n">
         <v>5557</v>
@@ -8460,7 +8460,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G279" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457342147827</v>
       </c>
       <c r="H279" t="n">
         <v>4220</v>
@@ -8489,7 +8489,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G280" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457342147827</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>4.71288871765137</v>
+        <v>4.71288919448853</v>
       </c>
       <c r="H281" t="n">
         <v>1663</v>
@@ -8547,7 +8547,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583492279053</v>
       </c>
       <c r="H282" t="n">
         <v>2700</v>
@@ -8576,7 +8576,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>4.64583539962769</v>
+        <v>4.64583492279053</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G289" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H289" t="n">
         <v>13078</v>
@@ -8779,7 +8779,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G290" t="n">
-        <v>4.84699440002441</v>
+        <v>4.84699535369873</v>
       </c>
       <c r="H290" t="n">
         <v>3925</v>
@@ -8808,7 +8808,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G291" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H291" t="n">
         <v>3150</v>
@@ -8837,7 +8837,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G292" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G294" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078414916992</v>
       </c>
       <c r="H294" t="n">
         <v>2200</v>
@@ -8924,7 +8924,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457342147827</v>
       </c>
       <c r="H295" t="n">
         <v>2811</v>
@@ -8953,7 +8953,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>4.67457246780396</v>
+        <v>4.67457342147827</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G305" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H305" t="n">
         <v>4750</v>
@@ -9272,7 +9272,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>4.84699440002441</v>
+        <v>4.84699535369873</v>
       </c>
       <c r="H307" t="n">
         <v>5606</v>
@@ -9301,7 +9301,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G308" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H308" t="n">
         <v>2465</v>
@@ -9330,7 +9330,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G309" t="n">
-        <v>4.84699440002441</v>
+        <v>4.84699535369873</v>
       </c>
       <c r="H309" t="n">
         <v>5000</v>
@@ -9359,7 +9359,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G310" t="n">
-        <v>4.84699440002441</v>
+        <v>4.84699535369873</v>
       </c>
       <c r="H310" t="n">
         <v>4957</v>
@@ -9475,7 +9475,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G314" t="n">
-        <v>4.77994203567505</v>
+        <v>4.77994155883789</v>
       </c>
       <c r="H314" t="n">
         <v>4048</v>
@@ -9504,7 +9504,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G315" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078414916992</v>
       </c>
       <c r="H315" t="n">
         <v>2985</v>
@@ -9562,7 +9562,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G317" t="n">
-        <v>4.77036380767822</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H317" t="n">
         <v>6452</v>
@@ -9591,7 +9591,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G318" t="n">
-        <v>4.77036380767822</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H320" t="n">
         <v>100</v>
@@ -9678,7 +9678,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G321" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H323" t="n">
         <v>54154</v>
@@ -9765,7 +9765,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G324" t="n">
-        <v>4.80867958068848</v>
+        <v>4.80867910385132</v>
       </c>
       <c r="H324" t="n">
         <v>26052</v>
@@ -9794,7 +9794,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H325" t="n">
         <v>1040</v>
@@ -9852,7 +9852,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G327" t="n">
-        <v>4.84699440002441</v>
+        <v>4.84699535369873</v>
       </c>
       <c r="H327" t="n">
         <v>50</v>
@@ -9881,7 +9881,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H328" t="n">
         <v>170</v>
@@ -9910,7 +9910,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.84699440002441</v>
+        <v>4.84699535369873</v>
       </c>
       <c r="H331" t="n">
         <v>10342</v>
@@ -9997,7 +9997,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G332" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H332" t="n">
         <v>4683</v>
@@ -10084,7 +10084,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G335" t="n">
-        <v>4.77036380767822</v>
+        <v>4.77036333084106</v>
       </c>
       <c r="H335" t="n">
         <v>16377</v>
@@ -10171,7 +10171,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>4.82783794403076</v>
+        <v>4.82783699035645</v>
       </c>
       <c r="H338" t="n">
         <v>6710</v>
@@ -10200,7 +10200,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G339" t="n">
-        <v>4.88531112670898</v>
+        <v>4.88531064987183</v>
       </c>
       <c r="H339" t="n">
         <v>7300</v>
@@ -10229,7 +10229,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>4.98110198974609</v>
+        <v>4.98110151290894</v>
       </c>
       <c r="H340" t="n">
         <v>8709</v>
@@ -10258,7 +10258,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G341" t="n">
-        <v>4.88531112670898</v>
+        <v>4.88531064987183</v>
       </c>
       <c r="H341" t="n">
         <v>8729</v>
@@ -10287,7 +10287,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>4.98110198974609</v>
+        <v>4.98110151290894</v>
       </c>
       <c r="H342" t="n">
         <v>12262</v>
@@ -10345,7 +10345,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.13436651229858</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H344" t="n">
         <v>6260</v>
@@ -10374,7 +10374,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G345" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H345" t="n">
         <v>14432</v>
@@ -10403,7 +10403,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.11520862579346</v>
+        <v>5.11520910263062</v>
       </c>
       <c r="H346" t="n">
         <v>11091</v>
@@ -10490,7 +10490,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G349" t="n">
-        <v>5.21099948883057</v>
+        <v>5.21099996566772</v>
       </c>
       <c r="H349" t="n">
         <v>3837</v>
@@ -10519,7 +10519,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.13436651229858</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H350" t="n">
         <v>5572</v>
@@ -10548,7 +10548,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G351" t="n">
-        <v>5.13436651229858</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H351" t="n">
         <v>2712</v>
@@ -10577,7 +10577,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G352" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H352" t="n">
         <v>14027</v>
@@ -10606,7 +10606,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G353" t="n">
-        <v>5.09605073928833</v>
+        <v>5.09605026245117</v>
       </c>
       <c r="H353" t="n">
         <v>1649</v>
@@ -10635,7 +10635,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H354" t="n">
         <v>10600</v>
@@ -10693,7 +10693,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H356" t="n">
         <v>10934</v>
@@ -10722,7 +10722,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G357" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H357" t="n">
         <v>2620</v>
@@ -10751,7 +10751,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G358" t="n">
-        <v>5.17268323898315</v>
+        <v>5.172682762146</v>
       </c>
       <c r="H358" t="n">
         <v>2200</v>
@@ -10780,7 +10780,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G359" t="n">
-        <v>5.01941776275635</v>
+        <v>5.01941823959351</v>
       </c>
       <c r="H359" t="n">
         <v>5962</v>
@@ -10809,7 +10809,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H360" t="n">
         <v>2670</v>
@@ -10838,7 +10838,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G361" t="n">
-        <v>5.21099948883057</v>
+        <v>5.21099996566772</v>
       </c>
       <c r="H361" t="n">
         <v>5616</v>
@@ -10867,7 +10867,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G362" t="n">
-        <v>5.0768928527832</v>
+        <v>5.07689237594604</v>
       </c>
       <c r="H362" t="n">
         <v>2700</v>
@@ -10896,7 +10896,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.13436651229858</v>
+        <v>5.13436698913574</v>
       </c>
       <c r="H363" t="n">
         <v>9005</v>
@@ -10925,7 +10925,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G364" t="n">
-        <v>5.15352535247803</v>
+        <v>5.15352487564087</v>
       </c>
       <c r="H364" t="n">
         <v>6000</v>
@@ -11041,7 +11041,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G368" t="n">
-        <v>5.47921228408813</v>
+        <v>5.47921276092529</v>
       </c>
       <c r="H368" t="n">
         <v>12600</v>
@@ -11070,7 +11070,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G369" t="n">
-        <v>5.53668642044067</v>
+        <v>5.53668689727783</v>
       </c>
       <c r="H369" t="n">
         <v>11072</v>
@@ -11099,7 +11099,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G370" t="n">
-        <v>5.53668642044067</v>
+        <v>5.53668689727783</v>
       </c>
       <c r="H370" t="n">
         <v>4790</v>
@@ -11128,7 +11128,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G371" t="n">
-        <v>5.68995189666748</v>
+        <v>5.68995141983032</v>
       </c>
       <c r="H371" t="n">
         <v>95523</v>
@@ -11186,7 +11186,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G373" t="n">
-        <v>5.84321546554565</v>
+        <v>5.84321594238281</v>
       </c>
       <c r="H373" t="n">
         <v>42690</v>
@@ -11215,7 +11215,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H374" t="n">
         <v>28432</v>
@@ -11273,7 +11273,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G376" t="n">
-        <v>5.91984796524048</v>
+        <v>5.91984844207764</v>
       </c>
       <c r="H376" t="n">
         <v>68584</v>
@@ -11302,7 +11302,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G377" t="n">
-        <v>5.90069055557251</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H377" t="n">
         <v>7100</v>
@@ -11360,7 +11360,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G379" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H379" t="n">
         <v>9296</v>
@@ -11389,7 +11389,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G380" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H380" t="n">
         <v>9397</v>
@@ -11418,7 +11418,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G381" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H381" t="n">
         <v>7655</v>
@@ -11447,7 +11447,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G382" t="n">
-        <v>5.88153219223022</v>
+        <v>5.88153171539307</v>
       </c>
       <c r="H382" t="n">
         <v>6996</v>
@@ -11505,7 +11505,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G384" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H384" t="n">
         <v>4781</v>
@@ -11534,7 +11534,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H385" t="n">
         <v>6939</v>
@@ -11563,7 +11563,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G386" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H386" t="n">
         <v>4823</v>
@@ -11592,7 +11592,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G387" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H387" t="n">
         <v>12576</v>
@@ -11650,7 +11650,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>5.82405805587769</v>
+        <v>5.82405853271484</v>
       </c>
       <c r="H389" t="n">
         <v>8803</v>
@@ -11679,7 +11679,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G390" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H390" t="n">
         <v>1250</v>
@@ -11708,7 +11708,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G391" t="n">
-        <v>5.91984796524048</v>
+        <v>5.91984844207764</v>
       </c>
       <c r="H391" t="n">
         <v>7410</v>
@@ -11737,7 +11737,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H392" t="n">
         <v>6232</v>
@@ -11795,7 +11795,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G394" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H394" t="n">
         <v>1262</v>
@@ -11824,7 +11824,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G395" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H395" t="n">
         <v>4960</v>
@@ -11911,7 +11911,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G398" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964296340942</v>
       </c>
       <c r="H398" t="n">
         <v>14389</v>
@@ -11940,7 +11940,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G399" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964296340942</v>
       </c>
       <c r="H399" t="n">
         <v>32191</v>
@@ -11969,7 +11969,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>6.32216835021973</v>
+        <v>6.32216787338257</v>
       </c>
       <c r="H400" t="n">
         <v>11804</v>
@@ -11998,7 +11998,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G401" t="n">
-        <v>6.36048412322998</v>
+        <v>6.36048460006714</v>
       </c>
       <c r="H401" t="n">
         <v>5726</v>
@@ -12027,7 +12027,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G402" t="n">
-        <v>6.37964248657227</v>
+        <v>6.37964296340942</v>
       </c>
       <c r="H402" t="n">
         <v>7998</v>
@@ -12056,7 +12056,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G403" t="n">
-        <v>6.45627498626709</v>
+        <v>6.45627450942993</v>
       </c>
       <c r="H403" t="n">
         <v>12037</v>
@@ -12085,7 +12085,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G404" t="n">
-        <v>6.39879989624023</v>
+        <v>6.39880037307739</v>
       </c>
       <c r="H404" t="n">
         <v>3594</v>
@@ -12114,7 +12114,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G405" t="n">
-        <v>6.32216835021973</v>
+        <v>6.32216787338257</v>
       </c>
       <c r="H405" t="n">
         <v>37562</v>
@@ -12143,7 +12143,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>6.36048412322998</v>
+        <v>6.36048460006714</v>
       </c>
       <c r="H406" t="n">
         <v>10355</v>
@@ -12172,7 +12172,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G407" t="n">
-        <v>6.49459171295166</v>
+        <v>6.49459075927734</v>
       </c>
       <c r="H407" t="n">
         <v>9368</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.55584478378296</v>
+        <v>5.55584526062012</v>
       </c>
       <c r="H415" t="n">
         <v>21916</v>
@@ -12462,7 +12462,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G417" t="n">
-        <v>5.90069055557251</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H417" t="n">
         <v>11796</v>
@@ -12491,7 +12491,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G418" t="n">
-        <v>5.72826766967773</v>
+        <v>5.72826719284058</v>
       </c>
       <c r="H418" t="n">
         <v>21988</v>
@@ -12520,7 +12520,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G419" t="n">
-        <v>5.90069055557251</v>
+        <v>5.90069007873535</v>
       </c>
       <c r="H419" t="n">
         <v>4174</v>
@@ -12549,7 +12549,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>5.70910835266113</v>
+        <v>5.70910882949829</v>
       </c>
       <c r="H420" t="n">
         <v>8111</v>
@@ -12578,7 +12578,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G421" t="n">
-        <v>5.70910835266113</v>
+        <v>5.70910882949829</v>
       </c>
       <c r="H421" t="n">
         <v>18321</v>
@@ -12694,7 +12694,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G425" t="n">
-        <v>5.93900632858276</v>
+        <v>5.93900585174561</v>
       </c>
       <c r="H425" t="n">
         <v>2570</v>
@@ -12897,7 +12897,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G432" t="n">
-        <v>6.11142873764038</v>
+        <v>6.11142921447754</v>
       </c>
       <c r="H432" t="n">
         <v>9507</v>
@@ -13013,7 +13013,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G436" t="n">
-        <v>6.57122278213501</v>
+        <v>6.57122325897217</v>
       </c>
       <c r="H436" t="n">
         <v>24597</v>
@@ -13071,7 +13071,7 @@
         <v>7</v>
       </c>
       <c r="G438" t="n">
-        <v>6.70532941818237</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H438" t="n">
         <v>17634</v>
@@ -13100,7 +13100,7 @@
         <v>7</v>
       </c>
       <c r="G439" t="n">
-        <v>6.70532941818237</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H439" t="n">
         <v>12013</v>
@@ -13158,7 +13158,7 @@
         <v>7</v>
       </c>
       <c r="G441" t="n">
-        <v>6.70532941818237</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H441" t="n">
         <v>8061</v>
@@ -13216,7 +13216,7 @@
         <v>7</v>
       </c>
       <c r="G443" t="n">
-        <v>6.70532941818237</v>
+        <v>6.70532989501953</v>
       </c>
       <c r="H443" t="n">
         <v>701</v>
@@ -13274,7 +13274,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>6.99270057678223</v>
+        <v>6.99270153045654</v>
       </c>
       <c r="H445" t="n">
         <v>26998</v>
@@ -13303,7 +13303,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G446" t="n">
-        <v>7.16512393951416</v>
+        <v>7.16512441635132</v>
       </c>
       <c r="H446" t="n">
         <v>13821</v>
@@ -13332,7 +13332,7 @@
         <v>7.5</v>
       </c>
       <c r="G447" t="n">
-        <v>7.18428230285645</v>
+        <v>7.18428182601929</v>
       </c>
       <c r="H447" t="n">
         <v>16792</v>
@@ -13419,7 +13419,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G450" t="n">
-        <v>7.68239259719849</v>
+        <v>7.68239307403564</v>
       </c>
       <c r="H450" t="n">
         <v>46433</v>
@@ -13448,7 +13448,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G451" t="n">
-        <v>8.00807952880859</v>
+        <v>8.00807857513428</v>
       </c>
       <c r="H451" t="n">
         <v>28419</v>
@@ -13477,7 +13477,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G452" t="n">
-        <v>8.11382865905762</v>
+        <v>8.11382675170898</v>
       </c>
       <c r="H452" t="n">
         <v>11712</v>
@@ -13506,7 +13506,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>8.13305568695068</v>
+        <v>8.133056640625</v>
       </c>
       <c r="H453" t="n">
         <v>8878</v>
@@ -13535,7 +13535,7 @@
         <v>8.5</v>
       </c>
       <c r="G454" t="n">
-        <v>8.17150974273682</v>
+        <v>8.17151069641113</v>
       </c>
       <c r="H454" t="n">
         <v>44078</v>
@@ -13564,7 +13564,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G455" t="n">
-        <v>7.99846506118774</v>
+        <v>7.99846410751343</v>
       </c>
       <c r="H455" t="n">
         <v>13585</v>
@@ -13593,7 +13593,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G456" t="n">
-        <v>8.07537269592285</v>
+        <v>8.07537364959717</v>
       </c>
       <c r="H456" t="n">
         <v>15884</v>
@@ -13622,7 +13622,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G457" t="n">
-        <v>8.07537269592285</v>
+        <v>8.07537364959717</v>
       </c>
       <c r="H457" t="n">
         <v>8749</v>
@@ -13651,7 +13651,7 @@
         <v>8.5</v>
       </c>
       <c r="G458" t="n">
-        <v>8.17150974273682</v>
+        <v>8.17151069641113</v>
       </c>
       <c r="H458" t="n">
         <v>10004</v>
@@ -13680,7 +13680,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>8.13305568695068</v>
+        <v>8.133056640625</v>
       </c>
       <c r="H459" t="n">
         <v>5157</v>
@@ -13709,7 +13709,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G460" t="n">
-        <v>8.01769256591797</v>
+        <v>8.01769351959229</v>
       </c>
       <c r="H460" t="n">
         <v>2888</v>
@@ -13738,7 +13738,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G461" t="n">
-        <v>8.07537269592285</v>
+        <v>8.07537364959717</v>
       </c>
       <c r="H461" t="n">
         <v>4060</v>
@@ -13767,7 +13767,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G462" t="n">
-        <v>8.11382865905762</v>
+        <v>8.11382675170898</v>
       </c>
       <c r="H462" t="n">
         <v>6009</v>
@@ -13796,7 +13796,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G463" t="n">
-        <v>8.07537269592285</v>
+        <v>8.07537364959717</v>
       </c>
       <c r="H463" t="n">
         <v>3875</v>
@@ -13825,7 +13825,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G464" t="n">
-        <v>7.80619478225708</v>
+        <v>7.80619525909424</v>
       </c>
       <c r="H464" t="n">
         <v>13308</v>
@@ -13854,7 +13854,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701543807983</v>
       </c>
       <c r="H465" t="n">
         <v>22593</v>
@@ -13883,7 +13883,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>7.13324737548828</v>
+        <v>7.13324689865112</v>
       </c>
       <c r="H466" t="n">
         <v>26621</v>
@@ -13970,7 +13970,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G469" t="n">
-        <v>7.2678370475769</v>
+        <v>7.26783657073975</v>
       </c>
       <c r="H469" t="n">
         <v>3130</v>
@@ -14028,7 +14028,7 @@
         <v>7.5</v>
       </c>
       <c r="G471" t="n">
-        <v>7.21015548706055</v>
+        <v>7.21015501022339</v>
       </c>
       <c r="H471" t="n">
         <v>4606</v>
@@ -14086,7 +14086,7 @@
         <v>7.5</v>
       </c>
       <c r="G473" t="n">
-        <v>7.21015548706055</v>
+        <v>7.21015501022339</v>
       </c>
       <c r="H473" t="n">
         <v>577622</v>
@@ -14173,7 +14173,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G476" t="n">
-        <v>7.59469652175903</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H476" t="n">
         <v>6071</v>
@@ -14289,7 +14289,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>7.59469652175903</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H480" t="n">
         <v>5804</v>
@@ -14318,7 +14318,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G481" t="n">
-        <v>7.61392402648926</v>
+        <v>7.61392450332642</v>
       </c>
       <c r="H481" t="n">
         <v>6569</v>
@@ -14347,7 +14347,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G482" t="n">
-        <v>7.59469652175903</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H482" t="n">
         <v>3228</v>
@@ -14405,7 +14405,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G484" t="n">
-        <v>7.59469652175903</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H484" t="n">
         <v>2166</v>
@@ -14434,7 +14434,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G485" t="n">
-        <v>7.59469652175903</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H485" t="n">
         <v>10</v>
@@ -14463,7 +14463,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>7.61392402648926</v>
+        <v>7.61392450332642</v>
       </c>
       <c r="H486" t="n">
         <v>6297</v>
@@ -14492,7 +14492,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>7.59469652175903</v>
+        <v>7.59469699859619</v>
       </c>
       <c r="H487" t="n">
         <v>63</v>
@@ -14695,7 +14695,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G494" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701543807983</v>
       </c>
       <c r="H494" t="n">
         <v>1276</v>
@@ -14724,7 +14724,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701543807983</v>
       </c>
       <c r="H495" t="n">
         <v>3732</v>
@@ -14753,7 +14753,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G496" t="n">
-        <v>7.51778888702393</v>
+        <v>7.51778841018677</v>
       </c>
       <c r="H496" t="n">
         <v>648</v>
@@ -14782,7 +14782,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G497" t="n">
-        <v>7.53701591491699</v>
+        <v>7.53701543807983</v>
       </c>
       <c r="H497" t="n">
         <v>370</v>
@@ -14811,7 +14811,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>7.61392402648926</v>
+        <v>7.61392450332642</v>
       </c>
       <c r="H498" t="n">
         <v>19417</v>
@@ -14869,7 +14869,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>7.76774024963379</v>
+        <v>7.76774072647095</v>
       </c>
       <c r="H500" t="n">
         <v>19279</v>
@@ -14898,7 +14898,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G501" t="n">
-        <v>7.76774024963379</v>
+        <v>7.76774072647095</v>
       </c>
       <c r="H501" t="n">
         <v>1200</v>
@@ -14985,7 +14985,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G504" t="n">
-        <v>7.8254222869873</v>
+        <v>7.82542276382446</v>
       </c>
       <c r="H504" t="n">
         <v>8213</v>
@@ -15014,7 +15014,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G505" t="n">
-        <v>8.01769256591797</v>
+        <v>8.01769351959229</v>
       </c>
       <c r="H505" t="n">
         <v>6595</v>
@@ -15043,7 +15043,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G506" t="n">
-        <v>8.15228271484375</v>
+        <v>8.15228176116943</v>
       </c>
       <c r="H506" t="n">
         <v>23464</v>
@@ -15072,7 +15072,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G507" t="n">
-        <v>8.34455394744873</v>
+        <v>8.34455490112305</v>
       </c>
       <c r="H507" t="n">
         <v>18075</v>
@@ -15101,7 +15101,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G508" t="n">
-        <v>8.38300704956055</v>
+        <v>8.38300800323486</v>
       </c>
       <c r="H508" t="n">
         <v>13336</v>
@@ -15159,7 +15159,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G510" t="n">
-        <v>8.55604934692383</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H510" t="n">
         <v>4438</v>
@@ -15188,7 +15188,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G511" t="n">
-        <v>8.55604934692383</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H511" t="n">
         <v>2825</v>
@@ -15246,7 +15246,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G513" t="n">
-        <v>8.74832248687744</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H513" t="n">
         <v>3322</v>
@@ -15478,7 +15478,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G521" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H521" t="n">
         <v>5058</v>
@@ -15507,7 +15507,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G522" t="n">
-        <v>9.49817943572998</v>
+        <v>9.49817848205566</v>
       </c>
       <c r="H522" t="n">
         <v>4632</v>
@@ -15565,7 +15565,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G524" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H524" t="n">
         <v>3582</v>
@@ -15594,7 +15594,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G525" t="n">
-        <v>9.34436225891113</v>
+        <v>9.34436321258545</v>
       </c>
       <c r="H525" t="n">
         <v>2160</v>
@@ -15681,7 +15681,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G528" t="n">
-        <v>8.84445667266846</v>
+        <v>8.84445762634277</v>
       </c>
       <c r="H528" t="n">
         <v>4558</v>
@@ -15710,7 +15710,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>8.84445667266846</v>
+        <v>8.84445762634277</v>
       </c>
       <c r="H529" t="n">
         <v>1878</v>
@@ -15797,7 +15797,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G532" t="n">
-        <v>9.07518196105957</v>
+        <v>9.07518291473389</v>
       </c>
       <c r="H532" t="n">
         <v>11482</v>
@@ -15913,7 +15913,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G536" t="n">
-        <v>8.92136573791504</v>
+        <v>8.92136478424072</v>
       </c>
       <c r="H536" t="n">
         <v>2410</v>
@@ -15942,7 +15942,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G537" t="n">
-        <v>8.84445667266846</v>
+        <v>8.84445762634277</v>
       </c>
       <c r="H537" t="n">
         <v>3601</v>
@@ -15971,7 +15971,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G538" t="n">
-        <v>8.74832248687744</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H538" t="n">
         <v>4284</v>
@@ -16058,7 +16058,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G541" t="n">
-        <v>8.63295841217041</v>
+        <v>8.63295936584473</v>
       </c>
       <c r="H541" t="n">
         <v>2081</v>
@@ -16116,7 +16116,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>8.61373329162598</v>
+        <v>8.61373233795166</v>
       </c>
       <c r="H543" t="n">
         <v>3178</v>
@@ -16203,7 +16203,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G546" t="n">
-        <v>8.38300704956055</v>
+        <v>8.38300800323486</v>
       </c>
       <c r="H546" t="n">
         <v>12892</v>
@@ -16232,7 +16232,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G547" t="n">
-        <v>8.38300704956055</v>
+        <v>8.38300800323486</v>
       </c>
       <c r="H547" t="n">
         <v>2415</v>
@@ -16551,7 +16551,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>8.55604934692383</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H558" t="n">
         <v>10958</v>
@@ -16580,7 +16580,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G559" t="n">
-        <v>8.55604934692383</v>
+        <v>8.55605030059814</v>
       </c>
       <c r="H559" t="n">
         <v>5484</v>
@@ -16609,7 +16609,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G560" t="n">
-        <v>8.59450531005859</v>
+        <v>8.59450435638428</v>
       </c>
       <c r="H560" t="n">
         <v>5860</v>
@@ -16667,7 +16667,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G562" t="n">
-        <v>8.95982074737549</v>
+        <v>8.95981979370117</v>
       </c>
       <c r="H562" t="n">
         <v>13014</v>
@@ -16696,7 +16696,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G563" t="n">
-        <v>8.90213871002197</v>
+        <v>8.90213966369629</v>
       </c>
       <c r="H563" t="n">
         <v>9291</v>
@@ -16783,7 +16783,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G566" t="n">
-        <v>8.95982074737549</v>
+        <v>8.95981979370117</v>
       </c>
       <c r="H566" t="n">
         <v>4531</v>
@@ -16812,7 +16812,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G567" t="n">
-        <v>9.19054412841797</v>
+        <v>9.19054508209229</v>
       </c>
       <c r="H567" t="n">
         <v>36349</v>
@@ -16841,7 +16841,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G568" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H568" t="n">
         <v>17237</v>
@@ -16928,7 +16928,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G571" t="n">
-        <v>9.07518196105957</v>
+        <v>9.07518291473389</v>
       </c>
       <c r="H571" t="n">
         <v>10495</v>
@@ -16986,7 +16986,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G573" t="n">
-        <v>9.07518196105957</v>
+        <v>9.07518291473389</v>
       </c>
       <c r="H573" t="n">
         <v>1872</v>
@@ -17044,7 +17044,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G575" t="n">
-        <v>8.84445667266846</v>
+        <v>8.84445762634277</v>
       </c>
       <c r="H575" t="n">
         <v>8026</v>
@@ -17160,7 +17160,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G579" t="n">
-        <v>8.90213871002197</v>
+        <v>8.90213966369629</v>
       </c>
       <c r="H579" t="n">
         <v>6126</v>
@@ -17189,7 +17189,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G580" t="n">
-        <v>8.86368560791016</v>
+        <v>8.86368465423584</v>
       </c>
       <c r="H580" t="n">
         <v>7665</v>
@@ -17218,7 +17218,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G581" t="n">
-        <v>8.84445667266846</v>
+        <v>8.84445762634277</v>
       </c>
       <c r="H581" t="n">
         <v>4098</v>
@@ -17363,7 +17363,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G586" t="n">
-        <v>8.74832248687744</v>
+        <v>8.74832153320312</v>
       </c>
       <c r="H586" t="n">
         <v>3747</v>
@@ -17537,7 +17537,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G592" t="n">
-        <v>8.59450531005859</v>
+        <v>8.59450435638428</v>
       </c>
       <c r="H592" t="n">
         <v>1305</v>
@@ -17595,7 +17595,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G594" t="n">
-        <v>8.80600261688232</v>
+        <v>8.80600166320801</v>
       </c>
       <c r="H594" t="n">
         <v>19270</v>
@@ -17711,7 +17711,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G598" t="n">
-        <v>9.32513523101807</v>
+        <v>9.32513427734375</v>
       </c>
       <c r="H598" t="n">
         <v>35354</v>
@@ -17769,7 +17769,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G600" t="n">
-        <v>9.34436225891113</v>
+        <v>9.34436321258545</v>
       </c>
       <c r="H600" t="n">
         <v>5708</v>
@@ -17798,7 +17798,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G601" t="n">
-        <v>9.15209197998047</v>
+        <v>9.15209102630615</v>
       </c>
       <c r="H601" t="n">
         <v>10060</v>
@@ -17827,7 +17827,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>9.32513523101807</v>
+        <v>9.32513427734375</v>
       </c>
       <c r="H602" t="n">
         <v>7188</v>
@@ -17856,7 +17856,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G603" t="n">
-        <v>9.20977306365967</v>
+        <v>9.20977210998535</v>
       </c>
       <c r="H603" t="n">
         <v>8280</v>
@@ -17943,7 +17943,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G606" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H606" t="n">
         <v>3670</v>
@@ -17972,7 +17972,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H607" t="n">
         <v>5619</v>
@@ -18001,7 +18001,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G608" t="n">
-        <v>9.40204238891602</v>
+        <v>9.40204334259033</v>
       </c>
       <c r="H608" t="n">
         <v>1810</v>
@@ -18146,7 +18146,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G613" t="n">
-        <v>9.15209197998047</v>
+        <v>9.15209102630615</v>
       </c>
       <c r="H613" t="n">
         <v>3820</v>
@@ -18175,7 +18175,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G614" t="n">
-        <v>9.20977306365967</v>
+        <v>9.20977210998535</v>
       </c>
       <c r="H614" t="n">
         <v>4084</v>
@@ -18204,7 +18204,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G615" t="n">
-        <v>9.20977306365967</v>
+        <v>9.20977210998535</v>
       </c>
       <c r="H615" t="n">
         <v>2315</v>
@@ -18233,7 +18233,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G616" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H616" t="n">
         <v>7286</v>
@@ -18262,7 +18262,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G617" t="n">
-        <v>9.15209197998047</v>
+        <v>9.15209102630615</v>
       </c>
       <c r="H617" t="n">
         <v>668</v>
@@ -18320,7 +18320,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G619" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H619" t="n">
         <v>2736</v>
@@ -18349,7 +18349,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G620" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H620" t="n">
         <v>9237</v>
@@ -18407,7 +18407,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G622" t="n">
-        <v>9.22900009155273</v>
+        <v>9.22899913787842</v>
       </c>
       <c r="H622" t="n">
         <v>200</v>
@@ -18465,7 +18465,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G624" t="n">
-        <v>9.4212703704834</v>
+        <v>9.42126941680908</v>
       </c>
       <c r="H624" t="n">
         <v>23348</v>
@@ -18552,7 +18552,7 @@
         <v>10.5</v>
       </c>
       <c r="G627" t="n">
-        <v>10.094217300415</v>
+        <v>10.0942182540894</v>
       </c>
       <c r="H627" t="n">
         <v>26237</v>
@@ -18668,7 +18668,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G631" t="n">
-        <v>10.1422853469849</v>
+        <v>10.1422863006592</v>
       </c>
       <c r="H631" t="n">
         <v>5772</v>
@@ -18697,7 +18697,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G632" t="n">
-        <v>10.1422853469849</v>
+        <v>10.1422863006592</v>
       </c>
       <c r="H632" t="n">
         <v>5416</v>
@@ -18726,7 +18726,7 @@
         <v>10.5</v>
       </c>
       <c r="G633" t="n">
-        <v>10.094217300415</v>
+        <v>10.0942182540894</v>
       </c>
       <c r="H633" t="n">
         <v>3222</v>
@@ -18755,7 +18755,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>9.9500150680542</v>
+        <v>9.95001411437988</v>
       </c>
       <c r="H634" t="n">
         <v>8284</v>
@@ -18784,7 +18784,7 @@
         <v>10.5</v>
       </c>
       <c r="G635" t="n">
-        <v>10.094217300415</v>
+        <v>10.0942182540894</v>
       </c>
       <c r="H635" t="n">
         <v>1941</v>
@@ -18842,7 +18842,7 @@
         <v>10.5</v>
       </c>
       <c r="G637" t="n">
-        <v>10.094217300415</v>
+        <v>10.0942182540894</v>
       </c>
       <c r="H637" t="n">
         <v>8159</v>
@@ -18871,7 +18871,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G638" t="n">
-        <v>10.190354347229</v>
+        <v>10.1903533935547</v>
       </c>
       <c r="H638" t="n">
         <v>4002</v>
@@ -19161,7 +19161,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>10.6710300445557</v>
+        <v>10.6710290908813</v>
       </c>
       <c r="H648" t="n">
         <v>11173</v>
@@ -19190,7 +19190,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>10.6710300445557</v>
+        <v>10.6710290908813</v>
       </c>
       <c r="H649" t="n">
         <v>2351</v>
@@ -19219,7 +19219,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>10.767165184021</v>
+        <v>10.7671642303467</v>
       </c>
       <c r="H650" t="n">
         <v>4282</v>
@@ -19248,7 +19248,7 @@
         <v>11.5</v>
       </c>
       <c r="G651" t="n">
-        <v>11.0555725097656</v>
+        <v>11.0555715560913</v>
       </c>
       <c r="H651" t="n">
         <v>18312</v>
@@ -19277,7 +19277,7 @@
         <v>11.5</v>
       </c>
       <c r="G652" t="n">
-        <v>11.0555725097656</v>
+        <v>11.0555715560913</v>
       </c>
       <c r="H652" t="n">
         <v>27024</v>
@@ -19306,7 +19306,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G653" t="n">
-        <v>11.6323852539062</v>
+        <v>11.6323862075806</v>
       </c>
       <c r="H653" t="n">
         <v>42790</v>
@@ -19335,7 +19335,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>11.8246545791626</v>
+        <v>11.8246555328369</v>
       </c>
       <c r="H654" t="n">
         <v>17953</v>
@@ -19364,7 +19364,7 @@
         <v>12.5</v>
       </c>
       <c r="G655" t="n">
-        <v>12.0169248580933</v>
+        <v>12.0169267654419</v>
       </c>
       <c r="H655" t="n">
         <v>11862</v>
@@ -19480,7 +19480,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>12.9302129745483</v>
+        <v>12.930212020874</v>
       </c>
       <c r="H659" t="n">
         <v>22441</v>
@@ -19596,7 +19596,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G663" t="n">
-        <v>12.7860097885132</v>
+        <v>12.7860078811646</v>
       </c>
       <c r="H663" t="n">
         <v>12196</v>
@@ -19625,7 +19625,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G664" t="n">
-        <v>12.8821439743042</v>
+        <v>12.8821449279785</v>
       </c>
       <c r="H664" t="n">
         <v>11286</v>
@@ -19654,7 +19654,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G665" t="n">
-        <v>12.6418056488037</v>
+        <v>12.641806602478</v>
       </c>
       <c r="H665" t="n">
         <v>5141</v>
@@ -19683,7 +19683,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>12.7860097885132</v>
+        <v>12.7860078811646</v>
       </c>
       <c r="H666" t="n">
         <v>8354</v>
@@ -19712,7 +19712,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>12.7860097885132</v>
+        <v>12.7860078811646</v>
       </c>
       <c r="H667" t="n">
         <v>10497</v>
@@ -19770,7 +19770,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>12.7860097885132</v>
+        <v>12.7860078811646</v>
       </c>
       <c r="H669" t="n">
         <v>5925</v>
@@ -19944,7 +19944,7 @@
         <v>14.5</v>
       </c>
       <c r="G675" t="n">
-        <v>13.9396352767944</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H675" t="n">
         <v>5327</v>
@@ -19973,7 +19973,7 @@
         <v>14.5</v>
       </c>
       <c r="G676" t="n">
-        <v>13.9396352767944</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H676" t="n">
         <v>16748</v>
@@ -20002,7 +20002,7 @@
         <v>14.5</v>
       </c>
       <c r="G677" t="n">
-        <v>13.9396352767944</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H677" t="n">
         <v>8967</v>
@@ -20031,7 +20031,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H678" t="n">
         <v>14525</v>
@@ -20060,7 +20060,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>13.7954320907593</v>
+        <v>13.795431137085</v>
       </c>
       <c r="H679" t="n">
         <v>3476</v>
@@ -20118,7 +20118,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>13.6512279510498</v>
+        <v>13.6512269973755</v>
       </c>
       <c r="H681" t="n">
         <v>21605</v>
@@ -20147,7 +20147,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H682" t="n">
         <v>8370</v>
@@ -20205,7 +20205,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>14.1319046020508</v>
+        <v>14.1319055557251</v>
       </c>
       <c r="H684" t="n">
         <v>13280</v>
@@ -20234,7 +20234,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G685" t="n">
-        <v>14.1319046020508</v>
+        <v>14.1319055557251</v>
       </c>
       <c r="H685" t="n">
         <v>10052</v>
@@ -20321,7 +20321,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>13.7954320907593</v>
+        <v>13.795431137085</v>
       </c>
       <c r="H688" t="n">
         <v>6328</v>
@@ -20350,7 +20350,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G689" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H689" t="n">
         <v>13501</v>
@@ -20379,7 +20379,7 @@
         <v>14.5</v>
       </c>
       <c r="G690" t="n">
-        <v>13.9396352767944</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H690" t="n">
         <v>26199</v>
@@ -20408,7 +20408,7 @@
         <v>14.5</v>
       </c>
       <c r="G691" t="n">
-        <v>13.9396352767944</v>
+        <v>13.9396343231201</v>
       </c>
       <c r="H691" t="n">
         <v>5887</v>
@@ -20437,7 +20437,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H692" t="n">
         <v>7855</v>
@@ -20466,7 +20466,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G693" t="n">
-        <v>13.8915662765503</v>
+        <v>13.891565322876</v>
       </c>
       <c r="H693" t="n">
         <v>3250</v>
@@ -20553,7 +20553,7 @@
         <v>14</v>
       </c>
       <c r="G696" t="n">
-        <v>13.4589557647705</v>
+        <v>13.4589567184448</v>
       </c>
       <c r="H696" t="n">
         <v>8970</v>
@@ -20582,7 +20582,7 @@
         <v>14</v>
       </c>
       <c r="G697" t="n">
-        <v>13.4589557647705</v>
+        <v>13.4589567184448</v>
       </c>
       <c r="H697" t="n">
         <v>3209</v>
@@ -20611,7 +20611,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G698" t="n">
-        <v>13.5550928115845</v>
+        <v>13.5550937652588</v>
       </c>
       <c r="H698" t="n">
         <v>6847</v>
@@ -20640,7 +20640,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>13.60315990448</v>
+        <v>13.6031589508057</v>
       </c>
       <c r="H699" t="n">
         <v>8458</v>
@@ -20669,7 +20669,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>13.7473621368408</v>
+        <v>13.7473630905151</v>
       </c>
       <c r="H700" t="n">
         <v>2077</v>
@@ -20698,7 +20698,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G701" t="n">
-        <v>13.7473621368408</v>
+        <v>13.7473630905151</v>
       </c>
       <c r="H701" t="n">
         <v>6476</v>
@@ -20843,7 +20843,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G706" t="n">
-        <v>14.3631267547607</v>
+        <v>14.3631258010864</v>
       </c>
       <c r="H706" t="n">
         <v>8472</v>
@@ -21075,7 +21075,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G714" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910652160645</v>
       </c>
       <c r="H714" t="n">
         <v>15736</v>
@@ -21104,7 +21104,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G715" t="n">
-        <v>16.5802555084229</v>
+        <v>16.5802536010742</v>
       </c>
       <c r="H715" t="n">
         <v>22030</v>
@@ -21133,7 +21133,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G716" t="n">
-        <v>16.9176406860352</v>
+        <v>16.9176425933838</v>
       </c>
       <c r="H716" t="n">
         <v>15375</v>
@@ -21220,7 +21220,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G719" t="n">
-        <v>16.9176406860352</v>
+        <v>16.9176425933838</v>
       </c>
       <c r="H719" t="n">
         <v>10063</v>
@@ -21249,7 +21249,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G720" t="n">
-        <v>16.7248477935791</v>
+        <v>16.7248497009277</v>
       </c>
       <c r="H720" t="n">
         <v>9012</v>
@@ -21307,7 +21307,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G722" t="n">
-        <v>16.339262008667</v>
+        <v>16.3392639160156</v>
       </c>
       <c r="H722" t="n">
         <v>16164</v>
@@ -21336,7 +21336,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>16.4838581085205</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H723" t="n">
         <v>4063</v>
@@ -21365,7 +21365,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>16.339262008667</v>
+        <v>16.3392639160156</v>
       </c>
       <c r="H724" t="n">
         <v>3987</v>
@@ -21394,7 +21394,7 @@
         <v>17</v>
       </c>
       <c r="G725" t="n">
-        <v>16.3874607086182</v>
+        <v>16.3874626159668</v>
       </c>
       <c r="H725" t="n">
         <v>4851</v>
@@ -21423,7 +21423,7 @@
         <v>16.5</v>
       </c>
       <c r="G726" t="n">
-        <v>15.9054746627808</v>
+        <v>15.9054765701294</v>
       </c>
       <c r="H726" t="n">
         <v>13151</v>
@@ -21481,7 +21481,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910652160645</v>
       </c>
       <c r="H728" t="n">
         <v>9170</v>
@@ -21510,7 +21510,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>16.339262008667</v>
+        <v>16.3392639160156</v>
       </c>
       <c r="H729" t="n">
         <v>5390</v>
@@ -21539,7 +21539,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G730" t="n">
-        <v>16.5802555084229</v>
+        <v>16.5802536010742</v>
       </c>
       <c r="H730" t="n">
         <v>5817</v>
@@ -21568,7 +21568,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>16.4838581085205</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H731" t="n">
         <v>7493</v>
@@ -21597,7 +21597,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>16.4838581085205</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H732" t="n">
         <v>8992</v>
@@ -21626,7 +21626,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G733" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910652160645</v>
       </c>
       <c r="H733" t="n">
         <v>5388</v>
@@ -21655,7 +21655,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G734" t="n">
-        <v>16.1946659088135</v>
+        <v>16.1946678161621</v>
       </c>
       <c r="H734" t="n">
         <v>4299</v>
@@ -21684,7 +21684,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G735" t="n">
-        <v>16.0982685089111</v>
+        <v>16.0982704162598</v>
       </c>
       <c r="H735" t="n">
         <v>2046</v>
@@ -21713,7 +21713,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G736" t="n">
-        <v>16.1946659088135</v>
+        <v>16.1946678161621</v>
       </c>
       <c r="H736" t="n">
         <v>11338</v>
@@ -21742,7 +21742,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>16.2428665161133</v>
+        <v>16.2428646087646</v>
       </c>
       <c r="H737" t="n">
         <v>1646</v>
@@ -21771,7 +21771,7 @@
         <v>16.75</v>
       </c>
       <c r="G738" t="n">
-        <v>16.1464691162109</v>
+        <v>16.1464672088623</v>
       </c>
       <c r="H738" t="n">
         <v>22483</v>
@@ -21800,7 +21800,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G739" t="n">
-        <v>16.0982685089111</v>
+        <v>16.0982704162598</v>
       </c>
       <c r="H739" t="n">
         <v>6854</v>
@@ -21887,7 +21887,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>15.5198879241943</v>
+        <v>15.5198888778687</v>
       </c>
       <c r="H742" t="n">
         <v>9416</v>
@@ -22148,7 +22148,7 @@
         <v>15.75</v>
       </c>
       <c r="G751" t="n">
-        <v>15.1825008392334</v>
+        <v>15.1824989318848</v>
       </c>
       <c r="H751" t="n">
         <v>1284</v>
@@ -22206,7 +22206,7 @@
         <v>15.75</v>
       </c>
       <c r="G753" t="n">
-        <v>15.1825008392334</v>
+        <v>15.1824989318848</v>
       </c>
       <c r="H753" t="n">
         <v>5094</v>
@@ -22322,7 +22322,7 @@
         <v>16.25</v>
       </c>
       <c r="G757" t="n">
-        <v>15.6644840240479</v>
+        <v>15.6644849777222</v>
       </c>
       <c r="H757" t="n">
         <v>2755</v>
@@ -22467,7 +22467,7 @@
         <v>16.25</v>
       </c>
       <c r="G762" t="n">
-        <v>15.6644840240479</v>
+        <v>15.6644849777222</v>
       </c>
       <c r="H762" t="n">
         <v>3876</v>
@@ -22496,7 +22496,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>15.5198879241943</v>
+        <v>15.5198888778687</v>
       </c>
       <c r="H763" t="n">
         <v>4072</v>
@@ -22699,7 +22699,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G770" t="n">
-        <v>16.2910633087158</v>
+        <v>16.2910652160645</v>
       </c>
       <c r="H770" t="n">
         <v>23740</v>
@@ -22728,7 +22728,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G771" t="n">
-        <v>17.0622406005859</v>
+        <v>17.0622386932373</v>
       </c>
       <c r="H771" t="n">
         <v>21378</v>
@@ -22757,7 +22757,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G772" t="n">
-        <v>17.447826385498</v>
+        <v>17.4478244781494</v>
       </c>
       <c r="H772" t="n">
         <v>13430</v>
@@ -22786,7 +22786,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G773" t="n">
-        <v>17.447826385498</v>
+        <v>17.4478244781494</v>
       </c>
       <c r="H773" t="n">
         <v>11725</v>
@@ -22815,7 +22815,7 @@
         <v>18</v>
       </c>
       <c r="G774" t="n">
-        <v>17.3514289855957</v>
+        <v>17.3514270782471</v>
       </c>
       <c r="H774" t="n">
         <v>18784</v>
@@ -22844,7 +22844,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G775" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032283782959</v>
       </c>
       <c r="H775" t="n">
         <v>12401</v>
@@ -22873,7 +22873,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>16.7248477935791</v>
+        <v>16.7248497009277</v>
       </c>
       <c r="H776" t="n">
         <v>31211</v>
@@ -22902,7 +22902,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G777" t="n">
-        <v>17.158634185791</v>
+        <v>17.1586360931396</v>
       </c>
       <c r="H777" t="n">
         <v>3670</v>
@@ -23105,7 +23105,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G784" t="n">
-        <v>16.5320568084717</v>
+        <v>16.532054901123</v>
       </c>
       <c r="H784" t="n">
         <v>2334</v>
@@ -23134,7 +23134,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G785" t="n">
-        <v>16.4838581085205</v>
+        <v>16.4838562011719</v>
       </c>
       <c r="H785" t="n">
         <v>3050</v>
@@ -23192,7 +23192,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>16.9176406860352</v>
+        <v>16.9176425933838</v>
       </c>
       <c r="H787" t="n">
         <v>5321</v>
@@ -23279,7 +23279,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G790" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032283782959</v>
       </c>
       <c r="H790" t="n">
         <v>7506</v>
@@ -23337,7 +23337,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G792" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032283782959</v>
       </c>
       <c r="H792" t="n">
         <v>4523</v>
@@ -23366,7 +23366,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G793" t="n">
-        <v>17.158634185791</v>
+        <v>17.1586360931396</v>
       </c>
       <c r="H793" t="n">
         <v>1275</v>
@@ -23395,7 +23395,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032283782959</v>
       </c>
       <c r="H794" t="n">
         <v>2784</v>
@@ -23424,7 +23424,7 @@
         <v>17.75</v>
       </c>
       <c r="G795" t="n">
-        <v>17.1104354858398</v>
+        <v>17.1104373931885</v>
       </c>
       <c r="H795" t="n">
         <v>2578</v>
@@ -23482,7 +23482,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>17.0622406005859</v>
+        <v>17.0622386932373</v>
       </c>
       <c r="H797" t="n">
         <v>4120</v>
@@ -23569,7 +23569,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>17.3032302856445</v>
+        <v>17.3032283782959</v>
       </c>
       <c r="H800" t="n">
         <v>6644</v>
@@ -23627,7 +23627,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G802" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H802" t="n">
         <v>18762</v>
@@ -23714,7 +23714,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>19.2311687469482</v>
+        <v>19.2311668395996</v>
       </c>
       <c r="H805" t="n">
         <v>23355</v>
@@ -23743,7 +23743,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G806" t="n">
-        <v>18.6527862548828</v>
+        <v>18.6527881622314</v>
       </c>
       <c r="H806" t="n">
         <v>27880</v>
@@ -23772,7 +23772,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G807" t="n">
-        <v>18.7491817474365</v>
+        <v>18.7491836547852</v>
       </c>
       <c r="H807" t="n">
         <v>9901</v>
@@ -23830,7 +23830,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G809" t="n">
-        <v>18.5081920623779</v>
+        <v>18.5081901550293</v>
       </c>
       <c r="H809" t="n">
         <v>5340</v>
@@ -23859,7 +23859,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G810" t="n">
-        <v>18.3635921478271</v>
+        <v>18.3635940551758</v>
       </c>
       <c r="H810" t="n">
         <v>8073</v>
@@ -23888,7 +23888,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G811" t="n">
-        <v>18.4117946624756</v>
+        <v>18.411792755127</v>
       </c>
       <c r="H811" t="n">
         <v>4783</v>
@@ -23917,7 +23917,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H812" t="n">
         <v>21969</v>
@@ -23975,7 +23975,7 @@
         <v>19</v>
       </c>
       <c r="G814" t="n">
-        <v>18.3153972625732</v>
+        <v>18.3153991699219</v>
       </c>
       <c r="H814" t="n">
         <v>4369</v>
@@ -24004,7 +24004,7 @@
         <v>19</v>
       </c>
       <c r="G815" t="n">
-        <v>18.3153972625732</v>
+        <v>18.3153991699219</v>
       </c>
       <c r="H815" t="n">
         <v>3021</v>
@@ -24033,7 +24033,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1707992553711</v>
       </c>
       <c r="H816" t="n">
         <v>2568</v>
@@ -24120,7 +24120,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G819" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1707992553711</v>
       </c>
       <c r="H819" t="n">
         <v>5941</v>
@@ -24207,7 +24207,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
       </c>
       <c r="H822" t="n">
         <v>2366</v>
@@ -24265,7 +24265,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1707992553711</v>
       </c>
       <c r="H824" t="n">
         <v>10467</v>
@@ -24294,7 +24294,7 @@
         <v>18.75</v>
       </c>
       <c r="G825" t="n">
-        <v>18.074405670166</v>
+        <v>18.0744037628174</v>
       </c>
       <c r="H825" t="n">
         <v>9281</v>
@@ -24323,7 +24323,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G826" t="n">
-        <v>17.447826385498</v>
+        <v>17.4478244781494</v>
       </c>
       <c r="H826" t="n">
         <v>34597</v>
@@ -24439,7 +24439,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G830" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1707992553711</v>
       </c>
       <c r="H830" t="n">
         <v>1749</v>
@@ -24468,7 +24468,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G831" t="n">
-        <v>17.8816108703613</v>
+        <v>17.88161277771</v>
       </c>
       <c r="H831" t="n">
         <v>4940</v>
@@ -24497,7 +24497,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>18.1708030700684</v>
+        <v>18.1707992553711</v>
       </c>
       <c r="H832" t="n">
         <v>1475</v>
@@ -24555,7 +24555,7 @@
         <v>19</v>
       </c>
       <c r="G834" t="n">
-        <v>18.3153972625732</v>
+        <v>18.3153991699219</v>
       </c>
       <c r="H834" t="n">
         <v>14459</v>
@@ -24613,7 +24613,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G836" t="n">
-        <v>17.447826385498</v>
+        <v>17.4478244781494</v>
       </c>
       <c r="H836" t="n">
         <v>3775</v>
@@ -24642,7 +24642,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>17.6406154632568</v>
+        <v>17.6406173706055</v>
       </c>
       <c r="H837" t="n">
         <v>40035</v>
@@ -24671,7 +24671,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G838" t="n">
-        <v>18.0262088775635</v>
+        <v>18.0262069702148</v>
 